--- a/data/HER.MI.xlsx
+++ b/data/HER.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1868" uniqueCount="1868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1869" uniqueCount="1869">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,46 +38,46 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70756649971008</t>
+    <t xml:space="preserve">1.70756661891937</t>
   </si>
   <si>
     <t xml:space="preserve">HER.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70896363258362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70616924762726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71036112308502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68800354003906</t>
+    <t xml:space="preserve">1.70896375179291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70616888999939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71036100387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68800342082977</t>
   </si>
   <si>
     <t xml:space="preserve">1.72573220729828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79140746593475</t>
+    <t xml:space="preserve">1.79140758514404</t>
   </si>
   <si>
     <t xml:space="preserve">1.79420220851898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77044713497162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74669218063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70337426662445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77324223518372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74948716163635</t>
+    <t xml:space="preserve">1.77044725418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74669229984283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70337414741516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77324199676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74948704242706</t>
   </si>
   <si>
     <t xml:space="preserve">1.76625514030457</t>
@@ -86,37 +86,37 @@
     <t xml:space="preserve">1.80538141727448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79001045227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80398404598236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83472585678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81655991077423</t>
+    <t xml:space="preserve">1.79001009464264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8039835691452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83472561836243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81655979156494</t>
   </si>
   <si>
     <t xml:space="preserve">1.80258643627167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84869909286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85568559169769</t>
+    <t xml:space="preserve">1.84869885444641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85568571090698</t>
   </si>
   <si>
     <t xml:space="preserve">1.84031510353088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8235467672348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82913637161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72852694988251</t>
+    <t xml:space="preserve">1.82354652881622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82913613319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72852659225464</t>
   </si>
   <si>
     <t xml:space="preserve">1.74110293388367</t>
@@ -128,277 +128,277 @@
     <t xml:space="preserve">1.69918215274811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75507652759552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79559969902039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78302347660065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77603697776794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79839432239532</t>
+    <t xml:space="preserve">1.75507664680481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7955995798111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78302335739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77603685855865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79839420318604</t>
   </si>
   <si>
     <t xml:space="preserve">1.80118918418884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82075202465057</t>
+    <t xml:space="preserve">1.82075226306915</t>
   </si>
   <si>
     <t xml:space="preserve">1.83053338527679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78861308097839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76485788822174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74529492855072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73970568180084</t>
+    <t xml:space="preserve">1.78861260414124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76485776901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74529480934143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73970544338226</t>
   </si>
   <si>
     <t xml:space="preserve">1.72992396354675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74389743804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73271882534027</t>
+    <t xml:space="preserve">1.74389755725861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73271894454956</t>
   </si>
   <si>
     <t xml:space="preserve">1.76346039772034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77883112430573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76066601276398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77463960647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79699695110321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83752048015594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81097030639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85708343982697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84310984611511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76765263080597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78162610530853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78721582889557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77743422985077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78022885322571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80817580223083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80957329273224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79280483722687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78442084789276</t>
+    <t xml:space="preserve">1.77883160114288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76066589355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77463936805725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7969970703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83752036094666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81097042560577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85708355903625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84310972690582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76765251159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78162622451782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7872154712677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7774338722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78022873401642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80817568302155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80957293510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79280459880829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78442108631134</t>
   </si>
   <si>
     <t xml:space="preserve">1.75647366046906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74808990955353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82634139060974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84590446949005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83193099498749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84450733661652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82214939594269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83332824707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82494425773621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81376504898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76206338405609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73132121562958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74250030517578</t>
+    <t xml:space="preserve">1.74808979034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82634162902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84590470790863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8319308757782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84450721740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82214951515198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83332812786102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82494390010834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81376516819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76206350326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73132145404816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7425000667572</t>
   </si>
   <si>
     <t xml:space="preserve">1.71175849437714</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75751066207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77344822883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7401237487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75895941257477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70390141010284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6734744310379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70969676971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73867464065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78069281578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83430171012878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80822169780731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.811119556427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78503930568695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77924394607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72708356380463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76040816307068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74591934680939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77055048942566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76620364189148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76185691356659</t>
+    <t xml:space="preserve">1.75751042366028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77344834804535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74012386798859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75895917415619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70390129089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67347431182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70969665050507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7386748790741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78069257736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83430182933807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8082218170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81111967563629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78503918647766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77924370765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72708380222321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76040804386139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7459192276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77055060863495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7662034034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76185715198517</t>
   </si>
   <si>
     <t xml:space="preserve">1.76910150051117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77489709854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78359043598175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83719968795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85748386383057</t>
+    <t xml:space="preserve">1.77489721775055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78359019756317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83719956874847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85748410224915</t>
   </si>
   <si>
     <t xml:space="preserve">1.85023975372314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83575069904327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86617767810822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83140420913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84444391727448</t>
+    <t xml:space="preserve">1.83575057983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8661777973175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83140408992767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84444415569305</t>
   </si>
   <si>
     <t xml:space="preserve">1.79663062095642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81981301307678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81256854534149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7488169670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74447023868561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77634596824646</t>
+    <t xml:space="preserve">1.8198127746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81256866455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74881708621979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7444703578949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77634608745575</t>
   </si>
   <si>
     <t xml:space="preserve">1.79083490371704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7995285987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78648805618286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78938615322113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81546604633331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75606143474579</t>
+    <t xml:space="preserve">1.79952824115753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78648841381073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78938639163971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8154661655426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7560613155365</t>
   </si>
   <si>
     <t xml:space="preserve">1.73577690124512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70679903030396</t>
+    <t xml:space="preserve">1.70679879188538</t>
   </si>
   <si>
     <t xml:space="preserve">1.73722589015961</t>
@@ -410,40 +410,40 @@
     <t xml:space="preserve">1.71114563941956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70824790000916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70245218276978</t>
+    <t xml:space="preserve">1.70824801921844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70245242118835</t>
   </si>
   <si>
     <t xml:space="preserve">1.69230997562408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71694123744965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69665670394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63145661354065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60537660121918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59233629703522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57929635047913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.601029753685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60972309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61406946182251</t>
+    <t xml:space="preserve">1.71694111824036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69665682315826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63145637512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6053763628006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59233593940735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57929623126984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60102951526642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6097229719162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61406970024109</t>
   </si>
   <si>
     <t xml:space="preserve">1.62131416797638</t>
@@ -452,22 +452,22 @@
     <t xml:space="preserve">1.63290524482727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61841642856598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63870120048523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63725209236145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65029227733612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62276303768158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61551880836487</t>
+    <t xml:space="preserve">1.6184161901474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63870096206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63725197315216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65029239654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62276315689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61551856994629</t>
   </si>
   <si>
     <t xml:space="preserve">1.61696743965149</t>
@@ -476,55 +476,55 @@
     <t xml:space="preserve">1.62566089630127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66188311576843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6691278219223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68796348571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59378504753113</t>
+    <t xml:space="preserve">1.66188323497772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66912758350372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68796336650848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59378516674042</t>
   </si>
   <si>
     <t xml:space="preserve">1.56625604629517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56335830688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54307389259338</t>
+    <t xml:space="preserve">1.56335854530334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54307401180267</t>
   </si>
   <si>
     <t xml:space="preserve">1.4604868888855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46338450908661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44599783420563</t>
+    <t xml:space="preserve">1.4633846282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44599795341492</t>
   </si>
   <si>
     <t xml:space="preserve">1.44527328014374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45034468173981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43005979061127</t>
+    <t xml:space="preserve">1.45034456253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43005990982056</t>
   </si>
   <si>
     <t xml:space="preserve">1.42209100723267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39601099491119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3945620059967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40905094146729</t>
+    <t xml:space="preserve">1.3960108757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39456188678741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40905106067657</t>
   </si>
   <si>
     <t xml:space="preserve">1.41267323493958</t>
@@ -533,25 +533,25 @@
     <t xml:space="preserve">1.39818429946899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40180635452271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40542876720428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41629540920258</t>
+    <t xml:space="preserve">1.40180647373199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40542888641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41629564762115</t>
   </si>
   <si>
     <t xml:space="preserve">1.38152194023132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35906422138214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37717521190643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43875336647034</t>
+    <t xml:space="preserve">1.35906410217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37717533111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43875324726105</t>
   </si>
   <si>
     <t xml:space="preserve">1.48077130317688</t>
@@ -560,76 +560,76 @@
     <t xml:space="preserve">1.49236249923706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48511779308319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53293168544769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52713584899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50105595588684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50685155391693</t>
+    <t xml:space="preserve">1.48511791229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5329315662384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52713596820831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50105571746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50685143470764</t>
   </si>
   <si>
     <t xml:space="preserve">1.54886949062347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55756282806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57060265541077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59088742733002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56915378570557</t>
+    <t xml:space="preserve">1.55756270885468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57060277462006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59088730812073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56915402412415</t>
   </si>
   <si>
     <t xml:space="preserve">1.58798956871033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.608274102211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5966831445694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5995808839798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56480705738068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65174090862274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64159870147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65318989753723</t>
+    <t xml:space="preserve">1.60827422142029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59668278694153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59958076477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56480753421783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65174114704132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64159882068634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65318977832794</t>
   </si>
   <si>
     <t xml:space="preserve">1.65463864803314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65898549556732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64014971256256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64304733276367</t>
+    <t xml:space="preserve">1.65898537635803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64014983177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64304721355438</t>
   </si>
   <si>
     <t xml:space="preserve">1.57494950294495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57784724235535</t>
+    <t xml:space="preserve">1.57784736156464</t>
   </si>
   <si>
     <t xml:space="preserve">1.55176711082458</t>
@@ -638,16 +638,16 @@
     <t xml:space="preserve">1.58654081821442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63000762462616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68216788768768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66622960567474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6778210401535</t>
+    <t xml:space="preserve">1.63000750541687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6821676492691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6662300825119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67782115936279</t>
   </si>
   <si>
     <t xml:space="preserve">1.69086110591888</t>
@@ -656,94 +656,94 @@
     <t xml:space="preserve">1.69375920295715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69810605049133</t>
+    <t xml:space="preserve">1.69810569286346</t>
   </si>
   <si>
     <t xml:space="preserve">1.69520771503448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71404337882996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72998154163361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73432791233063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71983909606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72418594360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71549260616302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71839022636414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74157249927521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78214168548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78793728351593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81401705741882</t>
+    <t xml:space="preserve">1.71404361724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72998130321503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7343282699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71983897686005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72418606281281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71549224853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71839034557343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74157226085663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78214144706726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78793716430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81401741504669</t>
   </si>
   <si>
     <t xml:space="preserve">1.82995522022247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86907529830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89950215816498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91399097442627</t>
+    <t xml:space="preserve">1.86907541751862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89950227737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91399121284485</t>
   </si>
   <si>
     <t xml:space="preserve">1.91544020175934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8806666135788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8719733953476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88936007022858</t>
+    <t xml:space="preserve">1.88066625595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87197327613831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88935995101929</t>
   </si>
   <si>
     <t xml:space="preserve">1.90095114707947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90529787540436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91254210472107</t>
+    <t xml:space="preserve">1.90529751777649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91254234313965</t>
   </si>
   <si>
     <t xml:space="preserve">1.94441783428192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93717360496521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87921798229218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88356411457062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92848014831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89805352687836</t>
+    <t xml:space="preserve">1.9371737241745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87921786308289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88356423377991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92847979068756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89805316925049</t>
   </si>
   <si>
     <t xml:space="preserve">1.88791108131409</t>
@@ -758,34 +758,34 @@
     <t xml:space="preserve">1.92413318157196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93572413921356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93862271308899</t>
+    <t xml:space="preserve">1.93572473526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93862223625183</t>
   </si>
   <si>
     <t xml:space="preserve">1.94876444339752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99512934684753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0284538269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05743193626404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06902289390564</t>
+    <t xml:space="preserve">1.99512946605682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02845358848572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05743169784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06902313232422</t>
   </si>
   <si>
     <t xml:space="preserve">2.05163621902466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10234713554382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06467604637146</t>
+    <t xml:space="preserve">2.10234761238098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06467628479004</t>
   </si>
   <si>
     <t xml:space="preserve">2.03859639167786</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">2.07336974143982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0864098072052</t>
+    <t xml:space="preserve">2.08640956878662</t>
   </si>
   <si>
     <t xml:space="preserve">2.12842774391174</t>
@@ -803,10 +803,10 @@
     <t xml:space="preserve">2.11248993873596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11104083061218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10089874267578</t>
+    <t xml:space="preserve">2.11104106903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10089898109436</t>
   </si>
   <si>
     <t xml:space="preserve">2.05453372001648</t>
@@ -818,13 +818,13 @@
     <t xml:space="preserve">2.12263202667236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07916522026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1037962436676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11973404884338</t>
+    <t xml:space="preserve">2.07916498184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10379648208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11973428726196</t>
   </si>
   <si>
     <t xml:space="preserve">2.10814309120178</t>
@@ -833,49 +833,49 @@
     <t xml:space="preserve">2.1472635269165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13277459144592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1545078754425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14291667938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15595698356628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16790914535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17836785316467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17239189147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09918189048767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11262845993042</t>
+    <t xml:space="preserve">2.13277411460876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15450763702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14291644096375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15595674514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1679093837738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17836809158325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17239165306091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09918165206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.112628698349</t>
   </si>
   <si>
     <t xml:space="preserve">2.07228827476501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05884146690369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01700735092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99907851219177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01103115081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00804281234741</t>
+    <t xml:space="preserve">2.05884170532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01700758934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99907839298248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01103091239929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00804257392883</t>
   </si>
   <si>
     <t xml:space="preserve">1.99758422374725</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">1.95126783847809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97069096565247</t>
+    <t xml:space="preserve">1.97069072723389</t>
   </si>
   <si>
     <t xml:space="preserve">2.00505471229553</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">2.03045392036438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05286502838135</t>
+    <t xml:space="preserve">2.05286526679993</t>
   </si>
   <si>
     <t xml:space="preserve">2.0394184589386</t>
@@ -905,22 +905,22 @@
     <t xml:space="preserve">2.03194832801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04539465904236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02447772026062</t>
+    <t xml:space="preserve">2.04539489746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0244779586792</t>
   </si>
   <si>
     <t xml:space="preserve">2.06182980537415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07677054405212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03344178199768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01401925086975</t>
+    <t xml:space="preserve">2.07677030563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03344225883484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01401948928833</t>
   </si>
   <si>
     <t xml:space="preserve">2.05435967445374</t>
@@ -935,16 +935,16 @@
     <t xml:space="preserve">2.0364305973053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0483832359314</t>
+    <t xml:space="preserve">2.04838347434998</t>
   </si>
   <si>
     <t xml:space="preserve">2.04987716674805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00206661224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05585360527039</t>
+    <t xml:space="preserve">2.00206637382507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05585336685181</t>
   </si>
   <si>
     <t xml:space="preserve">2.03493618965149</t>
@@ -953,28 +953,28 @@
     <t xml:space="preserve">1.99459624290466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97517347335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96172666549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9677027463913</t>
+    <t xml:space="preserve">1.97517311573029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96172654628754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96770262718201</t>
   </si>
   <si>
     <t xml:space="preserve">2.02597188949585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01252508163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00953698158264</t>
+    <t xml:space="preserve">2.0125253200531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00953674316406</t>
   </si>
   <si>
     <t xml:space="preserve">2.0035605430603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07826447486877</t>
+    <t xml:space="preserve">2.0782642364502</t>
   </si>
   <si>
     <t xml:space="preserve">2.01850128173828</t>
@@ -986,10 +986,10 @@
     <t xml:space="preserve">1.98563182353973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98712611198425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97218477725983</t>
+    <t xml:space="preserve">1.98712551593781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9721851348877</t>
   </si>
   <si>
     <t xml:space="preserve">2.02148962020874</t>
@@ -998,49 +998,49 @@
     <t xml:space="preserve">2.03792452812195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06033563613892</t>
+    <t xml:space="preserve">2.0603358745575</t>
   </si>
   <si>
     <t xml:space="preserve">2.07079434394836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07378244400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06631207466125</t>
+    <t xml:space="preserve">2.07378268241882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0663115978241</t>
   </si>
   <si>
     <t xml:space="preserve">2.06332397460938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07527637481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08424067497253</t>
+    <t xml:space="preserve">2.07527661323547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08424091339111</t>
   </si>
   <si>
     <t xml:space="preserve">2.10665202140808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12458109855652</t>
+    <t xml:space="preserve">2.1245813369751</t>
   </si>
   <si>
     <t xml:space="preserve">2.14998054504395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16043925285339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18135619163513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19629716873169</t>
+    <t xml:space="preserve">2.16043901443481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18135643005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19629669189453</t>
   </si>
   <si>
     <t xml:space="preserve">2.18733215332031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1798620223999</t>
+    <t xml:space="preserve">2.17986226081848</t>
   </si>
   <si>
     <t xml:space="preserve">2.16641545295715</t>
@@ -1052,13 +1052,13 @@
     <t xml:space="preserve">2.19181489944458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19330859184265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19480276107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22468447685242</t>
+    <t xml:space="preserve">2.19330883026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1948025226593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22468423843384</t>
   </si>
   <si>
     <t xml:space="preserve">2.27100086212158</t>
@@ -1067,13 +1067,13 @@
     <t xml:space="preserve">2.25605988502502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25904846191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28145909309387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2949059009552</t>
+    <t xml:space="preserve">2.25904774665833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28145956993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29490613937378</t>
   </si>
   <si>
     <t xml:space="preserve">2.30536460876465</t>
@@ -1082,49 +1082,49 @@
     <t xml:space="preserve">2.30088233947754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33972859382629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28892970085144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27398872375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30387091636658</t>
+    <t xml:space="preserve">2.33972835540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28892993927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27398896217346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.303870677948</t>
   </si>
   <si>
     <t xml:space="preserve">2.31582307815552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25456595420837</t>
+    <t xml:space="preserve">2.25456571578979</t>
   </si>
   <si>
     <t xml:space="preserve">2.25755405426025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27847146987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22916674613953</t>
+    <t xml:space="preserve">2.27847123146057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22916698455811</t>
   </si>
   <si>
     <t xml:space="preserve">2.22617864608765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2187077999115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17388534545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15446257591248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21123790740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26054215431213</t>
+    <t xml:space="preserve">2.21870827674866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17388582229614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15446281433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21123766899109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26054191589355</t>
   </si>
   <si>
     <t xml:space="preserve">2.31134104728699</t>
@@ -1133,40 +1133,40 @@
     <t xml:space="preserve">2.24111914634705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26950693130493</t>
+    <t xml:space="preserve">2.26950669288635</t>
   </si>
   <si>
     <t xml:space="preserve">2.23813104629517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27697730064392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28594160079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29938840866089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24709534645081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2799654006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24560165405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18434453010559</t>
+    <t xml:space="preserve">2.2769775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28594183921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29938864707947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24709486961365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27996563911438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24560117721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18434429168701</t>
   </si>
   <si>
     <t xml:space="preserve">2.13503956794739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11113452911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05734729766846</t>
+    <t xml:space="preserve">2.11113429069519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05734753608704</t>
   </si>
   <si>
     <t xml:space="preserve">2.02895998954773</t>
@@ -1178,34 +1178,34 @@
     <t xml:space="preserve">2.12607502937317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13354539871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09320545196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06930017471313</t>
+    <t xml:space="preserve">2.13354563713074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09320521354675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06929993629456</t>
   </si>
   <si>
     <t xml:space="preserve">2.04091262817383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08573508262634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08274722099304</t>
+    <t xml:space="preserve">2.08573484420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08274674415588</t>
   </si>
   <si>
     <t xml:space="preserve">2.08125257492065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10216975212097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09768772125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12009906768799</t>
+    <t xml:space="preserve">2.10216999053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09768748283386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12009882926941</t>
   </si>
   <si>
     <t xml:space="preserve">2.21273159980774</t>
@@ -1220,79 +1220,79 @@
     <t xml:space="preserve">2.24261331558228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26353073120117</t>
+    <t xml:space="preserve">2.26353025436401</t>
   </si>
   <si>
     <t xml:space="preserve">2.23514294624329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25307202339172</t>
+    <t xml:space="preserve">2.25307178497314</t>
   </si>
   <si>
     <t xml:space="preserve">2.29341220855713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29789423942566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28444790840149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2276725769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25157737731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14101576805115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12159276008606</t>
+    <t xml:space="preserve">2.29789447784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28444743156433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22767281532288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25157785415649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14101600646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12159299850464</t>
   </si>
   <si>
     <t xml:space="preserve">2.02298378944397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94678592681885</t>
+    <t xml:space="preserve">1.94678568840027</t>
   </si>
   <si>
     <t xml:space="preserve">1.96471464633942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98114955425262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96919667720795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97816109657288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94827973842621</t>
+    <t xml:space="preserve">1.98114919662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96919679641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97816097736359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9482798576355</t>
   </si>
   <si>
     <t xml:space="preserve">2.02856659889221</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06108570098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0719256401062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03785753250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04095482826233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07347393035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05953764915466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08895897865295</t>
+    <t xml:space="preserve">2.06108593940735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07192540168762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0378577709198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04095506668091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07347369194031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05953741073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08895921707153</t>
   </si>
   <si>
     <t xml:space="preserve">2.06727981567383</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">2.15399694442749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16019082069397</t>
+    <t xml:space="preserve">2.16019153594971</t>
   </si>
   <si>
     <t xml:space="preserve">2.14470601081848</t>
@@ -1325,46 +1325,46 @@
     <t xml:space="preserve">2.16793394088745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17257928848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15244889259338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10444450378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09205627441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20664668083191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17103052139282</t>
+    <t xml:space="preserve">2.17257976531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1524486541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1044442653656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09205603599548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20664691925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17103099822998</t>
   </si>
   <si>
     <t xml:space="preserve">2.19580721855164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18651628494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21748638153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21593832969666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18341898918152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16328859329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15090012550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13231778144836</t>
+    <t xml:space="preserve">2.18651604652405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21748685836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21593809127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1834192276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16328811645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1509006023407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13231801986694</t>
   </si>
   <si>
     <t xml:space="preserve">2.12612390518188</t>
@@ -1373,124 +1373,124 @@
     <t xml:space="preserve">2.11992955207825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16638541221619</t>
+    <t xml:space="preserve">2.16638565063477</t>
   </si>
   <si>
     <t xml:space="preserve">2.1570942401886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14935159683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09670186042786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09979891777039</t>
+    <t xml:space="preserve">2.14935183525085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09670209884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09979867935181</t>
   </si>
   <si>
     <t xml:space="preserve">2.0905077457428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10754108428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12457513809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12767243385315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18806505203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20045280456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19735598564148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20200157165527</t>
+    <t xml:space="preserve">2.10754156112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12457537651062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12767195701599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18806457519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20045328140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1973557472229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20200181007385</t>
   </si>
   <si>
     <t xml:space="preserve">2.20819544792175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21129250526428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17567658424377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12147808074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11683297157288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07657074928284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06882834434509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05179476737976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01463007926941</t>
+    <t xml:space="preserve">2.21129274368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1756763458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12147831916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11683249473572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07657098770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06882858276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05179452896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01462984085083</t>
   </si>
   <si>
     <t xml:space="preserve">1.9619802236557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98211109638214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93720424175262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90313637256622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86287426948547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91552436351776</t>
+    <t xml:space="preserve">1.98211085796356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93720400333405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90313625335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86287462711334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91552424430847</t>
   </si>
   <si>
     <t xml:space="preserve">1.87216591835022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89384520053864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90158796310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87061715126038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8597776889801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92791259288788</t>
+    <t xml:space="preserve">1.89384531974792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90158784389496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87061750888824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85977780818939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92791283130646</t>
   </si>
   <si>
     <t xml:space="preserve">1.89694225788116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89074802398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87990856170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88919973373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88765096664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90468466281891</t>
+    <t xml:space="preserve">1.89074814319611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87990844249725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88919949531555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88765072822571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9046847820282</t>
   </si>
   <si>
     <t xml:space="preserve">1.92171859741211</t>
@@ -1499,61 +1499,61 @@
     <t xml:space="preserve">1.96662592887878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91862154006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97901391983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96972274780273</t>
+    <t xml:space="preserve">1.91862165927887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9790141582489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96972286701202</t>
   </si>
   <si>
     <t xml:space="preserve">1.97746539115906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94184947013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93101000785828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92481577396393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92017006874084</t>
+    <t xml:space="preserve">1.94184911251068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93100941181183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92481589317322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92017018795013</t>
   </si>
   <si>
     <t xml:space="preserve">1.89229655265808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90933012962341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87836027145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93875205516815</t>
+    <t xml:space="preserve">1.90933084487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87835991382599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93875253200531</t>
   </si>
   <si>
     <t xml:space="preserve">1.8690687417984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9480437040329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98675644397736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09360480308533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03630971908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06573152542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09825038909912</t>
+    <t xml:space="preserve">1.94804346561432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98675632476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09360456466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03630924224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06573128700256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0982506275177</t>
   </si>
   <si>
     <t xml:space="preserve">2.0827648639679</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">2.19425892829895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17877340316772</t>
+    <t xml:space="preserve">2.1787736415863</t>
   </si>
   <si>
     <t xml:space="preserve">2.2050986289978</t>
@@ -1574,70 +1574,70 @@
     <t xml:space="preserve">2.2097442150116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22987484931946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20354986190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19890451431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22677803039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26084542274475</t>
+    <t xml:space="preserve">2.22987508773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20355010032654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19890427589417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22677779197693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26084518432617</t>
   </si>
   <si>
     <t xml:space="preserve">2.26239371299744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28562188148499</t>
+    <t xml:space="preserve">2.28562164306641</t>
   </si>
   <si>
     <t xml:space="preserve">2.29336428642273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28252458572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28407311439514</t>
+    <t xml:space="preserve">2.28252482414246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2840735912323</t>
   </si>
   <si>
     <t xml:space="preserve">2.2902672290802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27013659477234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25619983673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28097653388977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3026556968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30110669136047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30730128288269</t>
+    <t xml:space="preserve">2.27013635635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25620007514954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28097629547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30265545845032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30110692977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30730104446411</t>
   </si>
   <si>
     <t xml:space="preserve">2.29800987243652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28871870040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25929689407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32433485984802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29181623458862</t>
+    <t xml:space="preserve">2.28871893882751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25929665565491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3243350982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29181599617004</t>
   </si>
   <si>
     <t xml:space="preserve">2.25465130805969</t>
@@ -1646,13 +1646,13 @@
     <t xml:space="preserve">2.26858806610107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26549077033997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29955840110779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29646182060242</t>
+    <t xml:space="preserve">2.26549124717712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29955887794495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29646158218384</t>
   </si>
   <si>
     <t xml:space="preserve">2.31349515914917</t>
@@ -1667,16 +1667,16 @@
     <t xml:space="preserve">2.23916625976562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34446573257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38008165359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38163018226624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40330958366394</t>
+    <t xml:space="preserve">2.34446597099304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38008189201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38163042068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40330982208252</t>
   </si>
   <si>
     <t xml:space="preserve">2.42808604240417</t>
@@ -1688,34 +1688,34 @@
     <t xml:space="preserve">2.47609043121338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49467277526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49002742767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49622130393982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50860905647278</t>
+    <t xml:space="preserve">2.49467253684998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49002695083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49622106552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50860929489136</t>
   </si>
   <si>
     <t xml:space="preserve">2.54887080192566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52099752426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5024151802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51635193824768</t>
+    <t xml:space="preserve">2.52099776268005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50241541862488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5163516998291</t>
   </si>
   <si>
     <t xml:space="preserve">2.46215343475342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47918725013733</t>
+    <t xml:space="preserve">2.47918701171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.46525073051453</t>
@@ -1724,25 +1724,25 @@
     <t xml:space="preserve">2.43428015708923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44976544380188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45286202430725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46679902076721</t>
+    <t xml:space="preserve">2.4497652053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45286226272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46679925918579</t>
   </si>
   <si>
     <t xml:space="preserve">2.44666838645935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4575080871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47144484519958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45905661582947</t>
+    <t xml:space="preserve">2.45750784873962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47144460678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45905685424805</t>
   </si>
   <si>
     <t xml:space="preserve">2.42653751373291</t>
@@ -1751,19 +1751,19 @@
     <t xml:space="preserve">2.44821667671204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42963457107544</t>
+    <t xml:space="preserve">2.42963433265686</t>
   </si>
   <si>
     <t xml:space="preserve">2.48692989349365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53028845787048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53803110122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54112863540649</t>
+    <t xml:space="preserve">2.53028869628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53803133964539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54112815856934</t>
   </si>
   <si>
     <t xml:space="preserve">2.54422521591187</t>
@@ -1781,25 +1781,25 @@
     <t xml:space="preserve">2.53493404388428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52874040603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51790070533752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56435608863831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59068083763123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60306906700134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60461807250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59997224807739</t>
+    <t xml:space="preserve">2.52873992919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51790022850037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56435656547546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5906810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60306930541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60461783409119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59997200965881</t>
   </si>
   <si>
     <t xml:space="preserve">2.60152053833008</t>
@@ -1814,85 +1814,85 @@
     <t xml:space="preserve">2.64642786979675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65262198448181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68514108657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71611166000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69698405265808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67945027351379</t>
+    <t xml:space="preserve">2.65262222290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68514084815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71611142158508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6969838142395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67945051193237</t>
   </si>
   <si>
     <t xml:space="preserve">2.68263840675354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65075898170471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68104457855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66669869422913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7304573059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81174945831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80856156349182</t>
+    <t xml:space="preserve">2.65075922012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68104434013367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66669893264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73045754432678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81174921989441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80856132507324</t>
   </si>
   <si>
     <t xml:space="preserve">2.7846519947052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77349400520325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78305816650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79740333557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79580950737</t>
+    <t xml:space="preserve">2.77349424362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78305768966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79740357398987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79580974578857</t>
   </si>
   <si>
     <t xml:space="preserve">2.82768893241882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80696749687195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75914835929871</t>
+    <t xml:space="preserve">2.80696725845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75914859771729</t>
   </si>
   <si>
     <t xml:space="preserve">2.74480271339417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74958467483521</t>
+    <t xml:space="preserve">2.74958491325378</t>
   </si>
   <si>
     <t xml:space="preserve">2.7320511341095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72886347770691</t>
+    <t xml:space="preserve">2.72886323928833</t>
   </si>
   <si>
     <t xml:space="preserve">2.73364520072937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66988682746887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68582630157471</t>
+    <t xml:space="preserve">2.66988635063171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68582606315613</t>
   </si>
   <si>
     <t xml:space="preserve">2.73683309555054</t>
@@ -1901,13 +1901,13 @@
     <t xml:space="preserve">2.71132969856262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69538998603821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70654797554016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72726941108704</t>
+    <t xml:space="preserve">2.69539022445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70654773712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72726893424988</t>
   </si>
   <si>
     <t xml:space="preserve">2.70495367050171</t>
@@ -1916,16 +1916,16 @@
     <t xml:space="preserve">2.73523902893066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68742036819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76233673095703</t>
+    <t xml:space="preserve">2.687420129776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76233649253845</t>
   </si>
   <si>
     <t xml:space="preserve">2.78783988952637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77827596664429</t>
+    <t xml:space="preserve">2.77827620506287</t>
   </si>
   <si>
     <t xml:space="preserve">2.78624606132507</t>
@@ -1943,25 +1943,25 @@
     <t xml:space="preserve">2.91535687446594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89144730567932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88666534423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88825941085815</t>
+    <t xml:space="preserve">2.89144706726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88666582107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88825964927673</t>
   </si>
   <si>
     <t xml:space="preserve">2.91695094108582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89622950553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80059170722961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79262161254883</t>
+    <t xml:space="preserve">2.89622926712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80059146881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79262185096741</t>
   </si>
   <si>
     <t xml:space="preserve">2.84522223472595</t>
@@ -1970,13 +1970,13 @@
     <t xml:space="preserve">2.81812500953674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82131314277649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84681630134583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90738701820374</t>
+    <t xml:space="preserve">2.82131290435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8468165397644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90738677978516</t>
   </si>
   <si>
     <t xml:space="preserve">2.90419912338257</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">2.95042395591736</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02055811882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96476984024048</t>
+    <t xml:space="preserve">3.02055835723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9647696018219</t>
   </si>
   <si>
     <t xml:space="preserve">3.00143074989319</t>
@@ -2003,40 +2003,40 @@
     <t xml:space="preserve">2.95679998397827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97114539146423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01577639579773</t>
+    <t xml:space="preserve">2.97114562988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01577591896057</t>
   </si>
   <si>
     <t xml:space="preserve">3.02215242385864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00461888313293</t>
+    <t xml:space="preserve">3.00461864471436</t>
   </si>
   <si>
     <t xml:space="preserve">2.97911524772644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00302457809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01418256759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98389673233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02374625205994</t>
+    <t xml:space="preserve">3.00302481651306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01418280601501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98389744758606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02374649047852</t>
   </si>
   <si>
     <t xml:space="preserve">2.99664902687073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96636343002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99346113204956</t>
+    <t xml:space="preserve">2.96636366844177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99346089363098</t>
   </si>
   <si>
     <t xml:space="preserve">3.00621271133423</t>
@@ -2045,22 +2045,22 @@
     <t xml:space="preserve">3.04606175422668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05881381034851</t>
+    <t xml:space="preserve">3.05881357192993</t>
   </si>
   <si>
     <t xml:space="preserve">3.04924964904785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06997132301331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03012204170227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05403161048889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06678295135498</t>
+    <t xml:space="preserve">3.06997108459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03012228012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05403137207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06678318977356</t>
   </si>
   <si>
     <t xml:space="preserve">3.05243754386902</t>
@@ -2075,13 +2075,13 @@
     <t xml:space="preserve">3.10025644302368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17357850074768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1974880695343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19429993629456</t>
+    <t xml:space="preserve">3.17357873916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19748830795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19430017471313</t>
   </si>
   <si>
     <t xml:space="preserve">3.21820974349976</t>
@@ -2090,40 +2090,40 @@
     <t xml:space="preserve">3.19589447975159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16242074966431</t>
+    <t xml:space="preserve">3.16242098808289</t>
   </si>
   <si>
     <t xml:space="preserve">3.17995429039001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15604496002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18473672866821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17517232894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19111275672913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06200122833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08750510215759</t>
+    <t xml:space="preserve">3.15604519844055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18473649024963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17517280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19111204147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0620014667511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08750486373901</t>
   </si>
   <si>
     <t xml:space="preserve">3.1241660118103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10185027122498</t>
+    <t xml:space="preserve">3.10185050964355</t>
   </si>
   <si>
     <t xml:space="preserve">3.09547448158264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07156538963318</t>
+    <t xml:space="preserve">3.0715651512146</t>
   </si>
   <si>
     <t xml:space="preserve">3.10344433784485</t>
@@ -2141,10 +2141,10 @@
     <t xml:space="preserve">3.17198467254639</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16879653930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16401505470276</t>
+    <t xml:space="preserve">3.16879677772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16401481628418</t>
   </si>
   <si>
     <t xml:space="preserve">3.22139739990234</t>
@@ -2153,34 +2153,34 @@
     <t xml:space="preserve">3.16082692146301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16560888290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10822629928589</t>
+    <t xml:space="preserve">3.16560864448547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10822653770447</t>
   </si>
   <si>
     <t xml:space="preserve">3.09706854820251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10663247108459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08112859725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07794070243835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14329361915588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18633031845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18314266204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13213562965393</t>
+    <t xml:space="preserve">3.10663223266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08112907409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07794094085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1432933807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18633055686951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18314242362976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13213586807251</t>
   </si>
   <si>
     <t xml:space="preserve">3.27240443229675</t>
@@ -2189,7 +2189,7 @@
     <t xml:space="preserve">3.37760591506958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31384706497192</t>
+    <t xml:space="preserve">3.3138473033905</t>
   </si>
   <si>
     <t xml:space="preserve">3.44774079322815</t>
@@ -2198,37 +2198,37 @@
     <t xml:space="preserve">3.44614577293396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37919950485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26921629905701</t>
+    <t xml:space="preserve">3.37919974327087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26921677589417</t>
   </si>
   <si>
     <t xml:space="preserve">3.27718615531921</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28675031661987</t>
+    <t xml:space="preserve">3.28674983978271</t>
   </si>
   <si>
     <t xml:space="preserve">3.33297514915466</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37282395362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38557577133179</t>
+    <t xml:space="preserve">3.37282419204712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38557600975037</t>
   </si>
   <si>
     <t xml:space="preserve">3.40948510169983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42701888084412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43977046012878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47802495956421</t>
+    <t xml:space="preserve">3.42701864242554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43977069854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47802519798279</t>
   </si>
   <si>
     <t xml:space="preserve">3.45252180099487</t>
@@ -2240,16 +2240,16 @@
     <t xml:space="preserve">3.47005581855774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55612993240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5370020866394</t>
+    <t xml:space="preserve">3.55612969398499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53700256347656</t>
   </si>
   <si>
     <t xml:space="preserve">3.51628065109253</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33935070037842</t>
+    <t xml:space="preserve">3.339350938797</t>
   </si>
   <si>
     <t xml:space="preserve">3.30906510353088</t>
@@ -2258,25 +2258,25 @@
     <t xml:space="preserve">3.33775687217712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27878022193909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09069299697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11300826072693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26124668121338</t>
+    <t xml:space="preserve">3.27877998352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09069275856018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11300802230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2612464427948</t>
   </si>
   <si>
     <t xml:space="preserve">2.83247089385986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65872883796692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69060802459717</t>
+    <t xml:space="preserve">2.65872859954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69060826301575</t>
   </si>
   <si>
     <t xml:space="preserve">2.2203893661499</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">2.46585941314697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51049041748047</t>
+    <t xml:space="preserve">2.51049017906189</t>
   </si>
   <si>
     <t xml:space="preserve">2.5168662071228</t>
@@ -2297,7 +2297,7 @@
     <t xml:space="preserve">2.46107769012451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58381295204163</t>
+    <t xml:space="preserve">2.58381271362305</t>
   </si>
   <si>
     <t xml:space="preserve">2.44195008277893</t>
@@ -2315,19 +2315,19 @@
     <t xml:space="preserve">2.62206792831421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60453391075134</t>
+    <t xml:space="preserve">2.6045343875885</t>
   </si>
   <si>
     <t xml:space="preserve">2.52802395820618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56468486785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53121209144592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5519335269928</t>
+    <t xml:space="preserve">2.56468510627747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5312123298645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55193305015564</t>
   </si>
   <si>
     <t xml:space="preserve">2.45948362350464</t>
@@ -2339,13 +2339,13 @@
     <t xml:space="preserve">2.56787300109863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54715156555176</t>
+    <t xml:space="preserve">2.54715180397034</t>
   </si>
   <si>
     <t xml:space="preserve">2.54396367073059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60772204399109</t>
+    <t xml:space="preserve">2.60772180557251</t>
   </si>
   <si>
     <t xml:space="preserve">2.62047386169434</t>
@@ -2354,37 +2354,37 @@
     <t xml:space="preserve">2.51846027374268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59018874168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58062481880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67307448387146</t>
+    <t xml:space="preserve">2.5901882648468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5806245803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67307472229004</t>
   </si>
   <si>
     <t xml:space="preserve">2.69220209121704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57903099060059</t>
+    <t xml:space="preserve">2.57903051376343</t>
   </si>
   <si>
     <t xml:space="preserve">2.57265472412109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52483582496643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49295663833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59178280830383</t>
+    <t xml:space="preserve">2.52483606338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49295687675476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59178233146667</t>
   </si>
   <si>
     <t xml:space="preserve">2.61887955665588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5614972114563</t>
+    <t xml:space="preserve">2.56149697303772</t>
   </si>
   <si>
     <t xml:space="preserve">2.47542333602905</t>
@@ -2393,10 +2393,10 @@
     <t xml:space="preserve">2.46267151832581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51367831230164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50092673301697</t>
+    <t xml:space="preserve">2.51367855072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50092649459839</t>
   </si>
   <si>
     <t xml:space="preserve">2.55352735519409</t>
@@ -2408,25 +2408,25 @@
     <t xml:space="preserve">2.65713500976562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66032266616821</t>
+    <t xml:space="preserve">2.66032314300537</t>
   </si>
   <si>
     <t xml:space="preserve">2.85159826278687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85638046264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81653118133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77668213844299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67785620689392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80218577384949</t>
+    <t xml:space="preserve">2.85638022422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81653094291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77668237686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6778564453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80218553543091</t>
   </si>
   <si>
     <t xml:space="preserve">2.78943371772766</t>
@@ -2435,10 +2435,10 @@
     <t xml:space="preserve">2.77030634880066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75755429267883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75436687469482</t>
+    <t xml:space="preserve">2.75755476951599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75436639785767</t>
   </si>
   <si>
     <t xml:space="preserve">2.68901419639587</t>
@@ -2447,16 +2447,16 @@
     <t xml:space="preserve">2.63800740242004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70335960388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70017218589783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72567534446716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74209499359131</t>
+    <t xml:space="preserve">2.70335984230042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70017194747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72567510604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74209475517273</t>
   </si>
   <si>
     <t xml:space="preserve">2.69940376281738</t>
@@ -2468,34 +2468,34 @@
     <t xml:space="preserve">2.641934633255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63372468948364</t>
+    <t xml:space="preserve">2.63372492790222</t>
   </si>
   <si>
     <t xml:space="preserve">2.6747739315033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63865065574646</t>
+    <t xml:space="preserve">2.63865089416504</t>
   </si>
   <si>
     <t xml:space="preserve">2.65014433860779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69447803497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7306010723114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73388528823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7355272769928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76508283615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66163873672485</t>
+    <t xml:space="preserve">2.69447779655457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73060131072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73388504981995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73552703857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76508259773254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66163849830627</t>
   </si>
   <si>
     <t xml:space="preserve">2.61894726753235</t>
@@ -2516,19 +2516,19 @@
     <t xml:space="preserve">2.61073708534241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6025276184082</t>
+    <t xml:space="preserve">2.60252714157104</t>
   </si>
   <si>
     <t xml:space="preserve">2.59595918655396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58774971961975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66820645332336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72403335571289</t>
+    <t xml:space="preserve">2.58774948120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66820621490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72403359413147</t>
   </si>
   <si>
     <t xml:space="preserve">2.78642821311951</t>
@@ -2543,28 +2543,28 @@
     <t xml:space="preserve">2.66656422615051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70925545692444</t>
+    <t xml:space="preserve">2.70925569534302</t>
   </si>
   <si>
     <t xml:space="preserve">2.68298387527466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66328001022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75030493736267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7223916053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6468608379364</t>
+    <t xml:space="preserve">2.66328024864197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75030469894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72239136695862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64686036109924</t>
   </si>
   <si>
     <t xml:space="preserve">2.62715697288513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6287989616394</t>
+    <t xml:space="preserve">2.62879872322083</t>
   </si>
   <si>
     <t xml:space="preserve">2.61566305160522</t>
@@ -2579,7 +2579,7 @@
     <t xml:space="preserve">2.64850258827209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64029312133789</t>
+    <t xml:space="preserve">2.64029264450073</t>
   </si>
   <si>
     <t xml:space="preserve">2.68134212493896</t>
@@ -2591,40 +2591,40 @@
     <t xml:space="preserve">2.67970013618469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69776177406311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71253943443298</t>
+    <t xml:space="preserve">2.69776153564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7125391960144</t>
   </si>
   <si>
     <t xml:space="preserve">2.63700866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62387323379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60745334625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64521884918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63044095039368</t>
+    <t xml:space="preserve">2.62387275695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60745310783386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64521861076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6304407119751</t>
   </si>
   <si>
     <t xml:space="preserve">2.54998421669006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55819416046143</t>
+    <t xml:space="preserve">2.55819392204285</t>
   </si>
   <si>
     <t xml:space="preserve">2.54505825042725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51386094093323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52042889595032</t>
+    <t xml:space="preserve">2.51386046409607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52042865753174</t>
   </si>
   <si>
     <t xml:space="preserve">2.5023672580719</t>
@@ -2636,13 +2636,13 @@
     <t xml:space="preserve">2.42191028594971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44325590133667</t>
+    <t xml:space="preserve">2.44325613975525</t>
   </si>
   <si>
     <t xml:space="preserve">2.35951542854309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38414454460144</t>
+    <t xml:space="preserve">2.38414478302002</t>
   </si>
   <si>
     <t xml:space="preserve">2.41205835342407</t>
@@ -2654,28 +2654,28 @@
     <t xml:space="preserve">2.39563870429993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37593531608582</t>
+    <t xml:space="preserve">2.37593483924866</t>
   </si>
   <si>
     <t xml:space="preserve">2.37757682800293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31518220901489</t>
+    <t xml:space="preserve">2.31518197059631</t>
   </si>
   <si>
     <t xml:space="preserve">2.29219460487366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2347252368927</t>
+    <t xml:space="preserve">2.23472499847412</t>
   </si>
   <si>
     <t xml:space="preserve">2.19696021080017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21666383743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23636722564697</t>
+    <t xml:space="preserve">2.21666359901428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23636698722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.25442910194397</t>
@@ -2687,19 +2687,19 @@
     <t xml:space="preserve">2.30533027648926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28070068359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.454749584198</t>
+    <t xml:space="preserve">2.28070044517517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45474982261658</t>
   </si>
   <si>
     <t xml:space="preserve">2.42519426345825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44982409477234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49251508712769</t>
+    <t xml:space="preserve">2.44982385635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49251484870911</t>
   </si>
   <si>
     <t xml:space="preserve">2.47937917709351</t>
@@ -2711,13 +2711,13 @@
     <t xml:space="preserve">2.50893497467041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49579906463623</t>
+    <t xml:space="preserve">2.49579930305481</t>
   </si>
   <si>
     <t xml:space="preserve">2.50400900840759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48102116584778</t>
+    <t xml:space="preserve">2.48102140426636</t>
   </si>
   <si>
     <t xml:space="preserve">2.47609543800354</t>
@@ -2726,40 +2726,40 @@
     <t xml:space="preserve">2.52207040786743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53520655632019</t>
+    <t xml:space="preserve">2.53520631790161</t>
   </si>
   <si>
     <t xml:space="preserve">2.51221871376038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4711697101593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43997192382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46788573265076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44489789009094</t>
+    <t xml:space="preserve">2.47116947174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43997168540955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4678852558136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44489765167236</t>
   </si>
   <si>
     <t xml:space="preserve">2.43012022972107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4153425693512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38907098770142</t>
+    <t xml:space="preserve">2.41534233093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38907074928284</t>
   </si>
   <si>
     <t xml:space="preserve">2.36444139480591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39399695396423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36608338356018</t>
+    <t xml:space="preserve">2.39399671554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3660831451416</t>
   </si>
   <si>
     <t xml:space="preserve">2.40384864807129</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">2.33981156349182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38742876052856</t>
+    <t xml:space="preserve">2.38742899894714</t>
   </si>
   <si>
     <t xml:space="preserve">2.45310759544373</t>
@@ -2780,25 +2780,25 @@
     <t xml:space="preserve">2.45967555046082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44654011726379</t>
+    <t xml:space="preserve">2.44653964042664</t>
   </si>
   <si>
     <t xml:space="preserve">2.50565099716187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44161415100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49087309837341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48594737052917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59431767463684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54177451133728</t>
+    <t xml:space="preserve">2.4416139125824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49087285995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4859471321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59431743621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5417742729187</t>
   </si>
   <si>
     <t xml:space="preserve">2.38086104393005</t>
@@ -2810,19 +2810,19 @@
     <t xml:space="preserve">2.35787320137024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36772537231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32996010780334</t>
+    <t xml:space="preserve">2.36772513389587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32995963096619</t>
   </si>
   <si>
     <t xml:space="preserve">2.46952724456787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49415731430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55326819419861</t>
+    <t xml:space="preserve">2.49415707588196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55326795578003</t>
   </si>
   <si>
     <t xml:space="preserve">2.51057696342468</t>
@@ -2831,7 +2831,7 @@
     <t xml:space="preserve">2.52371263504028</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55491018295288</t>
+    <t xml:space="preserve">2.5549099445343</t>
   </si>
   <si>
     <t xml:space="preserve">2.58939146995544</t>
@@ -2843,22 +2843,22 @@
     <t xml:space="preserve">2.53684830665588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52535438537598</t>
+    <t xml:space="preserve">2.52535462379456</t>
   </si>
   <si>
     <t xml:space="preserve">2.43176198005676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40220665931702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5286386013031</t>
+    <t xml:space="preserve">2.4022068977356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52863836288452</t>
   </si>
   <si>
     <t xml:space="preserve">2.56311988830566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56968808174133</t>
+    <t xml:space="preserve">2.56968784332275</t>
   </si>
   <si>
     <t xml:space="preserve">2.6041693687439</t>
@@ -2876,7 +2876,7 @@
     <t xml:space="preserve">2.70843458175659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69611978530884</t>
+    <t xml:space="preserve">2.69611954689026</t>
   </si>
   <si>
     <t xml:space="preserve">2.71171855926514</t>
@@ -2891,13 +2891,13 @@
     <t xml:space="preserve">2.76097774505615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75441026687622</t>
+    <t xml:space="preserve">2.75440979003906</t>
   </si>
   <si>
     <t xml:space="preserve">2.75523090362549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75605201721191</t>
+    <t xml:space="preserve">2.75605177879333</t>
   </si>
   <si>
     <t xml:space="preserve">2.7461998462677</t>
@@ -2909,25 +2909,25 @@
     <t xml:space="preserve">2.76261973381042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76672458648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79710149765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8381507396698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77082991600037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77247166633606</t>
+    <t xml:space="preserve">2.76672434806824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79710125923157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83815050125122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77082943916321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77247142791748</t>
   </si>
   <si>
     <t xml:space="preserve">2.7642617225647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86278009414673</t>
+    <t xml:space="preserve">2.86277985572815</t>
   </si>
   <si>
     <t xml:space="preserve">2.83240365982056</t>
@@ -2936,10 +2936,10 @@
     <t xml:space="preserve">2.82255172729492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86031723022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87837910652161</t>
+    <t xml:space="preserve">2.86031699180603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87837886810303</t>
   </si>
   <si>
     <t xml:space="preserve">2.88330483436584</t>
@@ -2948,13 +2948,13 @@
     <t xml:space="preserve">2.88740944862366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88248348236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86524295806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8611376285553</t>
+    <t xml:space="preserve">2.88248372077942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86524319648743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86113810539246</t>
   </si>
   <si>
     <t xml:space="preserve">2.86606383323669</t>
@@ -2963,31 +2963,31 @@
     <t xml:space="preserve">2.86360120773315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87427401542664</t>
+    <t xml:space="preserve">2.87427377700806</t>
   </si>
   <si>
     <t xml:space="preserve">2.89726161956787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93256378173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95883560180664</t>
+    <t xml:space="preserve">2.93256402015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95883584022522</t>
   </si>
   <si>
     <t xml:space="preserve">2.97197127342224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02533507347107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00481104850769</t>
+    <t xml:space="preserve">3.02533531188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00481081008911</t>
   </si>
   <si>
     <t xml:space="preserve">3.00809478759766</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04093432426453</t>
+    <t xml:space="preserve">3.04093408584595</t>
   </si>
   <si>
     <t xml:space="preserve">3.01794648170471</t>
@@ -3008,13 +3008,13 @@
     <t xml:space="preserve">2.95801424980164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90218758583069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92353343963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8956196308136</t>
+    <t xml:space="preserve">2.90218734741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92353320121765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89561939239502</t>
   </si>
   <si>
     <t xml:space="preserve">2.89069366455078</t>
@@ -3023,7 +3023,7 @@
     <t xml:space="preserve">2.89151477813721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8668851852417</t>
+    <t xml:space="preserve">2.86688494682312</t>
   </si>
   <si>
     <t xml:space="preserve">2.89479851722717</t>
@@ -3041,7 +3041,7 @@
     <t xml:space="preserve">2.86598610877991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86429142951965</t>
+    <t xml:space="preserve">2.86429166793823</t>
   </si>
   <si>
     <t xml:space="preserve">2.93208527565002</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">2.92191600799561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89564633369446</t>
+    <t xml:space="preserve">2.89564609527588</t>
   </si>
   <si>
     <t xml:space="preserve">2.92615342140198</t>
@@ -3080,25 +3080,25 @@
     <t xml:space="preserve">3.03292870521545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06428337097168</t>
+    <t xml:space="preserve">3.0642831325531</t>
   </si>
   <si>
     <t xml:space="preserve">3.04055547714233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04479241371155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02275943756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01004838943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00157380104065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02021718025208</t>
+    <t xml:space="preserve">3.04479217529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02275967597961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01004815101624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00157403945923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02021741867065</t>
   </si>
   <si>
     <t xml:space="preserve">3.04648733139038</t>
@@ -3107,10 +3107,10 @@
     <t xml:space="preserve">3.03547096252441</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08546900749207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09733271598816</t>
+    <t xml:space="preserve">3.08546876907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09733295440674</t>
   </si>
   <si>
     <t xml:space="preserve">3.13122963905334</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">3.14563584327698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15665221214294</t>
+    <t xml:space="preserve">3.15665245056152</t>
   </si>
   <si>
     <t xml:space="preserve">3.18038010597229</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">3.11089158058167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10411238670349</t>
+    <t xml:space="preserve">3.10411214828491</t>
   </si>
   <si>
     <t xml:space="preserve">3.13716149330139</t>
@@ -3161,19 +3161,19 @@
     <t xml:space="preserve">3.11004424095154</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12529802322388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08123159408569</t>
+    <t xml:space="preserve">3.1252977848053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08123183250427</t>
   </si>
   <si>
     <t xml:space="preserve">3.03631830215454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07360529899597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09902787208557</t>
+    <t xml:space="preserve">3.07360506057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09902763366699</t>
   </si>
   <si>
     <t xml:space="preserve">3.04987740516663</t>
@@ -3182,7 +3182,7 @@
     <t xml:space="preserve">3.08377385139465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04140281677246</t>
+    <t xml:space="preserve">3.04140305519104</t>
   </si>
   <si>
     <t xml:space="preserve">3.08631634712219</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">3.01428532600403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99648952484131</t>
+    <t xml:space="preserve">2.99648928642273</t>
   </si>
   <si>
     <t xml:space="preserve">2.99564218521118</t>
@@ -3224,7 +3224,7 @@
     <t xml:space="preserve">2.91089963912964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.877849817276</t>
+    <t xml:space="preserve">2.87785005569458</t>
   </si>
   <si>
     <t xml:space="preserve">2.91174721717834</t>
@@ -3233,13 +3233,13 @@
     <t xml:space="preserve">2.94564414024353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97530388832092</t>
+    <t xml:space="preserve">2.97530364990234</t>
   </si>
   <si>
     <t xml:space="preserve">2.95327067375183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92445826530457</t>
+    <t xml:space="preserve">2.92445850372314</t>
   </si>
   <si>
     <t xml:space="preserve">2.94394898414612</t>
@@ -3254,7 +3254,7 @@
     <t xml:space="preserve">3.04902982711792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01767492294312</t>
+    <t xml:space="preserve">3.01767516136169</t>
   </si>
   <si>
     <t xml:space="preserve">3.05241942405701</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">3.01682758331299</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05750370025635</t>
+    <t xml:space="preserve">3.05750393867493</t>
   </si>
   <si>
     <t xml:space="preserve">3.0693678855896</t>
@@ -3302,7 +3302,7 @@
     <t xml:space="preserve">3.0007266998291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85581707954407</t>
+    <t xml:space="preserve">2.85581684112549</t>
   </si>
   <si>
     <t xml:space="preserve">2.87022352218628</t>
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">2.98208332061768</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00835299491882</t>
+    <t xml:space="preserve">3.0083532333374</t>
   </si>
   <si>
     <t xml:space="preserve">2.97869348526001</t>
@@ -3332,10 +3332,10 @@
     <t xml:space="preserve">3.00326871871948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02445459365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04564023017883</t>
+    <t xml:space="preserve">3.02445435523987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04563999176025</t>
   </si>
   <si>
     <t xml:space="preserve">3.05072426795959</t>
@@ -3344,25 +3344,25 @@
     <t xml:space="preserve">3.06089353561401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11682343482971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10241723060608</t>
+    <t xml:space="preserve">3.11682367324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10241746902466</t>
   </si>
   <si>
     <t xml:space="preserve">3.14055156707764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11173868179321</t>
+    <t xml:space="preserve">3.11173892021179</t>
   </si>
   <si>
     <t xml:space="preserve">3.08716368675232</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02699661254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01343774795532</t>
+    <t xml:space="preserve">3.02699685096741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0134379863739</t>
   </si>
   <si>
     <t xml:space="preserve">2.99394726753235</t>
@@ -3380,25 +3380,25 @@
     <t xml:space="preserve">2.90835738182068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91767907142639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97360897064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07614731788635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14817810058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13377213478088</t>
+    <t xml:space="preserve">2.91767930984497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97360920906067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07614755630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14817786216736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1337718963623</t>
   </si>
   <si>
     <t xml:space="preserve">3.07021522521973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9388644695282</t>
+    <t xml:space="preserve">2.93886470794678</t>
   </si>
   <si>
     <t xml:space="preserve">2.88039255142212</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">2.91852641105652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93801689147949</t>
+    <t xml:space="preserve">2.93801712989807</t>
   </si>
   <si>
     <t xml:space="preserve">2.92530608177185</t>
@@ -3437,7 +3437,7 @@
     <t xml:space="preserve">2.82446241378784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.740567445755</t>
+    <t xml:space="preserve">2.74056768417358</t>
   </si>
   <si>
     <t xml:space="preserve">2.93632245063782</t>
@@ -3455,16 +3455,16 @@
     <t xml:space="preserve">2.69904351234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71175527572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77446413040161</t>
+    <t xml:space="preserve">2.71175503730774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77446436882019</t>
   </si>
   <si>
     <t xml:space="preserve">2.87700271606445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86344385147095</t>
+    <t xml:space="preserve">2.86344408988953</t>
   </si>
   <si>
     <t xml:space="preserve">2.85666465759277</t>
@@ -3491,28 +3491,28 @@
     <t xml:space="preserve">2.814293384552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82700490951538</t>
+    <t xml:space="preserve">2.8270046710968</t>
   </si>
   <si>
     <t xml:space="preserve">2.85327506065369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83547902107239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87615561485291</t>
+    <t xml:space="preserve">2.83547878265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87615537643433</t>
   </si>
   <si>
     <t xml:space="preserve">2.90750980377197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00581121444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04733467102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00496387481689</t>
+    <t xml:space="preserve">3.00581097602844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04733490943909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00496363639832</t>
   </si>
   <si>
     <t xml:space="preserve">3.0439453125</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">3.01598024368286</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04818201065063</t>
+    <t xml:space="preserve">3.04818224906921</t>
   </si>
   <si>
     <t xml:space="preserve">2.97276163101196</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">2.98377799987793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9524233341217</t>
+    <t xml:space="preserve">2.95242357254028</t>
   </si>
   <si>
     <t xml:space="preserve">2.98632025718689</t>
@@ -3542,22 +3542,22 @@
     <t xml:space="preserve">3.06343579292297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84141087532043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86513900756836</t>
+    <t xml:space="preserve">2.84141063690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86513876914978</t>
   </si>
   <si>
     <t xml:space="preserve">2.92954301834106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95072865486145</t>
+    <t xml:space="preserve">2.95072841644287</t>
   </si>
   <si>
     <t xml:space="preserve">3.03801321983337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98801517486572</t>
+    <t xml:space="preserve">2.9880154132843</t>
   </si>
   <si>
     <t xml:space="preserve">2.96598219871521</t>
@@ -3575,13 +3575,13 @@
     <t xml:space="preserve">2.86174917221069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83717370033264</t>
+    <t xml:space="preserve">2.83717393875122</t>
   </si>
   <si>
     <t xml:space="preserve">2.83886861801147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7270085811615</t>
+    <t xml:space="preserve">2.72700881958008</t>
   </si>
   <si>
     <t xml:space="preserve">2.53125381469727</t>
@@ -3599,7 +3599,7 @@
     <t xml:space="preserve">2.38888692855835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41769886016846</t>
+    <t xml:space="preserve">2.41769909858704</t>
   </si>
   <si>
     <t xml:space="preserve">2.3823139667511</t>
@@ -3608,13 +3608,13 @@
     <t xml:space="preserve">2.34250545501709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32569742202759</t>
+    <t xml:space="preserve">2.32569718360901</t>
   </si>
   <si>
     <t xml:space="preserve">2.37435221672058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46193075180054</t>
+    <t xml:space="preserve">2.46193051338196</t>
   </si>
   <si>
     <t xml:space="preserve">2.46812319755554</t>
@@ -3629,13 +3629,13 @@
     <t xml:space="preserve">2.44158411026001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4875853061676</t>
+    <t xml:space="preserve">2.48758506774902</t>
   </si>
   <si>
     <t xml:space="preserve">2.48493123054504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41327595710754</t>
+    <t xml:space="preserve">2.41327619552612</t>
   </si>
   <si>
     <t xml:space="preserve">2.45750761032104</t>
@@ -3650,7 +3650,7 @@
     <t xml:space="preserve">2.45927667617798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37523698806763</t>
+    <t xml:space="preserve">2.37523674964905</t>
   </si>
   <si>
     <t xml:space="preserve">2.30446624755859</t>
@@ -3659,10 +3659,10 @@
     <t xml:space="preserve">2.37789058685303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38673710823059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41150689125061</t>
+    <t xml:space="preserve">2.38673686981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41150665283203</t>
   </si>
   <si>
     <t xml:space="preserve">2.38319849967957</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">2.50527763366699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47077703475952</t>
+    <t xml:space="preserve">2.47077679634094</t>
   </si>
   <si>
     <t xml:space="preserve">2.44246888160706</t>
@@ -3710,7 +3710,7 @@
     <t xml:space="preserve">2.47520017623901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44954586029053</t>
+    <t xml:space="preserve">2.44954609870911</t>
   </si>
   <si>
     <t xml:space="preserve">2.43804574012756</t>
@@ -3722,13 +3722,13 @@
     <t xml:space="preserve">2.42300701141357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40442967414856</t>
+    <t xml:space="preserve">2.40442991256714</t>
   </si>
   <si>
     <t xml:space="preserve">2.36904430389404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2965042591095</t>
+    <t xml:space="preserve">2.29650449752808</t>
   </si>
   <si>
     <t xml:space="preserve">2.35312104225159</t>
@@ -3740,19 +3740,19 @@
     <t xml:space="preserve">2.21246457099915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24342679977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18504095077515</t>
+    <t xml:space="preserve">2.24342656135559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18504118919373</t>
   </si>
   <si>
     <t xml:space="preserve">2.07269239425659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12842416763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11603975296021</t>
+    <t xml:space="preserve">2.12842440605164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11603951454163</t>
   </si>
   <si>
     <t xml:space="preserve">2.2009642124176</t>
@@ -3764,10 +3764,10 @@
     <t xml:space="preserve">2.23015713691711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14965581893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14700174331665</t>
+    <t xml:space="preserve">2.14965558052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14700198173523</t>
   </si>
   <si>
     <t xml:space="preserve">2.11957812309265</t>
@@ -3785,19 +3785,19 @@
     <t xml:space="preserve">2.04261517524719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97803699970245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98422944545746</t>
+    <t xml:space="preserve">1.97803711891174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98422956466675</t>
   </si>
   <si>
     <t xml:space="preserve">1.87895834445953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92584383487701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91611278057098</t>
+    <t xml:space="preserve">1.9258439540863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91611289978027</t>
   </si>
   <si>
     <t xml:space="preserve">1.93380546569824</t>
@@ -3812,13 +3812,13 @@
     <t xml:space="preserve">1.90018939971924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84003436565399</t>
+    <t xml:space="preserve">1.84003448486328</t>
   </si>
   <si>
     <t xml:space="preserve">1.82588028907776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87011194229126</t>
+    <t xml:space="preserve">1.87011206150055</t>
   </si>
   <si>
     <t xml:space="preserve">1.80464923381805</t>
@@ -3827,13 +3827,13 @@
     <t xml:space="preserve">1.77280247211456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80022621154785</t>
+    <t xml:space="preserve">1.80022609233856</t>
   </si>
   <si>
     <t xml:space="preserve">1.83030354976654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87807357311249</t>
+    <t xml:space="preserve">1.87807369232178</t>
   </si>
   <si>
     <t xml:space="preserve">1.88249695301056</t>
@@ -3842,10 +3842,10 @@
     <t xml:space="preserve">1.8630348443985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87541949748993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85153472423553</t>
+    <t xml:space="preserve">1.87541961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85153460502625</t>
   </si>
   <si>
     <t xml:space="preserve">1.91257429122925</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">1.99838364124298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01696085929871</t>
+    <t xml:space="preserve">2.01696109771729</t>
   </si>
   <si>
     <t xml:space="preserve">2.12577080726624</t>
@@ -3863,7 +3863,7 @@
     <t xml:space="preserve">2.13373231887817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14434766769409</t>
+    <t xml:space="preserve">2.14434790611267</t>
   </si>
   <si>
     <t xml:space="preserve">2.14257860183716</t>
@@ -3872,10 +3872,10 @@
     <t xml:space="preserve">2.13196301460266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1779637336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19034886360168</t>
+    <t xml:space="preserve">2.17796397209167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19034862518311</t>
   </si>
   <si>
     <t xml:space="preserve">2.23281097412109</t>
@@ -3887,13 +3887,13 @@
     <t xml:space="preserve">2.30800485610962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28058099746704</t>
+    <t xml:space="preserve">2.28058123588562</t>
   </si>
   <si>
     <t xml:space="preserve">2.29915857315063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33454370498657</t>
+    <t xml:space="preserve">2.33454346656799</t>
   </si>
   <si>
     <t xml:space="preserve">2.31773567199707</t>
@@ -3902,37 +3902,37 @@
     <t xml:space="preserve">2.33631300926208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32835125923157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3274667263031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30623555183411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34515929222107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35046744346619</t>
+    <t xml:space="preserve">2.32835149765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32746648788452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30623579025269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34515953063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35046720504761</t>
   </si>
   <si>
     <t xml:space="preserve">2.33188962936401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34338998794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35400557518005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37169814109802</t>
+    <t xml:space="preserve">2.34338974952698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35400581359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3716983795166</t>
   </si>
   <si>
     <t xml:space="preserve">2.37966012954712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37612175941467</t>
+    <t xml:space="preserve">2.37612152099609</t>
   </si>
   <si>
     <t xml:space="preserve">2.43273782730103</t>
@@ -3941,10 +3941,10 @@
     <t xml:space="preserve">2.48050808906555</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50350856781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44600749015808</t>
+    <t xml:space="preserve">2.50350832939148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4460072517395</t>
   </si>
   <si>
     <t xml:space="preserve">2.3106586933136</t>
@@ -3983,7 +3983,7 @@
     <t xml:space="preserve">2.2894275188446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3354287147522</t>
+    <t xml:space="preserve">2.33542847633362</t>
   </si>
   <si>
     <t xml:space="preserve">2.32304334640503</t>
@@ -4001,13 +4001,13 @@
     <t xml:space="preserve">2.42919945716858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40708374977112</t>
+    <t xml:space="preserve">2.40708351135254</t>
   </si>
   <si>
     <t xml:space="preserve">2.34781312942505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38850617408752</t>
+    <t xml:space="preserve">2.3885064125061</t>
   </si>
   <si>
     <t xml:space="preserve">2.41416072845459</t>
@@ -4019,10 +4019,10 @@
     <t xml:space="preserve">2.39646816253662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34692859649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34073615074158</t>
+    <t xml:space="preserve">2.34692883491516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.340735912323</t>
   </si>
   <si>
     <t xml:space="preserve">2.3442747592926</t>
@@ -4043,7 +4043,7 @@
     <t xml:space="preserve">2.29561996459961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3000431060791</t>
+    <t xml:space="preserve">2.30004286766052</t>
   </si>
   <si>
     <t xml:space="preserve">2.29473567008972</t>
@@ -4055,43 +4055,43 @@
     <t xml:space="preserve">2.23458027839661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22661852836609</t>
+    <t xml:space="preserve">2.22661876678467</t>
   </si>
   <si>
     <t xml:space="preserve">2.22219562530518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23192667961121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1753101348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1947717666626</t>
+    <t xml:space="preserve">2.23192644119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17530989646912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19477200508118</t>
   </si>
   <si>
     <t xml:space="preserve">2.22573399543762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1815025806427</t>
+    <t xml:space="preserve">2.18150234222412</t>
   </si>
   <si>
     <t xml:space="preserve">2.15054035186768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1125009059906</t>
+    <t xml:space="preserve">2.11250114440918</t>
   </si>
   <si>
     <t xml:space="preserve">2.10807776451111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13727045059204</t>
+    <t xml:space="preserve">2.13727068901062</t>
   </si>
   <si>
     <t xml:space="preserve">2.12753987312317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11692404747009</t>
+    <t xml:space="preserve">2.11692428588867</t>
   </si>
   <si>
     <t xml:space="preserve">2.18857932090759</t>
@@ -4103,7 +4103,7 @@
     <t xml:space="preserve">2.22131085395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20361804962158</t>
+    <t xml:space="preserve">2.20361828804016</t>
   </si>
   <si>
     <t xml:space="preserve">2.21423387527466</t>
@@ -4124,7 +4124,7 @@
     <t xml:space="preserve">2.42212247848511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31950521469116</t>
+    <t xml:space="preserve">2.31950497627258</t>
   </si>
   <si>
     <t xml:space="preserve">2.39558339118958</t>
@@ -4142,22 +4142,22 @@
     <t xml:space="preserve">2.44512271881104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49643158912659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53181648254395</t>
+    <t xml:space="preserve">2.49643135070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53181672096252</t>
   </si>
   <si>
     <t xml:space="preserve">2.52297043800354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54066276550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62381863594055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65035724639893</t>
+    <t xml:space="preserve">2.54066300392151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62381839752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6503574848175</t>
   </si>
   <si>
     <t xml:space="preserve">2.67689633369446</t>
@@ -4172,10 +4172,10 @@
     <t xml:space="preserve">2.53712439537048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61497235298157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63266468048096</t>
+    <t xml:space="preserve">2.61497211456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63266491889954</t>
   </si>
   <si>
     <t xml:space="preserve">2.62204909324646</t>
@@ -4184,7 +4184,7 @@
     <t xml:space="preserve">2.54950928688049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52827835083008</t>
+    <t xml:space="preserve">2.5282781124115</t>
   </si>
   <si>
     <t xml:space="preserve">2.57958674430847</t>
@@ -4196,19 +4196,19 @@
     <t xml:space="preserve">2.60966420173645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58666372299194</t>
+    <t xml:space="preserve">2.58666396141052</t>
   </si>
   <si>
     <t xml:space="preserve">2.59020256996155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.538893699646</t>
+    <t xml:space="preserve">2.53889346122742</t>
   </si>
   <si>
     <t xml:space="preserve">2.572509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54420161247253</t>
+    <t xml:space="preserve">2.54420137405396</t>
   </si>
   <si>
     <t xml:space="preserve">2.55304765701294</t>
@@ -5616,6 +5616,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.9760000705719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97000002861023</t>
   </si>
 </sst>
 </file>
@@ -70876,7 +70879,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6912847222</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>1897786</v>
@@ -70897,6 +70900,32 @@
         <v>1867</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.693587963</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>1335194</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>3.99399995803833</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>3.94600009918213</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>3.98399996757507</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>3.97000002861023</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>1868</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HER.MI.xlsx
+++ b/data/HER.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1872" uniqueCount="1872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1873" uniqueCount="1873">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70756649971008</t>
+    <t xml:space="preserve">1.70756638050079</t>
   </si>
   <si>
     <t xml:space="preserve">HER.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70896375179291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70616912841797</t>
+    <t xml:space="preserve">1.70896399021149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70616900920868</t>
   </si>
   <si>
     <t xml:space="preserve">1.71036100387573</t>
@@ -62,34 +62,34 @@
     <t xml:space="preserve">1.79140770435333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79420220851898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7704473733902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74669253826141</t>
+    <t xml:space="preserve">1.79420244693756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77044725418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74669229984283</t>
   </si>
   <si>
     <t xml:space="preserve">1.70337438583374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77324223518372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74948704242706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76625525951385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80538141727448</t>
+    <t xml:space="preserve">1.77324199676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74948692321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76625537872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80538153648376</t>
   </si>
   <si>
     <t xml:space="preserve">1.79001033306122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80398404598236</t>
+    <t xml:space="preserve">1.80398380756378</t>
   </si>
   <si>
     <t xml:space="preserve">1.83472537994385</t>
@@ -101,274 +101,274 @@
     <t xml:space="preserve">1.80258643627167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84869921207428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85568583011627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84031510353088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82354629039764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82913637161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72852671146393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74110305309296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75926828384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6991822719574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75507640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79559969902039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78302359580994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77603650093079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79839444160461</t>
+    <t xml:space="preserve">1.8486989736557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85568606853485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8403148651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82354664802551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82913649082184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72852659225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74110281467438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75926840305328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69918251037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75507628917694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7955995798111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78302347660065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77603662014008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79839432239532</t>
   </si>
   <si>
     <t xml:space="preserve">1.80118918418884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82075190544128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83053362369537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78861308097839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76485800743103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74529492855072</t>
+    <t xml:space="preserve">1.82075202465057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83053338527679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7886129617691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76485788822174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74529469013214</t>
   </si>
   <si>
     <t xml:space="preserve">1.73970568180084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72992420196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7438976764679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73271882534027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76346063613892</t>
+    <t xml:space="preserve">1.72992432117462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74389791488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73271870613098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76346075534821</t>
   </si>
   <si>
     <t xml:space="preserve">1.77883148193359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7606657743454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77463936805725</t>
+    <t xml:space="preserve">1.76066601276398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77463948726654</t>
   </si>
   <si>
     <t xml:space="preserve">1.79699718952179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83752012252808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81097066402435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85708343982697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84310960769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76765286922455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78162622451782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78721559047699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77743399143219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78022873401642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80817580223083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80957329273224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79280495643616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78442060947418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75647366046906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74808979034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82634127140045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84590435028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83193099498749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84450685977936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8221492767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8333283662796</t>
+    <t xml:space="preserve">1.83752048015594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81097054481506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85708320140839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8431099653244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76765275001526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78162634372711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78721582889557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77743422985077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.780228972435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8081761598587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80957305431366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79280483722687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78442072868347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75647377967834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74808990955353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82634174823761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84590446949005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83193111419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84450709819794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82214951515198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83332824707031</t>
   </si>
   <si>
     <t xml:space="preserve">1.82494413852692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81376504898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76206338405609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73132145404816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7425000667572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.711758852005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75751054286957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77344810962677</t>
+    <t xml:space="preserve">1.81376540660858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76206350326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73132133483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74250030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71175861358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75751042366028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77344787120819</t>
   </si>
   <si>
     <t xml:space="preserve">1.7401237487793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75895941257477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70390105247498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6734744310379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70969665050507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73867464065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78069257736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83430182933807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8082218170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81111967563629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78503930568695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77924382686615</t>
+    <t xml:space="preserve">1.75895929336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70390117168427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67347455024719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70969676971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73867475986481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78069269657135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83430159091949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80822157859802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.811119556427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78503954410553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77924394607544</t>
   </si>
   <si>
     <t xml:space="preserve">1.72708356380463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76040828227997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7459192276001</t>
+    <t xml:space="preserve">1.76040816307068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74591910839081</t>
   </si>
   <si>
     <t xml:space="preserve">1.77055025100708</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76620388031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76185691356659</t>
+    <t xml:space="preserve">1.76620376110077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76185715198517</t>
   </si>
   <si>
     <t xml:space="preserve">1.76910161972046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77489745616913</t>
+    <t xml:space="preserve">1.77489709854126</t>
   </si>
   <si>
     <t xml:space="preserve">1.78359043598175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83719968795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85748422145844</t>
+    <t xml:space="preserve">1.83719992637634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85748445987701</t>
   </si>
   <si>
     <t xml:space="preserve">1.85023939609528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83575081825256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86617732048035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83140397071838</t>
+    <t xml:space="preserve">1.83575046062469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86617755889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83140420913696</t>
   </si>
   <si>
     <t xml:space="preserve">1.84444415569305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79663074016571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81981289386749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8125684261322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7488169670105</t>
+    <t xml:space="preserve">1.79663050174713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81981325149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81256830692291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74881720542908</t>
   </si>
   <si>
     <t xml:space="preserve">1.74447023868561</t>
@@ -380,10 +380,10 @@
     <t xml:space="preserve">1.79083478450775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79952824115753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78648841381073</t>
+    <t xml:space="preserve">1.79952812194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78648829460144</t>
   </si>
   <si>
     <t xml:space="preserve">1.78938627243042</t>
@@ -392,22 +392,22 @@
     <t xml:space="preserve">1.81546628475189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75606155395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73577702045441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70679914951324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73722589015961</t>
+    <t xml:space="preserve">1.7560613155365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73577690124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70679891109467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73722577095032</t>
   </si>
   <si>
     <t xml:space="preserve">1.7546124458313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71114575862885</t>
+    <t xml:space="preserve">1.71114552021027</t>
   </si>
   <si>
     <t xml:space="preserve">1.70824801921844</t>
@@ -416,37 +416,37 @@
     <t xml:space="preserve">1.70245218276978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69231009483337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71694123744965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69665694236755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63145637512207</t>
+    <t xml:space="preserve">1.69230985641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71694135665894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69665706157684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63145649433136</t>
   </si>
   <si>
     <t xml:space="preserve">1.60537648200989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59233629703522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57929635047913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60102987289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60972285270691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6140695810318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6213139295578</t>
+    <t xml:space="preserve">1.59233641624451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57929623126984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.601029753685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6097229719162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61406970024109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62131416797638</t>
   </si>
   <si>
     <t xml:space="preserve">1.63290536403656</t>
@@ -455,82 +455,82 @@
     <t xml:space="preserve">1.61841642856598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63870108127594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63725185394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65029215812683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62276315689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61551868915558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61696755886078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62566077709198</t>
+    <t xml:space="preserve">1.63870096206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63725221157074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65029203891754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62276291847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61551856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61696743965149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62566065788269</t>
   </si>
   <si>
     <t xml:space="preserve">1.66188323497772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66912770271301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68796348571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59378516674042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56625616550446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56335830688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54307401180267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4604868888855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46338450908661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44599783420563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44527351856232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45034444332123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43005979061127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42209100723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39601099491119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39456188678741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40905094146729</t>
+    <t xml:space="preserve">1.66912758350372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68796324729919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59378528594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56625604629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56335842609406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54307389259338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46048676967621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4633846282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44599771499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44527339935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45034456253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43005990982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42209112644196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3960108757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3945620059967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40905106067657</t>
   </si>
   <si>
     <t xml:space="preserve">1.41267335414886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3981841802597</t>
+    <t xml:space="preserve">1.39818406105042</t>
   </si>
   <si>
     <t xml:space="preserve">1.40180647373199</t>
@@ -545,40 +545,40 @@
     <t xml:space="preserve">1.38152182102203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35906410217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37717521190643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43875336647034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4807710647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49236249923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48511791229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53293144702911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52713620662689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50105583667755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50685143470764</t>
+    <t xml:space="preserve">1.35906398296356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37717509269714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43875324726105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48077130317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49236261844635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48511803150177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53293168544769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52713596820831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50105595588684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50685131549835</t>
   </si>
   <si>
     <t xml:space="preserve">1.54886949062347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55756306648254</t>
+    <t xml:space="preserve">1.55756294727325</t>
   </si>
   <si>
     <t xml:space="preserve">1.57060277462006</t>
@@ -599,64 +599,64 @@
     <t xml:space="preserve">1.59668278694153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59958064556122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56480729579926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65174078941345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64159870147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65319001674652</t>
+    <t xml:space="preserve">1.59958076477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56480741500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65174090862274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64159882068634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65318977832794</t>
   </si>
   <si>
     <t xml:space="preserve">1.65463876724243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65898537635803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64014971256256</t>
+    <t xml:space="preserve">1.65898549556732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64014983177185</t>
   </si>
   <si>
     <t xml:space="preserve">1.64304757118225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57494974136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57784736156464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5517669916153</t>
+    <t xml:space="preserve">1.57494950294495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57784724235535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55176723003387</t>
   </si>
   <si>
     <t xml:space="preserve">1.58654081821442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63000750541687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68216776847839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66622972488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6778210401535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69086134433746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69375896453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69810569286346</t>
+    <t xml:space="preserve">1.63000762462616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68216788768768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66622984409332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67782115936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69086110591888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69375908374786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69810593128204</t>
   </si>
   <si>
     <t xml:space="preserve">1.69520747661591</t>
@@ -665,37 +665,37 @@
     <t xml:space="preserve">1.71404349803925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72998142242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73432791233063</t>
+    <t xml:space="preserve">1.72998094558716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7343282699585</t>
   </si>
   <si>
     <t xml:space="preserve">1.71983897686005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72418570518494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71549248695374</t>
+    <t xml:space="preserve">1.72418582439423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71549224853516</t>
   </si>
   <si>
     <t xml:space="preserve">1.71839022636414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74157249927521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78214132785797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78793716430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81401741504669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82995510101318</t>
+    <t xml:space="preserve">1.74157285690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78214168548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78793728351593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81401705741882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82995533943176</t>
   </si>
   <si>
     <t xml:space="preserve">1.86907517910004</t>
@@ -704,46 +704,46 @@
     <t xml:space="preserve">1.89950239658356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91399121284485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91543984413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88066625595093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87197351455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88935971260071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90095138549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90529763698578</t>
+    <t xml:space="preserve">1.91399109363556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91543996334076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8806666135788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8719733953476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88936007022858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90095126628876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90529775619507</t>
   </si>
   <si>
     <t xml:space="preserve">1.91254210472107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94441771507263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93717336654663</t>
+    <t xml:space="preserve">1.94441783428192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93717348575592</t>
   </si>
   <si>
     <t xml:space="preserve">1.8792177438736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88356399536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92848026752472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89805328845978</t>
+    <t xml:space="preserve">1.88356423377991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92847979068756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89805340766907</t>
   </si>
   <si>
     <t xml:space="preserve">1.88791072368622</t>
@@ -752,43 +752,43 @@
     <t xml:space="preserve">1.9023996591568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91688883304596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92413318157196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93572461605072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93862235546112</t>
+    <t xml:space="preserve">1.91688907146454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92413330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93572437763214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93862247467041</t>
   </si>
   <si>
     <t xml:space="preserve">1.94876456260681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99512934684753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0284538269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05743169784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06902313232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05163621902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10234761238098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06467604637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0385959148407</t>
+    <t xml:space="preserve">1.99512910842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02845358848572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05743193626404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06902241706848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05163598060608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1023473739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06467628479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03859639167786</t>
   </si>
   <si>
     <t xml:space="preserve">2.07336974143982</t>
@@ -797,22 +797,22 @@
     <t xml:space="preserve">2.0864098072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12842750549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11248970031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11104083061218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10089874267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05453395843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0893075466156</t>
+    <t xml:space="preserve">2.12842774391174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11248993873596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1110405921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10089898109436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05453372001648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08930730819702</t>
   </si>
   <si>
     <t xml:space="preserve">2.12263226509094</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">2.07916498184204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10379648208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11973428726196</t>
+    <t xml:space="preserve">2.1037962436676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11973452568054</t>
   </si>
   <si>
     <t xml:space="preserve">2.10814332962036</t>
@@ -839,124 +839,124 @@
     <t xml:space="preserve">2.15450763702393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14291667938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15595650672913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1679093837738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17836785316467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17239165306091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09918165206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.112628698349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07228851318359</t>
+    <t xml:space="preserve">2.14291644096375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15595674514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16790890693665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17836809158325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17239141464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09918189048767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11262845993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07228827476501</t>
   </si>
   <si>
     <t xml:space="preserve">2.05884194374084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01700735092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99907839298248</t>
+    <t xml:space="preserve">2.01700758934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99907827377319</t>
   </si>
   <si>
     <t xml:space="preserve">2.01103091239929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00804257392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99758422374725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95126795768738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97069084644318</t>
+    <t xml:space="preserve">2.00804281234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99758434295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95126783847809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97069096565247</t>
   </si>
   <si>
     <t xml:space="preserve">2.00505447387695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98264348506927</t>
+    <t xml:space="preserve">1.9826432466507</t>
   </si>
   <si>
     <t xml:space="preserve">2.03045392036438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05286502838135</t>
+    <t xml:space="preserve">2.05286526679993</t>
   </si>
   <si>
     <t xml:space="preserve">2.0394184589386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03194785118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04539465904236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02447748184204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06182980537415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07677054405212</t>
+    <t xml:space="preserve">2.03194808959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04539489746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02447772026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06182956695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07677030563354</t>
   </si>
   <si>
     <t xml:space="preserve">2.03344202041626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01401948928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05435919761658</t>
+    <t xml:space="preserve">2.01401925086975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05435943603516</t>
   </si>
   <si>
     <t xml:space="preserve">2.04390072822571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04240679740906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03643083572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04838299751282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04987716674805</t>
+    <t xml:space="preserve">2.04240655899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0364305973053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0483832359314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04987692832947</t>
   </si>
   <si>
     <t xml:space="preserve">2.00206661224365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05585336685181</t>
+    <t xml:space="preserve">2.05585360527039</t>
   </si>
   <si>
     <t xml:space="preserve">2.03493618965149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99459612369537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.975172996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96172618865967</t>
+    <t xml:space="preserve">1.99459624290466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97517311573029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96172642707825</t>
   </si>
   <si>
     <t xml:space="preserve">1.96770262718201</t>
@@ -968,13 +968,13 @@
     <t xml:space="preserve">2.01252508163452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00953698158264</t>
+    <t xml:space="preserve">2.00953674316406</t>
   </si>
   <si>
     <t xml:space="preserve">2.00356030464172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07826471328735</t>
+    <t xml:space="preserve">2.07826447486877</t>
   </si>
   <si>
     <t xml:space="preserve">2.01850128173828</t>
@@ -986,19 +986,19 @@
     <t xml:space="preserve">1.98563182353973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98712587356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97218477725983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02148985862732</t>
+    <t xml:space="preserve">1.98712599277496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9721851348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02148962020874</t>
   </si>
   <si>
     <t xml:space="preserve">2.03792452812195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06033539772034</t>
+    <t xml:space="preserve">2.06033563613892</t>
   </si>
   <si>
     <t xml:space="preserve">2.07079410552979</t>
@@ -1013,37 +1013,37 @@
     <t xml:space="preserve">2.06332397460938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07527661323547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08424115180969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10665202140808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12458086013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14998030662537</t>
+    <t xml:space="preserve">2.07527637481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08424091339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1066517829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12458109855652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14998078346252</t>
   </si>
   <si>
     <t xml:space="preserve">2.16043877601624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18135595321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19629693031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18733239173889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1798620223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16641521453857</t>
+    <t xml:space="preserve">2.18135619163513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19629669189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18733215332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17986226081848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16641545295715</t>
   </si>
   <si>
     <t xml:space="preserve">2.17089748382568</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">2.191814661026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19330859184265</t>
+    <t xml:space="preserve">2.19330883026123</t>
   </si>
   <si>
     <t xml:space="preserve">2.19480276107788</t>
@@ -1061,22 +1061,22 @@
     <t xml:space="preserve">2.22468447685242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27100086212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2560601234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25904846191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28145933151245</t>
+    <t xml:space="preserve">2.271000623703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25605988502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25904822349548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28145909309387</t>
   </si>
   <si>
     <t xml:space="preserve">2.29490637779236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30536460876465</t>
+    <t xml:space="preserve">2.30536484718323</t>
   </si>
   <si>
     <t xml:space="preserve">2.30088210105896</t>
@@ -1094,64 +1094,64 @@
     <t xml:space="preserve">2.303870677948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31582307815552</t>
+    <t xml:space="preserve">2.3158233165741</t>
   </si>
   <si>
     <t xml:space="preserve">2.25456571578979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25755429267883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27847123146057</t>
+    <t xml:space="preserve">2.25755405426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27847146987915</t>
   </si>
   <si>
     <t xml:space="preserve">2.22916650772095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22617864608765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21870803833008</t>
+    <t xml:space="preserve">2.22617840766907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2187077999115</t>
   </si>
   <si>
     <t xml:space="preserve">2.17388582229614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15446257591248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21123766899109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26054239273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31134128570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24111914634705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26950693130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23813104629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27697682380676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28594183921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29938817024231</t>
+    <t xml:space="preserve">2.15446281433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21123790740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26054215431213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31134104728699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24111938476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26950645446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23813128471375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27697706222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28594160079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29938864707947</t>
   </si>
   <si>
     <t xml:space="preserve">2.24709558486938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27996516227722</t>
+    <t xml:space="preserve">2.2799654006958</t>
   </si>
   <si>
     <t xml:space="preserve">2.24560141563416</t>
@@ -1160,10 +1160,10 @@
     <t xml:space="preserve">2.18434429168701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13504004478455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11113452911377</t>
+    <t xml:space="preserve">2.13503980636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11113429069519</t>
   </si>
   <si>
     <t xml:space="preserve">2.05734753608704</t>
@@ -1172,28 +1172,28 @@
     <t xml:space="preserve">2.02895998954773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0946991443634</t>
+    <t xml:space="preserve">2.09469962120056</t>
   </si>
   <si>
     <t xml:space="preserve">2.12607526779175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13354563713074</t>
+    <t xml:space="preserve">2.13354539871216</t>
   </si>
   <si>
     <t xml:space="preserve">2.09320521354675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06929969787598</t>
+    <t xml:space="preserve">2.06930017471313</t>
   </si>
   <si>
     <t xml:space="preserve">2.04091262817383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08573484420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08274698257446</t>
+    <t xml:space="preserve">2.08573508262634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08274722099304</t>
   </si>
   <si>
     <t xml:space="preserve">2.08125305175781</t>
@@ -1202,22 +1202,22 @@
     <t xml:space="preserve">2.10216975212097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09768772125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12009882926941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21273159980774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22169613838196</t>
+    <t xml:space="preserve">2.09768748283386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12009906768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21273183822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22169637680054</t>
   </si>
   <si>
     <t xml:space="preserve">2.23066067695618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24261331558228</t>
+    <t xml:space="preserve">2.24261355400085</t>
   </si>
   <si>
     <t xml:space="preserve">2.26353049278259</t>
@@ -1226,28 +1226,28 @@
     <t xml:space="preserve">2.23514318466187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25307202339172</t>
+    <t xml:space="preserve">2.25307178497314</t>
   </si>
   <si>
     <t xml:space="preserve">2.29341197013855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29789447784424</t>
+    <t xml:space="preserve">2.29789423942566</t>
   </si>
   <si>
     <t xml:space="preserve">2.28444766998291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22767305374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25157785415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14101600646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12159299850464</t>
+    <t xml:space="preserve">2.22767281532288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25157809257507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14101576805115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12159276008606</t>
   </si>
   <si>
     <t xml:space="preserve">2.02298355102539</t>
@@ -1256,22 +1256,22 @@
     <t xml:space="preserve">1.9467853307724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96471452713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98114931583405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96919667720795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97816109657288</t>
+    <t xml:space="preserve">1.96471476554871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98114955425262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96919679641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97816097736359</t>
   </si>
   <si>
     <t xml:space="preserve">1.94827950000763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02856683731079</t>
+    <t xml:space="preserve">2.02856707572937</t>
   </si>
   <si>
     <t xml:space="preserve">2.06108570098877</t>
@@ -1283,43 +1283,43 @@
     <t xml:space="preserve">2.0378577709198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04095482826233</t>
+    <t xml:space="preserve">2.04095506668091</t>
   </si>
   <si>
     <t xml:space="preserve">2.07347416877747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05953741073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08895921707153</t>
+    <t xml:space="preserve">2.05953764915466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08895897865295</t>
   </si>
   <si>
     <t xml:space="preserve">2.06728005409241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10599327087402</t>
+    <t xml:space="preserve">2.10599303245544</t>
   </si>
   <si>
     <t xml:space="preserve">2.13541483879089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15399742126465</t>
+    <t xml:space="preserve">2.15399718284607</t>
   </si>
   <si>
     <t xml:space="preserve">2.16019129753113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14470624923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13696312904358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14780354499817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13386631011963</t>
+    <t xml:space="preserve">2.14470601081848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13696336746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14780330657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13386654853821</t>
   </si>
   <si>
     <t xml:space="preserve">2.16793394088745</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">2.17257952690125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15244889259338</t>
+    <t xml:space="preserve">2.15244841575623</t>
   </si>
   <si>
     <t xml:space="preserve">2.10444450378418</t>
@@ -1337,43 +1337,43 @@
     <t xml:space="preserve">2.09205627441406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20664691925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1710307598114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19580745697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18651628494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21748661994934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2159378528595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1834192276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16328835487366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1509006023407</t>
+    <t xml:space="preserve">2.20664715766907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17103099822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19580721855164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18651652336121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21748685836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21593809127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18341898918152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16328811645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15090012550354</t>
   </si>
   <si>
     <t xml:space="preserve">2.13231778144836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12612390518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11992955207825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16638588905334</t>
+    <t xml:space="preserve">2.12612366676331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11992979049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16638541221619</t>
   </si>
   <si>
     <t xml:space="preserve">2.15709447860718</t>
@@ -1385,13 +1385,13 @@
     <t xml:space="preserve">2.09670186042786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09979891777039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09050750732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10754156112671</t>
+    <t xml:space="preserve">2.09979867935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09050798416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10754108428955</t>
   </si>
   <si>
     <t xml:space="preserve">2.12457513809204</t>
@@ -1400,70 +1400,70 @@
     <t xml:space="preserve">2.12767219543457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18806505203247</t>
+    <t xml:space="preserve">2.18806457519531</t>
   </si>
   <si>
     <t xml:space="preserve">2.20045304298401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1973557472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20200157165527</t>
+    <t xml:space="preserve">2.19735598564148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20200133323669</t>
   </si>
   <si>
     <t xml:space="preserve">2.20819544792175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2112922668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1756763458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12147831916809</t>
+    <t xml:space="preserve">2.21129250526428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17567658424377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12147808074951</t>
   </si>
   <si>
     <t xml:space="preserve">2.11683249473572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07657098770142</t>
+    <t xml:space="preserve">2.07657074928284</t>
   </si>
   <si>
     <t xml:space="preserve">2.06882810592651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05179476737976</t>
+    <t xml:space="preserve">2.05179452896118</t>
   </si>
   <si>
     <t xml:space="preserve">2.01463031768799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9619802236557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98211097717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93720388412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90313613414764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86287462711334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91552460193634</t>
+    <t xml:space="preserve">1.96198010444641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98211085796356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93720376491547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90313625335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86287450790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91552472114563</t>
   </si>
   <si>
     <t xml:space="preserve">1.87216579914093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89384531974792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90158772468567</t>
+    <t xml:space="preserve">1.89384508132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90158784389496</t>
   </si>
   <si>
     <t xml:space="preserve">1.87061727046967</t>
@@ -1472,22 +1472,22 @@
     <t xml:space="preserve">1.85977780818939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92791295051575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89694237709045</t>
+    <t xml:space="preserve">1.92791283130646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89694249629974</t>
   </si>
   <si>
     <t xml:space="preserve">1.8907482624054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87990832328796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88919997215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88765132427216</t>
+    <t xml:space="preserve">1.87990844249725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88919961452484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88765120506287</t>
   </si>
   <si>
     <t xml:space="preserve">1.90468490123749</t>
@@ -1502,70 +1502,70 @@
     <t xml:space="preserve">1.91862142086029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97901391983032</t>
+    <t xml:space="preserve">1.9790141582489</t>
   </si>
   <si>
     <t xml:space="preserve">1.96972262859344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97746551036835</t>
+    <t xml:space="preserve">1.97746527194977</t>
   </si>
   <si>
     <t xml:space="preserve">1.94184947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9310097694397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92481589317322</t>
+    <t xml:space="preserve">1.93100941181183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92481553554535</t>
   </si>
   <si>
     <t xml:space="preserve">1.92016994953156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89229667186737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90933048725128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87836015224457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93875217437744</t>
+    <t xml:space="preserve">1.89229643344879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90933060646057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87835991382599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93875205516815</t>
   </si>
   <si>
     <t xml:space="preserve">1.86906898021698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94804334640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98675644397736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09360456466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03630971908569</t>
+    <t xml:space="preserve">1.94804382324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98675656318665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09360480308533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03630948066711</t>
   </si>
   <si>
     <t xml:space="preserve">2.06573152542114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09825015068054</t>
+    <t xml:space="preserve">2.09825038909912</t>
   </si>
   <si>
     <t xml:space="preserve">2.08276510238647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.191162109375</t>
+    <t xml:space="preserve">2.19116163253784</t>
   </si>
   <si>
     <t xml:space="preserve">2.19425892829895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17877340316772</t>
+    <t xml:space="preserve">2.1787736415863</t>
   </si>
   <si>
     <t xml:space="preserve">2.2050986289978</t>
@@ -1574,10 +1574,10 @@
     <t xml:space="preserve">2.20974397659302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22987484931946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20355010032654</t>
+    <t xml:space="preserve">2.22987508773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20354986190796</t>
   </si>
   <si>
     <t xml:space="preserve">2.19890427589417</t>
@@ -1589,10 +1589,10 @@
     <t xml:space="preserve">2.26084542274475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26239371299744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28562188148499</t>
+    <t xml:space="preserve">2.26239395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28562164306641</t>
   </si>
   <si>
     <t xml:space="preserve">2.29336428642273</t>
@@ -1601,13 +1601,13 @@
     <t xml:space="preserve">2.28252458572388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28407335281372</t>
+    <t xml:space="preserve">2.28407311439514</t>
   </si>
   <si>
     <t xml:space="preserve">2.2902672290802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27013611793518</t>
+    <t xml:space="preserve">2.27013635635376</t>
   </si>
   <si>
     <t xml:space="preserve">2.25619983673096</t>
@@ -1619,22 +1619,22 @@
     <t xml:space="preserve">2.30265545845032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30110669136047</t>
+    <t xml:space="preserve">2.30110692977905</t>
   </si>
   <si>
     <t xml:space="preserve">2.30730104446411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2980101108551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28871893882751</t>
+    <t xml:space="preserve">2.29800987243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28871917724609</t>
   </si>
   <si>
     <t xml:space="preserve">2.25929689407349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32433533668518</t>
+    <t xml:space="preserve">2.3243350982666</t>
   </si>
   <si>
     <t xml:space="preserve">2.29181575775146</t>
@@ -1649,46 +1649,46 @@
     <t xml:space="preserve">2.26549077033997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29955863952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29646158218384</t>
+    <t xml:space="preserve">2.29955840110779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29646134376526</t>
   </si>
   <si>
     <t xml:space="preserve">2.31349515914917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32123780250549</t>
+    <t xml:space="preserve">2.32123756408691</t>
   </si>
   <si>
     <t xml:space="preserve">2.25774836540222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23916625976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34446573257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38008189201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38163018226624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40330934524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42808628082275</t>
+    <t xml:space="preserve">2.23916578292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34446620941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38008165359497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38163042068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40330958366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4280858039856</t>
   </si>
   <si>
     <t xml:space="preserve">2.43118333816528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47608995437622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4946722984314</t>
+    <t xml:space="preserve">2.47609043121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49467277526855</t>
   </si>
   <si>
     <t xml:space="preserve">2.49002695083618</t>
@@ -1697,37 +1697,37 @@
     <t xml:space="preserve">2.49622082710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50860953330994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54887104034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52099752426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50241541862488</t>
+    <t xml:space="preserve">2.50860929489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54887080192566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5209972858429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5024151802063</t>
   </si>
   <si>
     <t xml:space="preserve">2.51635193824768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46215391159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47918725013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46525073051453</t>
+    <t xml:space="preserve">2.462153673172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47918701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46525049209595</t>
   </si>
   <si>
     <t xml:space="preserve">2.43428015708923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44976544380188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45286250114441</t>
+    <t xml:space="preserve">2.44976568222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45286226272583</t>
   </si>
   <si>
     <t xml:space="preserve">2.46679925918579</t>
@@ -1739,19 +1739,19 @@
     <t xml:space="preserve">2.4575080871582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47144484519958</t>
+    <t xml:space="preserve">2.47144460678101</t>
   </si>
   <si>
     <t xml:space="preserve">2.45905637741089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42653775215149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44821691513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42963457107544</t>
+    <t xml:space="preserve">2.42653751373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44821667671204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42963433265686</t>
   </si>
   <si>
     <t xml:space="preserve">2.48692965507507</t>
@@ -1763,13 +1763,13 @@
     <t xml:space="preserve">2.53803157806396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54112815856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54422521591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55661392211914</t>
+    <t xml:space="preserve">2.54112839698792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54422545433044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55661344528198</t>
   </si>
   <si>
     <t xml:space="preserve">2.55816197395325</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">2.53648281097412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53493428230286</t>
+    <t xml:space="preserve">2.5349338054657</t>
   </si>
   <si>
     <t xml:space="preserve">2.52873992919922</t>
@@ -1793,10 +1793,10 @@
     <t xml:space="preserve">2.5906810760498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60306930541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60461783409119</t>
+    <t xml:space="preserve">2.60306906700134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60461807250977</t>
   </si>
   <si>
     <t xml:space="preserve">2.59997224807739</t>
@@ -1805,43 +1805,43 @@
     <t xml:space="preserve">2.60152077674866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58913230895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58603549003601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64642810821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65262222290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68514132499695</t>
+    <t xml:space="preserve">2.58913278579712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58603525161743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64642786979675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65262198448181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68514108657837</t>
   </si>
   <si>
     <t xml:space="preserve">2.71611142158508</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69698405265808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67945051193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68263816833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65075898170471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68104434013367</t>
+    <t xml:space="preserve">2.69698429107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67945027351379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68263840675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65075945854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68104457855225</t>
   </si>
   <si>
     <t xml:space="preserve">2.66669869422913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7304573059082</t>
+    <t xml:space="preserve">2.73045706748962</t>
   </si>
   <si>
     <t xml:space="preserve">2.81174945831299</t>
@@ -1853,19 +1853,19 @@
     <t xml:space="preserve">2.7846519947052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77349448204041</t>
+    <t xml:space="preserve">2.77349424362183</t>
   </si>
   <si>
     <t xml:space="preserve">2.78305816650391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79740333557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79580950737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82768869400024</t>
+    <t xml:space="preserve">2.79740357398987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79580926895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82768845558167</t>
   </si>
   <si>
     <t xml:space="preserve">2.80696749687195</t>
@@ -1874,16 +1874,16 @@
     <t xml:space="preserve">2.75914835929871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74480319023132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74958491325378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7320511341095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72886347770691</t>
+    <t xml:space="preserve">2.74480295181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74958467483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73205089569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72886323928833</t>
   </si>
   <si>
     <t xml:space="preserve">2.73364520072937</t>
@@ -1901,40 +1901,40 @@
     <t xml:space="preserve">2.71132969856262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69538974761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70654797554016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72726941108704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70495390892029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73523902893066</t>
+    <t xml:space="preserve">2.69538998603821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70654773712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72726917266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70495367050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73523926734924</t>
   </si>
   <si>
     <t xml:space="preserve">2.68742036819458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76233673095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78783988952637</t>
+    <t xml:space="preserve">2.76233649253845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78784012794495</t>
   </si>
   <si>
     <t xml:space="preserve">2.77827620506287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78624606132507</t>
+    <t xml:space="preserve">2.78624582290649</t>
   </si>
   <si>
     <t xml:space="preserve">2.81334328651428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88188362121582</t>
+    <t xml:space="preserve">2.88188338279724</t>
   </si>
   <si>
     <t xml:space="preserve">2.87869596481323</t>
@@ -1949,22 +1949,22 @@
     <t xml:space="preserve">2.88666534423828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88825964927673</t>
+    <t xml:space="preserve">2.88825988769531</t>
   </si>
   <si>
     <t xml:space="preserve">2.91695094108582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89622926712036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80059146881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79262161254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84522223472595</t>
+    <t xml:space="preserve">2.89622902870178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80059123039246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79262185096741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84522247314453</t>
   </si>
   <si>
     <t xml:space="preserve">2.81812500953674</t>
@@ -1973,25 +1973,25 @@
     <t xml:space="preserve">2.82131314277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84681630134583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90738701820374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90419912338257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86913180351257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95201778411865</t>
+    <t xml:space="preserve">2.8468165397644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90738725662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90419936180115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86913156509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95201802253723</t>
   </si>
   <si>
     <t xml:space="preserve">2.95042395591736</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02055835723877</t>
+    <t xml:space="preserve">3.02055811882019</t>
   </si>
   <si>
     <t xml:space="preserve">2.9647696018219</t>
@@ -2006,7 +2006,7 @@
     <t xml:space="preserve">2.97114539146423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01577663421631</t>
+    <t xml:space="preserve">3.01577639579773</t>
   </si>
   <si>
     <t xml:space="preserve">3.02215242385864</t>
@@ -2015,25 +2015,25 @@
     <t xml:space="preserve">3.00461864471436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97911524772644</t>
+    <t xml:space="preserve">2.97911548614502</t>
   </si>
   <si>
     <t xml:space="preserve">3.00302481651306</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01418280601501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98389720916748</t>
+    <t xml:space="preserve">3.01418256759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98389744758606</t>
   </si>
   <si>
     <t xml:space="preserve">3.02374625205994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99664902687073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96636366844177</t>
+    <t xml:space="preserve">2.99664878845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96636343002319</t>
   </si>
   <si>
     <t xml:space="preserve">2.99346113204956</t>
@@ -2048,43 +2048,43 @@
     <t xml:space="preserve">3.05881333351135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04924964904785</t>
+    <t xml:space="preserve">3.04924941062927</t>
   </si>
   <si>
     <t xml:space="preserve">3.06997108459473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03012228012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05403161048889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06678295135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05243754386902</t>
+    <t xml:space="preserve">3.03012204170227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05403184890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06678342819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0524377822876</t>
   </si>
   <si>
     <t xml:space="preserve">3.07315897941589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07475280761719</t>
+    <t xml:space="preserve">3.07475328445435</t>
   </si>
   <si>
     <t xml:space="preserve">3.10025668144226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17357850074768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19748830795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19430017471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21820950508118</t>
+    <t xml:space="preserve">3.17357873916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1974880695343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19430041313171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21820974349976</t>
   </si>
   <si>
     <t xml:space="preserve">3.19589447975159</t>
@@ -2102,43 +2102,43 @@
     <t xml:space="preserve">3.18473672866821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17517256736755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19111251831055</t>
+    <t xml:space="preserve">3.17517280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19111227989197</t>
   </si>
   <si>
     <t xml:space="preserve">3.06200122833252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08750486373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12416553497314</t>
+    <t xml:space="preserve">3.08750462532043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12416577339172</t>
   </si>
   <si>
     <t xml:space="preserve">3.10185027122498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09547448158264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0715651512146</t>
+    <t xml:space="preserve">3.09547472000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07156538963318</t>
   </si>
   <si>
     <t xml:space="preserve">3.10344433784485</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11141419410706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06040740013123</t>
+    <t xml:space="preserve">3.11141443252563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06040716171265</t>
   </si>
   <si>
     <t xml:space="preserve">3.12735390663147</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17198443412781</t>
+    <t xml:space="preserve">3.17198491096497</t>
   </si>
   <si>
     <t xml:space="preserve">3.16879677772522</t>
@@ -2147,76 +2147,76 @@
     <t xml:space="preserve">3.16401481628418</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22139739990234</t>
+    <t xml:space="preserve">3.22139763832092</t>
   </si>
   <si>
     <t xml:space="preserve">3.16082692146301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16560888290405</t>
+    <t xml:space="preserve">3.16560864448547</t>
   </si>
   <si>
     <t xml:space="preserve">3.10822653770447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09706830978394</t>
+    <t xml:space="preserve">3.09706854820251</t>
   </si>
   <si>
     <t xml:space="preserve">3.10663223266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08112859725952</t>
+    <t xml:space="preserve">3.08112907409668</t>
   </si>
   <si>
     <t xml:space="preserve">3.07794070243835</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1432933807373</t>
+    <t xml:space="preserve">3.14329361915588</t>
   </si>
   <si>
     <t xml:space="preserve">3.18633031845093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18314266204834</t>
+    <t xml:space="preserve">3.18314242362976</t>
   </si>
   <si>
     <t xml:space="preserve">3.13213562965393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27240443229675</t>
+    <t xml:space="preserve">3.27240419387817</t>
   </si>
   <si>
     <t xml:space="preserve">3.377605676651</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31384706497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44774007797241</t>
+    <t xml:space="preserve">3.3138473033905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44774031639099</t>
   </si>
   <si>
     <t xml:space="preserve">3.44614624977112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37919974327087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26921629905701</t>
+    <t xml:space="preserve">3.37919950485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26921653747559</t>
   </si>
   <si>
     <t xml:space="preserve">3.27718639373779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28675007820129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33297491073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37282395362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38557553291321</t>
+    <t xml:space="preserve">3.28674983978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33297514915466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37282419204712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38557600975037</t>
   </si>
   <si>
     <t xml:space="preserve">3.40948510169983</t>
@@ -2225,43 +2225,43 @@
     <t xml:space="preserve">3.4270191192627</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43977046012878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47802519798279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45252203941345</t>
+    <t xml:space="preserve">3.43977022171021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47802495956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45252180099487</t>
   </si>
   <si>
     <t xml:space="preserve">3.45730400085449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47005558013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55612945556641</t>
+    <t xml:space="preserve">3.47005581855774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55612993240356</t>
   </si>
   <si>
     <t xml:space="preserve">3.53700232505798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51628065109253</t>
+    <t xml:space="preserve">3.51628041267395</t>
   </si>
   <si>
     <t xml:space="preserve">3.33935070037842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30906534194946</t>
+    <t xml:space="preserve">3.30906558036804</t>
   </si>
   <si>
     <t xml:space="preserve">3.3377571105957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27878046035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09069275856018</t>
+    <t xml:space="preserve">3.27878022193909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0906925201416</t>
   </si>
   <si>
     <t xml:space="preserve">3.11300802230835</t>
@@ -2270,25 +2270,25 @@
     <t xml:space="preserve">3.26124668121338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83247065544128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6587290763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69060802459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22038960456848</t>
+    <t xml:space="preserve">2.83247089385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65872859954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69060826301575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2203893661499</t>
   </si>
   <si>
     <t xml:space="preserve">2.55830907821655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46585941314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51049041748047</t>
+    <t xml:space="preserve">2.46585917472839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51049065589905</t>
   </si>
   <si>
     <t xml:space="preserve">2.51686644554138</t>
@@ -2300,13 +2300,13 @@
     <t xml:space="preserve">2.58381271362305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44195032119751</t>
+    <t xml:space="preserve">2.44195008277893</t>
   </si>
   <si>
     <t xml:space="preserve">2.41804051399231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44035649299622</t>
+    <t xml:space="preserve">2.44035625457764</t>
   </si>
   <si>
     <t xml:space="preserve">2.50252079963684</t>
@@ -2333,25 +2333,25 @@
     <t xml:space="preserve">2.45948386192322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57584309577942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56787276268005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54715156555176</t>
+    <t xml:space="preserve">2.57584285736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56787300109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54715180397034</t>
   </si>
   <si>
     <t xml:space="preserve">2.54396367073059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60772180557251</t>
+    <t xml:space="preserve">2.60772228240967</t>
   </si>
   <si>
     <t xml:space="preserve">2.62047386169434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51846027374268</t>
+    <t xml:space="preserve">2.51846051216125</t>
   </si>
   <si>
     <t xml:space="preserve">2.59018850326538</t>
@@ -2363,16 +2363,16 @@
     <t xml:space="preserve">2.67307472229004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69220209121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57903099060059</t>
+    <t xml:space="preserve">2.69220232963562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57903075218201</t>
   </si>
   <si>
     <t xml:space="preserve">2.57265496253967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52483606338501</t>
+    <t xml:space="preserve">2.52483630180359</t>
   </si>
   <si>
     <t xml:space="preserve">2.49295687675476</t>
@@ -2387,10 +2387,10 @@
     <t xml:space="preserve">2.56149697303772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47542333602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46267151832581</t>
+    <t xml:space="preserve">2.47542309761047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46267127990723</t>
   </si>
   <si>
     <t xml:space="preserve">2.51367831230164</t>
@@ -2399,25 +2399,25 @@
     <t xml:space="preserve">2.50092673301697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55352735519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54874515533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65713500976562</t>
+    <t xml:space="preserve">2.55352759361267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54874539375305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65713477134705</t>
   </si>
   <si>
     <t xml:space="preserve">2.66032290458679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85159826278687</t>
+    <t xml:space="preserve">2.85159850120544</t>
   </si>
   <si>
     <t xml:space="preserve">2.85638022422791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81653094291687</t>
+    <t xml:space="preserve">2.81653118133545</t>
   </si>
   <si>
     <t xml:space="preserve">2.77668213844299</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">2.6778564453125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80218553543091</t>
+    <t xml:space="preserve">2.80218577384949</t>
   </si>
   <si>
     <t xml:space="preserve">2.78943395614624</t>
@@ -2438,100 +2438,100 @@
     <t xml:space="preserve">2.75755453109741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75436687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68901443481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63800716400146</t>
+    <t xml:space="preserve">2.75436663627625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68901419639587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63800764083862</t>
   </si>
   <si>
     <t xml:space="preserve">2.70335960388184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70017194747925</t>
+    <t xml:space="preserve">2.70017170906067</t>
   </si>
   <si>
     <t xml:space="preserve">2.72567558288574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74209499359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69940400123596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71418142318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.641934633255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63372492790222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6747739315033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63865065574646</t>
+    <t xml:space="preserve">2.74209475517273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69940376281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71418118476868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64193487167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63372468948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67477416992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63865089416504</t>
   </si>
   <si>
     <t xml:space="preserve">2.65014457702637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69447803497314</t>
+    <t xml:space="preserve">2.69447779655457</t>
   </si>
   <si>
     <t xml:space="preserve">2.73060131072998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73388504981995</t>
+    <t xml:space="preserve">2.73388528823853</t>
   </si>
   <si>
     <t xml:space="preserve">2.7355272769928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76508283615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72567534446716</t>
+    <t xml:space="preserve">2.76508259773254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72567510604858</t>
   </si>
   <si>
     <t xml:space="preserve">2.66163849830627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61894702911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63536667823792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70268774032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6879096031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59267544746399</t>
+    <t xml:space="preserve">2.61894726753235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63536691665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70268797874451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68790984153748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59267568588257</t>
   </si>
   <si>
     <t xml:space="preserve">2.61073732376099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6025276184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59595918655396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58774948120117</t>
+    <t xml:space="preserve">2.60252737998962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59595942497253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58774971961975</t>
   </si>
   <si>
     <t xml:space="preserve">2.66820645332336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72403335571289</t>
+    <t xml:space="preserve">2.72403359413147</t>
   </si>
   <si>
     <t xml:space="preserve">2.78642845153809</t>
@@ -2540,28 +2540,28 @@
     <t xml:space="preserve">2.77657628059387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75851464271545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66656422615051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70925545692444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68298387527466</t>
+    <t xml:space="preserve">2.75851488113403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66656398773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70925569534302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68298363685608</t>
   </si>
   <si>
     <t xml:space="preserve">2.66328024864197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75030493736267</t>
+    <t xml:space="preserve">2.75030517578125</t>
   </si>
   <si>
     <t xml:space="preserve">2.72239136695862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6468608379364</t>
+    <t xml:space="preserve">2.64686059951782</t>
   </si>
   <si>
     <t xml:space="preserve">2.62715697288513</t>
@@ -2579,10 +2579,10 @@
     <t xml:space="preserve">2.59760141372681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64850258827209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64029288291931</t>
+    <t xml:space="preserve">2.64850234985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64029312133789</t>
   </si>
   <si>
     <t xml:space="preserve">2.68134212493896</t>
@@ -2591,10 +2591,10 @@
     <t xml:space="preserve">2.66492247581482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67970013618469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69776177406311</t>
+    <t xml:space="preserve">2.67969989776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69776153564453</t>
   </si>
   <si>
     <t xml:space="preserve">2.71253943443298</t>
@@ -2609,13 +2609,13 @@
     <t xml:space="preserve">2.60745334625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64521861076355</t>
+    <t xml:space="preserve">2.64521837234497</t>
   </si>
   <si>
     <t xml:space="preserve">2.63044095039368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54998397827148</t>
+    <t xml:space="preserve">2.54998421669006</t>
   </si>
   <si>
     <t xml:space="preserve">2.55819392204285</t>
@@ -2633,7 +2633,7 @@
     <t xml:space="preserve">2.50236701965332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.472811460495</t>
+    <t xml:space="preserve">2.47281169891357</t>
   </si>
   <si>
     <t xml:space="preserve">2.42191028594971</t>
@@ -2642,10 +2642,10 @@
     <t xml:space="preserve">2.44325590133667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35951519012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38414454460144</t>
+    <t xml:space="preserve">2.35951542854309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38414478302002</t>
   </si>
   <si>
     <t xml:space="preserve">2.41205835342407</t>
@@ -2654,94 +2654,94 @@
     <t xml:space="preserve">2.46295952796936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39563870429993</t>
+    <t xml:space="preserve">2.39563894271851</t>
   </si>
   <si>
     <t xml:space="preserve">2.37593507766724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37757706642151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31518197059631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29219436645508</t>
+    <t xml:space="preserve">2.37757682800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31518173217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29219460487366</t>
   </si>
   <si>
     <t xml:space="preserve">2.2347252368927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19695997238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21666383743286</t>
+    <t xml:space="preserve">2.19696021080017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21666359901428</t>
   </si>
   <si>
     <t xml:space="preserve">2.23636722564697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25442910194397</t>
+    <t xml:space="preserve">2.25442886352539</t>
   </si>
   <si>
     <t xml:space="preserve">2.3102560043335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30533003807068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28070092201233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.454749584198</t>
+    <t xml:space="preserve">2.30533027648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28070068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45475006103516</t>
   </si>
   <si>
     <t xml:space="preserve">2.42519450187683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44982385635376</t>
+    <t xml:space="preserve">2.44982361793518</t>
   </si>
   <si>
     <t xml:space="preserve">2.49251532554626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47937917709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56147789955139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50893497467041</t>
+    <t xml:space="preserve">2.47937941551208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56147813796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50893473625183</t>
   </si>
   <si>
     <t xml:space="preserve">2.49579906463623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50400900840759</t>
+    <t xml:space="preserve">2.50400924682617</t>
   </si>
   <si>
     <t xml:space="preserve">2.48102116584778</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47609543800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52207064628601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53520679473877</t>
+    <t xml:space="preserve">2.47609567642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52207088470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53520655632019</t>
   </si>
   <si>
     <t xml:space="preserve">2.51221871376038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47116947174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4399721622467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46788573265076</t>
+    <t xml:space="preserve">2.4711697101593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43997192382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46788549423218</t>
   </si>
   <si>
     <t xml:space="preserve">2.44489812850952</t>
@@ -2750,49 +2750,49 @@
     <t xml:space="preserve">2.43012022972107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4153425693512</t>
+    <t xml:space="preserve">2.41534233093262</t>
   </si>
   <si>
     <t xml:space="preserve">2.38907098770142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36444115638733</t>
+    <t xml:space="preserve">2.36444139480591</t>
   </si>
   <si>
     <t xml:space="preserve">2.39399695396423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36608338356018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40384864807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45146584510803</t>
+    <t xml:space="preserve">2.3660831451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40384840965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45146560668945</t>
   </si>
   <si>
     <t xml:space="preserve">2.3398118019104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38742899894714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4531078338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45967555046082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44654011726379</t>
+    <t xml:space="preserve">2.38742876052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45310759544373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45967578887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44653987884521</t>
   </si>
   <si>
     <t xml:space="preserve">2.50565099716187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4416139125824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49087285995483</t>
+    <t xml:space="preserve">2.44161415100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49087309837341</t>
   </si>
   <si>
     <t xml:space="preserve">2.48594737052917</t>
@@ -2804,28 +2804,28 @@
     <t xml:space="preserve">2.54177451133728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38086080551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33652758598328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35787320137024</t>
+    <t xml:space="preserve">2.38086104393005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33652782440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35787343978882</t>
   </si>
   <si>
     <t xml:space="preserve">2.36772537231445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32996010780334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46952724456787</t>
+    <t xml:space="preserve">2.32995986938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46952748298645</t>
   </si>
   <si>
     <t xml:space="preserve">2.49415731430054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55326819419861</t>
+    <t xml:space="preserve">2.55326843261719</t>
   </si>
   <si>
     <t xml:space="preserve">2.51057696342468</t>
@@ -2852,16 +2852,16 @@
     <t xml:space="preserve">2.43176198005676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40220642089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5286386013031</t>
+    <t xml:space="preserve">2.40220665931702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52863836288452</t>
   </si>
   <si>
     <t xml:space="preserve">2.56312012672424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56968784332275</t>
+    <t xml:space="preserve">2.56968808174133</t>
   </si>
   <si>
     <t xml:space="preserve">2.6041693687439</t>
@@ -2870,16 +2870,16 @@
     <t xml:space="preserve">2.71582365036011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68216300010681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72895932197571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70843482017517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69611954689026</t>
+    <t xml:space="preserve">2.68216276168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72895908355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70843458175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69611978530884</t>
   </si>
   <si>
     <t xml:space="preserve">2.71171855926514</t>
@@ -2891,13 +2891,13 @@
     <t xml:space="preserve">2.76918745040894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76097774505615</t>
+    <t xml:space="preserve">2.76097750663757</t>
   </si>
   <si>
     <t xml:space="preserve">2.75441002845764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75523066520691</t>
+    <t xml:space="preserve">2.75523090362549</t>
   </si>
   <si>
     <t xml:space="preserve">2.75605201721191</t>
@@ -2906,13 +2906,13 @@
     <t xml:space="preserve">2.74620008468628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79381728172302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76261949539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76672434806824</t>
+    <t xml:space="preserve">2.7938175201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76261973381042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76672458648682</t>
   </si>
   <si>
     <t xml:space="preserve">2.79710125923157</t>
@@ -2921,43 +2921,43 @@
     <t xml:space="preserve">2.83815050125122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77082943916321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77247166633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76426196098328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86278033256531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83240342140198</t>
+    <t xml:space="preserve">2.77082967758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77247142791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7642617225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86278009414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83240365982056</t>
   </si>
   <si>
     <t xml:space="preserve">2.82255172729492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86031723022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87837910652161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88330483436584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88740944862366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88248348236084</t>
+    <t xml:space="preserve">2.86031699180603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87837886810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88330507278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88740968704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.882483959198</t>
   </si>
   <si>
     <t xml:space="preserve">2.86524295806885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86113786697388</t>
+    <t xml:space="preserve">2.86113810539246</t>
   </si>
   <si>
     <t xml:space="preserve">2.86606383323669</t>
@@ -2969,31 +2969,31 @@
     <t xml:space="preserve">2.87427401542664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89726161956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93256378173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95883560180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97197127342224</t>
+    <t xml:space="preserve">2.89726138114929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93256425857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95883536338806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97197103500366</t>
   </si>
   <si>
     <t xml:space="preserve">3.02533531188965</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00481104850769</t>
+    <t xml:space="preserve">3.00481081008911</t>
   </si>
   <si>
     <t xml:space="preserve">3.00809478759766</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04093432426453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01794648170471</t>
+    <t xml:space="preserve">3.04093408584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01794672012329</t>
   </si>
   <si>
     <t xml:space="preserve">3.04586029052734</t>
@@ -3005,31 +3005,31 @@
     <t xml:space="preserve">3.00727391242981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98921227455139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95801448822021</t>
+    <t xml:space="preserve">2.98921203613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95801424980164</t>
   </si>
   <si>
     <t xml:space="preserve">2.90218782424927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92353343963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8956196308136</t>
+    <t xml:space="preserve">2.92353320121765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89561939239502</t>
   </si>
   <si>
     <t xml:space="preserve">2.89069366455078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89151477813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86688542366028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89479851722717</t>
+    <t xml:space="preserve">2.89151453971863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8668851852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89479827880859</t>
   </si>
   <si>
     <t xml:space="preserve">2.90920472145081</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">2.86429142951965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93208527565002</t>
+    <t xml:space="preserve">2.9320855140686</t>
   </si>
   <si>
     <t xml:space="preserve">2.93293261528015</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">2.92191600799561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89564633369446</t>
+    <t xml:space="preserve">2.8956458568573</t>
   </si>
   <si>
     <t xml:space="preserve">2.92615342140198</t>
@@ -3080,10 +3080,10 @@
     <t xml:space="preserve">2.99055743217468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03292846679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06428337097168</t>
+    <t xml:space="preserve">3.03292870521545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0642831325531</t>
   </si>
   <si>
     <t xml:space="preserve">3.04055571556091</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">3.04479265213013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02275919914246</t>
+    <t xml:space="preserve">3.02275943756104</t>
   </si>
   <si>
     <t xml:space="preserve">3.01004838943481</t>
@@ -3104,13 +3104,13 @@
     <t xml:space="preserve">3.02021718025208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04648733139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03547096252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08546924591064</t>
+    <t xml:space="preserve">3.04648756980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03547072410583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08546900749207</t>
   </si>
   <si>
     <t xml:space="preserve">3.09733271598816</t>
@@ -3125,7 +3125,7 @@
     <t xml:space="preserve">3.15665245056152</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18038034439087</t>
+    <t xml:space="preserve">3.18038010597229</t>
   </si>
   <si>
     <t xml:space="preserve">3.19648122787476</t>
@@ -3134,19 +3134,19 @@
     <t xml:space="preserve">3.18546485900879</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18715953826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16682147979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12953519821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10157012939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11597633361816</t>
+    <t xml:space="preserve">3.18715977668762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16682171821594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12953495979309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10156989097595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11597609519958</t>
   </si>
   <si>
     <t xml:space="preserve">3.11089158058167</t>
@@ -3155,10 +3155,10 @@
     <t xml:space="preserve">3.10411238670349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13716173171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12275528907776</t>
+    <t xml:space="preserve">3.13716149330139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12275552749634</t>
   </si>
   <si>
     <t xml:space="preserve">3.11004424095154</t>
@@ -3170,13 +3170,13 @@
     <t xml:space="preserve">3.08123159408569</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03631854057312</t>
+    <t xml:space="preserve">3.03631806373596</t>
   </si>
   <si>
     <t xml:space="preserve">3.07360506057739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09902787208557</t>
+    <t xml:space="preserve">3.09902763366699</t>
   </si>
   <si>
     <t xml:space="preserve">3.04987716674805</t>
@@ -3188,25 +3188,25 @@
     <t xml:space="preserve">3.04140281677246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08631610870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08292675018311</t>
+    <t xml:space="preserve">3.08631634712219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08292651176453</t>
   </si>
   <si>
     <t xml:space="preserve">3.09224820137024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02360701560974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9744565486908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01428556442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99648952484131</t>
+    <t xml:space="preserve">3.02360725402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97445607185364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01428532600403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99648928642273</t>
   </si>
   <si>
     <t xml:space="preserve">2.99564218521118</t>
@@ -3215,7 +3215,7 @@
     <t xml:space="preserve">2.99818420410156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00411629676819</t>
+    <t xml:space="preserve">3.00411605834961</t>
   </si>
   <si>
     <t xml:space="preserve">2.96089768409729</t>
@@ -3224,7 +3224,7 @@
     <t xml:space="preserve">2.98547291755676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91089963912964</t>
+    <t xml:space="preserve">2.91089940071106</t>
   </si>
   <si>
     <t xml:space="preserve">2.87785005569458</t>
@@ -3236,22 +3236,22 @@
     <t xml:space="preserve">2.94564414024353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97530388832092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95327067375183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92445826530457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94394898414612</t>
+    <t xml:space="preserve">2.97530364990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95327091217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92445850372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9439492225647</t>
   </si>
   <si>
     <t xml:space="preserve">3.00242114067078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03377628326416</t>
+    <t xml:space="preserve">3.03377604484558</t>
   </si>
   <si>
     <t xml:space="preserve">3.04902958869934</t>
@@ -3266,10 +3266,10 @@
     <t xml:space="preserve">2.99733686447144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0125904083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99479460716248</t>
+    <t xml:space="preserve">3.01259064674377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9947943687439</t>
   </si>
   <si>
     <t xml:space="preserve">3.03462338447571</t>
@@ -3278,58 +3278,58 @@
     <t xml:space="preserve">3.1125864982605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09309554100037</t>
+    <t xml:space="preserve">3.09309601783752</t>
   </si>
   <si>
     <t xml:space="preserve">3.0566565990448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01682758331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05750370025635</t>
+    <t xml:space="preserve">3.01682734489441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05750393867493</t>
   </si>
   <si>
     <t xml:space="preserve">3.06936764717102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07275748252869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03208112716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02953886985779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00072646141052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85581707954407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8702232837677</t>
+    <t xml:space="preserve">3.07275772094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03208136558533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02953910827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00072622299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85581684112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87022352218628</t>
   </si>
   <si>
     <t xml:space="preserve">2.88547706604004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95750784873962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88971400260925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02530169487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98208332061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00835299491882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97869348526001</t>
+    <t xml:space="preserve">2.95750761032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88971424102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02530193328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9820830821991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0083532333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97869372367859</t>
   </si>
   <si>
     <t xml:space="preserve">3.00326871871948</t>
@@ -3338,7 +3338,7 @@
     <t xml:space="preserve">3.02445459365845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04564023017883</t>
+    <t xml:space="preserve">3.04563999176025</t>
   </si>
   <si>
     <t xml:space="preserve">3.05072450637817</t>
@@ -3347,37 +3347,37 @@
     <t xml:space="preserve">3.06089377403259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11682343482971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10241723060608</t>
+    <t xml:space="preserve">3.11682319641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10241746902466</t>
   </si>
   <si>
     <t xml:space="preserve">3.14055132865906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11173892021179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08716368675232</t>
+    <t xml:space="preserve">3.11173915863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0871639251709</t>
   </si>
   <si>
     <t xml:space="preserve">3.02699661254883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01343774795532</t>
+    <t xml:space="preserve">3.0134379863739</t>
   </si>
   <si>
     <t xml:space="preserve">2.99394726753235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97106671333313</t>
+    <t xml:space="preserve">2.97106695175171</t>
   </si>
   <si>
     <t xml:space="preserve">2.98123574256897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94903373718262</t>
+    <t xml:space="preserve">2.9490339756012</t>
   </si>
   <si>
     <t xml:space="preserve">2.90835738182068</t>
@@ -3386,19 +3386,19 @@
     <t xml:space="preserve">2.91767907142639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97360873222351</t>
+    <t xml:space="preserve">2.97360897064209</t>
   </si>
   <si>
     <t xml:space="preserve">3.07614731788635</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14817833900452</t>
+    <t xml:space="preserve">3.14817810058594</t>
   </si>
   <si>
     <t xml:space="preserve">3.13377213478088</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07021522521973</t>
+    <t xml:space="preserve">3.07021546363831</t>
   </si>
   <si>
     <t xml:space="preserve">2.9388644695282</t>
@@ -3407,22 +3407,22 @@
     <t xml:space="preserve">2.88039231300354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9185266494751</t>
+    <t xml:space="preserve">2.91852641105652</t>
   </si>
   <si>
     <t xml:space="preserve">2.93801712989807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92530584335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86005425453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88717174530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87276554107666</t>
+    <t xml:space="preserve">2.92530560493469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86005401611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88717198371887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87276577949524</t>
   </si>
   <si>
     <t xml:space="preserve">2.84310579299927</t>
@@ -3434,7 +3434,7 @@
     <t xml:space="preserve">2.79734492301941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80836129188538</t>
+    <t xml:space="preserve">2.80836153030396</t>
   </si>
   <si>
     <t xml:space="preserve">2.82446241378784</t>
@@ -3446,10 +3446,10 @@
     <t xml:space="preserve">2.93632221221924</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8320894241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78971815109253</t>
+    <t xml:space="preserve">2.83208918571472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78971838951111</t>
   </si>
   <si>
     <t xml:space="preserve">2.76260042190552</t>
@@ -3461,22 +3461,22 @@
     <t xml:space="preserve">2.71175527572632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77446413040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87700271606445</t>
+    <t xml:space="preserve">2.77446436882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87700247764587</t>
   </si>
   <si>
     <t xml:space="preserve">2.86344385147095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85666465759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85157990455627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81937766075134</t>
+    <t xml:space="preserve">2.85666441917419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85158014297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81937789916992</t>
   </si>
   <si>
     <t xml:space="preserve">2.85412216186523</t>
@@ -3485,10 +3485,10 @@
     <t xml:space="preserve">2.89140892028809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7880232334137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75666880607605</t>
+    <t xml:space="preserve">2.78802347183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75666856765747</t>
   </si>
   <si>
     <t xml:space="preserve">2.814293384552</t>
@@ -3503,13 +3503,13 @@
     <t xml:space="preserve">2.83547878265381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87615537643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90750980377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00581121444702</t>
+    <t xml:space="preserve">2.87615513801575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90751004219055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00581097602844</t>
   </si>
   <si>
     <t xml:space="preserve">3.04733467102051</t>
@@ -3518,7 +3518,7 @@
     <t xml:space="preserve">3.00496363639832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0439453125</t>
+    <t xml:space="preserve">3.04394507408142</t>
   </si>
   <si>
     <t xml:space="preserve">3.05835127830505</t>
@@ -3527,16 +3527,16 @@
     <t xml:space="preserve">3.01598024368286</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04818201065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97276163101196</t>
+    <t xml:space="preserve">3.04818224906921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97276139259338</t>
   </si>
   <si>
     <t xml:space="preserve">2.98377799987793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9524233341217</t>
+    <t xml:space="preserve">2.95242357254028</t>
   </si>
   <si>
     <t xml:space="preserve">2.98632025718689</t>
@@ -3545,7 +3545,7 @@
     <t xml:space="preserve">3.06343579292297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84141087532043</t>
+    <t xml:space="preserve">2.84141063690186</t>
   </si>
   <si>
     <t xml:space="preserve">2.86513900756836</t>
@@ -3554,13 +3554,13 @@
     <t xml:space="preserve">2.92954301834106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95072865486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03801321983337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98801493644714</t>
+    <t xml:space="preserve">2.95072889328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03801298141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98801517486572</t>
   </si>
   <si>
     <t xml:space="preserve">2.96598219871521</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">2.82785201072693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86174917221069</t>
+    <t xml:space="preserve">2.86174893379211</t>
   </si>
   <si>
     <t xml:space="preserve">2.83717393875122</t>
@@ -3587,19 +3587,19 @@
     <t xml:space="preserve">2.72700881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53125381469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41685175895691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35668468475342</t>
+    <t xml:space="preserve">2.53125405311584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41685152053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35668444633484</t>
   </si>
   <si>
     <t xml:space="preserve">2.45837569236755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38888692855835</t>
+    <t xml:space="preserve">2.38888669013977</t>
   </si>
   <si>
     <t xml:space="preserve">2.41769909858704</t>
@@ -3611,7 +3611,7 @@
     <t xml:space="preserve">2.34250545501709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32569742202759</t>
+    <t xml:space="preserve">2.32569718360901</t>
   </si>
   <si>
     <t xml:space="preserve">2.37435221672058</t>
@@ -3620,10 +3620,10 @@
     <t xml:space="preserve">2.46193075180054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46812319755554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49908542633057</t>
+    <t xml:space="preserve">2.46812295913696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49908518791199</t>
   </si>
   <si>
     <t xml:space="preserve">2.47608494758606</t>
@@ -3632,28 +3632,28 @@
     <t xml:space="preserve">2.44158411026001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4875853061676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48493123054504</t>
+    <t xml:space="preserve">2.48758506774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48493099212646</t>
   </si>
   <si>
     <t xml:space="preserve">2.41327595710754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45750761032104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49112343788147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47696948051453</t>
+    <t xml:space="preserve">2.45750784873962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49112367630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47696924209595</t>
   </si>
   <si>
     <t xml:space="preserve">2.45927667617798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37523698806763</t>
+    <t xml:space="preserve">2.37523674964905</t>
   </si>
   <si>
     <t xml:space="preserve">2.30446624755859</t>
@@ -3662,13 +3662,13 @@
     <t xml:space="preserve">2.37789058685303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38673710823059</t>
+    <t xml:space="preserve">2.38673686981201</t>
   </si>
   <si>
     <t xml:space="preserve">2.41150689125061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38319849967957</t>
+    <t xml:space="preserve">2.38319826126099</t>
   </si>
   <si>
     <t xml:space="preserve">2.40619897842407</t>
@@ -3686,34 +3686,34 @@
     <t xml:space="preserve">2.43008399009705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44689226150513</t>
+    <t xml:space="preserve">2.44689202308655</t>
   </si>
   <si>
     <t xml:space="preserve">2.50970077514648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50527763366699</t>
+    <t xml:space="preserve">2.50527787208557</t>
   </si>
   <si>
     <t xml:space="preserve">2.47077703475952</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44246888160706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4398148059845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44335341453552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46900749206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47520017623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44954586029053</t>
+    <t xml:space="preserve">2.44246864318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43981504440308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4433536529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46900773048401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47520041465759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44954609870911</t>
   </si>
   <si>
     <t xml:space="preserve">2.43804574012756</t>
@@ -3731,37 +3731,37 @@
     <t xml:space="preserve">2.36904430389404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2965042591095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35312104225159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21158003807068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21246457099915</t>
+    <t xml:space="preserve">2.29650449752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35312128067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2115797996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21246433258057</t>
   </si>
   <si>
     <t xml:space="preserve">2.24342679977417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18504095077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07269239425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12842416763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11603975296021</t>
+    <t xml:space="preserve">2.18504071235657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07269263267517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12842440605164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11603951454163</t>
   </si>
   <si>
     <t xml:space="preserve">2.2009642124176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25934982299805</t>
+    <t xml:space="preserve">2.25935006141663</t>
   </si>
   <si>
     <t xml:space="preserve">2.23015713691711</t>
@@ -3776,7 +3776,7 @@
     <t xml:space="preserve">2.11957812309265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1063084602356</t>
+    <t xml:space="preserve">2.10630869865417</t>
   </si>
   <si>
     <t xml:space="preserve">2.07800054550171</t>
@@ -3788,34 +3788,34 @@
     <t xml:space="preserve">2.04261517524719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97803699970245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98422944545746</t>
+    <t xml:space="preserve">1.97803723812103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98422956466675</t>
   </si>
   <si>
     <t xml:space="preserve">1.87895834445953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92584383487701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91611278057098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93380546569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94442081451416</t>
+    <t xml:space="preserve">1.92584371566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91611266136169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93380570411682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94442105293274</t>
   </si>
   <si>
     <t xml:space="preserve">2.00192213058472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90018939971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84003436565399</t>
+    <t xml:space="preserve">1.90018951892853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84003448486328</t>
   </si>
   <si>
     <t xml:space="preserve">1.82588028907776</t>
@@ -3827,19 +3827,19 @@
     <t xml:space="preserve">1.80464923381805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77280247211456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80022621154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83030354976654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87807357311249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88249695301056</t>
+    <t xml:space="preserve">1.77280235290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80022609233856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83030343055725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87807369232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88249683380127</t>
   </si>
   <si>
     <t xml:space="preserve">1.8630348443985</t>
@@ -3851,28 +3851,28 @@
     <t xml:space="preserve">1.85153472423553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91257429122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99838364124298</t>
+    <t xml:space="preserve">1.91257441043854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99838352203369</t>
   </si>
   <si>
     <t xml:space="preserve">2.01696085929871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12577080726624</t>
+    <t xml:space="preserve">2.12577056884766</t>
   </si>
   <si>
     <t xml:space="preserve">2.13373231887817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14434766769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14257860183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13196301460266</t>
+    <t xml:space="preserve">2.14434790611267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14257836341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13196325302124</t>
   </si>
   <si>
     <t xml:space="preserve">2.1779637336731</t>
@@ -3884,13 +3884,13 @@
     <t xml:space="preserve">2.23281097412109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27969646453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30800485610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28058099746704</t>
+    <t xml:space="preserve">2.27969622612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30800461769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28058123588562</t>
   </si>
   <si>
     <t xml:space="preserve">2.29915857315063</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">2.33631300926208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32835125923157</t>
+    <t xml:space="preserve">2.32835149765015</t>
   </si>
   <si>
     <t xml:space="preserve">2.3274667263031</t>
@@ -3917,40 +3917,40 @@
     <t xml:space="preserve">2.34515929222107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35046744346619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33188962936401</t>
+    <t xml:space="preserve">2.35046720504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33188986778259</t>
   </si>
   <si>
     <t xml:space="preserve">2.34338998794556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35400557518005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37169814109802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37966012954712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37612175941467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43273782730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48050808906555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50350856781006</t>
+    <t xml:space="preserve">2.35400581359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3716983795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37965989112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37612152099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4327380657196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48050785064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50350832939148</t>
   </si>
   <si>
     <t xml:space="preserve">2.44600749015808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3106586933136</t>
+    <t xml:space="preserve">2.31065893173218</t>
   </si>
   <si>
     <t xml:space="preserve">2.25669622421265</t>
@@ -3962,7 +3962,7 @@
     <t xml:space="preserve">2.26200389862061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24165725708008</t>
+    <t xml:space="preserve">2.24165749549866</t>
   </si>
   <si>
     <t xml:space="preserve">2.25758075714111</t>
@@ -3971,22 +3971,22 @@
     <t xml:space="preserve">2.25492691993713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20273375511169</t>
+    <t xml:space="preserve">2.20273327827454</t>
   </si>
   <si>
     <t xml:space="preserve">2.25227308273315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22838807106018</t>
+    <t xml:space="preserve">2.2283878326416</t>
   </si>
   <si>
     <t xml:space="preserve">2.28765821456909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2894275188446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3354287147522</t>
+    <t xml:space="preserve">2.28942728042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33542847633362</t>
   </si>
   <si>
     <t xml:space="preserve">2.32304334640503</t>
@@ -4010,7 +4010,7 @@
     <t xml:space="preserve">2.34781312942505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38850617408752</t>
+    <t xml:space="preserve">2.3885064125061</t>
   </si>
   <si>
     <t xml:space="preserve">2.41416072845459</t>
@@ -4025,13 +4025,13 @@
     <t xml:space="preserve">2.34692859649658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34073615074158</t>
+    <t xml:space="preserve">2.340735912323</t>
   </si>
   <si>
     <t xml:space="preserve">2.3442747592926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41062188148499</t>
+    <t xml:space="preserve">2.41062211990356</t>
   </si>
   <si>
     <t xml:space="preserve">2.37081384658813</t>
@@ -4043,28 +4043,28 @@
     <t xml:space="preserve">2.28854274749756</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29561996459961</t>
+    <t xml:space="preserve">2.29562020301819</t>
   </si>
   <si>
     <t xml:space="preserve">2.3000431060791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29473567008972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2664270401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23458027839661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22661852836609</t>
+    <t xml:space="preserve">2.29473543167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26642727851868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23458051681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22661876678467</t>
   </si>
   <si>
     <t xml:space="preserve">2.22219562530518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23192667961121</t>
+    <t xml:space="preserve">2.23192644119263</t>
   </si>
   <si>
     <t xml:space="preserve">2.1753101348877</t>
@@ -4076,7 +4076,7 @@
     <t xml:space="preserve">2.22573399543762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1815025806427</t>
+    <t xml:space="preserve">2.18150234222412</t>
   </si>
   <si>
     <t xml:space="preserve">2.15054035186768</t>
@@ -4085,13 +4085,13 @@
     <t xml:space="preserve">2.1125009059906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10807776451111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13727045059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12753987312317</t>
+    <t xml:space="preserve">2.10807800292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13727068901062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12753963470459</t>
   </si>
   <si>
     <t xml:space="preserve">2.11692404747009</t>
@@ -4103,13 +4103,13 @@
     <t xml:space="preserve">2.20627212524414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22131085395813</t>
+    <t xml:space="preserve">2.22131061553955</t>
   </si>
   <si>
     <t xml:space="preserve">2.20361804962158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21423387527466</t>
+    <t xml:space="preserve">2.21423363685608</t>
   </si>
   <si>
     <t xml:space="preserve">2.24254202842712</t>
@@ -4124,10 +4124,10 @@
     <t xml:space="preserve">2.40266036987305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42212247848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31950521469116</t>
+    <t xml:space="preserve">2.42212224006653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31950497627258</t>
   </si>
   <si>
     <t xml:space="preserve">2.39558339118958</t>
@@ -4136,28 +4136,28 @@
     <t xml:space="preserve">2.39027547836304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46989250183105</t>
+    <t xml:space="preserve">2.46989226341248</t>
   </si>
   <si>
     <t xml:space="preserve">2.49820065498352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44512271881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49643158912659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53181648254395</t>
+    <t xml:space="preserve">2.44512248039246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49643135070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53181672096252</t>
   </si>
   <si>
     <t xml:space="preserve">2.52297043800354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54066276550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62381863594055</t>
+    <t xml:space="preserve">2.54066300392151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62381839752197</t>
   </si>
   <si>
     <t xml:space="preserve">2.65035724639893</t>
@@ -4166,46 +4166,46 @@
     <t xml:space="preserve">2.67689633369446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67866563796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6379725933075</t>
+    <t xml:space="preserve">2.67866587638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63797283172607</t>
   </si>
   <si>
     <t xml:space="preserve">2.53712439537048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61497235298157</t>
+    <t xml:space="preserve">2.61497211456299</t>
   </si>
   <si>
     <t xml:space="preserve">2.63266468048096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62204909324646</t>
+    <t xml:space="preserve">2.62204885482788</t>
   </si>
   <si>
     <t xml:space="preserve">2.54950928688049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52827835083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57958674430847</t>
+    <t xml:space="preserve">2.5282781124115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57958650588989</t>
   </si>
   <si>
     <t xml:space="preserve">2.58135604858398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60966420173645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58666372299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59020256996155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.538893699646</t>
+    <t xml:space="preserve">2.60966444015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58666396141052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59020233154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53889346122742</t>
   </si>
   <si>
     <t xml:space="preserve">2.572509765625</t>
@@ -4217,22 +4217,22 @@
     <t xml:space="preserve">2.55304765701294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56366348266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55127859115601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53004717826843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56897115707397</t>
+    <t xml:space="preserve">2.56366324424744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55127882957458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53004741668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56897139549255</t>
   </si>
   <si>
     <t xml:space="preserve">2.51812791824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52922129631042</t>
+    <t xml:space="preserve">2.52922105789185</t>
   </si>
   <si>
     <t xml:space="preserve">2.53661632537842</t>
@@ -4259,16 +4259,16 @@
     <t xml:space="preserve">2.46451139450073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41274356842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40904593467712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42013907432556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44787192344666</t>
+    <t xml:space="preserve">2.41274380683899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4090461730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42013931274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44787168502808</t>
   </si>
   <si>
     <t xml:space="preserve">2.47375583648682</t>
@@ -4289,10 +4289,10 @@
     <t xml:space="preserve">2.52737212181091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54216289520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53846549987793</t>
+    <t xml:space="preserve">2.54216313362122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53846526145935</t>
   </si>
   <si>
     <t xml:space="preserve">2.58653521537781</t>
@@ -4301,7 +4301,7 @@
     <t xml:space="preserve">2.56250047683716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59393048286438</t>
+    <t xml:space="preserve">2.59393072128296</t>
   </si>
   <si>
     <t xml:space="preserve">2.63275647163391</t>
@@ -4316,10 +4316,10 @@
     <t xml:space="preserve">2.60132598876953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45711612701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39980173110962</t>
+    <t xml:space="preserve">2.45711588859558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3998019695282</t>
   </si>
   <si>
     <t xml:space="preserve">2.44602274894714</t>
@@ -4331,10 +4331,10 @@
     <t xml:space="preserve">2.47190690040588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47005772590637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42383694648743</t>
+    <t xml:space="preserve">2.47005796432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42383670806885</t>
   </si>
   <si>
     <t xml:space="preserve">2.38316226005554</t>
@@ -4346,34 +4346,34 @@
     <t xml:space="preserve">2.49594187736511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52182579040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5403139591217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55140709877014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57913994789124</t>
+    <t xml:space="preserve">2.52182555198669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54031419754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55140733718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57913970947266</t>
   </si>
   <si>
     <t xml:space="preserve">2.5680468082428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58468627929688</t>
+    <t xml:space="preserve">2.58468651771545</t>
   </si>
   <si>
     <t xml:space="preserve">2.57544207572937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54770970344543</t>
+    <t xml:space="preserve">2.54770946502686</t>
   </si>
   <si>
     <t xml:space="preserve">2.60687255859375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60317468643188</t>
+    <t xml:space="preserve">2.60317492485046</t>
   </si>
   <si>
     <t xml:space="preserve">2.6456983089447</t>
@@ -4397,7 +4397,7 @@
     <t xml:space="preserve">2.667884349823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69376826286316</t>
+    <t xml:space="preserve">2.69376850128174</t>
   </si>
   <si>
     <t xml:space="preserve">2.56434917449951</t>
@@ -4430,22 +4430,22 @@
     <t xml:space="preserve">2.35358071327209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39795327186584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41089487075806</t>
+    <t xml:space="preserve">2.39795303344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41089510917664</t>
   </si>
   <si>
     <t xml:space="preserve">2.42753434181213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40534853935242</t>
+    <t xml:space="preserve">2.40534830093384</t>
   </si>
   <si>
     <t xml:space="preserve">2.39240646362305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37206935882568</t>
+    <t xml:space="preserve">2.3720691204071</t>
   </si>
   <si>
     <t xml:space="preserve">2.34988307952881</t>
@@ -4460,7 +4460,7 @@
     <t xml:space="preserve">2.34803414344788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45341825485229</t>
+    <t xml:space="preserve">2.45341849327087</t>
   </si>
   <si>
     <t xml:space="preserve">2.49224424362183</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">2.49779057502747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4626624584198</t>
+    <t xml:space="preserve">2.46266269683838</t>
   </si>
   <si>
     <t xml:space="preserve">2.45526719093323</t>
@@ -4487,7 +4487,7 @@
     <t xml:space="preserve">2.62536096572876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64015173912048</t>
+    <t xml:space="preserve">2.64015197753906</t>
   </si>
   <si>
     <t xml:space="preserve">2.62720990180969</t>
@@ -4496,19 +4496,19 @@
     <t xml:space="preserve">2.63090753555298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68082642555237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68637299537659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68822193145752</t>
+    <t xml:space="preserve">2.68082666397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68637275695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68822169303894</t>
   </si>
   <si>
     <t xml:space="preserve">2.66603565216064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68267512321472</t>
+    <t xml:space="preserve">2.6826753616333</t>
   </si>
   <si>
     <t xml:space="preserve">2.68452405929565</t>
@@ -4517,19 +4517,19 @@
     <t xml:space="preserve">2.69007062911987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74368691444397</t>
+    <t xml:space="preserve">2.74368715286255</t>
   </si>
   <si>
     <t xml:space="preserve">2.71225690841675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69561719894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73444271087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80100131034851</t>
+    <t xml:space="preserve">2.69561696052551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73444294929504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80100154876709</t>
   </si>
   <si>
     <t xml:space="preserve">2.78990817070007</t>
@@ -4541,7 +4541,7 @@
     <t xml:space="preserve">2.79545474052429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78621077537537</t>
+    <t xml:space="preserve">2.78621053695679</t>
   </si>
   <si>
     <t xml:space="preserve">2.76772212982178</t>
@@ -4553,7 +4553,7 @@
     <t xml:space="preserve">2.75662922859192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73998951911926</t>
+    <t xml:space="preserve">2.73998928070068</t>
   </si>
   <si>
     <t xml:space="preserve">2.74738478660583</t>
@@ -4601,22 +4601,22 @@
     <t xml:space="preserve">2.98033928871155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96924638748169</t>
+    <t xml:space="preserve">2.96924614906311</t>
   </si>
   <si>
     <t xml:space="preserve">3.02286291122437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92672300338745</t>
+    <t xml:space="preserve">2.92672276496887</t>
   </si>
   <si>
     <t xml:space="preserve">2.91562986373901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87495493888855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90083909034729</t>
+    <t xml:space="preserve">2.87495517730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90083885192871</t>
   </si>
   <si>
     <t xml:space="preserve">2.9193274974823</t>
@@ -4643,7 +4643,7 @@
     <t xml:space="preserve">2.99513030052185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98773503303528</t>
+    <t xml:space="preserve">2.9877347946167</t>
   </si>
   <si>
     <t xml:space="preserve">2.98958349227905</t>
@@ -4652,16 +4652,16 @@
     <t xml:space="preserve">2.93411827087402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96000218391418</t>
+    <t xml:space="preserve">2.96000194549561</t>
   </si>
   <si>
     <t xml:space="preserve">2.94890904426575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95445561408997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97849059104919</t>
+    <t xml:space="preserve">2.95445585250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97849035263062</t>
   </si>
   <si>
     <t xml:space="preserve">2.95260691642761</t>
@@ -4685,10 +4685,10 @@
     <t xml:space="preserve">3.08572363853455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09496784210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11900305747986</t>
+    <t xml:space="preserve">3.09496808052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11900281906128</t>
   </si>
   <si>
     <t xml:space="preserve">3.05983972549438</t>
@@ -4706,13 +4706,13 @@
     <t xml:space="preserve">3.06908392906189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02471160888672</t>
+    <t xml:space="preserve">3.0247118473053</t>
   </si>
   <si>
     <t xml:space="preserve">3.01916527748108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97479271888733</t>
+    <t xml:space="preserve">2.97479295730591</t>
   </si>
   <si>
     <t xml:space="preserve">2.92302513122559</t>
@@ -4721,7 +4721,7 @@
     <t xml:space="preserve">2.93781590461731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88419914245605</t>
+    <t xml:space="preserve">2.88419938087463</t>
   </si>
   <si>
     <t xml:space="preserve">2.90823435783386</t>
@@ -4736,19 +4736,19 @@
     <t xml:space="preserve">2.95815324783325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97109532356262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01546740531921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11345624923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13933992385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10975885391235</t>
+    <t xml:space="preserve">2.97109508514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01546764373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11345648765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13934016227722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10975861549377</t>
   </si>
   <si>
     <t xml:space="preserve">3.16337513923645</t>
@@ -4757,7 +4757,7 @@
     <t xml:space="preserve">3.13379383087158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15782833099365</t>
+    <t xml:space="preserve">3.15782856941223</t>
   </si>
   <si>
     <t xml:space="preserve">3.16892170906067</t>
@@ -4766,7 +4766,7 @@
     <t xml:space="preserve">3.19480562210083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24287557601929</t>
+    <t xml:space="preserve">3.24287533760071</t>
   </si>
   <si>
     <t xml:space="preserve">3.20959615707397</t>
@@ -4775,7 +4775,7 @@
     <t xml:space="preserve">3.20589852333069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23548007011414</t>
+    <t xml:space="preserve">3.23548030853271</t>
   </si>
   <si>
     <t xml:space="preserve">3.29464316368103</t>
@@ -4790,10 +4790,10 @@
     <t xml:space="preserve">3.20774745941162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17446804046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12085175514221</t>
+    <t xml:space="preserve">3.17446827888489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12085151672363</t>
   </si>
   <si>
     <t xml:space="preserve">3.07832813262939</t>
@@ -4805,7 +4805,7 @@
     <t xml:space="preserve">3.09866547584534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07647967338562</t>
+    <t xml:space="preserve">3.07647943496704</t>
   </si>
   <si>
     <t xml:space="preserve">3.06723523139954</t>
@@ -4820,19 +4820,19 @@
     <t xml:space="preserve">3.19665431976318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20404982566833</t>
+    <t xml:space="preserve">3.20405006408691</t>
   </si>
   <si>
     <t xml:space="preserve">3.19850325584412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1245493888855</t>
+    <t xml:space="preserve">3.12454962730408</t>
   </si>
   <si>
     <t xml:space="preserve">3.16707301139832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14858412742615</t>
+    <t xml:space="preserve">3.14858436584473</t>
   </si>
   <si>
     <t xml:space="preserve">3.00067663192749</t>
@@ -4841,7 +4841,7 @@
     <t xml:space="preserve">3.04874682426453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10051465034485</t>
+    <t xml:space="preserve">3.10051441192627</t>
   </si>
   <si>
     <t xml:space="preserve">3.14488673210144</t>
@@ -5628,6 +5628,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.89000010490417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94799995422363</t>
   </si>
 </sst>
 </file>
@@ -70992,7 +70995,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.691087963</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>2998899</v>
@@ -71013,6 +71016,32 @@
         <v>1871</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6909953704</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>2582552</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>3.94799995422363</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>3.88800001144409</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>3.88800001144409</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>3.94799995422363</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>1872</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HER.MI.xlsx
+++ b/data/HER.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="1874">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1875" uniqueCount="1875">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,49 +38,49 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70756638050079</t>
+    <t xml:space="preserve">1.70756649971008</t>
   </si>
   <si>
     <t xml:space="preserve">HER.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70896410942078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70616924762726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71036088466644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68800354003906</t>
+    <t xml:space="preserve">1.7089638710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70616900920868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71036124229431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68800342082977</t>
   </si>
   <si>
     <t xml:space="preserve">1.72573208808899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79140758514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79420244693756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7704473733902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74669229984283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70337414741516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77324235439301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74948680400848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76625537872314</t>
+    <t xml:space="preserve">1.79140746593475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79420220851898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77044713497162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7466926574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70337438583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77324199676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74948704242706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76625525951385</t>
   </si>
   <si>
     <t xml:space="preserve">1.80538141727448</t>
@@ -92,130 +92,130 @@
     <t xml:space="preserve">1.80398392677307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83472526073456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81655991077423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80258655548096</t>
+    <t xml:space="preserve">1.83472573757172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81656002998352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80258619785309</t>
   </si>
   <si>
     <t xml:space="preserve">1.8486989736557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85568594932556</t>
+    <t xml:space="preserve">1.85568571090698</t>
   </si>
   <si>
     <t xml:space="preserve">1.84031510353088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82354664802551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82913613319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72852671146393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74110281467438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75926804542542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69918239116669</t>
+    <t xml:space="preserve">1.82354688644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82913625240326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72852694988251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74110329151154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75926828384399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69918191432953</t>
   </si>
   <si>
     <t xml:space="preserve">1.75507640838623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79559934139252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78302347660065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77603697776794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79839444160461</t>
+    <t xml:space="preserve">1.79559981822968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78302359580994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77603673934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79839432239532</t>
   </si>
   <si>
     <t xml:space="preserve">1.80118918418884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82075202465057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8305332660675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78861284255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76485776901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74529480934143</t>
+    <t xml:space="preserve">1.82075214385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83053350448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78861308097839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76485788822174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74529504776001</t>
   </si>
   <si>
     <t xml:space="preserve">1.73970568180084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72992408275604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74389803409576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73271906375885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76346063613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77883172035217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76066601276398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77463960647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7969970703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83752071857452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81097054481506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85708332061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84311020374298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76765275001526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78162610530853</t>
+    <t xml:space="preserve">1.72992420196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74389779567719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73271870613098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76346039772034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77883148193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76066553592682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77463936805725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79699730873108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83752036094666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81097030639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85708343982697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84310960769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76765239238739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78162598609924</t>
   </si>
   <si>
     <t xml:space="preserve">1.78721570968628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7774338722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78022885322571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8081761598587</t>
+    <t xml:space="preserve">1.77743422985077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78022909164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80817592144012</t>
   </si>
   <si>
     <t xml:space="preserve">1.80957305431366</t>
@@ -227,19 +227,19 @@
     <t xml:space="preserve">1.78442084789276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75647389888763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74808979034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82634139060974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84590435028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83193099498749</t>
+    <t xml:space="preserve">1.75647377967834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74809002876282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82634162902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84590411186218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83193111419678</t>
   </si>
   <si>
     <t xml:space="preserve">1.84450697898865</t>
@@ -254,82 +254,82 @@
     <t xml:space="preserve">1.82494425773621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81376504898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76206314563751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73132121562958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74250030517578</t>
+    <t xml:space="preserve">1.81376528739929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76206338405609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73132133483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74250018596649</t>
   </si>
   <si>
     <t xml:space="preserve">1.71175873279572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75751066207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77344810962677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74012386798859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75895953178406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70390105247498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6734744310379</t>
+    <t xml:space="preserve">1.75751030445099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77344822883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74012351036072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75895929336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70390117168427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67347419261932</t>
   </si>
   <si>
     <t xml:space="preserve">1.70969676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73867464065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78069269657135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83430194854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80822169780731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81111979484558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78503942489624</t>
+    <t xml:space="preserve">1.73867475986481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78069257736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83430159091949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8082218170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81111967563629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78503930568695</t>
   </si>
   <si>
     <t xml:space="preserve">1.77924370765686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72708368301392</t>
+    <t xml:space="preserve">1.72708356380463</t>
   </si>
   <si>
     <t xml:space="preserve">1.76040804386139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7459192276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77055048942566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76620388031006</t>
+    <t xml:space="preserve">1.74591934680939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77055037021637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76620399951935</t>
   </si>
   <si>
     <t xml:space="preserve">1.76185691356659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76910150051117</t>
+    <t xml:space="preserve">1.76910161972046</t>
   </si>
   <si>
     <t xml:space="preserve">1.77489733695984</t>
@@ -341,130 +341,133 @@
     <t xml:space="preserve">1.83719956874847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85748434066772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85023963451385</t>
+    <t xml:space="preserve">1.85748410224915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85023951530457</t>
   </si>
   <si>
     <t xml:space="preserve">1.83575069904327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86617767810822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83140408992767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84444403648376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79663038253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81981301307678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81256854534149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7488169670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74447011947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77634584903717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79083490371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79952847957611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78648853302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78938627243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81546640396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75606119632721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73577678203583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70679926872253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73722577095032</t>
+    <t xml:space="preserve">1.86617732048035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83140420913696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84444427490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79663062095642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81981289386749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8125684261322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74881708621979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74447023868561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76765263080597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77634620666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79083478450775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79952812194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78648841381073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78938615322113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81546604633331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7560613155365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73577690124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70679903030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73722565174103</t>
   </si>
   <si>
     <t xml:space="preserve">1.75461256504059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71114563941956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70824790000916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70245218276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69230997562408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71694123744965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69665682315826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63145637512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6053763628006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59233629703522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57929646968842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.601029753685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60972285270691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61406970024109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62131416797638</t>
+    <t xml:space="preserve">1.71114575862885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70824813842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70245230197906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69230985641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71694099903107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69665694236755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63145625591278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60537660121918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59233617782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57929623126984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60102963447571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60972309112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6140695810318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62131404876709</t>
   </si>
   <si>
     <t xml:space="preserve">1.63290524482727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61841630935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63870096206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63725209236145</t>
+    <t xml:space="preserve">1.61841654777527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63870084285736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63725197315216</t>
   </si>
   <si>
     <t xml:space="preserve">1.65029227733612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62276315689087</t>
+    <t xml:space="preserve">1.62276303768158</t>
   </si>
   <si>
     <t xml:space="preserve">1.615518450737</t>
@@ -473,16 +476,16 @@
     <t xml:space="preserve">1.61696755886078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62566089630127</t>
+    <t xml:space="preserve">1.62566077709198</t>
   </si>
   <si>
     <t xml:space="preserve">1.66188335418701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66912770271301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68796336650848</t>
+    <t xml:space="preserve">1.66912758350372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68796360492706</t>
   </si>
   <si>
     <t xml:space="preserve">1.59378516674042</t>
@@ -491,10 +494,10 @@
     <t xml:space="preserve">1.56625628471375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56335830688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54307389259338</t>
+    <t xml:space="preserve">1.56335842609406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54307401180267</t>
   </si>
   <si>
     <t xml:space="preserve">1.46048676967621</t>
@@ -512,40 +515,40 @@
     <t xml:space="preserve">1.45034456253052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43005990982056</t>
+    <t xml:space="preserve">1.43006002902985</t>
   </si>
   <si>
     <t xml:space="preserve">1.42209100723267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39601075649261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39456188678741</t>
+    <t xml:space="preserve">1.39601099491119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3945620059967</t>
   </si>
   <si>
     <t xml:space="preserve">1.40905106067657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41267311573029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39818406105042</t>
+    <t xml:space="preserve">1.41267335414886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3981841802597</t>
   </si>
   <si>
     <t xml:space="preserve">1.40180647373199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40542876720428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41629540920258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38152182102203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35906422138214</t>
+    <t xml:space="preserve">1.40542888641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41629552841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38152170181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35906410217285</t>
   </si>
   <si>
     <t xml:space="preserve">1.37717533111572</t>
@@ -557,7 +560,7 @@
     <t xml:space="preserve">1.48077118396759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49236261844635</t>
+    <t xml:space="preserve">1.49236249923706</t>
   </si>
   <si>
     <t xml:space="preserve">1.48511791229248</t>
@@ -569,133 +572,133 @@
     <t xml:space="preserve">1.52713584899902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50105583667755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50685119628906</t>
+    <t xml:space="preserve">1.50105595588684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50685131549835</t>
   </si>
   <si>
     <t xml:space="preserve">1.54886937141418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55756282806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57060289382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59088742733002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56915366649628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58798944950104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.608274102211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59668302536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59958064556122</t>
+    <t xml:space="preserve">1.55756294727325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57060277462006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59088730812073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56915378570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58798956871033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60827422142029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59668278694153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59958052635193</t>
   </si>
   <si>
     <t xml:space="preserve">1.56480741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65174078941345</t>
+    <t xml:space="preserve">1.65174090862274</t>
   </si>
   <si>
     <t xml:space="preserve">1.64159882068634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65318989753723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65463864803314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65898525714874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64014983177185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64304733276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57494950294495</t>
+    <t xml:space="preserve">1.65319001674652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65463876724243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65898537635803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64014971256256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64304757118225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57494962215424</t>
   </si>
   <si>
     <t xml:space="preserve">1.57784724235535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55176711082458</t>
+    <t xml:space="preserve">1.55176723003387</t>
   </si>
   <si>
     <t xml:space="preserve">1.58654069900513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63000762462616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68216800689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6662300825119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6778210401535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69086122512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69375908374786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69810581207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6952075958252</t>
+    <t xml:space="preserve">1.63000738620758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68216788768768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66622984409332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67782092094421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69086146354675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69375896453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69810593128204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69520783424377</t>
   </si>
   <si>
     <t xml:space="preserve">1.71404337882996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72998118400574</t>
+    <t xml:space="preserve">1.72998130321503</t>
   </si>
   <si>
     <t xml:space="preserve">1.7343282699585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71983897686005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72418594360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71549236774445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71839022636414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7415726184845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78214144706726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78793704509735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81401717662811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82995522022247</t>
+    <t xml:space="preserve">1.71983885765076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72418582439423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71549248695374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71838998794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74157249927521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78214156627655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78793692588806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8140172958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82995498180389</t>
   </si>
   <si>
     <t xml:space="preserve">1.86907517910004</t>
@@ -707,55 +710,55 @@
     <t xml:space="preserve">1.91399109363556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91544032096863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88066637516022</t>
+    <t xml:space="preserve">1.91543996334076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88066613674164</t>
   </si>
   <si>
     <t xml:space="preserve">1.87197315692902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88935959339142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90095114707947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90529763698578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91254234313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94441819190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93717324733734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87921798229218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88356447219849</t>
+    <t xml:space="preserve">1.88936018943787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90095126628876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90529787540436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91254186630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94441795349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93717348575592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87921786308289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8835643529892</t>
   </si>
   <si>
     <t xml:space="preserve">1.92848014831543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89805328845978</t>
+    <t xml:space="preserve">1.89805316925049</t>
   </si>
   <si>
     <t xml:space="preserve">1.8879109621048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9023996591568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91688847541809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92413353919983</t>
+    <t xml:space="preserve">1.90240001678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91688871383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92413318157196</t>
   </si>
   <si>
     <t xml:space="preserve">1.93572449684143</t>
@@ -764,19 +767,19 @@
     <t xml:space="preserve">1.93862223625183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94876480102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99512922763824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02845406532288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05743169784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06902313232422</t>
+    <t xml:space="preserve">1.9487646818161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99512910842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0284538269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05743193626404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06902289390564</t>
   </si>
   <si>
     <t xml:space="preserve">2.05163645744324</t>
@@ -785,19 +788,19 @@
     <t xml:space="preserve">2.1023473739624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06467628479004</t>
+    <t xml:space="preserve">2.06467604637146</t>
   </si>
   <si>
     <t xml:space="preserve">2.03859567642212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07336974143982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08640956878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12842750549316</t>
+    <t xml:space="preserve">2.07336950302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08640933036804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12842726707458</t>
   </si>
   <si>
     <t xml:space="preserve">2.11248993873596</t>
@@ -809,37 +812,37 @@
     <t xml:space="preserve">2.1008985042572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05453395843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08930778503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12263178825378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07916498184204</t>
+    <t xml:space="preserve">2.05453419685364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08930730819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12263202667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07916522026062</t>
   </si>
   <si>
     <t xml:space="preserve">2.1037962436676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11973428726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10814309120178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14726328849792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13277459144592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15450739860535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14291644096375</t>
+    <t xml:space="preserve">2.11973452568054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1081428527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14726305007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13277435302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15450763702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1429169178009</t>
   </si>
   <si>
     <t xml:space="preserve">2.15595674514771</t>
@@ -848,43 +851,40 @@
     <t xml:space="preserve">2.16790914535522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17836785316467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17239165306091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15595650672913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09918189048767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11262845993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07228827476501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05884170532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01700735092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99907839298248</t>
+    <t xml:space="preserve">2.17836809158325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17239141464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09918165206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.112628698349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07228851318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05884146690369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01700711250305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99907827377319</t>
   </si>
   <si>
     <t xml:space="preserve">2.01103091239929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00804305076599</t>
+    <t xml:space="preserve">2.00804281234741</t>
   </si>
   <si>
     <t xml:space="preserve">1.99758434295654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95126807689667</t>
+    <t xml:space="preserve">1.95126760005951</t>
   </si>
   <si>
     <t xml:space="preserve">1.97069072723389</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">1.98264348506927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03045392036438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05286502838135</t>
+    <t xml:space="preserve">2.03045415878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05286526679993</t>
   </si>
   <si>
     <t xml:space="preserve">2.0394184589386</t>
@@ -911,67 +911,67 @@
     <t xml:space="preserve">2.04539489746094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02447772026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06183004379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07677006721497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03344225883484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01401948928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05435967445374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04390096664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04240679740906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0364305973053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04838299751282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04987740516663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00206661224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05585360527039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03493571281433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99459588527679</t>
+    <t xml:space="preserve">2.02447748184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06182956695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07677030563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03344249725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01401925086975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05435943603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04390048980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0424063205719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03643035888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0483832359314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04987716674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00206685066223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05585336685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03493595123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99459624290466</t>
   </si>
   <si>
     <t xml:space="preserve">1.97517311573029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96172630786896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96770298480988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02597188949585</t>
+    <t xml:space="preserve">1.96172642707825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96770262718201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02597212791443</t>
   </si>
   <si>
     <t xml:space="preserve">2.01252508163452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00953722000122</t>
+    <t xml:space="preserve">2.00953698158264</t>
   </si>
   <si>
     <t xml:space="preserve">2.0035605430603</t>
@@ -986,16 +986,16 @@
     <t xml:space="preserve">2.000572681427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98563170433044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98712575435638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9721851348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02148985862732</t>
+    <t xml:space="preserve">1.98563182353973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98712599277496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97218465805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02148962020874</t>
   </si>
   <si>
     <t xml:space="preserve">2.03792452812195</t>
@@ -1010,31 +1010,31 @@
     <t xml:space="preserve">2.07378244400024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06631207466125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06332397460938</t>
+    <t xml:space="preserve">2.0663115978241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0633237361908</t>
   </si>
   <si>
     <t xml:space="preserve">2.07527661323547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08424067497253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10665202140808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12458086013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14998030662537</t>
+    <t xml:space="preserve">2.08424091339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10665154457092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12458109855652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14998054504395</t>
   </si>
   <si>
     <t xml:space="preserve">2.16043901443481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18135595321655</t>
+    <t xml:space="preserve">2.18135619163513</t>
   </si>
   <si>
     <t xml:space="preserve">2.19629693031311</t>
@@ -1043,49 +1043,49 @@
     <t xml:space="preserve">2.18733215332031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17986226081848</t>
+    <t xml:space="preserve">2.1798620223999</t>
   </si>
   <si>
     <t xml:space="preserve">2.16641521453857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17089772224426</t>
+    <t xml:space="preserve">2.17089748382568</t>
   </si>
   <si>
     <t xml:space="preserve">2.19181442260742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19330859184265</t>
+    <t xml:space="preserve">2.19330883026123</t>
   </si>
   <si>
     <t xml:space="preserve">2.1948025226593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.224684715271</t>
+    <t xml:space="preserve">2.22468447685242</t>
   </si>
   <si>
     <t xml:space="preserve">2.27100086212158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2560601234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25904822349548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28145933151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29490613937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30536437034607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30088233947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33972859382629</t>
+    <t xml:space="preserve">2.25606036186218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2590479850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28145956993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29490637779236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30536484718323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30088257789612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33972883224487</t>
   </si>
   <si>
     <t xml:space="preserve">2.28892970085144</t>
@@ -1094,46 +1094,46 @@
     <t xml:space="preserve">2.27398896217346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.303870677948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31582307815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25456619262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25755429267883</t>
+    <t xml:space="preserve">2.30387043952942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3158233165741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25456595420837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25755405426025</t>
   </si>
   <si>
     <t xml:space="preserve">2.27847123146057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22916674613953</t>
+    <t xml:space="preserve">2.22916650772095</t>
   </si>
   <si>
     <t xml:space="preserve">2.22617840766907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21870827674866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17388558387756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15446305274963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21123790740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26054263114929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31134104728699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24111914634705</t>
+    <t xml:space="preserve">2.21870803833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17388534545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15446257591248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21123766899109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26054239273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31134080886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24111938476562</t>
   </si>
   <si>
     <t xml:space="preserve">2.26950693130493</t>
@@ -1142,13 +1142,13 @@
     <t xml:space="preserve">2.23813104629517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27697706222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28594183921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29938817024231</t>
+    <t xml:space="preserve">2.27697730064392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28594160079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29938840866089</t>
   </si>
   <si>
     <t xml:space="preserve">2.24709534645081</t>
@@ -1157,43 +1157,43 @@
     <t xml:space="preserve">2.2799654006958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24560141563416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18434405326843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13503980636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11113452911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05734753608704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02895998954773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09469938278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12607502937317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13354563713074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09320521354675</t>
+    <t xml:space="preserve">2.24560189247131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18434429168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13503956794739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11113429069519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05734729766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02896022796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0946991443634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12607526779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13354539871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09320569038391</t>
   </si>
   <si>
     <t xml:space="preserve">2.06930017471313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04091238975525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08573508262634</t>
+    <t xml:space="preserve">2.04091286659241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08573532104492</t>
   </si>
   <si>
     <t xml:space="preserve">2.08274698257446</t>
@@ -1208,10 +1208,10 @@
     <t xml:space="preserve">2.09768795967102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12009859085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21273183822632</t>
+    <t xml:space="preserve">2.12009906768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21273159980774</t>
   </si>
   <si>
     <t xml:space="preserve">2.22169613838196</t>
@@ -1220,31 +1220,31 @@
     <t xml:space="preserve">2.23066067695618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24261331558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26353025436401</t>
+    <t xml:space="preserve">2.24261379241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26353049278259</t>
   </si>
   <si>
     <t xml:space="preserve">2.23514294624329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25307202339172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29341173171997</t>
+    <t xml:space="preserve">2.2530722618103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29341197013855</t>
   </si>
   <si>
     <t xml:space="preserve">2.29789423942566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28444743156433</t>
+    <t xml:space="preserve">2.28444766998291</t>
   </si>
   <si>
     <t xml:space="preserve">2.2276725769043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25157761573792</t>
+    <t xml:space="preserve">2.25157785415649</t>
   </si>
   <si>
     <t xml:space="preserve">2.14101576805115</t>
@@ -1253,73 +1253,73 @@
     <t xml:space="preserve">2.12159299850464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02298331260681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94678568840027</t>
+    <t xml:space="preserve">2.02298355102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94678556919098</t>
   </si>
   <si>
     <t xml:space="preserve">1.96471476554871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98114907741547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96919691562653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97816109657288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94827961921692</t>
+    <t xml:space="preserve">1.98114955425262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96919655799866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97816121578217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94827997684479</t>
   </si>
   <si>
     <t xml:space="preserve">2.02856683731079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06108570098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07192540168762</t>
+    <t xml:space="preserve">2.06108593940735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0719256401062</t>
   </si>
   <si>
     <t xml:space="preserve">2.03785800933838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04095482826233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07347416877747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05953693389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08895921707153</t>
+    <t xml:space="preserve">2.04095458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07347393035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05953741073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08895897865295</t>
   </si>
   <si>
     <t xml:space="preserve">2.06728005409241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10599303245544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13541483879089</t>
+    <t xml:space="preserve">2.10599327087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13541460037231</t>
   </si>
   <si>
     <t xml:space="preserve">2.15399718284607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16019082069397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14470601081848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13696360588074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14780282974243</t>
+    <t xml:space="preserve">2.16019129753113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14470624923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13696312904358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14780330657959</t>
   </si>
   <si>
     <t xml:space="preserve">2.13386631011963</t>
@@ -1334,10 +1334,10 @@
     <t xml:space="preserve">2.1524486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1044442653656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09205627441406</t>
+    <t xml:space="preserve">2.10444450378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09205603599548</t>
   </si>
   <si>
     <t xml:space="preserve">2.20664691925049</t>
@@ -1349,58 +1349,58 @@
     <t xml:space="preserve">2.19580745697021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18651628494263</t>
+    <t xml:space="preserve">2.18651604652405</t>
   </si>
   <si>
     <t xml:space="preserve">2.21748685836792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21593832969666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1834192276001</t>
+    <t xml:space="preserve">2.21593809127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18341898918152</t>
   </si>
   <si>
     <t xml:space="preserve">2.16328811645508</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15090012550354</t>
+    <t xml:space="preserve">2.15090036392212</t>
   </si>
   <si>
     <t xml:space="preserve">2.13231778144836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12612342834473</t>
+    <t xml:space="preserve">2.12612390518188</t>
   </si>
   <si>
     <t xml:space="preserve">2.11992979049683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16638541221619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15709447860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14935207366943</t>
+    <t xml:space="preserve">2.16638565063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1570942401886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14935183525085</t>
   </si>
   <si>
     <t xml:space="preserve">2.09670186042786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09979867935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09050798416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10754132270813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12457537651062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12767195701599</t>
+    <t xml:space="preserve">2.09979891777039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09050750732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10754156112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12457513809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12767219543457</t>
   </si>
   <si>
     <t xml:space="preserve">2.18806481361389</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">2.19735598564148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20200157165527</t>
+    <t xml:space="preserve">2.20200133323669</t>
   </si>
   <si>
     <t xml:space="preserve">2.20819544792175</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">2.17567658424377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12147808074951</t>
+    <t xml:space="preserve">2.12147831916809</t>
   </si>
   <si>
     <t xml:space="preserve">2.11683249473572</t>
@@ -1436,43 +1436,43 @@
     <t xml:space="preserve">2.06882834434509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05179500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01463007926941</t>
+    <t xml:space="preserve">2.05179452896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01463031768799</t>
   </si>
   <si>
     <t xml:space="preserve">1.96198010444641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98211097717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93720412254333</t>
+    <t xml:space="preserve">1.98211109638214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93720388412476</t>
   </si>
   <si>
     <t xml:space="preserve">1.90313625335693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86287438869476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91552448272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87216591835022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89384520053864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90158796310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87061715126038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8597776889801</t>
+    <t xml:space="preserve">1.86287462711334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91552472114563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87216579914093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89384531974792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90158760547638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87061727046967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85977756977081</t>
   </si>
   <si>
     <t xml:space="preserve">1.92791283130646</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">1.89694237709045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89074814319611</t>
+    <t xml:space="preserve">1.8907482624054</t>
   </si>
   <si>
     <t xml:space="preserve">1.87990820407867</t>
@@ -1490,55 +1490,55 @@
     <t xml:space="preserve">1.88919961452484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88765132427216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9046847820282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9217187166214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96662580966949</t>
+    <t xml:space="preserve">1.88765120506287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90468466281891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92171859741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96662569046021</t>
   </si>
   <si>
     <t xml:space="preserve">1.91862142086029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97901380062103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96972274780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97746539115906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94184935092926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9310097694397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92481577396393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92016994953156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89229643344879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90933060646057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87836015224457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93875217437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86906886100769</t>
+    <t xml:space="preserve">1.97901391983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96972286701202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97746551036835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94184923171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93100965023041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92481553554535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92017018795013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89229667186737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90933036804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87836003303528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93875253200531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86906898021698</t>
   </si>
   <si>
     <t xml:space="preserve">1.94804334640503</t>
@@ -1559,40 +1559,40 @@
     <t xml:space="preserve">2.09825015068054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08276510238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19116163253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19425868988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1787736415863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20509886741638</t>
+    <t xml:space="preserve">2.08276534080505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19116187095642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19425916671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17877340316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2050986289978</t>
   </si>
   <si>
     <t xml:space="preserve">2.20974397659302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22987508773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20355010032654</t>
+    <t xml:space="preserve">2.22987484931946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20354986190796</t>
   </si>
   <si>
     <t xml:space="preserve">2.19890451431274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22677779197693</t>
+    <t xml:space="preserve">2.22677755355835</t>
   </si>
   <si>
     <t xml:space="preserve">2.26084566116333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26239371299744</t>
+    <t xml:space="preserve">2.26239395141602</t>
   </si>
   <si>
     <t xml:space="preserve">2.28562188148499</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">2.29336428642273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28252458572388</t>
+    <t xml:space="preserve">2.28252482414246</t>
   </si>
   <si>
     <t xml:space="preserve">2.28407335281372</t>
@@ -1610,13 +1610,13 @@
     <t xml:space="preserve">2.2902672290802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27013683319092</t>
+    <t xml:space="preserve">2.27013635635376</t>
   </si>
   <si>
     <t xml:space="preserve">2.25619983673096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28097605705261</t>
+    <t xml:space="preserve">2.28097653388977</t>
   </si>
   <si>
     <t xml:space="preserve">2.30265545845032</t>
@@ -1625,37 +1625,37 @@
     <t xml:space="preserve">2.30110692977905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30730104446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2980101108551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28871893882751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25929689407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32433485984802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29181599617004</t>
+    <t xml:space="preserve">2.30730128288269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29800987243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28871917724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25929665565491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3243350982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29181575775146</t>
   </si>
   <si>
     <t xml:space="preserve">2.25465130805969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26858806610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26549100875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29955840110779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29646182060242</t>
+    <t xml:space="preserve">2.26858830451965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26549077033997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29955863952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29646158218384</t>
   </si>
   <si>
     <t xml:space="preserve">2.31349539756775</t>
@@ -1673,70 +1673,70 @@
     <t xml:space="preserve">2.34446573257446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38008189201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38163018226624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40330958366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4280858039856</t>
+    <t xml:space="preserve">2.38008165359497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38163042068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40330982208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42808604240417</t>
   </si>
   <si>
     <t xml:space="preserve">2.4311830997467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4760901927948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49467253684998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49002695083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49622082710266</t>
+    <t xml:space="preserve">2.47609043121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49467277526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49002718925476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49622106552124</t>
   </si>
   <si>
     <t xml:space="preserve">2.50860929489136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54887104034424</t>
+    <t xml:space="preserve">2.54887080192566</t>
   </si>
   <si>
     <t xml:space="preserve">2.52099752426147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5024151802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51635193824768</t>
+    <t xml:space="preserve">2.50241541862488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5163516998291</t>
   </si>
   <si>
     <t xml:space="preserve">2.462153673172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47918725013733</t>
+    <t xml:space="preserve">2.47918677330017</t>
   </si>
   <si>
     <t xml:space="preserve">2.46525073051453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43428015708923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4497652053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45286250114441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46679925918579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44666838645935</t>
+    <t xml:space="preserve">2.43427991867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44976568222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45286273956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46679902076721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44666814804077</t>
   </si>
   <si>
     <t xml:space="preserve">2.4575080871582</t>
@@ -1760,7 +1760,7 @@
     <t xml:space="preserve">2.48692965507507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53028845787048</t>
+    <t xml:space="preserve">2.5302882194519</t>
   </si>
   <si>
     <t xml:space="preserve">2.53803157806396</t>
@@ -1772,25 +1772,25 @@
     <t xml:space="preserve">2.54422545433044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55661368370056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55816221237183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53648257255554</t>
+    <t xml:space="preserve">2.55661344528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55816197395325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53648281097412</t>
   </si>
   <si>
     <t xml:space="preserve">2.53493428230286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5287401676178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51790070533752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56435632705688</t>
+    <t xml:space="preserve">2.52873992919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51790046691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56435656547546</t>
   </si>
   <si>
     <t xml:space="preserve">2.5906810760498</t>
@@ -1799,16 +1799,16 @@
     <t xml:space="preserve">2.60306930541992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60461759567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59997248649597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60152053833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58913254737854</t>
+    <t xml:space="preserve">2.60461783409119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59997200965881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60152077674866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58913278579712</t>
   </si>
   <si>
     <t xml:space="preserve">2.58603549003601</t>
@@ -1820,10 +1820,10 @@
     <t xml:space="preserve">2.65262198448181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68514108657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7161111831665</t>
+    <t xml:space="preserve">2.68514084815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71611166000366</t>
   </si>
   <si>
     <t xml:space="preserve">2.69698405265808</t>
@@ -1832,10 +1832,10 @@
     <t xml:space="preserve">2.67945027351379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68263840675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65075922012329</t>
+    <t xml:space="preserve">2.68263816833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65075898170471</t>
   </si>
   <si>
     <t xml:space="preserve">2.68104434013367</t>
@@ -1844,55 +1844,55 @@
     <t xml:space="preserve">2.66669869422913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7304573059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81174921989441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80856132507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78465175628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77349448204041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78305816650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79740333557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79580950737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8276891708374</t>
+    <t xml:space="preserve">2.73045706748962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81174945831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80856156349182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7846519947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77349424362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78305840492249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79740357398987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79580974578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82768869400024</t>
   </si>
   <si>
     <t xml:space="preserve">2.80696749687195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75914835929871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74480295181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74958467483521</t>
+    <t xml:space="preserve">2.75914859771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74480319023132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74958491325378</t>
   </si>
   <si>
     <t xml:space="preserve">2.7320511341095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72886300086975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73364496231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66988682746887</t>
+    <t xml:space="preserve">2.72886323928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73364520072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66988658905029</t>
   </si>
   <si>
     <t xml:space="preserve">2.68582630157471</t>
@@ -1901,34 +1901,34 @@
     <t xml:space="preserve">2.73683333396912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71132969856262</t>
+    <t xml:space="preserve">2.7113299369812</t>
   </si>
   <si>
     <t xml:space="preserve">2.69538974761963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70654797554016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72726941108704</t>
+    <t xml:space="preserve">2.70654773712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72726917266846</t>
   </si>
   <si>
     <t xml:space="preserve">2.70495367050171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73523902893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.687420129776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76233625411987</t>
+    <t xml:space="preserve">2.73523926734924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68742036819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76233673095703</t>
   </si>
   <si>
     <t xml:space="preserve">2.78783988952637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77827620506287</t>
+    <t xml:space="preserve">2.77827596664429</t>
   </si>
   <si>
     <t xml:space="preserve">2.78624606132507</t>
@@ -1937,16 +1937,16 @@
     <t xml:space="preserve">2.81334328651428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8818838596344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87869572639465</t>
+    <t xml:space="preserve">2.88188362121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87869596481323</t>
   </si>
   <si>
     <t xml:space="preserve">2.91535663604736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8914475440979</t>
+    <t xml:space="preserve">2.89144730567932</t>
   </si>
   <si>
     <t xml:space="preserve">2.88666534423828</t>
@@ -1955,16 +1955,16 @@
     <t xml:space="preserve">2.88825964927673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91695094108582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89622926712036</t>
+    <t xml:space="preserve">2.91695070266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89622902870178</t>
   </si>
   <si>
     <t xml:space="preserve">2.80059146881104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79262208938599</t>
+    <t xml:space="preserve">2.79262185096741</t>
   </si>
   <si>
     <t xml:space="preserve">2.84522223472595</t>
@@ -1973,43 +1973,43 @@
     <t xml:space="preserve">2.81812500953674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82131338119507</t>
+    <t xml:space="preserve">2.82131314277649</t>
   </si>
   <si>
     <t xml:space="preserve">2.8468165397644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90738725662231</t>
+    <t xml:space="preserve">2.90738701820374</t>
   </si>
   <si>
     <t xml:space="preserve">2.90419912338257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86913204193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95201778411865</t>
+    <t xml:space="preserve">2.86913180351257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95201826095581</t>
   </si>
   <si>
     <t xml:space="preserve">2.95042395591736</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02055811882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9647696018219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00143074989319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95679974555969</t>
+    <t xml:space="preserve">3.02055835723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96476984024048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00143051147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95679998397827</t>
   </si>
   <si>
     <t xml:space="preserve">2.97114539146423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01577615737915</t>
+    <t xml:space="preserve">3.01577663421631</t>
   </si>
   <si>
     <t xml:space="preserve">3.02215242385864</t>
@@ -2018,16 +2018,16 @@
     <t xml:space="preserve">3.00461864471436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97911548614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0030243396759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01418280601501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9838969707489</t>
+    <t xml:space="preserve">2.97911524772644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00302481651306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01418256759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98389720916748</t>
   </si>
   <si>
     <t xml:space="preserve">3.02374625205994</t>
@@ -2036,70 +2036,70 @@
     <t xml:space="preserve">2.99664878845215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96636343002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99346113204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00621294975281</t>
+    <t xml:space="preserve">2.96636366844177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99346089363098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00621247291565</t>
   </si>
   <si>
     <t xml:space="preserve">3.04606175422668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05881333351135</t>
+    <t xml:space="preserve">3.05881357192993</t>
   </si>
   <si>
     <t xml:space="preserve">3.04924964904785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06997132301331</t>
+    <t xml:space="preserve">3.06997108459473</t>
   </si>
   <si>
     <t xml:space="preserve">3.03012204170227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05403137207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06678318977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05243754386902</t>
+    <t xml:space="preserve">3.05403184890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06678342819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05243730545044</t>
   </si>
   <si>
     <t xml:space="preserve">3.07315897941589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07475328445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10025644302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17357897758484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19748830795288</t>
+    <t xml:space="preserve">3.07475304603577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10025668144226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17357873916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1974880695343</t>
   </si>
   <si>
     <t xml:space="preserve">3.19430041313171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2182092666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19589424133301</t>
+    <t xml:space="preserve">3.21820950508118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19589447975159</t>
   </si>
   <si>
     <t xml:space="preserve">3.16242074966431</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17995476722717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15604519844055</t>
+    <t xml:space="preserve">3.17995429039001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15604543685913</t>
   </si>
   <si>
     <t xml:space="preserve">3.18473625183105</t>
@@ -2108,10 +2108,10 @@
     <t xml:space="preserve">3.17517256736755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19111204147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06200170516968</t>
+    <t xml:space="preserve">3.19111227989197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06200122833252</t>
   </si>
   <si>
     <t xml:space="preserve">3.08750462532043</t>
@@ -2120,31 +2120,31 @@
     <t xml:space="preserve">3.12416577339172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1018500328064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09547472000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0715651512146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10344457626343</t>
+    <t xml:space="preserve">3.10185050964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09547424316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07156538963318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10344433784485</t>
   </si>
   <si>
     <t xml:space="preserve">3.11141419410706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06040716171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12735366821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17198467254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16879677772522</t>
+    <t xml:space="preserve">3.06040740013123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12735390663147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17198443412781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1687970161438</t>
   </si>
   <si>
     <t xml:space="preserve">3.16401505470276</t>
@@ -2171,25 +2171,25 @@
     <t xml:space="preserve">3.0811288356781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07794094085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1432933807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18633055686951</t>
+    <t xml:space="preserve">3.07794070243835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14329361915588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18633031845093</t>
   </si>
   <si>
     <t xml:space="preserve">3.18314242362976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13213586807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27240395545959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37760543823242</t>
+    <t xml:space="preserve">3.13213562965393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27240419387817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.377605676651</t>
   </si>
   <si>
     <t xml:space="preserve">3.3138473033905</t>
@@ -2201,7 +2201,7 @@
     <t xml:space="preserve">3.4461464881897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37919998168945</t>
+    <t xml:space="preserve">3.37919950485229</t>
   </si>
   <si>
     <t xml:space="preserve">3.26921629905701</t>
@@ -2216,76 +2216,76 @@
     <t xml:space="preserve">3.33297491073608</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37282395362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38557600975037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40948486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4270191192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43977022171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47802495956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45252180099487</t>
+    <t xml:space="preserve">3.37282419204712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38557577133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40948510169983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42701888084412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43977046012878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47802519798279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45252203941345</t>
   </si>
   <si>
     <t xml:space="preserve">3.45730400085449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47005581855774</t>
+    <t xml:space="preserve">3.47005558013916</t>
   </si>
   <si>
     <t xml:space="preserve">3.55612945556641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53700256347656</t>
+    <t xml:space="preserve">3.53700232505798</t>
   </si>
   <si>
     <t xml:space="preserve">3.51628065109253</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33935046195984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30906558036804</t>
+    <t xml:space="preserve">3.33935070037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30906534194946</t>
   </si>
   <si>
     <t xml:space="preserve">3.3377571105957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27877998352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09069275856018</t>
+    <t xml:space="preserve">3.27878046035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0906925201416</t>
   </si>
   <si>
     <t xml:space="preserve">3.11300826072693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26124691963196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83247041702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6587290763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69060802459717</t>
+    <t xml:space="preserve">3.2612464427948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83247089385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65872883796692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69060826301575</t>
   </si>
   <si>
     <t xml:space="preserve">2.2203893661499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55830955505371</t>
+    <t xml:space="preserve">2.55830907821655</t>
   </si>
   <si>
     <t xml:space="preserve">2.46585941314697</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">2.44194984436035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41804051399231</t>
+    <t xml:space="preserve">2.41804027557373</t>
   </si>
   <si>
     <t xml:space="preserve">2.44035625457764</t>
@@ -2318,43 +2318,43 @@
     <t xml:space="preserve">2.62206792831421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60453414916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5280237197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56468534469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53121209144592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5519335269928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45948338508606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57584285736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56787300109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54715156555176</t>
+    <t xml:space="preserve">2.60453391075134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52802395820618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56468510627747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53121185302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55193305015564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45948362350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57584309577942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56787323951721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54715180397034</t>
   </si>
   <si>
     <t xml:space="preserve">2.54396367073059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60772228240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62047410011292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51846051216125</t>
+    <t xml:space="preserve">2.60772180557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62047386169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51846027374268</t>
   </si>
   <si>
     <t xml:space="preserve">2.59018850326538</t>
@@ -2363,10 +2363,10 @@
     <t xml:space="preserve">2.5806245803833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67307448387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69220209121704</t>
+    <t xml:space="preserve">2.67307472229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69220185279846</t>
   </si>
   <si>
     <t xml:space="preserve">2.57903075218201</t>
@@ -2375,28 +2375,28 @@
     <t xml:space="preserve">2.57265520095825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52483606338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49295663833618</t>
+    <t xml:space="preserve">2.52483654022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49295687675476</t>
   </si>
   <si>
     <t xml:space="preserve">2.59178280830383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61887979507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5614972114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47542309761047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46267151832581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51367831230164</t>
+    <t xml:space="preserve">2.61888003349304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56149697303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47542333602905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46267127990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51367807388306</t>
   </si>
   <si>
     <t xml:space="preserve">2.50092673301697</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">2.65713500976562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66032266616821</t>
+    <t xml:space="preserve">2.66032314300537</t>
   </si>
   <si>
     <t xml:space="preserve">2.85159850120544</t>
@@ -2420,13 +2420,13 @@
     <t xml:space="preserve">2.85638046264648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81653094291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77668213844299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67785620689392</t>
+    <t xml:space="preserve">2.81653118133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77668190002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6778564453125</t>
   </si>
   <si>
     <t xml:space="preserve">2.80218553543091</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">2.75755476951599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75436663627625</t>
+    <t xml:space="preserve">2.75436687469482</t>
   </si>
   <si>
     <t xml:space="preserve">2.68901443481445</t>
@@ -2456,13 +2456,13 @@
     <t xml:space="preserve">2.70017194747925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72567558288574</t>
+    <t xml:space="preserve">2.72567534446716</t>
   </si>
   <si>
     <t xml:space="preserve">2.74209499359131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69940400123596</t>
+    <t xml:space="preserve">2.69940376281738</t>
   </si>
   <si>
     <t xml:space="preserve">2.71418166160583</t>
@@ -2477,7 +2477,7 @@
     <t xml:space="preserve">2.6747739315033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63865065574646</t>
+    <t xml:space="preserve">2.63865089416504</t>
   </si>
   <si>
     <t xml:space="preserve">2.65014481544495</t>
@@ -2501,19 +2501,19 @@
     <t xml:space="preserve">2.72567510604858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66163849830627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61894702911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63536715507507</t>
+    <t xml:space="preserve">2.66163873672485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61894726753235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63536691665649</t>
   </si>
   <si>
     <t xml:space="preserve">2.70268774032593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68791007995605</t>
+    <t xml:space="preserve">2.68790984153748</t>
   </si>
   <si>
     <t xml:space="preserve">2.59267568588257</t>
@@ -2522,10 +2522,10 @@
     <t xml:space="preserve">2.61073732376099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60252737998962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59595942497253</t>
+    <t xml:space="preserve">2.6025276184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59595966339111</t>
   </si>
   <si>
     <t xml:space="preserve">2.58774948120117</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">2.66820621490479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72403335571289</t>
+    <t xml:space="preserve">2.72403359413147</t>
   </si>
   <si>
     <t xml:space="preserve">2.78642821311951</t>
@@ -2543,58 +2543,58 @@
     <t xml:space="preserve">2.77657628059387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75851464271545</t>
+    <t xml:space="preserve">2.75851488113403</t>
   </si>
   <si>
     <t xml:space="preserve">2.66656422615051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70925545692444</t>
+    <t xml:space="preserve">2.70925569534302</t>
   </si>
   <si>
     <t xml:space="preserve">2.68298387527466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66328048706055</t>
+    <t xml:space="preserve">2.66328024864197</t>
   </si>
   <si>
     <t xml:space="preserve">2.75030517578125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7223916053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64686036109924</t>
+    <t xml:space="preserve">2.72239112854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64686059951782</t>
   </si>
   <si>
     <t xml:space="preserve">2.62715697288513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6287989616394</t>
+    <t xml:space="preserve">2.62879872322083</t>
   </si>
   <si>
     <t xml:space="preserve">2.6156632900238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69283580780029</t>
+    <t xml:space="preserve">2.69283604621887</t>
   </si>
   <si>
     <t xml:space="preserve">2.59760141372681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64850282669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64029264450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68134212493896</t>
+    <t xml:space="preserve">2.64850258827209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64029288291931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68134236335754</t>
   </si>
   <si>
     <t xml:space="preserve">2.66492247581482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67970013618469</t>
+    <t xml:space="preserve">2.67969989776611</t>
   </si>
   <si>
     <t xml:space="preserve">2.69776177406311</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">2.63700842857361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62387299537659</t>
+    <t xml:space="preserve">2.62387323379517</t>
   </si>
   <si>
     <t xml:space="preserve">2.60745334625244</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">2.63044095039368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54998397827148</t>
+    <t xml:space="preserve">2.54998421669006</t>
   </si>
   <si>
     <t xml:space="preserve">2.55819392204285</t>
@@ -2630,28 +2630,28 @@
     <t xml:space="preserve">2.51386094093323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52042865753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50236678123474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47281169891357</t>
+    <t xml:space="preserve">2.52042841911316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50236701965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.472811460495</t>
   </si>
   <si>
     <t xml:space="preserve">2.42191028594971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44325613975525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35951519012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38414478302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41205811500549</t>
+    <t xml:space="preserve">2.44325590133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35951542854309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3841450214386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41205835342407</t>
   </si>
   <si>
     <t xml:space="preserve">2.46295952796936</t>
@@ -2678,22 +2678,22 @@
     <t xml:space="preserve">2.19695997238159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21666383743286</t>
+    <t xml:space="preserve">2.21666359901428</t>
   </si>
   <si>
     <t xml:space="preserve">2.23636722564697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25442886352539</t>
+    <t xml:space="preserve">2.25442910194397</t>
   </si>
   <si>
     <t xml:space="preserve">2.3102560043335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30533003807068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28070068359375</t>
+    <t xml:space="preserve">2.30533027648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28070044517517</t>
   </si>
   <si>
     <t xml:space="preserve">2.45474982261658</t>
@@ -2705,10 +2705,10 @@
     <t xml:space="preserve">2.44982385635376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49251532554626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47937941551208</t>
+    <t xml:space="preserve">2.49251508712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47937965393066</t>
   </si>
   <si>
     <t xml:space="preserve">2.56147789955139</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">2.50400900840759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48102116584778</t>
+    <t xml:space="preserve">2.48102140426636</t>
   </si>
   <si>
     <t xml:space="preserve">2.47609567642212</t>
@@ -2732,7 +2732,7 @@
     <t xml:space="preserve">2.52207088470459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53520655632019</t>
+    <t xml:space="preserve">2.53520631790161</t>
   </si>
   <si>
     <t xml:space="preserve">2.51221871376038</t>
@@ -2753,7 +2753,7 @@
     <t xml:space="preserve">2.43012022972107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41534233093262</t>
+    <t xml:space="preserve">2.4153425693512</t>
   </si>
   <si>
     <t xml:space="preserve">2.38907098770142</t>
@@ -2762,16 +2762,16 @@
     <t xml:space="preserve">2.36444139480591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39399671554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36608338356018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40384864807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45146584510803</t>
+    <t xml:space="preserve">2.39399695396423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3660831451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40384840965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45146560668945</t>
   </si>
   <si>
     <t xml:space="preserve">2.33981156349182</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">2.38742899894714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4531078338623</t>
+    <t xml:space="preserve">2.45310807228088</t>
   </si>
   <si>
     <t xml:space="preserve">2.45967602729797</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">2.44653987884521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50565075874329</t>
+    <t xml:space="preserve">2.50565099716187</t>
   </si>
   <si>
     <t xml:space="preserve">2.4416139125824</t>
@@ -2801,10 +2801,10 @@
     <t xml:space="preserve">2.48594737052917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59431767463684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54177451133728</t>
+    <t xml:space="preserve">2.59431743621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5417742729187</t>
   </si>
   <si>
     <t xml:space="preserve">2.38086104393005</t>
@@ -2819,16 +2819,16 @@
     <t xml:space="preserve">2.36772537231445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32995986938477</t>
+    <t xml:space="preserve">2.32995963096619</t>
   </si>
   <si>
     <t xml:space="preserve">2.46952748298645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49415755271912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55326819419861</t>
+    <t xml:space="preserve">2.49415707588196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55326843261719</t>
   </si>
   <si>
     <t xml:space="preserve">2.51057696342468</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">2.52371263504028</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5549099445343</t>
+    <t xml:space="preserve">2.55491018295288</t>
   </si>
   <si>
     <t xml:space="preserve">2.58939146995544</t>
@@ -2858,22 +2858,22 @@
     <t xml:space="preserve">2.40220665931702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5286386013031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56312036514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56968784332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60416913032532</t>
+    <t xml:space="preserve">2.52863836288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56311988830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56968808174133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6041693687439</t>
   </si>
   <si>
     <t xml:space="preserve">2.71582365036011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68216276168823</t>
+    <t xml:space="preserve">2.68216300010681</t>
   </si>
   <si>
     <t xml:space="preserve">2.72895932197571</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">2.70843458175659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69611954689026</t>
+    <t xml:space="preserve">2.69611978530884</t>
   </si>
   <si>
     <t xml:space="preserve">2.71171832084656</t>
@@ -2891,13 +2891,13 @@
     <t xml:space="preserve">2.73224329948425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76918768882751</t>
+    <t xml:space="preserve">2.76918745040894</t>
   </si>
   <si>
     <t xml:space="preserve">2.76097750663757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75440979003906</t>
+    <t xml:space="preserve">2.75441002845764</t>
   </si>
   <si>
     <t xml:space="preserve">2.75523090362549</t>
@@ -2909,10 +2909,10 @@
     <t xml:space="preserve">2.74620008468628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79381728172302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.762619972229</t>
+    <t xml:space="preserve">2.7938175201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76261973381042</t>
   </si>
   <si>
     <t xml:space="preserve">2.76672458648682</t>
@@ -2924,25 +2924,25 @@
     <t xml:space="preserve">2.83815050125122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77082943916321</t>
+    <t xml:space="preserve">2.77082967758179</t>
   </si>
   <si>
     <t xml:space="preserve">2.77247166633606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76426196098328</t>
+    <t xml:space="preserve">2.7642617225647</t>
   </si>
   <si>
     <t xml:space="preserve">2.86278033256531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83240342140198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82255172729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86031723022461</t>
+    <t xml:space="preserve">2.83240365982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82255148887634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86031699180603</t>
   </si>
   <si>
     <t xml:space="preserve">2.87837910652161</t>
@@ -2951,16 +2951,16 @@
     <t xml:space="preserve">2.88330483436584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88740968704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88248372077942</t>
+    <t xml:space="preserve">2.88740992546082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.882483959198</t>
   </si>
   <si>
     <t xml:space="preserve">2.86524271965027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86113810539246</t>
+    <t xml:space="preserve">2.86113834381104</t>
   </si>
   <si>
     <t xml:space="preserve">2.86606407165527</t>
@@ -2969,10 +2969,10 @@
     <t xml:space="preserve">2.86360096931458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87427377700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89726161956787</t>
+    <t xml:space="preserve">2.87427401542664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89726114273071</t>
   </si>
   <si>
     <t xml:space="preserve">2.93256402015686</t>
@@ -2984,7 +2984,7 @@
     <t xml:space="preserve">2.97197127342224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02533555030823</t>
+    <t xml:space="preserve">3.02533531188965</t>
   </si>
   <si>
     <t xml:space="preserve">3.00481104850769</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">3.04093408584595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01794672012329</t>
+    <t xml:space="preserve">3.01794695854187</t>
   </si>
   <si>
     <t xml:space="preserve">3.04586005210876</t>
@@ -3026,10 +3026,10 @@
     <t xml:space="preserve">2.89069390296936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89151477813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8668851852417</t>
+    <t xml:space="preserve">2.89151453971863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86688542366028</t>
   </si>
   <si>
     <t xml:space="preserve">2.89479851722717</t>
@@ -5634,6 +5634,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.94799995422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99399995803833</t>
   </si>
 </sst>
 </file>
@@ -10280,7 +10283,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G166" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -10332,7 +10335,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G168" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -10384,7 +10387,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G170" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -10410,7 +10413,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G171" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -10462,7 +10465,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G173" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -10488,7 +10491,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G174" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -10514,7 +10517,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G175" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -10540,7 +10543,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G176" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -10618,7 +10621,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G179" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -10644,7 +10647,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G180" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -10696,7 +10699,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G182" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -10722,7 +10725,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G183" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -10748,7 +10751,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G184" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -10774,7 +10777,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G185" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -10800,7 +10803,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G186" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -10826,7 +10829,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G187" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -10852,7 +10855,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G188" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -10878,7 +10881,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G189" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -10904,7 +10907,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G190" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -10930,7 +10933,7 @@
         <v>2.33599996566772</v>
       </c>
       <c r="G191" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -10956,7 +10959,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G192" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -10982,7 +10985,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G193" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -11008,7 +11011,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G194" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -11034,7 +11037,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G195" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -11060,7 +11063,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G196" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -11086,7 +11089,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G197" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -11112,7 +11115,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G198" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -11138,7 +11141,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G199" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -11164,7 +11167,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G200" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -11190,7 +11193,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G201" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -11216,7 +11219,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G202" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -11242,7 +11245,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G203" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -11268,7 +11271,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G204" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -11294,7 +11297,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G205" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -11320,7 +11323,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G206" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -11346,7 +11349,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G207" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -11372,7 +11375,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G208" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -11398,7 +11401,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G209" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -11424,7 +11427,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G210" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -11450,7 +11453,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G211" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -11476,7 +11479,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G212" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -11502,7 +11505,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G213" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -11528,7 +11531,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G214" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -11580,7 +11583,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G216" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -11606,7 +11609,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G217" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -11632,7 +11635,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G218" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -11658,7 +11661,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G219" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -11684,7 +11687,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G220" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -11710,7 +11713,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G221" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -11736,7 +11739,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G222" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -11762,7 +11765,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G223" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -11788,7 +11791,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G224" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -11814,7 +11817,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G225" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -11840,7 +11843,7 @@
         <v>2.00200009346008</v>
       </c>
       <c r="G226" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -11866,7 +11869,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G227" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -11892,7 +11895,7 @@
         <v>1.96300005912781</v>
       </c>
       <c r="G228" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -11918,7 +11921,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G229" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -11944,7 +11947,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G230" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -11970,7 +11973,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G231" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -11996,7 +11999,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G232" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -12022,7 +12025,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G233" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -12048,7 +12051,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G234" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -12074,7 +12077,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G235" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -12100,7 +12103,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G236" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -12126,7 +12129,7 @@
         <v>1.90699994564056</v>
       </c>
       <c r="G237" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -12152,7 +12155,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G238" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -12178,7 +12181,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G239" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -12204,7 +12207,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G240" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -12230,7 +12233,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G241" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -12256,7 +12259,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G242" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -12282,7 +12285,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G243" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -12308,7 +12311,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G244" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -12334,7 +12337,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G245" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -12360,7 +12363,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G246" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -12386,7 +12389,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G247" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -12412,7 +12415,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G248" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -12438,7 +12441,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G249" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -12464,7 +12467,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G250" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -12490,7 +12493,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G251" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -12516,7 +12519,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G252" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -12542,7 +12545,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G253" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -12568,7 +12571,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G254" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -12594,7 +12597,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G255" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -12620,7 +12623,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G256" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -12646,7 +12649,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G257" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -12672,7 +12675,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G258" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -12698,7 +12701,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G259" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -12724,7 +12727,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G260" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -12750,7 +12753,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G261" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -12776,7 +12779,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G262" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -12802,7 +12805,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G263" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -12828,7 +12831,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G264" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -12854,7 +12857,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G265" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -12880,7 +12883,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G266" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -12906,7 +12909,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G267" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -12932,7 +12935,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G268" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -12958,7 +12961,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G269" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -12984,7 +12987,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G270" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -13010,7 +13013,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G271" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -13036,7 +13039,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G272" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -13062,7 +13065,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G273" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -13088,7 +13091,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G274" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -13114,7 +13117,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G275" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -13140,7 +13143,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G276" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -13166,7 +13169,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G277" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -13192,7 +13195,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G278" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -13218,7 +13221,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G279" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -13244,7 +13247,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G280" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -13270,7 +13273,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G281" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -13296,7 +13299,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G282" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -13322,7 +13325,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G283" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -13348,7 +13351,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G284" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -13374,7 +13377,7 @@
         <v>2.25</v>
       </c>
       <c r="G285" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -13400,7 +13403,7 @@
         <v>2.25</v>
       </c>
       <c r="G286" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -13426,7 +13429,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G287" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -13452,7 +13455,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G288" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -13478,7 +13481,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G289" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -13504,7 +13507,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G290" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -13530,7 +13533,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G291" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -13556,7 +13559,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G292" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -13582,7 +13585,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G293" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -13608,7 +13611,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G294" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -13634,7 +13637,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G295" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -13660,7 +13663,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G296" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -13686,7 +13689,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G297" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -13712,7 +13715,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G298" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -13738,7 +13741,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G299" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -13790,7 +13793,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G301" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -13816,7 +13819,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G302" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -13842,7 +13845,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G303" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -13868,7 +13871,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G304" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -13894,7 +13897,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G305" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -13920,7 +13923,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G306" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -13946,7 +13949,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G307" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -13972,7 +13975,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G308" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -13998,7 +14001,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G309" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -14024,7 +14027,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G310" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -14050,7 +14053,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G311" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -14076,7 +14079,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G312" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -14102,7 +14105,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G313" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -14128,7 +14131,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G314" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -14154,7 +14157,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G315" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -14180,7 +14183,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G316" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -14206,7 +14209,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G317" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -14232,7 +14235,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G318" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -14258,7 +14261,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G319" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -14284,7 +14287,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G320" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -14310,7 +14313,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G321" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -14336,7 +14339,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G322" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -14362,7 +14365,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G323" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -14388,7 +14391,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G324" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -14414,7 +14417,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G325" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -14440,7 +14443,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G326" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -14466,7 +14469,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G327" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -14492,7 +14495,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G328" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -14518,7 +14521,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G329" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -14544,7 +14547,7 @@
         <v>2.67400002479553</v>
       </c>
       <c r="G330" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -14570,7 +14573,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G331" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -14596,7 +14599,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G332" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -14622,7 +14625,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G333" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -14648,7 +14651,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G334" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -14674,7 +14677,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G335" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -14700,7 +14703,7 @@
         <v>2.66199994087219</v>
       </c>
       <c r="G336" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -14726,7 +14729,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G337" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -14752,7 +14755,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G338" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -14778,7 +14781,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G339" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -14804,7 +14807,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G340" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -14830,7 +14833,7 @@
         <v>2.64599990844727</v>
       </c>
       <c r="G341" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -14856,7 +14859,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G342" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -14882,7 +14885,7 @@
         <v>2.67199993133545</v>
       </c>
       <c r="G343" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -14908,7 +14911,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G344" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -14934,7 +14937,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G345" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -14960,7 +14963,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G346" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -14986,7 +14989,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G347" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -15012,7 +15015,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G348" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -15038,7 +15041,7 @@
         <v>2.85599994659424</v>
       </c>
       <c r="G349" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -15064,7 +15067,7 @@
         <v>2.83200001716614</v>
       </c>
       <c r="G350" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -15090,7 +15093,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G351" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -15116,7 +15119,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G352" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -15142,7 +15145,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G353" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -15168,7 +15171,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G354" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -15194,7 +15197,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G355" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -15220,7 +15223,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G356" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -15246,7 +15249,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G357" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -15272,7 +15275,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G358" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -15298,7 +15301,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G359" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -15324,7 +15327,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G360" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -15350,7 +15353,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G361" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -15376,7 +15379,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G362" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -15402,7 +15405,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G363" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -15428,7 +15431,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G364" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -15454,7 +15457,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G365" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -15480,7 +15483,7 @@
         <v>2.90400004386902</v>
       </c>
       <c r="G366" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -15506,7 +15509,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G367" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -15532,7 +15535,7 @@
         <v>2.92600011825562</v>
       </c>
       <c r="G368" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -15558,7 +15561,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G369" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -15584,7 +15587,7 @@
         <v>2.96399998664856</v>
       </c>
       <c r="G370" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -15610,7 +15613,7 @@
         <v>2.94400000572205</v>
       </c>
       <c r="G371" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -15636,7 +15639,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="G372" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -15662,7 +15665,7 @@
         <v>2.95799994468689</v>
       </c>
       <c r="G373" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -15688,7 +15691,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G374" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -15714,7 +15717,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G375" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -15740,7 +15743,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G376" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -15766,7 +15769,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G377" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -15792,7 +15795,7 @@
         <v>2.88599991798401</v>
       </c>
       <c r="G378" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -18548,7 +18551,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G484" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -18600,7 +18603,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G486" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -71050,7 +71053,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6912615741</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>2353028</v>
@@ -71071,6 +71074,32 @@
         <v>1816</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.6923842593</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>2133479</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>4.00600004196167</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>3.95600008964539</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>3.96799993515015</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>3.99399995803833</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1874</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HER.MI.xlsx
+++ b/data/HER.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1879" uniqueCount="1879">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1880" uniqueCount="1880">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70756614208221</t>
+    <t xml:space="preserve">1.70756638050079</t>
   </si>
   <si>
     <t xml:space="preserve">HER.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70896363258362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70616912841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71036076545715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68800354003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7257319688797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79140758514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79420220851898</t>
+    <t xml:space="preserve">1.7089638710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7061687707901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71036112308502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68800330162048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72573208808899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79140782356262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79420244693756</t>
   </si>
   <si>
     <t xml:space="preserve">1.7704473733902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74669229984283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70337450504303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77324199676514</t>
+    <t xml:space="preserve">1.74669253826141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70337462425232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77324187755585</t>
   </si>
   <si>
     <t xml:space="preserve">1.74948692321777</t>
@@ -83,40 +83,40 @@
     <t xml:space="preserve">1.76625549793243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80538153648376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7900105714798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80398392677307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83472549915314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81656014919281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80258655548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8486989736557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85568594932556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84031534194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82354700565338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82913613319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72852683067322</t>
+    <t xml:space="preserve">1.80538141727448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79001009464264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80398380756378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83472537994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81655979156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80258631706238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84869909286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85568571090698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8403148651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82354652881622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82913625240326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72852659225464</t>
   </si>
   <si>
     <t xml:space="preserve">1.74110317230225</t>
@@ -125,88 +125,88 @@
     <t xml:space="preserve">1.7592681646347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69918239116669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75507640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79559969902039</t>
+    <t xml:space="preserve">1.69918215274811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75507664680481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79559946060181</t>
   </si>
   <si>
     <t xml:space="preserve">1.78302347660065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77603662014008</t>
+    <t xml:space="preserve">1.77603685855865</t>
   </si>
   <si>
     <t xml:space="preserve">1.79839432239532</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80118906497955</t>
+    <t xml:space="preserve">1.80118870735168</t>
   </si>
   <si>
     <t xml:space="preserve">1.82075214385986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83053374290466</t>
+    <t xml:space="preserve">1.83053338527679</t>
   </si>
   <si>
     <t xml:space="preserve">1.78861272335052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76485788822174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74529504776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73970592021942</t>
+    <t xml:space="preserve">1.76485800743103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74529492855072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73970568180084</t>
   </si>
   <si>
     <t xml:space="preserve">1.72992432117462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7438976764679</t>
+    <t xml:space="preserve">1.74389743804932</t>
   </si>
   <si>
     <t xml:space="preserve">1.73271882534027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76346075534821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77883160114288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76066589355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77463936805725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79699718952179</t>
+    <t xml:space="preserve">1.76346051692963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77883148193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76066601276398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77463948726654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7969970703125</t>
   </si>
   <si>
     <t xml:space="preserve">1.83752048015594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81097042560577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85708355903625</t>
+    <t xml:space="preserve">1.81097054481506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85708343982697</t>
   </si>
   <si>
     <t xml:space="preserve">1.84310972690582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76765251159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78162622451782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78721594810486</t>
+    <t xml:space="preserve">1.76765263080597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78162610530853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78721559047699</t>
   </si>
   <si>
     <t xml:space="preserve">1.77743399143219</t>
@@ -215,37 +215,37 @@
     <t xml:space="preserve">1.780228972435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80817592144012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80957317352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79280483722687</t>
+    <t xml:space="preserve">1.80817580223083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80957329273224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79280519485474</t>
   </si>
   <si>
     <t xml:space="preserve">1.78442084789276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75647413730621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74808979034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82634139060974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84590423107147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83193099498749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84450709819794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82214915752411</t>
+    <t xml:space="preserve">1.75647377967834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74808967113495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82634162902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84590435028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83193111419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8445075750351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8221492767334</t>
   </si>
   <si>
     <t xml:space="preserve">1.83332824707031</t>
@@ -260,88 +260,88 @@
     <t xml:space="preserve">1.76206314563751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73132133483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74250018596649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71175849437714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75751042366028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7734477519989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74012362957001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75895929336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70390129089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67347455024719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70969700813293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73867475986481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78069257736206</t>
+    <t xml:space="preserve">1.73132145404816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74250030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71175873279572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75751030445099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77344822883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74012351036072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75895953178406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70390105247498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67347431182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70969676971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7386748790741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78069269657135</t>
   </si>
   <si>
     <t xml:space="preserve">1.83430194854736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80822169780731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81111943721771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78503930568695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77924370765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72708356380463</t>
+    <t xml:space="preserve">1.80822157859802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81111979484558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78503918647766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77924382686615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72708368301392</t>
   </si>
   <si>
     <t xml:space="preserve">1.76040816307068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74591934680939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77055025100708</t>
+    <t xml:space="preserve">1.7459192276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77055048942566</t>
   </si>
   <si>
     <t xml:space="preserve">1.76620399951935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76185715198517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76910150051117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77489721775055</t>
+    <t xml:space="preserve">1.76185703277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76910126209259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77489733695984</t>
   </si>
   <si>
     <t xml:space="preserve">1.78359043598175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83719980716705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85748410224915</t>
+    <t xml:space="preserve">1.83719968795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85748422145844</t>
   </si>
   <si>
     <t xml:space="preserve">1.85023963451385</t>
@@ -350,19 +350,19 @@
     <t xml:space="preserve">1.83575069904327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86617755889893</t>
+    <t xml:space="preserve">1.86617791652679</t>
   </si>
   <si>
     <t xml:space="preserve">1.83140420913696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84444427490234</t>
+    <t xml:space="preserve">1.84444415569305</t>
   </si>
   <si>
     <t xml:space="preserve">1.79663062095642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81981289386749</t>
+    <t xml:space="preserve">1.81981301307678</t>
   </si>
   <si>
     <t xml:space="preserve">1.8125684261322</t>
@@ -371,16 +371,16 @@
     <t xml:space="preserve">1.74881732463837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74447011947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77634620666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79083502292633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79952812194824</t>
+    <t xml:space="preserve">1.74447023868561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77634596824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79083466529846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79952836036682</t>
   </si>
   <si>
     <t xml:space="preserve">1.78648829460144</t>
@@ -389,262 +389,262 @@
     <t xml:space="preserve">1.78938615322113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81546628475189</t>
+    <t xml:space="preserve">1.8154661655426</t>
   </si>
   <si>
     <t xml:space="preserve">1.7560613155365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73577702045441</t>
+    <t xml:space="preserve">1.7357771396637</t>
   </si>
   <si>
     <t xml:space="preserve">1.70679903030396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73722577095032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7546124458313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71114575862885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70824801921844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70245218276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69231009483337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71694135665894</t>
+    <t xml:space="preserve">1.73722553253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75461268424988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71114552021027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70824790000916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70245242118835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69230997562408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71694099903107</t>
   </si>
   <si>
     <t xml:space="preserve">1.69665682315826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63145661354065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60537648200989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59233641624451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57929623126984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.601029753685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60972309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61406981945038</t>
+    <t xml:space="preserve">1.63145637512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60537612438202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59233617782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57929611206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60102963447571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6097229719162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6140695810318</t>
   </si>
   <si>
     <t xml:space="preserve">1.62131404876709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63290536403656</t>
+    <t xml:space="preserve">1.63290524482727</t>
   </si>
   <si>
     <t xml:space="preserve">1.61841630935669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63870096206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63725197315216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65029227733612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62276291847229</t>
+    <t xml:space="preserve">1.63870084285736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63725221157074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65029239654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62276315689087</t>
   </si>
   <si>
     <t xml:space="preserve">1.61551868915558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61696755886078</t>
+    <t xml:space="preserve">1.61696767807007</t>
   </si>
   <si>
     <t xml:space="preserve">1.62566065788269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6618834733963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66912758350372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68796348571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59378516674042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56625628471375</t>
+    <t xml:space="preserve">1.66188323497772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66912770271301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68796324729919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59378504753113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56625604629517</t>
   </si>
   <si>
     <t xml:space="preserve">1.56335830688477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54307401180267</t>
+    <t xml:space="preserve">1.54307389259338</t>
   </si>
   <si>
     <t xml:space="preserve">1.46048676967621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4633846282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44599783420563</t>
+    <t xml:space="preserve">1.46338438987732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44599795341492</t>
   </si>
   <si>
     <t xml:space="preserve">1.44527339935303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45034456253052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43005990982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42209112644196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39601111412048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39456212520599</t>
+    <t xml:space="preserve">1.45034468173981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43005979061127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42209124565125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39601099491119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3945620059967</t>
   </si>
   <si>
     <t xml:space="preserve">1.40905106067657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41267323493958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39818406105042</t>
+    <t xml:space="preserve">1.41267335414886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3981841802597</t>
   </si>
   <si>
     <t xml:space="preserve">1.40180635452271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40542888641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41629552841187</t>
+    <t xml:space="preserve">1.40542876720428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41629540920258</t>
   </si>
   <si>
     <t xml:space="preserve">1.38152194023132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35906386375427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37717521190643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43875324726105</t>
+    <t xml:space="preserve">1.35906422138214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37717533111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43875348567963</t>
   </si>
   <si>
     <t xml:space="preserve">1.48077118396759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49236249923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48511791229248</t>
+    <t xml:space="preserve">1.49236238002777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48511803150177</t>
   </si>
   <si>
     <t xml:space="preserve">1.53293144702911</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52713596820831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50105571746826</t>
+    <t xml:space="preserve">1.5271360874176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50105583667755</t>
   </si>
   <si>
     <t xml:space="preserve">1.50685131549835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54886972904205</t>
+    <t xml:space="preserve">1.54886949062347</t>
   </si>
   <si>
     <t xml:space="preserve">1.55756282806396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57060277462006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59088754653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56915378570557</t>
+    <t xml:space="preserve">1.57060265541077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59088742733002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56915390491486</t>
   </si>
   <si>
     <t xml:space="preserve">1.58798956871033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.608274102211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59668278694153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59958076477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56480741500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65174090862274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64159870147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65319001674652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65463876724243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65898549556732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64014983177185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64304745197296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57494950294495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57784736156464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55176711082458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58654069900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63000762462616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68216776847839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66622972488403</t>
+    <t xml:space="preserve">1.60827422142029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5966831445694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59958064556122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56480717658997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65174078941345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64159882068634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65318977832794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65463864803314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65898525714874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64014971256256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64304757118225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57494962215424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57784724235535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55176723003387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58654057979584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63000786304474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6821676492691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66622996330261</t>
   </si>
   <si>
     <t xml:space="preserve">1.6778210401535</t>
@@ -653,13 +653,13 @@
     <t xml:space="preserve">1.69086134433746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69375908374786</t>
+    <t xml:space="preserve">1.69375884532928</t>
   </si>
   <si>
     <t xml:space="preserve">1.69810581207275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69520783424377</t>
+    <t xml:space="preserve">1.69520795345306</t>
   </si>
   <si>
     <t xml:space="preserve">1.71404349803925</t>
@@ -668,25 +668,25 @@
     <t xml:space="preserve">1.72998118400574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73432838916779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71983885765076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72418606281281</t>
+    <t xml:space="preserve">1.73432815074921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71983921527863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72418594360352</t>
   </si>
   <si>
     <t xml:space="preserve">1.71549236774445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71839010715485</t>
+    <t xml:space="preserve">1.71839022636414</t>
   </si>
   <si>
     <t xml:space="preserve">1.74157273769379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78214156627655</t>
+    <t xml:space="preserve">1.78214192390442</t>
   </si>
   <si>
     <t xml:space="preserve">1.78793728351593</t>
@@ -695,88 +695,88 @@
     <t xml:space="preserve">1.81401717662811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82995510101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86907529830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89950215816498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91399097442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91544032096863</t>
+    <t xml:space="preserve">1.82995533943176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86907517910004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89950227737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91399085521698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91544020175934</t>
   </si>
   <si>
     <t xml:space="preserve">1.8806666135788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87197327613831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88935971260071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90095090866089</t>
+    <t xml:space="preserve">1.8719733953476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88935983181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90095102787018</t>
   </si>
   <si>
     <t xml:space="preserve">1.90529787540436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91254222393036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94441795349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93717360496521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87921762466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8835643529892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92847979068756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89805316925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88791120052338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90239977836609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91688859462738</t>
+    <t xml:space="preserve">1.91254270076752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94441759586334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93717312812805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8792177438736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88356411457062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92847990989685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8980530500412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8879109621048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9023996591568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91688883304596</t>
   </si>
   <si>
     <t xml:space="preserve">1.92413318157196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93572437763214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93862235546112</t>
+    <t xml:space="preserve">1.93572461605072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93862247467041</t>
   </si>
   <si>
     <t xml:space="preserve">1.9487646818161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99512934684753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0284538269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05743169784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06902313232422</t>
+    <t xml:space="preserve">1.99512910842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02845358848572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05743217468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06902289390564</t>
   </si>
   <si>
     <t xml:space="preserve">2.05163621902466</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">2.06467628479004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0385959148407</t>
+    <t xml:space="preserve">2.03859615325928</t>
   </si>
   <si>
     <t xml:space="preserve">2.07336950302124</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">2.0864098072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12842750549316</t>
+    <t xml:space="preserve">2.12842774391174</t>
   </si>
   <si>
     <t xml:space="preserve">2.11248993873596</t>
@@ -809,7 +809,7 @@
     <t xml:space="preserve">2.1008985042572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05453395843506</t>
+    <t xml:space="preserve">2.05453372001648</t>
   </si>
   <si>
     <t xml:space="preserve">2.0893075466156</t>
@@ -821,46 +821,46 @@
     <t xml:space="preserve">2.07916522026062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10379600524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11973428726196</t>
+    <t xml:space="preserve">2.10379672050476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11973452568054</t>
   </si>
   <si>
     <t xml:space="preserve">2.10814332962036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14726305007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13277435302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15450763702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14291667938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15595698356628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16790914535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17836809158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17239165306091</t>
+    <t xml:space="preserve">2.1472635269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13277459144592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1545078754425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1429169178009</t>
   </si>
   <si>
     <t xml:space="preserve">2.15595674514771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09918189048767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11262822151184</t>
+    <t xml:space="preserve">2.16790962219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17836785316467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17239141464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15595650672913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09918165206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11262845993042</t>
   </si>
   <si>
     <t xml:space="preserve">2.07228851318359</t>
@@ -869,64 +869,64 @@
     <t xml:space="preserve">2.05884170532227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01700711250305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99907839298248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01103138923645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00804257392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99758446216583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95126795768738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97069084644318</t>
+    <t xml:space="preserve">2.01700735092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99907851219177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01103091239929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00804281234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99758422374725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95126783847809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97069096565247</t>
   </si>
   <si>
     <t xml:space="preserve">2.00505471229553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98264348506927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03045415878296</t>
+    <t xml:space="preserve">1.98264360427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03045392036438</t>
   </si>
   <si>
     <t xml:space="preserve">2.05286502838135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03941893577576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03194832801819</t>
+    <t xml:space="preserve">2.0394184589386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03194808959961</t>
   </si>
   <si>
     <t xml:space="preserve">2.04539465904236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02447748184204</t>
+    <t xml:space="preserve">2.02447772026062</t>
   </si>
   <si>
     <t xml:space="preserve">2.06182956695557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07677030563354</t>
+    <t xml:space="preserve">2.07677006721497</t>
   </si>
   <si>
     <t xml:space="preserve">2.03344225883484</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01401925086975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05435967445374</t>
+    <t xml:space="preserve">2.01401901245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05435919761658</t>
   </si>
   <si>
     <t xml:space="preserve">2.04390072822571</t>
@@ -935,34 +935,34 @@
     <t xml:space="preserve">2.04240655899048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03643035888672</t>
+    <t xml:space="preserve">2.0364305973053</t>
   </si>
   <si>
     <t xml:space="preserve">2.04838299751282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04987716674805</t>
+    <t xml:space="preserve">2.04987740516663</t>
   </si>
   <si>
     <t xml:space="preserve">2.00206661224365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05585384368896</t>
+    <t xml:space="preserve">2.05585336685181</t>
   </si>
   <si>
     <t xml:space="preserve">2.03493595123291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99459636211395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97517347335815</t>
+    <t xml:space="preserve">1.99459624290466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.975172996521</t>
   </si>
   <si>
     <t xml:space="preserve">1.96172618865967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96770286560059</t>
+    <t xml:space="preserve">1.96770262718201</t>
   </si>
   <si>
     <t xml:space="preserve">2.02597188949585</t>
@@ -974,31 +974,31 @@
     <t xml:space="preserve">2.00953698158264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00356078147888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07826447486877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01850128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.000572681427</t>
+    <t xml:space="preserve">2.0035605430603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07826471328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01850152015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00057244300842</t>
   </si>
   <si>
     <t xml:space="preserve">1.98563182353973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98712587356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97218501567841</t>
+    <t xml:space="preserve">1.98712563514709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97218525409698</t>
   </si>
   <si>
     <t xml:space="preserve">2.02148962020874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03792405128479</t>
+    <t xml:space="preserve">2.03792452812195</t>
   </si>
   <si>
     <t xml:space="preserve">2.06033539772034</t>
@@ -1007,22 +1007,22 @@
     <t xml:space="preserve">2.07079434394836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07378244400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0663115978241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0633237361908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07527685165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08424115180969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1066517829895</t>
+    <t xml:space="preserve">2.07378268241882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06631207466125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06332349777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07527637481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08424067497253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10665225982666</t>
   </si>
   <si>
     <t xml:space="preserve">2.12458086013794</t>
@@ -1049,37 +1049,37 @@
     <t xml:space="preserve">2.16641521453857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17089748382568</t>
+    <t xml:space="preserve">2.1708972454071</t>
   </si>
   <si>
     <t xml:space="preserve">2.191814661026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19330859184265</t>
+    <t xml:space="preserve">2.19330906867981</t>
   </si>
   <si>
     <t xml:space="preserve">2.19480276107788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22468447685242</t>
+    <t xml:space="preserve">2.22468423843384</t>
   </si>
   <si>
     <t xml:space="preserve">2.27100086212158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25605988502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25904846191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28145933151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29490637779236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30536460876465</t>
+    <t xml:space="preserve">2.2560601234436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2590479850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28145909309387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29490613937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30536437034607</t>
   </si>
   <si>
     <t xml:space="preserve">2.30088233947754</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">2.27398872375488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.303870677948</t>
+    <t xml:space="preserve">2.30387091636658</t>
   </si>
   <si>
     <t xml:space="preserve">2.31582307815552</t>
@@ -1112,37 +1112,37 @@
     <t xml:space="preserve">2.22916650772095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22617864608765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21870803833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17388582229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15446281433105</t>
+    <t xml:space="preserve">2.22617816925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2187077999115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17388558387756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15446257591248</t>
   </si>
   <si>
     <t xml:space="preserve">2.21123766899109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26054239273071</t>
+    <t xml:space="preserve">2.26054191589355</t>
   </si>
   <si>
     <t xml:space="preserve">2.31134104728699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24111890792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26950669288635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23813104629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27697706222534</t>
+    <t xml:space="preserve">2.24111938476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26950716972351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23813080787659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27697730064392</t>
   </si>
   <si>
     <t xml:space="preserve">2.28594160079956</t>
@@ -1154,37 +1154,37 @@
     <t xml:space="preserve">2.24709558486938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27996563911438</t>
+    <t xml:space="preserve">2.2799654006958</t>
   </si>
   <si>
     <t xml:space="preserve">2.24560141563416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18434453010559</t>
+    <t xml:space="preserve">2.18434405326843</t>
   </si>
   <si>
     <t xml:space="preserve">2.13503980636597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11113452911377</t>
+    <t xml:space="preserve">2.11113429069519</t>
   </si>
   <si>
     <t xml:space="preserve">2.05734753608704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02896022796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09469938278198</t>
+    <t xml:space="preserve">2.02895975112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09469962120056</t>
   </si>
   <si>
     <t xml:space="preserve">2.12607526779175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13354563713074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09320521354675</t>
+    <t xml:space="preserve">2.13354539871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09320545196533</t>
   </si>
   <si>
     <t xml:space="preserve">2.06930017471313</t>
@@ -1193,10 +1193,10 @@
     <t xml:space="preserve">2.04091262817383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08573484420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08274698257446</t>
+    <t xml:space="preserve">2.08573508262634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08274674415588</t>
   </si>
   <si>
     <t xml:space="preserve">2.08125281333923</t>
@@ -1208,115 +1208,115 @@
     <t xml:space="preserve">2.09768772125244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12009882926941</t>
+    <t xml:space="preserve">2.12009906768799</t>
   </si>
   <si>
     <t xml:space="preserve">2.21273159980774</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22169613838196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2306604385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24261331558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26353049278259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23514342308044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25307178497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29341173171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29789423942566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28444790840149</t>
+    <t xml:space="preserve">2.22169661521912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23066091537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24261355400085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26353073120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23514294624329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25307202339172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29341197013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29789400100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28444766998291</t>
   </si>
   <si>
     <t xml:space="preserve">2.2276725769043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25157809257507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14101552963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12159276008606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02298355102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94678580760956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96471476554871</t>
+    <t xml:space="preserve">2.25157761573792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14101576805115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12159299850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02298331260681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94678544998169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.964714884758</t>
   </si>
   <si>
     <t xml:space="preserve">1.98114931583405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96919691562653</t>
+    <t xml:space="preserve">1.96919667720795</t>
   </si>
   <si>
     <t xml:space="preserve">1.97816133499146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94827950000763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02856683731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06108546257019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07192540168762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03785800933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04095506668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07347416877747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05953741073608</t>
+    <t xml:space="preserve">1.94827973842621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02856659889221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06108570098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0719256401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0378577709198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04095482826233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07347393035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0595371723175</t>
   </si>
   <si>
     <t xml:space="preserve">2.08895921707153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06728005409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10599327087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13541483879089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15399718284607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16019129753113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14470624923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13696336746216</t>
+    <t xml:space="preserve">2.06727981567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10599303245544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13541460037231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15399742126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16019105911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14470601081848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13696312904358</t>
   </si>
   <si>
     <t xml:space="preserve">2.14780330657959</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">2.16793394088745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17257952690125</t>
+    <t xml:space="preserve">2.17257928848267</t>
   </si>
   <si>
     <t xml:space="preserve">2.15244841575623</t>
@@ -1337,19 +1337,19 @@
     <t xml:space="preserve">2.10444450378418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09205627441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20664715766907</t>
+    <t xml:space="preserve">2.09205651283264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20664691925049</t>
   </si>
   <si>
     <t xml:space="preserve">2.17103099822998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19580745697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18651604652405</t>
+    <t xml:space="preserve">2.19580698013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18651628494263</t>
   </si>
   <si>
     <t xml:space="preserve">2.21748685836792</t>
@@ -1358,19 +1358,19 @@
     <t xml:space="preserve">2.21593809127808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18341898918152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16328835487366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1509006023407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13231801986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12612366676331</t>
+    <t xml:space="preserve">2.1834192276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16328859329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15090036392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13231778144836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12612390518188</t>
   </si>
   <si>
     <t xml:space="preserve">2.11992955207825</t>
@@ -1382,28 +1382,28 @@
     <t xml:space="preserve">2.1570942401886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14935159683228</t>
+    <t xml:space="preserve">2.14935183525085</t>
   </si>
   <si>
     <t xml:space="preserve">2.09670162200928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09979891777039</t>
+    <t xml:space="preserve">2.09979867935181</t>
   </si>
   <si>
     <t xml:space="preserve">2.09050750732422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10754132270813</t>
+    <t xml:space="preserve">2.10754156112671</t>
   </si>
   <si>
     <t xml:space="preserve">2.12457537651062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12767195701599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18806505203247</t>
+    <t xml:space="preserve">2.12767219543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18806457519531</t>
   </si>
   <si>
     <t xml:space="preserve">2.20045304298401</t>
@@ -1424,16 +1424,16 @@
     <t xml:space="preserve">2.17567658424377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12147831916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11683249473572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07657122612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06882810592651</t>
+    <t xml:space="preserve">2.12147808074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1168327331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07657074928284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06882858276367</t>
   </si>
   <si>
     <t xml:space="preserve">2.05179476737976</t>
@@ -1445,10 +1445,10 @@
     <t xml:space="preserve">1.9619802236557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98211073875427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93720388412476</t>
+    <t xml:space="preserve">1.98211085796356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93720424175262</t>
   </si>
   <si>
     <t xml:space="preserve">1.90313625335693</t>
@@ -1457,73 +1457,73 @@
     <t xml:space="preserve">1.86287438869476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91552460193634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87216591835022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89384496212006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90158760547638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87061738967896</t>
+    <t xml:space="preserve">1.91552424430847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87216567993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89384520053864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90158772468567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87061715126038</t>
   </si>
   <si>
     <t xml:space="preserve">1.85977756977081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92791306972504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89694237709045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89074814319611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87990844249725</t>
+    <t xml:space="preserve">1.92791259288788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89694249629974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89074790477753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87990856170654</t>
   </si>
   <si>
     <t xml:space="preserve">1.88919961452484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88765132427216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9046847820282</t>
+    <t xml:space="preserve">1.88765120506287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90468490123749</t>
   </si>
   <si>
     <t xml:space="preserve">1.92171847820282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96662569046021</t>
+    <t xml:space="preserve">1.96662592887878</t>
   </si>
   <si>
     <t xml:space="preserve">1.91862142086029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97901368141174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96972262859344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97746527194977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94184899330139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93100965023041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92481553554535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92017006874084</t>
+    <t xml:space="preserve">1.9790141582489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96972274780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97746539115906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94184947013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9310097694397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92481577396393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92017018795013</t>
   </si>
   <si>
     <t xml:space="preserve">1.89229643344879</t>
@@ -1535,19 +1535,19 @@
     <t xml:space="preserve">1.87836003303528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93875217437744</t>
+    <t xml:space="preserve">1.93875229358673</t>
   </si>
   <si>
     <t xml:space="preserve">1.86906909942627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9480437040329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98675644397736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09360480308533</t>
+    <t xml:space="preserve">1.94804346561432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98675692081451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09360504150391</t>
   </si>
   <si>
     <t xml:space="preserve">2.03630971908569</t>
@@ -1556,7 +1556,7 @@
     <t xml:space="preserve">2.06573128700256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09824991226196</t>
+    <t xml:space="preserve">2.09825038909912</t>
   </si>
   <si>
     <t xml:space="preserve">2.08276510238647</t>
@@ -1565,13 +1565,13 @@
     <t xml:space="preserve">2.19116187095642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19425892829895</t>
+    <t xml:space="preserve">2.19425868988037</t>
   </si>
   <si>
     <t xml:space="preserve">2.17877340316772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20509839057922</t>
+    <t xml:space="preserve">2.2050986289978</t>
   </si>
   <si>
     <t xml:space="preserve">2.2097442150116</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">2.20355010032654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19890427589417</t>
+    <t xml:space="preserve">2.19890475273132</t>
   </si>
   <si>
     <t xml:space="preserve">2.22677779197693</t>
@@ -1598,118 +1598,118 @@
     <t xml:space="preserve">2.28562164306641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29336404800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2825243473053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28407335281372</t>
+    <t xml:space="preserve">2.29336428642273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28252482414246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28407311439514</t>
   </si>
   <si>
     <t xml:space="preserve">2.2902672290802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27013659477234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25619959831238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28097629547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30265545845032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30110716819763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30730128288269</t>
+    <t xml:space="preserve">2.27013635635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25619983673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28097653388977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3026556968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30110669136047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30730080604553</t>
   </si>
   <si>
     <t xml:space="preserve">2.29800987243652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28871917724609</t>
+    <t xml:space="preserve">2.28871893882751</t>
   </si>
   <si>
     <t xml:space="preserve">2.25929713249207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3243350982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29181575775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25465154647827</t>
+    <t xml:space="preserve">2.32433485984802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29181599617004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25465130805969</t>
   </si>
   <si>
     <t xml:space="preserve">2.26858806610107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26549077033997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29955863952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29646158218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31349515914917</t>
+    <t xml:space="preserve">2.26549124717712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29955840110779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29646182060242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31349492073059</t>
   </si>
   <si>
     <t xml:space="preserve">2.32123780250549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2577486038208</t>
+    <t xml:space="preserve">2.25774836540222</t>
   </si>
   <si>
     <t xml:space="preserve">2.23916602134705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34446597099304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38008189201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38163018226624</t>
+    <t xml:space="preserve">2.34446573257446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38008165359497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38162994384766</t>
   </si>
   <si>
     <t xml:space="preserve">2.40330958366394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42808604240417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43118333816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47609043121338</t>
+    <t xml:space="preserve">2.42808628082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43118286132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4760901927948</t>
   </si>
   <si>
     <t xml:space="preserve">2.49467253684998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49002742767334</t>
+    <t xml:space="preserve">2.49002695083618</t>
   </si>
   <si>
     <t xml:space="preserve">2.49622082710266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50860953330994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54887104034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52099776268005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5024151802063</t>
+    <t xml:space="preserve">2.50860929489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54887080192566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52099752426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50241541862488</t>
   </si>
   <si>
     <t xml:space="preserve">2.51635217666626</t>
@@ -1721,7 +1721,7 @@
     <t xml:space="preserve">2.47918725013733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46525049209595</t>
+    <t xml:space="preserve">2.46525073051453</t>
   </si>
   <si>
     <t xml:space="preserve">2.43428039550781</t>
@@ -1730,31 +1730,31 @@
     <t xml:space="preserve">2.44976544380188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45286250114441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46679925918579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44666862487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4575080871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47144484519958</t>
+    <t xml:space="preserve">2.45286226272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46679902076721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44666838645935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45750832557678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47144460678101</t>
   </si>
   <si>
     <t xml:space="preserve">2.45905637741089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42653751373291</t>
+    <t xml:space="preserve">2.42653775215149</t>
   </si>
   <si>
     <t xml:space="preserve">2.44821667671204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42963457107544</t>
+    <t xml:space="preserve">2.42963480949402</t>
   </si>
   <si>
     <t xml:space="preserve">2.48692989349365</t>
@@ -1763,13 +1763,13 @@
     <t xml:space="preserve">2.53028845787048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53803157806396</t>
+    <t xml:space="preserve">2.53803110122681</t>
   </si>
   <si>
     <t xml:space="preserve">2.54112839698792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54422497749329</t>
+    <t xml:space="preserve">2.54422545433044</t>
   </si>
   <si>
     <t xml:space="preserve">2.55661368370056</t>
@@ -1781,16 +1781,16 @@
     <t xml:space="preserve">2.53648281097412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53493404388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52873992919922</t>
+    <t xml:space="preserve">2.53493428230286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5287401676178</t>
   </si>
   <si>
     <t xml:space="preserve">2.51790070533752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56435656547546</t>
+    <t xml:space="preserve">2.56435608863831</t>
   </si>
   <si>
     <t xml:space="preserve">2.5906810760498</t>
@@ -1799,46 +1799,46 @@
     <t xml:space="preserve">2.60306906700134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60461831092834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59997200965881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60152053833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58913230895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58603549003601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64642810821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65262222290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68514060974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71611142158508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69698429107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67945027351379</t>
+    <t xml:space="preserve">2.60461783409119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59997224807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60152077674866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58913278579712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58603525161743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64642786979675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65262198448181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68514084815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71611166000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69698405265808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67945051193237</t>
   </si>
   <si>
     <t xml:space="preserve">2.68263816833496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65075922012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68104481697083</t>
+    <t xml:space="preserve">2.65075898170471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68104457855225</t>
   </si>
   <si>
     <t xml:space="preserve">2.66669869422913</t>
@@ -1847,13 +1847,13 @@
     <t xml:space="preserve">2.7304573059082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81174921989441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80856108665466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7846519947052</t>
+    <t xml:space="preserve">2.81174969673157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80856132507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78465175628662</t>
   </si>
   <si>
     <t xml:space="preserve">2.77349448204041</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">2.79740357398987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79580950737</t>
+    <t xml:space="preserve">2.79580974578857</t>
   </si>
   <si>
     <t xml:space="preserve">2.82768869400024</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">2.74480295181274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74958515167236</t>
+    <t xml:space="preserve">2.74958467483521</t>
   </si>
   <si>
     <t xml:space="preserve">2.7320511341095</t>
@@ -1889,10 +1889,10 @@
     <t xml:space="preserve">2.72886323928833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73364496231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66988682746887</t>
+    <t xml:space="preserve">2.73364520072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66988658905029</t>
   </si>
   <si>
     <t xml:space="preserve">2.68582630157471</t>
@@ -1901,19 +1901,19 @@
     <t xml:space="preserve">2.73683309555054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7113299369812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69538974761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70654773712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72726941108704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70495390892029</t>
+    <t xml:space="preserve">2.71132969856262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69538998603821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70654726028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72726917266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70495367050171</t>
   </si>
   <si>
     <t xml:space="preserve">2.73523926734924</t>
@@ -1934,16 +1934,16 @@
     <t xml:space="preserve">2.78624606132507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81334352493286</t>
+    <t xml:space="preserve">2.8133430480957</t>
   </si>
   <si>
     <t xml:space="preserve">2.88188362121582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87869572639465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91535663604736</t>
+    <t xml:space="preserve">2.87869548797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91535687446594</t>
   </si>
   <si>
     <t xml:space="preserve">2.89144730567932</t>
@@ -1952,28 +1952,28 @@
     <t xml:space="preserve">2.88666534423828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88825964927673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91695070266724</t>
+    <t xml:space="preserve">2.88825941085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91695094108582</t>
   </si>
   <si>
     <t xml:space="preserve">2.89622926712036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80059170722961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79262185096741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84522271156311</t>
+    <t xml:space="preserve">2.80059146881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79262161254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84522247314453</t>
   </si>
   <si>
     <t xml:space="preserve">2.81812524795532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82131314277649</t>
+    <t xml:space="preserve">2.82131290435791</t>
   </si>
   <si>
     <t xml:space="preserve">2.8468165397644</t>
@@ -1982,43 +1982,43 @@
     <t xml:space="preserve">2.90738725662231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90419888496399</t>
+    <t xml:space="preserve">2.90419912338257</t>
   </si>
   <si>
     <t xml:space="preserve">2.86913204193115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95201778411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95042395591736</t>
+    <t xml:space="preserve">2.95201802253723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95042371749878</t>
   </si>
   <si>
     <t xml:space="preserve">3.02055835723877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96476984024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00143051147461</t>
+    <t xml:space="preserve">2.9647696018219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00143074989319</t>
   </si>
   <si>
     <t xml:space="preserve">2.95679998397827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97114515304565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01577615737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02215266227722</t>
+    <t xml:space="preserve">2.97114586830139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01577639579773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02215242385864</t>
   </si>
   <si>
     <t xml:space="preserve">3.00461864471436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97911548614502</t>
+    <t xml:space="preserve">2.97911524772644</t>
   </si>
   <si>
     <t xml:space="preserve">3.00302457809448</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">2.98389720916748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02374649047852</t>
+    <t xml:space="preserve">3.02374625205994</t>
   </si>
   <si>
     <t xml:space="preserve">2.99664902687073</t>
@@ -2045,19 +2045,19 @@
     <t xml:space="preserve">3.00621294975281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04606151580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05881309509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04924941062927</t>
+    <t xml:space="preserve">3.04606175422668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05881333351135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04924964904785</t>
   </si>
   <si>
     <t xml:space="preserve">3.06997132301331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03012204170227</t>
+    <t xml:space="preserve">3.03012228012085</t>
   </si>
   <si>
     <t xml:space="preserve">3.05403161048889</t>
@@ -2066,49 +2066,49 @@
     <t xml:space="preserve">3.06678318977356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0524377822876</t>
+    <t xml:space="preserve">3.05243730545044</t>
   </si>
   <si>
     <t xml:space="preserve">3.07315897941589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07475328445435</t>
+    <t xml:space="preserve">3.07475304603577</t>
   </si>
   <si>
     <t xml:space="preserve">3.10025668144226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17357873916626</t>
+    <t xml:space="preserve">3.17357850074768</t>
   </si>
   <si>
     <t xml:space="preserve">3.19748830795288</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19430017471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21820974349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19589424133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16242051124573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17995452880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15604543685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18473672866821</t>
+    <t xml:space="preserve">3.19430041313171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21820950508118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19589447975159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16242074966431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17995476722717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15604519844055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18473649024963</t>
   </si>
   <si>
     <t xml:space="preserve">3.17517256736755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19111227989197</t>
+    <t xml:space="preserve">3.19111251831055</t>
   </si>
   <si>
     <t xml:space="preserve">3.0620014667511</t>
@@ -2117,19 +2117,19 @@
     <t xml:space="preserve">3.08750486373901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12416553497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10185050964355</t>
+    <t xml:space="preserve">3.12416577339172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1018500328064</t>
   </si>
   <si>
     <t xml:space="preserve">3.09547472000122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07156538963318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10344433784485</t>
+    <t xml:space="preserve">3.0715651512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10344409942627</t>
   </si>
   <si>
     <t xml:space="preserve">3.11141419410706</t>
@@ -2147,13 +2147,13 @@
     <t xml:space="preserve">3.16879677772522</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16401505470276</t>
+    <t xml:space="preserve">3.16401481628418</t>
   </si>
   <si>
     <t xml:space="preserve">3.22139739990234</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16082715988159</t>
+    <t xml:space="preserve">3.16082692146301</t>
   </si>
   <si>
     <t xml:space="preserve">3.16560864448547</t>
@@ -2162,10 +2162,10 @@
     <t xml:space="preserve">3.10822629928589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09706807136536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10663223266602</t>
+    <t xml:space="preserve">3.09706830978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10663247108459</t>
   </si>
   <si>
     <t xml:space="preserve">3.0811288356781</t>
@@ -2174,34 +2174,34 @@
     <t xml:space="preserve">3.07794070243835</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1432933807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18633055686951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18314242362976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13213562965393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27240395545959</t>
+    <t xml:space="preserve">3.14329361915588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18633031845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18314266204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13213586807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27240443229675</t>
   </si>
   <si>
     <t xml:space="preserve">3.37760591506958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3138473033905</t>
+    <t xml:space="preserve">3.31384706497192</t>
   </si>
   <si>
     <t xml:space="preserve">3.44774007797241</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4461464881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37919974327087</t>
+    <t xml:space="preserve">3.44614601135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37919950485229</t>
   </si>
   <si>
     <t xml:space="preserve">3.26921629905701</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">3.27718615531921</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28674983978271</t>
+    <t xml:space="preserve">3.28675007820129</t>
   </si>
   <si>
     <t xml:space="preserve">3.33297491073608</t>
@@ -2222,40 +2222,40 @@
     <t xml:space="preserve">3.38557553291321</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40948486328125</t>
+    <t xml:space="preserve">3.40948510169983</t>
   </si>
   <si>
     <t xml:space="preserve">3.42701888084412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43977022171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47802495956421</t>
+    <t xml:space="preserve">3.43977046012878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47802543640137</t>
   </si>
   <si>
     <t xml:space="preserve">3.45252203941345</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45730376243591</t>
+    <t xml:space="preserve">3.45730400085449</t>
   </si>
   <si>
     <t xml:space="preserve">3.47005581855774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55612945556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53700232505798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51628041267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.339350938797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30906558036804</t>
+    <t xml:space="preserve">3.55612969398499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53700184822083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51628088951111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33935070037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30906534194946</t>
   </si>
   <si>
     <t xml:space="preserve">3.33775687217712</t>
@@ -2267,13 +2267,13 @@
     <t xml:space="preserve">3.09069275856018</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11300826072693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26124668121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83247065544128</t>
+    <t xml:space="preserve">3.11300802230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2612464427948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83247089385986</t>
   </si>
   <si>
     <t xml:space="preserve">2.6587290763855</t>
@@ -2291,34 +2291,34 @@
     <t xml:space="preserve">2.46585941314697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51049041748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51686644554138</t>
+    <t xml:space="preserve">2.51049065589905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5168662071228</t>
   </si>
   <si>
     <t xml:space="preserve">2.46107769012451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58381271362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44194984436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41804051399231</t>
+    <t xml:space="preserve">2.58381295204163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44195008277893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41804027557373</t>
   </si>
   <si>
     <t xml:space="preserve">2.44035625457764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50252079963684</t>
+    <t xml:space="preserve">2.50252056121826</t>
   </si>
   <si>
     <t xml:space="preserve">2.62206792831421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60453414916992</t>
+    <t xml:space="preserve">2.60453391075134</t>
   </si>
   <si>
     <t xml:space="preserve">2.52802395820618</t>
@@ -2330,76 +2330,76 @@
     <t xml:space="preserve">2.53121185302734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55193328857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45948362350464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57584285736084</t>
+    <t xml:space="preserve">2.5519335269928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45948338508606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57584309577942</t>
   </si>
   <si>
     <t xml:space="preserve">2.56787300109863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54715204238892</t>
+    <t xml:space="preserve">2.54715156555176</t>
   </si>
   <si>
     <t xml:space="preserve">2.54396367073059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60772228240967</t>
+    <t xml:space="preserve">2.60772204399109</t>
   </si>
   <si>
     <t xml:space="preserve">2.62047386169434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51846051216125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59018874168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5806245803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67307472229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69220209121704</t>
+    <t xml:space="preserve">2.5184600353241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59018850326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58062481880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67307496070862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69220185279846</t>
   </si>
   <si>
     <t xml:space="preserve">2.57903075218201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57265472412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52483606338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49295663833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59178280830383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61887955665588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5614972114563</t>
+    <t xml:space="preserve">2.57265496253967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52483582496643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49295711517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59178256988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61887979507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56149744987488</t>
   </si>
   <si>
     <t xml:space="preserve">2.47542309761047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46267175674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51367831230164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50092673301697</t>
+    <t xml:space="preserve">2.46267151832581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51367855072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50092697143555</t>
   </si>
   <si>
     <t xml:space="preserve">2.55352735519409</t>
@@ -2408,25 +2408,25 @@
     <t xml:space="preserve">2.54874563217163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65713500976562</t>
+    <t xml:space="preserve">2.65713477134705</t>
   </si>
   <si>
     <t xml:space="preserve">2.66032290458679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85159850120544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85637998580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81653118133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77668213844299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67785620689392</t>
+    <t xml:space="preserve">2.85159826278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85638046264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81653094291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77668190002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6778564453125</t>
   </si>
   <si>
     <t xml:space="preserve">2.80218553543091</t>
@@ -2438,10 +2438,10 @@
     <t xml:space="preserve">2.77030634880066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75755476951599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75436687469482</t>
+    <t xml:space="preserve">2.75755453109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75436663627625</t>
   </si>
   <si>
     <t xml:space="preserve">2.68901443481445</t>
@@ -2450,88 +2450,88 @@
     <t xml:space="preserve">2.63800740242004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70335960388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70017194747925</t>
+    <t xml:space="preserve">2.70335984230042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70017170906067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72567558288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74209475517273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69940400123596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71418142318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.641934633255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63372492790222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6747739315033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63865089416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65014457702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69447803497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7306010723114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73388481140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73552703857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76508283615112</t>
   </si>
   <si>
     <t xml:space="preserve">2.72567534446716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74209499359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69940376281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71418142318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.641934633255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63372468948364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67477416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63865065574646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65014433860779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69447803497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73060131072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73388528823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7355272769928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76508259773254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72567510604858</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.66163849830627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61894702911377</t>
+    <t xml:space="preserve">2.61894726753235</t>
   </si>
   <si>
     <t xml:space="preserve">2.63536691665649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70268797874451</t>
+    <t xml:space="preserve">2.70268774032593</t>
   </si>
   <si>
     <t xml:space="preserve">2.68790984153748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59267568588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61073732376099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6025276184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59595942497253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58774948120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66820645332336</t>
+    <t xml:space="preserve">2.59267544746399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61073708534241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60252737998962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59595918655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58774971961975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66820621490479</t>
   </si>
   <si>
     <t xml:space="preserve">2.72403335571289</t>
@@ -2549,55 +2549,55 @@
     <t xml:space="preserve">2.66656422615051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70925545692444</t>
+    <t xml:space="preserve">2.70925569534302</t>
   </si>
   <si>
     <t xml:space="preserve">2.68298387527466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66328024864197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75030517578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7223916053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64686036109924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62715697288513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62879872322083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6156632900238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69283580780029</t>
+    <t xml:space="preserve">2.66328001022339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75030493736267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72239136695862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64686059951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62715721130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6287989616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61566305160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69283604621887</t>
   </si>
   <si>
     <t xml:space="preserve">2.59760141372681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64850258827209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64029312133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68134188652039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66492223739624</t>
+    <t xml:space="preserve">2.64850282669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64029288291931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68134212493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66492247581482</t>
   </si>
   <si>
     <t xml:space="preserve">2.67970013618469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69776153564453</t>
+    <t xml:space="preserve">2.69776201248169</t>
   </si>
   <si>
     <t xml:space="preserve">2.71253943443298</t>
@@ -2606,13 +2606,13 @@
     <t xml:space="preserve">2.63700866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62387347221375</t>
+    <t xml:space="preserve">2.62387299537659</t>
   </si>
   <si>
     <t xml:space="preserve">2.60745310783386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64521861076355</t>
+    <t xml:space="preserve">2.64521884918213</t>
   </si>
   <si>
     <t xml:space="preserve">2.63044095039368</t>
@@ -2630,10 +2630,10 @@
     <t xml:space="preserve">2.51386094093323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52042865753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50236701965332</t>
+    <t xml:space="preserve">2.52042889595032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5023672580719</t>
   </si>
   <si>
     <t xml:space="preserve">2.472811460495</t>
@@ -2645,16 +2645,16 @@
     <t xml:space="preserve">2.44325613975525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35951542854309</t>
+    <t xml:space="preserve">2.35951519012451</t>
   </si>
   <si>
     <t xml:space="preserve">2.38414478302002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41205835342407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46295952796936</t>
+    <t xml:space="preserve">2.41205859184265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46295976638794</t>
   </si>
   <si>
     <t xml:space="preserve">2.39563894271851</t>
@@ -2666,13 +2666,13 @@
     <t xml:space="preserve">2.37757682800293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31518173217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29219436645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2347252368927</t>
+    <t xml:space="preserve">2.31518197059631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29219460487366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23472547531128</t>
   </si>
   <si>
     <t xml:space="preserve">2.19695997238159</t>
@@ -2681,10 +2681,10 @@
     <t xml:space="preserve">2.21666359901428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23636698722839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25442886352539</t>
+    <t xml:space="preserve">2.23636722564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25442910194397</t>
   </si>
   <si>
     <t xml:space="preserve">2.3102560043335</t>
@@ -2693,43 +2693,43 @@
     <t xml:space="preserve">2.30533027648926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28070092201233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45475006103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42519450187683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44982385635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49251532554626</t>
+    <t xml:space="preserve">2.28070068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45474982261658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42519426345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44982409477234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49251508712769</t>
   </si>
   <si>
     <t xml:space="preserve">2.47937917709351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56147813796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50893473625183</t>
+    <t xml:space="preserve">2.56147789955139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50893497467041</t>
   </si>
   <si>
     <t xml:space="preserve">2.49579906463623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50400900840759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48102116584778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47609543800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52207088470459</t>
+    <t xml:space="preserve">2.50400876998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48102140426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47609519958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52207064628601</t>
   </si>
   <si>
     <t xml:space="preserve">2.53520655632019</t>
@@ -2741,19 +2741,19 @@
     <t xml:space="preserve">2.4711697101593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4399721622467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46788549423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44489789009094</t>
+    <t xml:space="preserve">2.43997192382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46788573265076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44489765167236</t>
   </si>
   <si>
     <t xml:space="preserve">2.43011999130249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4153425693512</t>
+    <t xml:space="preserve">2.41534233093262</t>
   </si>
   <si>
     <t xml:space="preserve">2.38907098770142</t>
@@ -2762,19 +2762,19 @@
     <t xml:space="preserve">2.36444139480591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39399695396423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36608338356018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40384840965271</t>
+    <t xml:space="preserve">2.39399671554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3660831451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40384888648987</t>
   </si>
   <si>
     <t xml:space="preserve">2.45146560668945</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3398118019104</t>
+    <t xml:space="preserve">2.33981156349182</t>
   </si>
   <si>
     <t xml:space="preserve">2.38742876052856</t>
@@ -2783,43 +2783,43 @@
     <t xml:space="preserve">2.45310759544373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45967578887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44654011726379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50565123558044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4416139125824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49087309837341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48594760894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59431767463684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54177451133728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38086104393005</t>
+    <t xml:space="preserve">2.45967555046082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44653987884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50565099716187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44161415100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49087285995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48594737052917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59431743621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5417742729187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38086080551147</t>
   </si>
   <si>
     <t xml:space="preserve">2.33652782440186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35787343978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36772537231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32995986938477</t>
+    <t xml:space="preserve">2.35787320137024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36772513389587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32996010780334</t>
   </si>
   <si>
     <t xml:space="preserve">2.46952748298645</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">2.49415731430054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55326843261719</t>
+    <t xml:space="preserve">2.55326819419861</t>
   </si>
   <si>
     <t xml:space="preserve">2.51057696342468</t>
@@ -2840,34 +2840,34 @@
     <t xml:space="preserve">2.55491018295288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58939146995544</t>
+    <t xml:space="preserve">2.58939170837402</t>
   </si>
   <si>
     <t xml:space="preserve">2.54670023918152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53684854507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52535462379456</t>
+    <t xml:space="preserve">2.53684830665588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52535438537598</t>
   </si>
   <si>
     <t xml:space="preserve">2.43176198005676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40220642089844</t>
+    <t xml:space="preserve">2.4022068977356</t>
   </si>
   <si>
     <t xml:space="preserve">2.5286386013031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56312012672424</t>
+    <t xml:space="preserve">2.56311988830566</t>
   </si>
   <si>
     <t xml:space="preserve">2.56968808174133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6041693687439</t>
+    <t xml:space="preserve">2.60416913032532</t>
   </si>
   <si>
     <t xml:space="preserve">2.71582365036011</t>
@@ -2882,13 +2882,13 @@
     <t xml:space="preserve">2.70843482017517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69611954689026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71171832084656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73224329948425</t>
+    <t xml:space="preserve">2.69611978530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71171855926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73224353790283</t>
   </si>
   <si>
     <t xml:space="preserve">2.76918745040894</t>
@@ -2900,31 +2900,31 @@
     <t xml:space="preserve">2.75441002845764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75523066520691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75605201721191</t>
+    <t xml:space="preserve">2.75523090362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75605177879333</t>
   </si>
   <si>
     <t xml:space="preserve">2.74620008468628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79381728172302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76261949539185</t>
+    <t xml:space="preserve">2.79381704330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76261973381042</t>
   </si>
   <si>
     <t xml:space="preserve">2.76672458648682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79710125923157</t>
+    <t xml:space="preserve">2.79710149765015</t>
   </si>
   <si>
     <t xml:space="preserve">2.83815050125122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77082943916321</t>
+    <t xml:space="preserve">2.77082967758179</t>
   </si>
   <si>
     <t xml:space="preserve">2.77247166633606</t>
@@ -2936,16 +2936,16 @@
     <t xml:space="preserve">2.86278009414673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83240389823914</t>
+    <t xml:space="preserve">2.83240365982056</t>
   </si>
   <si>
     <t xml:space="preserve">2.82255172729492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86031723022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87837886810303</t>
+    <t xml:space="preserve">2.86031699180603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87837910652161</t>
   </si>
   <si>
     <t xml:space="preserve">2.88330483436584</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">2.88248372077942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86524295806885</t>
+    <t xml:space="preserve">2.86524319648743</t>
   </si>
   <si>
     <t xml:space="preserve">2.86113786697388</t>
@@ -2966,7 +2966,7 @@
     <t xml:space="preserve">2.86606407165527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86360096931458</t>
+    <t xml:space="preserve">2.86360120773315</t>
   </si>
   <si>
     <t xml:space="preserve">2.87427401542664</t>
@@ -2987,25 +2987,25 @@
     <t xml:space="preserve">3.02533531188965</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00481081008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00809478759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04093408584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01794672012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04586029052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02123045921326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00727367401123</t>
+    <t xml:space="preserve">3.00481104850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00809502601624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04093432426453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01794648170471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04586005210876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02123069763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00727391242981</t>
   </si>
   <si>
     <t xml:space="preserve">2.98921203613281</t>
@@ -3014,34 +3014,34 @@
     <t xml:space="preserve">2.95801424980164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90218782424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92353320121765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89561939239502</t>
+    <t xml:space="preserve">2.90218758583069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92353343963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8956196308136</t>
   </si>
   <si>
     <t xml:space="preserve">2.89069366455078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89151477813721</t>
+    <t xml:space="preserve">2.89151453971863</t>
   </si>
   <si>
     <t xml:space="preserve">2.8668851852417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89479827880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90920472145081</t>
+    <t xml:space="preserve">2.89479851722717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90920495986938</t>
   </si>
   <si>
     <t xml:space="preserve">2.89649343490601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96005034446716</t>
+    <t xml:space="preserve">2.96005010604858</t>
   </si>
   <si>
     <t xml:space="preserve">2.86598610877991</t>
@@ -3059,13 +3059,13 @@
     <t xml:space="preserve">2.92191600799561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89564609527588</t>
+    <t xml:space="preserve">2.89564633369446</t>
   </si>
   <si>
     <t xml:space="preserve">2.92615342140198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84225821495056</t>
+    <t xml:space="preserve">2.84225845336914</t>
   </si>
   <si>
     <t xml:space="preserve">2.85073280334473</t>
@@ -3074,7 +3074,7 @@
     <t xml:space="preserve">2.94733881950378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9998791217804</t>
+    <t xml:space="preserve">2.99987888336182</t>
   </si>
   <si>
     <t xml:space="preserve">2.9778459072113</t>
@@ -3083,16 +3083,16 @@
     <t xml:space="preserve">2.99055743217468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03292846679688</t>
+    <t xml:space="preserve">3.03292870521545</t>
   </si>
   <si>
     <t xml:space="preserve">3.06428337097168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04055571556091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04479265213013</t>
+    <t xml:space="preserve">3.04055547714233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04479241371155</t>
   </si>
   <si>
     <t xml:space="preserve">3.02275943756104</t>
@@ -3101,13 +3101,13 @@
     <t xml:space="preserve">3.01004838943481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00157403945923</t>
+    <t xml:space="preserve">3.00157380104065</t>
   </si>
   <si>
     <t xml:space="preserve">3.02021718025208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04648756980896</t>
+    <t xml:space="preserve">3.04648733139038</t>
   </si>
   <si>
     <t xml:space="preserve">3.03547096252441</t>
@@ -3125,13 +3125,13 @@
     <t xml:space="preserve">3.14563584327698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15665245056152</t>
+    <t xml:space="preserve">3.15665221214294</t>
   </si>
   <si>
     <t xml:space="preserve">3.18038034439087</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19648122787476</t>
+    <t xml:space="preserve">3.19648146629333</t>
   </si>
   <si>
     <t xml:space="preserve">3.18546485900879</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">3.10157012939453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11597633361816</t>
+    <t xml:space="preserve">3.11597609519958</t>
   </si>
   <si>
     <t xml:space="preserve">3.11089158058167</t>
@@ -3158,31 +3158,31 @@
     <t xml:space="preserve">3.10411238670349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13716173171997</t>
+    <t xml:space="preserve">3.13716149330139</t>
   </si>
   <si>
     <t xml:space="preserve">3.12275552749634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11004400253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1252977848053</t>
+    <t xml:space="preserve">3.11004424095154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12529802322388</t>
   </si>
   <si>
     <t xml:space="preserve">3.08123159408569</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03631830215454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07360506057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09902763366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04987716674805</t>
+    <t xml:space="preserve">3.03631854057312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07360529899597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09902787208557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04987740516663</t>
   </si>
   <si>
     <t xml:space="preserve">3.08377385139465</t>
@@ -3194,19 +3194,19 @@
     <t xml:space="preserve">3.08631634712219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08292675018311</t>
+    <t xml:space="preserve">3.08292651176453</t>
   </si>
   <si>
     <t xml:space="preserve">3.09224820137024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02360725402832</t>
+    <t xml:space="preserve">3.02360701560974</t>
   </si>
   <si>
     <t xml:space="preserve">2.97445631027222</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01428532600403</t>
+    <t xml:space="preserve">3.01428508758545</t>
   </si>
   <si>
     <t xml:space="preserve">2.99648952484131</t>
@@ -3215,34 +3215,34 @@
     <t xml:space="preserve">2.99564218521118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99818444252014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00411605834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96089792251587</t>
+    <t xml:space="preserve">2.99818420410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00411629676819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96089744567871</t>
   </si>
   <si>
     <t xml:space="preserve">2.98547291755676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91089940071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87785005569458</t>
+    <t xml:space="preserve">2.91089963912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.877849817276</t>
   </si>
   <si>
     <t xml:space="preserve">2.91174721717834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94564414024353</t>
+    <t xml:space="preserve">2.94564390182495</t>
   </si>
   <si>
     <t xml:space="preserve">2.97530388832092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95327091217041</t>
+    <t xml:space="preserve">2.95327067375183</t>
   </si>
   <si>
     <t xml:space="preserve">2.92445826530457</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">2.9439492225647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00242114067078</t>
+    <t xml:space="preserve">3.00242137908936</t>
   </si>
   <si>
     <t xml:space="preserve">3.03377604484558</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">3.04902958869934</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01767492294312</t>
+    <t xml:space="preserve">3.01767516136169</t>
   </si>
   <si>
     <t xml:space="preserve">3.05241942405701</t>
@@ -3278,13 +3278,13 @@
     <t xml:space="preserve">3.03462338447571</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1125864982605</t>
+    <t xml:space="preserve">3.11258673667908</t>
   </si>
   <si>
     <t xml:space="preserve">3.09309577941895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05665683746338</t>
+    <t xml:space="preserve">3.0566565990448</t>
   </si>
   <si>
     <t xml:space="preserve">3.01682758331299</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">3.05750393867493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06936740875244</t>
+    <t xml:space="preserve">3.06936764717102</t>
   </si>
   <si>
     <t xml:space="preserve">3.07275748252869</t>
@@ -3314,10 +3314,10 @@
     <t xml:space="preserve">2.8702232837677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88547706604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95750784873962</t>
+    <t xml:space="preserve">2.88547682762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9575080871582</t>
   </si>
   <si>
     <t xml:space="preserve">2.88971424102783</t>
@@ -3326,16 +3326,16 @@
     <t xml:space="preserve">3.02530169487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98208332061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0083532333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97869372367859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00326871871948</t>
+    <t xml:space="preserve">2.98208355903625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00835299491882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97869348526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00326895713806</t>
   </si>
   <si>
     <t xml:space="preserve">3.02445459365845</t>
@@ -3344,25 +3344,25 @@
     <t xml:space="preserve">3.04564023017883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05072426795959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06089377403259</t>
+    <t xml:space="preserve">3.05072450637817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06089353561401</t>
   </si>
   <si>
     <t xml:space="preserve">3.11682343482971</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10241746902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14055132865906</t>
+    <t xml:space="preserve">3.10241723060608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14055156707764</t>
   </si>
   <si>
     <t xml:space="preserve">3.11173892021179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0871639251709</t>
+    <t xml:space="preserve">3.08716368675232</t>
   </si>
   <si>
     <t xml:space="preserve">3.02699661254883</t>
@@ -3371,7 +3371,7 @@
     <t xml:space="preserve">3.01343774795532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99394750595093</t>
+    <t xml:space="preserve">2.99394726753235</t>
   </si>
   <si>
     <t xml:space="preserve">2.97106671333313</t>
@@ -3389,7 +3389,7 @@
     <t xml:space="preserve">2.91767907142639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97360873222351</t>
+    <t xml:space="preserve">2.97360897064209</t>
   </si>
   <si>
     <t xml:space="preserve">3.07614731788635</t>
@@ -3404,25 +3404,25 @@
     <t xml:space="preserve">3.07021522521973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93886470794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88039231300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9185266494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93801712989807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92530560493469</t>
+    <t xml:space="preserve">2.9388644695282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88039255142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91852641105652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93801689147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92530584335327</t>
   </si>
   <si>
     <t xml:space="preserve">2.86005425453186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88717174530029</t>
+    <t xml:space="preserve">2.88717198371887</t>
   </si>
   <si>
     <t xml:space="preserve">2.87276554107666</t>
@@ -3431,28 +3431,28 @@
     <t xml:space="preserve">2.84310579299927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83802127838135</t>
+    <t xml:space="preserve">2.83802103996277</t>
   </si>
   <si>
     <t xml:space="preserve">2.79734492301941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80836153030396</t>
+    <t xml:space="preserve">2.80836129188538</t>
   </si>
   <si>
     <t xml:space="preserve">2.82446241378784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74056768417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93632221221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83208918571472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78971838951111</t>
+    <t xml:space="preserve">2.740567445755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93632245063782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8320894241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78971815109253</t>
   </si>
   <si>
     <t xml:space="preserve">2.76260042190552</t>
@@ -3491,7 +3491,7 @@
     <t xml:space="preserve">2.7880232334137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75666880607605</t>
+    <t xml:space="preserve">2.75666856765747</t>
   </si>
   <si>
     <t xml:space="preserve">2.814293384552</t>
@@ -3503,10 +3503,10 @@
     <t xml:space="preserve">2.85327506065369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83547878265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87615513801575</t>
+    <t xml:space="preserve">2.83547902107239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87615537643433</t>
   </si>
   <si>
     <t xml:space="preserve">2.90750980377197</t>
@@ -3518,13 +3518,13 @@
     <t xml:space="preserve">3.04733467102051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00496363639832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04394507408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05835127830505</t>
+    <t xml:space="preserve">3.00496387481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0439453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05835151672363</t>
   </si>
   <si>
     <t xml:space="preserve">3.01598024368286</t>
@@ -3533,25 +3533,25 @@
     <t xml:space="preserve">3.04818201065063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97276139259338</t>
+    <t xml:space="preserve">2.97276163101196</t>
   </si>
   <si>
     <t xml:space="preserve">2.98377799987793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9524233341217</t>
+    <t xml:space="preserve">2.95242309570312</t>
   </si>
   <si>
     <t xml:space="preserve">2.98632025718689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06343579292297</t>
+    <t xml:space="preserve">3.06343603134155</t>
   </si>
   <si>
     <t xml:space="preserve">2.84141087532043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86513900756836</t>
+    <t xml:space="preserve">2.86513876914978</t>
   </si>
   <si>
     <t xml:space="preserve">2.92954301834106</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">3.03801321983337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98801493644714</t>
+    <t xml:space="preserve">2.98801517486572</t>
   </si>
   <si>
     <t xml:space="preserve">2.96598219871521</t>
@@ -3578,10 +3578,10 @@
     <t xml:space="preserve">2.82785201072693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86174893379211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83717393875122</t>
+    <t xml:space="preserve">2.86174917221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83717370033264</t>
   </si>
   <si>
     <t xml:space="preserve">2.83886861801147</t>
@@ -3602,7 +3602,7 @@
     <t xml:space="preserve">2.45837569236755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38888669013977</t>
+    <t xml:space="preserve">2.38888692855835</t>
   </si>
   <si>
     <t xml:space="preserve">2.41769909858704</t>
@@ -3632,19 +3632,19 @@
     <t xml:space="preserve">2.47608494758606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44158434867859</t>
+    <t xml:space="preserve">2.44158411026001</t>
   </si>
   <si>
     <t xml:space="preserve">2.4875853061676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48493099212646</t>
+    <t xml:space="preserve">2.48493123054504</t>
   </si>
   <si>
     <t xml:space="preserve">2.41327595710754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45750784873962</t>
+    <t xml:space="preserve">2.45750761032104</t>
   </si>
   <si>
     <t xml:space="preserve">2.49112343788147</t>
@@ -3656,7 +3656,7 @@
     <t xml:space="preserve">2.45927667617798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37523674964905</t>
+    <t xml:space="preserve">2.37523698806763</t>
   </si>
   <si>
     <t xml:space="preserve">2.30446624755859</t>
@@ -3689,10 +3689,10 @@
     <t xml:space="preserve">2.43008399009705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44689202308655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50970053672791</t>
+    <t xml:space="preserve">2.44689226150513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50970077514648</t>
   </si>
   <si>
     <t xml:space="preserve">2.50527763366699</t>
@@ -3707,10 +3707,10 @@
     <t xml:space="preserve">2.4398148059845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4433536529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46900773048401</t>
+    <t xml:space="preserve">2.44335341453552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46900749206543</t>
   </si>
   <si>
     <t xml:space="preserve">2.47520017623901</t>
@@ -3728,13 +3728,13 @@
     <t xml:space="preserve">2.42300701141357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40442943572998</t>
+    <t xml:space="preserve">2.40442967414856</t>
   </si>
   <si>
     <t xml:space="preserve">2.36904430389404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29650449752808</t>
+    <t xml:space="preserve">2.2965042591095</t>
   </si>
   <si>
     <t xml:space="preserve">2.35312104225159</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">2.21158003807068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21246433258057</t>
+    <t xml:space="preserve">2.21246457099915</t>
   </si>
   <si>
     <t xml:space="preserve">2.24342679977417</t>
@@ -3752,10 +3752,10 @@
     <t xml:space="preserve">2.18504095077515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07269263267517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12842440605164</t>
+    <t xml:space="preserve">2.07269239425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12842416763306</t>
   </si>
   <si>
     <t xml:space="preserve">2.11603975296021</t>
@@ -3791,31 +3791,31 @@
     <t xml:space="preserve">2.04261517524719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97803723812103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98422968387604</t>
+    <t xml:space="preserve">1.97803699970245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98422944545746</t>
   </si>
   <si>
     <t xml:space="preserve">1.87895834445953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92584371566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9161125421524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93380570411682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94442105293274</t>
+    <t xml:space="preserve">1.92584383487701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91611278057098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93380546569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94442081451416</t>
   </si>
   <si>
     <t xml:space="preserve">2.00192213058472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90018951892853</t>
+    <t xml:space="preserve">1.90018939971924</t>
   </si>
   <si>
     <t xml:space="preserve">1.84003436565399</t>
@@ -3827,16 +3827,16 @@
     <t xml:space="preserve">1.87011194229126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80464911460876</t>
+    <t xml:space="preserve">1.80464923381805</t>
   </si>
   <si>
     <t xml:space="preserve">1.77280247211456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80022609233856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83030343055725</t>
+    <t xml:space="preserve">1.80022621154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83030354976654</t>
   </si>
   <si>
     <t xml:space="preserve">1.87807357311249</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">1.85153472423553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91257441043854</t>
+    <t xml:space="preserve">1.91257429122925</t>
   </si>
   <si>
     <t xml:space="preserve">1.99838364124298</t>
@@ -3869,10 +3869,10 @@
     <t xml:space="preserve">2.13373231887817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14434790611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14257836341858</t>
+    <t xml:space="preserve">2.14434766769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14257860183716</t>
   </si>
   <si>
     <t xml:space="preserve">2.13196301460266</t>
@@ -3890,10 +3890,10 @@
     <t xml:space="preserve">2.27969646453857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30800461769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28058123588562</t>
+    <t xml:space="preserve">2.30800485610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28058099746704</t>
   </si>
   <si>
     <t xml:space="preserve">2.29915857315063</t>
@@ -3920,10 +3920,10 @@
     <t xml:space="preserve">2.34515929222107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35046720504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33188986778259</t>
+    <t xml:space="preserve">2.35046744346619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33188962936401</t>
   </si>
   <si>
     <t xml:space="preserve">2.34338998794556</t>
@@ -3935,16 +3935,16 @@
     <t xml:space="preserve">2.37169814109802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37965989112854</t>
+    <t xml:space="preserve">2.37966012954712</t>
   </si>
   <si>
     <t xml:space="preserve">2.37612175941467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4327380657196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48050785064697</t>
+    <t xml:space="preserve">2.43273782730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48050808906555</t>
   </si>
   <si>
     <t xml:space="preserve">2.50350856781006</t>
@@ -3965,7 +3965,7 @@
     <t xml:space="preserve">2.26200389862061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24165749549866</t>
+    <t xml:space="preserve">2.24165725708008</t>
   </si>
   <si>
     <t xml:space="preserve">2.25758075714111</t>
@@ -3974,7 +3974,7 @@
     <t xml:space="preserve">2.25492691993713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20273351669312</t>
+    <t xml:space="preserve">2.20273375511169</t>
   </si>
   <si>
     <t xml:space="preserve">2.25227308273315</t>
@@ -3989,7 +3989,7 @@
     <t xml:space="preserve">2.2894275188446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33542847633362</t>
+    <t xml:space="preserve">2.3354287147522</t>
   </si>
   <si>
     <t xml:space="preserve">2.32304334640503</t>
@@ -4001,25 +4001,25 @@
     <t xml:space="preserve">2.45131516456604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42389130592346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42919921875</t>
+    <t xml:space="preserve">2.42389154434204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42919945716858</t>
   </si>
   <si>
     <t xml:space="preserve">2.40708374977112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34781336784363</t>
+    <t xml:space="preserve">2.34781312942505</t>
   </si>
   <si>
     <t xml:space="preserve">2.38850617408752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41416049003601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40177583694458</t>
+    <t xml:space="preserve">2.41416072845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.401775598526</t>
   </si>
   <si>
     <t xml:space="preserve">2.39646816253662</t>
@@ -4034,7 +4034,7 @@
     <t xml:space="preserve">2.3442747592926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41062211990356</t>
+    <t xml:space="preserve">2.41062188148499</t>
   </si>
   <si>
     <t xml:space="preserve">2.37081384658813</t>
@@ -4052,16 +4052,16 @@
     <t xml:space="preserve">2.3000431060791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29473543167114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26642727851868</t>
+    <t xml:space="preserve">2.29473567008972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2664270401001</t>
   </si>
   <si>
     <t xml:space="preserve">2.23458027839661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22661876678467</t>
+    <t xml:space="preserve">2.22661852836609</t>
   </si>
   <si>
     <t xml:space="preserve">2.22219562530518</t>
@@ -4094,7 +4094,7 @@
     <t xml:space="preserve">2.13727045059204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12753963470459</t>
+    <t xml:space="preserve">2.12753987312317</t>
   </si>
   <si>
     <t xml:space="preserve">2.11692404747009</t>
@@ -4112,7 +4112,7 @@
     <t xml:space="preserve">2.20361804962158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21423363685608</t>
+    <t xml:space="preserve">2.21423387527466</t>
   </si>
   <si>
     <t xml:space="preserve">2.24254202842712</t>
@@ -4127,10 +4127,10 @@
     <t xml:space="preserve">2.40266036987305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42212224006653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31950497627258</t>
+    <t xml:space="preserve">2.42212247848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31950521469116</t>
   </si>
   <si>
     <t xml:space="preserve">2.39558339118958</t>
@@ -4139,19 +4139,19 @@
     <t xml:space="preserve">2.39027547836304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46989226341248</t>
+    <t xml:space="preserve">2.46989250183105</t>
   </si>
   <si>
     <t xml:space="preserve">2.49820065498352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44512248039246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49643135070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53181672096252</t>
+    <t xml:space="preserve">2.44512271881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49643158912659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53181648254395</t>
   </si>
   <si>
     <t xml:space="preserve">2.52297043800354</t>
@@ -4160,10 +4160,10 @@
     <t xml:space="preserve">2.54066276550293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62381839752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6503574848175</t>
+    <t xml:space="preserve">2.62381863594055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65035724639893</t>
   </si>
   <si>
     <t xml:space="preserve">2.67689633369446</t>
@@ -4184,10 +4184,10 @@
     <t xml:space="preserve">2.63266468048096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62204885482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54950952529907</t>
+    <t xml:space="preserve">2.62204909324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54950928688049</t>
   </si>
   <si>
     <t xml:space="preserve">2.52827835083008</t>
@@ -4196,10 +4196,10 @@
     <t xml:space="preserve">2.57958674430847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58135581016541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60966444015503</t>
+    <t xml:space="preserve">2.58135604858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60966420173645</t>
   </si>
   <si>
     <t xml:space="preserve">2.58666372299194</t>
@@ -4217,7 +4217,7 @@
     <t xml:space="preserve">2.54420161247253</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55304789543152</t>
+    <t xml:space="preserve">2.55304765701294</t>
   </si>
   <si>
     <t xml:space="preserve">2.56366348266602</t>
@@ -4229,7 +4229,7 @@
     <t xml:space="preserve">2.53004717826843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56897139549255</t>
+    <t xml:space="preserve">2.56897115707397</t>
   </si>
   <si>
     <t xml:space="preserve">2.51812791824341</t>
@@ -5649,6 +5649,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.94199991226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05200004577637</t>
   </si>
 </sst>
 </file>
@@ -71221,7 +71224,7 @@
     </row>
     <row r="2510">
       <c r="A2510" s="1" t="n">
-        <v>45973.691724537</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2510" t="n">
         <v>6375755</v>
@@ -71242,6 +71245,32 @@
         <v>1878</v>
       </c>
       <c r="H2510" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" s="1" t="n">
+        <v>45974.6912037037</v>
+      </c>
+      <c r="B2511" t="n">
+        <v>5684714</v>
+      </c>
+      <c r="C2511" t="n">
+        <v>4.06599998474121</v>
+      </c>
+      <c r="D2511" t="n">
+        <v>3.96199989318848</v>
+      </c>
+      <c r="E2511" t="n">
+        <v>3.98399996757507</v>
+      </c>
+      <c r="F2511" t="n">
+        <v>4.05200004577637</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>1879</v>
+      </c>
+      <c r="H2511" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HER.MI.xlsx
+++ b/data/HER.MI.xlsx
@@ -38,109 +38,109 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70756649971008</t>
+    <t xml:space="preserve">1.7075662612915</t>
   </si>
   <si>
     <t xml:space="preserve">HER.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70896410942078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70616936683655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71036100387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68800342082977</t>
+    <t xml:space="preserve">1.70896399021149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70616924762726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71036112308502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68800365924835</t>
   </si>
   <si>
     <t xml:space="preserve">1.7257319688797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79140770435333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79420244693756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77044713497162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74669229984283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70337402820587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77324211597443</t>
+    <t xml:space="preserve">1.79140782356262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79420232772827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77044725418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74669218063354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70337414741516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77324187755585</t>
   </si>
   <si>
     <t xml:space="preserve">1.74948704242706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76625525951385</t>
+    <t xml:space="preserve">1.76625561714172</t>
   </si>
   <si>
     <t xml:space="preserve">1.80538129806519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79001009464264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80398380756378</t>
+    <t xml:space="preserve">1.79000997543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80398392677307</t>
   </si>
   <si>
     <t xml:space="preserve">1.83472573757172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81656002998352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80258619785309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84869921207428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85568583011627</t>
+    <t xml:space="preserve">1.81655991077423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80258643627167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84869909286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85568571090698</t>
   </si>
   <si>
     <t xml:space="preserve">1.84031522274017</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82354664802551</t>
+    <t xml:space="preserve">1.82354652881622</t>
   </si>
   <si>
     <t xml:space="preserve">1.82913625240326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72852683067322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74110305309296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75926840305328</t>
+    <t xml:space="preserve">1.72852659225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74110317230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75926864147186</t>
   </si>
   <si>
     <t xml:space="preserve">1.69918203353882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75507640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79559993743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78302347660065</t>
+    <t xml:space="preserve">1.75507652759552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79559969902039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78302359580994</t>
   </si>
   <si>
     <t xml:space="preserve">1.77603673934937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7983945608139</t>
+    <t xml:space="preserve">1.79839444160461</t>
   </si>
   <si>
     <t xml:space="preserve">1.80118918418884</t>
@@ -149,163 +149,163 @@
     <t xml:space="preserve">1.82075226306915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83053350448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78861284255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76485800743103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74529504776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73970544338226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72992420196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7438976764679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73271870613098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76346063613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77883172035217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76066613197327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77463936805725</t>
+    <t xml:space="preserve">1.83053362369537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78861308097839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76485776901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74529480934143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73970556259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72992408275604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74389755725861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73271882534027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76346051692963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7788313627243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76066589355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77463948726654</t>
   </si>
   <si>
     <t xml:space="preserve">1.79699718952179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83752000331879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81097054481506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85708343982697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8431099653244</t>
+    <t xml:space="preserve">1.83752048015594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81097042560577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85708332061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84310984611511</t>
   </si>
   <si>
     <t xml:space="preserve">1.76765275001526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78162610530853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7872154712677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77743399143219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78022861480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80817580223083</t>
+    <t xml:space="preserve">1.78162586688995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78721559047699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77743411064148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.780228972435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80817568302155</t>
   </si>
   <si>
     <t xml:space="preserve">1.80957329273224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79280483722687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78442060947418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75647389888763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74808943271637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82634150981903</t>
+    <t xml:space="preserve">1.79280519485474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78442096710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75647377967834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74808990955353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82634174823761</t>
   </si>
   <si>
     <t xml:space="preserve">1.84590446949005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83193075656891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84450721740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82214963436127</t>
+    <t xml:space="preserve">1.83193099498749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84450709819794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82214939594269</t>
   </si>
   <si>
     <t xml:space="preserve">1.8333283662796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82494390010834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81376540660858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76206314563751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73132157325745</t>
+    <t xml:space="preserve">1.82494413852692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81376516819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76206302642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73132169246674</t>
   </si>
   <si>
     <t xml:space="preserve">1.74250030517578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71175849437714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7575101852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77344799041748</t>
+    <t xml:space="preserve">1.71175813674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75751042366028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77344822883606</t>
   </si>
   <si>
     <t xml:space="preserve">1.74012362957001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7589590549469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70390129089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67347431182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70969653129578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73867464065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78069245815277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83430182933807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80822157859802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81111943721771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78503942489624</t>
+    <t xml:space="preserve">1.75895941257477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70390141010284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67347419261932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70969665050507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7386748790741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78069269657135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83430218696594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80822169780731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.811119556427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78503966331482</t>
   </si>
   <si>
     <t xml:space="preserve">1.77924394607544</t>
@@ -320,94 +320,94 @@
     <t xml:space="preserve">1.7459192276001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77055025100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76620364189148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76185667514801</t>
+    <t xml:space="preserve">1.77055048942566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7662034034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76185703277588</t>
   </si>
   <si>
     <t xml:space="preserve">1.76910138130188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77489733695984</t>
+    <t xml:space="preserve">1.77489709854126</t>
   </si>
   <si>
     <t xml:space="preserve">1.78359055519104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83719944953918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85748386383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85023963451385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83575069904327</t>
+    <t xml:space="preserve">1.83719968795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85748422145844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85023939609528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83575057983398</t>
   </si>
   <si>
     <t xml:space="preserve">1.86617755889893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83140408992767</t>
+    <t xml:space="preserve">1.83140420913696</t>
   </si>
   <si>
     <t xml:space="preserve">1.84444415569305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79663062095642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81981313228607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81256830692291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74881732463837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74447059631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77634596824646</t>
+    <t xml:space="preserve">1.79663038253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81981289386749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81256806850433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7488169670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7444703578949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77634608745575</t>
   </si>
   <si>
     <t xml:space="preserve">1.79083514213562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79952836036682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78648865222931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78938627243042</t>
+    <t xml:space="preserve">1.79952847957611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78648841381073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78938603401184</t>
   </si>
   <si>
     <t xml:space="preserve">1.8154661655426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75606167316437</t>
+    <t xml:space="preserve">1.75606143474579</t>
   </si>
   <si>
     <t xml:space="preserve">1.73577702045441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70679914951324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73722589015961</t>
+    <t xml:space="preserve">1.70679903030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73722577095032</t>
   </si>
   <si>
     <t xml:space="preserve">1.75461256504059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71114563941956</t>
+    <t xml:space="preserve">1.71114540100098</t>
   </si>
   <si>
     <t xml:space="preserve">1.70824778079987</t>
@@ -419,19 +419,19 @@
     <t xml:space="preserve">1.69231009483337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71694135665894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69665682315826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63145637512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60537648200989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59233605861664</t>
+    <t xml:space="preserve">1.71694111824036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69665658473969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63145649433136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60537660121918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59233629703522</t>
   </si>
   <si>
     <t xml:space="preserve">1.57929635047913</t>
@@ -443,46 +443,46 @@
     <t xml:space="preserve">1.6097229719162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61406970024109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62131404876709</t>
+    <t xml:space="preserve">1.61406981945038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6213139295578</t>
   </si>
   <si>
     <t xml:space="preserve">1.63290524482727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61841642856598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63870108127594</t>
+    <t xml:space="preserve">1.61841630935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63870096206665</t>
   </si>
   <si>
     <t xml:space="preserve">1.63725209236145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65029227733612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62276303768158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61551856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61696779727936</t>
+    <t xml:space="preserve">1.65029203891754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62276291847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61551868915558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61696767807007</t>
   </si>
   <si>
     <t xml:space="preserve">1.62566077709198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6618834733963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66912770271301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6879631280899</t>
+    <t xml:space="preserve">1.66188299655914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66912758350372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68796336650848</t>
   </si>
   <si>
     <t xml:space="preserve">1.59378516674042</t>
@@ -491,34 +491,34 @@
     <t xml:space="preserve">1.56625616550446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56335854530334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54307401180267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46048676967621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46338438987732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44599783420563</t>
+    <t xml:space="preserve">1.56335842609406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54307389259338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4604868888855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4633846282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44599795341492</t>
   </si>
   <si>
     <t xml:space="preserve">1.44527328014374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4503448009491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43005990982056</t>
+    <t xml:space="preserve">1.45034456253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43006002902985</t>
   </si>
   <si>
     <t xml:space="preserve">1.42209112644196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3960108757019</t>
+    <t xml:space="preserve">1.39601099491119</t>
   </si>
   <si>
     <t xml:space="preserve">1.3945620059967</t>
@@ -530,25 +530,25 @@
     <t xml:space="preserve">1.41267323493958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39818406105042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40180659294128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40542876720428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41629528999329</t>
+    <t xml:space="preserve">1.39818429946899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40180647373199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40542888641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41629540920258</t>
   </si>
   <si>
     <t xml:space="preserve">1.38152194023132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35906410217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37717509269714</t>
+    <t xml:space="preserve">1.35906434059143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37717521190643</t>
   </si>
   <si>
     <t xml:space="preserve">1.43875336647034</t>
@@ -557,22 +557,22 @@
     <t xml:space="preserve">1.48077130317688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49236249923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48511803150177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53293144702911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52713584899902</t>
+    <t xml:space="preserve">1.49236238002777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48511791229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5329315662384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5271360874176</t>
   </si>
   <si>
     <t xml:space="preserve">1.50105583667755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50685131549835</t>
+    <t xml:space="preserve">1.50685143470764</t>
   </si>
   <si>
     <t xml:space="preserve">1.54886949062347</t>
@@ -581,67 +581,67 @@
     <t xml:space="preserve">1.55756270885468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57060277462006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59088742733002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56915366649628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58798968791962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60827422142029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59668302536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59958064556122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56480741500854</t>
+    <t xml:space="preserve">1.57060289382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59088754653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56915378570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58798956871033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.608274102211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59668290615082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5995808839798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56480729579926</t>
   </si>
   <si>
     <t xml:space="preserve">1.65174102783203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64159870147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65319013595581</t>
+    <t xml:space="preserve">1.64159858226776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65318989753723</t>
   </si>
   <si>
     <t xml:space="preserve">1.65463864803314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65898561477661</t>
+    <t xml:space="preserve">1.65898513793945</t>
   </si>
   <si>
     <t xml:space="preserve">1.64014971256256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64304745197296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57494950294495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57784736156464</t>
+    <t xml:space="preserve">1.64304757118225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57494962215424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57784748077393</t>
   </si>
   <si>
     <t xml:space="preserve">1.55176723003387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58654093742371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63000762462616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68216776847839</t>
+    <t xml:space="preserve">1.58654081821442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63000738620758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68216788768768</t>
   </si>
   <si>
     <t xml:space="preserve">1.66622996330261</t>
@@ -650,25 +650,25 @@
     <t xml:space="preserve">1.6778210401535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69086122512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69375920295715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69810557365417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69520771503448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71404349803925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72998142242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73432803153992</t>
+    <t xml:space="preserve">1.69086134433746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69375908374786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69810593128204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69520795345306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71404325962067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72998130321503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73432791233063</t>
   </si>
   <si>
     <t xml:space="preserve">1.71983897686005</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">1.72418570518494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71549236774445</t>
+    <t xml:space="preserve">1.71549224853516</t>
   </si>
   <si>
     <t xml:space="preserve">1.71839010715485</t>
@@ -686,97 +686,97 @@
     <t xml:space="preserve">1.74157249927521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78214168548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78793704509735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81401741504669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82995545864105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86907529830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89950203895569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91399109363556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91544008255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8806666135788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87197351455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88935983181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90095090866089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90529799461365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91254234313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94441795349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93717336654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8792177438736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8835643529892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92847979068756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8980530500412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88791108131409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90240025520325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91688907146454</t>
+    <t xml:space="preserve">1.78214204311371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78793728351593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8140172958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82995533943176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86907517910004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8995019197464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91399073600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91543984413147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88066685199738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87197327613831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88935995101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90095102787018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90529763698578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91254246234894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9444180727005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93717312812805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87921786308289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88356447219849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92847990989685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89805316925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88791084289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90239977836609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91688883304596</t>
   </si>
   <si>
     <t xml:space="preserve">1.92413306236267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93572473526001</t>
+    <t xml:space="preserve">1.93572461605072</t>
   </si>
   <si>
     <t xml:space="preserve">1.93862223625183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94876480102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99512910842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02845358848572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05743169784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06902313232422</t>
+    <t xml:space="preserve">1.9487646818161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99512934684753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02845406532288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05743193626404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06902265548706</t>
   </si>
   <si>
     <t xml:space="preserve">2.05163645744324</t>
@@ -785,19 +785,19 @@
     <t xml:space="preserve">2.10234761238098</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06467628479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0385959148407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07336950302124</t>
+    <t xml:space="preserve">2.06467580795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03859615325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07336926460266</t>
   </si>
   <si>
     <t xml:space="preserve">2.0864098072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12842750549316</t>
+    <t xml:space="preserve">2.12842774391174</t>
   </si>
   <si>
     <t xml:space="preserve">2.11248970031738</t>
@@ -806,10 +806,10 @@
     <t xml:space="preserve">2.11104083061218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10089826583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05453372001648</t>
+    <t xml:space="preserve">2.10089874267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05453395843506</t>
   </si>
   <si>
     <t xml:space="preserve">2.0893075466156</t>
@@ -818,16 +818,16 @@
     <t xml:space="preserve">2.12263226509094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07916522026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10379648208618</t>
+    <t xml:space="preserve">2.07916498184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10379672050476</t>
   </si>
   <si>
     <t xml:space="preserve">2.11973404884338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10814332962036</t>
+    <t xml:space="preserve">2.10814309120178</t>
   </si>
   <si>
     <t xml:space="preserve">2.14726305007935</t>
@@ -839,55 +839,55 @@
     <t xml:space="preserve">2.15450763702393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14291620254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15595674514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1679093837738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17836737632751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17239141464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09918165206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11262845993042</t>
+    <t xml:space="preserve">2.14291644096375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15595650672913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16790914535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17836761474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17239189147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09918189048767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11262822151184</t>
   </si>
   <si>
     <t xml:space="preserve">2.07228827476501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05884170532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01700758934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99907839298248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01103115081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00804257392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99758434295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95126795768738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97069084644318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00505471229553</t>
+    <t xml:space="preserve">2.05884146690369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01700735092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99907851219177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01103067398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00804305076599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99758446216583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95126807689667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97069072723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00505495071411</t>
   </si>
   <si>
     <t xml:space="preserve">1.98264360427856</t>
@@ -896,37 +896,37 @@
     <t xml:space="preserve">2.03045392036438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05286502838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0394184589386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03194832801819</t>
+    <t xml:space="preserve">2.05286526679993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03941822052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03194808959961</t>
   </si>
   <si>
     <t xml:space="preserve">2.04539465904236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0244779586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06182956695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07677054405212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03344225883484</t>
+    <t xml:space="preserve">2.02447819709778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06182980537415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0767707824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03344249725342</t>
   </si>
   <si>
     <t xml:space="preserve">2.01401901245117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05435943603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04390120506287</t>
+    <t xml:space="preserve">2.05435919761658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04390096664429</t>
   </si>
   <si>
     <t xml:space="preserve">2.04240655899048</t>
@@ -941,37 +941,37 @@
     <t xml:space="preserve">2.04987692832947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00206661224365</t>
+    <t xml:space="preserve">2.00206637382507</t>
   </si>
   <si>
     <t xml:space="preserve">2.05585336685181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03493618965149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99459648132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97517323493958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96172630786896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96770262718201</t>
+    <t xml:space="preserve">2.03493595123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99459624290466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97517347335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96172642707825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9677027463913</t>
   </si>
   <si>
     <t xml:space="preserve">2.02597188949585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01252484321594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00953722000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00356030464172</t>
+    <t xml:space="preserve">2.01252508163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00953698158264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0035605430603</t>
   </si>
   <si>
     <t xml:space="preserve">2.07826447486877</t>
@@ -980,52 +980,52 @@
     <t xml:space="preserve">2.01850128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00057244300842</t>
+    <t xml:space="preserve">2.000572681427</t>
   </si>
   <si>
     <t xml:space="preserve">1.98563182353973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98712563514709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97218501567841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02148962020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03792428970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06033563613892</t>
+    <t xml:space="preserve">1.98712587356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97218525409698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02148985862732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03792452812195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06033539772034</t>
   </si>
   <si>
     <t xml:space="preserve">2.07079434394836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07378220558167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06631183624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06332397460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07527661323547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08424115180969</t>
+    <t xml:space="preserve">2.07378244400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06631207466125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0633237361908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07527637481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08424067497253</t>
   </si>
   <si>
     <t xml:space="preserve">2.10665202140808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12458086013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14998030662537</t>
+    <t xml:space="preserve">2.12458109855652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14998054504395</t>
   </si>
   <si>
     <t xml:space="preserve">2.16043901443481</t>
@@ -1034,28 +1034,28 @@
     <t xml:space="preserve">2.18135619163513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19629669189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18733239173889</t>
+    <t xml:space="preserve">2.19629693031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18733263015747</t>
   </si>
   <si>
     <t xml:space="preserve">2.17986178398132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16641521453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17089748382568</t>
+    <t xml:space="preserve">2.16641545295715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17089700698853</t>
   </si>
   <si>
     <t xml:space="preserve">2.191814661026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19330835342407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1948025226593</t>
+    <t xml:space="preserve">2.19330883026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19480276107788</t>
   </si>
   <si>
     <t xml:space="preserve">2.22468423843384</t>
@@ -1064,34 +1064,34 @@
     <t xml:space="preserve">2.27100086212158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2560601234436</t>
+    <t xml:space="preserve">2.25606036186218</t>
   </si>
   <si>
     <t xml:space="preserve">2.25904822349548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28145933151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29490613937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30536484718323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30088257789612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33972859382629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28892993927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27398872375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30387091636658</t>
+    <t xml:space="preserve">2.28145956993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29490637779236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30536460876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30088233947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33972835540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28892970085144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27398920059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30387115478516</t>
   </si>
   <si>
     <t xml:space="preserve">2.31582307815552</t>
@@ -1103,25 +1103,25 @@
     <t xml:space="preserve">2.25755429267883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27847099304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22916626930237</t>
+    <t xml:space="preserve">2.27847123146057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22916650772095</t>
   </si>
   <si>
     <t xml:space="preserve">2.22617840766907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21870803833008</t>
+    <t xml:space="preserve">2.2187077999115</t>
   </si>
   <si>
     <t xml:space="preserve">2.17388558387756</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15446281433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21123766899109</t>
+    <t xml:space="preserve">2.15446257591248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21123743057251</t>
   </si>
   <si>
     <t xml:space="preserve">2.26054239273071</t>
@@ -1133,16 +1133,16 @@
     <t xml:space="preserve">2.24111938476562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26950716972351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23813104629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2769775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28594183921814</t>
+    <t xml:space="preserve">2.26950669288635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23813128471375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27697706222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28594160079956</t>
   </si>
   <si>
     <t xml:space="preserve">2.29938864707947</t>
@@ -1154,31 +1154,31 @@
     <t xml:space="preserve">2.2799654006958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24560141563416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18434405326843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13503909111023</t>
+    <t xml:space="preserve">2.24560165405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18434429168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13503956794739</t>
   </si>
   <si>
     <t xml:space="preserve">2.11113429069519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05734705924988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02895998954773</t>
+    <t xml:space="preserve">2.05734729766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02896022796631</t>
   </si>
   <si>
     <t xml:space="preserve">2.09469962120056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12607502937317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13354563713074</t>
+    <t xml:space="preserve">2.12607526779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13354539871216</t>
   </si>
   <si>
     <t xml:space="preserve">2.09320545196533</t>
@@ -1190,55 +1190,55 @@
     <t xml:space="preserve">2.04091262817383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08573484420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08274674415588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08125257492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10216999053955</t>
+    <t xml:space="preserve">2.08573532104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08274698257446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08125281333923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10216975212097</t>
   </si>
   <si>
     <t xml:space="preserve">2.09768748283386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12009859085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21273136138916</t>
+    <t xml:space="preserve">2.12009906768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2127320766449</t>
   </si>
   <si>
     <t xml:space="preserve">2.22169613838196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2306604385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24261331558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26353025436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23514318466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25307202339172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29341220855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29789447784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28444790840149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2276725769043</t>
+    <t xml:space="preserve">2.23066091537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24261355400085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26353073120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23514294624329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25307178497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29341173171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29789400100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28444743156433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22767281532288</t>
   </si>
   <si>
     <t xml:space="preserve">2.25157785415649</t>
@@ -1247,31 +1247,31 @@
     <t xml:space="preserve">2.14101576805115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12159299850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02298355102539</t>
+    <t xml:space="preserve">2.12159276008606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02298378944397</t>
   </si>
   <si>
     <t xml:space="preserve">1.94678568840027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96471464633942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98114943504333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96919667720795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97816121578217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94827997684479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02856683731079</t>
+    <t xml:space="preserve">1.964714884758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98114955425262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96919691562653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97816133499146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94827950000763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02856659889221</t>
   </si>
   <si>
     <t xml:space="preserve">2.06108570098877</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">2.07192540168762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03785800933838</t>
+    <t xml:space="preserve">2.0378577709198</t>
   </si>
   <si>
     <t xml:space="preserve">2.04095482826233</t>
@@ -1292,13 +1292,13 @@
     <t xml:space="preserve">2.0595371723175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08895921707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06728005409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10599279403687</t>
+    <t xml:space="preserve">2.08895897865295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06727981567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10599327087402</t>
   </si>
   <si>
     <t xml:space="preserve">2.13541483879089</t>
@@ -1307,10 +1307,10 @@
     <t xml:space="preserve">2.15399742126465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16019153594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14470624923706</t>
+    <t xml:space="preserve">2.16019129753113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14470601081848</t>
   </si>
   <si>
     <t xml:space="preserve">2.13696336746216</t>
@@ -1337,31 +1337,31 @@
     <t xml:space="preserve">2.09205627441406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20664715766907</t>
+    <t xml:space="preserve">2.20664691925049</t>
   </si>
   <si>
     <t xml:space="preserve">2.17103099822998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19580745697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18651604652405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21748685836792</t>
+    <t xml:space="preserve">2.19580769538879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18651628494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21748661994934</t>
   </si>
   <si>
     <t xml:space="preserve">2.21593832969666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1834192276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16328811645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15090012550354</t>
+    <t xml:space="preserve">2.18341898918152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16328835487366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1509006023407</t>
   </si>
   <si>
     <t xml:space="preserve">2.13231778144836</t>
@@ -1373,10 +1373,10 @@
     <t xml:space="preserve">2.11992955207825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16638541221619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15709400177002</t>
+    <t xml:space="preserve">2.16638565063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15709447860718</t>
   </si>
   <si>
     <t xml:space="preserve">2.14935159683228</t>
@@ -1388,31 +1388,31 @@
     <t xml:space="preserve">2.09979891777039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09050798416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10754156112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12457537651062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12767195701599</t>
+    <t xml:space="preserve">2.0905077457428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10754132270813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12457513809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12767243385315</t>
   </si>
   <si>
     <t xml:space="preserve">2.18806457519531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20045304298401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1973557472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20200133323669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20819544792175</t>
+    <t xml:space="preserve">2.20045328140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19735598564148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20200157165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20819520950317</t>
   </si>
   <si>
     <t xml:space="preserve">2.21129274368286</t>
@@ -1427,97 +1427,97 @@
     <t xml:space="preserve">2.11683249473572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07657074928284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06882858276367</t>
+    <t xml:space="preserve">2.07657098770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06882810592651</t>
   </si>
   <si>
     <t xml:space="preserve">2.05179476737976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01462984085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96198010444641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98211121559143</t>
+    <t xml:space="preserve">2.01463007926941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9619802236557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98211109638214</t>
   </si>
   <si>
     <t xml:space="preserve">1.93720376491547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90313637256622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86287486553192</t>
+    <t xml:space="preserve">1.90313601493835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86287438869476</t>
   </si>
   <si>
     <t xml:space="preserve">1.91552436351776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87216591835022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89384508132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90158784389496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87061738967896</t>
+    <t xml:space="preserve">1.87216579914093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89384484291077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90158796310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87061715126038</t>
   </si>
   <si>
     <t xml:space="preserve">1.8597776889801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92791271209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89694237709045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8907482624054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87990880012512</t>
+    <t xml:space="preserve">1.92791247367859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89694225788116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89074814319611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87990832328796</t>
   </si>
   <si>
     <t xml:space="preserve">1.88919961452484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88765108585358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90468490123749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92171859741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96662580966949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91862165927887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97901380062103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96972298622131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97746551036835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94184970855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93101000785828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92481565475464</t>
+    <t xml:space="preserve">1.88765096664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9046847820282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92171847820282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96662569046021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.918621301651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97901391983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96972274780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97746539115906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94184923171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9310097694397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92481589317322</t>
   </si>
   <si>
     <t xml:space="preserve">1.92017030715942</t>
@@ -1529,28 +1529,28 @@
     <t xml:space="preserve">1.90933060646057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87835991382599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93875217437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86906886100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94804346561432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98675668239594</t>
+    <t xml:space="preserve">1.8783597946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93875205516815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86906850337982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94804322719574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98675644397736</t>
   </si>
   <si>
     <t xml:space="preserve">2.09360456466675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03630948066711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06573104858398</t>
+    <t xml:space="preserve">2.03630924224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06573128700256</t>
   </si>
   <si>
     <t xml:space="preserve">2.09825038909912</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">2.19116163253784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19425916671753</t>
+    <t xml:space="preserve">2.19425892829895</t>
   </si>
   <si>
     <t xml:space="preserve">2.17877340316772</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">2.2050986289978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20974397659302</t>
+    <t xml:space="preserve">2.2097442150116</t>
   </si>
   <si>
     <t xml:space="preserve">2.22987484931946</t>
@@ -1580,13 +1580,13 @@
     <t xml:space="preserve">2.20354986190796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19890427589417</t>
+    <t xml:space="preserve">2.19890451431274</t>
   </si>
   <si>
     <t xml:space="preserve">2.22677779197693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26084542274475</t>
+    <t xml:space="preserve">2.26084566116333</t>
   </si>
   <si>
     <t xml:space="preserve">2.26239371299744</t>
@@ -1595,16 +1595,16 @@
     <t xml:space="preserve">2.28562164306641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29336404800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28252458572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28407311439514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29026699066162</t>
+    <t xml:space="preserve">2.29336452484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28252482414246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28407335281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2902672290802</t>
   </si>
   <si>
     <t xml:space="preserve">2.27013659477234</t>
@@ -1613,7 +1613,7 @@
     <t xml:space="preserve">2.25619983673096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28097629547119</t>
+    <t xml:space="preserve">2.28097653388977</t>
   </si>
   <si>
     <t xml:space="preserve">2.30265545845032</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">2.30110692977905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30730080604553</t>
+    <t xml:space="preserve">2.30730104446411</t>
   </si>
   <si>
     <t xml:space="preserve">2.29800987243652</t>
@@ -1634,34 +1634,34 @@
     <t xml:space="preserve">2.25929665565491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32433462142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29181599617004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25465130805969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2685878276825</t>
+    <t xml:space="preserve">2.32433485984802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29181623458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25465106964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26858806610107</t>
   </si>
   <si>
     <t xml:space="preserve">2.26549100875854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29955840110779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29646134376526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31349515914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32123804092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25774812698364</t>
+    <t xml:space="preserve">2.29955863952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29646182060242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31349492073059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32123780250549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25774836540222</t>
   </si>
   <si>
     <t xml:space="preserve">2.23916602134705</t>
@@ -1676,10 +1676,10 @@
     <t xml:space="preserve">2.38163042068481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4033100605011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42808604240417</t>
+    <t xml:space="preserve">2.40330982208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4280858039856</t>
   </si>
   <si>
     <t xml:space="preserve">2.4311830997467</t>
@@ -1688,10 +1688,10 @@
     <t xml:space="preserve">2.47609043121338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4946722984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49002718925476</t>
+    <t xml:space="preserve">2.49467253684998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49002695083618</t>
   </si>
   <si>
     <t xml:space="preserve">2.49622130393982</t>
@@ -1700,10 +1700,10 @@
     <t xml:space="preserve">2.50860929489136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54887056350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52099776268005</t>
+    <t xml:space="preserve">2.54887080192566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5209972858429</t>
   </si>
   <si>
     <t xml:space="preserve">2.5024151802063</t>
@@ -1712,19 +1712,19 @@
     <t xml:space="preserve">2.51635193824768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46215343475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47918725013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46525096893311</t>
+    <t xml:space="preserve">2.46215391159058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47918701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46525073051453</t>
   </si>
   <si>
     <t xml:space="preserve">2.43428015708923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44976544380188</t>
+    <t xml:space="preserve">2.4497652053833</t>
   </si>
   <si>
     <t xml:space="preserve">2.45286250114441</t>
@@ -1733,40 +1733,40 @@
     <t xml:space="preserve">2.46679925918579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44666838645935</t>
+    <t xml:space="preserve">2.44666862487793</t>
   </si>
   <si>
     <t xml:space="preserve">2.4575080871582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47144460678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45905685424805</t>
+    <t xml:space="preserve">2.47144508361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45905661582947</t>
   </si>
   <si>
     <t xml:space="preserve">2.42653775215149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44821691513062</t>
+    <t xml:space="preserve">2.44821715354919</t>
   </si>
   <si>
     <t xml:space="preserve">2.42963457107544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48692989349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53028869628906</t>
+    <t xml:space="preserve">2.48693037033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53028845787048</t>
   </si>
   <si>
     <t xml:space="preserve">2.53803110122681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54112839698792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54422545433044</t>
+    <t xml:space="preserve">2.54112815856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54422521591187</t>
   </si>
   <si>
     <t xml:space="preserve">2.55661344528198</t>
@@ -1778,22 +1778,22 @@
     <t xml:space="preserve">2.53648281097412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53493428230286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5287401676178</t>
+    <t xml:space="preserve">2.53493404388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52873992919922</t>
   </si>
   <si>
     <t xml:space="preserve">2.51790046691895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56435632705688</t>
+    <t xml:space="preserve">2.56435608863831</t>
   </si>
   <si>
     <t xml:space="preserve">2.5906810760498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6030695438385</t>
+    <t xml:space="preserve">2.60306906700134</t>
   </si>
   <si>
     <t xml:space="preserve">2.60461759567261</t>
@@ -1802,13 +1802,13 @@
     <t xml:space="preserve">2.59997200965881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60152053833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58913230895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58603572845459</t>
+    <t xml:space="preserve">2.60152077674866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58913254737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58603549003601</t>
   </si>
   <si>
     <t xml:space="preserve">2.64642786979675</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">2.68514108657837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7161111831665</t>
+    <t xml:space="preserve">2.71611142158508</t>
   </si>
   <si>
     <t xml:space="preserve">2.69698429107666</t>
@@ -1829,13 +1829,13 @@
     <t xml:space="preserve">2.67945051193237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68263816833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65075922012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68104410171509</t>
+    <t xml:space="preserve">2.68263792991638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65075898170471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68104457855225</t>
   </si>
   <si>
     <t xml:space="preserve">2.66669869422913</t>
@@ -1847,10 +1847,10 @@
     <t xml:space="preserve">2.81174921989441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80856132507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7846519947052</t>
+    <t xml:space="preserve">2.80856156349182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78465175628662</t>
   </si>
   <si>
     <t xml:space="preserve">2.77349424362183</t>
@@ -1862,10 +1862,10 @@
     <t xml:space="preserve">2.79740381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79580974578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82768893241882</t>
+    <t xml:space="preserve">2.79580926895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8276891708374</t>
   </si>
   <si>
     <t xml:space="preserve">2.80696749687195</t>
@@ -1874,10 +1874,10 @@
     <t xml:space="preserve">2.75914835929871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74480295181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74958491325378</t>
+    <t xml:space="preserve">2.74480271339417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74958467483521</t>
   </si>
   <si>
     <t xml:space="preserve">2.7320511341095</t>
@@ -1886,22 +1886,22 @@
     <t xml:space="preserve">2.72886323928833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73364496231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66988635063171</t>
+    <t xml:space="preserve">2.73364520072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66988682746887</t>
   </si>
   <si>
     <t xml:space="preserve">2.68582630157471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73683285713196</t>
+    <t xml:space="preserve">2.73683333396912</t>
   </si>
   <si>
     <t xml:space="preserve">2.71132946014404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69539022445679</t>
+    <t xml:space="preserve">2.69538998603821</t>
   </si>
   <si>
     <t xml:space="preserve">2.706547498703</t>
@@ -1910,13 +1910,13 @@
     <t xml:space="preserve">2.72726917266846</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70495390892029</t>
+    <t xml:space="preserve">2.70495367050171</t>
   </si>
   <si>
     <t xml:space="preserve">2.73523902893066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.687420129776</t>
+    <t xml:space="preserve">2.68742036819458</t>
   </si>
   <si>
     <t xml:space="preserve">2.76233649253845</t>
@@ -1925,10 +1925,10 @@
     <t xml:space="preserve">2.78783988952637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77827620506287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78624606132507</t>
+    <t xml:space="preserve">2.77827596664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78624582290649</t>
   </si>
   <si>
     <t xml:space="preserve">2.81334328651428</t>
@@ -1937,49 +1937,49 @@
     <t xml:space="preserve">2.88188362121582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87869596481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91535711288452</t>
+    <t xml:space="preserve">2.87869548797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91535663604736</t>
   </si>
   <si>
     <t xml:space="preserve">2.89144730567932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88666558265686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88825964927673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91695094108582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89622926712036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80059146881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79262161254883</t>
+    <t xml:space="preserve">2.88666534423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88825941085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91695117950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89622902870178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80059123039246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79262185096741</t>
   </si>
   <si>
     <t xml:space="preserve">2.84522223472595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81812500953674</t>
+    <t xml:space="preserve">2.81812524795532</t>
   </si>
   <si>
     <t xml:space="preserve">2.82131314277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8468165397644</t>
+    <t xml:space="preserve">2.84681630134583</t>
   </si>
   <si>
     <t xml:space="preserve">2.90738701820374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90419936180115</t>
+    <t xml:space="preserve">2.90419912338257</t>
   </si>
   <si>
     <t xml:space="preserve">2.86913180351257</t>
@@ -1988,25 +1988,25 @@
     <t xml:space="preserve">2.95201802253723</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95042395591736</t>
+    <t xml:space="preserve">2.95042419433594</t>
   </si>
   <si>
     <t xml:space="preserve">3.02055835723877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96476936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00143074989319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95679974555969</t>
+    <t xml:space="preserve">2.9647696018219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00143098831177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95680022239685</t>
   </si>
   <si>
     <t xml:space="preserve">2.97114539146423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01577639579773</t>
+    <t xml:space="preserve">3.01577615737915</t>
   </si>
   <si>
     <t xml:space="preserve">3.02215218544006</t>
@@ -2018,52 +2018,52 @@
     <t xml:space="preserve">2.97911524772644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00302481651306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01418256759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9838969707489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02374601364136</t>
+    <t xml:space="preserve">3.00302457809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01418280601501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98389720916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02374625205994</t>
   </si>
   <si>
     <t xml:space="preserve">2.99664878845215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96636319160461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99346089363098</t>
+    <t xml:space="preserve">2.96636343002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99346113204956</t>
   </si>
   <si>
     <t xml:space="preserve">3.00621271133423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04606151580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05881357192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04924964904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06997108459473</t>
+    <t xml:space="preserve">3.04606199264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05881333351135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04924941062927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06997084617615</t>
   </si>
   <si>
     <t xml:space="preserve">3.03012204170227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05403184890747</t>
+    <t xml:space="preserve">3.05403161048889</t>
   </si>
   <si>
     <t xml:space="preserve">3.06678318977356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05243754386902</t>
+    <t xml:space="preserve">3.05243730545044</t>
   </si>
   <si>
     <t xml:space="preserve">3.07315897941589</t>
@@ -2075,10 +2075,10 @@
     <t xml:space="preserve">3.10025644302368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17357897758484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1974880695343</t>
+    <t xml:space="preserve">3.17357873916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19748830795288</t>
   </si>
   <si>
     <t xml:space="preserve">3.19430017471313</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">3.21820974349976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19589424133301</t>
+    <t xml:space="preserve">3.19589447975159</t>
   </si>
   <si>
     <t xml:space="preserve">3.16242098808289</t>
@@ -2096,49 +2096,49 @@
     <t xml:space="preserve">3.17995452880859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15604543685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18473649024963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17517232894897</t>
+    <t xml:space="preserve">3.15604519844055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18473672866821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17517256736755</t>
   </si>
   <si>
     <t xml:space="preserve">3.19111251831055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06200122833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08750486373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12416577339172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10185027122498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09547424316406</t>
+    <t xml:space="preserve">3.0620014667511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08750510215759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1241660118103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10185050964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09547448158264</t>
   </si>
   <si>
     <t xml:space="preserve">3.07156538963318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10344457626343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11141419410706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06040716171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12735414505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17198491096497</t>
+    <t xml:space="preserve">3.10344433784485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11141395568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06040740013123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12735390663147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17198467254639</t>
   </si>
   <si>
     <t xml:space="preserve">3.16879677772522</t>
@@ -2147,7 +2147,7 @@
     <t xml:space="preserve">3.16401505470276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22139739990234</t>
+    <t xml:space="preserve">3.22139716148376</t>
   </si>
   <si>
     <t xml:space="preserve">3.16082715988159</t>
@@ -2156,40 +2156,40 @@
     <t xml:space="preserve">3.16560864448547</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10822653770447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09706830978394</t>
+    <t xml:space="preserve">3.10822629928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09706854820251</t>
   </si>
   <si>
     <t xml:space="preserve">3.10663223266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08112907409668</t>
+    <t xml:space="preserve">3.0811288356781</t>
   </si>
   <si>
     <t xml:space="preserve">3.07794094085693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14329361915588</t>
+    <t xml:space="preserve">3.1432933807373</t>
   </si>
   <si>
     <t xml:space="preserve">3.18633031845093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18314266204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13213586807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27240419387817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.377605676651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31384706497192</t>
+    <t xml:space="preserve">3.18314242362976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13213562965393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27240443229675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37760591506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3138473033905</t>
   </si>
   <si>
     <t xml:space="preserve">3.44774055480957</t>
@@ -2204,52 +2204,52 @@
     <t xml:space="preserve">3.26921653747559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27718591690063</t>
+    <t xml:space="preserve">3.27718639373779</t>
   </si>
   <si>
     <t xml:space="preserve">3.28674983978271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33297514915466</t>
+    <t xml:space="preserve">3.33297491073608</t>
   </si>
   <si>
     <t xml:space="preserve">3.37282395362854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38557600975037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40948486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42701864242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43977069854736</t>
+    <t xml:space="preserve">3.38557577133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40948510169983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4270191192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43977046012878</t>
   </si>
   <si>
     <t xml:space="preserve">3.47802519798279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45252180099487</t>
+    <t xml:space="preserve">3.45252203941345</t>
   </si>
   <si>
     <t xml:space="preserve">3.45730400085449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47005581855774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55612969398499</t>
+    <t xml:space="preserve">3.47005605697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55612993240356</t>
   </si>
   <si>
     <t xml:space="preserve">3.53700256347656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51628065109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.339350938797</t>
+    <t xml:space="preserve">3.51628088951111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33935070037842</t>
   </si>
   <si>
     <t xml:space="preserve">3.30906534194946</t>
@@ -2258,43 +2258,43 @@
     <t xml:space="preserve">3.3377571105957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27877998352051</t>
+    <t xml:space="preserve">3.27878022193909</t>
   </si>
   <si>
     <t xml:space="preserve">3.09069275856018</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11300778388977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26124668121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83247089385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65872859954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69060802459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2203893661499</t>
+    <t xml:space="preserve">3.11300802230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2612464427948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83247065544128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65872883796692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69060826301575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22038960456848</t>
   </si>
   <si>
     <t xml:space="preserve">2.55830931663513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46585965156555</t>
+    <t xml:space="preserve">2.46585917472839</t>
   </si>
   <si>
     <t xml:space="preserve">2.51049041748047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51686644554138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46107745170593</t>
+    <t xml:space="preserve">2.5168662071228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46107769012451</t>
   </si>
   <si>
     <t xml:space="preserve">2.58381271362305</t>
@@ -2306,16 +2306,16 @@
     <t xml:space="preserve">2.41804051399231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44035601615906</t>
+    <t xml:space="preserve">2.44035625457764</t>
   </si>
   <si>
     <t xml:space="preserve">2.50252079963684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62206816673279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6045343875885</t>
+    <t xml:space="preserve">2.62206792831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60453391075134</t>
   </si>
   <si>
     <t xml:space="preserve">2.52802395820618</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">2.56468510627747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53121185302734</t>
+    <t xml:space="preserve">2.53121209144592</t>
   </si>
   <si>
     <t xml:space="preserve">2.55193328857422</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">2.57584309577942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56787323951721</t>
+    <t xml:space="preserve">2.56787276268005</t>
   </si>
   <si>
     <t xml:space="preserve">2.54715180397034</t>
@@ -2345,10 +2345,10 @@
     <t xml:space="preserve">2.54396390914917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60772204399109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62047410011292</t>
+    <t xml:space="preserve">2.60772228240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62047386169434</t>
   </si>
   <si>
     <t xml:space="preserve">2.51846027374268</t>
@@ -2357,43 +2357,43 @@
     <t xml:space="preserve">2.59018874168396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5806245803833</t>
+    <t xml:space="preserve">2.58062505722046</t>
   </si>
   <si>
     <t xml:space="preserve">2.67307472229004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69220185279846</t>
+    <t xml:space="preserve">2.69220209121704</t>
   </si>
   <si>
     <t xml:space="preserve">2.57903075218201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57265496253967</t>
+    <t xml:space="preserve">2.57265472412109</t>
   </si>
   <si>
     <t xml:space="preserve">2.52483606338501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49295711517334</t>
+    <t xml:space="preserve">2.49295687675476</t>
   </si>
   <si>
     <t xml:space="preserve">2.59178280830383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61887979507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5614972114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47542333602905</t>
+    <t xml:space="preserve">2.61887955665588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56149697303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47542309761047</t>
   </si>
   <si>
     <t xml:space="preserve">2.46267151832581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51367807388306</t>
+    <t xml:space="preserve">2.51367855072021</t>
   </si>
   <si>
     <t xml:space="preserve">2.50092673301697</t>
@@ -2405,13 +2405,13 @@
     <t xml:space="preserve">2.54874563217163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6571352481842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66032266616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85159850120544</t>
+    <t xml:space="preserve">2.65713500976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66032290458679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85159826278687</t>
   </si>
   <si>
     <t xml:space="preserve">2.85638022422791</t>
@@ -2420,7 +2420,7 @@
     <t xml:space="preserve">2.81653094291687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77668213844299</t>
+    <t xml:space="preserve">2.77668237686157</t>
   </si>
   <si>
     <t xml:space="preserve">2.6778564453125</t>
@@ -2432,16 +2432,16 @@
     <t xml:space="preserve">2.78943347930908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77030634880066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75755476951599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75436639785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68901395797729</t>
+    <t xml:space="preserve">2.77030658721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75755453109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75436663627625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68901419639587</t>
   </si>
   <si>
     <t xml:space="preserve">2.63800740242004</t>
@@ -2453,25 +2453,25 @@
     <t xml:space="preserve">2.70017194747925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72567510604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74209499359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69940423965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71418166160583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64193487167358</t>
+    <t xml:space="preserve">2.72567534446716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74209475517273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69940376281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71418142318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.641934633255</t>
   </si>
   <si>
     <t xml:space="preserve">2.63372492790222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67477369308472</t>
+    <t xml:space="preserve">2.67477416992188</t>
   </si>
   <si>
     <t xml:space="preserve">2.63865065574646</t>
@@ -2480,13 +2480,13 @@
     <t xml:space="preserve">2.65014457702637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69447779655457</t>
+    <t xml:space="preserve">2.69447803497314</t>
   </si>
   <si>
     <t xml:space="preserve">2.7306010723114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73388528823853</t>
+    <t xml:space="preserve">2.73388504981995</t>
   </si>
   <si>
     <t xml:space="preserve">2.7355272769928</t>
@@ -2495,10 +2495,10 @@
     <t xml:space="preserve">2.76508283615112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66163849830627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61894679069519</t>
+    <t xml:space="preserve">2.6616382598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61894726753235</t>
   </si>
   <si>
     <t xml:space="preserve">2.63536691665649</t>
@@ -2510,22 +2510,22 @@
     <t xml:space="preserve">2.68790984153748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59267568588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61073732376099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60252714157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59595942497253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58774948120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66820645332336</t>
+    <t xml:space="preserve">2.59267544746399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61073708534241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60252737998962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59595918655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58774971961975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66820621490479</t>
   </si>
   <si>
     <t xml:space="preserve">2.72403335571289</t>
@@ -2534,10 +2534,10 @@
     <t xml:space="preserve">2.78642845153809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77657651901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75851464271545</t>
+    <t xml:space="preserve">2.77657628059387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75851488113403</t>
   </si>
   <si>
     <t xml:space="preserve">2.66656422615051</t>
@@ -2549,40 +2549,40 @@
     <t xml:space="preserve">2.68298387527466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66328024864197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75030469894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72239136695862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64686036109924</t>
+    <t xml:space="preserve">2.66328001022339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75030493736267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72239112854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6468608379364</t>
   </si>
   <si>
     <t xml:space="preserve">2.62715721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6287989616394</t>
+    <t xml:space="preserve">2.62879872322083</t>
   </si>
   <si>
     <t xml:space="preserve">2.6156632900238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69283580780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59760141372681</t>
+    <t xml:space="preserve">2.69283604621887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59760117530823</t>
   </si>
   <si>
     <t xml:space="preserve">2.64850282669067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64029264450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68134212493896</t>
+    <t xml:space="preserve">2.64029288291931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68134188652039</t>
   </si>
   <si>
     <t xml:space="preserve">2.66492247581482</t>
@@ -2591,46 +2591,46 @@
     <t xml:space="preserve">2.67970013618469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69776177406311</t>
+    <t xml:space="preserve">2.69776201248169</t>
   </si>
   <si>
     <t xml:space="preserve">2.71253943443298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63700866699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62387323379517</t>
+    <t xml:space="preserve">2.63700890541077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62387299537659</t>
   </si>
   <si>
     <t xml:space="preserve">2.60745334625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64521861076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63044118881226</t>
+    <t xml:space="preserve">2.64521884918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63044095039368</t>
   </si>
   <si>
     <t xml:space="preserve">2.54998397827148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55819416046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54505848884583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51386094093323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52042865753174</t>
+    <t xml:space="preserve">2.55819392204285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54505801200867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51386117935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52042889595032</t>
   </si>
   <si>
     <t xml:space="preserve">2.50236701965332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47281169891357</t>
+    <t xml:space="preserve">2.472811460495</t>
   </si>
   <si>
     <t xml:space="preserve">2.42191052436829</t>
@@ -2639,28 +2639,28 @@
     <t xml:space="preserve">2.44325613975525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35951542854309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38414478302002</t>
+    <t xml:space="preserve">2.35951519012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3841450214386</t>
   </si>
   <si>
     <t xml:space="preserve">2.41205835342407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46295928955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39563846588135</t>
+    <t xml:space="preserve">2.46295976638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39563870429993</t>
   </si>
   <si>
     <t xml:space="preserve">2.37593507766724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37757658958435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31518220901489</t>
+    <t xml:space="preserve">2.37757682800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31518173217773</t>
   </si>
   <si>
     <t xml:space="preserve">2.29219436645508</t>
@@ -2669,10 +2669,10 @@
     <t xml:space="preserve">2.23472547531128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19696021080017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21666383743286</t>
+    <t xml:space="preserve">2.19695997238159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21666359901428</t>
   </si>
   <si>
     <t xml:space="preserve">2.23636722564697</t>
@@ -2684,10 +2684,10 @@
     <t xml:space="preserve">2.3102560043335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30533027648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28070068359375</t>
+    <t xml:space="preserve">2.30533051490784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28070092201233</t>
   </si>
   <si>
     <t xml:space="preserve">2.45474982261658</t>
@@ -2696,49 +2696,49 @@
     <t xml:space="preserve">2.42519426345825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44982385635376</t>
+    <t xml:space="preserve">2.44982409477234</t>
   </si>
   <si>
     <t xml:space="preserve">2.49251532554626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47937941551208</t>
+    <t xml:space="preserve">2.47937893867493</t>
   </si>
   <si>
     <t xml:space="preserve">2.56147789955139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50893473625183</t>
+    <t xml:space="preserve">2.50893497467041</t>
   </si>
   <si>
     <t xml:space="preserve">2.49579906463623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50400900840759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48102116584778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47609543800354</t>
+    <t xml:space="preserve">2.50400876998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48102140426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47609519958496</t>
   </si>
   <si>
     <t xml:space="preserve">2.52207064628601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53520655632019</t>
+    <t xml:space="preserve">2.53520631790161</t>
   </si>
   <si>
     <t xml:space="preserve">2.51221871376038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47116947174072</t>
+    <t xml:space="preserve">2.4711697101593</t>
   </si>
   <si>
     <t xml:space="preserve">2.43997192382812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46788549423218</t>
+    <t xml:space="preserve">2.46788597106934</t>
   </si>
   <si>
     <t xml:space="preserve">2.44489789009094</t>
@@ -2750,19 +2750,19 @@
     <t xml:space="preserve">2.41534233093262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38907098770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36444115638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39399647712708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3660831451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40384864807129</t>
+    <t xml:space="preserve">2.38907122612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36444139480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39399671554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36608338356018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40384888648987</t>
   </si>
   <si>
     <t xml:space="preserve">2.45146584510803</t>
@@ -2771,40 +2771,40 @@
     <t xml:space="preserve">2.33981156349182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38742899894714</t>
+    <t xml:space="preserve">2.38742876052856</t>
   </si>
   <si>
     <t xml:space="preserve">2.45310759544373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45967602729797</t>
+    <t xml:space="preserve">2.45967578887939</t>
   </si>
   <si>
     <t xml:space="preserve">2.44653987884521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50565075874329</t>
+    <t xml:space="preserve">2.50565099716187</t>
   </si>
   <si>
     <t xml:space="preserve">2.4416139125824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49087285995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48594760894775</t>
+    <t xml:space="preserve">2.49087309837341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48594737052917</t>
   </si>
   <si>
     <t xml:space="preserve">2.59431767463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54177451133728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38086104393005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33652758598328</t>
+    <t xml:space="preserve">2.5417742729187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38086080551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33652782440186</t>
   </si>
   <si>
     <t xml:space="preserve">2.35787320137024</t>
@@ -2819,13 +2819,13 @@
     <t xml:space="preserve">2.46952748298645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49415731430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55326795578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51057696342468</t>
+    <t xml:space="preserve">2.49415707588196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55326843261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51057720184326</t>
   </si>
   <si>
     <t xml:space="preserve">2.52371263504028</t>
@@ -2834,13 +2834,13 @@
     <t xml:space="preserve">2.55491018295288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58939146995544</t>
+    <t xml:space="preserve">2.58939170837402</t>
   </si>
   <si>
     <t xml:space="preserve">2.54670023918152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53684830665588</t>
+    <t xml:space="preserve">2.5368480682373</t>
   </si>
   <si>
     <t xml:space="preserve">2.52535462379456</t>
@@ -2855,25 +2855,25 @@
     <t xml:space="preserve">2.5286386013031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56312012672424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56968784332275</t>
+    <t xml:space="preserve">2.56311988830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56968808174133</t>
   </si>
   <si>
     <t xml:space="preserve">2.60416913032532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71582341194153</t>
+    <t xml:space="preserve">2.71582365036011</t>
   </si>
   <si>
     <t xml:space="preserve">2.68216300010681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72895932197571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70843458175659</t>
+    <t xml:space="preserve">2.72895908355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70843482017517</t>
   </si>
   <si>
     <t xml:space="preserve">2.69611978530884</t>
@@ -2882,31 +2882,31 @@
     <t xml:space="preserve">2.71171855926514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73224306106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76918768882751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76097750663757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75440979003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75523114204407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75605201721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7461998462677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79381728172302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.762619972229</t>
+    <t xml:space="preserve">2.73224329948425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76918745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76097774505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75441002845764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75523066520691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75605177879333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74620008468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79381704330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76261973381042</t>
   </si>
   <si>
     <t xml:space="preserve">2.76672458648682</t>
@@ -2924,19 +2924,19 @@
     <t xml:space="preserve">2.77247166633606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7642617225647</t>
+    <t xml:space="preserve">2.76426196098328</t>
   </si>
   <si>
     <t xml:space="preserve">2.86278009414673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83240342140198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82255172729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86031699180603</t>
+    <t xml:space="preserve">2.83240365982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82255148887634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86031723022461</t>
   </si>
   <si>
     <t xml:space="preserve">2.87837910652161</t>
@@ -2963,13 +2963,13 @@
     <t xml:space="preserve">2.86360096931458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87427353858948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89726185798645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93256378173828</t>
+    <t xml:space="preserve">2.87427377700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89726138114929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93256402015686</t>
   </si>
   <si>
     <t xml:space="preserve">2.95883560180664</t>
@@ -2978,25 +2978,25 @@
     <t xml:space="preserve">2.97197103500366</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02533555030823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00481081008911</t>
+    <t xml:space="preserve">3.02533531188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00481104850769</t>
   </si>
   <si>
     <t xml:space="preserve">3.00809478759766</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04093408584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01794672012329</t>
+    <t xml:space="preserve">3.04093432426453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01794648170471</t>
   </si>
   <si>
     <t xml:space="preserve">3.04586005210876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02123045921326</t>
+    <t xml:space="preserve">3.02123069763184</t>
   </si>
   <si>
     <t xml:space="preserve">3.00727391242981</t>
@@ -3005,37 +3005,37 @@
     <t xml:space="preserve">2.98921203613281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95801448822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90218734741211</t>
+    <t xml:space="preserve">2.95801424980164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90218758583069</t>
   </si>
   <si>
     <t xml:space="preserve">2.92353320121765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8956196308136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8906934261322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89151477813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86688494682312</t>
+    <t xml:space="preserve">2.89561939239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89069366455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89151453971863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8668851852417</t>
   </si>
   <si>
     <t xml:space="preserve">2.89479851722717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90920472145081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89649367332458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96005034446716</t>
+    <t xml:space="preserve">2.90920495986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89649343490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96005010604858</t>
   </si>
   <si>
     <t xml:space="preserve">2.86598610877991</t>
@@ -3044,7 +3044,7 @@
     <t xml:space="preserve">2.86429142951965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9320855140686</t>
+    <t xml:space="preserve">2.93208527565002</t>
   </si>
   <si>
     <t xml:space="preserve">2.93293261528015</t>
@@ -3053,10 +3053,10 @@
     <t xml:space="preserve">2.92191600799561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8956458568573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92615342140198</t>
+    <t xml:space="preserve">2.89564633369446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9261531829834</t>
   </si>
   <si>
     <t xml:space="preserve">2.84225845336914</t>
@@ -3065,19 +3065,19 @@
     <t xml:space="preserve">2.85073256492615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94733905792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9998791217804</t>
+    <t xml:space="preserve">2.94733881950378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99987888336182</t>
   </si>
   <si>
     <t xml:space="preserve">2.9778459072113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99055767059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03292870521545</t>
+    <t xml:space="preserve">2.99055743217468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03292846679688</t>
   </si>
   <si>
     <t xml:space="preserve">3.06428337097168</t>
@@ -3086,25 +3086,25 @@
     <t xml:space="preserve">3.04055547714233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04479241371155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02275919914246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01004815101624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00157403945923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02021718025208</t>
+    <t xml:space="preserve">3.04479265213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02275943756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01004838943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00157380104065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0202169418335</t>
   </si>
   <si>
     <t xml:space="preserve">3.04648756980896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03547120094299</t>
+    <t xml:space="preserve">3.03547096252441</t>
   </si>
   <si>
     <t xml:space="preserve">3.08546900749207</t>
@@ -3113,7 +3113,7 @@
     <t xml:space="preserve">3.09733271598816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13122987747192</t>
+    <t xml:space="preserve">3.13122963905334</t>
   </si>
   <si>
     <t xml:space="preserve">3.14563608169556</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">3.12953495979309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10156989097595</t>
+    <t xml:space="preserve">3.10157012939453</t>
   </si>
   <si>
     <t xml:space="preserve">3.11597609519958</t>
@@ -3152,13 +3152,13 @@
     <t xml:space="preserve">3.10411238670349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13716149330139</t>
+    <t xml:space="preserve">3.13716173171997</t>
   </si>
   <si>
     <t xml:space="preserve">3.12275552749634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11004424095154</t>
+    <t xml:space="preserve">3.11004400253296</t>
   </si>
   <si>
     <t xml:space="preserve">3.1252977848053</t>
@@ -3167,10 +3167,10 @@
     <t xml:space="preserve">3.08123159408569</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03631806373596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07360482215881</t>
+    <t xml:space="preserve">3.03631854057312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07360506057739</t>
   </si>
   <si>
     <t xml:space="preserve">3.09902787208557</t>
@@ -3179,19 +3179,19 @@
     <t xml:space="preserve">3.04987740516663</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08377385139465</t>
+    <t xml:space="preserve">3.08377408981323</t>
   </si>
   <si>
     <t xml:space="preserve">3.04140281677246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08631634712219</t>
+    <t xml:space="preserve">3.08631610870361</t>
   </si>
   <si>
     <t xml:space="preserve">3.08292651176453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09224820137024</t>
+    <t xml:space="preserve">3.09224843978882</t>
   </si>
   <si>
     <t xml:space="preserve">3.02360701560974</t>
@@ -3200,22 +3200,22 @@
     <t xml:space="preserve">2.97445631027222</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01428532600403</t>
+    <t xml:space="preserve">3.01428508758545</t>
   </si>
   <si>
     <t xml:space="preserve">2.99648952484131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9956419467926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99818420410156</t>
+    <t xml:space="preserve">2.99564218521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99818444252014</t>
   </si>
   <si>
     <t xml:space="preserve">3.00411629676819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96089768409729</t>
+    <t xml:space="preserve">2.96089744567871</t>
   </si>
   <si>
     <t xml:space="preserve">2.98547291755676</t>
@@ -3224,13 +3224,13 @@
     <t xml:space="preserve">2.91089963912964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87785005569458</t>
+    <t xml:space="preserve">2.877849817276</t>
   </si>
   <si>
     <t xml:space="preserve">2.91174721717834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94564414024353</t>
+    <t xml:space="preserve">2.94564390182495</t>
   </si>
   <si>
     <t xml:space="preserve">2.97530388832092</t>
@@ -3245,7 +3245,7 @@
     <t xml:space="preserve">2.9439492225647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00242114067078</t>
+    <t xml:space="preserve">3.00242161750793</t>
   </si>
   <si>
     <t xml:space="preserve">3.03377604484558</t>
@@ -3254,34 +3254,34 @@
     <t xml:space="preserve">3.04902958869934</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01767516136169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05241918563843</t>
+    <t xml:space="preserve">3.01767492294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05241942405701</t>
   </si>
   <si>
     <t xml:space="preserve">2.99733686447144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0125904083252</t>
+    <t xml:space="preserve">3.01259064674377</t>
   </si>
   <si>
     <t xml:space="preserve">2.9947943687439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03462362289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11258625984192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09309601783752</t>
+    <t xml:space="preserve">3.03462338447571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11258673667908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09309577941895</t>
   </si>
   <si>
     <t xml:space="preserve">3.0566565990448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01682758331299</t>
+    <t xml:space="preserve">3.01682782173157</t>
   </si>
   <si>
     <t xml:space="preserve">3.05750393867493</t>
@@ -3293,10 +3293,10 @@
     <t xml:space="preserve">3.07275748252869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03208136558533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02953910827637</t>
+    <t xml:space="preserve">3.03208112716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02953886985779</t>
   </si>
   <si>
     <t xml:space="preserve">3.00072646141052</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">2.85581707954407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87022352218628</t>
+    <t xml:space="preserve">2.8702232837677</t>
   </si>
   <si>
     <t xml:space="preserve">2.88547682762146</t>
@@ -3317,25 +3317,25 @@
     <t xml:space="preserve">2.88971424102783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02530193328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9820830821991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0083532333374</t>
+    <t xml:space="preserve">3.02530169487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98208355903625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00835299491882</t>
   </si>
   <si>
     <t xml:space="preserve">2.97869372367859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00326895713806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02445435523987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04563999176025</t>
+    <t xml:space="preserve">3.00326871871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02445459365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04564023017883</t>
   </si>
   <si>
     <t xml:space="preserve">3.05072450637817</t>
@@ -3350,7 +3350,7 @@
     <t xml:space="preserve">3.10241723060608</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14055132865906</t>
+    <t xml:space="preserve">3.14055156707764</t>
   </si>
   <si>
     <t xml:space="preserve">3.11173892021179</t>
@@ -3359,7 +3359,7 @@
     <t xml:space="preserve">3.08716368675232</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02699637413025</t>
+    <t xml:space="preserve">3.02699661254883</t>
   </si>
   <si>
     <t xml:space="preserve">3.01343774795532</t>
@@ -3368,31 +3368,31 @@
     <t xml:space="preserve">2.99394702911377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97106695175171</t>
+    <t xml:space="preserve">2.97106671333313</t>
   </si>
   <si>
     <t xml:space="preserve">2.98123550415039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94903349876404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9083571434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91767930984497</t>
+    <t xml:space="preserve">2.9490339756012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90835738182068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91767907142639</t>
   </si>
   <si>
     <t xml:space="preserve">2.97360897064209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07614755630493</t>
+    <t xml:space="preserve">3.07614731788635</t>
   </si>
   <si>
     <t xml:space="preserve">3.14817810058594</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13377213478088</t>
+    <t xml:space="preserve">3.1337718963623</t>
   </si>
   <si>
     <t xml:space="preserve">3.07021522521973</t>
@@ -3401,7 +3401,7 @@
     <t xml:space="preserve">2.9388644695282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88039231300354</t>
+    <t xml:space="preserve">2.88039255142212</t>
   </si>
   <si>
     <t xml:space="preserve">2.91852641105652</t>
@@ -3413,22 +3413,22 @@
     <t xml:space="preserve">2.92530584335327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86005425453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88717198371887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87276577949524</t>
+    <t xml:space="preserve">2.86005449295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88717174530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87276530265808</t>
   </si>
   <si>
     <t xml:space="preserve">2.84310579299927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83802103996277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79734516143799</t>
+    <t xml:space="preserve">2.83802127838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79734468460083</t>
   </si>
   <si>
     <t xml:space="preserve">2.80836129188538</t>
@@ -3437,13 +3437,13 @@
     <t xml:space="preserve">2.82446217536926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.740567445755</t>
+    <t xml:space="preserve">2.74056768417358</t>
   </si>
   <si>
     <t xml:space="preserve">2.93632221221924</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83208918571472</t>
+    <t xml:space="preserve">2.8320894241333</t>
   </si>
   <si>
     <t xml:space="preserve">2.78971815109253</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">2.76260042190552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69904375076294</t>
+    <t xml:space="preserve">2.69904351234436</t>
   </si>
   <si>
     <t xml:space="preserve">2.71175527572632</t>
@@ -3461,40 +3461,40 @@
     <t xml:space="preserve">2.77446436882019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87700247764587</t>
+    <t xml:space="preserve">2.87700271606445</t>
   </si>
   <si>
     <t xml:space="preserve">2.86344361305237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85666441917419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85158014297485</t>
+    <t xml:space="preserve">2.85666465759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85157990455627</t>
   </si>
   <si>
     <t xml:space="preserve">2.81937789916992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85412240028381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89140868186951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78802347183228</t>
+    <t xml:space="preserve">2.85412216186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89140892028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78802299499512</t>
   </si>
   <si>
     <t xml:space="preserve">2.75666856765747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.814293384552</t>
+    <t xml:space="preserve">2.81429362297058</t>
   </si>
   <si>
     <t xml:space="preserve">2.82700490951538</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85327482223511</t>
+    <t xml:space="preserve">2.85327506065369</t>
   </si>
   <si>
     <t xml:space="preserve">2.83547878265381</t>
@@ -3503,16 +3503,16 @@
     <t xml:space="preserve">2.87615537643433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90751004219055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00581097602844</t>
+    <t xml:space="preserve">2.90750980377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00581121444702</t>
   </si>
   <si>
     <t xml:space="preserve">3.04733467102051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00496387481689</t>
+    <t xml:space="preserve">3.00496363639832</t>
   </si>
   <si>
     <t xml:space="preserve">3.04394507408142</t>
@@ -3524,19 +3524,19 @@
     <t xml:space="preserve">3.01598024368286</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04818224906921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97276139259338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98377776145935</t>
+    <t xml:space="preserve">3.04818201065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97276163101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98377823829651</t>
   </si>
   <si>
     <t xml:space="preserve">2.9524233341217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98632049560547</t>
+    <t xml:space="preserve">2.98632025718689</t>
   </si>
   <si>
     <t xml:space="preserve">3.06343603134155</t>
@@ -3554,7 +3554,7 @@
     <t xml:space="preserve">2.95072865486145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03801298141479</t>
+    <t xml:space="preserve">3.03801321983337</t>
   </si>
   <si>
     <t xml:space="preserve">2.98801517486572</t>
@@ -3566,7 +3566,7 @@
     <t xml:space="preserve">2.89056158065796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86683344841003</t>
+    <t xml:space="preserve">2.86683368682861</t>
   </si>
   <si>
     <t xml:space="preserve">2.82785201072693</t>
@@ -3575,28 +3575,28 @@
     <t xml:space="preserve">2.86174917221069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83717393875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8388683795929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72700881958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53125405311584</t>
+    <t xml:space="preserve">2.83717370033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83886861801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7270085811615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53125381469727</t>
   </si>
   <si>
     <t xml:space="preserve">2.41685175895691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35668444633484</t>
+    <t xml:space="preserve">2.35668468475342</t>
   </si>
   <si>
     <t xml:space="preserve">2.45837545394897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38888669013977</t>
+    <t xml:space="preserve">2.38888692855835</t>
   </si>
   <si>
     <t xml:space="preserve">2.41769909858704</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">2.34250545501709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32569718360901</t>
+    <t xml:space="preserve">2.32569742202759</t>
   </si>
   <si>
     <t xml:space="preserve">2.37435221672058</t>
@@ -3626,46 +3626,46 @@
     <t xml:space="preserve">2.47608494758606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44158411026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48758506774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48493123054504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41327571868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45750761032104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49112367630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47696924209595</t>
+    <t xml:space="preserve">2.44158434867859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4875853061676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48493099212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41327595710754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45750784873962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49112343788147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47696948051453</t>
   </si>
   <si>
     <t xml:space="preserve">2.45927667617798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37523698806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30446600914001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37789082527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38673686981201</t>
+    <t xml:space="preserve">2.37523674964905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30446624755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37789058685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38673710823059</t>
   </si>
   <si>
     <t xml:space="preserve">2.41150689125061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38319826126099</t>
+    <t xml:space="preserve">2.38319849967957</t>
   </si>
   <si>
     <t xml:space="preserve">2.40619897842407</t>
@@ -3674,37 +3674,37 @@
     <t xml:space="preserve">2.41946816444397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40089130401611</t>
+    <t xml:space="preserve">2.40089106559753</t>
   </si>
   <si>
     <t xml:space="preserve">2.47873878479004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43008375167847</t>
+    <t xml:space="preserve">2.43008399009705</t>
   </si>
   <si>
     <t xml:space="preserve">2.44689202308655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50970077514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50527787208557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47077679634094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44246864318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43981504440308</t>
+    <t xml:space="preserve">2.50970053672791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50527763366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47077703475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44246888160706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4398148059845</t>
   </si>
   <si>
     <t xml:space="preserve">2.4433536529541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46900796890259</t>
+    <t xml:space="preserve">2.46900773048401</t>
   </si>
   <si>
     <t xml:space="preserve">2.47520017623901</t>
@@ -3722,7 +3722,7 @@
     <t xml:space="preserve">2.42300701141357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40442967414856</t>
+    <t xml:space="preserve">2.40442943572998</t>
   </si>
   <si>
     <t xml:space="preserve">2.36904430389404</t>
@@ -3740,10 +3740,10 @@
     <t xml:space="preserve">2.21246433258057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24342656135559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18504071235657</t>
+    <t xml:space="preserve">2.24342679977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18504095077515</t>
   </si>
   <si>
     <t xml:space="preserve">2.07269263267517</t>
@@ -3752,7 +3752,7 @@
     <t xml:space="preserve">2.12842440605164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11603951454163</t>
+    <t xml:space="preserve">2.11603975296021</t>
   </si>
   <si>
     <t xml:space="preserve">2.2009642124176</t>
@@ -3767,28 +3767,28 @@
     <t xml:space="preserve">2.14965581893921</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14700198173523</t>
+    <t xml:space="preserve">2.14700174331665</t>
   </si>
   <si>
     <t xml:space="preserve">2.11957812309265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10630869865417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07800030708313</t>
+    <t xml:space="preserve">2.1063084602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07800054550171</t>
   </si>
   <si>
     <t xml:space="preserve">2.07357740402222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04261541366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97803699970245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98422932624817</t>
+    <t xml:space="preserve">2.04261517524719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97803723812103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98422968387604</t>
   </si>
   <si>
     <t xml:space="preserve">1.87895834445953</t>
@@ -3797,7 +3797,7 @@
     <t xml:space="preserve">1.92584371566772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91611266136169</t>
+    <t xml:space="preserve">1.9161125421524</t>
   </si>
   <si>
     <t xml:space="preserve">1.93380570411682</t>
@@ -3812,19 +3812,19 @@
     <t xml:space="preserve">1.90018951892853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84003448486328</t>
+    <t xml:space="preserve">1.84003436565399</t>
   </si>
   <si>
     <t xml:space="preserve">1.82588028907776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87011206150055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80464923381805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77280235290527</t>
+    <t xml:space="preserve">1.87011194229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80464911460876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77280247211456</t>
   </si>
   <si>
     <t xml:space="preserve">1.80022609233856</t>
@@ -3833,25 +3833,25 @@
     <t xml:space="preserve">1.83030343055725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87807369232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88249683380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86303472518921</t>
+    <t xml:space="preserve">1.87807357311249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88249695301056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8630348443985</t>
   </si>
   <si>
     <t xml:space="preserve">1.87541949748993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85153460502625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91257429122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99838376045227</t>
+    <t xml:space="preserve">1.85153472423553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91257441043854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99838364124298</t>
   </si>
   <si>
     <t xml:space="preserve">2.01696085929871</t>
@@ -3866,10 +3866,10 @@
     <t xml:space="preserve">2.14434790611267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14257860183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13196325302124</t>
+    <t xml:space="preserve">2.14257836341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13196301460266</t>
   </si>
   <si>
     <t xml:space="preserve">2.1779637336731</t>
@@ -3896,13 +3896,13 @@
     <t xml:space="preserve">2.33454370498657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31773591041565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33631277084351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32835149765015</t>
+    <t xml:space="preserve">2.31773567199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33631300926208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32835125923157</t>
   </si>
   <si>
     <t xml:space="preserve">2.3274667263031</t>
@@ -3923,16 +3923,16 @@
     <t xml:space="preserve">2.34338998794556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35400581359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3716983795166</t>
+    <t xml:space="preserve">2.35400557518005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37169814109802</t>
   </si>
   <si>
     <t xml:space="preserve">2.37965989112854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37612152099609</t>
+    <t xml:space="preserve">2.37612175941467</t>
   </si>
   <si>
     <t xml:space="preserve">2.4327380657196</t>
@@ -3941,7 +3941,7 @@
     <t xml:space="preserve">2.48050785064697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50350832939148</t>
+    <t xml:space="preserve">2.50350856781006</t>
   </si>
   <si>
     <t xml:space="preserve">2.44600749015808</t>
@@ -3962,7 +3962,7 @@
     <t xml:space="preserve">2.24165749549866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25758051872253</t>
+    <t xml:space="preserve">2.25758075714111</t>
   </si>
   <si>
     <t xml:space="preserve">2.25492691993713</t>
@@ -3974,13 +3974,13 @@
     <t xml:space="preserve">2.25227308273315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2283878326416</t>
+    <t xml:space="preserve">2.22838807106018</t>
   </si>
   <si>
     <t xml:space="preserve">2.28765821456909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28942728042603</t>
+    <t xml:space="preserve">2.2894275188446</t>
   </si>
   <si>
     <t xml:space="preserve">2.33542847633362</t>
@@ -3989,16 +3989,16 @@
     <t xml:space="preserve">2.32304334640503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45043063163757</t>
+    <t xml:space="preserve">2.45043039321899</t>
   </si>
   <si>
     <t xml:space="preserve">2.45131516456604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42389154434204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42919945716858</t>
+    <t xml:space="preserve">2.42389130592346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42919921875</t>
   </si>
   <si>
     <t xml:space="preserve">2.40708374977112</t>
@@ -4007,13 +4007,13 @@
     <t xml:space="preserve">2.34781336784363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3885064125061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41416072845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.401775598526</t>
+    <t xml:space="preserve">2.38850617408752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41416049003601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40177583694458</t>
   </si>
   <si>
     <t xml:space="preserve">2.39646816253662</t>
@@ -4022,19 +4022,19 @@
     <t xml:space="preserve">2.34692859649658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.340735912323</t>
+    <t xml:space="preserve">2.34073615074158</t>
   </si>
   <si>
     <t xml:space="preserve">2.3442747592926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41062188148499</t>
+    <t xml:space="preserve">2.41062211990356</t>
   </si>
   <si>
     <t xml:space="preserve">2.37081384658813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31596660614014</t>
+    <t xml:space="preserve">2.31596636772156</t>
   </si>
   <si>
     <t xml:space="preserve">2.28854274749756</t>
@@ -4052,7 +4052,7 @@
     <t xml:space="preserve">2.26642727851868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23458051681519</t>
+    <t xml:space="preserve">2.23458027839661</t>
   </si>
   <si>
     <t xml:space="preserve">2.22661876678467</t>
@@ -4061,19 +4061,19 @@
     <t xml:space="preserve">2.22219562530518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23192620277405</t>
+    <t xml:space="preserve">2.23192667961121</t>
   </si>
   <si>
     <t xml:space="preserve">2.1753101348877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19477200508118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2257342338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18150234222412</t>
+    <t xml:space="preserve">2.1947717666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22573399543762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1815025806427</t>
   </si>
   <si>
     <t xml:space="preserve">2.15054035186768</t>
@@ -4085,13 +4085,13 @@
     <t xml:space="preserve">2.10807776451111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13727068901062</t>
+    <t xml:space="preserve">2.13727045059204</t>
   </si>
   <si>
     <t xml:space="preserve">2.12753963470459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11692428588867</t>
+    <t xml:space="preserve">2.11692404747009</t>
   </si>
   <si>
     <t xml:space="preserve">2.18857932090759</t>
@@ -4100,7 +4100,7 @@
     <t xml:space="preserve">2.20627212524414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22131061553955</t>
+    <t xml:space="preserve">2.22131085395813</t>
   </si>
   <si>
     <t xml:space="preserve">2.20361804962158</t>
@@ -4109,31 +4109,31 @@
     <t xml:space="preserve">2.21423363685608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24254179000854</t>
+    <t xml:space="preserve">2.24254202842712</t>
   </si>
   <si>
     <t xml:space="preserve">2.30181241035461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29827404022217</t>
+    <t xml:space="preserve">2.29827380180359</t>
   </si>
   <si>
     <t xml:space="preserve">2.40266036987305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42212247848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.319504737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.395583152771</t>
+    <t xml:space="preserve">2.42212224006653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31950497627258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39558339118958</t>
   </si>
   <si>
     <t xml:space="preserve">2.39027547836304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46989250183105</t>
+    <t xml:space="preserve">2.46989226341248</t>
   </si>
   <si>
     <t xml:space="preserve">2.49820065498352</t>
@@ -4145,13 +4145,13 @@
     <t xml:space="preserve">2.49643135070801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53181648254395</t>
+    <t xml:space="preserve">2.53181672096252</t>
   </si>
   <si>
     <t xml:space="preserve">2.52297043800354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54066300392151</t>
+    <t xml:space="preserve">2.54066276550293</t>
   </si>
   <si>
     <t xml:space="preserve">2.62381839752197</t>
@@ -4163,7 +4163,7 @@
     <t xml:space="preserve">2.67689633369446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67866587638855</t>
+    <t xml:space="preserve">2.67866563796997</t>
   </si>
   <si>
     <t xml:space="preserve">2.6379725933075</t>
@@ -4172,37 +4172,37 @@
     <t xml:space="preserve">2.53712439537048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61497211456299</t>
+    <t xml:space="preserve">2.61497235298157</t>
   </si>
   <si>
     <t xml:space="preserve">2.63266468048096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62204909324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54950904846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5282781124115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57958650588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58135604858398</t>
+    <t xml:space="preserve">2.62204885482788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54950952529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52827835083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57958674430847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58135581016541</t>
   </si>
   <si>
     <t xml:space="preserve">2.60966444015503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58666396141052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59020233154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53889346122742</t>
+    <t xml:space="preserve">2.58666372299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59020256996155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.538893699646</t>
   </si>
   <si>
     <t xml:space="preserve">2.572509765625</t>
@@ -4211,25 +4211,25 @@
     <t xml:space="preserve">2.54420161247253</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55304765701294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56366324424744</t>
+    <t xml:space="preserve">2.55304789543152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56366348266602</t>
   </si>
   <si>
     <t xml:space="preserve">2.55127859115601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53004741668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56897115707397</t>
+    <t xml:space="preserve">2.53004717826843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56897139549255</t>
   </si>
   <si>
     <t xml:space="preserve">2.51812791824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52922105789185</t>
+    <t xml:space="preserve">2.52922129631042</t>
   </si>
   <si>
     <t xml:space="preserve">2.53661632537842</t>
@@ -4256,16 +4256,16 @@
     <t xml:space="preserve">2.46451139450073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41274380683899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4090461730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42013931274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44787168502808</t>
+    <t xml:space="preserve">2.41274356842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40904593467712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42013907432556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44787192344666</t>
   </si>
   <si>
     <t xml:space="preserve">2.47375583648682</t>
@@ -4286,10 +4286,10 @@
     <t xml:space="preserve">2.52737212181091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54216313362122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53846526145935</t>
+    <t xml:space="preserve">2.54216289520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53846549987793</t>
   </si>
   <si>
     <t xml:space="preserve">2.58653521537781</t>
@@ -4298,7 +4298,7 @@
     <t xml:space="preserve">2.56250047683716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59393072128296</t>
+    <t xml:space="preserve">2.59393048286438</t>
   </si>
   <si>
     <t xml:space="preserve">2.63275647163391</t>
@@ -4313,10 +4313,10 @@
     <t xml:space="preserve">2.60132598876953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45711588859558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3998019695282</t>
+    <t xml:space="preserve">2.45711612701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39980173110962</t>
   </si>
   <si>
     <t xml:space="preserve">2.44602274894714</t>
@@ -4328,10 +4328,10 @@
     <t xml:space="preserve">2.47190690040588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47005796432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42383670806885</t>
+    <t xml:space="preserve">2.47005772590637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42383694648743</t>
   </si>
   <si>
     <t xml:space="preserve">2.38316226005554</t>
@@ -4343,34 +4343,34 @@
     <t xml:space="preserve">2.49594187736511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52182555198669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54031419754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55140733718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57913970947266</t>
+    <t xml:space="preserve">2.52182579040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5403139591217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55140709877014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57913994789124</t>
   </si>
   <si>
     <t xml:space="preserve">2.5680468082428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58468651771545</t>
+    <t xml:space="preserve">2.58468627929688</t>
   </si>
   <si>
     <t xml:space="preserve">2.57544207572937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54770946502686</t>
+    <t xml:space="preserve">2.54770970344543</t>
   </si>
   <si>
     <t xml:space="preserve">2.60687255859375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60317492485046</t>
+    <t xml:space="preserve">2.60317468643188</t>
   </si>
   <si>
     <t xml:space="preserve">2.6456983089447</t>
@@ -4394,7 +4394,7 @@
     <t xml:space="preserve">2.667884349823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69376850128174</t>
+    <t xml:space="preserve">2.69376826286316</t>
   </si>
   <si>
     <t xml:space="preserve">2.56434917449951</t>
@@ -4427,22 +4427,22 @@
     <t xml:space="preserve">2.35358071327209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39795303344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41089510917664</t>
+    <t xml:space="preserve">2.39795327186584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41089487075806</t>
   </si>
   <si>
     <t xml:space="preserve">2.42753434181213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40534830093384</t>
+    <t xml:space="preserve">2.40534853935242</t>
   </si>
   <si>
     <t xml:space="preserve">2.39240646362305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3720691204071</t>
+    <t xml:space="preserve">2.37206935882568</t>
   </si>
   <si>
     <t xml:space="preserve">2.34988307952881</t>
@@ -4457,7 +4457,7 @@
     <t xml:space="preserve">2.34803414344788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45341849327087</t>
+    <t xml:space="preserve">2.45341825485229</t>
   </si>
   <si>
     <t xml:space="preserve">2.49224424362183</t>
@@ -4469,7 +4469,7 @@
     <t xml:space="preserve">2.49779057502747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46266269683838</t>
+    <t xml:space="preserve">2.4626624584198</t>
   </si>
   <si>
     <t xml:space="preserve">2.45526719093323</t>
@@ -4484,7 +4484,7 @@
     <t xml:space="preserve">2.62536096572876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64015197753906</t>
+    <t xml:space="preserve">2.64015173912048</t>
   </si>
   <si>
     <t xml:space="preserve">2.62720990180969</t>
@@ -4493,19 +4493,19 @@
     <t xml:space="preserve">2.63090753555298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68082666397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68637275695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68822169303894</t>
+    <t xml:space="preserve">2.68082642555237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68637299537659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68822193145752</t>
   </si>
   <si>
     <t xml:space="preserve">2.66603565216064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6826753616333</t>
+    <t xml:space="preserve">2.68267512321472</t>
   </si>
   <si>
     <t xml:space="preserve">2.68452405929565</t>
@@ -4514,19 +4514,19 @@
     <t xml:space="preserve">2.69007062911987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74368715286255</t>
+    <t xml:space="preserve">2.74368691444397</t>
   </si>
   <si>
     <t xml:space="preserve">2.71225690841675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69561696052551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73444294929504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80100154876709</t>
+    <t xml:space="preserve">2.69561719894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73444271087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80100131034851</t>
   </si>
   <si>
     <t xml:space="preserve">2.78990817070007</t>
@@ -4538,7 +4538,7 @@
     <t xml:space="preserve">2.79545474052429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78621053695679</t>
+    <t xml:space="preserve">2.78621077537537</t>
   </si>
   <si>
     <t xml:space="preserve">2.76772212982178</t>
@@ -4550,7 +4550,7 @@
     <t xml:space="preserve">2.75662922859192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73998928070068</t>
+    <t xml:space="preserve">2.73998951911926</t>
   </si>
   <si>
     <t xml:space="preserve">2.74738478660583</t>
@@ -4598,22 +4598,22 @@
     <t xml:space="preserve">2.98033928871155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96924614906311</t>
+    <t xml:space="preserve">2.96924638748169</t>
   </si>
   <si>
     <t xml:space="preserve">3.02286291122437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92672276496887</t>
+    <t xml:space="preserve">2.92672300338745</t>
   </si>
   <si>
     <t xml:space="preserve">2.91562986373901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87495517730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90083885192871</t>
+    <t xml:space="preserve">2.87495493888855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90083909034729</t>
   </si>
   <si>
     <t xml:space="preserve">2.9193274974823</t>
@@ -4640,7 +4640,7 @@
     <t xml:space="preserve">2.99513030052185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9877347946167</t>
+    <t xml:space="preserve">2.98773503303528</t>
   </si>
   <si>
     <t xml:space="preserve">2.98958349227905</t>
@@ -4649,16 +4649,16 @@
     <t xml:space="preserve">2.93411827087402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96000194549561</t>
+    <t xml:space="preserve">2.96000218391418</t>
   </si>
   <si>
     <t xml:space="preserve">2.94890904426575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95445585250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97849035263062</t>
+    <t xml:space="preserve">2.95445561408997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97849059104919</t>
   </si>
   <si>
     <t xml:space="preserve">2.95260691642761</t>
@@ -4682,10 +4682,10 @@
     <t xml:space="preserve">3.08572363853455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09496808052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11900281906128</t>
+    <t xml:space="preserve">3.09496784210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11900305747986</t>
   </si>
   <si>
     <t xml:space="preserve">3.05983972549438</t>
@@ -4703,13 +4703,13 @@
     <t xml:space="preserve">3.06908392906189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0247118473053</t>
+    <t xml:space="preserve">3.02471160888672</t>
   </si>
   <si>
     <t xml:space="preserve">3.01916527748108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97479295730591</t>
+    <t xml:space="preserve">2.97479271888733</t>
   </si>
   <si>
     <t xml:space="preserve">2.92302513122559</t>
@@ -4718,7 +4718,7 @@
     <t xml:space="preserve">2.93781590461731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88419938087463</t>
+    <t xml:space="preserve">2.88419914245605</t>
   </si>
   <si>
     <t xml:space="preserve">2.90823435783386</t>
@@ -4733,19 +4733,19 @@
     <t xml:space="preserve">2.95815324783325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97109508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01546764373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11345648765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13934016227722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10975861549377</t>
+    <t xml:space="preserve">2.97109532356262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01546740531921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11345624923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13933992385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10975885391235</t>
   </si>
   <si>
     <t xml:space="preserve">3.16337513923645</t>
@@ -4754,7 +4754,7 @@
     <t xml:space="preserve">3.13379383087158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15782856941223</t>
+    <t xml:space="preserve">3.15782833099365</t>
   </si>
   <si>
     <t xml:space="preserve">3.16892170906067</t>
@@ -4763,7 +4763,7 @@
     <t xml:space="preserve">3.19480562210083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24287533760071</t>
+    <t xml:space="preserve">3.24287557601929</t>
   </si>
   <si>
     <t xml:space="preserve">3.20959615707397</t>
@@ -4772,7 +4772,7 @@
     <t xml:space="preserve">3.20589852333069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23548030853271</t>
+    <t xml:space="preserve">3.23548007011414</t>
   </si>
   <si>
     <t xml:space="preserve">3.29464316368103</t>
@@ -4787,10 +4787,10 @@
     <t xml:space="preserve">3.20774745941162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17446827888489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12085151672363</t>
+    <t xml:space="preserve">3.17446804046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12085175514221</t>
   </si>
   <si>
     <t xml:space="preserve">3.07832813262939</t>
@@ -4802,7 +4802,7 @@
     <t xml:space="preserve">3.09866547584534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07647943496704</t>
+    <t xml:space="preserve">3.07647967338562</t>
   </si>
   <si>
     <t xml:space="preserve">3.06723523139954</t>
@@ -4817,19 +4817,19 @@
     <t xml:space="preserve">3.19665431976318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20405006408691</t>
+    <t xml:space="preserve">3.20404982566833</t>
   </si>
   <si>
     <t xml:space="preserve">3.19850325584412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12454962730408</t>
+    <t xml:space="preserve">3.1245493888855</t>
   </si>
   <si>
     <t xml:space="preserve">3.16707301139832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14858436584473</t>
+    <t xml:space="preserve">3.14858412742615</t>
   </si>
   <si>
     <t xml:space="preserve">3.00067663192749</t>
@@ -4838,7 +4838,7 @@
     <t xml:space="preserve">3.04874682426453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10051441192627</t>
+    <t xml:space="preserve">3.10051465034485</t>
   </si>
   <si>
     <t xml:space="preserve">3.14488673210144</t>
@@ -71925,7 +71925,7 @@
     </row>
     <row r="2535">
       <c r="A2535" s="1" t="n">
-        <v>46008.6909953704</v>
+        <v>46008.3333333333</v>
       </c>
       <c r="B2535" t="n">
         <v>2495449</v>
@@ -71946,6 +71946,32 @@
         <v>1896</v>
       </c>
       <c r="H2535" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2536">
+      <c r="A2536" s="1" t="n">
+        <v>46009.6911805556</v>
+      </c>
+      <c r="B2536" t="n">
+        <v>2300355</v>
+      </c>
+      <c r="C2536" t="n">
+        <v>3.99000000953674</v>
+      </c>
+      <c r="D2536" t="n">
+        <v>3.96199989318848</v>
+      </c>
+      <c r="E2536" t="n">
+        <v>3.9779999256134</v>
+      </c>
+      <c r="F2536" t="n">
+        <v>3.9779999256134</v>
+      </c>
+      <c r="G2536" t="s">
+        <v>1866</v>
+      </c>
+      <c r="H2536" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HER.MI.xlsx
+++ b/data/HER.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1908" uniqueCount="1908">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1909" uniqueCount="1909">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70756649971008</t>
+    <t xml:space="preserve">1.70756638050079</t>
   </si>
   <si>
     <t xml:space="preserve">HER.MI</t>
@@ -47,49 +47,49 @@
     <t xml:space="preserve">1.7089638710022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70616924762726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71036124229431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68800330162048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72573184967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79140734672546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79420256614685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77044701576233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74669241905212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70337414741516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77324247360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74948716163635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76625525951385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80538129806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79001021385193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80398368835449</t>
+    <t xml:space="preserve">1.70616888999939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71036100387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68800365924835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7257319688797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79140770435333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79420232772827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7704473733902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74669206142426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70337426662445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77324211597443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74948692321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76625537872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8053811788559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79001045227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80398380756378</t>
   </si>
   <si>
     <t xml:space="preserve">1.83472549915314</t>
@@ -98,25 +98,25 @@
     <t xml:space="preserve">1.81656002998352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80258631706238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8486989736557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85568594932556</t>
+    <t xml:space="preserve">1.80258643627167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84869933128357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85568571090698</t>
   </si>
   <si>
     <t xml:space="preserve">1.84031510353088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82354688644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82913625240326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72852694988251</t>
+    <t xml:space="preserve">1.82354652881622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82913613319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72852647304535</t>
   </si>
   <si>
     <t xml:space="preserve">1.74110293388367</t>
@@ -125,46 +125,46 @@
     <t xml:space="preserve">1.75926828384399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69918251037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75507664680481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7955995798111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78302359580994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77603662014008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79839432239532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80118918418884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82075238227844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83053350448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7886129617691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76485776901245</t>
+    <t xml:space="preserve">1.69918215274811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75507640838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79559981822968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78302347660065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77603673934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79839444160461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80118930339813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82075190544128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83053338527679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78861260414124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76485800743103</t>
   </si>
   <si>
     <t xml:space="preserve">1.74529492855072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73970556259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72992408275604</t>
+    <t xml:space="preserve">1.73970544338226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72992384433746</t>
   </si>
   <si>
     <t xml:space="preserve">1.74389779567719</t>
@@ -173,220 +173,220 @@
     <t xml:space="preserve">1.73271894454956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76346063613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77883160114288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76066589355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77463924884796</t>
+    <t xml:space="preserve">1.76346051692963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77883124351501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76066601276398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77463960647583</t>
   </si>
   <si>
     <t xml:space="preserve">1.79699718952179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83752071857452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81097102165222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8570830821991</t>
+    <t xml:space="preserve">1.83752059936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81097066402435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85708367824554</t>
   </si>
   <si>
     <t xml:space="preserve">1.84310960769653</t>
   </si>
   <si>
+    <t xml:space="preserve">1.76765239238739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78162622451782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78721559047699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77743399143219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78022909164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80817592144012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80957317352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79280483722687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78442096710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75647377967834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74808979034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82634139060974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84590458869934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83193099498749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84450733661652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82214975357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8333283662796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82494401931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81376504898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76206350326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73132145404816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74250030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71175849437714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75751030445099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77344822883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7401237487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75895941257477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70390093326569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67347407341003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70969676971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73867475986481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78069269657135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83430194854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8082218170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81111919879913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78503954410553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77924370765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72708368301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76040828227997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74591946601868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77055037021637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76620352268219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76185691356659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76910150051117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77489721775055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78359019756317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83719980716705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85748410224915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85023963451385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83575069904327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86617732048035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83140408992767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84444391727448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79663074016571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81981289386749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81256854534149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74881708621979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7444703578949</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.76765251159668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78162610530853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78721582889557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77743399143219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78022873401642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80817568302155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80957293510437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79280471801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78442096710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75647389888763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74808967113495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82634162902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84590446949005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8319308757782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84450709819794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82214963436127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83332824707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82494401931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81376540660858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76206314563751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73132133483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74249982833862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71175849437714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75751042366028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77344834804535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74012351036072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75895929336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70390117168427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67347431182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70969676971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7386748790741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78069257736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83430194854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80822193622589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81111967563629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78503930568695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77924394607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72708368301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76040804386139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7459192276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77055037021637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76620352268219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76185715198517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76910161972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77489697933197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78359043598175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83719992637634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85748386383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85023963451385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83575057983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86617743968964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83140397071838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84444427490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79663074016571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81981301307678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81256854534149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7488169670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74447047710419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76765286922455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77634572982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79083478450775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79952847957611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78648829460144</t>
+    <t xml:space="preserve">1.77634608745575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79083490371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79952836036682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78648865222931</t>
   </si>
   <si>
     <t xml:space="preserve">1.78938591480255</t>
@@ -395,28 +395,28 @@
     <t xml:space="preserve">1.81546604633331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75606143474579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73577678203583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70679903030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7372260093689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75461256504059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71114575862885</t>
+    <t xml:space="preserve">1.75606155395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73577690124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70679891109467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73722589015961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75461280345917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71114563941956</t>
   </si>
   <si>
     <t xml:space="preserve">1.70824790000916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70245242118835</t>
+    <t xml:space="preserve">1.70245230197906</t>
   </si>
   <si>
     <t xml:space="preserve">1.69231021404266</t>
@@ -425,25 +425,25 @@
     <t xml:space="preserve">1.71694111824036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69665658473969</t>
+    <t xml:space="preserve">1.69665682315826</t>
   </si>
   <si>
     <t xml:space="preserve">1.63145649433136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6053763628006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59233641624451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57929646968842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.601029753685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60972309112549</t>
+    <t xml:space="preserve">1.60537648200989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59233629703522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57929623126984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60102951526642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6097229719162</t>
   </si>
   <si>
     <t xml:space="preserve">1.61406981945038</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">1.63290524482727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61841666698456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63870096206665</t>
+    <t xml:space="preserve">1.61841630935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63870108127594</t>
   </si>
   <si>
     <t xml:space="preserve">1.63725209236145</t>
@@ -467,43 +467,43 @@
     <t xml:space="preserve">1.65029203891754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62276291847229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.615518450737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61696767807007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62566077709198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66188299655914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66912758350372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68796336650848</t>
+    <t xml:space="preserve">1.62276315689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61551868915558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61696743965149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62566089630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66188335418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66912746429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68796360492706</t>
   </si>
   <si>
     <t xml:space="preserve">1.593785405159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56625628471375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56335830688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54307377338409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46048665046692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4633846282959</t>
+    <t xml:space="preserve">1.56625592708588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56335854530334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54307389259338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4604868888855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46338438987732</t>
   </si>
   <si>
     <t xml:space="preserve">1.44599783420563</t>
@@ -512,52 +512,52 @@
     <t xml:space="preserve">1.44527339935303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45034468173981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43005990982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42209100723267</t>
+    <t xml:space="preserve">1.45034456253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43005979061127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42209088802338</t>
   </si>
   <si>
     <t xml:space="preserve">1.39601099491119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39456188678741</t>
+    <t xml:space="preserve">1.3945620059967</t>
   </si>
   <si>
     <t xml:space="preserve">1.40905106067657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41267323493958</t>
+    <t xml:space="preserve">1.41267335414886</t>
   </si>
   <si>
     <t xml:space="preserve">1.39818429946899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40180647373199</t>
+    <t xml:space="preserve">1.40180635452271</t>
   </si>
   <si>
     <t xml:space="preserve">1.40542876720428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41629564762115</t>
+    <t xml:space="preserve">1.41629552841187</t>
   </si>
   <si>
     <t xml:space="preserve">1.38152194023132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35906410217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37717521190643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43875336647034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48077130317688</t>
+    <t xml:space="preserve">1.35906422138214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37717533111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43875324726105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48077142238617</t>
   </si>
   <si>
     <t xml:space="preserve">1.49236249923706</t>
@@ -569,40 +569,40 @@
     <t xml:space="preserve">1.5329315662384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52713584899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50105583667755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50685143470764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54886937141418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55756270885468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57060277462006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5908876657486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56915390491486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58798944950104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.608274102211</t>
+    <t xml:space="preserve">1.52713596820831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50105571746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50685131549835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54886949062347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55756282806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57060265541077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59088718891144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56915378570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58798968791962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60827398300171</t>
   </si>
   <si>
     <t xml:space="preserve">1.59668290615082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5995808839798</t>
+    <t xml:space="preserve">1.59958064556122</t>
   </si>
   <si>
     <t xml:space="preserve">1.56480741500854</t>
@@ -611,34 +611,34 @@
     <t xml:space="preserve">1.65174102783203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64159893989563</t>
+    <t xml:space="preserve">1.64159870147705</t>
   </si>
   <si>
     <t xml:space="preserve">1.65318977832794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65463864803314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65898549556732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64014959335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64304745197296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57494974136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57784712314606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55176711082458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58654081821442</t>
+    <t xml:space="preserve">1.65463852882385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65898537635803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64014983177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64304733276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57494962215424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57784748077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5517669916153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58654057979584</t>
   </si>
   <si>
     <t xml:space="preserve">1.63000738620758</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">1.68216788768768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66622984409332</t>
+    <t xml:space="preserve">1.66622996330261</t>
   </si>
   <si>
     <t xml:space="preserve">1.6778210401535</t>
@@ -656,25 +656,25 @@
     <t xml:space="preserve">1.69086122512817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69375920295715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69810557365417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69520795345306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71404349803925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72998106479645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73432838916779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71983933448792</t>
+    <t xml:space="preserve">1.69375884532928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69810581207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69520783424377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71404361724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72998118400574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73432815074921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71983909606934</t>
   </si>
   <si>
     <t xml:space="preserve">1.72418594360352</t>
@@ -689,52 +689,52 @@
     <t xml:space="preserve">1.74157249927521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78214168548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78793704509735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81401741504669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82995510101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86907529830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89950227737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91399121284485</t>
+    <t xml:space="preserve">1.78214144706726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78793728351593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81401717662811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82995533943176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86907541751862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89950215816498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91399109363556</t>
   </si>
   <si>
     <t xml:space="preserve">1.91543996334076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88066649436951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87197327613831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88935995101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90095090866089</t>
+    <t xml:space="preserve">1.88066625595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87197303771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88936007022858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90095126628876</t>
   </si>
   <si>
     <t xml:space="preserve">1.90529787540436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91254234313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94441759586334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9371737241745</t>
+    <t xml:space="preserve">1.91254258155823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94441795349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93717360496521</t>
   </si>
   <si>
     <t xml:space="preserve">1.87921786308289</t>
@@ -743,34 +743,34 @@
     <t xml:space="preserve">1.8835643529892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92848002910614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89805316925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88791108131409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90239989757538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91688883304596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92413341999054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93572425842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93862223625183</t>
+    <t xml:space="preserve">1.92847990989685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8980530500412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88791084289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90239977836609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91688895225525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92413318157196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93572473526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9386225938797</t>
   </si>
   <si>
     <t xml:space="preserve">1.9487646818161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99512898921967</t>
+    <t xml:space="preserve">1.99512910842896</t>
   </si>
   <si>
     <t xml:space="preserve">2.0284538269043</t>
@@ -779,16 +779,16 @@
     <t xml:space="preserve">2.05743145942688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06902313232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05163621902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10234785079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06467604637146</t>
+    <t xml:space="preserve">2.06902265548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05163598060608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10234713554382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06467652320862</t>
   </si>
   <si>
     <t xml:space="preserve">2.03859615325928</t>
@@ -803,13 +803,13 @@
     <t xml:space="preserve">2.12842750549316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1124894618988</t>
+    <t xml:space="preserve">2.11248970031738</t>
   </si>
   <si>
     <t xml:space="preserve">2.11104083061218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10089874267578</t>
+    <t xml:space="preserve">2.10089898109436</t>
   </si>
   <si>
     <t xml:space="preserve">2.05453395843506</t>
@@ -818,37 +818,37 @@
     <t xml:space="preserve">2.08930778503418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12263226509094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07916498184204</t>
+    <t xml:space="preserve">2.12263202667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07916522026062</t>
   </si>
   <si>
     <t xml:space="preserve">2.1037962436676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11973452568054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10814356803894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1472635269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13277435302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1545078754425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14291667938232</t>
+    <t xml:space="preserve">2.11973428726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10814309120178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14726328849792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13277411460876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15450763702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14291644096375</t>
   </si>
   <si>
     <t xml:space="preserve">2.15595674514771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1679093837738</t>
+    <t xml:space="preserve">2.16790914535522</t>
   </si>
   <si>
     <t xml:space="preserve">2.17836785316467</t>
@@ -863,112 +863,112 @@
     <t xml:space="preserve">2.112628698349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07228851318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05884170532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01700735092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99907863140106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01103115081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00804305076599</t>
+    <t xml:space="preserve">2.07228803634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05884146690369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01700782775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99907886981964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01103091239929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00804281234741</t>
   </si>
   <si>
     <t xml:space="preserve">1.99758446216583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95126783847809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97069096565247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00505447387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98264336585999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0304536819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05286502838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03941822052002</t>
+    <t xml:space="preserve">1.95126760005951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97069084644318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00505471229553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9826432466507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03045392036438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05286526679993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0394184589386</t>
   </si>
   <si>
     <t xml:space="preserve">2.03194808959961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04539513587952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0244779586792</t>
+    <t xml:space="preserve">2.04539465904236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02447772026062</t>
   </si>
   <si>
     <t xml:space="preserve">2.06182980537415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07677030563354</t>
+    <t xml:space="preserve">2.07677054405212</t>
   </si>
   <si>
     <t xml:space="preserve">2.03344202041626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01401948928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05435943603516</t>
+    <t xml:space="preserve">2.01401901245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05435919761658</t>
   </si>
   <si>
     <t xml:space="preserve">2.04390096664429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04240679740906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0364305973053</t>
+    <t xml:space="preserve">2.04240655899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03643035888672</t>
   </si>
   <si>
     <t xml:space="preserve">2.0483832359314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04987716674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00206661224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05585360527039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03493618965149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99459600448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97517335414886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96172630786896</t>
+    <t xml:space="preserve">2.04987692832947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00206637382507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05585336685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03493642807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99459624290466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97517323493958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96172654628754</t>
   </si>
   <si>
     <t xml:space="preserve">1.96770286560059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02597165107727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01252484321594</t>
+    <t xml:space="preserve">2.02597188949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01252508163452</t>
   </si>
   <si>
     <t xml:space="preserve">2.00953722000122</t>
@@ -977,31 +977,31 @@
     <t xml:space="preserve">2.0035605430603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07826471328735</t>
+    <t xml:space="preserve">2.07826447486877</t>
   </si>
   <si>
     <t xml:space="preserve">2.01850128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.000572681427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98563182353973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98712599277496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9721851348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02148962020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03792428970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06033539772034</t>
+    <t xml:space="preserve">2.00057220458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98563194274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98712587356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97218525409698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02148985862732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03792452812195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06033563613892</t>
   </si>
   <si>
     <t xml:space="preserve">2.07079434394836</t>
@@ -1010,16 +1010,16 @@
     <t xml:space="preserve">2.07378220558167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06631207466125</t>
+    <t xml:space="preserve">2.06631183624268</t>
   </si>
   <si>
     <t xml:space="preserve">2.06332397460938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07527637481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08424115180969</t>
+    <t xml:space="preserve">2.07527685165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08424067497253</t>
   </si>
   <si>
     <t xml:space="preserve">2.10665225982666</t>
@@ -1037,10 +1037,10 @@
     <t xml:space="preserve">2.18135619163513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19629716873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18733215332031</t>
+    <t xml:space="preserve">2.19629693031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18733263015747</t>
   </si>
   <si>
     <t xml:space="preserve">2.1798620223999</t>
@@ -1049,88 +1049,88 @@
     <t xml:space="preserve">2.16641545295715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17089772224426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.191814661026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19330883026123</t>
+    <t xml:space="preserve">2.1708972454071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19181489944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19330859184265</t>
   </si>
   <si>
     <t xml:space="preserve">2.19480276107788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22468400001526</t>
+    <t xml:space="preserve">2.22468423843384</t>
   </si>
   <si>
     <t xml:space="preserve">2.27100086212158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2560601234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25904774665833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28145933151245</t>
+    <t xml:space="preserve">2.25606036186218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2590479850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28145980834961</t>
   </si>
   <si>
     <t xml:space="preserve">2.2949059009552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30536460876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30088210105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33972835540771</t>
+    <t xml:space="preserve">2.30536437034607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30088233947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33972883224487</t>
   </si>
   <si>
     <t xml:space="preserve">2.28892993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27398920059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.303870677948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3158233165741</t>
+    <t xml:space="preserve">2.27398896217346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30387091636658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31582307815552</t>
   </si>
   <si>
     <t xml:space="preserve">2.25456595420837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25755429267883</t>
+    <t xml:space="preserve">2.25755405426025</t>
   </si>
   <si>
     <t xml:space="preserve">2.27847123146057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22916674613953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22617864608765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21870851516724</t>
+    <t xml:space="preserve">2.22916650772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22617816925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21870827674866</t>
   </si>
   <si>
     <t xml:space="preserve">2.17388582229614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15446257591248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21123766899109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26054215431213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31134128570557</t>
+    <t xml:space="preserve">2.15446305274963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21123743057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26054239273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31134104728699</t>
   </si>
   <si>
     <t xml:space="preserve">2.24111938476562</t>
@@ -1142,34 +1142,34 @@
     <t xml:space="preserve">2.23813128471375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2769775390625</t>
+    <t xml:space="preserve">2.27697730064392</t>
   </si>
   <si>
     <t xml:space="preserve">2.28594183921814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29938864707947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24709558486938</t>
+    <t xml:space="preserve">2.29938840866089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24709510803223</t>
   </si>
   <si>
     <t xml:space="preserve">2.2799654006958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24560141563416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18434453010559</t>
+    <t xml:space="preserve">2.24560165405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18434429168701</t>
   </si>
   <si>
     <t xml:space="preserve">2.13503956794739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11113405227661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05734729766846</t>
+    <t xml:space="preserve">2.11113452911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05734777450562</t>
   </si>
   <si>
     <t xml:space="preserve">2.02895998954773</t>
@@ -1178,13 +1178,13 @@
     <t xml:space="preserve">2.09469938278198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12607502937317</t>
+    <t xml:space="preserve">2.12607526779175</t>
   </si>
   <si>
     <t xml:space="preserve">2.13354563713074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09320569038391</t>
+    <t xml:space="preserve">2.09320545196533</t>
   </si>
   <si>
     <t xml:space="preserve">2.06929993629456</t>
@@ -1193,58 +1193,58 @@
     <t xml:space="preserve">2.04091238975525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08573508262634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08274674415588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08125257492065</t>
+    <t xml:space="preserve">2.08573532104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08274698257446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08125281333923</t>
   </si>
   <si>
     <t xml:space="preserve">2.10216975212097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09768772125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12009906768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21273183822632</t>
+    <t xml:space="preserve">2.09768748283386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12009859085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2127320766449</t>
   </si>
   <si>
     <t xml:space="preserve">2.22169613838196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2306604385376</t>
+    <t xml:space="preserve">2.23066091537476</t>
   </si>
   <si>
     <t xml:space="preserve">2.24261355400085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26353073120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23514318466187</t>
+    <t xml:space="preserve">2.26353049278259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23514294624329</t>
   </si>
   <si>
     <t xml:space="preserve">2.25307202339172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29341173171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29789447784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28444743156433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2276725769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25157785415649</t>
+    <t xml:space="preserve">2.29341197013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29789423942566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28444719314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22767281532288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25157761573792</t>
   </si>
   <si>
     <t xml:space="preserve">2.14101600646973</t>
@@ -1253,25 +1253,25 @@
     <t xml:space="preserve">2.12159276008606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02298355102539</t>
+    <t xml:space="preserve">2.02298378944397</t>
   </si>
   <si>
     <t xml:space="preserve">1.94678544998169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.964714884758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98114943504333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96919679641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97816121578217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94827938079834</t>
+    <t xml:space="preserve">1.96471428871155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98114955425262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96919667720795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97816109657288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94828009605408</t>
   </si>
   <si>
     <t xml:space="preserve">2.02856683731079</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">2.06108570098877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0719256401062</t>
+    <t xml:space="preserve">2.07192587852478</t>
   </si>
   <si>
     <t xml:space="preserve">2.0378577709198</t>
@@ -1295,25 +1295,25 @@
     <t xml:space="preserve">2.05953741073608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08895897865295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06727981567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10599327087402</t>
+    <t xml:space="preserve">2.08895921707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06728005409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10599303245544</t>
   </si>
   <si>
     <t xml:space="preserve">2.13541507720947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15399742126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16019153594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14470624923706</t>
+    <t xml:space="preserve">2.15399694442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16019129753113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1447057723999</t>
   </si>
   <si>
     <t xml:space="preserve">2.13696360588074</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">2.14780306816101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13386631011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16793394088745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17257976531982</t>
+    <t xml:space="preserve">2.13386654853821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16793417930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17257952690125</t>
   </si>
   <si>
     <t xml:space="preserve">2.1524486541748</t>
@@ -1337,22 +1337,22 @@
     <t xml:space="preserve">2.1044442653656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09205627441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20664668083191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17103099822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19580721855164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18651604652405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21748661994934</t>
+    <t xml:space="preserve">2.09205603599548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20664691925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1710307598114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19580745697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18651628494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21748685836792</t>
   </si>
   <si>
     <t xml:space="preserve">2.21593809127808</t>
@@ -1361,22 +1361,22 @@
     <t xml:space="preserve">2.1834192276001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16328835487366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15090012550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13231778144836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12612414360046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11992979049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16638541221619</t>
+    <t xml:space="preserve">2.16328811645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1509006023407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13231801986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12612390518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11992955207825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16638565063477</t>
   </si>
   <si>
     <t xml:space="preserve">2.1570942401886</t>
@@ -1385,19 +1385,19 @@
     <t xml:space="preserve">2.14935183525085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09670162200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09979867935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0905077457428</t>
+    <t xml:space="preserve">2.09670186042786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09979891777039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09050798416138</t>
   </si>
   <si>
     <t xml:space="preserve">2.10754156112671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12457489967346</t>
+    <t xml:space="preserve">2.12457513809204</t>
   </si>
   <si>
     <t xml:space="preserve">2.12767219543457</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">2.20045304298401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1973557472229</t>
+    <t xml:space="preserve">2.19735598564148</t>
   </si>
   <si>
     <t xml:space="preserve">2.20200157165527</t>
@@ -1427,22 +1427,22 @@
     <t xml:space="preserve">2.12147831916809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1168327331543</t>
+    <t xml:space="preserve">2.11683297157288</t>
   </si>
   <si>
     <t xml:space="preserve">2.07657098770142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06882810592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05179452896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01462984085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9619802236557</t>
+    <t xml:space="preserve">2.06882834434509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05179476737976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01463007926941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96197998523712</t>
   </si>
   <si>
     <t xml:space="preserve">1.98211085796356</t>
@@ -1451,94 +1451,94 @@
     <t xml:space="preserve">1.93720400333405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90313625335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86287438869476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91552448272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87216591835022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89384508132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90158760547638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87061703205109</t>
+    <t xml:space="preserve">1.90313613414764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86287462711334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91552424430847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87216579914093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89384520053864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90158772468567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87061738967896</t>
   </si>
   <si>
     <t xml:space="preserve">1.85977756977081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92791283130646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89694201946259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89074802398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87990832328796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88919973373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88765096664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9046847820282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92171859741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96662569046021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91862165927887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97901391983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96972286701202</t>
+    <t xml:space="preserve">1.92791259288788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89694237709045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89074814319611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87990844249725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88919937610626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88765072822571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90468466281891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9217187166214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96662592887878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91862154006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97901403903961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96972298622131</t>
   </si>
   <si>
     <t xml:space="preserve">1.97746539115906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94184935092926</t>
+    <t xml:space="preserve">1.94184947013855</t>
   </si>
   <si>
     <t xml:space="preserve">1.93100965023041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92481541633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92017018795013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89229667186737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90933060646057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87835991382599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93875229358673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86906862258911</t>
+    <t xml:space="preserve">1.92481565475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92016994953156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89229679107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90933084487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87836003303528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93875253200531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86906886100769</t>
   </si>
   <si>
     <t xml:space="preserve">1.94804346561432</t>
@@ -1547,40 +1547,40 @@
     <t xml:space="preserve">1.98675656318665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360480308533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03630948066711</t>
+    <t xml:space="preserve">2.09360456466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03630924224854</t>
   </si>
   <si>
     <t xml:space="preserve">2.06573152542114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0982506275177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08276534080505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19116187095642</t>
+    <t xml:space="preserve">2.09825038909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08276510238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19116163253784</t>
   </si>
   <si>
     <t xml:space="preserve">2.19425892829895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17877316474915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2050986289978</t>
+    <t xml:space="preserve">2.17877388000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20509839057922</t>
   </si>
   <si>
     <t xml:space="preserve">2.2097442150116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22987484931946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20355010032654</t>
+    <t xml:space="preserve">2.22987508773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20354986190796</t>
   </si>
   <si>
     <t xml:space="preserve">2.19890427589417</t>
@@ -1589,28 +1589,28 @@
     <t xml:space="preserve">2.22677803039551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26084566116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26239395141602</t>
+    <t xml:space="preserve">2.26084542274475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26239371299744</t>
   </si>
   <si>
     <t xml:space="preserve">2.28562188148499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29336452484131</t>
+    <t xml:space="preserve">2.29336428642273</t>
   </si>
   <si>
     <t xml:space="preserve">2.28252482414246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28407311439514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2902672290802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27013635635376</t>
+    <t xml:space="preserve">2.2840735912323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29026746749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27013659477234</t>
   </si>
   <si>
     <t xml:space="preserve">2.25619983673096</t>
@@ -1622,19 +1622,19 @@
     <t xml:space="preserve">2.30265545845032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30110692977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30730104446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2980101108551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28871893882751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25929665565491</t>
+    <t xml:space="preserve">2.30110669136047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30730128288269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29801034927368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28871917724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25929689407349</t>
   </si>
   <si>
     <t xml:space="preserve">2.32433485984802</t>
@@ -1643,13 +1643,13 @@
     <t xml:space="preserve">2.29181575775146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25465154647827</t>
+    <t xml:space="preserve">2.25465130805969</t>
   </si>
   <si>
     <t xml:space="preserve">2.26858806610107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26549124717712</t>
+    <t xml:space="preserve">2.26549077033997</t>
   </si>
   <si>
     <t xml:space="preserve">2.29955887794495</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">2.29646134376526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31349515914917</t>
+    <t xml:space="preserve">2.31349539756775</t>
   </si>
   <si>
     <t xml:space="preserve">2.32123780250549</t>
@@ -1667,13 +1667,13 @@
     <t xml:space="preserve">2.25774836540222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23916578292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34446573257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38008189201355</t>
+    <t xml:space="preserve">2.23916625976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34446597099304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38008165359497</t>
   </si>
   <si>
     <t xml:space="preserve">2.38163018226624</t>
@@ -1682,46 +1682,46 @@
     <t xml:space="preserve">2.40330982208252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42808604240417</t>
+    <t xml:space="preserve">2.4280858039856</t>
   </si>
   <si>
     <t xml:space="preserve">2.4311830997467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47608995437622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4946722984314</t>
+    <t xml:space="preserve">2.4760901927948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49467253684998</t>
   </si>
   <si>
     <t xml:space="preserve">2.49002695083618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49622082710266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50860953330994</t>
+    <t xml:space="preserve">2.49622106552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50860929489136</t>
   </si>
   <si>
     <t xml:space="preserve">2.54887080192566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52099752426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50241541862488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51635193824768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46215343475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47918725013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46525096893311</t>
+    <t xml:space="preserve">2.52099776268005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5024151802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5163516998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.462153673172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47918748855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46525073051453</t>
   </si>
   <si>
     <t xml:space="preserve">2.43428015708923</t>
@@ -1730,52 +1730,52 @@
     <t xml:space="preserve">2.4497652053833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45286226272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46679902076721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44666838645935</t>
+    <t xml:space="preserve">2.45286250114441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46679925918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44666790962219</t>
   </si>
   <si>
     <t xml:space="preserve">2.4575080871582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47144460678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45905661582947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42653775215149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44821667671204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42963409423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48692989349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53028845787048</t>
+    <t xml:space="preserve">2.47144484519958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45905685424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42653751373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44821691513062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42963457107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48692965507507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53028869628906</t>
   </si>
   <si>
     <t xml:space="preserve">2.53803110122681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54112815856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54422545433044</t>
+    <t xml:space="preserve">2.54112839698792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54422521591187</t>
   </si>
   <si>
     <t xml:space="preserve">2.55661344528198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55816173553467</t>
+    <t xml:space="preserve">2.55816197395325</t>
   </si>
   <si>
     <t xml:space="preserve">2.53648281097412</t>
@@ -1787,73 +1787,73 @@
     <t xml:space="preserve">2.5287401676178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51790022850037</t>
+    <t xml:space="preserve">2.51790046691895</t>
   </si>
   <si>
     <t xml:space="preserve">2.56435632705688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5906810760498</t>
+    <t xml:space="preserve">2.59068131446838</t>
   </si>
   <si>
     <t xml:space="preserve">2.60306930541992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60461759567261</t>
+    <t xml:space="preserve">2.60461783409119</t>
   </si>
   <si>
     <t xml:space="preserve">2.59997224807739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60152053833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58913254737854</t>
+    <t xml:space="preserve">2.60152077674866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58913278579712</t>
   </si>
   <si>
     <t xml:space="preserve">2.58603549003601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64642786979675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65262198448181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68514084815979</t>
+    <t xml:space="preserve">2.64642810821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65262222290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68514108657837</t>
   </si>
   <si>
     <t xml:space="preserve">2.7161111831665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69698405265808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67945027351379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68263840675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65075922012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68104457855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66669869422913</t>
+    <t xml:space="preserve">2.69698429107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67945051193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68263816833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65075898170471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68104434013367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66669893264771</t>
   </si>
   <si>
     <t xml:space="preserve">2.73045754432678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81174921989441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80856132507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7846519947052</t>
+    <t xml:space="preserve">2.81174945831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80856108665466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78465151786804</t>
   </si>
   <si>
     <t xml:space="preserve">2.77349424362183</t>
@@ -1862,25 +1862,25 @@
     <t xml:space="preserve">2.78305792808533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79740381240845</t>
+    <t xml:space="preserve">2.79740357398987</t>
   </si>
   <si>
     <t xml:space="preserve">2.79580950737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8276891708374</t>
+    <t xml:space="preserve">2.82768893241882</t>
   </si>
   <si>
     <t xml:space="preserve">2.80696749687195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75914835929871</t>
+    <t xml:space="preserve">2.75914859771729</t>
   </si>
   <si>
     <t xml:space="preserve">2.74480271339417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74958467483521</t>
+    <t xml:space="preserve">2.74958491325378</t>
   </si>
   <si>
     <t xml:space="preserve">2.7320511341095</t>
@@ -1898,22 +1898,22 @@
     <t xml:space="preserve">2.68582630157471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73683333396912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7113299369812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69539022445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70654773712158</t>
+    <t xml:space="preserve">2.73683309555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71132969856262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69538998603821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70654797554016</t>
   </si>
   <si>
     <t xml:space="preserve">2.72726917266846</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70495367050171</t>
+    <t xml:space="preserve">2.70495390892029</t>
   </si>
   <si>
     <t xml:space="preserve">2.73523902893066</t>
@@ -1922,19 +1922,19 @@
     <t xml:space="preserve">2.68742036819458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76233673095703</t>
+    <t xml:space="preserve">2.76233649253845</t>
   </si>
   <si>
     <t xml:space="preserve">2.78783988952637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77827596664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78624606132507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8133430480957</t>
+    <t xml:space="preserve">2.77827620506287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78624582290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81334328651428</t>
   </si>
   <si>
     <t xml:space="preserve">2.88188362121582</t>
@@ -1943,28 +1943,28 @@
     <t xml:space="preserve">2.87869572639465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91535663604736</t>
+    <t xml:space="preserve">2.91535687446594</t>
   </si>
   <si>
     <t xml:space="preserve">2.89144730567932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88666558265686</t>
+    <t xml:space="preserve">2.88666534423828</t>
   </si>
   <si>
     <t xml:space="preserve">2.88825964927673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91695070266724</t>
+    <t xml:space="preserve">2.91695094108582</t>
   </si>
   <si>
     <t xml:space="preserve">2.89622926712036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80059123039246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79262161254883</t>
+    <t xml:space="preserve">2.80059146881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79262208938599</t>
   </si>
   <si>
     <t xml:space="preserve">2.84522247314453</t>
@@ -1973,7 +1973,7 @@
     <t xml:space="preserve">2.81812500953674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82131266593933</t>
+    <t xml:space="preserve">2.82131314277649</t>
   </si>
   <si>
     <t xml:space="preserve">2.84681630134583</t>
@@ -1982,22 +1982,22 @@
     <t xml:space="preserve">2.90738677978516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90419912338257</t>
+    <t xml:space="preserve">2.90419888496399</t>
   </si>
   <si>
     <t xml:space="preserve">2.86913180351257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95201778411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95042371749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02055788040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96476936340332</t>
+    <t xml:space="preserve">2.95201802253723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95042395591736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02055835723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9647696018219</t>
   </si>
   <si>
     <t xml:space="preserve">3.00143074989319</t>
@@ -2015,106 +2015,106 @@
     <t xml:space="preserve">3.02215242385864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00461888313293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97911548614502</t>
+    <t xml:space="preserve">3.00461864471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97911524772644</t>
   </si>
   <si>
     <t xml:space="preserve">3.00302457809448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01418256759644</t>
+    <t xml:space="preserve">3.01418232917786</t>
   </si>
   <si>
     <t xml:space="preserve">2.98389720916748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02374649047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99664878845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96636366844177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99346089363098</t>
+    <t xml:space="preserve">3.02374601364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99664902687073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96636343002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99346113204956</t>
   </si>
   <si>
     <t xml:space="preserve">3.00621271133423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04606151580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05881333351135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04924964904785</t>
+    <t xml:space="preserve">3.04606175422668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05881357192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04924941062927</t>
   </si>
   <si>
     <t xml:space="preserve">3.06997108459473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03012228012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05403137207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06678318977356</t>
+    <t xml:space="preserve">3.03012204170227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05403161048889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06678295135498</t>
   </si>
   <si>
     <t xml:space="preserve">3.05243754386902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07315921783447</t>
+    <t xml:space="preserve">3.07315897941589</t>
   </si>
   <si>
     <t xml:space="preserve">3.07475328445435</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10025644302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17357873916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19748830795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19429993629456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21820950508118</t>
+    <t xml:space="preserve">3.10025668144226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17357897758484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1974880695343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19430017471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21820974349976</t>
   </si>
   <si>
     <t xml:space="preserve">3.19589447975159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16242074966431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17995452880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15604496002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18473649024963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17517256736755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19111251831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06200122833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08750486373901</t>
+    <t xml:space="preserve">3.16242122650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17995429039001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15604543685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18473672866821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17517280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19111227989197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0620014667511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08750462532043</t>
   </si>
   <si>
     <t xml:space="preserve">3.1241660118103</t>
@@ -2123,16 +2123,16 @@
     <t xml:space="preserve">3.10185027122498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09547472000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07156491279602</t>
+    <t xml:space="preserve">3.09547448158264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0715651512146</t>
   </si>
   <si>
     <t xml:space="preserve">3.10344457626343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11141419410706</t>
+    <t xml:space="preserve">3.11141395568848</t>
   </si>
   <si>
     <t xml:space="preserve">3.06040740013123</t>
@@ -2144,13 +2144,13 @@
     <t xml:space="preserve">3.17198491096497</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16879677772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16401505470276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22139739990234</t>
+    <t xml:space="preserve">3.16879653930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16401481628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22139716148376</t>
   </si>
   <si>
     <t xml:space="preserve">3.16082715988159</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">3.10822629928589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09706854820251</t>
+    <t xml:space="preserve">3.09706830978394</t>
   </si>
   <si>
     <t xml:space="preserve">3.10663223266602</t>
@@ -2171,94 +2171,94 @@
     <t xml:space="preserve">3.0811288356781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07794117927551</t>
+    <t xml:space="preserve">3.07794094085693</t>
   </si>
   <si>
     <t xml:space="preserve">3.14329361915588</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18633055686951</t>
+    <t xml:space="preserve">3.18633031845093</t>
   </si>
   <si>
     <t xml:space="preserve">3.18314242362976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13213562965393</t>
+    <t xml:space="preserve">3.13213586807251</t>
   </si>
   <si>
     <t xml:space="preserve">3.27240443229675</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37760591506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3138473033905</t>
+    <t xml:space="preserve">3.377605676651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31384706497192</t>
   </si>
   <si>
     <t xml:space="preserve">3.44774055480957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44614624977112</t>
+    <t xml:space="preserve">3.44614577293396</t>
   </si>
   <si>
     <t xml:space="preserve">3.37919974327087</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26921629905701</t>
+    <t xml:space="preserve">3.26921677589417</t>
   </si>
   <si>
     <t xml:space="preserve">3.27718639373779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28674983978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33297491073608</t>
+    <t xml:space="preserve">3.28675031661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33297514915466</t>
   </si>
   <si>
     <t xml:space="preserve">3.37282395362854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38557577133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40948486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4270191192627</t>
+    <t xml:space="preserve">3.38557600975037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40948510169983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42701864242554</t>
   </si>
   <si>
     <t xml:space="preserve">3.43977046012878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47802567481995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45252180099487</t>
+    <t xml:space="preserve">3.47802495956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45252203941345</t>
   </si>
   <si>
     <t xml:space="preserve">3.45730400085449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47005605697632</t>
+    <t xml:space="preserve">3.47005581855774</t>
   </si>
   <si>
     <t xml:space="preserve">3.55612969398499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53700184822083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51628065109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.339350938797</t>
+    <t xml:space="preserve">3.53700256347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51628088951111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33935117721558</t>
   </si>
   <si>
     <t xml:space="preserve">3.30906534194946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33775663375854</t>
+    <t xml:space="preserve">3.3377571105957</t>
   </si>
   <si>
     <t xml:space="preserve">3.27877998352051</t>
@@ -2279,10 +2279,10 @@
     <t xml:space="preserve">2.65872883796692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69060802459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22038912773132</t>
+    <t xml:space="preserve">2.69060826301575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2203893661499</t>
   </si>
   <si>
     <t xml:space="preserve">2.55830931663513</t>
@@ -2291,16 +2291,16 @@
     <t xml:space="preserve">2.46585941314697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51049041748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51686596870422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46107745170593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58381295204163</t>
+    <t xml:space="preserve">2.51049065589905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5168662071228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46107792854309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58381271362305</t>
   </si>
   <si>
     <t xml:space="preserve">2.44195008277893</t>
@@ -2315,40 +2315,40 @@
     <t xml:space="preserve">2.50252079963684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62206768989563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60453391075134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52802419662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56468534469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5312123298645</t>
+    <t xml:space="preserve">2.62206745147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60453414916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52802395820618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56468510627747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53121209144592</t>
   </si>
   <si>
     <t xml:space="preserve">2.55193328857422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45948362350464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57584309577942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56787252426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54715180397034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54396367073059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60772228240967</t>
+    <t xml:space="preserve">2.45948338508606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57584285736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56787300109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54715156555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54396390914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60772204399109</t>
   </si>
   <si>
     <t xml:space="preserve">2.62047386169434</t>
@@ -2357,22 +2357,22 @@
     <t xml:space="preserve">2.5184600353241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59018850326538</t>
+    <t xml:space="preserve">2.5901882648468</t>
   </si>
   <si>
     <t xml:space="preserve">2.5806245803833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67307448387146</t>
+    <t xml:space="preserve">2.67307472229004</t>
   </si>
   <si>
     <t xml:space="preserve">2.69220209121704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57903075218201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57265472412109</t>
+    <t xml:space="preserve">2.57903051376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57265496253967</t>
   </si>
   <si>
     <t xml:space="preserve">2.52483630180359</t>
@@ -2384,40 +2384,40 @@
     <t xml:space="preserve">2.59178256988525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61887979507446</t>
+    <t xml:space="preserve">2.61887955665588</t>
   </si>
   <si>
     <t xml:space="preserve">2.56149697303772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47542357444763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46267151832581</t>
+    <t xml:space="preserve">2.47542333602905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46267175674438</t>
   </si>
   <si>
     <t xml:space="preserve">2.51367855072021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50092649459839</t>
+    <t xml:space="preserve">2.50092673301697</t>
   </si>
   <si>
     <t xml:space="preserve">2.55352759361267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54874539375305</t>
+    <t xml:space="preserve">2.54874563217163</t>
   </si>
   <si>
     <t xml:space="preserve">2.65713500976562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66032290458679</t>
+    <t xml:space="preserve">2.66032266616821</t>
   </si>
   <si>
     <t xml:space="preserve">2.85159826278687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85637998580933</t>
+    <t xml:space="preserve">2.85638022422791</t>
   </si>
   <si>
     <t xml:space="preserve">2.81653094291687</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">2.77668213844299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67785668373108</t>
+    <t xml:space="preserve">2.6778564453125</t>
   </si>
   <si>
     <t xml:space="preserve">2.80218553543091</t>
@@ -2435,10 +2435,10 @@
     <t xml:space="preserve">2.78943395614624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77030611038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75755453109741</t>
+    <t xml:space="preserve">2.77030634880066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75755476951599</t>
   </si>
   <si>
     <t xml:space="preserve">2.75436663627625</t>
@@ -2447,28 +2447,28 @@
     <t xml:space="preserve">2.68901419639587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63800764083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70335984230042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70017194747925</t>
+    <t xml:space="preserve">2.63800740242004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70335936546326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70017170906067</t>
   </si>
   <si>
     <t xml:space="preserve">2.72567534446716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74209475517273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69940376281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71418166160583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64193487167358</t>
+    <t xml:space="preserve">2.74209499359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69940400123596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71418142318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.641934633255</t>
   </si>
   <si>
     <t xml:space="preserve">2.63372492790222</t>
@@ -2480,28 +2480,28 @@
     <t xml:space="preserve">2.63865065574646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65014481544495</t>
+    <t xml:space="preserve">2.65014457702637</t>
   </si>
   <si>
     <t xml:space="preserve">2.69447803497314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7306010723114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73388504981995</t>
+    <t xml:space="preserve">2.73060131072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73388528823853</t>
   </si>
   <si>
     <t xml:space="preserve">2.73552703857422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76508283615112</t>
+    <t xml:space="preserve">2.76508235931396</t>
   </si>
   <si>
     <t xml:space="preserve">2.66163849830627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61894726753235</t>
+    <t xml:space="preserve">2.61894702911377</t>
   </si>
   <si>
     <t xml:space="preserve">2.63536667823792</t>
@@ -2519,7 +2519,7 @@
     <t xml:space="preserve">2.61073732376099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60252714157104</t>
+    <t xml:space="preserve">2.60252737998962</t>
   </si>
   <si>
     <t xml:space="preserve">2.59595918655396</t>
@@ -2537,52 +2537,52 @@
     <t xml:space="preserve">2.78642845153809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77657651901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75851511955261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66656422615051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70925569534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68298363685608</t>
+    <t xml:space="preserve">2.77657675743103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75851464271545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66656446456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7092559337616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68298387527466</t>
   </si>
   <si>
     <t xml:space="preserve">2.66328024864197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75030469894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72239136695862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64686036109924</t>
+    <t xml:space="preserve">2.75030493736267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72239112854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64686059951782</t>
   </si>
   <si>
     <t xml:space="preserve">2.62715697288513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62879872322083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61566305160522</t>
+    <t xml:space="preserve">2.62879920005798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6156632900238</t>
   </si>
   <si>
     <t xml:space="preserve">2.69283580780029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59760165214539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64850282669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64029288291931</t>
+    <t xml:space="preserve">2.59760141372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64850258827209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64029264450073</t>
   </si>
   <si>
     <t xml:space="preserve">2.68134212493896</t>
@@ -2597,31 +2597,31 @@
     <t xml:space="preserve">2.69776177406311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71253943443298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63700866699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62387323379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60745334625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64521837234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63044118881226</t>
+    <t xml:space="preserve">2.71253967285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63700890541077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62387299537659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60745358467102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64521861076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63044095039368</t>
   </si>
   <si>
     <t xml:space="preserve">2.54998421669006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55819368362427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54505801200867</t>
+    <t xml:space="preserve">2.55819392204285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54505848884583</t>
   </si>
   <si>
     <t xml:space="preserve">2.51386070251465</t>
@@ -2630,13 +2630,13 @@
     <t xml:space="preserve">2.52042865753174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5023672580719</t>
+    <t xml:space="preserve">2.50236701965332</t>
   </si>
   <si>
     <t xml:space="preserve">2.47281169891357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42191052436829</t>
+    <t xml:space="preserve">2.42191028594971</t>
   </si>
   <si>
     <t xml:space="preserve">2.44325613975525</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">2.35951542854309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38414478302002</t>
+    <t xml:space="preserve">2.3841450214386</t>
   </si>
   <si>
     <t xml:space="preserve">2.41205859184265</t>
@@ -2657,19 +2657,19 @@
     <t xml:space="preserve">2.39563870429993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37593483924866</t>
+    <t xml:space="preserve">2.37593507766724</t>
   </si>
   <si>
     <t xml:space="preserve">2.37757682800293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31518220901489</t>
+    <t xml:space="preserve">2.31518197059631</t>
   </si>
   <si>
     <t xml:space="preserve">2.29219460487366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2347252368927</t>
+    <t xml:space="preserve">2.23472499847412</t>
   </si>
   <si>
     <t xml:space="preserve">2.19696021080017</t>
@@ -2681,22 +2681,22 @@
     <t xml:space="preserve">2.23636722564697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25442910194397</t>
+    <t xml:space="preserve">2.25442934036255</t>
   </si>
   <si>
     <t xml:space="preserve">2.3102560043335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30533051490784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28070044517517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.454749584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42519426345825</t>
+    <t xml:space="preserve">2.30533027648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28070068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45474982261658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42519450187683</t>
   </si>
   <si>
     <t xml:space="preserve">2.44982385635376</t>
@@ -2705,19 +2705,19 @@
     <t xml:space="preserve">2.49251508712769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47937941551208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56147813796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50893497467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49579906463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50400876998901</t>
+    <t xml:space="preserve">2.47937917709351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56147766113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50893473625183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49579882621765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50400900840759</t>
   </si>
   <si>
     <t xml:space="preserve">2.48102140426636</t>
@@ -2726,13 +2726,13 @@
     <t xml:space="preserve">2.47609543800354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52207064628601</t>
+    <t xml:space="preserve">2.52207040786743</t>
   </si>
   <si>
     <t xml:space="preserve">2.53520655632019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51221871376038</t>
+    <t xml:space="preserve">2.51221895217896</t>
   </si>
   <si>
     <t xml:space="preserve">2.47116947174072</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">2.43997192382812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46788549423218</t>
+    <t xml:space="preserve">2.46788573265076</t>
   </si>
   <si>
     <t xml:space="preserve">2.44489789009094</t>
@@ -2753,7 +2753,7 @@
     <t xml:space="preserve">2.41534233093262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38907074928284</t>
+    <t xml:space="preserve">2.38907098770142</t>
   </si>
   <si>
     <t xml:space="preserve">2.36444139480591</t>
@@ -2762,58 +2762,58 @@
     <t xml:space="preserve">2.39399671554565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36608338356018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40384840965271</t>
+    <t xml:space="preserve">2.3660831451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40384864807129</t>
   </si>
   <si>
     <t xml:space="preserve">2.45146584510803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33981132507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38742876052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4531078338623</t>
+    <t xml:space="preserve">2.33981156349182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38742899894714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45310759544373</t>
   </si>
   <si>
     <t xml:space="preserve">2.45967578887939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44653987884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50565099716187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44161367416382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49087309837341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4859471321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59431743621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54177451133728</t>
+    <t xml:space="preserve">2.44654011726379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50565123558044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44161415100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49087285995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48594760894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59431767463684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5417742729187</t>
   </si>
   <si>
     <t xml:space="preserve">2.38086128234863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33652782440186</t>
+    <t xml:space="preserve">2.33652758598328</t>
   </si>
   <si>
     <t xml:space="preserve">2.35787320137024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36772513389587</t>
+    <t xml:space="preserve">2.36772537231445</t>
   </si>
   <si>
     <t xml:space="preserve">2.32995986938477</t>
@@ -2822,10 +2822,10 @@
     <t xml:space="preserve">2.46952748298645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49415707588196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55326819419861</t>
+    <t xml:space="preserve">2.49415731430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55326795578003</t>
   </si>
   <si>
     <t xml:space="preserve">2.51057696342468</t>
@@ -2837,25 +2837,25 @@
     <t xml:space="preserve">2.55491018295288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58939146995544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5467004776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53684830665588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52535462379456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43176221847534</t>
+    <t xml:space="preserve">2.58939170837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54670023918152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53684854507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52535486221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43176198005676</t>
   </si>
   <si>
     <t xml:space="preserve">2.4022068977356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52863836288452</t>
+    <t xml:space="preserve">2.5286386013031</t>
   </si>
   <si>
     <t xml:space="preserve">2.56311988830566</t>
@@ -2864,16 +2864,16 @@
     <t xml:space="preserve">2.56968808174133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6041693687439</t>
+    <t xml:space="preserve">2.60416913032532</t>
   </si>
   <si>
     <t xml:space="preserve">2.71582365036011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68216300010681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72895956039429</t>
+    <t xml:space="preserve">2.68216276168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72895932197571</t>
   </si>
   <si>
     <t xml:space="preserve">2.70843482017517</t>
@@ -2882,49 +2882,49 @@
     <t xml:space="preserve">2.69611978530884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71171832084656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73224329948425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76918768882751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76097774505615</t>
+    <t xml:space="preserve">2.71171855926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73224353790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76918745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76097750663757</t>
   </si>
   <si>
     <t xml:space="preserve">2.75440979003906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75523066520691</t>
+    <t xml:space="preserve">2.75523114204407</t>
   </si>
   <si>
     <t xml:space="preserve">2.75605177879333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74620008468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79381704330444</t>
+    <t xml:space="preserve">2.7461998462677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79381728172302</t>
   </si>
   <si>
     <t xml:space="preserve">2.76261973381042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7667248249054</t>
+    <t xml:space="preserve">2.76672434806824</t>
   </si>
   <si>
     <t xml:space="preserve">2.79710149765015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83815050125122</t>
+    <t xml:space="preserve">2.8381507396698</t>
   </si>
   <si>
     <t xml:space="preserve">2.77082967758179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77247166633606</t>
+    <t xml:space="preserve">2.77247190475464</t>
   </si>
   <si>
     <t xml:space="preserve">2.7642617225647</t>
@@ -2939,22 +2939,22 @@
     <t xml:space="preserve">2.82255172729492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86031699180603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87837862968445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88330507278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88740968704224</t>
+    <t xml:space="preserve">2.86031723022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87837886810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88330459594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88740944862366</t>
   </si>
   <si>
     <t xml:space="preserve">2.88248372077942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86524295806885</t>
+    <t xml:space="preserve">2.86524319648743</t>
   </si>
   <si>
     <t xml:space="preserve">2.86113810539246</t>
@@ -2969,16 +2969,16 @@
     <t xml:space="preserve">2.87427377700806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89726161956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93256378173828</t>
+    <t xml:space="preserve">2.89726185798645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93256402015686</t>
   </si>
   <si>
     <t xml:space="preserve">2.95883560180664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97197127342224</t>
+    <t xml:space="preserve">2.97197103500366</t>
   </si>
   <si>
     <t xml:space="preserve">3.02533531188965</t>
@@ -2987,25 +2987,25 @@
     <t xml:space="preserve">3.00481081008911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00809502601624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04093408584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01794672012329</t>
+    <t xml:space="preserve">3.00809478759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04093432426453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01794648170471</t>
   </si>
   <si>
     <t xml:space="preserve">3.04586005210876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02123045921326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00727367401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98921203613281</t>
+    <t xml:space="preserve">3.02123069763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00727391242981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98921179771423</t>
   </si>
   <si>
     <t xml:space="preserve">2.95801448822021</t>
@@ -3017,19 +3017,19 @@
     <t xml:space="preserve">2.92353320121765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8956196308136</t>
+    <t xml:space="preserve">2.89561939239502</t>
   </si>
   <si>
     <t xml:space="preserve">2.8906934261322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89151477813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8668851852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89479851722717</t>
+    <t xml:space="preserve">2.89151453971863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86688494682312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89479875564575</t>
   </si>
   <si>
     <t xml:space="preserve">2.90920472145081</t>
@@ -3038,13 +3038,13 @@
     <t xml:space="preserve">2.89649343490601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96005034446716</t>
+    <t xml:space="preserve">2.96005058288574</t>
   </si>
   <si>
     <t xml:space="preserve">2.86598634719849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86429166793823</t>
+    <t xml:space="preserve">2.86429142951965</t>
   </si>
   <si>
     <t xml:space="preserve">2.93208527565002</t>
@@ -3059,16 +3059,16 @@
     <t xml:space="preserve">2.89564609527588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92615342140198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84225821495056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85073256492615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94733905792236</t>
+    <t xml:space="preserve">2.9261531829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84225845336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85073280334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94733881950378</t>
   </si>
   <si>
     <t xml:space="preserve">2.9998791217804</t>
@@ -3080,10 +3080,10 @@
     <t xml:space="preserve">2.99055743217468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03292846679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0642831325531</t>
+    <t xml:space="preserve">3.03292870521545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06428337097168</t>
   </si>
   <si>
     <t xml:space="preserve">3.04055571556091</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">3.04479241371155</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02275919914246</t>
+    <t xml:space="preserve">3.02275943756104</t>
   </si>
   <si>
     <t xml:space="preserve">3.01004838943481</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">3.00157403945923</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02021741867065</t>
+    <t xml:space="preserve">3.02021718025208</t>
   </si>
   <si>
     <t xml:space="preserve">3.04648733139038</t>
@@ -3113,28 +3113,28 @@
     <t xml:space="preserve">3.08546876907349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09733271598816</t>
+    <t xml:space="preserve">3.09733295440674</t>
   </si>
   <si>
     <t xml:space="preserve">3.13122987747192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14563584327698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15665245056152</t>
+    <t xml:space="preserve">3.14563608169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15665221214294</t>
   </si>
   <si>
     <t xml:space="preserve">3.18038034439087</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19648122787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18546485900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18715953826904</t>
+    <t xml:space="preserve">3.19648146629333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18546509742737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18715977668762</t>
   </si>
   <si>
     <t xml:space="preserve">3.16682147979736</t>
@@ -3149,10 +3149,10 @@
     <t xml:space="preserve">3.11597609519958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11089181900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10411214828491</t>
+    <t xml:space="preserve">3.11089134216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10411238670349</t>
   </si>
   <si>
     <t xml:space="preserve">3.13716149330139</t>
@@ -3167,13 +3167,13 @@
     <t xml:space="preserve">3.1252977848053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08123183250427</t>
+    <t xml:space="preserve">3.08123159408569</t>
   </si>
   <si>
     <t xml:space="preserve">3.03631830215454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07360482215881</t>
+    <t xml:space="preserve">3.07360529899597</t>
   </si>
   <si>
     <t xml:space="preserve">3.09902787208557</t>
@@ -3200,10 +3200,10 @@
     <t xml:space="preserve">3.02360701560974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9744565486908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01428508758545</t>
+    <t xml:space="preserve">2.97445631027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01428532600403</t>
   </si>
   <si>
     <t xml:space="preserve">2.99648952484131</t>
@@ -3218,16 +3218,16 @@
     <t xml:space="preserve">3.00411605834961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96089744567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98547291755676</t>
+    <t xml:space="preserve">2.96089768409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98547315597534</t>
   </si>
   <si>
     <t xml:space="preserve">2.91089963912964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87785029411316</t>
+    <t xml:space="preserve">2.87785005569458</t>
   </si>
   <si>
     <t xml:space="preserve">2.91174721717834</t>
@@ -3236,16 +3236,16 @@
     <t xml:space="preserve">2.94564414024353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97530364990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95327067375183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92445850372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94394898414612</t>
+    <t xml:space="preserve">2.97530388832092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95327091217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92445826530457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9439492225647</t>
   </si>
   <si>
     <t xml:space="preserve">3.00242114067078</t>
@@ -3260,10 +3260,10 @@
     <t xml:space="preserve">3.01767516136169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05241918563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99733686447144</t>
+    <t xml:space="preserve">3.05241942405701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99733662605286</t>
   </si>
   <si>
     <t xml:space="preserve">3.0125904083252</t>
@@ -3272,13 +3272,13 @@
     <t xml:space="preserve">2.99479460716248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03462362289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11258625984192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09309554100037</t>
+    <t xml:space="preserve">3.03462338447571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1125864982605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09309601783752</t>
   </si>
   <si>
     <t xml:space="preserve">3.0566565990448</t>
@@ -3290,37 +3290,37 @@
     <t xml:space="preserve">3.05750393867493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0693678855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07275724411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03208112716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02953910827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00072646141052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85581707954407</t>
+    <t xml:space="preserve">3.06936764717102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07275748252869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03208136558533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02953886985779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0007266998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85581684112549</t>
   </si>
   <si>
     <t xml:space="preserve">2.87022352218628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88547706604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95750784873962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88971376419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02530169487</t>
+    <t xml:space="preserve">2.88547682762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9575080871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88971424102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02530193328857</t>
   </si>
   <si>
     <t xml:space="preserve">2.9820830821991</t>
@@ -3329,13 +3329,13 @@
     <t xml:space="preserve">3.0083532333374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97869372367859</t>
+    <t xml:space="preserve">2.97869348526001</t>
   </si>
   <si>
     <t xml:space="preserve">3.00326871871948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02445435523987</t>
+    <t xml:space="preserve">3.02445459365845</t>
   </si>
   <si>
     <t xml:space="preserve">3.04563999176025</t>
@@ -3344,10 +3344,10 @@
     <t xml:space="preserve">3.05072450637817</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06089377403259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11682343482971</t>
+    <t xml:space="preserve">3.06089353561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11682367324829</t>
   </si>
   <si>
     <t xml:space="preserve">3.10241723060608</t>
@@ -3356,67 +3356,67 @@
     <t xml:space="preserve">3.14055156707764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11173915863037</t>
+    <t xml:space="preserve">3.11173868179321</t>
   </si>
   <si>
     <t xml:space="preserve">3.08716344833374</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02699661254883</t>
+    <t xml:space="preserve">3.02699685096741</t>
   </si>
   <si>
     <t xml:space="preserve">3.0134379863739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99394702911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97106647491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98123550415039</t>
+    <t xml:space="preserve">2.99394726753235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97106695175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98123574256897</t>
   </si>
   <si>
     <t xml:space="preserve">2.94903373718262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90835738182068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91767930984497</t>
+    <t xml:space="preserve">2.9083571434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91767907142639</t>
   </si>
   <si>
     <t xml:space="preserve">2.97360897064209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07614755630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14817810058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1337718963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07021546363831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93886470794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88039231300354</t>
+    <t xml:space="preserve">3.07614731788635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14817786216736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13377213478088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07021498680115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9388644695282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88039255142212</t>
   </si>
   <si>
     <t xml:space="preserve">2.9185266494751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93801736831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92530584335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86005425453186</t>
+    <t xml:space="preserve">2.93801712989807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92530560493469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86005401611328</t>
   </si>
   <si>
     <t xml:space="preserve">2.88717198371887</t>
@@ -3425,7 +3425,7 @@
     <t xml:space="preserve">2.87276577949524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84310579299927</t>
+    <t xml:space="preserve">2.84310555458069</t>
   </si>
   <si>
     <t xml:space="preserve">2.83802127838135</t>
@@ -3437,7 +3437,7 @@
     <t xml:space="preserve">2.80836129188538</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82446241378784</t>
+    <t xml:space="preserve">2.82446265220642</t>
   </si>
   <si>
     <t xml:space="preserve">2.740567445755</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">2.78971815109253</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7626006603241</t>
+    <t xml:space="preserve">2.76260042190552</t>
   </si>
   <si>
     <t xml:space="preserve">2.69904351234436</t>
@@ -3464,16 +3464,16 @@
     <t xml:space="preserve">2.77446460723877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87700295448303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86344385147095</t>
+    <t xml:space="preserve">2.87700271606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86344408988953</t>
   </si>
   <si>
     <t xml:space="preserve">2.85666465759277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85158014297485</t>
+    <t xml:space="preserve">2.85157990455627</t>
   </si>
   <si>
     <t xml:space="preserve">2.81937766075134</t>
@@ -3491,7 +3491,7 @@
     <t xml:space="preserve">2.75666880607605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.814293384552</t>
+    <t xml:space="preserve">2.81429362297058</t>
   </si>
   <si>
     <t xml:space="preserve">2.82700490951538</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">3.00581097602844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04733490943909</t>
+    <t xml:space="preserve">3.04733467102051</t>
   </si>
   <si>
     <t xml:space="preserve">3.00496363639832</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">3.04394507408142</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05835127830505</t>
+    <t xml:space="preserve">3.05835151672363</t>
   </si>
   <si>
     <t xml:space="preserve">3.01598024368286</t>
@@ -3530,10 +3530,10 @@
     <t xml:space="preserve">3.04818224906921</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97276139259338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98377776145935</t>
+    <t xml:space="preserve">2.97276163101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98377823829651</t>
   </si>
   <si>
     <t xml:space="preserve">2.9524233341217</t>
@@ -3551,10 +3551,10 @@
     <t xml:space="preserve">2.86513876914978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92954301834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95072841644287</t>
+    <t xml:space="preserve">2.92954325675964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95072865486145</t>
   </si>
   <si>
     <t xml:space="preserve">3.03801321983337</t>
@@ -3563,10 +3563,10 @@
     <t xml:space="preserve">2.98801517486572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96598243713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89056158065796</t>
+    <t xml:space="preserve">2.96598196029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89056134223938</t>
   </si>
   <si>
     <t xml:space="preserve">2.86683344841003</t>
@@ -3578,13 +3578,13 @@
     <t xml:space="preserve">2.86174917221069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8371741771698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8388683795929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72700881958008</t>
+    <t xml:space="preserve">2.83717393875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83886861801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7270085811615</t>
   </si>
   <si>
     <t xml:space="preserve">2.53125405311584</t>
@@ -3593,13 +3593,13 @@
     <t xml:space="preserve">2.41685175895691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35668444633484</t>
+    <t xml:space="preserve">2.35668468475342</t>
   </si>
   <si>
     <t xml:space="preserve">2.45837545394897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38888692855835</t>
+    <t xml:space="preserve">2.38888669013977</t>
   </si>
   <si>
     <t xml:space="preserve">2.41769909858704</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">2.3823139667511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34250521659851</t>
+    <t xml:space="preserve">2.34250545501709</t>
   </si>
   <si>
     <t xml:space="preserve">2.32569718360901</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">2.46193051338196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46812295913696</t>
+    <t xml:space="preserve">2.46812319755554</t>
   </si>
   <si>
     <t xml:space="preserve">2.49908542633057</t>
@@ -3629,28 +3629,28 @@
     <t xml:space="preserve">2.47608494758606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44158434867859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48758482933044</t>
+    <t xml:space="preserve">2.44158411026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48758506774902</t>
   </si>
   <si>
     <t xml:space="preserve">2.48493123054504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41327595710754</t>
+    <t xml:space="preserve">2.41327619552612</t>
   </si>
   <si>
     <t xml:space="preserve">2.45750761032104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49112367630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47696924209595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45927691459656</t>
+    <t xml:space="preserve">2.49112343788147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47696948051453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45927667617798</t>
   </si>
   <si>
     <t xml:space="preserve">2.37523674964905</t>
@@ -3665,7 +3665,7 @@
     <t xml:space="preserve">2.38673686981201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41150689125061</t>
+    <t xml:space="preserve">2.41150665283203</t>
   </si>
   <si>
     <t xml:space="preserve">2.38319849967957</t>
@@ -3686,7 +3686,7 @@
     <t xml:space="preserve">2.43008399009705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44689202308655</t>
+    <t xml:space="preserve">2.44689226150513</t>
   </si>
   <si>
     <t xml:space="preserve">2.50970077514648</t>
@@ -3698,22 +3698,22 @@
     <t xml:space="preserve">2.47077679634094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44246864318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43981504440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4433536529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46900773048401</t>
+    <t xml:space="preserve">2.44246888160706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4398148059845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44335341453552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46900749206543</t>
   </si>
   <si>
     <t xml:space="preserve">2.47520017623901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44954586029053</t>
+    <t xml:space="preserve">2.44954609870911</t>
   </si>
   <si>
     <t xml:space="preserve">2.43804574012756</t>
@@ -3725,13 +3725,13 @@
     <t xml:space="preserve">2.42300701141357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40442967414856</t>
+    <t xml:space="preserve">2.40442991256714</t>
   </si>
   <si>
     <t xml:space="preserve">2.36904430389404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29650473594666</t>
+    <t xml:space="preserve">2.29650449752808</t>
   </si>
   <si>
     <t xml:space="preserve">2.35312104225159</t>
@@ -3740,16 +3740,16 @@
     <t xml:space="preserve">2.21158003807068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21246433258057</t>
+    <t xml:space="preserve">2.21246457099915</t>
   </si>
   <si>
     <t xml:space="preserve">2.24342656135559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18504095077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07269263267517</t>
+    <t xml:space="preserve">2.18504118919373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07269239425659</t>
   </si>
   <si>
     <t xml:space="preserve">2.12842440605164</t>
@@ -3776,16 +3776,16 @@
     <t xml:space="preserve">2.11957812309265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10630869865417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07800030708313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07357716560364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04261541366577</t>
+    <t xml:space="preserve">2.1063084602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07800054550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07357740402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04261517524719</t>
   </si>
   <si>
     <t xml:space="preserve">1.97803711891174</t>
@@ -3800,40 +3800,40 @@
     <t xml:space="preserve">1.9258439540863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91611266136169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93380570411682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94442105293274</t>
+    <t xml:space="preserve">1.91611289978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93380546569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94442081451416</t>
   </si>
   <si>
     <t xml:space="preserve">2.00192213058472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90018951892853</t>
+    <t xml:space="preserve">1.90018939971924</t>
   </si>
   <si>
     <t xml:space="preserve">1.84003448486328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82588016986847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87011218070984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80464911460876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77280235290527</t>
+    <t xml:space="preserve">1.82588028907776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87011206150055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80464923381805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77280247211456</t>
   </si>
   <si>
     <t xml:space="preserve">1.80022609233856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83030343055725</t>
+    <t xml:space="preserve">1.83030354976654</t>
   </si>
   <si>
     <t xml:space="preserve">1.87807369232178</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">1.88249695301056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86303472518921</t>
+    <t xml:space="preserve">1.8630348443985</t>
   </si>
   <si>
     <t xml:space="preserve">1.87541961669922</t>
@@ -3869,16 +3869,16 @@
     <t xml:space="preserve">2.14434790611267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14257884025574</t>
+    <t xml:space="preserve">2.14257860183716</t>
   </si>
   <si>
     <t xml:space="preserve">2.13196301460266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1779637336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19034886360168</t>
+    <t xml:space="preserve">2.17796397209167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19034862518311</t>
   </si>
   <si>
     <t xml:space="preserve">2.23281097412109</t>
@@ -3887,16 +3887,16 @@
     <t xml:space="preserve">2.27969646453857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30800461769104</t>
+    <t xml:space="preserve">2.30800485610962</t>
   </si>
   <si>
     <t xml:space="preserve">2.28058123588562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29915833473206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33454370498657</t>
+    <t xml:space="preserve">2.29915857315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33454346656799</t>
   </si>
   <si>
     <t xml:space="preserve">2.31773567199707</t>
@@ -3911,10 +3911,10 @@
     <t xml:space="preserve">2.32746648788452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30623555183411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34515929222107</t>
+    <t xml:space="preserve">2.30623579025269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34515953063965</t>
   </si>
   <si>
     <t xml:space="preserve">2.35046720504761</t>
@@ -3923,7 +3923,7 @@
     <t xml:space="preserve">2.33188962936401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34338998794556</t>
+    <t xml:space="preserve">2.34338974952698</t>
   </si>
   <si>
     <t xml:space="preserve">2.35400581359863</t>
@@ -3938,7 +3938,7 @@
     <t xml:space="preserve">2.37612152099609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4327380657196</t>
+    <t xml:space="preserve">2.43273782730103</t>
   </si>
   <si>
     <t xml:space="preserve">2.48050808906555</t>
@@ -3947,10 +3947,10 @@
     <t xml:space="preserve">2.50350832939148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44600749015808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31065845489502</t>
+    <t xml:space="preserve">2.4460072517395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3106586933136</t>
   </si>
   <si>
     <t xml:space="preserve">2.25669622421265</t>
@@ -3959,7 +3959,7 @@
     <t xml:space="preserve">2.2726194858551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26200413703918</t>
+    <t xml:space="preserve">2.26200389862061</t>
   </si>
   <si>
     <t xml:space="preserve">2.24165725708008</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">2.22838807106018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28765845298767</t>
+    <t xml:space="preserve">2.28765821456909</t>
   </si>
   <si>
     <t xml:space="preserve">2.2894275188446</t>
@@ -3992,22 +3992,22 @@
     <t xml:space="preserve">2.32304334640503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45043063163757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45131492614746</t>
+    <t xml:space="preserve">2.45043039321899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45131516456604</t>
   </si>
   <si>
     <t xml:space="preserve">2.42389154434204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42919921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40708374977112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34781336784363</t>
+    <t xml:space="preserve">2.42919945716858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40708351135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34781312942505</t>
   </si>
   <si>
     <t xml:space="preserve">2.3885064125061</t>
@@ -4022,7 +4022,7 @@
     <t xml:space="preserve">2.39646816253662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34692859649658</t>
+    <t xml:space="preserve">2.34692883491516</t>
   </si>
   <si>
     <t xml:space="preserve">2.340735912323</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">2.37081384658813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31596660614014</t>
+    <t xml:space="preserve">2.31596636772156</t>
   </si>
   <si>
     <t xml:space="preserve">2.28854274749756</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">2.30004286766052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29473543167114</t>
+    <t xml:space="preserve">2.29473567008972</t>
   </si>
   <si>
     <t xml:space="preserve">2.2664270401001</t>
@@ -4064,10 +4064,10 @@
     <t xml:space="preserve">2.22219562530518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23192620277405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1753101348877</t>
+    <t xml:space="preserve">2.23192644119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17530989646912</t>
   </si>
   <si>
     <t xml:space="preserve">2.19477200508118</t>
@@ -4076,7 +4076,7 @@
     <t xml:space="preserve">2.22573399543762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1815025806427</t>
+    <t xml:space="preserve">2.18150234222412</t>
   </si>
   <si>
     <t xml:space="preserve">2.15054035186768</t>
@@ -4100,13 +4100,13 @@
     <t xml:space="preserve">2.18857932090759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20627188682556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22131061553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20361804962158</t>
+    <t xml:space="preserve">2.20627212524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22131085395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20361828804016</t>
   </si>
   <si>
     <t xml:space="preserve">2.21423387527466</t>
@@ -4115,10 +4115,10 @@
     <t xml:space="preserve">2.24254202842712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30181217193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29827404022217</t>
+    <t xml:space="preserve">2.30181241035461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29827380180359</t>
   </si>
   <si>
     <t xml:space="preserve">2.40266036987305</t>
@@ -4142,10 +4142,10 @@
     <t xml:space="preserve">2.49820065498352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44512248039246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49643111228943</t>
+    <t xml:space="preserve">2.44512271881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49643135070801</t>
   </si>
   <si>
     <t xml:space="preserve">2.53181672096252</t>
@@ -4181,7 +4181,7 @@
     <t xml:space="preserve">2.63266491889954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62204885482788</t>
+    <t xml:space="preserve">2.62204909324646</t>
   </si>
   <si>
     <t xml:space="preserve">2.54950928688049</t>
@@ -4190,25 +4190,25 @@
     <t xml:space="preserve">2.5282781124115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57958650588989</t>
+    <t xml:space="preserve">2.57958674430847</t>
   </si>
   <si>
     <t xml:space="preserve">2.58135604858398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60966444015503</t>
+    <t xml:space="preserve">2.60966420173645</t>
   </si>
   <si>
     <t xml:space="preserve">2.58666396141052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59020233154297</t>
+    <t xml:space="preserve">2.59020256996155</t>
   </si>
   <si>
     <t xml:space="preserve">2.53889346122742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57250952720642</t>
+    <t xml:space="preserve">2.572509765625</t>
   </si>
   <si>
     <t xml:space="preserve">2.54420137405396</t>
@@ -4217,7 +4217,7 @@
     <t xml:space="preserve">2.55304765701294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56366324424744</t>
+    <t xml:space="preserve">2.56366348266602</t>
   </si>
   <si>
     <t xml:space="preserve">2.55127859115601</t>
@@ -4232,7 +4232,7 @@
     <t xml:space="preserve">2.51812791824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52922105789185</t>
+    <t xml:space="preserve">2.52922129631042</t>
   </si>
   <si>
     <t xml:space="preserve">2.53661632537842</t>
@@ -4259,16 +4259,16 @@
     <t xml:space="preserve">2.46451139450073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41274380683899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4090461730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42013931274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44787168502808</t>
+    <t xml:space="preserve">2.41274356842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40904593467712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42013907432556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44787192344666</t>
   </si>
   <si>
     <t xml:space="preserve">2.47375583648682</t>
@@ -4289,10 +4289,10 @@
     <t xml:space="preserve">2.52737212181091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54216313362122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53846526145935</t>
+    <t xml:space="preserve">2.54216289520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53846549987793</t>
   </si>
   <si>
     <t xml:space="preserve">2.58653521537781</t>
@@ -4301,7 +4301,7 @@
     <t xml:space="preserve">2.56250047683716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59393072128296</t>
+    <t xml:space="preserve">2.59393048286438</t>
   </si>
   <si>
     <t xml:space="preserve">2.63275647163391</t>
@@ -4316,10 +4316,10 @@
     <t xml:space="preserve">2.60132598876953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45711588859558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3998019695282</t>
+    <t xml:space="preserve">2.45711612701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39980173110962</t>
   </si>
   <si>
     <t xml:space="preserve">2.44602274894714</t>
@@ -4331,10 +4331,10 @@
     <t xml:space="preserve">2.47190690040588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47005796432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42383670806885</t>
+    <t xml:space="preserve">2.47005772590637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42383694648743</t>
   </si>
   <si>
     <t xml:space="preserve">2.38316226005554</t>
@@ -4346,34 +4346,34 @@
     <t xml:space="preserve">2.49594187736511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52182555198669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54031419754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55140733718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57913970947266</t>
+    <t xml:space="preserve">2.52182579040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5403139591217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55140709877014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57913994789124</t>
   </si>
   <si>
     <t xml:space="preserve">2.5680468082428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58468651771545</t>
+    <t xml:space="preserve">2.58468627929688</t>
   </si>
   <si>
     <t xml:space="preserve">2.57544207572937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54770946502686</t>
+    <t xml:space="preserve">2.54770970344543</t>
   </si>
   <si>
     <t xml:space="preserve">2.60687255859375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60317492485046</t>
+    <t xml:space="preserve">2.60317468643188</t>
   </si>
   <si>
     <t xml:space="preserve">2.6456983089447</t>
@@ -4397,7 +4397,7 @@
     <t xml:space="preserve">2.667884349823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69376850128174</t>
+    <t xml:space="preserve">2.69376826286316</t>
   </si>
   <si>
     <t xml:space="preserve">2.56434917449951</t>
@@ -4430,22 +4430,22 @@
     <t xml:space="preserve">2.35358071327209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39795303344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41089510917664</t>
+    <t xml:space="preserve">2.39795327186584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41089487075806</t>
   </si>
   <si>
     <t xml:space="preserve">2.42753434181213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40534830093384</t>
+    <t xml:space="preserve">2.40534853935242</t>
   </si>
   <si>
     <t xml:space="preserve">2.39240646362305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3720691204071</t>
+    <t xml:space="preserve">2.37206935882568</t>
   </si>
   <si>
     <t xml:space="preserve">2.34988307952881</t>
@@ -4460,7 +4460,7 @@
     <t xml:space="preserve">2.34803414344788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45341849327087</t>
+    <t xml:space="preserve">2.45341825485229</t>
   </si>
   <si>
     <t xml:space="preserve">2.49224424362183</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">2.49779057502747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46266269683838</t>
+    <t xml:space="preserve">2.4626624584198</t>
   </si>
   <si>
     <t xml:space="preserve">2.45526719093323</t>
@@ -4487,7 +4487,7 @@
     <t xml:space="preserve">2.62536096572876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64015197753906</t>
+    <t xml:space="preserve">2.64015173912048</t>
   </si>
   <si>
     <t xml:space="preserve">2.62720990180969</t>
@@ -4496,19 +4496,19 @@
     <t xml:space="preserve">2.63090753555298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68082666397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68637275695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68822169303894</t>
+    <t xml:space="preserve">2.68082642555237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68637299537659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68822193145752</t>
   </si>
   <si>
     <t xml:space="preserve">2.66603565216064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6826753616333</t>
+    <t xml:space="preserve">2.68267512321472</t>
   </si>
   <si>
     <t xml:space="preserve">2.68452405929565</t>
@@ -4517,19 +4517,19 @@
     <t xml:space="preserve">2.69007062911987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74368715286255</t>
+    <t xml:space="preserve">2.74368691444397</t>
   </si>
   <si>
     <t xml:space="preserve">2.71225690841675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69561696052551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73444294929504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80100154876709</t>
+    <t xml:space="preserve">2.69561719894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73444271087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80100131034851</t>
   </si>
   <si>
     <t xml:space="preserve">2.78990817070007</t>
@@ -4541,7 +4541,7 @@
     <t xml:space="preserve">2.79545474052429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78621053695679</t>
+    <t xml:space="preserve">2.78621077537537</t>
   </si>
   <si>
     <t xml:space="preserve">2.76772212982178</t>
@@ -4553,7 +4553,7 @@
     <t xml:space="preserve">2.75662922859192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73998928070068</t>
+    <t xml:space="preserve">2.73998951911926</t>
   </si>
   <si>
     <t xml:space="preserve">2.74738478660583</t>
@@ -4601,22 +4601,22 @@
     <t xml:space="preserve">2.98033928871155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96924614906311</t>
+    <t xml:space="preserve">2.96924638748169</t>
   </si>
   <si>
     <t xml:space="preserve">3.02286291122437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92672276496887</t>
+    <t xml:space="preserve">2.92672300338745</t>
   </si>
   <si>
     <t xml:space="preserve">2.91562986373901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87495517730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90083885192871</t>
+    <t xml:space="preserve">2.87495493888855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90083909034729</t>
   </si>
   <si>
     <t xml:space="preserve">2.9193274974823</t>
@@ -4643,7 +4643,7 @@
     <t xml:space="preserve">2.99513030052185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9877347946167</t>
+    <t xml:space="preserve">2.98773503303528</t>
   </si>
   <si>
     <t xml:space="preserve">2.98958349227905</t>
@@ -4652,16 +4652,16 @@
     <t xml:space="preserve">2.93411827087402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96000194549561</t>
+    <t xml:space="preserve">2.96000218391418</t>
   </si>
   <si>
     <t xml:space="preserve">2.94890904426575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95445585250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97849035263062</t>
+    <t xml:space="preserve">2.95445561408997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97849059104919</t>
   </si>
   <si>
     <t xml:space="preserve">2.95260691642761</t>
@@ -4685,10 +4685,10 @@
     <t xml:space="preserve">3.08572363853455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09496808052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11900281906128</t>
+    <t xml:space="preserve">3.09496784210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11900305747986</t>
   </si>
   <si>
     <t xml:space="preserve">3.05983972549438</t>
@@ -4706,13 +4706,13 @@
     <t xml:space="preserve">3.06908392906189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0247118473053</t>
+    <t xml:space="preserve">3.02471160888672</t>
   </si>
   <si>
     <t xml:space="preserve">3.01916527748108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97479295730591</t>
+    <t xml:space="preserve">2.97479271888733</t>
   </si>
   <si>
     <t xml:space="preserve">2.92302513122559</t>
@@ -4721,7 +4721,7 @@
     <t xml:space="preserve">2.93781590461731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88419938087463</t>
+    <t xml:space="preserve">2.88419914245605</t>
   </si>
   <si>
     <t xml:space="preserve">2.90823435783386</t>
@@ -4736,19 +4736,19 @@
     <t xml:space="preserve">2.95815324783325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97109508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01546764373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11345648765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13934016227722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10975861549377</t>
+    <t xml:space="preserve">2.97109532356262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01546740531921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11345624923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13933992385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10975885391235</t>
   </si>
   <si>
     <t xml:space="preserve">3.16337513923645</t>
@@ -4757,7 +4757,7 @@
     <t xml:space="preserve">3.13379383087158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15782856941223</t>
+    <t xml:space="preserve">3.15782833099365</t>
   </si>
   <si>
     <t xml:space="preserve">3.16892170906067</t>
@@ -4766,7 +4766,7 @@
     <t xml:space="preserve">3.19480562210083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24287533760071</t>
+    <t xml:space="preserve">3.24287557601929</t>
   </si>
   <si>
     <t xml:space="preserve">3.20959615707397</t>
@@ -4775,7 +4775,7 @@
     <t xml:space="preserve">3.20589852333069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23548030853271</t>
+    <t xml:space="preserve">3.23548007011414</t>
   </si>
   <si>
     <t xml:space="preserve">3.29464316368103</t>
@@ -4790,10 +4790,10 @@
     <t xml:space="preserve">3.20774745941162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17446827888489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12085151672363</t>
+    <t xml:space="preserve">3.17446804046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12085175514221</t>
   </si>
   <si>
     <t xml:space="preserve">3.07832813262939</t>
@@ -4805,7 +4805,7 @@
     <t xml:space="preserve">3.09866547584534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07647943496704</t>
+    <t xml:space="preserve">3.07647967338562</t>
   </si>
   <si>
     <t xml:space="preserve">3.06723523139954</t>
@@ -4820,19 +4820,19 @@
     <t xml:space="preserve">3.19665431976318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20405006408691</t>
+    <t xml:space="preserve">3.20404982566833</t>
   </si>
   <si>
     <t xml:space="preserve">3.19850325584412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12454962730408</t>
+    <t xml:space="preserve">3.1245493888855</t>
   </si>
   <si>
     <t xml:space="preserve">3.16707301139832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14858436584473</t>
+    <t xml:space="preserve">3.14858412742615</t>
   </si>
   <si>
     <t xml:space="preserve">3.00067663192749</t>
@@ -4841,7 +4841,7 @@
     <t xml:space="preserve">3.04874682426453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10051441192627</t>
+    <t xml:space="preserve">3.10051465034485</t>
   </si>
   <si>
     <t xml:space="preserve">3.14488673210144</t>
@@ -5736,6 +5736,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.14599990844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17999982833862</t>
   </si>
 </sst>
 </file>
@@ -72348,7 +72351,7 @@
     </row>
     <row r="2550">
       <c r="A2550" s="1" t="n">
-        <v>46036.69125</v>
+        <v>46036.3333333333</v>
       </c>
       <c r="B2550" t="n">
         <v>2679258</v>
@@ -72369,6 +72372,32 @@
         <v>1907</v>
       </c>
       <c r="H2550" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2551">
+      <c r="A2551" s="1" t="n">
+        <v>46037.6912847222</v>
+      </c>
+      <c r="B2551" t="n">
+        <v>2823838</v>
+      </c>
+      <c r="C2551" t="n">
+        <v>4.18800020217896</v>
+      </c>
+      <c r="D2551" t="n">
+        <v>4.13000011444092</v>
+      </c>
+      <c r="E2551" t="n">
+        <v>4.15000009536743</v>
+      </c>
+      <c r="F2551" t="n">
+        <v>4.17999982833862</v>
+      </c>
+      <c r="G2551" t="s">
+        <v>1908</v>
+      </c>
+      <c r="H2551" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HER.MI.xlsx
+++ b/data/HER.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1909" uniqueCount="1909">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1910" uniqueCount="1910">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,67 +47,67 @@
     <t xml:space="preserve">1.7089638710022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70616888999939</t>
+    <t xml:space="preserve">1.70616900920868</t>
   </si>
   <si>
     <t xml:space="preserve">1.71036100387573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68800365924835</t>
+    <t xml:space="preserve">1.68800330162048</t>
   </si>
   <si>
     <t xml:space="preserve">1.7257319688797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79140770435333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79420232772827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7704473733902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74669206142426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70337426662445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77324211597443</t>
+    <t xml:space="preserve">1.79140746593475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79420256614685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77044725418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74669229984283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70337438583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77324223518372</t>
   </si>
   <si>
     <t xml:space="preserve">1.74948692321777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76625537872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8053811788559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79001045227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80398380756378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83472549915314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81656002998352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80258643627167</t>
+    <t xml:space="preserve">1.76625514030457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80538129806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79001009464264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80398368835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83472585678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81655979156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80258619785309</t>
   </si>
   <si>
     <t xml:space="preserve">1.84869933128357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85568571090698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84031510353088</t>
+    <t xml:space="preserve">1.85568583011627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84031522274017</t>
   </si>
   <si>
     <t xml:space="preserve">1.82354652881622</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">1.82913613319397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72852647304535</t>
+    <t xml:space="preserve">1.72852683067322</t>
   </si>
   <si>
     <t xml:space="preserve">1.74110293388367</t>
@@ -125,103 +125,103 @@
     <t xml:space="preserve">1.75926828384399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69918215274811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75507640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79559981822968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78302347660065</t>
+    <t xml:space="preserve">1.6991822719574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75507652759552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7955995798111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78302359580994</t>
   </si>
   <si>
     <t xml:space="preserve">1.77603673934937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79839444160461</t>
+    <t xml:space="preserve">1.79839420318604</t>
   </si>
   <si>
     <t xml:space="preserve">1.80118930339813</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82075190544128</t>
+    <t xml:space="preserve">1.82075214385986</t>
   </si>
   <si>
     <t xml:space="preserve">1.83053338527679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78861260414124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76485800743103</t>
+    <t xml:space="preserve">1.78861284255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76485764980316</t>
   </si>
   <si>
     <t xml:space="preserve">1.74529492855072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73970544338226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72992384433746</t>
+    <t xml:space="preserve">1.73970568180084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72992444038391</t>
   </si>
   <si>
     <t xml:space="preserve">1.74389779567719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73271894454956</t>
+    <t xml:space="preserve">1.73271882534027</t>
   </si>
   <si>
     <t xml:space="preserve">1.76346051692963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77883124351501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76066601276398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77463960647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79699718952179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83752059936523</t>
+    <t xml:space="preserve">1.77883148193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76066589355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77463948726654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79699695110321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83752036094666</t>
   </si>
   <si>
     <t xml:space="preserve">1.81097066402435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85708367824554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84310960769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76765239238739</t>
+    <t xml:space="preserve">1.85708332061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84310972690582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76765251159668</t>
   </si>
   <si>
     <t xml:space="preserve">1.78162622451782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78721559047699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77743399143219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78022909164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80817592144012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80957317352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79280483722687</t>
+    <t xml:space="preserve">1.7872154712677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7774338722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78022885322571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80817604064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80957305431366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79280471801758</t>
   </si>
   <si>
     <t xml:space="preserve">1.78442096710205</t>
@@ -230,49 +230,49 @@
     <t xml:space="preserve">1.75647377967834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74808979034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82634139060974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84590458869934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83193099498749</t>
+    <t xml:space="preserve">1.74808967113495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82634150981903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84590482711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8319308757782</t>
   </si>
   <si>
     <t xml:space="preserve">1.84450733661652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82214975357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8333283662796</t>
+    <t xml:space="preserve">1.82214939594269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83332824707031</t>
   </si>
   <si>
     <t xml:space="preserve">1.82494401931763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81376504898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76206350326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73132145404816</t>
+    <t xml:space="preserve">1.81376516819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76206314563751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73132133483887</t>
   </si>
   <si>
     <t xml:space="preserve">1.74250030517578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71175849437714</t>
+    <t xml:space="preserve">1.71175837516785</t>
   </si>
   <si>
     <t xml:space="preserve">1.75751030445099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77344822883606</t>
+    <t xml:space="preserve">1.77344834804535</t>
   </si>
   <si>
     <t xml:space="preserve">1.7401237487793</t>
@@ -281,103 +281,100 @@
     <t xml:space="preserve">1.75895941257477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70390093326569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67347407341003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70969676971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73867475986481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78069269657135</t>
+    <t xml:space="preserve">1.70390129089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67347431182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70969665050507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73867499828339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78069293498993</t>
   </si>
   <si>
     <t xml:space="preserve">1.83430194854736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8082218170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81111919879913</t>
+    <t xml:space="preserve">1.80822157859802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81111991405487</t>
   </si>
   <si>
     <t xml:space="preserve">1.78503954410553</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77924370765686</t>
+    <t xml:space="preserve">1.77924382686615</t>
   </si>
   <si>
     <t xml:space="preserve">1.72708368301392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76040828227997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74591946601868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77055037021637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76620352268219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76185691356659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76910150051117</t>
+    <t xml:space="preserve">1.76040804386139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74591910839081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77055060863495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76620376110077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76185715198517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76910138130188</t>
   </si>
   <si>
     <t xml:space="preserve">1.77489721775055</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78359019756317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83719980716705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85748410224915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85023963451385</t>
+    <t xml:space="preserve">1.78359031677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83719968795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85748398303986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85023939609528</t>
   </si>
   <si>
     <t xml:space="preserve">1.83575069904327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86617732048035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83140408992767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84444391727448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79663074016571</t>
+    <t xml:space="preserve">1.8661777973175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83140397071838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84444415569305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79663062095642</t>
   </si>
   <si>
     <t xml:space="preserve">1.81981289386749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81256854534149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74881708621979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7444703578949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76765251159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77634608745575</t>
+    <t xml:space="preserve">1.81256830692291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7488169670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74447023868561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77634584903717</t>
   </si>
   <si>
     <t xml:space="preserve">1.79083490371704</t>
@@ -386,28 +383,28 @@
     <t xml:space="preserve">1.79952836036682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78648865222931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78938591480255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81546604633331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75606155395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73577690124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70679891109467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73722589015961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75461280345917</t>
+    <t xml:space="preserve">1.78648829460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78938603401184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8154661655426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75606119632721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73577702045441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70679903030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73722577095032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75461268424988</t>
   </si>
   <si>
     <t xml:space="preserve">1.71114563941956</t>
@@ -419,58 +416,58 @@
     <t xml:space="preserve">1.70245230197906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69231021404266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71694111824036</t>
+    <t xml:space="preserve">1.69231009483337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71694099903107</t>
   </si>
   <si>
     <t xml:space="preserve">1.69665682315826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63145649433136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60537648200989</t>
+    <t xml:space="preserve">1.63145673274994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60537660121918</t>
   </si>
   <si>
     <t xml:space="preserve">1.59233629703522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57929623126984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60102951526642</t>
+    <t xml:space="preserve">1.57929646968842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60102927684784</t>
   </si>
   <si>
     <t xml:space="preserve">1.6097229719162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61406981945038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62131416797638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63290524482727</t>
+    <t xml:space="preserve">1.61406946182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62131404876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63290512561798</t>
   </si>
   <si>
     <t xml:space="preserve">1.61841630935669</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63870108127594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63725209236145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65029203891754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62276315689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61551868915558</t>
+    <t xml:space="preserve">1.63870096206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63725197315216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65029227733612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62276303768158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61551856994629</t>
   </si>
   <si>
     <t xml:space="preserve">1.61696743965149</t>
@@ -479,85 +476,85 @@
     <t xml:space="preserve">1.62566089630127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66188335418701</t>
+    <t xml:space="preserve">1.66188323497772</t>
   </si>
   <si>
     <t xml:space="preserve">1.66912746429443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68796360492706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.593785405159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56625592708588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56335854530334</t>
+    <t xml:space="preserve">1.68796372413635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59378528594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56625604629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56335842609406</t>
   </si>
   <si>
     <t xml:space="preserve">1.54307389259338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4604868888855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46338438987732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44599783420563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44527339935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45034456253052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43005979061127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42209088802338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39601099491119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3945620059967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40905106067657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41267335414886</t>
+    <t xml:space="preserve">1.46048676967621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4633846282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44599795341492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44527316093445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45034468173981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43005990982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42209112644196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39601111412048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39456212520599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40905094146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41267323493958</t>
   </si>
   <si>
     <t xml:space="preserve">1.39818429946899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40180635452271</t>
+    <t xml:space="preserve">1.40180647373199</t>
   </si>
   <si>
     <t xml:space="preserve">1.40542876720428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41629552841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38152194023132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35906422138214</t>
+    <t xml:space="preserve">1.41629564762115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38152182102203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35906410217285</t>
   </si>
   <si>
     <t xml:space="preserve">1.37717533111572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43875324726105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48077142238617</t>
+    <t xml:space="preserve">1.43875336647034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48077118396759</t>
   </si>
   <si>
     <t xml:space="preserve">1.49236249923706</t>
@@ -566,13 +563,13 @@
     <t xml:space="preserve">1.48511803150177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5329315662384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52713596820831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50105571746826</t>
+    <t xml:space="preserve">1.53293144702911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5271360874176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50105583667755</t>
   </si>
   <si>
     <t xml:space="preserve">1.50685131549835</t>
@@ -581,181 +578,181 @@
     <t xml:space="preserve">1.54886949062347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55756282806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57060265541077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59088718891144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56915378570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58798968791962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60827398300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59668290615082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59958064556122</t>
+    <t xml:space="preserve">1.55756270885468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57060277462006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59088742733002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56915390491486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58798944950104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60827434062958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59668302536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5995808839798</t>
   </si>
   <si>
     <t xml:space="preserve">1.56480741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65174102783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64159870147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65318977832794</t>
+    <t xml:space="preserve">1.65174114704132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64159882068634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65318989753723</t>
   </si>
   <si>
     <t xml:space="preserve">1.65463852882385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65898537635803</t>
+    <t xml:space="preserve">1.65898525714874</t>
   </si>
   <si>
     <t xml:space="preserve">1.64014983177185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64304733276367</t>
+    <t xml:space="preserve">1.64304745197296</t>
   </si>
   <si>
     <t xml:space="preserve">1.57494962215424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57784748077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5517669916153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58654057979584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63000738620758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68216788768768</t>
+    <t xml:space="preserve">1.57784724235535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55176734924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58654081821442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63000750541687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68216800689697</t>
   </si>
   <si>
     <t xml:space="preserve">1.66622996330261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6778210401535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69086122512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69375884532928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69810581207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69520783424377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71404361724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72998118400574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73432815074921</t>
+    <t xml:space="preserve">1.67782115936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69086134433746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69375920295715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69810569286346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69520807266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71404373645782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72998142242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7343282699585</t>
   </si>
   <si>
     <t xml:space="preserve">1.71983909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72418594360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71549224853516</t>
+    <t xml:space="preserve">1.72418582439423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71549236774445</t>
   </si>
   <si>
     <t xml:space="preserve">1.71839022636414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74157249927521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78214144706726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78793728351593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81401717662811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82995533943176</t>
+    <t xml:space="preserve">1.74157226085663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78214168548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78793692588806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8140172958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82995522022247</t>
   </si>
   <si>
     <t xml:space="preserve">1.86907541751862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89950215816498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91399109363556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91543996334076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88066625595093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87197303771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88936007022858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90095126628876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90529787540436</t>
+    <t xml:space="preserve">1.89950203895569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91399121284485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91544020175934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88066649436951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87197327613831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88936018943787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90095114707947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90529775619507</t>
   </si>
   <si>
     <t xml:space="preserve">1.91254258155823</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94441795349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93717360496521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87921786308289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8835643529892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92847990989685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8980530500412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88791084289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90239977836609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91688895225525</t>
+    <t xml:space="preserve">1.94441783428192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93717348575592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87921762466431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88356423377991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92848002910614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89805340766907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88791108131409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90240001678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91688859462738</t>
   </si>
   <si>
     <t xml:space="preserve">1.92413318157196</t>
@@ -764,13 +761,13 @@
     <t xml:space="preserve">1.93572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9386225938797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9487646818161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99512910842896</t>
+    <t xml:space="preserve">1.93862223625183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94876444339752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99512946605682</t>
   </si>
   <si>
     <t xml:space="preserve">2.0284538269043</t>
@@ -779,37 +776,37 @@
     <t xml:space="preserve">2.05743145942688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06902265548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05163598060608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10234713554382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06467652320862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03859615325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07336950302124</t>
+    <t xml:space="preserve">2.06902289390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05163621902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1023473739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06467628479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0385959148407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0733699798584</t>
   </si>
   <si>
     <t xml:space="preserve">2.08640956878662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12842750549316</t>
+    <t xml:space="preserve">2.12842774391174</t>
   </si>
   <si>
     <t xml:space="preserve">2.11248970031738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11104083061218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10089898109436</t>
+    <t xml:space="preserve">2.11104106903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10089874267578</t>
   </si>
   <si>
     <t xml:space="preserve">2.05453395843506</t>
@@ -821,82 +818,85 @@
     <t xml:space="preserve">2.12263202667236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07916522026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1037962436676</t>
+    <t xml:space="preserve">2.07916498184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10379648208618</t>
   </si>
   <si>
     <t xml:space="preserve">2.11973428726196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10814309120178</t>
+    <t xml:space="preserve">2.10814332962036</t>
   </si>
   <si>
     <t xml:space="preserve">2.14726328849792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13277411460876</t>
+    <t xml:space="preserve">2.13277435302734</t>
   </si>
   <si>
     <t xml:space="preserve">2.15450763702393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14291644096375</t>
+    <t xml:space="preserve">2.14291620254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15595698356628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16790914535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17836785316467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17239141464233</t>
   </si>
   <si>
     <t xml:space="preserve">2.15595674514771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16790914535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17836785316467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17239165306091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09918141365051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.112628698349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07228803634644</t>
+    <t xml:space="preserve">2.09918189048767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11262845993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07228827476501</t>
   </si>
   <si>
     <t xml:space="preserve">2.05884146690369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01700782775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99907886981964</t>
+    <t xml:space="preserve">2.01700735092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99907839298248</t>
   </si>
   <si>
     <t xml:space="preserve">2.01103091239929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00804281234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99758446216583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95126760005951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97069084644318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00505471229553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9826432466507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03045392036438</t>
+    <t xml:space="preserve">2.00804257392883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99758422374725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95126783847809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97069072723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00505495071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98264336585999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03045415878296</t>
   </si>
   <si>
     <t xml:space="preserve">2.05286526679993</t>
@@ -923,40 +923,40 @@
     <t xml:space="preserve">2.03344202041626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01401901245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05435919761658</t>
+    <t xml:space="preserve">2.01401948928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05435967445374</t>
   </si>
   <si>
     <t xml:space="preserve">2.04390096664429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04240655899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03643035888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0483832359314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04987692832947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00206637382507</t>
+    <t xml:space="preserve">2.04240679740906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03643012046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04838299751282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04987716674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00206661224365</t>
   </si>
   <si>
     <t xml:space="preserve">2.05585336685181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03493642807007</t>
+    <t xml:space="preserve">2.03493618965149</t>
   </si>
   <si>
     <t xml:space="preserve">1.99459624290466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97517323493958</t>
+    <t xml:space="preserve">1.97517335414886</t>
   </si>
   <si>
     <t xml:space="preserve">1.96172654628754</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">2.01252508163452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00953722000122</t>
+    <t xml:space="preserve">2.00953674316406</t>
   </si>
   <si>
     <t xml:space="preserve">2.0035605430603</t>
@@ -983,31 +983,31 @@
     <t xml:space="preserve">2.01850128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00057220458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98563194274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98712587356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97218525409698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02148985862732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03792452812195</t>
+    <t xml:space="preserve">2.000572681427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98563182353973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98712551593781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9721851348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02148962020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03792428970337</t>
   </si>
   <si>
     <t xml:space="preserve">2.06033563613892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07079434394836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07378220558167</t>
+    <t xml:space="preserve">2.07079410552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07378244400024</t>
   </si>
   <si>
     <t xml:space="preserve">2.06631183624268</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">2.06332397460938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07527685165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08424067497253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10665225982666</t>
+    <t xml:space="preserve">2.07527661323547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08424115180969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10665202140808</t>
   </si>
   <si>
     <t xml:space="preserve">2.12458109855652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14998030662537</t>
+    <t xml:space="preserve">2.14998078346252</t>
   </si>
   <si>
     <t xml:space="preserve">2.16043901443481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18135619163513</t>
+    <t xml:space="preserve">2.18135643005371</t>
   </si>
   <si>
     <t xml:space="preserve">2.19629693031311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18733263015747</t>
+    <t xml:space="preserve">2.18733239173889</t>
   </si>
   <si>
     <t xml:space="preserve">2.1798620223999</t>
@@ -1049,31 +1049,31 @@
     <t xml:space="preserve">2.16641545295715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1708972454071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19181489944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19330859184265</t>
+    <t xml:space="preserve">2.17089748382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.191814661026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19330883026123</t>
   </si>
   <si>
     <t xml:space="preserve">2.19480276107788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22468423843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27100086212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25606036186218</t>
+    <t xml:space="preserve">2.22468400001526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.271000623703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2560601234436</t>
   </si>
   <si>
     <t xml:space="preserve">2.2590479850769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28145980834961</t>
+    <t xml:space="preserve">2.28145956993103</t>
   </si>
   <si>
     <t xml:space="preserve">2.2949059009552</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">2.30088233947754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33972883224487</t>
+    <t xml:space="preserve">2.33972859382629</t>
   </si>
   <si>
     <t xml:space="preserve">2.28892993927002</t>
@@ -1094,37 +1094,37 @@
     <t xml:space="preserve">2.27398896217346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30387091636658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31582307815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25456595420837</t>
+    <t xml:space="preserve">2.30387043952942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31582283973694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25456571578979</t>
   </si>
   <si>
     <t xml:space="preserve">2.25755405426025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27847123146057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22916650772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22617816925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21870827674866</t>
+    <t xml:space="preserve">2.27847099304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22916674613953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22617840766907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21870803833008</t>
   </si>
   <si>
     <t xml:space="preserve">2.17388582229614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15446305274963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21123743057251</t>
+    <t xml:space="preserve">2.15446281433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21123766899109</t>
   </si>
   <si>
     <t xml:space="preserve">2.26054239273071</t>
@@ -1136,10 +1136,10 @@
     <t xml:space="preserve">2.24111938476562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26950669288635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23813128471375</t>
+    <t xml:space="preserve">2.26950693130493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23813104629517</t>
   </si>
   <si>
     <t xml:space="preserve">2.27697730064392</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">2.29938840866089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24709510803223</t>
+    <t xml:space="preserve">2.24709534645081</t>
   </si>
   <si>
     <t xml:space="preserve">2.2799654006958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24560165405273</t>
+    <t xml:space="preserve">2.24560141563416</t>
   </si>
   <si>
     <t xml:space="preserve">2.18434429168701</t>
@@ -1169,16 +1169,16 @@
     <t xml:space="preserve">2.11113452911377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05734777450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02895998954773</t>
+    <t xml:space="preserve">2.05734753608704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02895975112915</t>
   </si>
   <si>
     <t xml:space="preserve">2.09469938278198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12607526779175</t>
+    <t xml:space="preserve">2.12607502937317</t>
   </si>
   <si>
     <t xml:space="preserve">2.13354563713074</t>
@@ -1193,10 +1193,10 @@
     <t xml:space="preserve">2.04091238975525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08573532104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08274698257446</t>
+    <t xml:space="preserve">2.08573484420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08274674415588</t>
   </si>
   <si>
     <t xml:space="preserve">2.08125281333923</t>
@@ -1208,10 +1208,10 @@
     <t xml:space="preserve">2.09768748283386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12009859085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2127320766449</t>
+    <t xml:space="preserve">2.12009882926941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21273159980774</t>
   </si>
   <si>
     <t xml:space="preserve">2.22169613838196</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">2.26353049278259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23514294624329</t>
+    <t xml:space="preserve">2.23514318466187</t>
   </si>
   <si>
     <t xml:space="preserve">2.25307202339172</t>
@@ -1235,19 +1235,19 @@
     <t xml:space="preserve">2.29341197013855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29789423942566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28444719314575</t>
+    <t xml:space="preserve">2.29789447784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28444743156433</t>
   </si>
   <si>
     <t xml:space="preserve">2.22767281532288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25157761573792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14101600646973</t>
+    <t xml:space="preserve">2.25157785415649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14101552963257</t>
   </si>
   <si>
     <t xml:space="preserve">2.12159276008606</t>
@@ -1259,19 +1259,19 @@
     <t xml:space="preserve">1.94678544998169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96471428871155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98114955425262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96919667720795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97816109657288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94828009605408</t>
+    <t xml:space="preserve">1.96471464633942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98114943504333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96919679641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97816121578217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9482798576355</t>
   </si>
   <si>
     <t xml:space="preserve">2.02856683731079</t>
@@ -1280,19 +1280,19 @@
     <t xml:space="preserve">2.06108570098877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07192587852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0378577709198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04095482826233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07347393035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05953741073608</t>
+    <t xml:space="preserve">2.07192540168762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03785800933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04095506668091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07347416877747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0595371723175</t>
   </si>
   <si>
     <t xml:space="preserve">2.08895921707153</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">2.06728005409241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10599303245544</t>
+    <t xml:space="preserve">2.10599279403687</t>
   </si>
   <si>
     <t xml:space="preserve">2.13541507720947</t>
@@ -1310,46 +1310,46 @@
     <t xml:space="preserve">2.15399694442749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16019129753113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1447057723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13696360588074</t>
+    <t xml:space="preserve">2.16019153594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14470601081848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13696336746216</t>
   </si>
   <si>
     <t xml:space="preserve">2.14780306816101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13386654853821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16793417930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17257952690125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1524486541748</t>
+    <t xml:space="preserve">2.13386631011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16793394088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17257976531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15244841575623</t>
   </si>
   <si>
     <t xml:space="preserve">2.1044442653656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09205603599548</t>
+    <t xml:space="preserve">2.09205627441406</t>
   </si>
   <si>
     <t xml:space="preserve">2.20664691925049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1710307598114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19580745697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18651628494263</t>
+    <t xml:space="preserve">2.17103099822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19580698013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18651604652405</t>
   </si>
   <si>
     <t xml:space="preserve">2.21748685836792</t>
@@ -1367,49 +1367,49 @@
     <t xml:space="preserve">2.1509006023407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13231801986694</t>
+    <t xml:space="preserve">2.13231778144836</t>
   </si>
   <si>
     <t xml:space="preserve">2.12612390518188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11992955207825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16638565063477</t>
+    <t xml:space="preserve">2.11992979049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16638541221619</t>
   </si>
   <si>
     <t xml:space="preserve">2.1570942401886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14935183525085</t>
+    <t xml:space="preserve">2.14935159683228</t>
   </si>
   <si>
     <t xml:space="preserve">2.09670186042786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09979891777039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09050798416138</t>
+    <t xml:space="preserve">2.09979867935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0905077457428</t>
   </si>
   <si>
     <t xml:space="preserve">2.10754156112671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12457513809204</t>
+    <t xml:space="preserve">2.12457489967346</t>
   </si>
   <si>
     <t xml:space="preserve">2.12767219543457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18806481361389</t>
+    <t xml:space="preserve">2.18806457519531</t>
   </si>
   <si>
     <t xml:space="preserve">2.20045304298401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19735598564148</t>
+    <t xml:space="preserve">2.1973557472229</t>
   </si>
   <si>
     <t xml:space="preserve">2.20200157165527</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">2.20819544792175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21129274368286</t>
+    <t xml:space="preserve">2.21129298210144</t>
   </si>
   <si>
     <t xml:space="preserve">2.1756763458252</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">2.12147831916809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11683297157288</t>
+    <t xml:space="preserve">2.1168327331543</t>
   </si>
   <si>
     <t xml:space="preserve">2.07657098770142</t>
@@ -1439,37 +1439,37 @@
     <t xml:space="preserve">2.05179476737976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01463007926941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96197998523712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98211085796356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93720400333405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90313613414764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86287462711334</t>
+    <t xml:space="preserve">2.01462984085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96197974681854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98211109638214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93720376491547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90313625335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86287438869476</t>
   </si>
   <si>
     <t xml:space="preserve">1.91552424430847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87216579914093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89384520053864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90158772468567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87061738967896</t>
+    <t xml:space="preserve">1.87216591835022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89384508132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90158808231354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87061750888824</t>
   </si>
   <si>
     <t xml:space="preserve">1.85977756977081</t>
@@ -1481,64 +1481,64 @@
     <t xml:space="preserve">1.89694237709045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89074814319611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87990844249725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88919937610626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88765072822571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90468466281891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9217187166214</t>
+    <t xml:space="preserve">1.89074790477753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87990868091583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88919961452484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88765096664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9046847820282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92171859741211</t>
   </si>
   <si>
     <t xml:space="preserve">1.96662592887878</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91862154006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97901403903961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96972298622131</t>
+    <t xml:space="preserve">1.91862189769745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9790141582489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9697231054306</t>
   </si>
   <si>
     <t xml:space="preserve">1.97746539115906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94184947013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93100965023041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92481565475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92016994953156</t>
+    <t xml:space="preserve">1.94184935092926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93100988864899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92481589317322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92017018795013</t>
   </si>
   <si>
     <t xml:space="preserve">1.89229679107666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90933084487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87836003303528</t>
+    <t xml:space="preserve">1.90933060646057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87835991382599</t>
   </si>
   <si>
     <t xml:space="preserve">1.93875253200531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86906886100769</t>
+    <t xml:space="preserve">1.8690687417984</t>
   </si>
   <si>
     <t xml:space="preserve">1.94804346561432</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">2.19425892829895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17877388000488</t>
+    <t xml:space="preserve">2.1787736415863</t>
   </si>
   <si>
     <t xml:space="preserve">2.20509839057922</t>
@@ -1577,25 +1577,25 @@
     <t xml:space="preserve">2.2097442150116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22987508773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20354986190796</t>
+    <t xml:space="preserve">2.22987484931946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20355010032654</t>
   </si>
   <si>
     <t xml:space="preserve">2.19890427589417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22677803039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26084542274475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26239371299744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28562188148499</t>
+    <t xml:space="preserve">2.22677779197693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26084566116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26239395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28562164306641</t>
   </si>
   <si>
     <t xml:space="preserve">2.29336428642273</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">2.2840735912323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29026746749878</t>
+    <t xml:space="preserve">2.2902672290802</t>
   </si>
   <si>
     <t xml:space="preserve">2.27013659477234</t>
@@ -1616,31 +1616,31 @@
     <t xml:space="preserve">2.25619983673096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28097629547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30265545845032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30110669136047</t>
+    <t xml:space="preserve">2.28097605705261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30265522003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30110692977905</t>
   </si>
   <si>
     <t xml:space="preserve">2.30730128288269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29801034927368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28871917724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25929689407349</t>
+    <t xml:space="preserve">2.29800987243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28871893882751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25929665565491</t>
   </si>
   <si>
     <t xml:space="preserve">2.32433485984802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29181575775146</t>
+    <t xml:space="preserve">2.29181599617004</t>
   </si>
   <si>
     <t xml:space="preserve">2.25465130805969</t>
@@ -1649,10 +1649,10 @@
     <t xml:space="preserve">2.26858806610107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26549077033997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29955887794495</t>
+    <t xml:space="preserve">2.26549100875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29955863952637</t>
   </si>
   <si>
     <t xml:space="preserve">2.29646134376526</t>
@@ -1661,22 +1661,22 @@
     <t xml:space="preserve">2.31349539756775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32123780250549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25774836540222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23916625976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34446597099304</t>
+    <t xml:space="preserve">2.32123804092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2577486038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23916602134705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34446573257446</t>
   </si>
   <si>
     <t xml:space="preserve">2.38008165359497</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38163018226624</t>
+    <t xml:space="preserve">2.38163042068481</t>
   </si>
   <si>
     <t xml:space="preserve">2.40330982208252</t>
@@ -1688,10 +1688,10 @@
     <t xml:space="preserve">2.4311830997467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4760901927948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49467253684998</t>
+    <t xml:space="preserve">2.47609043121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4946722984314</t>
   </si>
   <si>
     <t xml:space="preserve">2.49002695083618</t>
@@ -1706,19 +1706,19 @@
     <t xml:space="preserve">2.54887080192566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52099776268005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5024151802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5163516998291</t>
+    <t xml:space="preserve">2.52099752426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50241541862488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51635193824768</t>
   </si>
   <si>
     <t xml:space="preserve">2.462153673172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47918748855591</t>
+    <t xml:space="preserve">2.47918725013733</t>
   </si>
   <si>
     <t xml:space="preserve">2.46525073051453</t>
@@ -1736,37 +1736,37 @@
     <t xml:space="preserve">2.46679925918579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44666790962219</t>
+    <t xml:space="preserve">2.44666838645935</t>
   </si>
   <si>
     <t xml:space="preserve">2.4575080871582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47144484519958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45905685424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42653751373291</t>
+    <t xml:space="preserve">2.47144460678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45905661582947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42653775215149</t>
   </si>
   <si>
     <t xml:space="preserve">2.44821691513062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42963457107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48692965507507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53028869628906</t>
+    <t xml:space="preserve">2.42963433265686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48692989349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53028845787048</t>
   </si>
   <si>
     <t xml:space="preserve">2.53803110122681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54112839698792</t>
+    <t xml:space="preserve">2.54112815856934</t>
   </si>
   <si>
     <t xml:space="preserve">2.54422521591187</t>
@@ -1778,40 +1778,40 @@
     <t xml:space="preserve">2.55816197395325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53648281097412</t>
+    <t xml:space="preserve">2.53648257255554</t>
   </si>
   <si>
     <t xml:space="preserve">2.53493404388428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5287401676178</t>
+    <t xml:space="preserve">2.52873992919922</t>
   </si>
   <si>
     <t xml:space="preserve">2.51790046691895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56435632705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59068131446838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60306930541992</t>
+    <t xml:space="preserve">2.56435656547546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59068059921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6030695438385</t>
   </si>
   <si>
     <t xml:space="preserve">2.60461783409119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59997224807739</t>
+    <t xml:space="preserve">2.59997200965881</t>
   </si>
   <si>
     <t xml:space="preserve">2.60152077674866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58913278579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58603549003601</t>
+    <t xml:space="preserve">2.58913254737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58603572845459</t>
   </si>
   <si>
     <t xml:space="preserve">2.64642810821533</t>
@@ -1820,40 +1820,40 @@
     <t xml:space="preserve">2.65262222290039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68514108657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7161111831665</t>
+    <t xml:space="preserve">2.68514084815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71611142158508</t>
   </si>
   <si>
     <t xml:space="preserve">2.69698429107666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67945051193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68263816833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65075898170471</t>
+    <t xml:space="preserve">2.67945075035095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68263840675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65075922012329</t>
   </si>
   <si>
     <t xml:space="preserve">2.68104434013367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66669893264771</t>
+    <t xml:space="preserve">2.66669845581055</t>
   </si>
   <si>
     <t xml:space="preserve">2.73045754432678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81174945831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80856108665466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78465151786804</t>
+    <t xml:space="preserve">2.81174898147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80856132507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7846519947052</t>
   </si>
   <si>
     <t xml:space="preserve">2.77349424362183</t>
@@ -1862,25 +1862,25 @@
     <t xml:space="preserve">2.78305792808533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79740357398987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79580950737</t>
+    <t xml:space="preserve">2.79740381240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79580974578857</t>
   </si>
   <si>
     <t xml:space="preserve">2.82768893241882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80696749687195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75914859771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74480271339417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74958491325378</t>
+    <t xml:space="preserve">2.80696725845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75914835929871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74480295181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74958467483521</t>
   </si>
   <si>
     <t xml:space="preserve">2.7320511341095</t>
@@ -1901,22 +1901,22 @@
     <t xml:space="preserve">2.73683309555054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71132969856262</t>
+    <t xml:space="preserve">2.71132946014404</t>
   </si>
   <si>
     <t xml:space="preserve">2.69538998603821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70654797554016</t>
+    <t xml:space="preserve">2.70654773712158</t>
   </si>
   <si>
     <t xml:space="preserve">2.72726917266846</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70495390892029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73523902893066</t>
+    <t xml:space="preserve">2.70495367050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73523926734924</t>
   </si>
   <si>
     <t xml:space="preserve">2.68742036819458</t>
@@ -1928,10 +1928,10 @@
     <t xml:space="preserve">2.78783988952637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77827620506287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78624582290649</t>
+    <t xml:space="preserve">2.77827596664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78624606132507</t>
   </si>
   <si>
     <t xml:space="preserve">2.81334328651428</t>
@@ -1949,13 +1949,13 @@
     <t xml:space="preserve">2.89144730567932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88666534423828</t>
+    <t xml:space="preserve">2.88666558265686</t>
   </si>
   <si>
     <t xml:space="preserve">2.88825964927673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91695094108582</t>
+    <t xml:space="preserve">2.91695070266724</t>
   </si>
   <si>
     <t xml:space="preserve">2.89622926712036</t>
@@ -1964,7 +1964,7 @@
     <t xml:space="preserve">2.80059146881104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79262208938599</t>
+    <t xml:space="preserve">2.79262185096741</t>
   </si>
   <si>
     <t xml:space="preserve">2.84522247314453</t>
@@ -1973,22 +1973,22 @@
     <t xml:space="preserve">2.81812500953674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82131314277649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84681630134583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90738677978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90419888496399</t>
+    <t xml:space="preserve">2.82131290435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8468165397644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90738654136658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90419912338257</t>
   </si>
   <si>
     <t xml:space="preserve">2.86913180351257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95201802253723</t>
+    <t xml:space="preserve">2.95201778411865</t>
   </si>
   <si>
     <t xml:space="preserve">2.95042395591736</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">3.02055835723877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9647696018219</t>
+    <t xml:space="preserve">2.96476936340332</t>
   </si>
   <si>
     <t xml:space="preserve">3.00143074989319</t>
@@ -2006,7 +2006,7 @@
     <t xml:space="preserve">2.95679998397827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97114539146423</t>
+    <t xml:space="preserve">2.97114562988281</t>
   </si>
   <si>
     <t xml:space="preserve">3.01577615737915</t>
@@ -2015,22 +2015,22 @@
     <t xml:space="preserve">3.02215242385864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00461864471436</t>
+    <t xml:space="preserve">3.00461840629578</t>
   </si>
   <si>
     <t xml:space="preserve">2.97911524772644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00302457809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01418232917786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98389720916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02374601364136</t>
+    <t xml:space="preserve">3.00302481651306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01418256759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98389744758606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02374625205994</t>
   </si>
   <si>
     <t xml:space="preserve">2.99664902687073</t>
@@ -2039,16 +2039,16 @@
     <t xml:space="preserve">2.96636343002319</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99346113204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00621271133423</t>
+    <t xml:space="preserve">2.99346089363098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00621294975281</t>
   </si>
   <si>
     <t xml:space="preserve">3.04606175422668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05881357192993</t>
+    <t xml:space="preserve">3.05881333351135</t>
   </si>
   <si>
     <t xml:space="preserve">3.04924941062927</t>
@@ -2066,16 +2066,16 @@
     <t xml:space="preserve">3.06678295135498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05243754386902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07315897941589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07475328445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10025668144226</t>
+    <t xml:space="preserve">3.05243730545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07315921783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07475304603577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1002562046051</t>
   </si>
   <si>
     <t xml:space="preserve">3.17357897758484</t>
@@ -2093,16 +2093,16 @@
     <t xml:space="preserve">3.19589447975159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16242122650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17995429039001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15604543685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18473672866821</t>
+    <t xml:space="preserve">3.16242074966431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17995452880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15604519844055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18473649024963</t>
   </si>
   <si>
     <t xml:space="preserve">3.17517280578613</t>
@@ -2111,16 +2111,16 @@
     <t xml:space="preserve">3.19111227989197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0620014667511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08750462532043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1241660118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10185027122498</t>
+    <t xml:space="preserve">3.06200122833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08750486373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12416625022888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10185050964355</t>
   </si>
   <si>
     <t xml:space="preserve">3.09547448158264</t>
@@ -2129,37 +2129,37 @@
     <t xml:space="preserve">3.0715651512146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10344457626343</t>
+    <t xml:space="preserve">3.10344433784485</t>
   </si>
   <si>
     <t xml:space="preserve">3.11141395568848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06040740013123</t>
+    <t xml:space="preserve">3.06040692329407</t>
   </si>
   <si>
     <t xml:space="preserve">3.12735390663147</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17198491096497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16879653930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16401481628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22139716148376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16082715988159</t>
+    <t xml:space="preserve">3.17198467254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16879677772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16401505470276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22139739990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16082692146301</t>
   </si>
   <si>
     <t xml:space="preserve">3.16560864448547</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10822629928589</t>
+    <t xml:space="preserve">3.10822653770447</t>
   </si>
   <si>
     <t xml:space="preserve">3.09706830978394</t>
@@ -2171,25 +2171,25 @@
     <t xml:space="preserve">3.0811288356781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07794094085693</t>
+    <t xml:space="preserve">3.07794070243835</t>
   </si>
   <si>
     <t xml:space="preserve">3.14329361915588</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18633031845093</t>
+    <t xml:space="preserve">3.18633055686951</t>
   </si>
   <si>
     <t xml:space="preserve">3.18314242362976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13213586807251</t>
+    <t xml:space="preserve">3.13213562965393</t>
   </si>
   <si>
     <t xml:space="preserve">3.27240443229675</t>
   </si>
   <si>
-    <t xml:space="preserve">3.377605676651</t>
+    <t xml:space="preserve">3.37760591506958</t>
   </si>
   <si>
     <t xml:space="preserve">3.31384706497192</t>
@@ -2198,10 +2198,10 @@
     <t xml:space="preserve">3.44774055480957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44614577293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37919974327087</t>
+    <t xml:space="preserve">3.44614601135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37919998168945</t>
   </si>
   <si>
     <t xml:space="preserve">3.26921677589417</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">3.27718639373779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28675031661987</t>
+    <t xml:space="preserve">3.28674983978271</t>
   </si>
   <si>
     <t xml:space="preserve">3.33297514915466</t>
@@ -2219,40 +2219,40 @@
     <t xml:space="preserve">3.37282395362854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38557600975037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40948510169983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42701864242554</t>
+    <t xml:space="preserve">3.38557624816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40948462486267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42701888084412</t>
   </si>
   <si>
     <t xml:space="preserve">3.43977046012878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47802495956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45252203941345</t>
+    <t xml:space="preserve">3.47802543640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45252180099487</t>
   </si>
   <si>
     <t xml:space="preserve">3.45730400085449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47005581855774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55612969398499</t>
+    <t xml:space="preserve">3.47005558013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55612993240356</t>
   </si>
   <si>
     <t xml:space="preserve">3.53700256347656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51628088951111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33935117721558</t>
+    <t xml:space="preserve">3.51628065109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.339350938797</t>
   </si>
   <si>
     <t xml:space="preserve">3.30906534194946</t>
@@ -2261,19 +2261,19 @@
     <t xml:space="preserve">3.3377571105957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27877998352051</t>
+    <t xml:space="preserve">3.27878022193909</t>
   </si>
   <si>
     <t xml:space="preserve">3.09069275856018</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11300802230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2612464427948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83247089385986</t>
+    <t xml:space="preserve">3.11300778388977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26124668121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83247113227844</t>
   </si>
   <si>
     <t xml:space="preserve">2.65872883796692</t>
@@ -2291,13 +2291,13 @@
     <t xml:space="preserve">2.46585941314697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51049065589905</t>
+    <t xml:space="preserve">2.51049041748047</t>
   </si>
   <si>
     <t xml:space="preserve">2.5168662071228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46107792854309</t>
+    <t xml:space="preserve">2.46107745170593</t>
   </si>
   <si>
     <t xml:space="preserve">2.58381271362305</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">2.50252079963684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62206745147705</t>
+    <t xml:space="preserve">2.62206792831421</t>
   </si>
   <si>
     <t xml:space="preserve">2.60453414916992</t>
@@ -2333,19 +2333,19 @@
     <t xml:space="preserve">2.55193328857422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45948338508606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57584285736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56787300109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54715156555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54396390914917</t>
+    <t xml:space="preserve">2.45948362350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57584309577942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56787276268005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54715180397034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54396367073059</t>
   </si>
   <si>
     <t xml:space="preserve">2.60772204399109</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">2.5184600353241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5901882648468</t>
+    <t xml:space="preserve">2.59018850326538</t>
   </si>
   <si>
     <t xml:space="preserve">2.5806245803833</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">2.57903051376343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57265496253967</t>
+    <t xml:space="preserve">2.57265472412109</t>
   </si>
   <si>
     <t xml:space="preserve">2.52483630180359</t>
@@ -2387,37 +2387,37 @@
     <t xml:space="preserve">2.61887955665588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56149697303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47542333602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46267175674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51367855072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50092673301697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55352759361267</t>
+    <t xml:space="preserve">2.5614972114563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47542357444763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46267151832581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51367831230164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50092649459839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55352735519409</t>
   </si>
   <si>
     <t xml:space="preserve">2.54874563217163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65713500976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66032266616821</t>
+    <t xml:space="preserve">2.6571352481842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66032290458679</t>
   </si>
   <si>
     <t xml:space="preserve">2.85159826278687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85638022422791</t>
+    <t xml:space="preserve">2.85637998580933</t>
   </si>
   <si>
     <t xml:space="preserve">2.81653094291687</t>
@@ -2426,13 +2426,13 @@
     <t xml:space="preserve">2.77668213844299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6778564453125</t>
+    <t xml:space="preserve">2.67785668373108</t>
   </si>
   <si>
     <t xml:space="preserve">2.80218553543091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78943395614624</t>
+    <t xml:space="preserve">2.78943371772766</t>
   </si>
   <si>
     <t xml:space="preserve">2.77030634880066</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">2.75755476951599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75436663627625</t>
+    <t xml:space="preserve">2.75436639785767</t>
   </si>
   <si>
     <t xml:space="preserve">2.68901419639587</t>
@@ -2450,10 +2450,10 @@
     <t xml:space="preserve">2.63800740242004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70335936546326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70017170906067</t>
+    <t xml:space="preserve">2.70335960388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70017218589783</t>
   </si>
   <si>
     <t xml:space="preserve">2.72567534446716</t>
@@ -2462,19 +2462,19 @@
     <t xml:space="preserve">2.74209499359131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69940400123596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71418142318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.641934633255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63372492790222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67477416992188</t>
+    <t xml:space="preserve">2.69940376281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71418166160583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64193487167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6337251663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6747739315033</t>
   </si>
   <si>
     <t xml:space="preserve">2.63865065574646</t>
@@ -2483,10 +2483,10 @@
     <t xml:space="preserve">2.65014457702637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69447803497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73060131072998</t>
+    <t xml:space="preserve">2.69447779655457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7306010723114</t>
   </si>
   <si>
     <t xml:space="preserve">2.73388528823853</t>
@@ -2495,13 +2495,13 @@
     <t xml:space="preserve">2.73552703857422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76508235931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66163849830627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61894702911377</t>
+    <t xml:space="preserve">2.76508259773254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66163873672485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61894726753235</t>
   </si>
   <si>
     <t xml:space="preserve">2.63536667823792</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">2.68791007995605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59267544746399</t>
+    <t xml:space="preserve">2.59267568588257</t>
   </si>
   <si>
     <t xml:space="preserve">2.61073732376099</t>
@@ -2522,13 +2522,13 @@
     <t xml:space="preserve">2.60252737998962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59595918655396</t>
+    <t xml:space="preserve">2.59595894813538</t>
   </si>
   <si>
     <t xml:space="preserve">2.58774948120117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66820645332336</t>
+    <t xml:space="preserve">2.66820621490479</t>
   </si>
   <si>
     <t xml:space="preserve">2.72403335571289</t>
@@ -2537,55 +2537,55 @@
     <t xml:space="preserve">2.78642845153809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77657675743103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75851464271545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66656446456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7092559337616</t>
+    <t xml:space="preserve">2.77657628059387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75851488113403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66656398773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70925569534302</t>
   </si>
   <si>
     <t xml:space="preserve">2.68298387527466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66328024864197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75030493736267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72239112854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64686059951782</t>
+    <t xml:space="preserve">2.66328048706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75030469894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72239136695862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64686036109924</t>
   </si>
   <si>
     <t xml:space="preserve">2.62715697288513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62879920005798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6156632900238</t>
+    <t xml:space="preserve">2.62879872322083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61566305160522</t>
   </si>
   <si>
     <t xml:space="preserve">2.69283580780029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59760141372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64850258827209</t>
+    <t xml:space="preserve">2.59760165214539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64850282669067</t>
   </si>
   <si>
     <t xml:space="preserve">2.64029264450073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68134212493896</t>
+    <t xml:space="preserve">2.68134236335754</t>
   </si>
   <si>
     <t xml:space="preserve">2.66492223739624</t>
@@ -2597,46 +2597,46 @@
     <t xml:space="preserve">2.69776177406311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71253967285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63700890541077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62387299537659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60745358467102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64521861076355</t>
+    <t xml:space="preserve">2.71253943443298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63700866699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62387323379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60745334625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64521837234497</t>
   </si>
   <si>
     <t xml:space="preserve">2.63044095039368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54998421669006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55819392204285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54505848884583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51386070251465</t>
+    <t xml:space="preserve">2.54998397827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55819368362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54505825042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51386094093323</t>
   </si>
   <si>
     <t xml:space="preserve">2.52042865753174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50236701965332</t>
+    <t xml:space="preserve">2.5023672580719</t>
   </si>
   <si>
     <t xml:space="preserve">2.47281169891357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42191028594971</t>
+    <t xml:space="preserve">2.42191052436829</t>
   </si>
   <si>
     <t xml:space="preserve">2.44325613975525</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">2.35951542854309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3841450214386</t>
+    <t xml:space="preserve">2.38414478302002</t>
   </si>
   <si>
     <t xml:space="preserve">2.41205859184265</t>
@@ -2663,13 +2663,13 @@
     <t xml:space="preserve">2.37757682800293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31518197059631</t>
+    <t xml:space="preserve">2.31518220901489</t>
   </si>
   <si>
     <t xml:space="preserve">2.29219460487366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23472499847412</t>
+    <t xml:space="preserve">2.2347252368927</t>
   </si>
   <si>
     <t xml:space="preserve">2.19696021080017</t>
@@ -2681,22 +2681,22 @@
     <t xml:space="preserve">2.23636722564697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25442934036255</t>
+    <t xml:space="preserve">2.25442910194397</t>
   </si>
   <si>
     <t xml:space="preserve">2.3102560043335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30533027648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28070068359375</t>
+    <t xml:space="preserve">2.30533051490784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28070044517517</t>
   </si>
   <si>
     <t xml:space="preserve">2.45474982261658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42519450187683</t>
+    <t xml:space="preserve">2.42519426345825</t>
   </si>
   <si>
     <t xml:space="preserve">2.44982385635376</t>
@@ -2708,13 +2708,13 @@
     <t xml:space="preserve">2.47937917709351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56147766113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50893473625183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49579882621765</t>
+    <t xml:space="preserve">2.56147813796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50893497467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49579906463623</t>
   </si>
   <si>
     <t xml:space="preserve">2.50400900840759</t>
@@ -2726,13 +2726,13 @@
     <t xml:space="preserve">2.47609543800354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52207040786743</t>
+    <t xml:space="preserve">2.52207064628601</t>
   </si>
   <si>
     <t xml:space="preserve">2.53520655632019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51221895217896</t>
+    <t xml:space="preserve">2.51221871376038</t>
   </si>
   <si>
     <t xml:space="preserve">2.47116947174072</t>
@@ -2741,10 +2741,10 @@
     <t xml:space="preserve">2.43997192382812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46788573265076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44489789009094</t>
+    <t xml:space="preserve">2.46788549423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44489812850952</t>
   </si>
   <si>
     <t xml:space="preserve">2.43012022972107</t>
@@ -2753,7 +2753,7 @@
     <t xml:space="preserve">2.41534233093262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38907098770142</t>
+    <t xml:space="preserve">2.38907074928284</t>
   </si>
   <si>
     <t xml:space="preserve">2.36444139480591</t>
@@ -2762,40 +2762,40 @@
     <t xml:space="preserve">2.39399671554565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3660831451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40384864807129</t>
+    <t xml:space="preserve">2.36608338356018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40384840965271</t>
   </si>
   <si>
     <t xml:space="preserve">2.45146584510803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33981156349182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38742899894714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45310759544373</t>
+    <t xml:space="preserve">2.33981132507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38742876052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4531078338623</t>
   </si>
   <si>
     <t xml:space="preserve">2.45967578887939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44654011726379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50565123558044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44161415100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49087285995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48594760894775</t>
+    <t xml:space="preserve">2.44653987884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50565075874329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44161367416382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49087309837341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4859471321106</t>
   </si>
   <si>
     <t xml:space="preserve">2.59431767463684</t>
@@ -2804,16 +2804,16 @@
     <t xml:space="preserve">2.5417742729187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38086128234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33652758598328</t>
+    <t xml:space="preserve">2.38086104393005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33652782440186</t>
   </si>
   <si>
     <t xml:space="preserve">2.35787320137024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36772537231445</t>
+    <t xml:space="preserve">2.36772513389587</t>
   </si>
   <si>
     <t xml:space="preserve">2.32995986938477</t>
@@ -2822,10 +2822,10 @@
     <t xml:space="preserve">2.46952748298645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49415731430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55326795578003</t>
+    <t xml:space="preserve">2.49415707588196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55326843261719</t>
   </si>
   <si>
     <t xml:space="preserve">2.51057696342468</t>
@@ -2834,49 +2834,49 @@
     <t xml:space="preserve">2.52371263504028</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55491018295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58939170837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54670023918152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53684854507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52535486221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43176198005676</t>
+    <t xml:space="preserve">2.55491042137146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58939146995544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5467004776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53684830665588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52535462379456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43176221847534</t>
   </si>
   <si>
     <t xml:space="preserve">2.4022068977356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5286386013031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56311988830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56968808174133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60416913032532</t>
+    <t xml:space="preserve">2.52863836288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56312012672424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56968784332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6041693687439</t>
   </si>
   <si>
     <t xml:space="preserve">2.71582365036011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68216276168823</t>
+    <t xml:space="preserve">2.68216300010681</t>
   </si>
   <si>
     <t xml:space="preserve">2.72895932197571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70843482017517</t>
+    <t xml:space="preserve">2.70843458175659</t>
   </si>
   <si>
     <t xml:space="preserve">2.69611978530884</t>
@@ -2891,52 +2891,52 @@
     <t xml:space="preserve">2.76918745040894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76097750663757</t>
+    <t xml:space="preserve">2.76097774505615</t>
   </si>
   <si>
     <t xml:space="preserve">2.75440979003906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75523114204407</t>
+    <t xml:space="preserve">2.75523066520691</t>
   </si>
   <si>
     <t xml:space="preserve">2.75605177879333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7461998462677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79381728172302</t>
+    <t xml:space="preserve">2.74620008468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79381704330444</t>
   </si>
   <si>
     <t xml:space="preserve">2.76261973381042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76672434806824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79710149765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8381507396698</t>
+    <t xml:space="preserve">2.76672458648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79710125923157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83815050125122</t>
   </si>
   <si>
     <t xml:space="preserve">2.77082967758179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77247190475464</t>
+    <t xml:space="preserve">2.77247166633606</t>
   </si>
   <si>
     <t xml:space="preserve">2.7642617225647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86278009414673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83240365982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82255172729492</t>
+    <t xml:space="preserve">2.86278033256531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83240389823914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8225519657135</t>
   </si>
   <si>
     <t xml:space="preserve">2.86031723022461</t>
@@ -2945,16 +2945,16 @@
     <t xml:space="preserve">2.87837886810303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88330459594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88740944862366</t>
+    <t xml:space="preserve">2.88330483436584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88740968704224</t>
   </si>
   <si>
     <t xml:space="preserve">2.88248372077942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86524319648743</t>
+    <t xml:space="preserve">2.86524271965027</t>
   </si>
   <si>
     <t xml:space="preserve">2.86113810539246</t>
@@ -2963,22 +2963,22 @@
     <t xml:space="preserve">2.86606383323669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86360120773315</t>
+    <t xml:space="preserve">2.86360096931458</t>
   </si>
   <si>
     <t xml:space="preserve">2.87427377700806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89726185798645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93256402015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95883560180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97197103500366</t>
+    <t xml:space="preserve">2.89726161956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93256378173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95883584022522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97197127342224</t>
   </si>
   <si>
     <t xml:space="preserve">3.02533531188965</t>
@@ -2987,13 +2987,13 @@
     <t xml:space="preserve">3.00481081008911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00809478759766</t>
+    <t xml:space="preserve">3.00809502601624</t>
   </si>
   <si>
     <t xml:space="preserve">3.04093432426453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01794648170471</t>
+    <t xml:space="preserve">3.01794672012329</t>
   </si>
   <si>
     <t xml:space="preserve">3.04586005210876</t>
@@ -3005,49 +3005,49 @@
     <t xml:space="preserve">3.00727391242981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98921179771423</t>
+    <t xml:space="preserve">2.98921227455139</t>
   </si>
   <si>
     <t xml:space="preserve">2.95801448822021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90218734741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92353320121765</t>
+    <t xml:space="preserve">2.90218758583069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92353296279907</t>
   </si>
   <si>
     <t xml:space="preserve">2.89561939239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8906934261322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89151453971863</t>
+    <t xml:space="preserve">2.89069366455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89151477813721</t>
   </si>
   <si>
     <t xml:space="preserve">2.86688494682312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89479875564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90920472145081</t>
+    <t xml:space="preserve">2.89479851722717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90920495986938</t>
   </si>
   <si>
     <t xml:space="preserve">2.89649343490601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96005058288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86598634719849</t>
+    <t xml:space="preserve">2.96005034446716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86598610877991</t>
   </si>
   <si>
     <t xml:space="preserve">2.86429142951965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93208527565002</t>
+    <t xml:space="preserve">2.9320855140686</t>
   </si>
   <si>
     <t xml:space="preserve">2.93293261528015</t>
@@ -3056,13 +3056,13 @@
     <t xml:space="preserve">2.92191600799561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89564609527588</t>
+    <t xml:space="preserve">2.8956458568573</t>
   </si>
   <si>
     <t xml:space="preserve">2.9261531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84225845336914</t>
+    <t xml:space="preserve">2.84225821495056</t>
   </si>
   <si>
     <t xml:space="preserve">2.85073280334473</t>
@@ -3080,13 +3080,13 @@
     <t xml:space="preserve">2.99055743217468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03292870521545</t>
+    <t xml:space="preserve">3.03292846679688</t>
   </si>
   <si>
     <t xml:space="preserve">3.06428337097168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04055571556091</t>
+    <t xml:space="preserve">3.04055547714233</t>
   </si>
   <si>
     <t xml:space="preserve">3.04479241371155</t>
@@ -3095,7 +3095,7 @@
     <t xml:space="preserve">3.02275943756104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01004838943481</t>
+    <t xml:space="preserve">3.01004815101624</t>
   </si>
   <si>
     <t xml:space="preserve">3.00157403945923</t>
@@ -3107,10 +3107,10 @@
     <t xml:space="preserve">3.04648733139038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03547096252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08546876907349</t>
+    <t xml:space="preserve">3.03547120094299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08546900749207</t>
   </si>
   <si>
     <t xml:space="preserve">3.09733295440674</t>
@@ -3122,16 +3122,16 @@
     <t xml:space="preserve">3.14563608169556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15665221214294</t>
+    <t xml:space="preserve">3.15665245056152</t>
   </si>
   <si>
     <t xml:space="preserve">3.18038034439087</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19648146629333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18546509742737</t>
+    <t xml:space="preserve">3.19648122787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18546485900879</t>
   </si>
   <si>
     <t xml:space="preserve">3.18715977668762</t>
@@ -3140,22 +3140,22 @@
     <t xml:space="preserve">3.16682147979736</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12953519821167</t>
+    <t xml:space="preserve">3.12953495979309</t>
   </si>
   <si>
     <t xml:space="preserve">3.10157012939453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11597609519958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11089134216309</t>
+    <t xml:space="preserve">3.11597633361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11089158058167</t>
   </si>
   <si>
     <t xml:space="preserve">3.10411238670349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13716149330139</t>
+    <t xml:space="preserve">3.13716173171997</t>
   </si>
   <si>
     <t xml:space="preserve">3.12275552749634</t>
@@ -3167,16 +3167,16 @@
     <t xml:space="preserve">3.1252977848053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08123159408569</t>
+    <t xml:space="preserve">3.08123183250427</t>
   </si>
   <si>
     <t xml:space="preserve">3.03631830215454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07360529899597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09902787208557</t>
+    <t xml:space="preserve">3.07360482215881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09902763366699</t>
   </si>
   <si>
     <t xml:space="preserve">3.04987716674805</t>
@@ -3185,22 +3185,22 @@
     <t xml:space="preserve">3.08377385139465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04140281677246</t>
+    <t xml:space="preserve">3.04140305519104</t>
   </si>
   <si>
     <t xml:space="preserve">3.08631634712219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08292651176453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09224820137024</t>
+    <t xml:space="preserve">3.08292675018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09224796295166</t>
   </si>
   <si>
     <t xml:space="preserve">3.02360701560974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97445631027222</t>
+    <t xml:space="preserve">2.9744565486908</t>
   </si>
   <si>
     <t xml:space="preserve">3.01428532600403</t>
@@ -3209,25 +3209,25 @@
     <t xml:space="preserve">2.99648952484131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9956419467926</t>
+    <t xml:space="preserve">2.99564218521118</t>
   </si>
   <si>
     <t xml:space="preserve">2.99818420410156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00411605834961</t>
+    <t xml:space="preserve">3.00411629676819</t>
   </si>
   <si>
     <t xml:space="preserve">2.96089768409729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98547315597534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91089963912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87785005569458</t>
+    <t xml:space="preserve">2.98547291755676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91089987754822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87785029411316</t>
   </si>
   <si>
     <t xml:space="preserve">2.91174721717834</t>
@@ -3239,7 +3239,7 @@
     <t xml:space="preserve">2.97530388832092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95327091217041</t>
+    <t xml:space="preserve">2.95327067375183</t>
   </si>
   <si>
     <t xml:space="preserve">2.92445826530457</t>
@@ -3248,16 +3248,16 @@
     <t xml:space="preserve">2.9439492225647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00242114067078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03377604484558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04902982711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01767516136169</t>
+    <t xml:space="preserve">3.00242137908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03377628326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04902958869934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01767492294312</t>
   </si>
   <si>
     <t xml:space="preserve">3.05241942405701</t>
@@ -3272,13 +3272,13 @@
     <t xml:space="preserve">2.99479460716248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03462338447571</t>
+    <t xml:space="preserve">3.03462362289429</t>
   </si>
   <si>
     <t xml:space="preserve">3.1125864982605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09309601783752</t>
+    <t xml:space="preserve">3.09309577941895</t>
   </si>
   <si>
     <t xml:space="preserve">3.0566565990448</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">3.01682758331299</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05750393867493</t>
+    <t xml:space="preserve">3.05750370025635</t>
   </si>
   <si>
     <t xml:space="preserve">3.06936764717102</t>
@@ -3296,13 +3296,13 @@
     <t xml:space="preserve">3.07275748252869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03208136558533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02953886985779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0007266998291</t>
+    <t xml:space="preserve">3.03208112716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02953910827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00072646141052</t>
   </si>
   <si>
     <t xml:space="preserve">2.85581684112549</t>
@@ -3314,10 +3314,10 @@
     <t xml:space="preserve">2.88547682762146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9575080871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88971424102783</t>
+    <t xml:space="preserve">2.95750761032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88971400260925</t>
   </si>
   <si>
     <t xml:space="preserve">3.02530193328857</t>
@@ -3335,34 +3335,34 @@
     <t xml:space="preserve">3.00326871871948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02445459365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04563999176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05072450637817</t>
+    <t xml:space="preserve">3.02445435523987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04564023017883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05072426795959</t>
   </si>
   <si>
     <t xml:space="preserve">3.06089353561401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11682367324829</t>
+    <t xml:space="preserve">3.11682343482971</t>
   </si>
   <si>
     <t xml:space="preserve">3.10241723060608</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14055156707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11173868179321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08716344833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02699685096741</t>
+    <t xml:space="preserve">3.14055132865906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11173892021179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08716368675232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02699661254883</t>
   </si>
   <si>
     <t xml:space="preserve">3.0134379863739</t>
@@ -3371,61 +3371,61 @@
     <t xml:space="preserve">2.99394726753235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97106695175171</t>
+    <t xml:space="preserve">2.97106671333313</t>
   </si>
   <si>
     <t xml:space="preserve">2.98123574256897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94903373718262</t>
+    <t xml:space="preserve">2.94903349876404</t>
   </si>
   <si>
     <t xml:space="preserve">2.9083571434021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91767907142639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97360897064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07614731788635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14817786216736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13377213478088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07021498680115</t>
+    <t xml:space="preserve">2.91767930984497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97360920906067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07614755630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14817810058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1337718963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07021522521973</t>
   </si>
   <si>
     <t xml:space="preserve">2.9388644695282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88039255142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9185266494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93801712989807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92530560493469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86005401611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88717198371887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87276577949524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84310555458069</t>
+    <t xml:space="preserve">2.88039231300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91852641105652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93801736831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92530584335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86005425453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88717174530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87276554107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84310579299927</t>
   </si>
   <si>
     <t xml:space="preserve">2.83802127838135</t>
@@ -3437,7 +3437,7 @@
     <t xml:space="preserve">2.80836129188538</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82446265220642</t>
+    <t xml:space="preserve">2.82446241378784</t>
   </si>
   <si>
     <t xml:space="preserve">2.740567445755</t>
@@ -3467,19 +3467,19 @@
     <t xml:space="preserve">2.87700271606445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86344408988953</t>
+    <t xml:space="preserve">2.86344385147095</t>
   </si>
   <si>
     <t xml:space="preserve">2.85666465759277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85157990455627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81937766075134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85412240028381</t>
+    <t xml:space="preserve">2.85158014297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81937789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85412216186523</t>
   </si>
   <si>
     <t xml:space="preserve">2.89140892028809</t>
@@ -3488,25 +3488,25 @@
     <t xml:space="preserve">2.7880232334137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75666880607605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81429362297058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82700490951538</t>
+    <t xml:space="preserve">2.75666856765747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81429314613342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8270046710968</t>
   </si>
   <si>
     <t xml:space="preserve">2.85327482223511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83547902107239</t>
+    <t xml:space="preserve">2.83547878265381</t>
   </si>
   <si>
     <t xml:space="preserve">2.87615537643433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90751004219055</t>
+    <t xml:space="preserve">2.90750980377197</t>
   </si>
   <si>
     <t xml:space="preserve">3.00581097602844</t>
@@ -3518,10 +3518,10 @@
     <t xml:space="preserve">3.00496363639832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04394507408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05835151672363</t>
+    <t xml:space="preserve">3.0439453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05835127830505</t>
   </si>
   <si>
     <t xml:space="preserve">3.01598024368286</t>
@@ -3533,13 +3533,13 @@
     <t xml:space="preserve">2.97276163101196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98377823829651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9524233341217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98632049560547</t>
+    <t xml:space="preserve">2.98377799987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95242357254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98632025718689</t>
   </si>
   <si>
     <t xml:space="preserve">3.06343579292297</t>
@@ -3551,22 +3551,22 @@
     <t xml:space="preserve">2.86513876914978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92954325675964</t>
+    <t xml:space="preserve">2.92954301834106</t>
   </si>
   <si>
     <t xml:space="preserve">2.95072865486145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03801321983337</t>
+    <t xml:space="preserve">3.03801298141479</t>
   </si>
   <si>
     <t xml:space="preserve">2.98801517486572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96598196029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89056134223938</t>
+    <t xml:space="preserve">2.96598219871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89056181907654</t>
   </si>
   <si>
     <t xml:space="preserve">2.86683344841003</t>
@@ -3584,7 +3584,7 @@
     <t xml:space="preserve">2.83886861801147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7270085811615</t>
+    <t xml:space="preserve">2.72700881958008</t>
   </si>
   <si>
     <t xml:space="preserve">2.53125405311584</t>
@@ -3593,13 +3593,13 @@
     <t xml:space="preserve">2.41685175895691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35668468475342</t>
+    <t xml:space="preserve">2.35668444633484</t>
   </si>
   <si>
     <t xml:space="preserve">2.45837545394897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38888669013977</t>
+    <t xml:space="preserve">2.38888692855835</t>
   </si>
   <si>
     <t xml:space="preserve">2.41769909858704</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">2.3823139667511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34250545501709</t>
+    <t xml:space="preserve">2.34250521659851</t>
   </si>
   <si>
     <t xml:space="preserve">2.32569718360901</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">2.46193051338196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46812319755554</t>
+    <t xml:space="preserve">2.46812295913696</t>
   </si>
   <si>
     <t xml:space="preserve">2.49908542633057</t>
@@ -3629,28 +3629,28 @@
     <t xml:space="preserve">2.47608494758606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44158411026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48758506774902</t>
+    <t xml:space="preserve">2.44158434867859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48758482933044</t>
   </si>
   <si>
     <t xml:space="preserve">2.48493123054504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41327619552612</t>
+    <t xml:space="preserve">2.41327595710754</t>
   </si>
   <si>
     <t xml:space="preserve">2.45750761032104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49112343788147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47696948051453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45927667617798</t>
+    <t xml:space="preserve">2.49112367630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47696924209595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45927691459656</t>
   </si>
   <si>
     <t xml:space="preserve">2.37523674964905</t>
@@ -3665,7 +3665,7 @@
     <t xml:space="preserve">2.38673686981201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41150665283203</t>
+    <t xml:space="preserve">2.41150689125061</t>
   </si>
   <si>
     <t xml:space="preserve">2.38319849967957</t>
@@ -3686,7 +3686,7 @@
     <t xml:space="preserve">2.43008399009705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44689226150513</t>
+    <t xml:space="preserve">2.44689202308655</t>
   </si>
   <si>
     <t xml:space="preserve">2.50970077514648</t>
@@ -3698,22 +3698,22 @@
     <t xml:space="preserve">2.47077679634094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44246888160706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4398148059845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44335341453552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46900749206543</t>
+    <t xml:space="preserve">2.44246864318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43981504440308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4433536529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46900773048401</t>
   </si>
   <si>
     <t xml:space="preserve">2.47520017623901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44954609870911</t>
+    <t xml:space="preserve">2.44954586029053</t>
   </si>
   <si>
     <t xml:space="preserve">2.43804574012756</t>
@@ -3725,13 +3725,13 @@
     <t xml:space="preserve">2.42300701141357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40442991256714</t>
+    <t xml:space="preserve">2.40442967414856</t>
   </si>
   <si>
     <t xml:space="preserve">2.36904430389404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29650449752808</t>
+    <t xml:space="preserve">2.29650473594666</t>
   </si>
   <si>
     <t xml:space="preserve">2.35312104225159</t>
@@ -3740,16 +3740,16 @@
     <t xml:space="preserve">2.21158003807068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21246457099915</t>
+    <t xml:space="preserve">2.21246433258057</t>
   </si>
   <si>
     <t xml:space="preserve">2.24342656135559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18504118919373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07269239425659</t>
+    <t xml:space="preserve">2.18504095077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07269263267517</t>
   </si>
   <si>
     <t xml:space="preserve">2.12842440605164</t>
@@ -3776,16 +3776,16 @@
     <t xml:space="preserve">2.11957812309265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1063084602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07800054550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07357740402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04261517524719</t>
+    <t xml:space="preserve">2.10630869865417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07800030708313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07357716560364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04261541366577</t>
   </si>
   <si>
     <t xml:space="preserve">1.97803711891174</t>
@@ -3800,40 +3800,40 @@
     <t xml:space="preserve">1.9258439540863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91611289978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93380546569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94442081451416</t>
+    <t xml:space="preserve">1.91611266136169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93380570411682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94442105293274</t>
   </si>
   <si>
     <t xml:space="preserve">2.00192213058472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90018939971924</t>
+    <t xml:space="preserve">1.90018951892853</t>
   </si>
   <si>
     <t xml:space="preserve">1.84003448486328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82588028907776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87011206150055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80464923381805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77280247211456</t>
+    <t xml:space="preserve">1.82588016986847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87011218070984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80464911460876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77280235290527</t>
   </si>
   <si>
     <t xml:space="preserve">1.80022609233856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83030354976654</t>
+    <t xml:space="preserve">1.83030343055725</t>
   </si>
   <si>
     <t xml:space="preserve">1.87807369232178</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">1.88249695301056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8630348443985</t>
+    <t xml:space="preserve">1.86303472518921</t>
   </si>
   <si>
     <t xml:space="preserve">1.87541961669922</t>
@@ -3869,16 +3869,16 @@
     <t xml:space="preserve">2.14434790611267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14257860183716</t>
+    <t xml:space="preserve">2.14257884025574</t>
   </si>
   <si>
     <t xml:space="preserve">2.13196301460266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17796397209167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19034862518311</t>
+    <t xml:space="preserve">2.1779637336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19034886360168</t>
   </si>
   <si>
     <t xml:space="preserve">2.23281097412109</t>
@@ -3887,16 +3887,16 @@
     <t xml:space="preserve">2.27969646453857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30800485610962</t>
+    <t xml:space="preserve">2.30800461769104</t>
   </si>
   <si>
     <t xml:space="preserve">2.28058123588562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29915857315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33454346656799</t>
+    <t xml:space="preserve">2.29915833473206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33454370498657</t>
   </si>
   <si>
     <t xml:space="preserve">2.31773567199707</t>
@@ -3911,10 +3911,10 @@
     <t xml:space="preserve">2.32746648788452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30623579025269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34515953063965</t>
+    <t xml:space="preserve">2.30623555183411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34515929222107</t>
   </si>
   <si>
     <t xml:space="preserve">2.35046720504761</t>
@@ -3923,7 +3923,7 @@
     <t xml:space="preserve">2.33188962936401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34338974952698</t>
+    <t xml:space="preserve">2.34338998794556</t>
   </si>
   <si>
     <t xml:space="preserve">2.35400581359863</t>
@@ -3938,7 +3938,7 @@
     <t xml:space="preserve">2.37612152099609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43273782730103</t>
+    <t xml:space="preserve">2.4327380657196</t>
   </si>
   <si>
     <t xml:space="preserve">2.48050808906555</t>
@@ -3947,10 +3947,10 @@
     <t xml:space="preserve">2.50350832939148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4460072517395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3106586933136</t>
+    <t xml:space="preserve">2.44600749015808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31065845489502</t>
   </si>
   <si>
     <t xml:space="preserve">2.25669622421265</t>
@@ -3959,7 +3959,7 @@
     <t xml:space="preserve">2.2726194858551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26200389862061</t>
+    <t xml:space="preserve">2.26200413703918</t>
   </si>
   <si>
     <t xml:space="preserve">2.24165725708008</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">2.22838807106018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28765821456909</t>
+    <t xml:space="preserve">2.28765845298767</t>
   </si>
   <si>
     <t xml:space="preserve">2.2894275188446</t>
@@ -3992,22 +3992,22 @@
     <t xml:space="preserve">2.32304334640503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45043039321899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45131516456604</t>
+    <t xml:space="preserve">2.45043063163757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45131492614746</t>
   </si>
   <si>
     <t xml:space="preserve">2.42389154434204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42919945716858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40708351135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34781312942505</t>
+    <t xml:space="preserve">2.42919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40708374977112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34781336784363</t>
   </si>
   <si>
     <t xml:space="preserve">2.3885064125061</t>
@@ -4022,7 +4022,7 @@
     <t xml:space="preserve">2.39646816253662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34692883491516</t>
+    <t xml:space="preserve">2.34692859649658</t>
   </si>
   <si>
     <t xml:space="preserve">2.340735912323</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">2.37081384658813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31596636772156</t>
+    <t xml:space="preserve">2.31596660614014</t>
   </si>
   <si>
     <t xml:space="preserve">2.28854274749756</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">2.30004286766052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29473567008972</t>
+    <t xml:space="preserve">2.29473543167114</t>
   </si>
   <si>
     <t xml:space="preserve">2.2664270401001</t>
@@ -4064,10 +4064,10 @@
     <t xml:space="preserve">2.22219562530518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23192644119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17530989646912</t>
+    <t xml:space="preserve">2.23192620277405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1753101348877</t>
   </si>
   <si>
     <t xml:space="preserve">2.19477200508118</t>
@@ -4076,7 +4076,7 @@
     <t xml:space="preserve">2.22573399543762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18150234222412</t>
+    <t xml:space="preserve">2.1815025806427</t>
   </si>
   <si>
     <t xml:space="preserve">2.15054035186768</t>
@@ -4100,13 +4100,13 @@
     <t xml:space="preserve">2.18857932090759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20627212524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22131085395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20361828804016</t>
+    <t xml:space="preserve">2.20627188682556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22131061553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20361804962158</t>
   </si>
   <si>
     <t xml:space="preserve">2.21423387527466</t>
@@ -4115,10 +4115,10 @@
     <t xml:space="preserve">2.24254202842712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30181241035461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29827380180359</t>
+    <t xml:space="preserve">2.30181217193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29827404022217</t>
   </si>
   <si>
     <t xml:space="preserve">2.40266036987305</t>
@@ -4142,10 +4142,10 @@
     <t xml:space="preserve">2.49820065498352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44512271881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49643135070801</t>
+    <t xml:space="preserve">2.44512248039246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49643111228943</t>
   </si>
   <si>
     <t xml:space="preserve">2.53181672096252</t>
@@ -4181,7 +4181,7 @@
     <t xml:space="preserve">2.63266491889954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62204909324646</t>
+    <t xml:space="preserve">2.62204885482788</t>
   </si>
   <si>
     <t xml:space="preserve">2.54950928688049</t>
@@ -4190,25 +4190,25 @@
     <t xml:space="preserve">2.5282781124115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57958674430847</t>
+    <t xml:space="preserve">2.57958650588989</t>
   </si>
   <si>
     <t xml:space="preserve">2.58135604858398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60966420173645</t>
+    <t xml:space="preserve">2.60966444015503</t>
   </si>
   <si>
     <t xml:space="preserve">2.58666396141052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59020256996155</t>
+    <t xml:space="preserve">2.59020233154297</t>
   </si>
   <si>
     <t xml:space="preserve">2.53889346122742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.572509765625</t>
+    <t xml:space="preserve">2.57250952720642</t>
   </si>
   <si>
     <t xml:space="preserve">2.54420137405396</t>
@@ -4217,7 +4217,7 @@
     <t xml:space="preserve">2.55304765701294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56366348266602</t>
+    <t xml:space="preserve">2.56366324424744</t>
   </si>
   <si>
     <t xml:space="preserve">2.55127859115601</t>
@@ -4232,7 +4232,7 @@
     <t xml:space="preserve">2.51812791824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52922129631042</t>
+    <t xml:space="preserve">2.52922105789185</t>
   </si>
   <si>
     <t xml:space="preserve">2.53661632537842</t>
@@ -4259,16 +4259,16 @@
     <t xml:space="preserve">2.46451139450073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41274356842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40904593467712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42013907432556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44787192344666</t>
+    <t xml:space="preserve">2.41274380683899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4090461730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42013931274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44787168502808</t>
   </si>
   <si>
     <t xml:space="preserve">2.47375583648682</t>
@@ -4289,10 +4289,10 @@
     <t xml:space="preserve">2.52737212181091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54216289520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53846549987793</t>
+    <t xml:space="preserve">2.54216313362122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53846526145935</t>
   </si>
   <si>
     <t xml:space="preserve">2.58653521537781</t>
@@ -4301,7 +4301,7 @@
     <t xml:space="preserve">2.56250047683716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59393048286438</t>
+    <t xml:space="preserve">2.59393072128296</t>
   </si>
   <si>
     <t xml:space="preserve">2.63275647163391</t>
@@ -4316,10 +4316,10 @@
     <t xml:space="preserve">2.60132598876953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45711612701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39980173110962</t>
+    <t xml:space="preserve">2.45711588859558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3998019695282</t>
   </si>
   <si>
     <t xml:space="preserve">2.44602274894714</t>
@@ -4331,10 +4331,10 @@
     <t xml:space="preserve">2.47190690040588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47005772590637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42383694648743</t>
+    <t xml:space="preserve">2.47005796432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42383670806885</t>
   </si>
   <si>
     <t xml:space="preserve">2.38316226005554</t>
@@ -4346,34 +4346,34 @@
     <t xml:space="preserve">2.49594187736511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52182579040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5403139591217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55140709877014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57913994789124</t>
+    <t xml:space="preserve">2.52182555198669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54031419754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55140733718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57913970947266</t>
   </si>
   <si>
     <t xml:space="preserve">2.5680468082428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58468627929688</t>
+    <t xml:space="preserve">2.58468651771545</t>
   </si>
   <si>
     <t xml:space="preserve">2.57544207572937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54770970344543</t>
+    <t xml:space="preserve">2.54770946502686</t>
   </si>
   <si>
     <t xml:space="preserve">2.60687255859375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60317468643188</t>
+    <t xml:space="preserve">2.60317492485046</t>
   </si>
   <si>
     <t xml:space="preserve">2.6456983089447</t>
@@ -4397,7 +4397,7 @@
     <t xml:space="preserve">2.667884349823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69376826286316</t>
+    <t xml:space="preserve">2.69376850128174</t>
   </si>
   <si>
     <t xml:space="preserve">2.56434917449951</t>
@@ -4430,22 +4430,22 @@
     <t xml:space="preserve">2.35358071327209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39795327186584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41089487075806</t>
+    <t xml:space="preserve">2.39795303344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41089510917664</t>
   </si>
   <si>
     <t xml:space="preserve">2.42753434181213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40534853935242</t>
+    <t xml:space="preserve">2.40534830093384</t>
   </si>
   <si>
     <t xml:space="preserve">2.39240646362305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37206935882568</t>
+    <t xml:space="preserve">2.3720691204071</t>
   </si>
   <si>
     <t xml:space="preserve">2.34988307952881</t>
@@ -4460,7 +4460,7 @@
     <t xml:space="preserve">2.34803414344788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45341825485229</t>
+    <t xml:space="preserve">2.45341849327087</t>
   </si>
   <si>
     <t xml:space="preserve">2.49224424362183</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">2.49779057502747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4626624584198</t>
+    <t xml:space="preserve">2.46266269683838</t>
   </si>
   <si>
     <t xml:space="preserve">2.45526719093323</t>
@@ -4487,7 +4487,7 @@
     <t xml:space="preserve">2.62536096572876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64015173912048</t>
+    <t xml:space="preserve">2.64015197753906</t>
   </si>
   <si>
     <t xml:space="preserve">2.62720990180969</t>
@@ -4496,19 +4496,19 @@
     <t xml:space="preserve">2.63090753555298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68082642555237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68637299537659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68822193145752</t>
+    <t xml:space="preserve">2.68082666397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68637275695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68822169303894</t>
   </si>
   <si>
     <t xml:space="preserve">2.66603565216064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68267512321472</t>
+    <t xml:space="preserve">2.6826753616333</t>
   </si>
   <si>
     <t xml:space="preserve">2.68452405929565</t>
@@ -4517,19 +4517,19 @@
     <t xml:space="preserve">2.69007062911987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74368691444397</t>
+    <t xml:space="preserve">2.74368715286255</t>
   </si>
   <si>
     <t xml:space="preserve">2.71225690841675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69561719894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73444271087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80100131034851</t>
+    <t xml:space="preserve">2.69561696052551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73444294929504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80100154876709</t>
   </si>
   <si>
     <t xml:space="preserve">2.78990817070007</t>
@@ -4541,7 +4541,7 @@
     <t xml:space="preserve">2.79545474052429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78621077537537</t>
+    <t xml:space="preserve">2.78621053695679</t>
   </si>
   <si>
     <t xml:space="preserve">2.76772212982178</t>
@@ -4553,7 +4553,7 @@
     <t xml:space="preserve">2.75662922859192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73998951911926</t>
+    <t xml:space="preserve">2.73998928070068</t>
   </si>
   <si>
     <t xml:space="preserve">2.74738478660583</t>
@@ -4601,22 +4601,22 @@
     <t xml:space="preserve">2.98033928871155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96924638748169</t>
+    <t xml:space="preserve">2.96924614906311</t>
   </si>
   <si>
     <t xml:space="preserve">3.02286291122437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92672300338745</t>
+    <t xml:space="preserve">2.92672276496887</t>
   </si>
   <si>
     <t xml:space="preserve">2.91562986373901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87495493888855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90083909034729</t>
+    <t xml:space="preserve">2.87495517730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90083885192871</t>
   </si>
   <si>
     <t xml:space="preserve">2.9193274974823</t>
@@ -4643,7 +4643,7 @@
     <t xml:space="preserve">2.99513030052185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98773503303528</t>
+    <t xml:space="preserve">2.9877347946167</t>
   </si>
   <si>
     <t xml:space="preserve">2.98958349227905</t>
@@ -4652,16 +4652,16 @@
     <t xml:space="preserve">2.93411827087402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96000218391418</t>
+    <t xml:space="preserve">2.96000194549561</t>
   </si>
   <si>
     <t xml:space="preserve">2.94890904426575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95445561408997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97849059104919</t>
+    <t xml:space="preserve">2.95445585250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97849035263062</t>
   </si>
   <si>
     <t xml:space="preserve">2.95260691642761</t>
@@ -4685,10 +4685,10 @@
     <t xml:space="preserve">3.08572363853455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09496784210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11900305747986</t>
+    <t xml:space="preserve">3.09496808052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11900281906128</t>
   </si>
   <si>
     <t xml:space="preserve">3.05983972549438</t>
@@ -4706,13 +4706,13 @@
     <t xml:space="preserve">3.06908392906189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02471160888672</t>
+    <t xml:space="preserve">3.0247118473053</t>
   </si>
   <si>
     <t xml:space="preserve">3.01916527748108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97479271888733</t>
+    <t xml:space="preserve">2.97479295730591</t>
   </si>
   <si>
     <t xml:space="preserve">2.92302513122559</t>
@@ -4721,7 +4721,7 @@
     <t xml:space="preserve">2.93781590461731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88419914245605</t>
+    <t xml:space="preserve">2.88419938087463</t>
   </si>
   <si>
     <t xml:space="preserve">2.90823435783386</t>
@@ -4736,19 +4736,19 @@
     <t xml:space="preserve">2.95815324783325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97109532356262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01546740531921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11345624923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13933992385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10975885391235</t>
+    <t xml:space="preserve">2.97109508514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01546764373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11345648765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13934016227722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10975861549377</t>
   </si>
   <si>
     <t xml:space="preserve">3.16337513923645</t>
@@ -4757,7 +4757,7 @@
     <t xml:space="preserve">3.13379383087158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15782833099365</t>
+    <t xml:space="preserve">3.15782856941223</t>
   </si>
   <si>
     <t xml:space="preserve">3.16892170906067</t>
@@ -4766,7 +4766,7 @@
     <t xml:space="preserve">3.19480562210083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24287557601929</t>
+    <t xml:space="preserve">3.24287533760071</t>
   </si>
   <si>
     <t xml:space="preserve">3.20959615707397</t>
@@ -4775,7 +4775,7 @@
     <t xml:space="preserve">3.20589852333069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23548007011414</t>
+    <t xml:space="preserve">3.23548030853271</t>
   </si>
   <si>
     <t xml:space="preserve">3.29464316368103</t>
@@ -4790,10 +4790,10 @@
     <t xml:space="preserve">3.20774745941162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17446804046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12085175514221</t>
+    <t xml:space="preserve">3.17446827888489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12085151672363</t>
   </si>
   <si>
     <t xml:space="preserve">3.07832813262939</t>
@@ -4805,7 +4805,7 @@
     <t xml:space="preserve">3.09866547584534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07647967338562</t>
+    <t xml:space="preserve">3.07647943496704</t>
   </si>
   <si>
     <t xml:space="preserve">3.06723523139954</t>
@@ -4820,19 +4820,19 @@
     <t xml:space="preserve">3.19665431976318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20404982566833</t>
+    <t xml:space="preserve">3.20405006408691</t>
   </si>
   <si>
     <t xml:space="preserve">3.19850325584412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1245493888855</t>
+    <t xml:space="preserve">3.12454962730408</t>
   </si>
   <si>
     <t xml:space="preserve">3.16707301139832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14858412742615</t>
+    <t xml:space="preserve">3.14858436584473</t>
   </si>
   <si>
     <t xml:space="preserve">3.00067663192749</t>
@@ -4841,7 +4841,7 @@
     <t xml:space="preserve">3.04874682426453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10051465034485</t>
+    <t xml:space="preserve">3.10051441192627</t>
   </si>
   <si>
     <t xml:space="preserve">3.14488673210144</t>
@@ -5739,6 +5739,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.17999982833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23000001907349</t>
   </si>
 </sst>
 </file>
@@ -10385,7 +10388,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G166" t="s">
-        <v>120</v>
+        <v>62</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -10437,7 +10440,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G168" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -10489,7 +10492,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G170" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -10515,7 +10518,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G171" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -10567,7 +10570,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G173" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -10593,7 +10596,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G174" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -10619,7 +10622,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G175" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -10645,7 +10648,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G176" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -10723,7 +10726,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G179" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -10749,7 +10752,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G180" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -10801,7 +10804,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G182" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -10827,7 +10830,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G183" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -10853,7 +10856,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G184" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -10879,7 +10882,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G185" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -10905,7 +10908,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G186" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -10931,7 +10934,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G187" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -10957,7 +10960,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G188" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -10983,7 +10986,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G189" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -11009,7 +11012,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G190" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -11035,7 +11038,7 @@
         <v>2.33599996566772</v>
       </c>
       <c r="G191" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -11061,7 +11064,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G192" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -11087,7 +11090,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G193" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -11113,7 +11116,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G194" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -11139,7 +11142,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G195" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -11165,7 +11168,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G196" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -11191,7 +11194,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G197" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -11217,7 +11220,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G198" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -11243,7 +11246,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G199" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -11269,7 +11272,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G200" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -11295,7 +11298,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G201" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -11321,7 +11324,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G202" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -11347,7 +11350,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G203" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -11373,7 +11376,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G204" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -11399,7 +11402,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G205" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -11425,7 +11428,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G206" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -11451,7 +11454,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G207" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -11477,7 +11480,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G208" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -11503,7 +11506,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G209" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -11529,7 +11532,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G210" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -11555,7 +11558,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G211" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -11581,7 +11584,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G212" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -11607,7 +11610,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G213" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -11633,7 +11636,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G214" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -11685,7 +11688,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G216" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -11711,7 +11714,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G217" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -11737,7 +11740,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G218" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -11763,7 +11766,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G219" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -11789,7 +11792,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G220" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -11815,7 +11818,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G221" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -11841,7 +11844,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G222" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -11867,7 +11870,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G223" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -11893,7 +11896,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G224" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -11919,7 +11922,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G225" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -11945,7 +11948,7 @@
         <v>2.00200009346008</v>
       </c>
       <c r="G226" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -11971,7 +11974,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G227" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -11997,7 +12000,7 @@
         <v>1.96300005912781</v>
       </c>
       <c r="G228" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -12023,7 +12026,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G229" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -12049,7 +12052,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G230" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -12075,7 +12078,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G231" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -12101,7 +12104,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G232" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -12127,7 +12130,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G233" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -12153,7 +12156,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G234" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -12179,7 +12182,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G235" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -12205,7 +12208,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G236" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -12231,7 +12234,7 @@
         <v>1.90699994564056</v>
       </c>
       <c r="G237" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -12257,7 +12260,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G238" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -12283,7 +12286,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G239" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -12309,7 +12312,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G240" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -12335,7 +12338,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G241" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -12361,7 +12364,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G242" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -12387,7 +12390,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G243" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -12413,7 +12416,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G244" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -12439,7 +12442,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G245" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -12465,7 +12468,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G246" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -12491,7 +12494,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G247" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -12517,7 +12520,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G248" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -12543,7 +12546,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G249" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -12569,7 +12572,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G250" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -12595,7 +12598,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G251" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -12621,7 +12624,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G252" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -12647,7 +12650,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G253" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -12673,7 +12676,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G254" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -12699,7 +12702,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G255" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -12725,7 +12728,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G256" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -12751,7 +12754,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G257" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -12777,7 +12780,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G258" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -12803,7 +12806,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G259" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -12829,7 +12832,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G260" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -12855,7 +12858,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G261" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -12881,7 +12884,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G262" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -12907,7 +12910,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G263" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -12933,7 +12936,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G264" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -12959,7 +12962,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G265" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -12985,7 +12988,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G266" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -13011,7 +13014,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G267" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -13037,7 +13040,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G268" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -13063,7 +13066,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G269" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -13089,7 +13092,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G270" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -13115,7 +13118,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G271" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -13141,7 +13144,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G272" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -13167,7 +13170,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G273" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -13193,7 +13196,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G274" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -13219,7 +13222,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G275" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -13245,7 +13248,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G276" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -13271,7 +13274,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G277" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -13297,7 +13300,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G278" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -13323,7 +13326,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G279" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -13349,7 +13352,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G280" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -13375,7 +13378,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G281" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -13401,7 +13404,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G282" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -13427,7 +13430,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G283" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -13453,7 +13456,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G284" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -13479,7 +13482,7 @@
         <v>2.25</v>
       </c>
       <c r="G285" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -13505,7 +13508,7 @@
         <v>2.25</v>
       </c>
       <c r="G286" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -13531,7 +13534,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G287" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -13557,7 +13560,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G288" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -13583,7 +13586,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G289" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -13609,7 +13612,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G290" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -13635,7 +13638,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G291" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -13661,7 +13664,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G292" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -13687,7 +13690,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G293" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -13713,7 +13716,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G294" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -13739,7 +13742,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G295" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -13765,7 +13768,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G296" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -13791,7 +13794,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G297" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -13817,7 +13820,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G298" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -13843,7 +13846,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G299" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -13895,7 +13898,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G301" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -13921,7 +13924,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G302" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -13947,7 +13950,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G303" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -13973,7 +13976,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G304" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -13999,7 +14002,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G305" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -14025,7 +14028,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G306" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -14051,7 +14054,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G307" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -14077,7 +14080,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G308" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -14103,7 +14106,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G309" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -14129,7 +14132,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G310" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -14155,7 +14158,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G311" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -14181,7 +14184,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G312" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -14207,7 +14210,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G313" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -14233,7 +14236,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G314" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -14259,7 +14262,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G315" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -14285,7 +14288,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G316" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -14311,7 +14314,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G317" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -14337,7 +14340,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G318" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -14363,7 +14366,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G319" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -14389,7 +14392,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G320" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -14415,7 +14418,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G321" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -14441,7 +14444,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G322" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -14467,7 +14470,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G323" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -14493,7 +14496,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G324" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -14519,7 +14522,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G325" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -14545,7 +14548,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G326" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -14571,7 +14574,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G327" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -14597,7 +14600,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G328" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -14623,7 +14626,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G329" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -14649,7 +14652,7 @@
         <v>2.67400002479553</v>
       </c>
       <c r="G330" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -14675,7 +14678,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G331" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -14701,7 +14704,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G332" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -14727,7 +14730,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G333" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -14753,7 +14756,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G334" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -14779,7 +14782,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G335" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -14805,7 +14808,7 @@
         <v>2.66199994087219</v>
       </c>
       <c r="G336" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -14831,7 +14834,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G337" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -14857,7 +14860,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G338" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -14883,7 +14886,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G339" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -14909,7 +14912,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G340" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -14935,7 +14938,7 @@
         <v>2.64599990844727</v>
       </c>
       <c r="G341" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -14961,7 +14964,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G342" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -14987,7 +14990,7 @@
         <v>2.67199993133545</v>
       </c>
       <c r="G343" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -15013,7 +15016,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G344" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -15039,7 +15042,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G345" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -15065,7 +15068,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G346" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -15091,7 +15094,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G347" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -15117,7 +15120,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G348" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -15143,7 +15146,7 @@
         <v>2.85599994659424</v>
       </c>
       <c r="G349" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -15169,7 +15172,7 @@
         <v>2.83200001716614</v>
       </c>
       <c r="G350" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -15195,7 +15198,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G351" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -15221,7 +15224,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G352" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -15247,7 +15250,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G353" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -15273,7 +15276,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G354" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -15299,7 +15302,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G355" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -15325,7 +15328,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G356" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -15351,7 +15354,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G357" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -15377,7 +15380,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G358" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -15403,7 +15406,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G359" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -15429,7 +15432,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G360" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -15455,7 +15458,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G361" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -15481,7 +15484,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G362" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -15507,7 +15510,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G363" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -15533,7 +15536,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G364" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -15559,7 +15562,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G365" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -15585,7 +15588,7 @@
         <v>2.90400004386902</v>
       </c>
       <c r="G366" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -15611,7 +15614,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G367" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -15637,7 +15640,7 @@
         <v>2.92600011825562</v>
       </c>
       <c r="G368" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -15663,7 +15666,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G369" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -15689,7 +15692,7 @@
         <v>2.96399998664856</v>
       </c>
       <c r="G370" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -15715,7 +15718,7 @@
         <v>2.94400000572205</v>
       </c>
       <c r="G371" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -15741,7 +15744,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="G372" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -15767,7 +15770,7 @@
         <v>2.95799994468689</v>
       </c>
       <c r="G373" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -15793,7 +15796,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G374" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -15819,7 +15822,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G375" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -15845,7 +15848,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G376" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -15871,7 +15874,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G377" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -15897,7 +15900,7 @@
         <v>2.88599991798401</v>
       </c>
       <c r="G378" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -18653,7 +18656,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G484" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -18705,7 +18708,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G486" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -72377,7 +72380,7 @@
     </row>
     <row r="2551">
       <c r="A2551" s="1" t="n">
-        <v>46037.6912847222</v>
+        <v>46037.3333333333</v>
       </c>
       <c r="B2551" t="n">
         <v>2823838</v>
@@ -72398,6 +72401,32 @@
         <v>1908</v>
       </c>
       <c r="H2551" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2552">
+      <c r="A2552" s="1" t="n">
+        <v>46038.6912037037</v>
+      </c>
+      <c r="B2552" t="n">
+        <v>3467586</v>
+      </c>
+      <c r="C2552" t="n">
+        <v>4.22599983215332</v>
+      </c>
+      <c r="D2552" t="n">
+        <v>4.17999982833862</v>
+      </c>
+      <c r="E2552" t="n">
+        <v>4.19399976730347</v>
+      </c>
+      <c r="F2552" t="n">
+        <v>4.23000001907349</v>
+      </c>
+      <c r="G2552" t="s">
+        <v>1909</v>
+      </c>
+      <c r="H2552" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HER.MI.xlsx
+++ b/data/HER.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1910" uniqueCount="1910">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1911" uniqueCount="1911">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,22 +44,22 @@
     <t xml:space="preserve">HER.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7089638710022</t>
+    <t xml:space="preserve">1.70896399021149</t>
   </si>
   <si>
     <t xml:space="preserve">1.70616900920868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71036100387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68800330162048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7257319688797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79140746593475</t>
+    <t xml:space="preserve">1.71036112308502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68800354003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72573208808899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79140758514404</t>
   </si>
   <si>
     <t xml:space="preserve">1.79420256614685</t>
@@ -71,34 +71,34 @@
     <t xml:space="preserve">1.74669229984283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70337438583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77324223518372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74948692321777</t>
+    <t xml:space="preserve">1.70337426662445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77324199676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74948716163635</t>
   </si>
   <si>
     <t xml:space="preserve">1.76625514030457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80538129806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79001009464264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80398368835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83472585678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81655979156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80258619785309</t>
+    <t xml:space="preserve">1.80538105964661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79001033306122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80398380756378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83472561836243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8165602684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80258631706238</t>
   </si>
   <si>
     <t xml:space="preserve">1.84869933128357</t>
@@ -107,46 +107,46 @@
     <t xml:space="preserve">1.85568583011627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84031522274017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82354652881622</t>
+    <t xml:space="preserve">1.84031510353088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82354664802551</t>
   </si>
   <si>
     <t xml:space="preserve">1.82913613319397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72852683067322</t>
+    <t xml:space="preserve">1.72852671146393</t>
   </si>
   <si>
     <t xml:space="preserve">1.74110293388367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75926828384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6991822719574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75507652759552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7955995798111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78302359580994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77603673934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79839420318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80118930339813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82075214385986</t>
+    <t xml:space="preserve">1.7592681646347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69918215274811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75507664680481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79559946060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78302347660065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77603685855865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79839432239532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80118894577026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82075178623199</t>
   </si>
   <si>
     <t xml:space="preserve">1.83053338527679</t>
@@ -155,43 +155,43 @@
     <t xml:space="preserve">1.78861284255981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76485764980316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74529492855072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73970568180084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72992444038391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74389779567719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73271882534027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76346051692963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77883148193359</t>
+    <t xml:space="preserve">1.76485788822174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74529504776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73970544338226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72992420196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7438976764679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73271894454956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76346039772034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7788313627243</t>
   </si>
   <si>
     <t xml:space="preserve">1.76066589355469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77463948726654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79699695110321</t>
+    <t xml:space="preserve">1.77463924884796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7969970703125</t>
   </si>
   <si>
     <t xml:space="preserve">1.83752036094666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81097066402435</t>
+    <t xml:space="preserve">1.81097054481506</t>
   </si>
   <si>
     <t xml:space="preserve">1.85708332061768</t>
@@ -200,220 +200,223 @@
     <t xml:space="preserve">1.84310972690582</t>
   </si>
   <si>
+    <t xml:space="preserve">1.76765275001526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78162586688995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7872154712677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77743411064148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78022861480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80817556381226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80957305431366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79280507564545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78442060947418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75647354125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74808990955353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82634150981903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84590435028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83193075656891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84450721740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82214951515198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83332824707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82494401931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81376516819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76206314563751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73132133483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74250030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71175861358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75751042366028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77344822883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74012362957001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75895941257477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70390105247498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67347431182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70969665050507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73867464065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78069245815277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83430182933807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80822169780731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81111931800842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78503930568695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77924394607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72708356380463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76040816307068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74591910839081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77055037021637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76620364189148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76185691356659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76910138130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77489721775055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78359055519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83719956874847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85748398303986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85023951530457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83575069904327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8661777973175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83140397071838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84444403648376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79663062095642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81981325149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81256854534149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74881708621979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74447023868561</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.76765251159668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78162622451782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7872154712677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7774338722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78022885322571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80817604064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80957305431366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79280471801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78442096710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75647377967834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74808967113495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82634150981903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84590482711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8319308757782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84450733661652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82214939594269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83332824707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82494401931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81376516819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76206314563751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73132133483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74250030517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71175837516785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75751030445099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77344834804535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7401237487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75895941257477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70390129089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67347431182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70969665050507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73867499828339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78069293498993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83430194854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80822157859802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81111991405487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78503954410553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77924382686615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72708368301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76040804386139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74591910839081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77055060863495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76620376110077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76185715198517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76910138130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77489721775055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78359031677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83719968795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85748398303986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85023939609528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83575069904327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8661777973175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83140397071838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84444415569305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79663062095642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81981289386749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81256830692291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7488169670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74447023868561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77634584903717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79083490371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79952836036682</t>
+    <t xml:space="preserve">1.77634620666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79083502292633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79952824115753</t>
   </si>
   <si>
     <t xml:space="preserve">1.78648829460144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78938603401184</t>
+    <t xml:space="preserve">1.78938615322113</t>
   </si>
   <si>
     <t xml:space="preserve">1.8154661655426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75606119632721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73577702045441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70679903030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73722577095032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75461268424988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71114563941956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70824790000916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70245230197906</t>
+    <t xml:space="preserve">1.75606155395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73577666282654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70679914951324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73722589015961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75461256504059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71114552021027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70824813842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70245242118835</t>
   </si>
   <si>
     <t xml:space="preserve">1.69231009483337</t>
@@ -422,67 +425,67 @@
     <t xml:space="preserve">1.71694099903107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69665682315826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63145673274994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60537660121918</t>
+    <t xml:space="preserve">1.69665670394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63145661354065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60537648200989</t>
   </si>
   <si>
     <t xml:space="preserve">1.59233629703522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57929646968842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60102927684784</t>
+    <t xml:space="preserve">1.57929635047913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60102963447571</t>
   </si>
   <si>
     <t xml:space="preserve">1.6097229719162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61406946182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62131404876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63290512561798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61841630935669</t>
+    <t xml:space="preserve">1.61406970024109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6213139295578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63290524482727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61841642856598</t>
   </si>
   <si>
     <t xml:space="preserve">1.63870096206665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63725197315216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65029227733612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62276303768158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61551856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61696743965149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62566089630127</t>
+    <t xml:space="preserve">1.63725221157074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65029203891754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62276291847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61551868915558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6169673204422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62566101551056</t>
   </si>
   <si>
     <t xml:space="preserve">1.66188323497772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66912746429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68796372413635</t>
+    <t xml:space="preserve">1.66912758350372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68796324729919</t>
   </si>
   <si>
     <t xml:space="preserve">1.59378528594971</t>
@@ -500,31 +503,31 @@
     <t xml:space="preserve">1.46048676967621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4633846282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44599795341492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44527316093445</t>
+    <t xml:space="preserve">1.46338450908661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44599783420563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44527328014374</t>
   </si>
   <si>
     <t xml:space="preserve">1.45034468173981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43005990982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42209112644196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39601111412048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39456212520599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40905094146729</t>
+    <t xml:space="preserve">1.43006002902985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42209100723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39601075649261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3945620059967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40905106067657</t>
   </si>
   <si>
     <t xml:space="preserve">1.41267323493958</t>
@@ -539,10 +542,10 @@
     <t xml:space="preserve">1.40542876720428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41629564762115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38152182102203</t>
+    <t xml:space="preserve">1.41629540920258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38152194023132</t>
   </si>
   <si>
     <t xml:space="preserve">1.35906410217285</t>
@@ -551,10 +554,10 @@
     <t xml:space="preserve">1.37717533111572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43875336647034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48077118396759</t>
+    <t xml:space="preserve">1.43875348567963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48077142238617</t>
   </si>
   <si>
     <t xml:space="preserve">1.49236249923706</t>
@@ -569,7 +572,7 @@
     <t xml:space="preserve">1.5271360874176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50105583667755</t>
+    <t xml:space="preserve">1.50105595588684</t>
   </si>
   <si>
     <t xml:space="preserve">1.50685131549835</t>
@@ -587,28 +590,28 @@
     <t xml:space="preserve">1.59088742733002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56915390491486</t>
+    <t xml:space="preserve">1.56915378570557</t>
   </si>
   <si>
     <t xml:space="preserve">1.58798944950104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60827434062958</t>
+    <t xml:space="preserve">1.608274102211</t>
   </si>
   <si>
     <t xml:space="preserve">1.59668302536011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5995808839798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56480741500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65174114704132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64159882068634</t>
+    <t xml:space="preserve">1.59958076477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56480729579926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65174090862274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64159858226776</t>
   </si>
   <si>
     <t xml:space="preserve">1.65318989753723</t>
@@ -617,31 +620,31 @@
     <t xml:space="preserve">1.65463852882385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65898525714874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64014983177185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64304745197296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57494962215424</t>
+    <t xml:space="preserve">1.65898537635803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64014971256256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64304769039154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57494938373566</t>
   </si>
   <si>
     <t xml:space="preserve">1.57784724235535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55176734924316</t>
+    <t xml:space="preserve">1.5517669916153</t>
   </si>
   <si>
     <t xml:space="preserve">1.58654081821442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63000750541687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68216800689697</t>
+    <t xml:space="preserve">1.63000774383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68216776847839</t>
   </si>
   <si>
     <t xml:space="preserve">1.66622996330261</t>
@@ -653,46 +656,46 @@
     <t xml:space="preserve">1.69086134433746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69375920295715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69810569286346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69520807266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71404373645782</t>
+    <t xml:space="preserve">1.69375896453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69810581207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69520795345306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71404337882996</t>
   </si>
   <si>
     <t xml:space="preserve">1.72998142242432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7343282699585</t>
+    <t xml:space="preserve">1.73432803153992</t>
   </si>
   <si>
     <t xml:space="preserve">1.71983909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72418582439423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71549236774445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71839022636414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74157226085663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78214168548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78793692588806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8140172958374</t>
+    <t xml:space="preserve">1.72418594360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71549212932587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71839010715485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7415726184845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78214192390442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78793716430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81401741504669</t>
   </si>
   <si>
     <t xml:space="preserve">1.82995522022247</t>
@@ -701,73 +704,73 @@
     <t xml:space="preserve">1.86907541751862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89950203895569</t>
+    <t xml:space="preserve">1.8995019197464</t>
   </si>
   <si>
     <t xml:space="preserve">1.91399121284485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91544020175934</t>
+    <t xml:space="preserve">1.91543972492218</t>
   </si>
   <si>
     <t xml:space="preserve">1.88066649436951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87197327613831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88936018943787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90095114707947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90529775619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91254258155823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94441783428192</t>
+    <t xml:space="preserve">1.87197303771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88936007022858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90095138549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9052973985672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91254246234894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94441795349121</t>
   </si>
   <si>
     <t xml:space="preserve">1.93717348575592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87921762466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88356423377991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92848002910614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89805340766907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88791108131409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90240001678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91688859462738</t>
+    <t xml:space="preserve">1.87921750545502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88356459140778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92847990989685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89805293083191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88791084289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90240025520325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91688895225525</t>
   </si>
   <si>
     <t xml:space="preserve">1.92413318157196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93572473526001</t>
+    <t xml:space="preserve">1.93572437763214</t>
   </si>
   <si>
     <t xml:space="preserve">1.93862223625183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94876444339752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99512946605682</t>
+    <t xml:space="preserve">1.94876480102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99512922763824</t>
   </si>
   <si>
     <t xml:space="preserve">2.0284538269043</t>
@@ -785,10 +788,10 @@
     <t xml:space="preserve">2.1023473739624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06467628479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0385959148407</t>
+    <t xml:space="preserve">2.06467604637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03859567642212</t>
   </si>
   <si>
     <t xml:space="preserve">2.0733699798584</t>
@@ -797,7 +800,7 @@
     <t xml:space="preserve">2.08640956878662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12842774391174</t>
+    <t xml:space="preserve">2.12842726707458</t>
   </si>
   <si>
     <t xml:space="preserve">2.11248970031738</t>
@@ -812,55 +815,52 @@
     <t xml:space="preserve">2.05453395843506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08930778503418</t>
+    <t xml:space="preserve">2.08930730819702</t>
   </si>
   <si>
     <t xml:space="preserve">2.12263202667236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07916498184204</t>
+    <t xml:space="preserve">2.07916522026062</t>
   </si>
   <si>
     <t xml:space="preserve">2.10379648208618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11973428726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10814332962036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14726328849792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13277435302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15450763702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14291620254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15595698356628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16790914535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17836785316467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17239141464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15595674514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09918189048767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11262845993042</t>
+    <t xml:space="preserve">2.11973404884338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10814309120178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1472635269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13277411460876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1545078754425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14291644096375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15595650672913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16790890693665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17836761474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17239165306091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09918165206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.112628698349</t>
   </si>
   <si>
     <t xml:space="preserve">2.07228827476501</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">2.05884146690369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01700735092163</t>
+    <t xml:space="preserve">2.01700711250305</t>
   </si>
   <si>
     <t xml:space="preserve">1.99907839298248</t>
@@ -878,19 +878,19 @@
     <t xml:space="preserve">2.01103091239929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00804257392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99758422374725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95126783847809</t>
+    <t xml:space="preserve">2.00804328918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99758434295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95126807689667</t>
   </si>
   <si>
     <t xml:space="preserve">1.97069072723389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00505495071411</t>
+    <t xml:space="preserve">2.00505447387695</t>
   </si>
   <si>
     <t xml:space="preserve">1.98264336585999</t>
@@ -899,19 +899,19 @@
     <t xml:space="preserve">2.03045415878296</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05286526679993</t>
+    <t xml:space="preserve">2.05286502838135</t>
   </si>
   <si>
     <t xml:space="preserve">2.0394184589386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03194808959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04539465904236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02447772026062</t>
+    <t xml:space="preserve">2.03194832801819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04539489746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0244779586792</t>
   </si>
   <si>
     <t xml:space="preserve">2.06182980537415</t>
@@ -923,55 +923,55 @@
     <t xml:space="preserve">2.03344202041626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01401948928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05435967445374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04390096664429</t>
+    <t xml:space="preserve">2.01401925086975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05435943603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04390072822571</t>
   </si>
   <si>
     <t xml:space="preserve">2.04240679740906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03643012046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04838299751282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04987716674805</t>
+    <t xml:space="preserve">2.0364305973053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0483832359314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04987692832947</t>
   </si>
   <si>
     <t xml:space="preserve">2.00206661224365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05585336685181</t>
+    <t xml:space="preserve">2.05585384368896</t>
   </si>
   <si>
     <t xml:space="preserve">2.03493618965149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99459624290466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97517335414886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96172654628754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96770286560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02597188949585</t>
+    <t xml:space="preserve">1.99459612369537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97517311573029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96172630786896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9677027463913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02597165107727</t>
   </si>
   <si>
     <t xml:space="preserve">2.01252508163452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00953674316406</t>
+    <t xml:space="preserve">2.00953698158264</t>
   </si>
   <si>
     <t xml:space="preserve">2.0035605430603</t>
@@ -986,142 +986,142 @@
     <t xml:space="preserve">2.000572681427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98563182353973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98712551593781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9721851348877</t>
+    <t xml:space="preserve">1.98563170433044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98712575435638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97218537330627</t>
   </si>
   <si>
     <t xml:space="preserve">2.02148962020874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03792428970337</t>
+    <t xml:space="preserve">2.03792476654053</t>
   </si>
   <si>
     <t xml:space="preserve">2.06033563613892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07079410552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07378244400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06631183624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06332397460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07527661323547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08424115180969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10665202140808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12458109855652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14998078346252</t>
+    <t xml:space="preserve">2.07079434394836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07378220558167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06631207466125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0633237361908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07527613639832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08424091339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1066517829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1245813369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14998054504395</t>
   </si>
   <si>
     <t xml:space="preserve">2.16043901443481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18135643005371</t>
+    <t xml:space="preserve">2.18135595321655</t>
   </si>
   <si>
     <t xml:space="preserve">2.19629693031311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18733239173889</t>
+    <t xml:space="preserve">2.18733263015747</t>
   </si>
   <si>
     <t xml:space="preserve">2.1798620223999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16641545295715</t>
+    <t xml:space="preserve">2.16641521453857</t>
   </si>
   <si>
     <t xml:space="preserve">2.17089748382568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.191814661026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19330883026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19480276107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22468400001526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.271000623703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2560601234436</t>
+    <t xml:space="preserve">2.19181442260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19330859184265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19480323791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22468447685242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27100086212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25606036186218</t>
   </si>
   <si>
     <t xml:space="preserve">2.2590479850769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28145956993103</t>
+    <t xml:space="preserve">2.28145909309387</t>
   </si>
   <si>
     <t xml:space="preserve">2.2949059009552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30536437034607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30088233947754</t>
+    <t xml:space="preserve">2.30536484718323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30088257789612</t>
   </si>
   <si>
     <t xml:space="preserve">2.33972859382629</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28892993927002</t>
+    <t xml:space="preserve">2.28892970085144</t>
   </si>
   <si>
     <t xml:space="preserve">2.27398896217346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30387043952942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31582283973694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25456571578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25755405426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27847099304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22916674613953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22617840766907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21870803833008</t>
+    <t xml:space="preserve">2.303870677948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31582355499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25456619262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25755429267883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27847123146057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22916650772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22617864608765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21870827674866</t>
   </si>
   <si>
     <t xml:space="preserve">2.17388582229614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15446281433105</t>
+    <t xml:space="preserve">2.15446257591248</t>
   </si>
   <si>
     <t xml:space="preserve">2.21123766899109</t>
@@ -1130,13 +1130,13 @@
     <t xml:space="preserve">2.26054239273071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31134104728699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24111938476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26950693130493</t>
+    <t xml:space="preserve">2.31134128570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24111914634705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26950669288635</t>
   </si>
   <si>
     <t xml:space="preserve">2.23813104629517</t>
@@ -1145,19 +1145,19 @@
     <t xml:space="preserve">2.27697730064392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28594183921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29938840866089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24709534645081</t>
+    <t xml:space="preserve">2.28594160079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29938864707947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24709558486938</t>
   </si>
   <si>
     <t xml:space="preserve">2.2799654006958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24560141563416</t>
+    <t xml:space="preserve">2.24560165405273</t>
   </si>
   <si>
     <t xml:space="preserve">2.18434429168701</t>
@@ -1166,13 +1166,13 @@
     <t xml:space="preserve">2.13503956794739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11113452911377</t>
+    <t xml:space="preserve">2.11113405227661</t>
   </si>
   <si>
     <t xml:space="preserve">2.05734753608704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02895975112915</t>
+    <t xml:space="preserve">2.02895998954773</t>
   </si>
   <si>
     <t xml:space="preserve">2.09469938278198</t>
@@ -1181,139 +1181,139 @@
     <t xml:space="preserve">2.12607502937317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13354563713074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09320545196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06929993629456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04091238975525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08573484420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08274674415588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08125281333923</t>
+    <t xml:space="preserve">2.13354539871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09320569038391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06930041313171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04091262817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08573508262634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08274698257446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08125257492065</t>
   </si>
   <si>
     <t xml:space="preserve">2.10216975212097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09768748283386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12009882926941</t>
+    <t xml:space="preserve">2.09768795967102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12009859085083</t>
   </si>
   <si>
     <t xml:space="preserve">2.21273159980774</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22169613838196</t>
+    <t xml:space="preserve">2.22169637680054</t>
   </si>
   <si>
     <t xml:space="preserve">2.23066091537476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24261355400085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26353049278259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23514318466187</t>
+    <t xml:space="preserve">2.24261379241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26353025436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23514294624329</t>
   </si>
   <si>
     <t xml:space="preserve">2.25307202339172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29341197013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29789447784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28444743156433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22767281532288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25157785415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14101552963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12159276008606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02298378944397</t>
+    <t xml:space="preserve">2.29341173171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29789423942566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28444766998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2276725769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25157761573792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14101576805115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12159299850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02298355102539</t>
   </si>
   <si>
     <t xml:space="preserve">1.94678544998169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96471464633942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98114943504333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96919679641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97816121578217</t>
+    <t xml:space="preserve">1.96471476554871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98114931583405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96919667720795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97816109657288</t>
   </si>
   <si>
     <t xml:space="preserve">1.9482798576355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02856683731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06108570098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07192540168762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03785800933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04095506668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07347416877747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0595371723175</t>
+    <t xml:space="preserve">2.02856659889221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06108593940735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0719256401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0378577709198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04095482826233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07347393035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05953693389893</t>
   </si>
   <si>
     <t xml:space="preserve">2.08895921707153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06728005409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10599279403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13541507720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15399694442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16019153594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14470601081848</t>
+    <t xml:space="preserve">2.06727981567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10599303245544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13541460037231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15399718284607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16019105911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14470624923706</t>
   </si>
   <si>
     <t xml:space="preserve">2.13696336746216</t>
@@ -1328,13 +1328,13 @@
     <t xml:space="preserve">2.16793394088745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17257976531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15244841575623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1044442653656</t>
+    <t xml:space="preserve">2.17257952690125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1524486541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10444450378418</t>
   </si>
   <si>
     <t xml:space="preserve">2.09205627441406</t>
@@ -1343,13 +1343,13 @@
     <t xml:space="preserve">2.20664691925049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17103099822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19580698013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18651604652405</t>
+    <t xml:space="preserve">2.17103123664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19580745697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18651652336121</t>
   </si>
   <si>
     <t xml:space="preserve">2.21748685836792</t>
@@ -1358,16 +1358,16 @@
     <t xml:space="preserve">2.21593809127808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1834192276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16328811645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1509006023407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13231778144836</t>
+    <t xml:space="preserve">2.18341898918152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16328835487366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15090036392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13231801986694</t>
   </si>
   <si>
     <t xml:space="preserve">2.12612390518188</t>
@@ -1382,10 +1382,10 @@
     <t xml:space="preserve">2.1570942401886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14935159683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09670186042786</t>
+    <t xml:space="preserve">2.14935183525085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09670162200928</t>
   </si>
   <si>
     <t xml:space="preserve">2.09979867935181</t>
@@ -1394,13 +1394,13 @@
     <t xml:space="preserve">2.0905077457428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10754156112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12457489967346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12767219543457</t>
+    <t xml:space="preserve">2.10754132270813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12457537651062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12767243385315</t>
   </si>
   <si>
     <t xml:space="preserve">2.18806457519531</t>
@@ -1412,25 +1412,25 @@
     <t xml:space="preserve">2.1973557472229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20200157165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20819544792175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21129298210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1756763458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12147831916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1168327331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07657098770142</t>
+    <t xml:space="preserve">2.20200133323669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20819568634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21129250526428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17567658424377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12147808074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11683249473572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07657074928284</t>
   </si>
   <si>
     <t xml:space="preserve">2.06882834434509</t>
@@ -1439,43 +1439,43 @@
     <t xml:space="preserve">2.05179476737976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01462984085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96197974681854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98211109638214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93720376491547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90313625335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86287438869476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91552424430847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87216591835022</t>
+    <t xml:space="preserve">2.01463007926941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96197998523712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98211073875427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93720388412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90313637256622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86287426948547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91552448272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87216579914093</t>
   </si>
   <si>
     <t xml:space="preserve">1.89384508132935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90158808231354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87061750888824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85977756977081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92791259288788</t>
+    <t xml:space="preserve">1.90158796310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8706169128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8597776889801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92791271209717</t>
   </si>
   <si>
     <t xml:space="preserve">1.89694237709045</t>
@@ -1484,31 +1484,31 @@
     <t xml:space="preserve">1.89074790477753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87990868091583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88919961452484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88765096664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9046847820282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92171859741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96662592887878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91862189769745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9790141582489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9697231054306</t>
+    <t xml:space="preserve">1.87990820407867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88919985294342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88765108585358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90468466281891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9217187166214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96662580966949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91862154006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97901403903961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96972274780273</t>
   </si>
   <si>
     <t xml:space="preserve">1.97746539115906</t>
@@ -1517,43 +1517,43 @@
     <t xml:space="preserve">1.94184935092926</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93100988864899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92481589317322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92017018795013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89229679107666</t>
+    <t xml:space="preserve">1.93100965023041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92481553554535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92017006874084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89229655265808</t>
   </si>
   <si>
     <t xml:space="preserve">1.90933060646057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87835991382599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93875253200531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8690687417984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94804346561432</t>
+    <t xml:space="preserve">1.87836015224457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93875229358673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86906898021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94804334640503</t>
   </si>
   <si>
     <t xml:space="preserve">1.98675656318665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360456466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03630924224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06573152542114</t>
+    <t xml:space="preserve">2.09360480308533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03630971908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06573128700256</t>
   </si>
   <si>
     <t xml:space="preserve">2.09825038909912</t>
@@ -1562,64 +1562,64 @@
     <t xml:space="preserve">2.08276510238647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19116163253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19425892829895</t>
+    <t xml:space="preserve">2.191162109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19425845146179</t>
   </si>
   <si>
     <t xml:space="preserve">2.1787736415863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20509839057922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2097442150116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22987484931946</t>
+    <t xml:space="preserve">2.20509886741638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20974397659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22987508773804</t>
   </si>
   <si>
     <t xml:space="preserve">2.20355010032654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19890427589417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22677779197693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26084566116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26239395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28562164306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29336428642273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28252482414246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2840735912323</t>
+    <t xml:space="preserve">2.19890475273132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22677803039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26084542274475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26239418983459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28562188148499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29336452484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28252458572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28407311439514</t>
   </si>
   <si>
     <t xml:space="preserve">2.2902672290802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27013659477234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25619983673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28097605705261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30265522003174</t>
+    <t xml:space="preserve">2.27013611793518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25619959831238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28097653388977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3026556968689</t>
   </si>
   <si>
     <t xml:space="preserve">2.30110692977905</t>
@@ -1628,19 +1628,19 @@
     <t xml:space="preserve">2.30730128288269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29800987243652</t>
+    <t xml:space="preserve">2.29800963401794</t>
   </si>
   <si>
     <t xml:space="preserve">2.28871893882751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25929665565491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32433485984802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29181599617004</t>
+    <t xml:space="preserve">2.25929689407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3243350982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29181575775146</t>
   </si>
   <si>
     <t xml:space="preserve">2.25465130805969</t>
@@ -1649,22 +1649,22 @@
     <t xml:space="preserve">2.26858806610107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26549100875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29955863952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29646134376526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31349539756775</t>
+    <t xml:space="preserve">2.26549124717712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29955840110779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29646182060242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31349515914917</t>
   </si>
   <si>
     <t xml:space="preserve">2.32123804092407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2577486038208</t>
+    <t xml:space="preserve">2.25774836540222</t>
   </si>
   <si>
     <t xml:space="preserve">2.23916602134705</t>
@@ -1673,37 +1673,37 @@
     <t xml:space="preserve">2.34446573257446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38008165359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38163042068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40330982208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4280858039856</t>
+    <t xml:space="preserve">2.38008189201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38163018226624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40330958366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42808628082275</t>
   </si>
   <si>
     <t xml:space="preserve">2.4311830997467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47609043121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4946722984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49002695083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49622106552124</t>
+    <t xml:space="preserve">2.4760901927948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49467277526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49002718925476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49622082710266</t>
   </si>
   <si>
     <t xml:space="preserve">2.50860929489136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54887080192566</t>
+    <t xml:space="preserve">2.54887127876282</t>
   </si>
   <si>
     <t xml:space="preserve">2.52099752426147</t>
@@ -1727,16 +1727,16 @@
     <t xml:space="preserve">2.43428015708923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4497652053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45286250114441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46679925918579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44666838645935</t>
+    <t xml:space="preserve">2.44976544380188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45286226272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46679902076721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44666790962219</t>
   </si>
   <si>
     <t xml:space="preserve">2.4575080871582</t>
@@ -1745,10 +1745,10 @@
     <t xml:space="preserve">2.47144460678101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45905661582947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42653775215149</t>
+    <t xml:space="preserve">2.45905637741089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42653751373291</t>
   </si>
   <si>
     <t xml:space="preserve">2.44821691513062</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">2.42963433265686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48692989349365</t>
+    <t xml:space="preserve">2.48692965507507</t>
   </si>
   <si>
     <t xml:space="preserve">2.53028845787048</t>
@@ -1769,58 +1769,58 @@
     <t xml:space="preserve">2.54112815856934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54422521591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55661344528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55816197395325</t>
+    <t xml:space="preserve">2.54422545433044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55661368370056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55816173553467</t>
   </si>
   <si>
     <t xml:space="preserve">2.53648257255554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53493404388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52873992919922</t>
+    <t xml:space="preserve">2.53493428230286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52874040603638</t>
   </si>
   <si>
     <t xml:space="preserve">2.51790046691895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56435656547546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59068059921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6030695438385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60461783409119</t>
+    <t xml:space="preserve">2.56435585021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59068131446838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60306930541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60461807250977</t>
   </si>
   <si>
     <t xml:space="preserve">2.59997200965881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60152077674866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58913254737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58603572845459</t>
+    <t xml:space="preserve">2.60152053833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58913278579712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58603525161743</t>
   </si>
   <si>
     <t xml:space="preserve">2.64642810821533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65262222290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68514084815979</t>
+    <t xml:space="preserve">2.65262198448181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68514108657837</t>
   </si>
   <si>
     <t xml:space="preserve">2.71611142158508</t>
@@ -1829,7 +1829,7 @@
     <t xml:space="preserve">2.69698429107666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67945075035095</t>
+    <t xml:space="preserve">2.67945027351379</t>
   </si>
   <si>
     <t xml:space="preserve">2.68263840675354</t>
@@ -1838,43 +1838,43 @@
     <t xml:space="preserve">2.65075922012329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68104434013367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66669845581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73045754432678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81174898147583</t>
+    <t xml:space="preserve">2.68104457855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66669869422913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7304573059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81174945831299</t>
   </si>
   <si>
     <t xml:space="preserve">2.80856132507324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7846519947052</t>
+    <t xml:space="preserve">2.78465175628662</t>
   </si>
   <si>
     <t xml:space="preserve">2.77349424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78305792808533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79740381240845</t>
+    <t xml:space="preserve">2.78305816650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79740357398987</t>
   </si>
   <si>
     <t xml:space="preserve">2.79580974578857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82768893241882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80696725845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75914835929871</t>
+    <t xml:space="preserve">2.82768869400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80696749687195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75914859771729</t>
   </si>
   <si>
     <t xml:space="preserve">2.74480295181274</t>
@@ -1883,28 +1883,28 @@
     <t xml:space="preserve">2.74958467483521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7320511341095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72886347770691</t>
+    <t xml:space="preserve">2.73205137252808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72886300086975</t>
   </si>
   <si>
     <t xml:space="preserve">2.73364520072937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66988635063171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68582630157471</t>
+    <t xml:space="preserve">2.66988658905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68582606315613</t>
   </si>
   <si>
     <t xml:space="preserve">2.73683309555054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71132946014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69538998603821</t>
+    <t xml:space="preserve">2.7113299369812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69539022445679</t>
   </si>
   <si>
     <t xml:space="preserve">2.70654773712158</t>
@@ -1913,49 +1913,49 @@
     <t xml:space="preserve">2.72726917266846</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70495367050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73523926734924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68742036819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76233649253845</t>
+    <t xml:space="preserve">2.70495390892029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73523879051208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.687420129776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76233625411987</t>
   </si>
   <si>
     <t xml:space="preserve">2.78783988952637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77827596664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78624606132507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81334328651428</t>
+    <t xml:space="preserve">2.77827620506287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78624582290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8133430480957</t>
   </si>
   <si>
     <t xml:space="preserve">2.88188362121582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87869572639465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91535687446594</t>
+    <t xml:space="preserve">2.87869548797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91535663604736</t>
   </si>
   <si>
     <t xml:space="preserve">2.89144730567932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88666558265686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88825964927673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91695070266724</t>
+    <t xml:space="preserve">2.88666534423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88825941085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91695094108582</t>
   </si>
   <si>
     <t xml:space="preserve">2.89622926712036</t>
@@ -1967,25 +1967,25 @@
     <t xml:space="preserve">2.79262185096741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84522247314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81812500953674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82131290435791</t>
+    <t xml:space="preserve">2.84522223472595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81812524795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82131314277649</t>
   </si>
   <si>
     <t xml:space="preserve">2.8468165397644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90738654136658</t>
+    <t xml:space="preserve">2.90738701820374</t>
   </si>
   <si>
     <t xml:space="preserve">2.90419912338257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86913180351257</t>
+    <t xml:space="preserve">2.86913204193115</t>
   </si>
   <si>
     <t xml:space="preserve">2.95201778411865</t>
@@ -2003,10 +2003,10 @@
     <t xml:space="preserve">3.00143074989319</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95679998397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97114562988281</t>
+    <t xml:space="preserve">2.95679974555969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97114586830139</t>
   </si>
   <si>
     <t xml:space="preserve">3.01577615737915</t>
@@ -2015,19 +2015,19 @@
     <t xml:space="preserve">3.02215242385864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00461840629578</t>
+    <t xml:space="preserve">3.00461864471436</t>
   </si>
   <si>
     <t xml:space="preserve">2.97911524772644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00302481651306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01418256759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98389744758606</t>
+    <t xml:space="preserve">3.0030243396759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01418280601501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98389720916748</t>
   </si>
   <si>
     <t xml:space="preserve">3.02374625205994</t>
@@ -2039,7 +2039,7 @@
     <t xml:space="preserve">2.96636343002319</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99346089363098</t>
+    <t xml:space="preserve">2.99346113204956</t>
   </si>
   <si>
     <t xml:space="preserve">3.00621294975281</t>
@@ -2051,10 +2051,10 @@
     <t xml:space="preserve">3.05881333351135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04924941062927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06997108459473</t>
+    <t xml:space="preserve">3.04924964904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06997156143188</t>
   </si>
   <si>
     <t xml:space="preserve">3.03012204170227</t>
@@ -2063,40 +2063,40 @@
     <t xml:space="preserve">3.05403161048889</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06678295135498</t>
+    <t xml:space="preserve">3.06678318977356</t>
   </si>
   <si>
     <t xml:space="preserve">3.05243730545044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07315921783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07475304603577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1002562046051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17357897758484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1974880695343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19430017471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21820974349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19589447975159</t>
+    <t xml:space="preserve">3.07315897941589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07475328445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10025668144226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17357873916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19748830795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19430041313171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21820950508118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19589424133301</t>
   </si>
   <si>
     <t xml:space="preserve">3.16242074966431</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17995452880859</t>
+    <t xml:space="preserve">3.17995476722717</t>
   </si>
   <si>
     <t xml:space="preserve">3.15604519844055</t>
@@ -2105,25 +2105,25 @@
     <t xml:space="preserve">3.18473649024963</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17517280578613</t>
+    <t xml:space="preserve">3.17517256736755</t>
   </si>
   <si>
     <t xml:space="preserve">3.19111227989197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06200122833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08750486373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12416625022888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10185050964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09547448158264</t>
+    <t xml:space="preserve">3.0620014667511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08750462532043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12416577339172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1018500328064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09547472000122</t>
   </si>
   <si>
     <t xml:space="preserve">3.0715651512146</t>
@@ -2132,52 +2132,52 @@
     <t xml:space="preserve">3.10344433784485</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11141395568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06040692329407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12735390663147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17198467254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16879677772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16401505470276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22139739990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16082692146301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16560864448547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10822653770447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09706830978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10663223266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0811288356781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07794070243835</t>
+    <t xml:space="preserve">3.11141419410706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06040716171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12735366821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17198491096497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1687970161438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16401481628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22139763832092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16082715988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16560888290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10822629928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09706854820251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10663247108459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08112859725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07794094085693</t>
   </si>
   <si>
     <t xml:space="preserve">3.14329361915588</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18633055686951</t>
+    <t xml:space="preserve">3.18633031845093</t>
   </si>
   <si>
     <t xml:space="preserve">3.18314242362976</t>
@@ -2189,64 +2189,64 @@
     <t xml:space="preserve">3.27240443229675</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37760591506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31384706497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44774055480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44614601135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37919998168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26921677589417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27718639373779</t>
+    <t xml:space="preserve">3.377605676651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3138473033905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44774031639099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44614624977112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37919950485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26921653747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27718615531921</t>
   </si>
   <si>
     <t xml:space="preserve">3.28674983978271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33297514915466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37282395362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38557624816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40948462486267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42701888084412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43977046012878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47802543640137</t>
+    <t xml:space="preserve">3.33297491073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37282419204712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38557577133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40948510169983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42701864242554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43976998329163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47802519798279</t>
   </si>
   <si>
     <t xml:space="preserve">3.45252180099487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45730400085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47005558013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55612993240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53700256347656</t>
+    <t xml:space="preserve">3.45730376243591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47005581855774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55612945556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5370020866394</t>
   </si>
   <si>
     <t xml:space="preserve">3.51628065109253</t>
@@ -2255,73 +2255,73 @@
     <t xml:space="preserve">3.339350938797</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30906534194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3377571105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27878022193909</t>
+    <t xml:space="preserve">3.30906558036804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33775687217712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27877998352051</t>
   </si>
   <si>
     <t xml:space="preserve">3.09069275856018</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11300778388977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26124668121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83247113227844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65872883796692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69060826301575</t>
+    <t xml:space="preserve">3.11300802230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2612464427948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83247065544128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6587290763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69060802459717</t>
   </si>
   <si>
     <t xml:space="preserve">2.2203893661499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55830931663513</t>
+    <t xml:space="preserve">2.55830955505371</t>
   </si>
   <si>
     <t xml:space="preserve">2.46585941314697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51049041748047</t>
+    <t xml:space="preserve">2.51049017906189</t>
   </si>
   <si>
     <t xml:space="preserve">2.5168662071228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46107745170593</t>
+    <t xml:space="preserve">2.46107769012451</t>
   </si>
   <si>
     <t xml:space="preserve">2.58381271362305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44195008277893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41804051399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44035625457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50252079963684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62206792831421</t>
+    <t xml:space="preserve">2.44194984436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41804027557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44035601615906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50252056121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62206768989563</t>
   </si>
   <si>
     <t xml:space="preserve">2.60453414916992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52802395820618</t>
+    <t xml:space="preserve">2.5280237197876</t>
   </si>
   <si>
     <t xml:space="preserve">2.56468510627747</t>
@@ -2330,103 +2330,103 @@
     <t xml:space="preserve">2.53121209144592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55193328857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45948362350464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57584309577942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56787276268005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54715180397034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54396367073059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60772204399109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62047386169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5184600353241</t>
+    <t xml:space="preserve">2.5519335269928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45948338508606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57584285736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56787300109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54715156555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54396390914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60772228240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62047410011292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51846027374268</t>
   </si>
   <si>
     <t xml:space="preserve">2.59018850326538</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5806245803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67307472229004</t>
+    <t xml:space="preserve">2.58062481880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67307448387146</t>
   </si>
   <si>
     <t xml:space="preserve">2.69220209121704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57903051376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57265472412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52483630180359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49295687675476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59178256988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61887955665588</t>
+    <t xml:space="preserve">2.57903075218201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57265496253967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52483582496643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49295711517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59178280830383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61887979507446</t>
   </si>
   <si>
     <t xml:space="preserve">2.5614972114563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47542357444763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46267151832581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51367831230164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50092649459839</t>
+    <t xml:space="preserve">2.47542333602905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46267175674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51367855072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50092673301697</t>
   </si>
   <si>
     <t xml:space="preserve">2.55352735519409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54874563217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6571352481842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66032290458679</t>
+    <t xml:space="preserve">2.54874539375305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65713500976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66032266616821</t>
   </si>
   <si>
     <t xml:space="preserve">2.85159826278687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85637998580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81653094291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77668213844299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67785668373108</t>
+    <t xml:space="preserve">2.85638046264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81653118133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77668166160583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67785620689392</t>
   </si>
   <si>
     <t xml:space="preserve">2.80218553543091</t>
@@ -2441,40 +2441,40 @@
     <t xml:space="preserve">2.75755476951599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75436639785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68901419639587</t>
+    <t xml:space="preserve">2.75436663627625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68901443481445</t>
   </si>
   <si>
     <t xml:space="preserve">2.63800740242004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70335960388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70017218589783</t>
+    <t xml:space="preserve">2.70335984230042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70017170906067</t>
   </si>
   <si>
     <t xml:space="preserve">2.72567534446716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74209499359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69940376281738</t>
+    <t xml:space="preserve">2.74209475517273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69940400123596</t>
   </si>
   <si>
     <t xml:space="preserve">2.71418166160583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64193487167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6337251663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6747739315033</t>
+    <t xml:space="preserve">2.641934633255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63372468948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67477416992188</t>
   </si>
   <si>
     <t xml:space="preserve">2.63865065574646</t>
@@ -2486,25 +2486,25 @@
     <t xml:space="preserve">2.69447779655457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7306010723114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73388528823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73552703857422</t>
+    <t xml:space="preserve">2.73060131072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73388504981995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7355272769928</t>
   </si>
   <si>
     <t xml:space="preserve">2.76508259773254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66163873672485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61894726753235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63536667823792</t>
+    <t xml:space="preserve">2.66163849830627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61894702911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63536715507507</t>
   </si>
   <si>
     <t xml:space="preserve">2.70268774032593</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">2.68791007995605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59267568588257</t>
+    <t xml:space="preserve">2.59267544746399</t>
   </si>
   <si>
     <t xml:space="preserve">2.61073732376099</t>
@@ -2522,7 +2522,7 @@
     <t xml:space="preserve">2.60252737998962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59595894813538</t>
+    <t xml:space="preserve">2.59595942497253</t>
   </si>
   <si>
     <t xml:space="preserve">2.58774948120117</t>
@@ -2531,19 +2531,19 @@
     <t xml:space="preserve">2.66820621490479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72403335571289</t>
+    <t xml:space="preserve">2.72403359413147</t>
   </si>
   <si>
     <t xml:space="preserve">2.78642845153809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77657628059387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75851488113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66656398773193</t>
+    <t xml:space="preserve">2.77657675743103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75851464271545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66656422615051</t>
   </si>
   <si>
     <t xml:space="preserve">2.70925569534302</t>
@@ -2552,10 +2552,10 @@
     <t xml:space="preserve">2.68298387527466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66328048706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75030469894409</t>
+    <t xml:space="preserve">2.66328024864197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75030493736267</t>
   </si>
   <si>
     <t xml:space="preserve">2.72239136695862</t>
@@ -2564,16 +2564,16 @@
     <t xml:space="preserve">2.64686036109924</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62715697288513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62879872322083</t>
+    <t xml:space="preserve">2.62715721130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6287989616394</t>
   </si>
   <si>
     <t xml:space="preserve">2.61566305160522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69283580780029</t>
+    <t xml:space="preserve">2.69283604621887</t>
   </si>
   <si>
     <t xml:space="preserve">2.59760165214539</t>
@@ -2585,49 +2585,49 @@
     <t xml:space="preserve">2.64029264450073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68134236335754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66492223739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67970013618469</t>
+    <t xml:space="preserve">2.68134212493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66492247581482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67969989776611</t>
   </si>
   <si>
     <t xml:space="preserve">2.69776177406311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71253943443298</t>
+    <t xml:space="preserve">2.71253967285156</t>
   </si>
   <si>
     <t xml:space="preserve">2.63700866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62387323379517</t>
+    <t xml:space="preserve">2.62387299537659</t>
   </si>
   <si>
     <t xml:space="preserve">2.60745334625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64521837234497</t>
+    <t xml:space="preserve">2.64521861076355</t>
   </si>
   <si>
     <t xml:space="preserve">2.63044095039368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54998397827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55819368362427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54505825042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51386094093323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52042865753174</t>
+    <t xml:space="preserve">2.54998421669006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55819416046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54505848884583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51386070251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52042889595032</t>
   </si>
   <si>
     <t xml:space="preserve">2.5023672580719</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">2.47281169891357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42191052436829</t>
+    <t xml:space="preserve">2.42191028594971</t>
   </si>
   <si>
     <t xml:space="preserve">2.44325613975525</t>
@@ -2651,22 +2651,22 @@
     <t xml:space="preserve">2.41205859184265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46295976638794</t>
+    <t xml:space="preserve">2.46295952796936</t>
   </si>
   <si>
     <t xml:space="preserve">2.39563870429993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37593507766724</t>
+    <t xml:space="preserve">2.37593531608582</t>
   </si>
   <si>
     <t xml:space="preserve">2.37757682800293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31518220901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29219460487366</t>
+    <t xml:space="preserve">2.31518197059631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29219436645508</t>
   </si>
   <si>
     <t xml:space="preserve">2.2347252368927</t>
@@ -2675,10 +2675,10 @@
     <t xml:space="preserve">2.19696021080017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21666383743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23636722564697</t>
+    <t xml:space="preserve">2.21666359901428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23636746406555</t>
   </si>
   <si>
     <t xml:space="preserve">2.25442910194397</t>
@@ -2687,10 +2687,10 @@
     <t xml:space="preserve">2.3102560043335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30533051490784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28070044517517</t>
+    <t xml:space="preserve">2.30533003807068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28070068359375</t>
   </si>
   <si>
     <t xml:space="preserve">2.45474982261658</t>
@@ -2699,22 +2699,22 @@
     <t xml:space="preserve">2.42519426345825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44982385635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49251508712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47937917709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56147813796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50893497467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49579906463623</t>
+    <t xml:space="preserve">2.44982409477234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49251532554626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47937965393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56147766113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50893473625183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49579882621765</t>
   </si>
   <si>
     <t xml:space="preserve">2.50400900840759</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">2.48102140426636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47609543800354</t>
+    <t xml:space="preserve">2.47609519958496</t>
   </si>
   <si>
     <t xml:space="preserve">2.52207064628601</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">2.46788549423218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44489812850952</t>
+    <t xml:space="preserve">2.44489765167236</t>
   </si>
   <si>
     <t xml:space="preserve">2.43012022972107</t>
@@ -2753,55 +2753,55 @@
     <t xml:space="preserve">2.41534233093262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38907074928284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36444139480591</t>
+    <t xml:space="preserve">2.38907098770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36444163322449</t>
   </si>
   <si>
     <t xml:space="preserve">2.39399671554565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36608338356018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40384840965271</t>
+    <t xml:space="preserve">2.3660831451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40384888648987</t>
   </si>
   <si>
     <t xml:space="preserve">2.45146584510803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33981132507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38742876052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4531078338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45967578887939</t>
+    <t xml:space="preserve">2.33981156349182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38742899894714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45310759544373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45967555046082</t>
   </si>
   <si>
     <t xml:space="preserve">2.44653987884521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50565075874329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44161367416382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49087309837341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4859471321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59431767463684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5417742729187</t>
+    <t xml:space="preserve">2.50565099716187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44161415100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49087285995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48594737052917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59431743621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54177451133728</t>
   </si>
   <si>
     <t xml:space="preserve">2.38086104393005</t>
@@ -2819,61 +2819,61 @@
     <t xml:space="preserve">2.32995986938477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46952748298645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49415707588196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55326843261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51057696342468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52371263504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55491042137146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58939146995544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5467004776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53684830665588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52535462379456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43176221847534</t>
+    <t xml:space="preserve">2.46952724456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49415755271912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55326795578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5105767250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5237123966217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55491018295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58939170837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54670023918152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53684854507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52535438537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43176198005676</t>
   </si>
   <si>
     <t xml:space="preserve">2.4022068977356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52863836288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56312012672424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56968784332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6041693687439</t>
+    <t xml:space="preserve">2.5286386013031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56311988830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56968808174133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60416913032532</t>
   </si>
   <si>
     <t xml:space="preserve">2.71582365036011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68216300010681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72895932197571</t>
+    <t xml:space="preserve">2.68216276168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72895908355713</t>
   </si>
   <si>
     <t xml:space="preserve">2.70843458175659</t>
@@ -2885,34 +2885,34 @@
     <t xml:space="preserve">2.71171855926514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73224353790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76918745040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76097774505615</t>
+    <t xml:space="preserve">2.73224329948425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76918768882751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76097750663757</t>
   </si>
   <si>
     <t xml:space="preserve">2.75440979003906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75523066520691</t>
+    <t xml:space="preserve">2.75523114204407</t>
   </si>
   <si>
     <t xml:space="preserve">2.75605177879333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74620008468628</t>
+    <t xml:space="preserve">2.7461998462677</t>
   </si>
   <si>
     <t xml:space="preserve">2.79381704330444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76261973381042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76672458648682</t>
+    <t xml:space="preserve">2.762619972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76672434806824</t>
   </si>
   <si>
     <t xml:space="preserve">2.79710125923157</t>
@@ -2921,28 +2921,28 @@
     <t xml:space="preserve">2.83815050125122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77082967758179</t>
+    <t xml:space="preserve">2.77082943916321</t>
   </si>
   <si>
     <t xml:space="preserve">2.77247166633606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7642617225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86278033256531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83240389823914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8225519657135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86031723022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87837886810303</t>
+    <t xml:space="preserve">2.76426196098328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86278009414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83240342140198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82255172729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86031675338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87837910652161</t>
   </si>
   <si>
     <t xml:space="preserve">2.88330483436584</t>
@@ -2951,19 +2951,19 @@
     <t xml:space="preserve">2.88740968704224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88248372077942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86524271965027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86113810539246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86606383323669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86360096931458</t>
+    <t xml:space="preserve">2.88248348236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86524319648743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86113786697388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86606407165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86360120773315</t>
   </si>
   <si>
     <t xml:space="preserve">2.87427377700806</t>
@@ -2972,25 +2972,25 @@
     <t xml:space="preserve">2.89726161956787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93256378173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95883584022522</t>
+    <t xml:space="preserve">2.93256402015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95883560180664</t>
   </si>
   <si>
     <t xml:space="preserve">2.97197127342224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02533531188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00481081008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00809502601624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04093432426453</t>
+    <t xml:space="preserve">3.02533555030823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00481104850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00809478759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04093408584595</t>
   </si>
   <si>
     <t xml:space="preserve">3.01794672012329</t>
@@ -3005,16 +3005,16 @@
     <t xml:space="preserve">3.00727391242981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98921227455139</t>
+    <t xml:space="preserve">2.98921179771423</t>
   </si>
   <si>
     <t xml:space="preserve">2.95801448822021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90218758583069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92353296279907</t>
+    <t xml:space="preserve">2.90218734741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92353320121765</t>
   </si>
   <si>
     <t xml:space="preserve">2.89561939239502</t>
@@ -3026,13 +3026,13 @@
     <t xml:space="preserve">2.89151477813721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86688494682312</t>
+    <t xml:space="preserve">2.8668851852417</t>
   </si>
   <si>
     <t xml:space="preserve">2.89479851722717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90920495986938</t>
+    <t xml:space="preserve">2.90920472145081</t>
   </si>
   <si>
     <t xml:space="preserve">2.89649343490601</t>
@@ -3041,13 +3041,13 @@
     <t xml:space="preserve">2.96005034446716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86598610877991</t>
+    <t xml:space="preserve">2.86598634719849</t>
   </si>
   <si>
     <t xml:space="preserve">2.86429142951965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9320855140686</t>
+    <t xml:space="preserve">2.93208527565002</t>
   </si>
   <si>
     <t xml:space="preserve">2.93293261528015</t>
@@ -3056,13 +3056,13 @@
     <t xml:space="preserve">2.92191600799561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8956458568573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9261531829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84225821495056</t>
+    <t xml:space="preserve">2.89564609527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92615342140198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84225845336914</t>
   </si>
   <si>
     <t xml:space="preserve">2.85073280334473</t>
@@ -3080,25 +3080,25 @@
     <t xml:space="preserve">2.99055743217468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03292846679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06428337097168</t>
+    <t xml:space="preserve">3.03292870521545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0642831325531</t>
   </si>
   <si>
     <t xml:space="preserve">3.04055547714233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04479241371155</t>
+    <t xml:space="preserve">3.04479217529297</t>
   </si>
   <si>
     <t xml:space="preserve">3.02275943756104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01004815101624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00157403945923</t>
+    <t xml:space="preserve">3.01004838943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00157380104065</t>
   </si>
   <si>
     <t xml:space="preserve">3.02021718025208</t>
@@ -3107,10 +3107,10 @@
     <t xml:space="preserve">3.04648733139038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03547120094299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08546900749207</t>
+    <t xml:space="preserve">3.03547096252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08546876907349</t>
   </si>
   <si>
     <t xml:space="preserve">3.09733295440674</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">3.13122987747192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14563608169556</t>
+    <t xml:space="preserve">3.14563584327698</t>
   </si>
   <si>
     <t xml:space="preserve">3.15665245056152</t>
@@ -3128,10 +3128,10 @@
     <t xml:space="preserve">3.18038034439087</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19648122787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18546485900879</t>
+    <t xml:space="preserve">3.19648146629333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18546509742737</t>
   </si>
   <si>
     <t xml:space="preserve">3.18715977668762</t>
@@ -3146,7 +3146,7 @@
     <t xml:space="preserve">3.10157012939453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11597633361816</t>
+    <t xml:space="preserve">3.11597609519958</t>
   </si>
   <si>
     <t xml:space="preserve">3.11089158058167</t>
@@ -3155,7 +3155,7 @@
     <t xml:space="preserve">3.10411238670349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13716173171997</t>
+    <t xml:space="preserve">3.13716149330139</t>
   </si>
   <si>
     <t xml:space="preserve">3.12275552749634</t>
@@ -3167,13 +3167,13 @@
     <t xml:space="preserve">3.1252977848053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08123183250427</t>
+    <t xml:space="preserve">3.08123159408569</t>
   </si>
   <si>
     <t xml:space="preserve">3.03631830215454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07360482215881</t>
+    <t xml:space="preserve">3.07360529899597</t>
   </si>
   <si>
     <t xml:space="preserve">3.09902763366699</t>
@@ -3185,16 +3185,16 @@
     <t xml:space="preserve">3.08377385139465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04140305519104</t>
+    <t xml:space="preserve">3.04140281677246</t>
   </si>
   <si>
     <t xml:space="preserve">3.08631634712219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08292675018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09224796295166</t>
+    <t xml:space="preserve">3.08292651176453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09224820137024</t>
   </si>
   <si>
     <t xml:space="preserve">3.02360701560974</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">2.99648952484131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99564218521118</t>
+    <t xml:space="preserve">2.9956419467926</t>
   </si>
   <si>
     <t xml:space="preserve">2.99818420410156</t>
@@ -3221,13 +3221,13 @@
     <t xml:space="preserve">2.96089768409729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98547291755676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91089987754822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87785029411316</t>
+    <t xml:space="preserve">2.98547315597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91089963912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87785005569458</t>
   </si>
   <si>
     <t xml:space="preserve">2.91174721717834</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">2.94564414024353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97530388832092</t>
+    <t xml:space="preserve">2.97530364990234</t>
   </si>
   <si>
     <t xml:space="preserve">2.95327067375183</t>
@@ -3248,25 +3248,25 @@
     <t xml:space="preserve">2.9439492225647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00242137908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03377628326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04902958869934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01767492294312</t>
+    <t xml:space="preserve">3.00242114067078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03377604484558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04902982711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01767516136169</t>
   </si>
   <si>
     <t xml:space="preserve">3.05241942405701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99733662605286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0125904083252</t>
+    <t xml:space="preserve">2.99733686447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01259064674377</t>
   </si>
   <si>
     <t xml:space="preserve">2.99479460716248</t>
@@ -3275,19 +3275,19 @@
     <t xml:space="preserve">3.03462362289429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1125864982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09309577941895</t>
+    <t xml:space="preserve">3.11258673667908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09309601783752</t>
   </si>
   <si>
     <t xml:space="preserve">3.0566565990448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01682758331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05750370025635</t>
+    <t xml:space="preserve">3.01682734489441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05750393867493</t>
   </si>
   <si>
     <t xml:space="preserve">3.06936764717102</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">3.03208112716675</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02953910827637</t>
+    <t xml:space="preserve">3.02953886985779</t>
   </si>
   <si>
     <t xml:space="preserve">3.00072646141052</t>
@@ -3308,22 +3308,22 @@
     <t xml:space="preserve">2.85581684112549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87022352218628</t>
+    <t xml:space="preserve">2.8702232837677</t>
   </si>
   <si>
     <t xml:space="preserve">2.88547682762146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95750761032104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88971400260925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02530193328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9820830821991</t>
+    <t xml:space="preserve">2.9575080871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88971424102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02530169487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98208332061768</t>
   </si>
   <si>
     <t xml:space="preserve">3.0083532333374</t>
@@ -3335,25 +3335,25 @@
     <t xml:space="preserve">3.00326871871948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02445435523987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04564023017883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05072426795959</t>
+    <t xml:space="preserve">3.02445459365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04563999176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05072450637817</t>
   </si>
   <si>
     <t xml:space="preserve">3.06089353561401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11682343482971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10241723060608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14055132865906</t>
+    <t xml:space="preserve">3.11682367324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10241746902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14055156707764</t>
   </si>
   <si>
     <t xml:space="preserve">3.11173892021179</t>
@@ -3362,7 +3362,7 @@
     <t xml:space="preserve">3.08716368675232</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02699661254883</t>
+    <t xml:space="preserve">3.02699685096741</t>
   </si>
   <si>
     <t xml:space="preserve">3.0134379863739</t>
@@ -3371,58 +3371,58 @@
     <t xml:space="preserve">2.99394726753235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97106671333313</t>
+    <t xml:space="preserve">2.97106695175171</t>
   </si>
   <si>
     <t xml:space="preserve">2.98123574256897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94903349876404</t>
+    <t xml:space="preserve">2.94903373718262</t>
   </si>
   <si>
     <t xml:space="preserve">2.9083571434021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91767930984497</t>
+    <t xml:space="preserve">2.91767907142639</t>
   </si>
   <si>
     <t xml:space="preserve">2.97360920906067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07614755630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14817810058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1337718963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07021522521973</t>
+    <t xml:space="preserve">3.07614731788635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14817786216736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13377213478088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07021498680115</t>
   </si>
   <si>
     <t xml:space="preserve">2.9388644695282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88039231300354</t>
+    <t xml:space="preserve">2.88039255142212</t>
   </si>
   <si>
     <t xml:space="preserve">2.91852641105652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93801736831665</t>
+    <t xml:space="preserve">2.93801689147949</t>
   </si>
   <si>
     <t xml:space="preserve">2.92530584335327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86005425453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88717174530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87276554107666</t>
+    <t xml:space="preserve">2.86005401611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88717198371887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87276577949524</t>
   </si>
   <si>
     <t xml:space="preserve">2.84310579299927</t>
@@ -3437,13 +3437,13 @@
     <t xml:space="preserve">2.80836129188538</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82446241378784</t>
+    <t xml:space="preserve">2.82446265220642</t>
   </si>
   <si>
     <t xml:space="preserve">2.740567445755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93632221221924</t>
+    <t xml:space="preserve">2.93632245063782</t>
   </si>
   <si>
     <t xml:space="preserve">2.83208918571472</t>
@@ -3458,7 +3458,7 @@
     <t xml:space="preserve">2.69904351234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71175503730774</t>
+    <t xml:space="preserve">2.71175527572632</t>
   </si>
   <si>
     <t xml:space="preserve">2.77446460723877</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">2.87700271606445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86344385147095</t>
+    <t xml:space="preserve">2.86344408988953</t>
   </si>
   <si>
     <t xml:space="preserve">2.85666465759277</t>
@@ -3491,22 +3491,22 @@
     <t xml:space="preserve">2.75666856765747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81429314613342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8270046710968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85327482223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83547878265381</t>
+    <t xml:space="preserve">2.81429362297058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82700490951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85327506065369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83547902107239</t>
   </si>
   <si>
     <t xml:space="preserve">2.87615537643433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90750980377197</t>
+    <t xml:space="preserve">2.90751004219055</t>
   </si>
   <si>
     <t xml:space="preserve">3.00581097602844</t>
@@ -3515,16 +3515,16 @@
     <t xml:space="preserve">3.04733467102051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00496363639832</t>
+    <t xml:space="preserve">3.00496387481689</t>
   </si>
   <si>
     <t xml:space="preserve">3.0439453125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05835127830505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01598024368286</t>
+    <t xml:space="preserve">3.05835151672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01598000526428</t>
   </si>
   <si>
     <t xml:space="preserve">3.04818224906921</t>
@@ -3536,13 +3536,13 @@
     <t xml:space="preserve">2.98377799987793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95242357254028</t>
+    <t xml:space="preserve">2.95242309570312</t>
   </si>
   <si>
     <t xml:space="preserve">2.98632025718689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06343579292297</t>
+    <t xml:space="preserve">3.06343603134155</t>
   </si>
   <si>
     <t xml:space="preserve">2.84141087532043</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">2.95072865486145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03801298141479</t>
+    <t xml:space="preserve">3.03801321983337</t>
   </si>
   <si>
     <t xml:space="preserve">2.98801517486572</t>
@@ -3566,34 +3566,34 @@
     <t xml:space="preserve">2.96598219871521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89056181907654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86683344841003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82785201072693</t>
+    <t xml:space="preserve">2.89056158065796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86683368682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82785224914551</t>
   </si>
   <si>
     <t xml:space="preserve">2.86174917221069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83717393875122</t>
+    <t xml:space="preserve">2.83717370033264</t>
   </si>
   <si>
     <t xml:space="preserve">2.83886861801147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72700881958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53125405311584</t>
+    <t xml:space="preserve">2.7270085811615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53125381469727</t>
   </si>
   <si>
     <t xml:space="preserve">2.41685175895691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35668444633484</t>
+    <t xml:space="preserve">2.35668468475342</t>
   </si>
   <si>
     <t xml:space="preserve">2.45837545394897</t>
@@ -3608,19 +3608,19 @@
     <t xml:space="preserve">2.3823139667511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34250521659851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32569718360901</t>
+    <t xml:space="preserve">2.34250545501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32569742202759</t>
   </si>
   <si>
     <t xml:space="preserve">2.37435221672058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46193051338196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46812295913696</t>
+    <t xml:space="preserve">2.46193075180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46812319755554</t>
   </si>
   <si>
     <t xml:space="preserve">2.49908542633057</t>
@@ -3629,10 +3629,10 @@
     <t xml:space="preserve">2.47608494758606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44158434867859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48758482933044</t>
+    <t xml:space="preserve">2.44158411026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4875853061676</t>
   </si>
   <si>
     <t xml:space="preserve">2.48493123054504</t>
@@ -3644,16 +3644,16 @@
     <t xml:space="preserve">2.45750761032104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49112367630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47696924209595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45927691459656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37523674964905</t>
+    <t xml:space="preserve">2.49112343788147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47696948051453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45927667617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37523698806763</t>
   </si>
   <si>
     <t xml:space="preserve">2.30446624755859</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">2.37789058685303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38673686981201</t>
+    <t xml:space="preserve">2.38673710823059</t>
   </si>
   <si>
     <t xml:space="preserve">2.41150689125061</t>
@@ -3686,7 +3686,7 @@
     <t xml:space="preserve">2.43008399009705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44689202308655</t>
+    <t xml:space="preserve">2.44689226150513</t>
   </si>
   <si>
     <t xml:space="preserve">2.50970077514648</t>
@@ -3695,19 +3695,19 @@
     <t xml:space="preserve">2.50527763366699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47077679634094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44246864318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43981504440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4433536529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46900773048401</t>
+    <t xml:space="preserve">2.47077703475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44246888160706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4398148059845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44335341453552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46900749206543</t>
   </si>
   <si>
     <t xml:space="preserve">2.47520017623901</t>
@@ -3731,7 +3731,7 @@
     <t xml:space="preserve">2.36904430389404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29650473594666</t>
+    <t xml:space="preserve">2.2965042591095</t>
   </si>
   <si>
     <t xml:space="preserve">2.35312104225159</t>
@@ -3740,22 +3740,22 @@
     <t xml:space="preserve">2.21158003807068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21246433258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24342656135559</t>
+    <t xml:space="preserve">2.21246457099915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24342679977417</t>
   </si>
   <si>
     <t xml:space="preserve">2.18504095077515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07269263267517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12842440605164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11603951454163</t>
+    <t xml:space="preserve">2.07269239425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12842416763306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11603975296021</t>
   </si>
   <si>
     <t xml:space="preserve">2.2009642124176</t>
@@ -3767,88 +3767,88 @@
     <t xml:space="preserve">2.23015713691711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14965558052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14700198173523</t>
+    <t xml:space="preserve">2.14965581893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14700174331665</t>
   </si>
   <si>
     <t xml:space="preserve">2.11957812309265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10630869865417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07800030708313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07357716560364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04261541366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97803711891174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98422956466675</t>
+    <t xml:space="preserve">2.1063084602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07800054550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07357740402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04261517524719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97803699970245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98422944545746</t>
   </si>
   <si>
     <t xml:space="preserve">1.87895834445953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9258439540863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91611266136169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93380570411682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94442105293274</t>
+    <t xml:space="preserve">1.92584383487701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91611278057098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93380546569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94442081451416</t>
   </si>
   <si>
     <t xml:space="preserve">2.00192213058472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90018951892853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84003448486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82588016986847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87011218070984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80464911460876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77280235290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80022609233856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83030343055725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87807369232178</t>
+    <t xml:space="preserve">1.90018939971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84003436565399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82588028907776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87011194229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80464923381805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77280247211456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80022621154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83030354976654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87807357311249</t>
   </si>
   <si>
     <t xml:space="preserve">1.88249695301056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86303472518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87541961669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85153460502625</t>
+    <t xml:space="preserve">1.8630348443985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87541949748993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85153472423553</t>
   </si>
   <si>
     <t xml:space="preserve">1.91257429122925</t>
@@ -3857,7 +3857,7 @@
     <t xml:space="preserve">1.99838364124298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01696109771729</t>
+    <t xml:space="preserve">2.01696085929871</t>
   </si>
   <si>
     <t xml:space="preserve">2.12577080726624</t>
@@ -3866,10 +3866,10 @@
     <t xml:space="preserve">2.13373231887817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14434790611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14257884025574</t>
+    <t xml:space="preserve">2.14434766769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14257860183716</t>
   </si>
   <si>
     <t xml:space="preserve">2.13196301460266</t>
@@ -3887,13 +3887,13 @@
     <t xml:space="preserve">2.27969646453857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30800461769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28058123588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29915833473206</t>
+    <t xml:space="preserve">2.30800485610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28058099746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29915857315063</t>
   </si>
   <si>
     <t xml:space="preserve">2.33454370498657</t>
@@ -3905,10 +3905,10 @@
     <t xml:space="preserve">2.33631300926208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32835149765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32746648788452</t>
+    <t xml:space="preserve">2.32835125923157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3274667263031</t>
   </si>
   <si>
     <t xml:space="preserve">2.30623555183411</t>
@@ -3917,7 +3917,7 @@
     <t xml:space="preserve">2.34515929222107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35046720504761</t>
+    <t xml:space="preserve">2.35046744346619</t>
   </si>
   <si>
     <t xml:space="preserve">2.33188962936401</t>
@@ -3926,31 +3926,31 @@
     <t xml:space="preserve">2.34338998794556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35400581359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3716983795166</t>
+    <t xml:space="preserve">2.35400557518005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37169814109802</t>
   </si>
   <si>
     <t xml:space="preserve">2.37966012954712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37612152099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4327380657196</t>
+    <t xml:space="preserve">2.37612175941467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43273782730103</t>
   </si>
   <si>
     <t xml:space="preserve">2.48050808906555</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50350832939148</t>
+    <t xml:space="preserve">2.50350856781006</t>
   </si>
   <si>
     <t xml:space="preserve">2.44600749015808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31065845489502</t>
+    <t xml:space="preserve">2.3106586933136</t>
   </si>
   <si>
     <t xml:space="preserve">2.25669622421265</t>
@@ -3959,7 +3959,7 @@
     <t xml:space="preserve">2.2726194858551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26200413703918</t>
+    <t xml:space="preserve">2.26200389862061</t>
   </si>
   <si>
     <t xml:space="preserve">2.24165725708008</t>
@@ -3980,37 +3980,37 @@
     <t xml:space="preserve">2.22838807106018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28765845298767</t>
+    <t xml:space="preserve">2.28765821456909</t>
   </si>
   <si>
     <t xml:space="preserve">2.2894275188446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33542847633362</t>
+    <t xml:space="preserve">2.3354287147522</t>
   </si>
   <si>
     <t xml:space="preserve">2.32304334640503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45043063163757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45131492614746</t>
+    <t xml:space="preserve">2.45043039321899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45131516456604</t>
   </si>
   <si>
     <t xml:space="preserve">2.42389154434204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42919921875</t>
+    <t xml:space="preserve">2.42919945716858</t>
   </si>
   <si>
     <t xml:space="preserve">2.40708374977112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34781336784363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3885064125061</t>
+    <t xml:space="preserve">2.34781312942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38850617408752</t>
   </si>
   <si>
     <t xml:space="preserve">2.41416072845459</t>
@@ -4025,7 +4025,7 @@
     <t xml:space="preserve">2.34692859649658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.340735912323</t>
+    <t xml:space="preserve">2.34073615074158</t>
   </si>
   <si>
     <t xml:space="preserve">2.3442747592926</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">2.37081384658813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31596660614014</t>
+    <t xml:space="preserve">2.31596636772156</t>
   </si>
   <si>
     <t xml:space="preserve">2.28854274749756</t>
@@ -4046,10 +4046,10 @@
     <t xml:space="preserve">2.29561996459961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30004286766052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29473543167114</t>
+    <t xml:space="preserve">2.3000431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29473567008972</t>
   </si>
   <si>
     <t xml:space="preserve">2.2664270401001</t>
@@ -4058,19 +4058,19 @@
     <t xml:space="preserve">2.23458027839661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22661876678467</t>
+    <t xml:space="preserve">2.22661852836609</t>
   </si>
   <si>
     <t xml:space="preserve">2.22219562530518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23192620277405</t>
+    <t xml:space="preserve">2.23192667961121</t>
   </si>
   <si>
     <t xml:space="preserve">2.1753101348877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19477200508118</t>
+    <t xml:space="preserve">2.1947717666626</t>
   </si>
   <si>
     <t xml:space="preserve">2.22573399543762</t>
@@ -4082,28 +4082,28 @@
     <t xml:space="preserve">2.15054035186768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11250114440918</t>
+    <t xml:space="preserve">2.1125009059906</t>
   </si>
   <si>
     <t xml:space="preserve">2.10807776451111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13727068901062</t>
+    <t xml:space="preserve">2.13727045059204</t>
   </si>
   <si>
     <t xml:space="preserve">2.12753987312317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11692428588867</t>
+    <t xml:space="preserve">2.11692404747009</t>
   </si>
   <si>
     <t xml:space="preserve">2.18857932090759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20627188682556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22131061553955</t>
+    <t xml:space="preserve">2.20627212524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22131085395813</t>
   </si>
   <si>
     <t xml:space="preserve">2.20361804962158</t>
@@ -4115,10 +4115,10 @@
     <t xml:space="preserve">2.24254202842712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30181217193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29827404022217</t>
+    <t xml:space="preserve">2.30181241035461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29827380180359</t>
   </si>
   <si>
     <t xml:space="preserve">2.40266036987305</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">2.42212247848511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31950497627258</t>
+    <t xml:space="preserve">2.31950521469116</t>
   </si>
   <si>
     <t xml:space="preserve">2.39558339118958</t>
@@ -4142,25 +4142,25 @@
     <t xml:space="preserve">2.49820065498352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44512248039246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49643111228943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53181672096252</t>
+    <t xml:space="preserve">2.44512271881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49643158912659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53181648254395</t>
   </si>
   <si>
     <t xml:space="preserve">2.52297043800354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54066300392151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62381839752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6503574848175</t>
+    <t xml:space="preserve">2.54066276550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62381863594055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65035724639893</t>
   </si>
   <si>
     <t xml:space="preserve">2.67689633369446</t>
@@ -4175,49 +4175,49 @@
     <t xml:space="preserve">2.53712439537048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61497211456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63266491889954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62204885482788</t>
+    <t xml:space="preserve">2.61497235298157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63266468048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62204909324646</t>
   </si>
   <si>
     <t xml:space="preserve">2.54950928688049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5282781124115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57958650588989</t>
+    <t xml:space="preserve">2.52827835083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57958674430847</t>
   </si>
   <si>
     <t xml:space="preserve">2.58135604858398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60966444015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58666396141052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59020233154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53889346122742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57250952720642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54420137405396</t>
+    <t xml:space="preserve">2.60966420173645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58666372299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59020256996155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.538893699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.572509765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54420161247253</t>
   </si>
   <si>
     <t xml:space="preserve">2.55304765701294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56366324424744</t>
+    <t xml:space="preserve">2.56366348266602</t>
   </si>
   <si>
     <t xml:space="preserve">2.55127859115601</t>
@@ -4232,7 +4232,7 @@
     <t xml:space="preserve">2.51812791824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52922105789185</t>
+    <t xml:space="preserve">2.52922129631042</t>
   </si>
   <si>
     <t xml:space="preserve">2.53661632537842</t>
@@ -4259,16 +4259,16 @@
     <t xml:space="preserve">2.46451139450073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41274380683899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4090461730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42013931274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44787168502808</t>
+    <t xml:space="preserve">2.41274356842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40904593467712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42013907432556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44787192344666</t>
   </si>
   <si>
     <t xml:space="preserve">2.47375583648682</t>
@@ -4289,10 +4289,10 @@
     <t xml:space="preserve">2.52737212181091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54216313362122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53846526145935</t>
+    <t xml:space="preserve">2.54216289520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53846549987793</t>
   </si>
   <si>
     <t xml:space="preserve">2.58653521537781</t>
@@ -4301,7 +4301,7 @@
     <t xml:space="preserve">2.56250047683716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59393072128296</t>
+    <t xml:space="preserve">2.59393048286438</t>
   </si>
   <si>
     <t xml:space="preserve">2.63275647163391</t>
@@ -4316,10 +4316,10 @@
     <t xml:space="preserve">2.60132598876953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45711588859558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3998019695282</t>
+    <t xml:space="preserve">2.45711612701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39980173110962</t>
   </si>
   <si>
     <t xml:space="preserve">2.44602274894714</t>
@@ -4331,10 +4331,10 @@
     <t xml:space="preserve">2.47190690040588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47005796432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42383670806885</t>
+    <t xml:space="preserve">2.47005772590637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42383694648743</t>
   </si>
   <si>
     <t xml:space="preserve">2.38316226005554</t>
@@ -4346,34 +4346,34 @@
     <t xml:space="preserve">2.49594187736511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52182555198669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54031419754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55140733718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57913970947266</t>
+    <t xml:space="preserve">2.52182579040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5403139591217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55140709877014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57913994789124</t>
   </si>
   <si>
     <t xml:space="preserve">2.5680468082428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58468651771545</t>
+    <t xml:space="preserve">2.58468627929688</t>
   </si>
   <si>
     <t xml:space="preserve">2.57544207572937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54770946502686</t>
+    <t xml:space="preserve">2.54770970344543</t>
   </si>
   <si>
     <t xml:space="preserve">2.60687255859375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60317492485046</t>
+    <t xml:space="preserve">2.60317468643188</t>
   </si>
   <si>
     <t xml:space="preserve">2.6456983089447</t>
@@ -4397,7 +4397,7 @@
     <t xml:space="preserve">2.667884349823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69376850128174</t>
+    <t xml:space="preserve">2.69376826286316</t>
   </si>
   <si>
     <t xml:space="preserve">2.56434917449951</t>
@@ -4430,22 +4430,22 @@
     <t xml:space="preserve">2.35358071327209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39795303344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41089510917664</t>
+    <t xml:space="preserve">2.39795327186584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41089487075806</t>
   </si>
   <si>
     <t xml:space="preserve">2.42753434181213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40534830093384</t>
+    <t xml:space="preserve">2.40534853935242</t>
   </si>
   <si>
     <t xml:space="preserve">2.39240646362305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3720691204071</t>
+    <t xml:space="preserve">2.37206935882568</t>
   </si>
   <si>
     <t xml:space="preserve">2.34988307952881</t>
@@ -4460,7 +4460,7 @@
     <t xml:space="preserve">2.34803414344788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45341849327087</t>
+    <t xml:space="preserve">2.45341825485229</t>
   </si>
   <si>
     <t xml:space="preserve">2.49224424362183</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">2.49779057502747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46266269683838</t>
+    <t xml:space="preserve">2.4626624584198</t>
   </si>
   <si>
     <t xml:space="preserve">2.45526719093323</t>
@@ -4487,7 +4487,7 @@
     <t xml:space="preserve">2.62536096572876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64015197753906</t>
+    <t xml:space="preserve">2.64015173912048</t>
   </si>
   <si>
     <t xml:space="preserve">2.62720990180969</t>
@@ -4496,19 +4496,19 @@
     <t xml:space="preserve">2.63090753555298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68082666397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68637275695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68822169303894</t>
+    <t xml:space="preserve">2.68082642555237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68637299537659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68822193145752</t>
   </si>
   <si>
     <t xml:space="preserve">2.66603565216064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6826753616333</t>
+    <t xml:space="preserve">2.68267512321472</t>
   </si>
   <si>
     <t xml:space="preserve">2.68452405929565</t>
@@ -4517,19 +4517,19 @@
     <t xml:space="preserve">2.69007062911987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74368715286255</t>
+    <t xml:space="preserve">2.74368691444397</t>
   </si>
   <si>
     <t xml:space="preserve">2.71225690841675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69561696052551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73444294929504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80100154876709</t>
+    <t xml:space="preserve">2.69561719894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73444271087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80100131034851</t>
   </si>
   <si>
     <t xml:space="preserve">2.78990817070007</t>
@@ -4541,7 +4541,7 @@
     <t xml:space="preserve">2.79545474052429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78621053695679</t>
+    <t xml:space="preserve">2.78621077537537</t>
   </si>
   <si>
     <t xml:space="preserve">2.76772212982178</t>
@@ -4553,7 +4553,7 @@
     <t xml:space="preserve">2.75662922859192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73998928070068</t>
+    <t xml:space="preserve">2.73998951911926</t>
   </si>
   <si>
     <t xml:space="preserve">2.74738478660583</t>
@@ -4601,22 +4601,22 @@
     <t xml:space="preserve">2.98033928871155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96924614906311</t>
+    <t xml:space="preserve">2.96924638748169</t>
   </si>
   <si>
     <t xml:space="preserve">3.02286291122437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92672276496887</t>
+    <t xml:space="preserve">2.92672300338745</t>
   </si>
   <si>
     <t xml:space="preserve">2.91562986373901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87495517730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90083885192871</t>
+    <t xml:space="preserve">2.87495493888855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90083909034729</t>
   </si>
   <si>
     <t xml:space="preserve">2.9193274974823</t>
@@ -4643,7 +4643,7 @@
     <t xml:space="preserve">2.99513030052185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9877347946167</t>
+    <t xml:space="preserve">2.98773503303528</t>
   </si>
   <si>
     <t xml:space="preserve">2.98958349227905</t>
@@ -4652,16 +4652,16 @@
     <t xml:space="preserve">2.93411827087402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96000194549561</t>
+    <t xml:space="preserve">2.96000218391418</t>
   </si>
   <si>
     <t xml:space="preserve">2.94890904426575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95445585250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97849035263062</t>
+    <t xml:space="preserve">2.95445561408997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97849059104919</t>
   </si>
   <si>
     <t xml:space="preserve">2.95260691642761</t>
@@ -4685,10 +4685,10 @@
     <t xml:space="preserve">3.08572363853455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09496808052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11900281906128</t>
+    <t xml:space="preserve">3.09496784210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11900305747986</t>
   </si>
   <si>
     <t xml:space="preserve">3.05983972549438</t>
@@ -4706,13 +4706,13 @@
     <t xml:space="preserve">3.06908392906189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0247118473053</t>
+    <t xml:space="preserve">3.02471160888672</t>
   </si>
   <si>
     <t xml:space="preserve">3.01916527748108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97479295730591</t>
+    <t xml:space="preserve">2.97479271888733</t>
   </si>
   <si>
     <t xml:space="preserve">2.92302513122559</t>
@@ -4721,7 +4721,7 @@
     <t xml:space="preserve">2.93781590461731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88419938087463</t>
+    <t xml:space="preserve">2.88419914245605</t>
   </si>
   <si>
     <t xml:space="preserve">2.90823435783386</t>
@@ -4736,19 +4736,19 @@
     <t xml:space="preserve">2.95815324783325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97109508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01546764373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11345648765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13934016227722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10975861549377</t>
+    <t xml:space="preserve">2.97109532356262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01546740531921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11345624923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13933992385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10975885391235</t>
   </si>
   <si>
     <t xml:space="preserve">3.16337513923645</t>
@@ -4757,7 +4757,7 @@
     <t xml:space="preserve">3.13379383087158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15782856941223</t>
+    <t xml:space="preserve">3.15782833099365</t>
   </si>
   <si>
     <t xml:space="preserve">3.16892170906067</t>
@@ -4766,7 +4766,7 @@
     <t xml:space="preserve">3.19480562210083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24287533760071</t>
+    <t xml:space="preserve">3.24287557601929</t>
   </si>
   <si>
     <t xml:space="preserve">3.20959615707397</t>
@@ -4775,7 +4775,7 @@
     <t xml:space="preserve">3.20589852333069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23548030853271</t>
+    <t xml:space="preserve">3.23548007011414</t>
   </si>
   <si>
     <t xml:space="preserve">3.29464316368103</t>
@@ -4790,10 +4790,10 @@
     <t xml:space="preserve">3.20774745941162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17446827888489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12085151672363</t>
+    <t xml:space="preserve">3.17446804046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12085175514221</t>
   </si>
   <si>
     <t xml:space="preserve">3.07832813262939</t>
@@ -4805,7 +4805,7 @@
     <t xml:space="preserve">3.09866547584534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07647943496704</t>
+    <t xml:space="preserve">3.07647967338562</t>
   </si>
   <si>
     <t xml:space="preserve">3.06723523139954</t>
@@ -4820,19 +4820,19 @@
     <t xml:space="preserve">3.19665431976318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20405006408691</t>
+    <t xml:space="preserve">3.20404982566833</t>
   </si>
   <si>
     <t xml:space="preserve">3.19850325584412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12454962730408</t>
+    <t xml:space="preserve">3.1245493888855</t>
   </si>
   <si>
     <t xml:space="preserve">3.16707301139832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14858436584473</t>
+    <t xml:space="preserve">3.14858412742615</t>
   </si>
   <si>
     <t xml:space="preserve">3.00067663192749</t>
@@ -4841,7 +4841,7 @@
     <t xml:space="preserve">3.04874682426453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10051441192627</t>
+    <t xml:space="preserve">3.10051465034485</t>
   </si>
   <si>
     <t xml:space="preserve">3.14488673210144</t>
@@ -5742,6 +5742,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.23000001907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24399995803833</t>
   </si>
 </sst>
 </file>
@@ -10388,7 +10391,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G166" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -10440,7 +10443,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G168" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -10492,7 +10495,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G170" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -10518,7 +10521,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G171" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -10570,7 +10573,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G173" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -10596,7 +10599,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G174" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -10622,7 +10625,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G175" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -10648,7 +10651,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G176" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -10726,7 +10729,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G179" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -10752,7 +10755,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G180" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -10804,7 +10807,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G182" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -10830,7 +10833,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G183" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -10856,7 +10859,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G184" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -10882,7 +10885,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G185" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -10908,7 +10911,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G186" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -10934,7 +10937,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G187" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -10960,7 +10963,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G188" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -10986,7 +10989,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G189" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -11012,7 +11015,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G190" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -11038,7 +11041,7 @@
         <v>2.33599996566772</v>
       </c>
       <c r="G191" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -11064,7 +11067,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G192" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -11090,7 +11093,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G193" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -11116,7 +11119,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G194" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -11142,7 +11145,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G195" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -11168,7 +11171,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G196" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -11194,7 +11197,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G197" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -11220,7 +11223,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G198" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -11246,7 +11249,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G199" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -11272,7 +11275,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G200" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -11298,7 +11301,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G201" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -11324,7 +11327,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G202" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -11350,7 +11353,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G203" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -11376,7 +11379,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G204" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -11402,7 +11405,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G205" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -11428,7 +11431,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G206" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -11454,7 +11457,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G207" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -11480,7 +11483,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G208" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -11506,7 +11509,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G209" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -11532,7 +11535,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G210" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -11558,7 +11561,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G211" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -11584,7 +11587,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G212" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -11610,7 +11613,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G213" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -11636,7 +11639,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G214" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -11688,7 +11691,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G216" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -11714,7 +11717,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G217" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -11740,7 +11743,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G218" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -11766,7 +11769,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G219" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -11792,7 +11795,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G220" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -11818,7 +11821,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G221" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -11844,7 +11847,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G222" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -11870,7 +11873,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G223" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -11896,7 +11899,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G224" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -11922,7 +11925,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G225" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -11948,7 +11951,7 @@
         <v>2.00200009346008</v>
       </c>
       <c r="G226" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -11974,7 +11977,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G227" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -12000,7 +12003,7 @@
         <v>1.96300005912781</v>
       </c>
       <c r="G228" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -12026,7 +12029,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G229" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -12052,7 +12055,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G230" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -12078,7 +12081,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G231" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -12104,7 +12107,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G232" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -12130,7 +12133,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G233" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -12156,7 +12159,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G234" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -12182,7 +12185,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G235" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -12208,7 +12211,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G236" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -12234,7 +12237,7 @@
         <v>1.90699994564056</v>
       </c>
       <c r="G237" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -12260,7 +12263,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G238" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -12286,7 +12289,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G239" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -12312,7 +12315,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G240" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -12338,7 +12341,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G241" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -12364,7 +12367,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G242" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -12390,7 +12393,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G243" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -12416,7 +12419,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G244" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -12442,7 +12445,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G245" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -12468,7 +12471,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G246" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -12494,7 +12497,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G247" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -12520,7 +12523,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G248" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -12546,7 +12549,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G249" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -12572,7 +12575,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G250" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -12598,7 +12601,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G251" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -12624,7 +12627,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G252" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -12650,7 +12653,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G253" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -12676,7 +12679,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G254" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -12702,7 +12705,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G255" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -12728,7 +12731,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G256" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -12754,7 +12757,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G257" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -12780,7 +12783,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G258" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -12806,7 +12809,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G259" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -12832,7 +12835,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G260" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -12858,7 +12861,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G261" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -12884,7 +12887,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G262" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -12910,7 +12913,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G263" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -12936,7 +12939,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G264" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -12962,7 +12965,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G265" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -12988,7 +12991,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G266" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -13014,7 +13017,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G267" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -13040,7 +13043,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G268" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -13066,7 +13069,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G269" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -13092,7 +13095,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G270" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -13118,7 +13121,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G271" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -13144,7 +13147,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G272" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -13170,7 +13173,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G273" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -13196,7 +13199,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G274" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -13222,7 +13225,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G275" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -13248,7 +13251,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G276" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -13274,7 +13277,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G277" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -13300,7 +13303,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G278" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -13326,7 +13329,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G279" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -13352,7 +13355,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G280" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -13378,7 +13381,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G281" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -13404,7 +13407,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G282" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -13430,7 +13433,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G283" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -13456,7 +13459,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G284" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -13482,7 +13485,7 @@
         <v>2.25</v>
       </c>
       <c r="G285" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -13508,7 +13511,7 @@
         <v>2.25</v>
       </c>
       <c r="G286" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -13534,7 +13537,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G287" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -13560,7 +13563,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G288" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -13586,7 +13589,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G289" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -13612,7 +13615,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G290" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -13638,7 +13641,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G291" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -13664,7 +13667,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G292" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -13690,7 +13693,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G293" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -13716,7 +13719,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G294" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -13742,7 +13745,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G295" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -13768,7 +13771,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G296" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -13794,7 +13797,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G297" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -13820,7 +13823,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G298" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -13846,7 +13849,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G299" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -13898,7 +13901,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G301" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -13924,7 +13927,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G302" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -13950,7 +13953,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G303" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -13976,7 +13979,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G304" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -14002,7 +14005,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G305" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -14028,7 +14031,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G306" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -14054,7 +14057,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G307" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -14080,7 +14083,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G308" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -14106,7 +14109,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G309" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -14132,7 +14135,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G310" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -14158,7 +14161,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G311" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -14184,7 +14187,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G312" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -14210,7 +14213,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G313" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -14236,7 +14239,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G314" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -14262,7 +14265,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G315" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -14288,7 +14291,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G316" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -14314,7 +14317,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G317" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -14340,7 +14343,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G318" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -14366,7 +14369,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G319" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -14392,7 +14395,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G320" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -14418,7 +14421,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G321" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -14444,7 +14447,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G322" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -14470,7 +14473,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G323" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -14496,7 +14499,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G324" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -14522,7 +14525,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G325" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -14548,7 +14551,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G326" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -14574,7 +14577,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G327" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -14600,7 +14603,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G328" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -14626,7 +14629,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G329" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -14652,7 +14655,7 @@
         <v>2.67400002479553</v>
       </c>
       <c r="G330" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -14678,7 +14681,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G331" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -14704,7 +14707,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G332" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -14730,7 +14733,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G333" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -14756,7 +14759,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G334" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -14782,7 +14785,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G335" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -14808,7 +14811,7 @@
         <v>2.66199994087219</v>
       </c>
       <c r="G336" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -14834,7 +14837,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G337" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -14860,7 +14863,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G338" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -14886,7 +14889,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G339" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -14912,7 +14915,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G340" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -14938,7 +14941,7 @@
         <v>2.64599990844727</v>
       </c>
       <c r="G341" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -14964,7 +14967,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G342" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -14990,7 +14993,7 @@
         <v>2.67199993133545</v>
       </c>
       <c r="G343" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -15016,7 +15019,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G344" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -15042,7 +15045,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G345" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -15068,7 +15071,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G346" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -15094,7 +15097,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G347" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -15120,7 +15123,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G348" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -15146,7 +15149,7 @@
         <v>2.85599994659424</v>
       </c>
       <c r="G349" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -15172,7 +15175,7 @@
         <v>2.83200001716614</v>
       </c>
       <c r="G350" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -15198,7 +15201,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G351" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -15224,7 +15227,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G352" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -15250,7 +15253,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G353" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -15276,7 +15279,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G354" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -15302,7 +15305,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G355" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -15328,7 +15331,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G356" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -15354,7 +15357,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G357" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -15380,7 +15383,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G358" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -15406,7 +15409,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G359" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -15432,7 +15435,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G360" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -15458,7 +15461,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G361" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -15484,7 +15487,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G362" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -15510,7 +15513,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G363" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -15536,7 +15539,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G364" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -15562,7 +15565,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G365" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -15588,7 +15591,7 @@
         <v>2.90400004386902</v>
       </c>
       <c r="G366" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -15614,7 +15617,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G367" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -15640,7 +15643,7 @@
         <v>2.92600011825562</v>
       </c>
       <c r="G368" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -15666,7 +15669,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G369" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -15692,7 +15695,7 @@
         <v>2.96399998664856</v>
       </c>
       <c r="G370" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -15718,7 +15721,7 @@
         <v>2.94400000572205</v>
       </c>
       <c r="G371" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -15744,7 +15747,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="G372" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -15770,7 +15773,7 @@
         <v>2.95799994468689</v>
       </c>
       <c r="G373" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -15796,7 +15799,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G374" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -15822,7 +15825,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G375" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -15848,7 +15851,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G376" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -15874,7 +15877,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G377" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -15900,7 +15903,7 @@
         <v>2.88599991798401</v>
       </c>
       <c r="G378" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -18656,7 +18659,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G484" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -18708,7 +18711,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G486" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -72406,13 +72409,13 @@
     </row>
     <row r="2552">
       <c r="A2552" s="1" t="n">
-        <v>46038.6912037037</v>
+        <v>46038.3333333333</v>
       </c>
       <c r="B2552" t="n">
         <v>3467586</v>
       </c>
       <c r="C2552" t="n">
-        <v>4.22599983215332</v>
+        <v>4.23000001907349</v>
       </c>
       <c r="D2552" t="n">
         <v>4.17999982833862</v>
@@ -72427,6 +72430,32 @@
         <v>1909</v>
       </c>
       <c r="H2552" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2553">
+      <c r="A2553" s="1" t="n">
+        <v>46041.6943402778</v>
+      </c>
+      <c r="B2553" t="n">
+        <v>2914159</v>
+      </c>
+      <c r="C2553" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="D2553" t="n">
+        <v>4.21199989318848</v>
+      </c>
+      <c r="E2553" t="n">
+        <v>4.23000001907349</v>
+      </c>
+      <c r="F2553" t="n">
+        <v>4.24399995803833</v>
+      </c>
+      <c r="G2553" t="s">
+        <v>1910</v>
+      </c>
+      <c r="H2553" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HER.MI.xlsx
+++ b/data/HER.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1913" uniqueCount="1913">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1914" uniqueCount="1914">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,157 +38,157 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70756638050079</t>
+    <t xml:space="preserve">1.70756649971008</t>
   </si>
   <si>
     <t xml:space="preserve">HER.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70896375179291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70616900920868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71036124229431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68800318241119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72573220729828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79140746593475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79420244693756</t>
+    <t xml:space="preserve">1.70896399021149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70616888999939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71036100387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68800354003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72573208808899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79140758514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79420220851898</t>
   </si>
   <si>
     <t xml:space="preserve">1.77044725418091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74669241905212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70337426662445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77324223518372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74948716163635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76625549793243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8053811788559</t>
+    <t xml:space="preserve">1.74669229984283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70337462425232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77324235439301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74948692321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76625514030457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80538094043732</t>
   </si>
   <si>
     <t xml:space="preserve">1.79001033306122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80398392677307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83472537994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81656002998352</t>
+    <t xml:space="preserve">1.80398428440094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83472585678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8165602684021</t>
   </si>
   <si>
     <t xml:space="preserve">1.80258643627167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84869909286499</t>
+    <t xml:space="preserve">1.8486989736557</t>
   </si>
   <si>
     <t xml:space="preserve">1.85568594932556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84031522274017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82354700565338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82913625240326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72852659225464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74110281467438</t>
+    <t xml:space="preserve">1.8403148651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8235467672348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82913613319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72852683067322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74110293388367</t>
   </si>
   <si>
     <t xml:space="preserve">1.75926840305328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69918215274811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7550767660141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79559934139252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78302335739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7760363817215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79839420318604</t>
+    <t xml:space="preserve">1.69918203353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75507664680481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79559993743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78302347660065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77603662014008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79839432239532</t>
   </si>
   <si>
     <t xml:space="preserve">1.80118918418884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82075178623199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83053314685822</t>
+    <t xml:space="preserve">1.82075202465057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83053350448608</t>
   </si>
   <si>
     <t xml:space="preserve">1.78861308097839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76485800743103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74529492855072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73970568180084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72992408275604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74389755725861</t>
+    <t xml:space="preserve">1.76485812664032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74529480934143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73970580101013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72992420196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7438976764679</t>
   </si>
   <si>
     <t xml:space="preserve">1.73271882534027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76346039772034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7788313627243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7606657743454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77463924884796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7969970703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83752059936523</t>
+    <t xml:space="preserve">1.76346063613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77883148193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76066553592682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77463936805725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79699742794037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83752048015594</t>
   </si>
   <si>
     <t xml:space="preserve">1.81097042560577</t>
@@ -197,163 +197,163 @@
     <t xml:space="preserve">1.85708332061768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84310948848724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76765239238739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78162610530853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78721570968628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77743422985077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.780228972435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80817580223083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80957305431366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79280519485474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78442096710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75647342205048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74808967113495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8263418674469</t>
+    <t xml:space="preserve">1.84310972690582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76765251159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78162634372711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78721582889557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77743399143219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78022885322571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80817592144012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80957281589508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79280471801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78442072868347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75647389888763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74808979034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82634162902832</t>
   </si>
   <si>
     <t xml:space="preserve">1.84590446949005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83193111419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84450709819794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82214915752411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83332824707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82494449615479</t>
+    <t xml:space="preserve">1.8319308757782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84450697898865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82214939594269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83332848548889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82494413852692</t>
   </si>
   <si>
     <t xml:space="preserve">1.81376516819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76206338405609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73132157325745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74250030517578</t>
+    <t xml:space="preserve">1.7620632648468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73132145404816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74250042438507</t>
   </si>
   <si>
     <t xml:space="preserve">1.71175849437714</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75751030445099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77344834804535</t>
+    <t xml:space="preserve">1.75751078128815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77344810962677</t>
   </si>
   <si>
     <t xml:space="preserve">1.74012386798859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7589590549469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70390152931213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6734744310379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70969676971436</t>
+    <t xml:space="preserve">1.75895941257477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70390129089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67347431182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70969688892365</t>
   </si>
   <si>
     <t xml:space="preserve">1.73867475986481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78069281578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83430171012878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80822157859802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81111967563629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78503930568695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77924382686615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72708368301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76040828227997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74591934680939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77055060863495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76620352268219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76185715198517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76910161972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77489709854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78359055519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83719968795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85748386383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85023975372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83575057983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86617755889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83140432834625</t>
+    <t xml:space="preserve">1.78069269657135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83430182933807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8082218170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81111943721771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78503942489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77924370765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72708380222321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76040816307068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74591910839081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77055048942566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76620388031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7618567943573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76910138130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77489721775055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78359043598175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83719980716705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85748410224915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85023951530457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83575081825256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86617767810822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83140385150909</t>
   </si>
   <si>
     <t xml:space="preserve">1.84444415569305</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">1.79663050174713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81981301307678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8125684261322</t>
+    <t xml:space="preserve">1.81981313228607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81256854534149</t>
   </si>
   <si>
     <t xml:space="preserve">1.74881708621979</t>
@@ -374,7 +374,10 @@
     <t xml:space="preserve">1.7444703578949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77634596824646</t>
+    <t xml:space="preserve">1.76765275001526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77634608745575</t>
   </si>
   <si>
     <t xml:space="preserve">1.79083478450775</t>
@@ -383,25 +386,25 @@
     <t xml:space="preserve">1.79952824115753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78648829460144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78938603401184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81546640396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75606167316437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73577702045441</t>
+    <t xml:space="preserve">1.78648841381073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78938615322113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81546604633331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75606143474579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73577678203583</t>
   </si>
   <si>
     <t xml:space="preserve">1.70679903030396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73722589015961</t>
+    <t xml:space="preserve">1.73722565174103</t>
   </si>
   <si>
     <t xml:space="preserve">1.75461256504059</t>
@@ -410,19 +413,19 @@
     <t xml:space="preserve">1.71114563941956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70824778079987</t>
+    <t xml:space="preserve">1.70824801921844</t>
   </si>
   <si>
     <t xml:space="preserve">1.70245218276978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69231009483337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71694111824036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69665670394897</t>
+    <t xml:space="preserve">1.69231021404266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71694123744965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69665658473969</t>
   </si>
   <si>
     <t xml:space="preserve">1.63145661354065</t>
@@ -431,22 +434,22 @@
     <t xml:space="preserve">1.6053763628006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59233617782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57929623126984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60102999210358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6097229719162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6140695810318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62131416797638</t>
+    <t xml:space="preserve">1.59233629703522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57929635047913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60102987289429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60972309112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61406981945038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62131428718567</t>
   </si>
   <si>
     <t xml:space="preserve">1.63290512561798</t>
@@ -455,16 +458,16 @@
     <t xml:space="preserve">1.61841642856598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63870120048523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63725221157074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65029227733612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62276303768158</t>
+    <t xml:space="preserve">1.63870108127594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63725197315216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65029203891754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62276327610016</t>
   </si>
   <si>
     <t xml:space="preserve">1.61551868915558</t>
@@ -473,82 +476,82 @@
     <t xml:space="preserve">1.61696743965149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62566089630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66188287734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66912770271301</t>
+    <t xml:space="preserve">1.62566077709198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66188335418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66912758350372</t>
   </si>
   <si>
     <t xml:space="preserve">1.68796336650848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59378516674042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56625628471375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56335842609406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54307401180267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4604868888855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4633846282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44599783420563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44527328014374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45034456253052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43006002902985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42209112644196</t>
+    <t xml:space="preserve">1.593785405159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56625616550446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56335818767548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54307389259338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46048676967621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46338450908661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44599771499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44527339935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45034468173981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43005990982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42209100723267</t>
   </si>
   <si>
     <t xml:space="preserve">1.39601099491119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39456212520599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40905094146729</t>
+    <t xml:space="preserve">1.3945620059967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40905106067657</t>
   </si>
   <si>
     <t xml:space="preserve">1.41267323493958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39818429946899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40180635452271</t>
+    <t xml:space="preserve">1.3981841802597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40180647373199</t>
   </si>
   <si>
     <t xml:space="preserve">1.40542876720428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41629552841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38152182102203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35906422138214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37717533111572</t>
+    <t xml:space="preserve">1.41629540920258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38152170181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35906434059143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37717521190643</t>
   </si>
   <si>
     <t xml:space="preserve">1.43875336647034</t>
@@ -557,34 +560,34 @@
     <t xml:space="preserve">1.48077130317688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49236238002777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48511779308319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5329315662384</t>
+    <t xml:space="preserve">1.49236249923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48511791229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53293168544769</t>
   </si>
   <si>
     <t xml:space="preserve">1.52713596820831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50105571746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50685131549835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5488692522049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55756282806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57060289382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59088730812073</t>
+    <t xml:space="preserve">1.50105583667755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50685119628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54886949062347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55756306648254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57060265541077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59088718891144</t>
   </si>
   <si>
     <t xml:space="preserve">1.56915378570557</t>
@@ -593,7 +596,7 @@
     <t xml:space="preserve">1.58798944950104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.608274102211</t>
+    <t xml:space="preserve">1.60827398300171</t>
   </si>
   <si>
     <t xml:space="preserve">1.59668302536011</t>
@@ -602,175 +605,175 @@
     <t xml:space="preserve">1.59958076477051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56480741500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65174102783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64159882068634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65318989753723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65463888645172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65898537635803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64014947414398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64304757118225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57494950294495</t>
+    <t xml:space="preserve">1.56480717658997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65174067020416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64159870147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65319001674652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65463876724243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65898561477661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64014983177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64304769039154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57494962215424</t>
   </si>
   <si>
     <t xml:space="preserve">1.57784748077393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55176711082458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58654069900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63000774383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6821676492691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6662300825119</t>
+    <t xml:space="preserve">1.55176734924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58654081821442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63000762462616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68216788768768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66622972488403</t>
   </si>
   <si>
     <t xml:space="preserve">1.67782092094421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69086146354675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69375896453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69810545444489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69520771503448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71404349803925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72998118400574</t>
+    <t xml:space="preserve">1.69086122512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69375920295715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69810569286346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69520783424377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71404337882996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72998106479645</t>
   </si>
   <si>
     <t xml:space="preserve">1.73432791233063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71983933448792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72418582439423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71549224853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71839010715485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7415726184845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78214180469513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78793692588806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81401753425598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82995557785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86907517910004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89950215816498</t>
+    <t xml:space="preserve">1.71983897686005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72418606281281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71549236774445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71838998794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74157273769379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78214156627655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78793728351593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81401717662811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82995533943176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86907529830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8995019197464</t>
   </si>
   <si>
     <t xml:space="preserve">1.91399121284485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91543984413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8806666135788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87197327613831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88935995101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90095102787018</t>
+    <t xml:space="preserve">1.91543996334076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88066613674164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87197291851044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88935983181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90095126628876</t>
   </si>
   <si>
     <t xml:space="preserve">1.90529763698578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91254246234894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94441783428192</t>
+    <t xml:space="preserve">1.91254210472107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94441795349121</t>
   </si>
   <si>
     <t xml:space="preserve">1.93717336654663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87921810150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88356423377991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92848038673401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89805316925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88791060447693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90239953994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91688859462738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92413330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93572437763214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93862247467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9487646818161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99512910842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02845406532288</t>
+    <t xml:space="preserve">1.87921798229218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8835643529892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92847990989685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89805328845978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8879109621048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90240013599396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91688883304596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92413318157196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93572449684143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93862223625183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94876480102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99512922763824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0284538269043</t>
   </si>
   <si>
     <t xml:space="preserve">2.05743169784546</t>
@@ -779,7 +782,7 @@
     <t xml:space="preserve">2.06902265548706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05163621902466</t>
+    <t xml:space="preserve">2.05163598060608</t>
   </si>
   <si>
     <t xml:space="preserve">2.1023473739624</t>
@@ -788,52 +791,52 @@
     <t xml:space="preserve">2.06467604637146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03859615325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07336974143982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08641004562378</t>
+    <t xml:space="preserve">2.0385959148407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07336950302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08640956878662</t>
   </si>
   <si>
     <t xml:space="preserve">2.12842774391174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11248970031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1110405921936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10089874267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05453372001648</t>
+    <t xml:space="preserve">2.11249017715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11104083061218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10089826583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05453395843506</t>
   </si>
   <si>
     <t xml:space="preserve">2.0893075466156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12263202667236</t>
+    <t xml:space="preserve">2.12263178825378</t>
   </si>
   <si>
     <t xml:space="preserve">2.07916522026062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10379672050476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11973428726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10814356803894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1472635269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13277435302734</t>
+    <t xml:space="preserve">2.1037962436676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11973404884338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10814309120178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14726305007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13277411460876</t>
   </si>
   <si>
     <t xml:space="preserve">2.15450763702393</t>
@@ -842,7 +845,7 @@
     <t xml:space="preserve">2.14291667938232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15595674514771</t>
+    <t xml:space="preserve">2.15595650672913</t>
   </si>
   <si>
     <t xml:space="preserve">2.16790914535522</t>
@@ -851,91 +854,88 @@
     <t xml:space="preserve">2.17836785316467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17239189147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15595650672913</t>
+    <t xml:space="preserve">2.17239165306091</t>
   </si>
   <si>
     <t xml:space="preserve">2.09918165206909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11262845993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07228851318359</t>
+    <t xml:space="preserve">2.11262822151184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07228827476501</t>
   </si>
   <si>
     <t xml:space="preserve">2.05884146690369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01700735092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99907851219177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01103067398071</t>
+    <t xml:space="preserve">2.01700711250305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9990781545639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01103091239929</t>
   </si>
   <si>
     <t xml:space="preserve">2.00804281234741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99758422374725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95126807689667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97069072723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00505495071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98264336585999</t>
+    <t xml:space="preserve">1.99758410453796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95126783847809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97069096565247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00505447387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98264348506927</t>
   </si>
   <si>
     <t xml:space="preserve">2.03045392036438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05286526679993</t>
+    <t xml:space="preserve">2.05286502838135</t>
   </si>
   <si>
     <t xml:space="preserve">2.0394184589386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03194808959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04539465904236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02447819709778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06182980537415</t>
+    <t xml:space="preserve">2.03194832801819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04539513587952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02447772026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06182956695557</t>
   </si>
   <si>
     <t xml:space="preserve">2.07677054405212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03344202041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01401925086975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05435919761658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04390096664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04240679740906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03643035888672</t>
+    <t xml:space="preserve">2.03344225883484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01401948928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05435943603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04390072822571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04240655899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03643083572388</t>
   </si>
   <si>
     <t xml:space="preserve">2.04838299751282</t>
@@ -947,31 +947,31 @@
     <t xml:space="preserve">2.00206661224365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05585360527039</t>
+    <t xml:space="preserve">2.05585384368896</t>
   </si>
   <si>
     <t xml:space="preserve">2.03493618965149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99459600448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.975172996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96172618865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9677027463913</t>
+    <t xml:space="preserve">1.99459612369537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97517311573029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96172630786896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96770298480988</t>
   </si>
   <si>
     <t xml:space="preserve">2.02597188949585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01252484321594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00953722000122</t>
+    <t xml:space="preserve">2.0125253200531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00953698158264</t>
   </si>
   <si>
     <t xml:space="preserve">2.0035605430603</t>
@@ -986,28 +986,28 @@
     <t xml:space="preserve">2.000572681427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98563182353973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98712587356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97218501567841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02148985862732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03792452812195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06033563613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07079434394836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07378244400024</t>
+    <t xml:space="preserve">1.98563158512115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98712575435638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97218489646912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02148962020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03792428970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06033539772034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07079386711121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07378220558167</t>
   </si>
   <si>
     <t xml:space="preserve">2.06631207466125</t>
@@ -1016,70 +1016,70 @@
     <t xml:space="preserve">2.0633237361908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07527637481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08424043655396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10665225982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12458109855652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14998030662537</t>
+    <t xml:space="preserve">2.07527661323547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08424067497253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1066517829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12458086013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14998006820679</t>
   </si>
   <si>
     <t xml:space="preserve">2.16043877601624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18135619163513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19629693031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18733239173889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17986178398132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16641521453857</t>
+    <t xml:space="preserve">2.18135595321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19629716873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18733215332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1798620223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16641545295715</t>
   </si>
   <si>
     <t xml:space="preserve">2.17089748382568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19181489944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19330930709839</t>
+    <t xml:space="preserve">2.19181442260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19330883026123</t>
   </si>
   <si>
     <t xml:space="preserve">2.19480276107788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22468423843384</t>
+    <t xml:space="preserve">2.22468447685242</t>
   </si>
   <si>
     <t xml:space="preserve">2.27100086212158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25605988502502</t>
+    <t xml:space="preserve">2.2560601234436</t>
   </si>
   <si>
     <t xml:space="preserve">2.25904822349548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28145909309387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29490637779236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30536460876465</t>
+    <t xml:space="preserve">2.28145956993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29490613937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30536484718323</t>
   </si>
   <si>
     <t xml:space="preserve">2.30088233947754</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">2.25456595420837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25755405426025</t>
+    <t xml:space="preserve">2.25755381584167</t>
   </si>
   <si>
     <t xml:space="preserve">2.27847123146057</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">2.22617864608765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2187077999115</t>
+    <t xml:space="preserve">2.21870827674866</t>
   </si>
   <si>
     <t xml:space="preserve">2.17388606071472</t>
@@ -1127,112 +1127,112 @@
     <t xml:space="preserve">2.21123743057251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26054215431213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31134080886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24111938476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26950645446777</t>
+    <t xml:space="preserve">2.26054263114929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31134104728699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24111890792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26950693130493</t>
   </si>
   <si>
     <t xml:space="preserve">2.23813104629517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27697706222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28594160079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29938864707947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24709582328796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2799654006958</t>
+    <t xml:space="preserve">2.27697682380676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28594183921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29938840866089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24709534645081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27996563911438</t>
   </si>
   <si>
     <t xml:space="preserve">2.24560165405273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18434429168701</t>
+    <t xml:space="preserve">2.18434453010559</t>
   </si>
   <si>
     <t xml:space="preserve">2.13503980636597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11113452911377</t>
+    <t xml:space="preserve">2.11113429069519</t>
   </si>
   <si>
     <t xml:space="preserve">2.05734753608704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02895998954773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09469962120056</t>
+    <t xml:space="preserve">2.02895975112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09469938278198</t>
   </si>
   <si>
     <t xml:space="preserve">2.12607502937317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13354539871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09320545196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06930017471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04091286659241</t>
+    <t xml:space="preserve">2.13354563713074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09320521354675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06929993629456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04091238975525</t>
   </si>
   <si>
     <t xml:space="preserve">2.08573508262634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08274698257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08125305175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10216975212097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09768748283386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12009906768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2127320766449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22169637680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23066091537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24261355400085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26353073120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23514270782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25307154655457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29341197013855</t>
+    <t xml:space="preserve">2.08274674415588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08125281333923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10216951370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09768795967102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12009882926941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21273159980774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22169589996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23066067695618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24261379241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26353025436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23514294624329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25307178497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29341220855713</t>
   </si>
   <si>
     <t xml:space="preserve">2.29789423942566</t>
@@ -1241,49 +1241,49 @@
     <t xml:space="preserve">2.28444766998291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22767281532288</t>
+    <t xml:space="preserve">2.2276725769043</t>
   </si>
   <si>
     <t xml:space="preserve">2.25157761573792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14101576805115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12159276008606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02298378944397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94678544998169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96471464633942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98114955425262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96919691562653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97816109657288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94827973842621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02856659889221</t>
+    <t xml:space="preserve">2.14101600646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12159299850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02298355102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94678592681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96471476554871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98114931583405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96919667720795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97816133499146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9482798576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02856683731079</t>
   </si>
   <si>
     <t xml:space="preserve">2.06108593940735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07192540168762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03785800933838</t>
+    <t xml:space="preserve">2.07192516326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0378577709198</t>
   </si>
   <si>
     <t xml:space="preserve">2.04095482826233</t>
@@ -1292,10 +1292,10 @@
     <t xml:space="preserve">2.07347416877747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05953764915466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08895897865295</t>
+    <t xml:space="preserve">2.0595371723175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08895921707153</t>
   </si>
   <si>
     <t xml:space="preserve">2.06727981567383</t>
@@ -1304,13 +1304,13 @@
     <t xml:space="preserve">2.10599303245544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13541460037231</t>
+    <t xml:space="preserve">2.13541436195374</t>
   </si>
   <si>
     <t xml:space="preserve">2.15399742126465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16019082069397</t>
+    <t xml:space="preserve">2.16019105911255</t>
   </si>
   <si>
     <t xml:space="preserve">2.14470601081848</t>
@@ -1319,22 +1319,22 @@
     <t xml:space="preserve">2.13696336746216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14780330657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13386654853821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16793370246887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17257952690125</t>
+    <t xml:space="preserve">2.14780306816101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13386631011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16793394088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17257928848267</t>
   </si>
   <si>
     <t xml:space="preserve">2.1524486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10444450378418</t>
+    <t xml:space="preserve">2.1044442653656</t>
   </si>
   <si>
     <t xml:space="preserve">2.09205603599548</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">2.17103099822998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19580721855164</t>
+    <t xml:space="preserve">2.19580745697021</t>
   </si>
   <si>
     <t xml:space="preserve">2.18651628494263</t>
@@ -1355,25 +1355,25 @@
     <t xml:space="preserve">2.21748661994934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21593832969666</t>
+    <t xml:space="preserve">2.21593809127808</t>
   </si>
   <si>
     <t xml:space="preserve">2.18341898918152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16328811645508</t>
+    <t xml:space="preserve">2.16328835487366</t>
   </si>
   <si>
     <t xml:space="preserve">2.15090036392212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13231778144836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12612390518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11992955207825</t>
+    <t xml:space="preserve">2.13231801986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12612342834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11993002891541</t>
   </si>
   <si>
     <t xml:space="preserve">2.16638541221619</t>
@@ -1394,40 +1394,40 @@
     <t xml:space="preserve">2.0905077457428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10754132270813</t>
+    <t xml:space="preserve">2.10754156112671</t>
   </si>
   <si>
     <t xml:space="preserve">2.12457513809204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12767243385315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18806457519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20045304298401</t>
+    <t xml:space="preserve">2.12767219543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18806481361389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20045280456543</t>
   </si>
   <si>
     <t xml:space="preserve">2.19735598564148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20200157165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20819544792175</t>
+    <t xml:space="preserve">2.20200133323669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20819568634033</t>
   </si>
   <si>
     <t xml:space="preserve">2.21129250526428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17567682266235</t>
+    <t xml:space="preserve">2.17567658424377</t>
   </si>
   <si>
     <t xml:space="preserve">2.12147831916809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1168327331543</t>
+    <t xml:space="preserve">2.11683249473572</t>
   </si>
   <si>
     <t xml:space="preserve">2.07657098770142</t>
@@ -1436,115 +1436,115 @@
     <t xml:space="preserve">2.06882834434509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05179500579834</t>
+    <t xml:space="preserve">2.05179476737976</t>
   </si>
   <si>
     <t xml:space="preserve">2.01463007926941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9619802236557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98211109638214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93720376491547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90313625335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86287450790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91552436351776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87216556072235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89384508132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90158796310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87061715126038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85977780818939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92791271209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89694225788116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89074814319611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87990832328796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88919937610626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88765096664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90468502044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9217187166214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96662569046021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91862154006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9790141582489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96972274780273</t>
+    <t xml:space="preserve">1.96198010444641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98211073875427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93720388412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90313613414764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86287462711334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91552412509918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87216591835022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89384531974792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90158772468567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87061703205109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85977756977081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92791283130646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89694237709045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89074790477753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87990820407867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88919973373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88765120506287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9046847820282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92171847820282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96662604808807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91862142086029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97901380062103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96972227096558</t>
   </si>
   <si>
     <t xml:space="preserve">1.97746562957764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94184947013855</t>
+    <t xml:space="preserve">1.94184911251068</t>
   </si>
   <si>
     <t xml:space="preserve">1.9310097694397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92481565475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92017006874084</t>
+    <t xml:space="preserve">1.92481577396393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92017018795013</t>
   </si>
   <si>
     <t xml:space="preserve">1.89229643344879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90933036804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8783597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93875253200531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8690687417984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94804346561432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98675668239594</t>
+    <t xml:space="preserve">1.90933060646057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87836027145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93875217437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86906862258911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94804358482361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98675656318665</t>
   </si>
   <si>
     <t xml:space="preserve">2.09360480308533</t>
@@ -1553,22 +1553,22 @@
     <t xml:space="preserve">2.03630948066711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06573128700256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0982506275177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08276534080505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19116163253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19425916671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1787736415863</t>
+    <t xml:space="preserve">2.06573152542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09825038909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08276510238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19116187095642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19425892829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17877340316772</t>
   </si>
   <si>
     <t xml:space="preserve">2.2050986289978</t>
@@ -1580,28 +1580,28 @@
     <t xml:space="preserve">2.22987508773804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20354986190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19890427589417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22677803039551</t>
+    <t xml:space="preserve">2.20355010032654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19890451431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22677755355835</t>
   </si>
   <si>
     <t xml:space="preserve">2.26084542274475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26239371299744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28562164306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29336452484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28252482414246</t>
+    <t xml:space="preserve">2.26239418983459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28562188148499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29336428642273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2825243473053</t>
   </si>
   <si>
     <t xml:space="preserve">2.28407335281372</t>
@@ -1610,43 +1610,43 @@
     <t xml:space="preserve">2.2902672290802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27013659477234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25619959831238</t>
+    <t xml:space="preserve">2.27013635635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25619983673096</t>
   </si>
   <si>
     <t xml:space="preserve">2.28097629547119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30265545845032</t>
+    <t xml:space="preserve">2.30265522003174</t>
   </si>
   <si>
     <t xml:space="preserve">2.30110692977905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30730104446411</t>
+    <t xml:space="preserve">2.30730128288269</t>
   </si>
   <si>
     <t xml:space="preserve">2.29800987243652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28871893882751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25929665565491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32433485984802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29181599617004</t>
+    <t xml:space="preserve">2.28871870040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25929689407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3243350982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29181575775146</t>
   </si>
   <si>
     <t xml:space="preserve">2.25465130805969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26858830451965</t>
+    <t xml:space="preserve">2.2685878276825</t>
   </si>
   <si>
     <t xml:space="preserve">2.26549100875854</t>
@@ -1655,25 +1655,25 @@
     <t xml:space="preserve">2.29955840110779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29646158218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31349492073059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32123756408691</t>
+    <t xml:space="preserve">2.296462059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31349539756775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32123780250549</t>
   </si>
   <si>
     <t xml:space="preserve">2.25774836540222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23916554450989</t>
+    <t xml:space="preserve">2.23916578292847</t>
   </si>
   <si>
     <t xml:space="preserve">2.34446597099304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38008165359497</t>
+    <t xml:space="preserve">2.38008189201355</t>
   </si>
   <si>
     <t xml:space="preserve">2.38163018226624</t>
@@ -1682,37 +1682,37 @@
     <t xml:space="preserve">2.40330958366394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42808604240417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43118262290955</t>
+    <t xml:space="preserve">2.4280858039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43118333816528</t>
   </si>
   <si>
     <t xml:space="preserve">2.4760901927948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49467253684998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49002695083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49622106552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50860929489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54887056350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52099752426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5024151802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51635193824768</t>
+    <t xml:space="preserve">2.4946722984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49002718925476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49622082710266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50860953330994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54887104034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52099776268005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50241541862488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5163516998291</t>
   </si>
   <si>
     <t xml:space="preserve">2.462153673172</t>
@@ -1721,22 +1721,22 @@
     <t xml:space="preserve">2.47918701171875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46525073051453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43427991867065</t>
+    <t xml:space="preserve">2.46525049209595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43428015708923</t>
   </si>
   <si>
     <t xml:space="preserve">2.44976544380188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45286202430725</t>
+    <t xml:space="preserve">2.45286273956299</t>
   </si>
   <si>
     <t xml:space="preserve">2.46679925918579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44666862487793</t>
+    <t xml:space="preserve">2.44666838645935</t>
   </si>
   <si>
     <t xml:space="preserve">2.4575080871582</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">2.47144460678101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45905661582947</t>
+    <t xml:space="preserve">2.45905637741089</t>
   </si>
   <si>
     <t xml:space="preserve">2.42653775215149</t>
@@ -1760,7 +1760,7 @@
     <t xml:space="preserve">2.48693013191223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5302882194519</t>
+    <t xml:space="preserve">2.53028845787048</t>
   </si>
   <si>
     <t xml:space="preserve">2.53803133964539</t>
@@ -1769,10 +1769,10 @@
     <t xml:space="preserve">2.54112839698792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54422521591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55661344528198</t>
+    <t xml:space="preserve">2.54422545433044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55661368370056</t>
   </si>
   <si>
     <t xml:space="preserve">2.55816197395325</t>
@@ -1781,13 +1781,13 @@
     <t xml:space="preserve">2.53648281097412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53493404388428</t>
+    <t xml:space="preserve">2.5349338054657</t>
   </si>
   <si>
     <t xml:space="preserve">2.5287401676178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51790070533752</t>
+    <t xml:space="preserve">2.51790046691895</t>
   </si>
   <si>
     <t xml:space="preserve">2.56435632705688</t>
@@ -1796,25 +1796,25 @@
     <t xml:space="preserve">2.5906810760498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60306930541992</t>
+    <t xml:space="preserve">2.6030695438385</t>
   </si>
   <si>
     <t xml:space="preserve">2.60461783409119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59997248649597</t>
+    <t xml:space="preserve">2.59997224807739</t>
   </si>
   <si>
     <t xml:space="preserve">2.60152053833008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58913278579712</t>
+    <t xml:space="preserve">2.58913254737854</t>
   </si>
   <si>
     <t xml:space="preserve">2.58603549003601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64642786979675</t>
+    <t xml:space="preserve">2.64642810821533</t>
   </si>
   <si>
     <t xml:space="preserve">2.65262198448181</t>
@@ -1823,25 +1823,25 @@
     <t xml:space="preserve">2.68514108657837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71611166000366</t>
+    <t xml:space="preserve">2.71611142158508</t>
   </si>
   <si>
     <t xml:space="preserve">2.69698429107666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67945075035095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68263816833496</t>
+    <t xml:space="preserve">2.67945051193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68263840675354</t>
   </si>
   <si>
     <t xml:space="preserve">2.65075898170471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68104434013367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66669869422913</t>
+    <t xml:space="preserve">2.68104457855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66669845581055</t>
   </si>
   <si>
     <t xml:space="preserve">2.7304573059082</t>
@@ -1850,34 +1850,34 @@
     <t xml:space="preserve">2.81174945831299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80856156349182</t>
+    <t xml:space="preserve">2.80856108665466</t>
   </si>
   <si>
     <t xml:space="preserve">2.78465175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77349448204041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78305792808533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79740381240845</t>
+    <t xml:space="preserve">2.77349424362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78305816650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79740357398987</t>
   </si>
   <si>
     <t xml:space="preserve">2.79580950737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82768893241882</t>
+    <t xml:space="preserve">2.82768869400024</t>
   </si>
   <si>
     <t xml:space="preserve">2.80696749687195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75914835929871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74480271339417</t>
+    <t xml:space="preserve">2.75914812088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74480295181274</t>
   </si>
   <si>
     <t xml:space="preserve">2.74958491325378</t>
@@ -1886,10 +1886,10 @@
     <t xml:space="preserve">2.7320511341095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72886347770691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73364543914795</t>
+    <t xml:space="preserve">2.72886323928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73364496231079</t>
   </si>
   <si>
     <t xml:space="preserve">2.66988658905029</t>
@@ -1898,25 +1898,25 @@
     <t xml:space="preserve">2.68582630157471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73683285713196</t>
+    <t xml:space="preserve">2.73683309555054</t>
   </si>
   <si>
     <t xml:space="preserve">2.71132969856262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69538998603821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70654773712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72726917266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70495343208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73523902893066</t>
+    <t xml:space="preserve">2.69538974761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70654797554016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72726941108704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70495390892029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73523926734924</t>
   </si>
   <si>
     <t xml:space="preserve">2.687420129776</t>
@@ -1928,13 +1928,13 @@
     <t xml:space="preserve">2.78783988952637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77827620506287</t>
+    <t xml:space="preserve">2.77827596664429</t>
   </si>
   <si>
     <t xml:space="preserve">2.78624582290649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81334328651428</t>
+    <t xml:space="preserve">2.81334352493286</t>
   </si>
   <si>
     <t xml:space="preserve">2.88188362121582</t>
@@ -1943,34 +1943,34 @@
     <t xml:space="preserve">2.87869572639465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91535663604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89144730567932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88666534423828</t>
+    <t xml:space="preserve">2.91535687446594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89144706726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88666558265686</t>
   </si>
   <si>
     <t xml:space="preserve">2.88825941085815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91695094108582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89622950553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80059146881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79262161254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84522247314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8181254863739</t>
+    <t xml:space="preserve">2.91695070266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89622926712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80059123039246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79262185096741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84522223472595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81812524795532</t>
   </si>
   <si>
     <t xml:space="preserve">2.82131290435791</t>
@@ -1979,10 +1979,10 @@
     <t xml:space="preserve">2.84681630134583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90738701820374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90419912338257</t>
+    <t xml:space="preserve">2.90738725662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90419888496399</t>
   </si>
   <si>
     <t xml:space="preserve">2.86913180351257</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">2.95042395591736</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02055811882019</t>
+    <t xml:space="preserve">3.02055835723877</t>
   </si>
   <si>
     <t xml:space="preserve">2.9647696018219</t>
@@ -2009,31 +2009,31 @@
     <t xml:space="preserve">2.97114562988281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01577639579773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02215218544006</t>
+    <t xml:space="preserve">3.01577615737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02215242385864</t>
   </si>
   <si>
     <t xml:space="preserve">3.00461864471436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97911500930786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00302481651306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01418256759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9838969707489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02374601364136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99664902687073</t>
+    <t xml:space="preserve">2.97911524772644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00302457809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01418280601501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98389720916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02374649047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99664878845215</t>
   </si>
   <si>
     <t xml:space="preserve">2.96636366844177</t>
@@ -2042,13 +2042,13 @@
     <t xml:space="preserve">2.99346113204956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00621247291565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04606199264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05881333351135</t>
+    <t xml:space="preserve">3.00621271133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04606175422668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05881357192993</t>
   </si>
   <si>
     <t xml:space="preserve">3.04924964904785</t>
@@ -2060,10 +2060,10 @@
     <t xml:space="preserve">3.03012204170227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05403184890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06678342819214</t>
+    <t xml:space="preserve">3.05403161048889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06678318977356</t>
   </si>
   <si>
     <t xml:space="preserve">3.05243754386902</t>
@@ -2072,10 +2072,10 @@
     <t xml:space="preserve">3.07315897941589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07475328445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1002562046051</t>
+    <t xml:space="preserve">3.07475304603577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10025668144226</t>
   </si>
   <si>
     <t xml:space="preserve">3.17357873916626</t>
@@ -2084,7 +2084,7 @@
     <t xml:space="preserve">3.19748830795288</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19430017471313</t>
+    <t xml:space="preserve">3.19430041313171</t>
   </si>
   <si>
     <t xml:space="preserve">3.21820950508118</t>
@@ -2093,25 +2093,25 @@
     <t xml:space="preserve">3.19589424133301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16242098808289</t>
+    <t xml:space="preserve">3.16242074966431</t>
   </si>
   <si>
     <t xml:space="preserve">3.17995452880859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15604519844055</t>
+    <t xml:space="preserve">3.15604543685913</t>
   </si>
   <si>
     <t xml:space="preserve">3.18473649024963</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17517256736755</t>
+    <t xml:space="preserve">3.17517280578613</t>
   </si>
   <si>
     <t xml:space="preserve">3.19111227989197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0620014667511</t>
+    <t xml:space="preserve">3.06200170516968</t>
   </si>
   <si>
     <t xml:space="preserve">3.08750486373901</t>
@@ -2120,58 +2120,58 @@
     <t xml:space="preserve">3.12416577339172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10185050964355</t>
+    <t xml:space="preserve">3.10185027122498</t>
   </si>
   <si>
     <t xml:space="preserve">3.09547472000122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0715651512146</t>
+    <t xml:space="preserve">3.07156491279602</t>
   </si>
   <si>
     <t xml:space="preserve">3.10344433784485</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11141419410706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06040716171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12735366821289</t>
+    <t xml:space="preserve">3.11141443252563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06040740013123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12735390663147</t>
   </si>
   <si>
     <t xml:space="preserve">3.17198467254639</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16879677772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1640145778656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22139716148376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16082715988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16560888290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10822629928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09706854820251</t>
+    <t xml:space="preserve">3.1687970161438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16401481628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22139739990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16082692146301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16560864448547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10822653770447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09706807136536</t>
   </si>
   <si>
     <t xml:space="preserve">3.10663223266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08112859725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07794117927551</t>
+    <t xml:space="preserve">3.0811288356781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07794094085693</t>
   </si>
   <si>
     <t xml:space="preserve">3.1432933807373</t>
@@ -2180,19 +2180,19 @@
     <t xml:space="preserve">3.18633031845093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18314266204834</t>
+    <t xml:space="preserve">3.18314242362976</t>
   </si>
   <si>
     <t xml:space="preserve">3.13213562965393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27240467071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37760591506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3138473033905</t>
+    <t xml:space="preserve">3.27240419387817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.377605676651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31384754180908</t>
   </si>
   <si>
     <t xml:space="preserve">3.44774031639099</t>
@@ -2201,13 +2201,13 @@
     <t xml:space="preserve">3.44614624977112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37919974327087</t>
+    <t xml:space="preserve">3.37919998168945</t>
   </si>
   <si>
     <t xml:space="preserve">3.26921653747559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27718663215637</t>
+    <t xml:space="preserve">3.27718615531921</t>
   </si>
   <si>
     <t xml:space="preserve">3.28675007820129</t>
@@ -2216,22 +2216,22 @@
     <t xml:space="preserve">3.33297514915466</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37282371520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38557577133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40948510169983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4270191192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43977046012878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47802567481995</t>
+    <t xml:space="preserve">3.37282395362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38557553291321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40948486328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42701888084412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43977022171021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47802472114563</t>
   </si>
   <si>
     <t xml:space="preserve">3.45252180099487</t>
@@ -2243,67 +2243,67 @@
     <t xml:space="preserve">3.47005558013916</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55612921714783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53700232505798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51628088951111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.339350938797</t>
+    <t xml:space="preserve">3.55612945556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53700256347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51628041267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33935046195984</t>
   </si>
   <si>
     <t xml:space="preserve">3.30906558036804</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33775663375854</t>
+    <t xml:space="preserve">3.3377571105957</t>
   </si>
   <si>
     <t xml:space="preserve">3.27877998352051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09069275856018</t>
+    <t xml:space="preserve">3.0906925201416</t>
   </si>
   <si>
     <t xml:space="preserve">3.11300802230835</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2612464427948</t>
+    <t xml:space="preserve">3.26124691963196</t>
   </si>
   <si>
     <t xml:space="preserve">2.83247089385986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6587290763855</t>
+    <t xml:space="preserve">2.65872931480408</t>
   </si>
   <si>
     <t xml:space="preserve">2.69060802459717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22038960456848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55830931663513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46585941314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51049041748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51686644554138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46107745170593</t>
+    <t xml:space="preserve">2.2203893661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55830907821655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46585917472839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51049017906189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5168662071228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46107769012451</t>
   </si>
   <si>
     <t xml:space="preserve">2.58381271362305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44195008277893</t>
+    <t xml:space="preserve">2.44194984436035</t>
   </si>
   <si>
     <t xml:space="preserve">2.41804051399231</t>
@@ -2312,40 +2312,40 @@
     <t xml:space="preserve">2.44035625457764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50252056121826</t>
+    <t xml:space="preserve">2.50252079963684</t>
   </si>
   <si>
     <t xml:space="preserve">2.62206768989563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60453391075134</t>
+    <t xml:space="preserve">2.60453414916992</t>
   </si>
   <si>
     <t xml:space="preserve">2.52802395820618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56468510627747</t>
+    <t xml:space="preserve">2.56468534469604</t>
   </si>
   <si>
     <t xml:space="preserve">2.53121209144592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55193328857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45948386192322</t>
+    <t xml:space="preserve">2.55193305015564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45948362350464</t>
   </si>
   <si>
     <t xml:space="preserve">2.57584309577942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56787300109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54715156555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54396367073059</t>
+    <t xml:space="preserve">2.56787276268005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54715180397034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54396390914917</t>
   </si>
   <si>
     <t xml:space="preserve">2.60772228240967</t>
@@ -2354,40 +2354,40 @@
     <t xml:space="preserve">2.62047386169434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51846027374268</t>
+    <t xml:space="preserve">2.51846051216125</t>
   </si>
   <si>
     <t xml:space="preserve">2.59018850326538</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58062481880188</t>
+    <t xml:space="preserve">2.5806245803833</t>
   </si>
   <si>
     <t xml:space="preserve">2.67307448387146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69220232963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57903099060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57265472412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52483582496643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49295687675476</t>
+    <t xml:space="preserve">2.69220185279846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57903051376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57265520095825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52483630180359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49295711517334</t>
   </si>
   <si>
     <t xml:space="preserve">2.59178280830383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61887979507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56149697303772</t>
+    <t xml:space="preserve">2.61887955665588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5614972114563</t>
   </si>
   <si>
     <t xml:space="preserve">2.47542309761047</t>
@@ -2402,7 +2402,7 @@
     <t xml:space="preserve">2.50092673301697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55352759361267</t>
+    <t xml:space="preserve">2.55352735519409</t>
   </si>
   <si>
     <t xml:space="preserve">2.54874563217163</t>
@@ -2411,31 +2411,31 @@
     <t xml:space="preserve">2.65713500976562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66032266616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85159826278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85638046264648</t>
+    <t xml:space="preserve">2.66032290458679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85159850120544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85638022422791</t>
   </si>
   <si>
     <t xml:space="preserve">2.81653118133545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77668213844299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6778564453125</t>
+    <t xml:space="preserve">2.77668190002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67785668373108</t>
   </si>
   <si>
     <t xml:space="preserve">2.80218553543091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78943371772766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77030658721924</t>
+    <t xml:space="preserve">2.78943347930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77030634880066</t>
   </si>
   <si>
     <t xml:space="preserve">2.75755453109741</t>
@@ -2444,34 +2444,34 @@
     <t xml:space="preserve">2.75436663627625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68901419639587</t>
+    <t xml:space="preserve">2.68901443481445</t>
   </si>
   <si>
     <t xml:space="preserve">2.63800740242004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70335960388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70017170906067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72567534446716</t>
+    <t xml:space="preserve">2.70335984230042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70017218589783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72567558288574</t>
   </si>
   <si>
     <t xml:space="preserve">2.74209499359131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69940400123596</t>
+    <t xml:space="preserve">2.69940376281738</t>
   </si>
   <si>
     <t xml:space="preserve">2.71418142318726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.641934633255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63372492790222</t>
+    <t xml:space="preserve">2.64193487167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63372468948364</t>
   </si>
   <si>
     <t xml:space="preserve">2.6747739315033</t>
@@ -2480,10 +2480,10 @@
     <t xml:space="preserve">2.63865065574646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65014457702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69447827339172</t>
+    <t xml:space="preserve">2.65014481544495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69447803497314</t>
   </si>
   <si>
     <t xml:space="preserve">2.7306010723114</t>
@@ -2501,34 +2501,34 @@
     <t xml:space="preserve">2.72567510604858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6616382598877</t>
+    <t xml:space="preserve">2.66163849830627</t>
   </si>
   <si>
     <t xml:space="preserve">2.61894702911377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63536691665649</t>
+    <t xml:space="preserve">2.63536667823792</t>
   </si>
   <si>
     <t xml:space="preserve">2.70268774032593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68790984153748</t>
+    <t xml:space="preserve">2.6879096031189</t>
   </si>
   <si>
     <t xml:space="preserve">2.59267544746399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61073708534241</t>
+    <t xml:space="preserve">2.61073732376099</t>
   </si>
   <si>
     <t xml:space="preserve">2.60252737998962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59595918655396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58774995803833</t>
+    <t xml:space="preserve">2.59595942497253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58774948120117</t>
   </si>
   <si>
     <t xml:space="preserve">2.66820621490479</t>
@@ -2537,13 +2537,13 @@
     <t xml:space="preserve">2.72403335571289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78642821311951</t>
+    <t xml:space="preserve">2.78642845153809</t>
   </si>
   <si>
     <t xml:space="preserve">2.77657628059387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75851464271545</t>
+    <t xml:space="preserve">2.75851511955261</t>
   </si>
   <si>
     <t xml:space="preserve">2.66656422615051</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">2.68298387527466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66328024864197</t>
+    <t xml:space="preserve">2.66328048706055</t>
   </si>
   <si>
     <t xml:space="preserve">2.75030493736267</t>
@@ -2564,25 +2564,25 @@
     <t xml:space="preserve">2.72239136695862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64686059951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62715721130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62879872322083</t>
+    <t xml:space="preserve">2.6468608379364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62715697288513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62879848480225</t>
   </si>
   <si>
     <t xml:space="preserve">2.6156632900238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69283580780029</t>
+    <t xml:space="preserve">2.69283604621887</t>
   </si>
   <si>
     <t xml:space="preserve">2.59760141372681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64850306510925</t>
+    <t xml:space="preserve">2.64850258827209</t>
   </si>
   <si>
     <t xml:space="preserve">2.64029288291931</t>
@@ -2591,19 +2591,19 @@
     <t xml:space="preserve">2.68134212493896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66492223739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67969989776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69776201248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71253943443298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63700890541077</t>
+    <t xml:space="preserve">2.66492247581482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67970013618469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69776153564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71253967285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63700866699219</t>
   </si>
   <si>
     <t xml:space="preserve">2.62387323379517</t>
@@ -2612,10 +2612,10 @@
     <t xml:space="preserve">2.60745334625244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64521884918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63044118881226</t>
+    <t xml:space="preserve">2.64521837234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63044095039368</t>
   </si>
   <si>
     <t xml:space="preserve">2.54998397827148</t>
@@ -2624,10 +2624,10 @@
     <t xml:space="preserve">2.55819392204285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54505801200867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51386117935181</t>
+    <t xml:space="preserve">2.54505825042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51386094093323</t>
   </si>
   <si>
     <t xml:space="preserve">2.52042865753174</t>
@@ -2639,22 +2639,22 @@
     <t xml:space="preserve">2.472811460495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42191052436829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44325613975525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35951519012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3841450214386</t>
+    <t xml:space="preserve">2.42191028594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44325566291809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35951542854309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38414478302002</t>
   </si>
   <si>
     <t xml:space="preserve">2.41205835342407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46295976638794</t>
+    <t xml:space="preserve">2.46295952796936</t>
   </si>
   <si>
     <t xml:space="preserve">2.39563870429993</t>
@@ -2666,133 +2666,133 @@
     <t xml:space="preserve">2.37757682800293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31518197059631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29219460487366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23472547531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19695997238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21666383743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23636722564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25442910194397</t>
+    <t xml:space="preserve">2.31518173217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29219436645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2347252368927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19696021080017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21666359901428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23636698722839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25442934036255</t>
   </si>
   <si>
     <t xml:space="preserve">2.3102560043335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30533051490784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28070092201233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.454749584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42519426345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44982409477234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49251532554626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47937917709351</t>
+    <t xml:space="preserve">2.30533003807068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28070068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45474982261658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42519450187683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44982361793518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49251508712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47937941551208</t>
   </si>
   <si>
     <t xml:space="preserve">2.56147789955139</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50893473625183</t>
+    <t xml:space="preserve">2.50893497467041</t>
   </si>
   <si>
     <t xml:space="preserve">2.49579906463623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50400876998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48102116584778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47609519958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52207064628601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53520631790161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51221895217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4711697101593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4399721622467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46788597106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44489789009094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43011999130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41534233093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38907122612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36444139480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39399671554565</t>
+    <t xml:space="preserve">2.50400924682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48102140426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47609543800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52207088470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53520655632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51221871376038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47116947174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43997192382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46788573265076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44489812850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43012022972107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4153425693512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38907098770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36444115638733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39399695396423</t>
   </si>
   <si>
     <t xml:space="preserve">2.36608338356018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40384888648987</t>
+    <t xml:space="preserve">2.40384840965271</t>
   </si>
   <si>
     <t xml:space="preserve">2.45146584510803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33981156349182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38742876052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45310759544373</t>
+    <t xml:space="preserve">2.3398118019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38742899894714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4531078338623</t>
   </si>
   <si>
     <t xml:space="preserve">2.45967578887939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44654011726379</t>
+    <t xml:space="preserve">2.44653987884521</t>
   </si>
   <si>
     <t xml:space="preserve">2.50565099716187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4416139125824</t>
+    <t xml:space="preserve">2.44161415100098</t>
   </si>
   <si>
     <t xml:space="preserve">2.49087309837341</t>
@@ -2804,13 +2804,13 @@
     <t xml:space="preserve">2.59431767463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5417742729187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38086104393005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33652758598328</t>
+    <t xml:space="preserve">2.54177451133728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38086080551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33652782440186</t>
   </si>
   <si>
     <t xml:space="preserve">2.35787320137024</t>
@@ -2822,10 +2822,10 @@
     <t xml:space="preserve">2.32995986938477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46952748298645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49415707588196</t>
+    <t xml:space="preserve">2.46952724456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49415731430054</t>
   </si>
   <si>
     <t xml:space="preserve">2.55326819419861</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">2.55491018295288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58939170837402</t>
+    <t xml:space="preserve">2.58939146995544</t>
   </si>
   <si>
     <t xml:space="preserve">2.54670023918152</t>
@@ -2852,52 +2852,52 @@
     <t xml:space="preserve">2.52535462379456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43176221847534</t>
+    <t xml:space="preserve">2.43176198005676</t>
   </si>
   <si>
     <t xml:space="preserve">2.40220665931702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5286386013031</t>
+    <t xml:space="preserve">2.52863836288452</t>
   </si>
   <si>
     <t xml:space="preserve">2.56311988830566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56968832015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60416913032532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71582365036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68216300010681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72895908355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70843505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69611978530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71171855926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73224329948425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76918768882751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76097774505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75440979003906</t>
+    <t xml:space="preserve">2.56968784332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6041693687439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71582388877869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68216323852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72895932197571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70843458175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69612002372742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71171832084656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73224353790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76918745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76097750663757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75441002845764</t>
   </si>
   <si>
     <t xml:space="preserve">2.75523090362549</t>
@@ -2906,10 +2906,10 @@
     <t xml:space="preserve">2.75605201721191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74620032310486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79381704330444</t>
+    <t xml:space="preserve">2.74620008468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7938175201416</t>
   </si>
   <si>
     <t xml:space="preserve">2.76261973381042</t>
@@ -2924,31 +2924,31 @@
     <t xml:space="preserve">2.83815050125122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77082967758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77247142791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76426196098328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86278009414673</t>
+    <t xml:space="preserve">2.77082943916321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77247166633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7642617225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86278033256531</t>
   </si>
   <si>
     <t xml:space="preserve">2.83240365982056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82255148887634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86031723022461</t>
+    <t xml:space="preserve">2.82255172729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86031699180603</t>
   </si>
   <si>
     <t xml:space="preserve">2.87837910652161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88330483436584</t>
+    <t xml:space="preserve">2.88330459594727</t>
   </si>
   <si>
     <t xml:space="preserve">2.88740968704224</t>
@@ -2963,31 +2963,31 @@
     <t xml:space="preserve">2.86113810539246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86606407165527</t>
+    <t xml:space="preserve">2.86606383323669</t>
   </si>
   <si>
     <t xml:space="preserve">2.86360096931458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87427377700806</t>
+    <t xml:space="preserve">2.87427401542664</t>
   </si>
   <si>
     <t xml:space="preserve">2.89726138114929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93256402015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95883560180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97197103500366</t>
+    <t xml:space="preserve">2.93256378173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95883536338806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97197127342224</t>
   </si>
   <si>
     <t xml:space="preserve">3.02533531188965</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00481104850769</t>
+    <t xml:space="preserve">3.00481081008911</t>
   </si>
   <si>
     <t xml:space="preserve">3.00809478759766</t>
@@ -2996,13 +2996,13 @@
     <t xml:space="preserve">3.04093432426453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01794648170471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04586005210876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02123045921326</t>
+    <t xml:space="preserve">3.01794672012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04586029052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02123022079468</t>
   </si>
   <si>
     <t xml:space="preserve">3.00727391242981</t>
@@ -3011,10 +3011,10 @@
     <t xml:space="preserve">2.98921203613281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95801424980164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90218734741211</t>
+    <t xml:space="preserve">2.95801448822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90218758583069</t>
   </si>
   <si>
     <t xml:space="preserve">2.92353320121765</t>
@@ -3023,10 +3023,10 @@
     <t xml:space="preserve">2.89561939239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89069366455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89151453971863</t>
+    <t xml:space="preserve">2.89069390296936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89151477813721</t>
   </si>
   <si>
     <t xml:space="preserve">2.8668851852417</t>
@@ -3038,16 +3038,16 @@
     <t xml:space="preserve">2.90920472145081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89649343490601</t>
+    <t xml:space="preserve">2.89649319648743</t>
   </si>
   <si>
     <t xml:space="preserve">2.96005034446716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86598610877991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86429166793823</t>
+    <t xml:space="preserve">2.86598587036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86429142951965</t>
   </si>
   <si>
     <t xml:space="preserve">2.93208527565002</t>
@@ -3062,19 +3062,19 @@
     <t xml:space="preserve">2.89564609527588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92615342140198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84225821495056</t>
+    <t xml:space="preserve">2.92615365982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84225845336914</t>
   </si>
   <si>
     <t xml:space="preserve">2.85073256492615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94733881950378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99987888336182</t>
+    <t xml:space="preserve">2.94733858108521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99987936019897</t>
   </si>
   <si>
     <t xml:space="preserve">2.9778459072113</t>
@@ -3083,28 +3083,28 @@
     <t xml:space="preserve">2.99055743217468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03292846679688</t>
+    <t xml:space="preserve">3.03292870521545</t>
   </si>
   <si>
     <t xml:space="preserve">3.06428337097168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04055547714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04479265213013</t>
+    <t xml:space="preserve">3.04055571556091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04479241371155</t>
   </si>
   <si>
     <t xml:space="preserve">3.02275943756104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01004815101624</t>
+    <t xml:space="preserve">3.01004838943481</t>
   </si>
   <si>
     <t xml:space="preserve">3.00157403945923</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02021718025208</t>
+    <t xml:space="preserve">3.02021741867065</t>
   </si>
   <si>
     <t xml:space="preserve">3.04648756980896</t>
@@ -3116,13 +3116,13 @@
     <t xml:space="preserve">3.08546900749207</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09733271598816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13122987747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14563608169556</t>
+    <t xml:space="preserve">3.09733295440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13122963905334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14563584327698</t>
   </si>
   <si>
     <t xml:space="preserve">3.15665245056152</t>
@@ -3131,13 +3131,13 @@
     <t xml:space="preserve">3.18038034439087</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19648122787476</t>
+    <t xml:space="preserve">3.19648146629333</t>
   </si>
   <si>
     <t xml:space="preserve">3.18546485900879</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18715953826904</t>
+    <t xml:space="preserve">3.18715977668762</t>
   </si>
   <si>
     <t xml:space="preserve">3.16682147979736</t>
@@ -3158,82 +3158,82 @@
     <t xml:space="preserve">3.10411238670349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13716173171997</t>
+    <t xml:space="preserve">3.13716149330139</t>
   </si>
   <si>
     <t xml:space="preserve">3.12275552749634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11004400253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12529754638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08123159408569</t>
+    <t xml:space="preserve">3.11004424095154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1252977848053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08123183250427</t>
   </si>
   <si>
     <t xml:space="preserve">3.03631830215454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07360506057739</t>
+    <t xml:space="preserve">3.07360482215881</t>
   </si>
   <si>
     <t xml:space="preserve">3.09902763366699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04987740516663</t>
+    <t xml:space="preserve">3.04987716674805</t>
   </si>
   <si>
     <t xml:space="preserve">3.08377408981323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04140281677246</t>
+    <t xml:space="preserve">3.04140257835388</t>
   </si>
   <si>
     <t xml:space="preserve">3.08631610870361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08292675018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09224843978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02360701560974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9744565486908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01428508758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99648952484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9956419467926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99818444252014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00411629676819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96089768409729</t>
+    <t xml:space="preserve">3.08292651176453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09224796295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02360725402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97445631027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01428532600403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99648928642273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99564218521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99818420410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00411605834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96089744567871</t>
   </si>
   <si>
     <t xml:space="preserve">2.98547291755676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91089963912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87785005569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91174745559692</t>
+    <t xml:space="preserve">2.91089940071106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87785029411316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91174721717834</t>
   </si>
   <si>
     <t xml:space="preserve">2.94564414024353</t>
@@ -3245,19 +3245,19 @@
     <t xml:space="preserve">2.95327091217041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92445802688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9439492225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00242137908936</t>
+    <t xml:space="preserve">2.92445850372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94394898414612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00242114067078</t>
   </si>
   <si>
     <t xml:space="preserve">3.03377604484558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04902982711792</t>
+    <t xml:space="preserve">3.04902958869934</t>
   </si>
   <si>
     <t xml:space="preserve">3.01767492294312</t>
@@ -3269,16 +3269,16 @@
     <t xml:space="preserve">2.99733686447144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01259064674377</t>
+    <t xml:space="preserve">3.0125904083252</t>
   </si>
   <si>
     <t xml:space="preserve">2.9947943687439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03462362289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11258673667908</t>
+    <t xml:space="preserve">3.03462338447571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11258625984192</t>
   </si>
   <si>
     <t xml:space="preserve">3.09309577941895</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">3.0566565990448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01682782173157</t>
+    <t xml:space="preserve">3.01682758331299</t>
   </si>
   <si>
     <t xml:space="preserve">3.05750393867493</t>
@@ -3299,10 +3299,10 @@
     <t xml:space="preserve">3.07275748252869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03208112716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02953863143921</t>
+    <t xml:space="preserve">3.03208136558533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02953910827637</t>
   </si>
   <si>
     <t xml:space="preserve">3.00072646141052</t>
@@ -3314,19 +3314,19 @@
     <t xml:space="preserve">2.8702232837677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88547682762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95750784873962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88971424102783</t>
+    <t xml:space="preserve">2.88547706604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95750761032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88971400260925</t>
   </si>
   <si>
     <t xml:space="preserve">3.02530169487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98208355903625</t>
+    <t xml:space="preserve">2.9820830821991</t>
   </si>
   <si>
     <t xml:space="preserve">3.0083532333374</t>
@@ -3335,31 +3335,31 @@
     <t xml:space="preserve">2.97869372367859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00326871871948</t>
+    <t xml:space="preserve">3.00326895713806</t>
   </si>
   <si>
     <t xml:space="preserve">3.02445435523987</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04564023017883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05072426795959</t>
+    <t xml:space="preserve">3.04563999176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05072450637817</t>
   </si>
   <si>
     <t xml:space="preserve">3.06089377403259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11682367324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10241746902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14055156707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11173892021179</t>
+    <t xml:space="preserve">3.11682343482971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10241723060608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14055132865906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11173915863037</t>
   </si>
   <si>
     <t xml:space="preserve">3.0871639251709</t>
@@ -3368,16 +3368,16 @@
     <t xml:space="preserve">3.02699661254883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01343774795532</t>
+    <t xml:space="preserve">3.0134379863739</t>
   </si>
   <si>
     <t xml:space="preserve">2.99394726753235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97106671333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98123550415039</t>
+    <t xml:space="preserve">2.97106695175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98123574256897</t>
   </si>
   <si>
     <t xml:space="preserve">2.9490339756012</t>
@@ -3395,10 +3395,10 @@
     <t xml:space="preserve">3.07614731788635</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14817810058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1337718963623</t>
+    <t xml:space="preserve">3.14817833900452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13377213478088</t>
   </si>
   <si>
     <t xml:space="preserve">3.07021522521973</t>
@@ -3416,37 +3416,37 @@
     <t xml:space="preserve">2.93801712989807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92530584335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86005449295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88717174530029</t>
+    <t xml:space="preserve">2.92530560493469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86005401611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88717198371887</t>
   </si>
   <si>
     <t xml:space="preserve">2.87276554107666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84310555458069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83802127838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79734492301941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80836129188538</t>
+    <t xml:space="preserve">2.84310579299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83802103996277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79734516143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80836153030396</t>
   </si>
   <si>
     <t xml:space="preserve">2.82446241378784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74056768417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93632221221924</t>
+    <t xml:space="preserve">2.740567445755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93632245063782</t>
   </si>
   <si>
     <t xml:space="preserve">2.83208918571472</t>
@@ -3455,28 +3455,28 @@
     <t xml:space="preserve">2.78971815109253</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7626006603241</t>
+    <t xml:space="preserve">2.76260042190552</t>
   </si>
   <si>
     <t xml:space="preserve">2.69904351234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71175527572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77446436882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87700271606445</t>
+    <t xml:space="preserve">2.71175503730774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77446460723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87700247764587</t>
   </si>
   <si>
     <t xml:space="preserve">2.86344385147095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85666465759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85157990455627</t>
+    <t xml:space="preserve">2.85666441917419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85158014297485</t>
   </si>
   <si>
     <t xml:space="preserve">2.81937789916992</t>
@@ -3488,13 +3488,13 @@
     <t xml:space="preserve">2.89140892028809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78802299499512</t>
+    <t xml:space="preserve">2.78802347183228</t>
   </si>
   <si>
     <t xml:space="preserve">2.75666856765747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.814293384552</t>
+    <t xml:space="preserve">2.81429362297058</t>
   </si>
   <si>
     <t xml:space="preserve">2.82700490951538</t>
@@ -3503,16 +3503,16 @@
     <t xml:space="preserve">2.85327506065369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83547878265381</t>
+    <t xml:space="preserve">2.83547902107239</t>
   </si>
   <si>
     <t xml:space="preserve">2.87615513801575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90750980377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00581121444702</t>
+    <t xml:space="preserve">2.90751004219055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00581097602844</t>
   </si>
   <si>
     <t xml:space="preserve">3.04733467102051</t>
@@ -3521,37 +3521,37 @@
     <t xml:space="preserve">3.00496363639832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04394483566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05835103988647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01598024368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04818201065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97276163101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98377799987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9524233341217</t>
+    <t xml:space="preserve">3.04394507408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05835127830505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01598048210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04818224906921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97276139259338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98377823829651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95242357254028</t>
   </si>
   <si>
     <t xml:space="preserve">2.98632025718689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06343603134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84141087532043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86513876914978</t>
+    <t xml:space="preserve">3.06343579292297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84141063690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86513900756836</t>
   </si>
   <si>
     <t xml:space="preserve">2.92954301834106</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">2.95072865486145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03801321983337</t>
+    <t xml:space="preserve">3.03801298141479</t>
   </si>
   <si>
     <t xml:space="preserve">2.98801517486572</t>
@@ -3578,19 +3578,19 @@
     <t xml:space="preserve">2.82785201072693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86174893379211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83717370033264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83886861801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7270085811615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53125381469727</t>
+    <t xml:space="preserve">2.86174917221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83717393875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83886885643005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72700881958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53125405311584</t>
   </si>
   <si>
     <t xml:space="preserve">2.41685175895691</t>
@@ -3599,13 +3599,13 @@
     <t xml:space="preserve">2.35668468475342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45837545394897</t>
+    <t xml:space="preserve">2.45837569236755</t>
   </si>
   <si>
     <t xml:space="preserve">2.38888669013977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41769909858704</t>
+    <t xml:space="preserve">2.41769933700562</t>
   </si>
   <si>
     <t xml:space="preserve">2.3823139667511</t>
@@ -3614,7 +3614,7 @@
     <t xml:space="preserve">2.34250545501709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32569742202759</t>
+    <t xml:space="preserve">2.32569718360901</t>
   </si>
   <si>
     <t xml:space="preserve">2.37435221672058</t>
@@ -3632,46 +3632,46 @@
     <t xml:space="preserve">2.47608494758606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44158434867859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4875853061676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48493099212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41327595710754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45750784873962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49112343788147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47696948051453</t>
+    <t xml:space="preserve">2.44158411026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48758506774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48493123054504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41327571868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45750761032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49112367630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47696924209595</t>
   </si>
   <si>
     <t xml:space="preserve">2.45927667617798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37523674964905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30446624755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37789058685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38673710823059</t>
+    <t xml:space="preserve">2.37523698806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30446600914001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37789082527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38673686981201</t>
   </si>
   <si>
     <t xml:space="preserve">2.41150689125061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38319849967957</t>
+    <t xml:space="preserve">2.38319826126099</t>
   </si>
   <si>
     <t xml:space="preserve">2.40619897842407</t>
@@ -3680,37 +3680,37 @@
     <t xml:space="preserve">2.41946816444397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40089106559753</t>
+    <t xml:space="preserve">2.40089130401611</t>
   </si>
   <si>
     <t xml:space="preserve">2.47873878479004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43008399009705</t>
+    <t xml:space="preserve">2.43008375167847</t>
   </si>
   <si>
     <t xml:space="preserve">2.44689202308655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50970053672791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50527763366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47077703475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44246888160706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4398148059845</t>
+    <t xml:space="preserve">2.50970077514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50527787208557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47077679634094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44246864318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43981504440308</t>
   </si>
   <si>
     <t xml:space="preserve">2.4433536529541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46900773048401</t>
+    <t xml:space="preserve">2.46900796890259</t>
   </si>
   <si>
     <t xml:space="preserve">2.47520017623901</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">2.42300701141357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40442943572998</t>
+    <t xml:space="preserve">2.40442967414856</t>
   </si>
   <si>
     <t xml:space="preserve">2.36904430389404</t>
@@ -3746,10 +3746,10 @@
     <t xml:space="preserve">2.21246433258057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24342679977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18504095077515</t>
+    <t xml:space="preserve">2.24342656135559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18504071235657</t>
   </si>
   <si>
     <t xml:space="preserve">2.07269263267517</t>
@@ -3758,7 +3758,7 @@
     <t xml:space="preserve">2.12842440605164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11603975296021</t>
+    <t xml:space="preserve">2.11603951454163</t>
   </si>
   <si>
     <t xml:space="preserve">2.2009642124176</t>
@@ -3773,28 +3773,28 @@
     <t xml:space="preserve">2.14965581893921</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14700174331665</t>
+    <t xml:space="preserve">2.14700198173523</t>
   </si>
   <si>
     <t xml:space="preserve">2.11957812309265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1063084602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07800054550171</t>
+    <t xml:space="preserve">2.10630869865417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07800030708313</t>
   </si>
   <si>
     <t xml:space="preserve">2.07357740402222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04261517524719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97803723812103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98422968387604</t>
+    <t xml:space="preserve">2.04261541366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97803699970245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98422932624817</t>
   </si>
   <si>
     <t xml:space="preserve">1.87895834445953</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">1.92584371566772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9161125421524</t>
+    <t xml:space="preserve">1.91611266136169</t>
   </si>
   <si>
     <t xml:space="preserve">1.93380570411682</t>
@@ -3818,19 +3818,19 @@
     <t xml:space="preserve">1.90018951892853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84003436565399</t>
+    <t xml:space="preserve">1.84003448486328</t>
   </si>
   <si>
     <t xml:space="preserve">1.82588028907776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87011194229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80464911460876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77280247211456</t>
+    <t xml:space="preserve">1.87011206150055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80464923381805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77280235290527</t>
   </si>
   <si>
     <t xml:space="preserve">1.80022609233856</t>
@@ -3839,25 +3839,25 @@
     <t xml:space="preserve">1.83030343055725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87807357311249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88249695301056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8630348443985</t>
+    <t xml:space="preserve">1.87807369232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88249683380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86303472518921</t>
   </si>
   <si>
     <t xml:space="preserve">1.87541949748993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85153472423553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91257441043854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99838364124298</t>
+    <t xml:space="preserve">1.85153460502625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91257429122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99838376045227</t>
   </si>
   <si>
     <t xml:space="preserve">2.01696085929871</t>
@@ -3872,10 +3872,10 @@
     <t xml:space="preserve">2.14434790611267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14257836341858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13196301460266</t>
+    <t xml:space="preserve">2.14257860183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13196325302124</t>
   </si>
   <si>
     <t xml:space="preserve">2.1779637336731</t>
@@ -3902,13 +3902,13 @@
     <t xml:space="preserve">2.33454370498657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31773567199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33631300926208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32835125923157</t>
+    <t xml:space="preserve">2.31773591041565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33631277084351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32835149765015</t>
   </si>
   <si>
     <t xml:space="preserve">2.3274667263031</t>
@@ -3929,16 +3929,16 @@
     <t xml:space="preserve">2.34338998794556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35400557518005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37169814109802</t>
+    <t xml:space="preserve">2.35400581359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3716983795166</t>
   </si>
   <si>
     <t xml:space="preserve">2.37965989112854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37612175941467</t>
+    <t xml:space="preserve">2.37612152099609</t>
   </si>
   <si>
     <t xml:space="preserve">2.4327380657196</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">2.48050785064697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50350856781006</t>
+    <t xml:space="preserve">2.50350832939148</t>
   </si>
   <si>
     <t xml:space="preserve">2.44600749015808</t>
@@ -3968,7 +3968,7 @@
     <t xml:space="preserve">2.24165749549866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25758075714111</t>
+    <t xml:space="preserve">2.25758051872253</t>
   </si>
   <si>
     <t xml:space="preserve">2.25492691993713</t>
@@ -3980,13 +3980,13 @@
     <t xml:space="preserve">2.25227308273315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22838807106018</t>
+    <t xml:space="preserve">2.2283878326416</t>
   </si>
   <si>
     <t xml:space="preserve">2.28765821456909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2894275188446</t>
+    <t xml:space="preserve">2.28942728042603</t>
   </si>
   <si>
     <t xml:space="preserve">2.33542847633362</t>
@@ -3995,16 +3995,16 @@
     <t xml:space="preserve">2.32304334640503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45043039321899</t>
+    <t xml:space="preserve">2.45043063163757</t>
   </si>
   <si>
     <t xml:space="preserve">2.45131516456604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42389130592346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42919921875</t>
+    <t xml:space="preserve">2.42389154434204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42919945716858</t>
   </si>
   <si>
     <t xml:space="preserve">2.40708374977112</t>
@@ -4013,13 +4013,13 @@
     <t xml:space="preserve">2.34781336784363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38850617408752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41416049003601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40177583694458</t>
+    <t xml:space="preserve">2.3885064125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41416072845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.401775598526</t>
   </si>
   <si>
     <t xml:space="preserve">2.39646816253662</t>
@@ -4028,19 +4028,19 @@
     <t xml:space="preserve">2.34692859649658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34073615074158</t>
+    <t xml:space="preserve">2.340735912323</t>
   </si>
   <si>
     <t xml:space="preserve">2.3442747592926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41062211990356</t>
+    <t xml:space="preserve">2.41062188148499</t>
   </si>
   <si>
     <t xml:space="preserve">2.37081384658813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31596636772156</t>
+    <t xml:space="preserve">2.31596660614014</t>
   </si>
   <si>
     <t xml:space="preserve">2.28854274749756</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">2.26642727851868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23458027839661</t>
+    <t xml:space="preserve">2.23458051681519</t>
   </si>
   <si>
     <t xml:space="preserve">2.22661876678467</t>
@@ -4067,19 +4067,19 @@
     <t xml:space="preserve">2.22219562530518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23192667961121</t>
+    <t xml:space="preserve">2.23192620277405</t>
   </si>
   <si>
     <t xml:space="preserve">2.1753101348877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1947717666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22573399543762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1815025806427</t>
+    <t xml:space="preserve">2.19477200508118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2257342338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18150234222412</t>
   </si>
   <si>
     <t xml:space="preserve">2.15054035186768</t>
@@ -4091,13 +4091,13 @@
     <t xml:space="preserve">2.10807776451111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13727045059204</t>
+    <t xml:space="preserve">2.13727068901062</t>
   </si>
   <si>
     <t xml:space="preserve">2.12753963470459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11692404747009</t>
+    <t xml:space="preserve">2.11692428588867</t>
   </si>
   <si>
     <t xml:space="preserve">2.18857932090759</t>
@@ -4106,7 +4106,7 @@
     <t xml:space="preserve">2.20627212524414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22131085395813</t>
+    <t xml:space="preserve">2.22131061553955</t>
   </si>
   <si>
     <t xml:space="preserve">2.20361804962158</t>
@@ -4115,31 +4115,31 @@
     <t xml:space="preserve">2.21423363685608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24254202842712</t>
+    <t xml:space="preserve">2.24254179000854</t>
   </si>
   <si>
     <t xml:space="preserve">2.30181241035461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29827380180359</t>
+    <t xml:space="preserve">2.29827404022217</t>
   </si>
   <si>
     <t xml:space="preserve">2.40266036987305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42212224006653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31950497627258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39558339118958</t>
+    <t xml:space="preserve">2.42212247848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.319504737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.395583152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.39027547836304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46989226341248</t>
+    <t xml:space="preserve">2.46989250183105</t>
   </si>
   <si>
     <t xml:space="preserve">2.49820065498352</t>
@@ -4151,13 +4151,13 @@
     <t xml:space="preserve">2.49643135070801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53181672096252</t>
+    <t xml:space="preserve">2.53181648254395</t>
   </si>
   <si>
     <t xml:space="preserve">2.52297043800354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54066276550293</t>
+    <t xml:space="preserve">2.54066300392151</t>
   </si>
   <si>
     <t xml:space="preserve">2.62381839752197</t>
@@ -4169,7 +4169,7 @@
     <t xml:space="preserve">2.67689633369446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67866563796997</t>
+    <t xml:space="preserve">2.67866587638855</t>
   </si>
   <si>
     <t xml:space="preserve">2.6379725933075</t>
@@ -4178,37 +4178,37 @@
     <t xml:space="preserve">2.53712439537048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61497235298157</t>
+    <t xml:space="preserve">2.61497211456299</t>
   </si>
   <si>
     <t xml:space="preserve">2.63266468048096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62204885482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54950952529907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52827835083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57958674430847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58135581016541</t>
+    <t xml:space="preserve">2.62204909324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54950904846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5282781124115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57958650588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58135604858398</t>
   </si>
   <si>
     <t xml:space="preserve">2.60966444015503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58666372299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59020256996155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.538893699646</t>
+    <t xml:space="preserve">2.58666396141052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59020233154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53889346122742</t>
   </si>
   <si>
     <t xml:space="preserve">2.572509765625</t>
@@ -4217,25 +4217,25 @@
     <t xml:space="preserve">2.54420161247253</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55304789543152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56366348266602</t>
+    <t xml:space="preserve">2.55304765701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56366324424744</t>
   </si>
   <si>
     <t xml:space="preserve">2.55127859115601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53004717826843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56897139549255</t>
+    <t xml:space="preserve">2.53004741668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56897115707397</t>
   </si>
   <si>
     <t xml:space="preserve">2.51812791824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52922129631042</t>
+    <t xml:space="preserve">2.52922105789185</t>
   </si>
   <si>
     <t xml:space="preserve">2.53661632537842</t>
@@ -4262,16 +4262,16 @@
     <t xml:space="preserve">2.46451139450073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41274356842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40904593467712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42013907432556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44787192344666</t>
+    <t xml:space="preserve">2.41274380683899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4090461730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42013931274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44787168502808</t>
   </si>
   <si>
     <t xml:space="preserve">2.47375583648682</t>
@@ -4292,10 +4292,10 @@
     <t xml:space="preserve">2.52737212181091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54216289520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53846549987793</t>
+    <t xml:space="preserve">2.54216313362122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53846526145935</t>
   </si>
   <si>
     <t xml:space="preserve">2.58653521537781</t>
@@ -4304,7 +4304,7 @@
     <t xml:space="preserve">2.56250047683716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59393048286438</t>
+    <t xml:space="preserve">2.59393072128296</t>
   </si>
   <si>
     <t xml:space="preserve">2.63275647163391</t>
@@ -4319,10 +4319,10 @@
     <t xml:space="preserve">2.60132598876953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45711612701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39980173110962</t>
+    <t xml:space="preserve">2.45711588859558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3998019695282</t>
   </si>
   <si>
     <t xml:space="preserve">2.44602274894714</t>
@@ -4334,10 +4334,10 @@
     <t xml:space="preserve">2.47190690040588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47005772590637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42383694648743</t>
+    <t xml:space="preserve">2.47005796432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42383670806885</t>
   </si>
   <si>
     <t xml:space="preserve">2.38316226005554</t>
@@ -4349,34 +4349,34 @@
     <t xml:space="preserve">2.49594187736511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52182579040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5403139591217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55140709877014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57913994789124</t>
+    <t xml:space="preserve">2.52182555198669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54031419754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55140733718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57913970947266</t>
   </si>
   <si>
     <t xml:space="preserve">2.5680468082428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58468627929688</t>
+    <t xml:space="preserve">2.58468651771545</t>
   </si>
   <si>
     <t xml:space="preserve">2.57544207572937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54770970344543</t>
+    <t xml:space="preserve">2.54770946502686</t>
   </si>
   <si>
     <t xml:space="preserve">2.60687255859375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60317468643188</t>
+    <t xml:space="preserve">2.60317492485046</t>
   </si>
   <si>
     <t xml:space="preserve">2.6456983089447</t>
@@ -4400,7 +4400,7 @@
     <t xml:space="preserve">2.667884349823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69376826286316</t>
+    <t xml:space="preserve">2.69376850128174</t>
   </si>
   <si>
     <t xml:space="preserve">2.56434917449951</t>
@@ -4433,22 +4433,22 @@
     <t xml:space="preserve">2.35358071327209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39795327186584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41089487075806</t>
+    <t xml:space="preserve">2.39795303344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41089510917664</t>
   </si>
   <si>
     <t xml:space="preserve">2.42753434181213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40534853935242</t>
+    <t xml:space="preserve">2.40534830093384</t>
   </si>
   <si>
     <t xml:space="preserve">2.39240646362305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37206935882568</t>
+    <t xml:space="preserve">2.3720691204071</t>
   </si>
   <si>
     <t xml:space="preserve">2.34988307952881</t>
@@ -4463,7 +4463,7 @@
     <t xml:space="preserve">2.34803414344788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45341825485229</t>
+    <t xml:space="preserve">2.45341849327087</t>
   </si>
   <si>
     <t xml:space="preserve">2.49224424362183</t>
@@ -4475,7 +4475,7 @@
     <t xml:space="preserve">2.49779057502747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4626624584198</t>
+    <t xml:space="preserve">2.46266269683838</t>
   </si>
   <si>
     <t xml:space="preserve">2.45526719093323</t>
@@ -4490,7 +4490,7 @@
     <t xml:space="preserve">2.62536096572876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64015173912048</t>
+    <t xml:space="preserve">2.64015197753906</t>
   </si>
   <si>
     <t xml:space="preserve">2.62720990180969</t>
@@ -4499,19 +4499,19 @@
     <t xml:space="preserve">2.63090753555298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68082642555237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68637299537659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68822193145752</t>
+    <t xml:space="preserve">2.68082666397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68637275695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68822169303894</t>
   </si>
   <si>
     <t xml:space="preserve">2.66603565216064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68267512321472</t>
+    <t xml:space="preserve">2.6826753616333</t>
   </si>
   <si>
     <t xml:space="preserve">2.68452405929565</t>
@@ -4520,19 +4520,19 @@
     <t xml:space="preserve">2.69007062911987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74368691444397</t>
+    <t xml:space="preserve">2.74368715286255</t>
   </si>
   <si>
     <t xml:space="preserve">2.71225690841675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69561719894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73444271087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80100131034851</t>
+    <t xml:space="preserve">2.69561696052551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73444294929504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80100154876709</t>
   </si>
   <si>
     <t xml:space="preserve">2.78990817070007</t>
@@ -4544,7 +4544,7 @@
     <t xml:space="preserve">2.79545474052429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78621077537537</t>
+    <t xml:space="preserve">2.78621053695679</t>
   </si>
   <si>
     <t xml:space="preserve">2.76772212982178</t>
@@ -4556,7 +4556,7 @@
     <t xml:space="preserve">2.75662922859192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73998951911926</t>
+    <t xml:space="preserve">2.73998928070068</t>
   </si>
   <si>
     <t xml:space="preserve">2.74738478660583</t>
@@ -4604,22 +4604,22 @@
     <t xml:space="preserve">2.98033928871155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96924638748169</t>
+    <t xml:space="preserve">2.96924614906311</t>
   </si>
   <si>
     <t xml:space="preserve">3.02286291122437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92672300338745</t>
+    <t xml:space="preserve">2.92672276496887</t>
   </si>
   <si>
     <t xml:space="preserve">2.91562986373901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87495493888855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90083909034729</t>
+    <t xml:space="preserve">2.87495517730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90083885192871</t>
   </si>
   <si>
     <t xml:space="preserve">2.9193274974823</t>
@@ -4646,7 +4646,7 @@
     <t xml:space="preserve">2.99513030052185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98773503303528</t>
+    <t xml:space="preserve">2.9877347946167</t>
   </si>
   <si>
     <t xml:space="preserve">2.98958349227905</t>
@@ -4655,16 +4655,16 @@
     <t xml:space="preserve">2.93411827087402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96000218391418</t>
+    <t xml:space="preserve">2.96000194549561</t>
   </si>
   <si>
     <t xml:space="preserve">2.94890904426575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95445561408997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97849059104919</t>
+    <t xml:space="preserve">2.95445585250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97849035263062</t>
   </si>
   <si>
     <t xml:space="preserve">2.95260691642761</t>
@@ -4688,10 +4688,10 @@
     <t xml:space="preserve">3.08572363853455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09496784210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11900305747986</t>
+    <t xml:space="preserve">3.09496808052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11900281906128</t>
   </si>
   <si>
     <t xml:space="preserve">3.05983972549438</t>
@@ -4709,13 +4709,13 @@
     <t xml:space="preserve">3.06908392906189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02471160888672</t>
+    <t xml:space="preserve">3.0247118473053</t>
   </si>
   <si>
     <t xml:space="preserve">3.01916527748108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97479271888733</t>
+    <t xml:space="preserve">2.97479295730591</t>
   </si>
   <si>
     <t xml:space="preserve">2.92302513122559</t>
@@ -4724,7 +4724,7 @@
     <t xml:space="preserve">2.93781590461731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88419914245605</t>
+    <t xml:space="preserve">2.88419938087463</t>
   </si>
   <si>
     <t xml:space="preserve">2.90823435783386</t>
@@ -4739,19 +4739,19 @@
     <t xml:space="preserve">2.95815324783325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97109532356262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01546740531921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11345624923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13933992385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10975885391235</t>
+    <t xml:space="preserve">2.97109508514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01546764373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11345648765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13934016227722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10975861549377</t>
   </si>
   <si>
     <t xml:space="preserve">3.16337513923645</t>
@@ -4760,7 +4760,7 @@
     <t xml:space="preserve">3.13379383087158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15782833099365</t>
+    <t xml:space="preserve">3.15782856941223</t>
   </si>
   <si>
     <t xml:space="preserve">3.16892170906067</t>
@@ -4769,7 +4769,7 @@
     <t xml:space="preserve">3.19480562210083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24287557601929</t>
+    <t xml:space="preserve">3.24287533760071</t>
   </si>
   <si>
     <t xml:space="preserve">3.20959615707397</t>
@@ -4778,7 +4778,7 @@
     <t xml:space="preserve">3.20589852333069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23548007011414</t>
+    <t xml:space="preserve">3.23548030853271</t>
   </si>
   <si>
     <t xml:space="preserve">3.29464316368103</t>
@@ -4793,10 +4793,10 @@
     <t xml:space="preserve">3.20774745941162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17446804046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12085175514221</t>
+    <t xml:space="preserve">3.17446827888489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12085151672363</t>
   </si>
   <si>
     <t xml:space="preserve">3.07832813262939</t>
@@ -4808,7 +4808,7 @@
     <t xml:space="preserve">3.09866547584534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07647967338562</t>
+    <t xml:space="preserve">3.07647943496704</t>
   </si>
   <si>
     <t xml:space="preserve">3.06723523139954</t>
@@ -4823,19 +4823,19 @@
     <t xml:space="preserve">3.19665431976318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20404982566833</t>
+    <t xml:space="preserve">3.20405006408691</t>
   </si>
   <si>
     <t xml:space="preserve">3.19850325584412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1245493888855</t>
+    <t xml:space="preserve">3.12454962730408</t>
   </si>
   <si>
     <t xml:space="preserve">3.16707301139832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14858412742615</t>
+    <t xml:space="preserve">3.14858436584473</t>
   </si>
   <si>
     <t xml:space="preserve">3.00067663192749</t>
@@ -4844,7 +4844,7 @@
     <t xml:space="preserve">3.04874682426453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10051465034485</t>
+    <t xml:space="preserve">3.10051441192627</t>
   </si>
   <si>
     <t xml:space="preserve">3.14488673210144</t>
@@ -5751,6 +5751,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.21199989318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07399988174438</t>
   </si>
 </sst>
 </file>
@@ -10397,7 +10400,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G166" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -10449,7 +10452,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G168" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -10501,7 +10504,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G170" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -10527,7 +10530,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G171" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -10579,7 +10582,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G173" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -10605,7 +10608,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G174" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -10631,7 +10634,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G175" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -10657,7 +10660,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G176" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -10735,7 +10738,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G179" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -10761,7 +10764,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G180" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -10813,7 +10816,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G182" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -10839,7 +10842,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G183" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -10865,7 +10868,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G184" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -10891,7 +10894,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G185" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -10917,7 +10920,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G186" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -10943,7 +10946,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G187" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -10969,7 +10972,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G188" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -10995,7 +10998,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G189" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -11021,7 +11024,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G190" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -11047,7 +11050,7 @@
         <v>2.33599996566772</v>
       </c>
       <c r="G191" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -11073,7 +11076,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G192" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -11099,7 +11102,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G193" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -11125,7 +11128,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G194" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -11151,7 +11154,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G195" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -11177,7 +11180,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G196" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -11203,7 +11206,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G197" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -11229,7 +11232,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G198" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -11255,7 +11258,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G199" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -11281,7 +11284,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G200" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -11307,7 +11310,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G201" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -11333,7 +11336,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G202" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -11359,7 +11362,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G203" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -11385,7 +11388,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G204" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -11411,7 +11414,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G205" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -11437,7 +11440,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G206" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -11463,7 +11466,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G207" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -11489,7 +11492,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G208" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -11515,7 +11518,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G209" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -11541,7 +11544,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G210" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -11567,7 +11570,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G211" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -11593,7 +11596,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G212" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -11619,7 +11622,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G213" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -11645,7 +11648,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G214" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -11697,7 +11700,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G216" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -11723,7 +11726,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G217" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -11749,7 +11752,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G218" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -11775,7 +11778,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G219" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -11801,7 +11804,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G220" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -11827,7 +11830,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G221" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -11853,7 +11856,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G222" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -11879,7 +11882,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G223" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -11905,7 +11908,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G224" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -11931,7 +11934,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G225" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -11957,7 +11960,7 @@
         <v>2.00200009346008</v>
       </c>
       <c r="G226" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -11983,7 +11986,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G227" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -12009,7 +12012,7 @@
         <v>1.96300005912781</v>
       </c>
       <c r="G228" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -12035,7 +12038,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G229" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -12061,7 +12064,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G230" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -12087,7 +12090,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G231" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -12113,7 +12116,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G232" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -12139,7 +12142,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G233" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -12165,7 +12168,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G234" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -12191,7 +12194,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G235" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -12217,7 +12220,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G236" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -12243,7 +12246,7 @@
         <v>1.90699994564056</v>
       </c>
       <c r="G237" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -12269,7 +12272,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G238" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -12295,7 +12298,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G239" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -12321,7 +12324,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G240" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -12347,7 +12350,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G241" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -12373,7 +12376,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G242" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -12399,7 +12402,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G243" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -12425,7 +12428,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G244" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -12451,7 +12454,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G245" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -12477,7 +12480,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G246" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -12503,7 +12506,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G247" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -12529,7 +12532,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G248" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -12555,7 +12558,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G249" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -12581,7 +12584,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G250" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -12607,7 +12610,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G251" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -12633,7 +12636,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G252" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -12659,7 +12662,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G253" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -12685,7 +12688,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G254" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -12711,7 +12714,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G255" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -12737,7 +12740,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G256" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -12763,7 +12766,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G257" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -12789,7 +12792,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G258" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -12815,7 +12818,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G259" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -12841,7 +12844,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G260" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -12867,7 +12870,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G261" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -12893,7 +12896,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G262" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -12919,7 +12922,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G263" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -12945,7 +12948,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G264" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -12971,7 +12974,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G265" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -12997,7 +13000,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G266" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -13023,7 +13026,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G267" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -13049,7 +13052,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G268" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -13075,7 +13078,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G269" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -13101,7 +13104,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G270" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -13127,7 +13130,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G271" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -13153,7 +13156,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G272" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -13179,7 +13182,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G273" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -13205,7 +13208,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G274" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -13231,7 +13234,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G275" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -13257,7 +13260,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G276" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -13283,7 +13286,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G277" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -13309,7 +13312,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G278" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -13335,7 +13338,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G279" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -13361,7 +13364,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G280" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -13387,7 +13390,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G281" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -13413,7 +13416,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G282" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -13439,7 +13442,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G283" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -13465,7 +13468,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G284" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -13491,7 +13494,7 @@
         <v>2.25</v>
       </c>
       <c r="G285" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -13517,7 +13520,7 @@
         <v>2.25</v>
       </c>
       <c r="G286" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -13543,7 +13546,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G287" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -13569,7 +13572,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G288" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -13595,7 +13598,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G289" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -13621,7 +13624,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G290" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -13647,7 +13650,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G291" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -13673,7 +13676,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G292" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -13699,7 +13702,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G293" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -13725,7 +13728,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G294" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -13751,7 +13754,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G295" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -13777,7 +13780,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G296" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -13803,7 +13806,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G297" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -13829,7 +13832,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G298" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -13855,7 +13858,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G299" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -13907,7 +13910,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G301" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -13933,7 +13936,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G302" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -13959,7 +13962,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G303" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -13985,7 +13988,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G304" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -14011,7 +14014,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G305" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -14037,7 +14040,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G306" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -14063,7 +14066,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G307" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -14089,7 +14092,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G308" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -14115,7 +14118,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G309" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -14141,7 +14144,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G310" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -14167,7 +14170,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G311" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -14193,7 +14196,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G312" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -14219,7 +14222,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G313" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -14245,7 +14248,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G314" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -14271,7 +14274,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G315" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -14297,7 +14300,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G316" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -14323,7 +14326,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G317" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -14349,7 +14352,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G318" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -14375,7 +14378,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G319" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -14401,7 +14404,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G320" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -14427,7 +14430,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G321" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -14453,7 +14456,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G322" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -14479,7 +14482,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G323" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -14505,7 +14508,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G324" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -14531,7 +14534,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G325" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -14557,7 +14560,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G326" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -14583,7 +14586,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G327" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -14609,7 +14612,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G328" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -14635,7 +14638,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G329" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -14661,7 +14664,7 @@
         <v>2.67400002479553</v>
       </c>
       <c r="G330" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -14687,7 +14690,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G331" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -14713,7 +14716,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G332" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -14739,7 +14742,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G333" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -14765,7 +14768,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G334" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -14791,7 +14794,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G335" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -14817,7 +14820,7 @@
         <v>2.66199994087219</v>
       </c>
       <c r="G336" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -14843,7 +14846,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G337" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -14869,7 +14872,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G338" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -14895,7 +14898,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G339" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -14921,7 +14924,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G340" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -14947,7 +14950,7 @@
         <v>2.64599990844727</v>
       </c>
       <c r="G341" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -14973,7 +14976,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G342" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -14999,7 +15002,7 @@
         <v>2.67199993133545</v>
       </c>
       <c r="G343" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -15025,7 +15028,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G344" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -15051,7 +15054,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G345" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -15077,7 +15080,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G346" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -15103,7 +15106,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G347" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -15129,7 +15132,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G348" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -15155,7 +15158,7 @@
         <v>2.85599994659424</v>
       </c>
       <c r="G349" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -15181,7 +15184,7 @@
         <v>2.83200001716614</v>
       </c>
       <c r="G350" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -15207,7 +15210,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G351" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -15233,7 +15236,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G352" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -15259,7 +15262,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G353" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -15285,7 +15288,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G354" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -15311,7 +15314,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G355" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -15337,7 +15340,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G356" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -15363,7 +15366,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G357" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -15389,7 +15392,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G358" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -15415,7 +15418,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G359" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -15441,7 +15444,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G360" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -15467,7 +15470,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G361" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -15493,7 +15496,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G362" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -15519,7 +15522,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G363" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -15545,7 +15548,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G364" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -15571,7 +15574,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G365" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -15597,7 +15600,7 @@
         <v>2.90400004386902</v>
       </c>
       <c r="G366" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -15623,7 +15626,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G367" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -15649,7 +15652,7 @@
         <v>2.92600011825562</v>
       </c>
       <c r="G368" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -15675,7 +15678,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G369" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -15701,7 +15704,7 @@
         <v>2.96399998664856</v>
       </c>
       <c r="G370" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -15727,7 +15730,7 @@
         <v>2.94400000572205</v>
       </c>
       <c r="G371" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -15753,7 +15756,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="G372" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -15779,7 +15782,7 @@
         <v>2.95799994468689</v>
       </c>
       <c r="G373" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -15805,7 +15808,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G374" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -15831,7 +15834,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G375" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -15857,7 +15860,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G376" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -15883,7 +15886,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G377" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -15909,7 +15912,7 @@
         <v>2.88599991798401</v>
       </c>
       <c r="G378" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -18665,7 +18668,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G484" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -18717,7 +18720,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G486" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -72467,7 +72470,7 @@
     </row>
     <row r="2554">
       <c r="A2554" s="1" t="n">
-        <v>46042.6910300926</v>
+        <v>46042.3333333333</v>
       </c>
       <c r="B2554" t="n">
         <v>1927196</v>
@@ -72488,6 +72491,32 @@
         <v>1912</v>
       </c>
       <c r="H2554" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2555">
+      <c r="A2555" s="1" t="n">
+        <v>46043.6926157407</v>
+      </c>
+      <c r="B2555" t="n">
+        <v>5772443</v>
+      </c>
+      <c r="C2555" t="n">
+        <v>4.21400022506714</v>
+      </c>
+      <c r="D2555" t="n">
+        <v>4.07000017166138</v>
+      </c>
+      <c r="E2555" t="n">
+        <v>4.19999980926514</v>
+      </c>
+      <c r="F2555" t="n">
+        <v>4.07399988174438</v>
+      </c>
+      <c r="G2555" t="s">
+        <v>1913</v>
+      </c>
+      <c r="H2555" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HER.MI.xlsx
+++ b/data/HER.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1912" uniqueCount="1912">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1913" uniqueCount="1913">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">1.70896399021149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7061687707901</t>
+    <t xml:space="preserve">1.70616912841797</t>
   </si>
   <si>
     <t xml:space="preserve">1.71036112308502</t>
@@ -56,13 +56,13 @@
     <t xml:space="preserve">1.68800354003906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72573208808899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79140794277191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79420232772827</t>
+    <t xml:space="preserve">1.72573220729828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79140758514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79420244693756</t>
   </si>
   <si>
     <t xml:space="preserve">1.77044725418091</t>
@@ -74,28 +74,28 @@
     <t xml:space="preserve">1.70337426662445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77324211597443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74948704242706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76625537872314</t>
+    <t xml:space="preserve">1.77324235439301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74948716163635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76625549793243</t>
   </si>
   <si>
     <t xml:space="preserve">1.80538129806519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7900105714798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80398344993591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83472573757172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81656002998352</t>
+    <t xml:space="preserve">1.79001021385193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80398380756378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83472561836243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81655967235565</t>
   </si>
   <si>
     <t xml:space="preserve">1.80258631706238</t>
@@ -104,31 +104,31 @@
     <t xml:space="preserve">1.8486989736557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85568571090698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84031498432159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82354664802551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82913613319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7285270690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74110281467438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75926840305328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69918215274811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75507652759552</t>
+    <t xml:space="preserve">1.85568559169769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84031522274017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82354640960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82913601398468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72852671146393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74110305309296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75926864147186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6991822719574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75507640838623</t>
   </si>
   <si>
     <t xml:space="preserve">1.7955995798111</t>
@@ -137,52 +137,52 @@
     <t xml:space="preserve">1.78302347660065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77603697776794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79839420318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80118894577026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82075190544128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83053350448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78861284255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76485824584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74529480934143</t>
+    <t xml:space="preserve">1.77603685855865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79839444160461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80118930339813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82075202465057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8305332660675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78861308097839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76485776901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74529469013214</t>
   </si>
   <si>
     <t xml:space="preserve">1.73970544338226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72992432117462</t>
+    <t xml:space="preserve">1.72992408275604</t>
   </si>
   <si>
     <t xml:space="preserve">1.74389743804932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73271870613098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76346063613892</t>
+    <t xml:space="preserve">1.73271882534027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76346075534821</t>
   </si>
   <si>
     <t xml:space="preserve">1.7788313627243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76066589355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77463924884796</t>
+    <t xml:space="preserve">1.76066601276398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77463948726654</t>
   </si>
   <si>
     <t xml:space="preserve">1.7969970703125</t>
@@ -191,94 +191,94 @@
     <t xml:space="preserve">1.83752012252808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81097042560577</t>
+    <t xml:space="preserve">1.81097078323364</t>
   </si>
   <si>
     <t xml:space="preserve">1.85708343982697</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8431099653244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76765263080597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78162610530853</t>
+    <t xml:space="preserve">1.84310984611511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76765275001526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78162622451782</t>
   </si>
   <si>
     <t xml:space="preserve">1.78721582889557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77743411064148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78022909164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80817556381226</t>
+    <t xml:space="preserve">1.77743399143219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.780228972435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80817592144012</t>
   </si>
   <si>
     <t xml:space="preserve">1.80957305431366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79280507564545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78442060947418</t>
+    <t xml:space="preserve">1.79280495643616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78442072868347</t>
   </si>
   <si>
     <t xml:space="preserve">1.75647377967834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74808955192566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82634174823761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84590458869934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83193135261536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84450733661652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82214963436127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83332848548889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8249443769455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81376516819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76206338405609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73132145404816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7425000667572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71175873279572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75751042366028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77344834804535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74012339115143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7589590549469</t>
+    <t xml:space="preserve">1.74808967113495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82634162902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84590435028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83193075656891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84450709819794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82214939594269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83332824707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82494378089905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81376576423645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76206314563751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73132121562958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74250018596649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71175861358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75751066207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77344810962677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74012362957001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75895917415619</t>
   </si>
   <si>
     <t xml:space="preserve">1.70390117168427</t>
@@ -287,70 +287,70 @@
     <t xml:space="preserve">1.67347431182861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70969665050507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73867499828339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78069281578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83430171012878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8082218170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81111967563629</t>
+    <t xml:space="preserve">1.70969653129578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73867452144623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78069257736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83430182933807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80822145938873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.811119556427</t>
   </si>
   <si>
     <t xml:space="preserve">1.78503942489624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77924370765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72708368301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76040840148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74591910839081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77055048942566</t>
+    <t xml:space="preserve">1.77924382686615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72708356380463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76040816307068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7459192276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77055060863495</t>
   </si>
   <si>
     <t xml:space="preserve">1.76620364189148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7618567943573</t>
+    <t xml:space="preserve">1.76185703277588</t>
   </si>
   <si>
     <t xml:space="preserve">1.76910150051117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77489721775055</t>
+    <t xml:space="preserve">1.77489745616913</t>
   </si>
   <si>
     <t xml:space="preserve">1.78359043598175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83719956874847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85748445987701</t>
+    <t xml:space="preserve">1.8371993303299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85748422145844</t>
   </si>
   <si>
     <t xml:space="preserve">1.85023951530457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83575069904327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86617743968964</t>
+    <t xml:space="preserve">1.83575081825256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86617767810822</t>
   </si>
   <si>
     <t xml:space="preserve">1.83140408992767</t>
@@ -365,55 +365,55 @@
     <t xml:space="preserve">1.81981301307678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8125684261322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74881708621979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74447047710419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77634608745575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79083514213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79952836036682</t>
+    <t xml:space="preserve">1.81256854534149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74881720542908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7444703578949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77634596824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79083502292633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79952824115753</t>
   </si>
   <si>
     <t xml:space="preserve">1.78648829460144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78938591480255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81546628475189</t>
+    <t xml:space="preserve">1.78938639163971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81546592712402</t>
   </si>
   <si>
     <t xml:space="preserve">1.75606155395508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73577678203583</t>
+    <t xml:space="preserve">1.73577702045441</t>
   </si>
   <si>
     <t xml:space="preserve">1.70679914951324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73722612857819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75461256504059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71114575862885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70824801921844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70245230197906</t>
+    <t xml:space="preserve">1.73722577095032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7546124458313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71114540100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70824778079987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70245242118835</t>
   </si>
   <si>
     <t xml:space="preserve">1.69231021404266</t>
@@ -425,31 +425,31 @@
     <t xml:space="preserve">1.69665682315826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63145649433136</t>
+    <t xml:space="preserve">1.63145637512207</t>
   </si>
   <si>
     <t xml:space="preserve">1.60537660121918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59233617782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57929611206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60102963447571</t>
+    <t xml:space="preserve">1.59233629703522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57929623126984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60102987289429</t>
   </si>
   <si>
     <t xml:space="preserve">1.60972309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61406946182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62131428718567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63290512561798</t>
+    <t xml:space="preserve">1.61406993865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62131404876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63290524482727</t>
   </si>
   <si>
     <t xml:space="preserve">1.61841642856598</t>
@@ -458,34 +458,34 @@
     <t xml:space="preserve">1.63870084285736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63725209236145</t>
+    <t xml:space="preserve">1.63725197315216</t>
   </si>
   <si>
     <t xml:space="preserve">1.65029215812683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62276291847229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61551868915558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61696767807007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62566089630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66188335418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66912770271301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68796324729919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59378528594971</t>
+    <t xml:space="preserve">1.62276303768158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61551880836487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61696743965149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62566077709198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66188311576843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66912758350372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68796336650848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59378516674042</t>
   </si>
   <si>
     <t xml:space="preserve">1.56625604629517</t>
@@ -497,25 +497,25 @@
     <t xml:space="preserve">1.54307389259338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46048676967621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46338438987732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44599783420563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44527339935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45034456253052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43005990982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42209124565125</t>
+    <t xml:space="preserve">1.4604868888855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46338450908661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44599795341492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44527328014374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4503448009491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43006002902985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42209100723267</t>
   </si>
   <si>
     <t xml:space="preserve">1.3960108757019</t>
@@ -527,16 +527,16 @@
     <t xml:space="preserve">1.40905106067657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41267335414886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39818406105042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40180635452271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40542876720428</t>
+    <t xml:space="preserve">1.41267311573029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3981841802597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40180647373199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.405428647995</t>
   </si>
   <si>
     <t xml:space="preserve">1.41629564762115</t>
@@ -548,19 +548,19 @@
     <t xml:space="preserve">1.35906410217285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37717533111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43875324726105</t>
+    <t xml:space="preserve">1.37717545032501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43875336647034</t>
   </si>
   <si>
     <t xml:space="preserve">1.48077130317688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49236238002777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48511779308319</t>
+    <t xml:space="preserve">1.49236261844635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48511815071106</t>
   </si>
   <si>
     <t xml:space="preserve">1.53293144702911</t>
@@ -569,52 +569,52 @@
     <t xml:space="preserve">1.52713596820831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50105595588684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50685143470764</t>
+    <t xml:space="preserve">1.50105571746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50685131549835</t>
   </si>
   <si>
     <t xml:space="preserve">1.54886937141418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55756294727325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57060277462006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59088730812073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56915378570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58798956871033</t>
+    <t xml:space="preserve">1.55756282806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57060289382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5908876657486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56915390491486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58798968791962</t>
   </si>
   <si>
     <t xml:space="preserve">1.608274102211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59668266773224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5995808839798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56480741500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65174102783203</t>
+    <t xml:space="preserve">1.5966831445694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59958064556122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56480729579926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65174090862274</t>
   </si>
   <si>
     <t xml:space="preserve">1.64159882068634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65319013595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65463864803314</t>
+    <t xml:space="preserve">1.65319001674652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65463852882385</t>
   </si>
   <si>
     <t xml:space="preserve">1.65898537635803</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">1.64304745197296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57494974136353</t>
+    <t xml:space="preserve">1.57494962215424</t>
   </si>
   <si>
     <t xml:space="preserve">1.57784724235535</t>
@@ -635,28 +635,28 @@
     <t xml:space="preserve">1.55176723003387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58654069900513</t>
+    <t xml:space="preserve">1.58654081821442</t>
   </si>
   <si>
     <t xml:space="preserve">1.63000750541687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68216788768768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66622972488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6778210401535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69086146354675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69375896453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69810569286346</t>
+    <t xml:space="preserve">1.68216776847839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66622996330261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67782115936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69086134433746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69375920295715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69810605049133</t>
   </si>
   <si>
     <t xml:space="preserve">1.69520771503448</t>
@@ -668,46 +668,46 @@
     <t xml:space="preserve">1.72998118400574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73432815074921</t>
+    <t xml:space="preserve">1.73432779312134</t>
   </si>
   <si>
     <t xml:space="preserve">1.71983909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72418582439423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71549224853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71839046478271</t>
+    <t xml:space="preserve">1.72418570518494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71549212932587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71839022636414</t>
   </si>
   <si>
     <t xml:space="preserve">1.74157249927521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78214156627655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78793716430664</t>
+    <t xml:space="preserve">1.78214180469513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78793704509735</t>
   </si>
   <si>
     <t xml:space="preserve">1.8140172958374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82995545864105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86907517910004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89950227737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91399073600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91544032096863</t>
+    <t xml:space="preserve">1.82995498180389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86907529830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89950215816498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91399109363556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91543984413147</t>
   </si>
   <si>
     <t xml:space="preserve">1.8806666135788</t>
@@ -716,52 +716,52 @@
     <t xml:space="preserve">1.8719733953476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88935983181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9009507894516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90529763698578</t>
+    <t xml:space="preserve">1.88935995101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90095067024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90529751777649</t>
   </si>
   <si>
     <t xml:space="preserve">1.91254222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94441759586334</t>
+    <t xml:space="preserve">1.94441819190979</t>
   </si>
   <si>
     <t xml:space="preserve">1.93717312812805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87921750545502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88356459140778</t>
+    <t xml:space="preserve">1.87921786308289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88356423377991</t>
   </si>
   <si>
     <t xml:space="preserve">1.92847967147827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8980530500412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88791120052338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90239989757538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91688859462738</t>
+    <t xml:space="preserve">1.89805316925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88791108131409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90240001678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91688895225525</t>
   </si>
   <si>
     <t xml:space="preserve">1.92413318157196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93572461605072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9386225938797</t>
+    <t xml:space="preserve">1.93572473526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93862211704254</t>
   </si>
   <si>
     <t xml:space="preserve">1.9487646818161</t>
@@ -770,25 +770,25 @@
     <t xml:space="preserve">1.99512934684753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0284538269043</t>
+    <t xml:space="preserve">2.02845406532288</t>
   </si>
   <si>
     <t xml:space="preserve">2.05743169784546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06902313232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0516357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1023473739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06467652320862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03859639167786</t>
+    <t xml:space="preserve">2.06902265548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05163669586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10234761238098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06467604637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0385959148407</t>
   </si>
   <si>
     <t xml:space="preserve">2.07336950302124</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">2.08640956878662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12842726707458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1124894618988</t>
+    <t xml:space="preserve">2.12842750549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11248970031738</t>
   </si>
   <si>
     <t xml:space="preserve">2.11104106903076</t>
@@ -818,10 +818,10 @@
     <t xml:space="preserve">2.12263226509094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07916498184204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10379672050476</t>
+    <t xml:space="preserve">2.0791654586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1037962436676</t>
   </si>
   <si>
     <t xml:space="preserve">2.11973452568054</t>
@@ -833,67 +833,67 @@
     <t xml:space="preserve">2.14726328849792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13277435302734</t>
+    <t xml:space="preserve">2.13277411460876</t>
   </si>
   <si>
     <t xml:space="preserve">2.15450763702393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14291667938232</t>
+    <t xml:space="preserve">2.14291644096375</t>
   </si>
   <si>
     <t xml:space="preserve">2.15595674514771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1679093837738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17836761474609</t>
+    <t xml:space="preserve">2.16790914535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17836785316467</t>
   </si>
   <si>
     <t xml:space="preserve">2.17239141464233</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09918189048767</t>
+    <t xml:space="preserve">2.09918165206909</t>
   </si>
   <si>
     <t xml:space="preserve">2.11262845993042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07228827476501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05884170532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01700735092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99907839298248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01103091239929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00804257392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99758422374725</t>
+    <t xml:space="preserve">2.07228803634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05884146690369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01700758934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99907863140106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01103067398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00804281234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99758434295654</t>
   </si>
   <si>
     <t xml:space="preserve">1.95126783847809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97069048881531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00505471229553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98264360427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03045415878296</t>
+    <t xml:space="preserve">1.97069084644318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00505447387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98264372348785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0304536819458</t>
   </si>
   <si>
     <t xml:space="preserve">2.05286526679993</t>
@@ -902,13 +902,13 @@
     <t xml:space="preserve">2.0394184589386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03194832801819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04539465904236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02447772026062</t>
+    <t xml:space="preserve">2.03194785118103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04539489746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0244779586792</t>
   </si>
   <si>
     <t xml:space="preserve">2.06182956695557</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">2.0767707824707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03344225883484</t>
+    <t xml:space="preserve">2.03344202041626</t>
   </si>
   <si>
     <t xml:space="preserve">2.01401901245117</t>
@@ -926,22 +926,22 @@
     <t xml:space="preserve">2.05435943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04390096664429</t>
+    <t xml:space="preserve">2.04390072822571</t>
   </si>
   <si>
     <t xml:space="preserve">2.04240655899048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03643012046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04838299751282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04987692832947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00206661224365</t>
+    <t xml:space="preserve">2.03643035888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0483832359314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04987716674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00206637382507</t>
   </si>
   <si>
     <t xml:space="preserve">2.05585360527039</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">2.03493618965149</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99459612369537</t>
+    <t xml:space="preserve">1.99459624290466</t>
   </si>
   <si>
     <t xml:space="preserve">1.975172996521</t>
@@ -959,10 +959,10 @@
     <t xml:space="preserve">1.96172630786896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96770262718201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02597188949585</t>
+    <t xml:space="preserve">1.96770286560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02597212791443</t>
   </si>
   <si>
     <t xml:space="preserve">2.01252508163452</t>
@@ -971,55 +971,55 @@
     <t xml:space="preserve">2.00953722000122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0035605430603</t>
+    <t xml:space="preserve">2.00356030464172</t>
   </si>
   <si>
     <t xml:space="preserve">2.07826471328735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01850152015686</t>
+    <t xml:space="preserve">2.01850128173828</t>
   </si>
   <si>
     <t xml:space="preserve">2.00057244300842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98563182353973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98712563514709</t>
+    <t xml:space="preserve">1.98563170433044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98712587356567</t>
   </si>
   <si>
     <t xml:space="preserve">1.97218501567841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02148938179016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03792428970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06033563613892</t>
+    <t xml:space="preserve">2.02148985862732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03792452812195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06033539772034</t>
   </si>
   <si>
     <t xml:space="preserve">2.07079434394836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07378220558167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06631183624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06332397460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07527661323547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08424091339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10665225982666</t>
+    <t xml:space="preserve">2.07378244400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06631207466125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0633237361908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07527637481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08424115180969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10665202140808</t>
   </si>
   <si>
     <t xml:space="preserve">2.12458109855652</t>
@@ -1034,49 +1034,49 @@
     <t xml:space="preserve">2.18135619163513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19629693031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18733239173889</t>
+    <t xml:space="preserve">2.19629669189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18733263015747</t>
   </si>
   <si>
     <t xml:space="preserve">2.1798620223999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16641569137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17089748382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.191814661026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19330883026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1948025226593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22468423843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27100086212158</t>
+    <t xml:space="preserve">2.16641521453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1708972454071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19181489944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19330859184265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19480276107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22468400001526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27100110054016</t>
   </si>
   <si>
     <t xml:space="preserve">2.2560601234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2590479850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28145980834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29490613937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30536460876465</t>
+    <t xml:space="preserve">2.25904822349548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28145956993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2949059009552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30536484718323</t>
   </si>
   <si>
     <t xml:space="preserve">2.30088233947754</t>
@@ -1088,10 +1088,10 @@
     <t xml:space="preserve">2.28892970085144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27398872375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30387091636658</t>
+    <t xml:space="preserve">2.27398920059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.303870677948</t>
   </si>
   <si>
     <t xml:space="preserve">2.31582307815552</t>
@@ -1103,13 +1103,13 @@
     <t xml:space="preserve">2.25755429267883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27847099304199</t>
+    <t xml:space="preserve">2.27847146987915</t>
   </si>
   <si>
     <t xml:space="preserve">2.22916650772095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22617864608765</t>
+    <t xml:space="preserve">2.22617793083191</t>
   </si>
   <si>
     <t xml:space="preserve">2.21870803833008</t>
@@ -1124,28 +1124,28 @@
     <t xml:space="preserve">2.21123790740967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26054263114929</t>
+    <t xml:space="preserve">2.26054239273071</t>
   </si>
   <si>
     <t xml:space="preserve">2.31134104728699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24111938476562</t>
+    <t xml:space="preserve">2.2411196231842</t>
   </si>
   <si>
     <t xml:space="preserve">2.26950693130493</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23813128471375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27697706222534</t>
+    <t xml:space="preserve">2.23813104629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27697730064392</t>
   </si>
   <si>
     <t xml:space="preserve">2.28594160079956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29938793182373</t>
+    <t xml:space="preserve">2.29938840866089</t>
   </si>
   <si>
     <t xml:space="preserve">2.24709558486938</t>
@@ -1154,46 +1154,46 @@
     <t xml:space="preserve">2.2799654006958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24560141563416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18434405326843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13503932952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11113429069519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05734729766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02895998954773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0946991443634</t>
+    <t xml:space="preserve">2.24560189247131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18434453010559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13503980636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11113452911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05734753608704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02896022796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09469962120056</t>
   </si>
   <si>
     <t xml:space="preserve">2.12607502937317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13354563713074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09320569038391</t>
+    <t xml:space="preserve">2.13354516029358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09320545196533</t>
   </si>
   <si>
     <t xml:space="preserve">2.06929993629456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04091262817383</t>
+    <t xml:space="preserve">2.04091238975525</t>
   </si>
   <si>
     <t xml:space="preserve">2.08573508262634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0827465057373</t>
+    <t xml:space="preserve">2.08274698257446</t>
   </si>
   <si>
     <t xml:space="preserve">2.08125281333923</t>
@@ -1202,34 +1202,34 @@
     <t xml:space="preserve">2.10216999053955</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09768772125244</t>
+    <t xml:space="preserve">2.09768748283386</t>
   </si>
   <si>
     <t xml:space="preserve">2.12009882926941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21273183822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22169589996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2306604385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24261331558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26353049278259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23514342308044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25307178497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29341244697571</t>
+    <t xml:space="preserve">2.2127320766449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22169613838196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23066091537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24261355400085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26353025436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23514270782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25307202339172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29341173171997</t>
   </si>
   <si>
     <t xml:space="preserve">2.29789423942566</t>
@@ -1238,49 +1238,49 @@
     <t xml:space="preserve">2.28444766998291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22767281532288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25157785415649</t>
+    <t xml:space="preserve">2.2276725769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25157761573792</t>
   </si>
   <si>
     <t xml:space="preserve">2.14101576805115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12159299850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02298378944397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94678521156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96471464633942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98114907741547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96919691562653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97816121578217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94827950000763</t>
+    <t xml:space="preserve">2.12159276008606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02298355102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94678544998169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96471452713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98114955425262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96919667720795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97816109657288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94827961921692</t>
   </si>
   <si>
     <t xml:space="preserve">2.02856683731079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06108570098877</t>
+    <t xml:space="preserve">2.06108593940735</t>
   </si>
   <si>
     <t xml:space="preserve">2.07192540168762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03785800933838</t>
+    <t xml:space="preserve">2.03785824775696</t>
   </si>
   <si>
     <t xml:space="preserve">2.04095506668091</t>
@@ -1292,16 +1292,16 @@
     <t xml:space="preserve">2.0595371723175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08895897865295</t>
+    <t xml:space="preserve">2.08895921707153</t>
   </si>
   <si>
     <t xml:space="preserve">2.06727981567383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10599327087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13541483879089</t>
+    <t xml:space="preserve">2.10599303245544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13541507720947</t>
   </si>
   <si>
     <t xml:space="preserve">2.15399742126465</t>
@@ -1322,10 +1322,10 @@
     <t xml:space="preserve">2.13386654853821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16793394088745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17257952690125</t>
+    <t xml:space="preserve">2.16793370246887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17257928848267</t>
   </si>
   <si>
     <t xml:space="preserve">2.15244889259338</t>
@@ -1334,19 +1334,19 @@
     <t xml:space="preserve">2.10444450378418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09205627441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20664691925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1710307598114</t>
+    <t xml:space="preserve">2.09205651283264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20664668083191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17103099822998</t>
   </si>
   <si>
     <t xml:space="preserve">2.19580745697021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18651604652405</t>
+    <t xml:space="preserve">2.18651652336121</t>
   </si>
   <si>
     <t xml:space="preserve">2.21748685836792</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">2.1834192276001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16328835487366</t>
+    <t xml:space="preserve">2.16328859329224</t>
   </si>
   <si>
     <t xml:space="preserve">2.15090036392212</t>
@@ -1367,19 +1367,19 @@
     <t xml:space="preserve">2.13231778144836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12612366676331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11992955207825</t>
+    <t xml:space="preserve">2.12612390518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11993002891541</t>
   </si>
   <si>
     <t xml:space="preserve">2.16638541221619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1570942401886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14935159683228</t>
+    <t xml:space="preserve">2.15709447860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14935183525085</t>
   </si>
   <si>
     <t xml:space="preserve">2.09670186042786</t>
@@ -1388,10 +1388,10 @@
     <t xml:space="preserve">2.09979891777039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0905077457428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10754156112671</t>
+    <t xml:space="preserve">2.09050798416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10754132270813</t>
   </si>
   <si>
     <t xml:space="preserve">2.12457513809204</t>
@@ -1400,28 +1400,28 @@
     <t xml:space="preserve">2.12767243385315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18806481361389</t>
+    <t xml:space="preserve">2.18806457519531</t>
   </si>
   <si>
     <t xml:space="preserve">2.20045304298401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19735598564148</t>
+    <t xml:space="preserve">2.1973557472229</t>
   </si>
   <si>
     <t xml:space="preserve">2.20200157165527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20819544792175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21129274368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17567682266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12147855758667</t>
+    <t xml:space="preserve">2.20819568634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21129298210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1756763458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12147831916809</t>
   </si>
   <si>
     <t xml:space="preserve">2.11683249473572</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">2.07657098770142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06882858276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05179500579834</t>
+    <t xml:space="preserve">2.06882834434509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05179452896118</t>
   </si>
   <si>
     <t xml:space="preserve">2.01462984085083</t>
@@ -1445,19 +1445,19 @@
     <t xml:space="preserve">1.98211109638214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93720400333405</t>
+    <t xml:space="preserve">1.93720376491547</t>
   </si>
   <si>
     <t xml:space="preserve">1.90313625335693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86287450790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91552436351776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87216556072235</t>
+    <t xml:space="preserve">1.86287462711334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91552448272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87216579914093</t>
   </si>
   <si>
     <t xml:space="preserve">1.89384520053864</t>
@@ -1469,28 +1469,28 @@
     <t xml:space="preserve">1.87061715126038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85977780818939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92791247367859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89694237709045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89074814319611</t>
+    <t xml:space="preserve">1.85977745056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92791259288788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89694225788116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89074802398682</t>
   </si>
   <si>
     <t xml:space="preserve">1.87990832328796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88919961452484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88765096664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9046847820282</t>
+    <t xml:space="preserve">1.88919949531555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88765108585358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90468502044678</t>
   </si>
   <si>
     <t xml:space="preserve">1.9217187166214</t>
@@ -1499,76 +1499,76 @@
     <t xml:space="preserve">1.96662569046021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.918621301651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9790141582489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96972250938416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97746539115906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94184923171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9310097694397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92481565475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92017006874084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89229667186737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90933060646057</t>
+    <t xml:space="preserve">1.91862165927887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97901403903961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96972298622131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97746515274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94184947013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93100965023041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92481589317322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92017018795013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89229679107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90933072566986</t>
   </si>
   <si>
     <t xml:space="preserve">1.87836003303528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93875229358673</t>
+    <t xml:space="preserve">1.93875253200531</t>
   </si>
   <si>
     <t xml:space="preserve">1.8690687417984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94804322719574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98675644397736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09360480308533</t>
+    <t xml:space="preserve">1.9480437040329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98675656318665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09360456466675</t>
   </si>
   <si>
     <t xml:space="preserve">2.03630948066711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06573104858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09825038909912</t>
+    <t xml:space="preserve">2.06573128700256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0982506275177</t>
   </si>
   <si>
     <t xml:space="preserve">2.08276534080505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19116187095642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19425892829895</t>
+    <t xml:space="preserve">2.19116163253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19425868988037</t>
   </si>
   <si>
     <t xml:space="preserve">2.1787736415863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2050986289978</t>
+    <t xml:space="preserve">2.20509839057922</t>
   </si>
   <si>
     <t xml:space="preserve">2.2097442150116</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">2.20354986190796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19890451431274</t>
+    <t xml:space="preserve">2.19890427589417</t>
   </si>
   <si>
     <t xml:space="preserve">2.22677779197693</t>
@@ -1589,31 +1589,31 @@
     <t xml:space="preserve">2.26084542274475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26239371299744</t>
+    <t xml:space="preserve">2.26239395141602</t>
   </si>
   <si>
     <t xml:space="preserve">2.28562164306641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29336452484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28252458572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2840735912323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2902672290802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27013659477234</t>
+    <t xml:space="preserve">2.29336428642273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28252482414246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28407335281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29026746749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27013683319092</t>
   </si>
   <si>
     <t xml:space="preserve">2.25619983673096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28097653388977</t>
+    <t xml:space="preserve">2.28097629547119</t>
   </si>
   <si>
     <t xml:space="preserve">2.30265522003174</t>
@@ -1628,34 +1628,34 @@
     <t xml:space="preserve">2.29800987243652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28871870040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25929689407349</t>
+    <t xml:space="preserve">2.28871893882751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25929665565491</t>
   </si>
   <si>
     <t xml:space="preserve">2.32433485984802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29181623458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25465106964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26858830451965</t>
+    <t xml:space="preserve">2.29181575775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25465154647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26858806610107</t>
   </si>
   <si>
     <t xml:space="preserve">2.26549100875854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29955840110779</t>
+    <t xml:space="preserve">2.29955863952637</t>
   </si>
   <si>
     <t xml:space="preserve">2.29646134376526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31349492073059</t>
+    <t xml:space="preserve">2.31349515914917</t>
   </si>
   <si>
     <t xml:space="preserve">2.32123780250549</t>
@@ -1664,16 +1664,16 @@
     <t xml:space="preserve">2.25774812698364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23916625976562</t>
+    <t xml:space="preserve">2.23916602134705</t>
   </si>
   <si>
     <t xml:space="preserve">2.34446573257446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38008165359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38163018226624</t>
+    <t xml:space="preserve">2.38008189201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38163042068481</t>
   </si>
   <si>
     <t xml:space="preserve">2.40330958366394</t>
@@ -1682,10 +1682,10 @@
     <t xml:space="preserve">2.4280858039856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43118286132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47609043121338</t>
+    <t xml:space="preserve">2.43118333816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47608995437622</t>
   </si>
   <si>
     <t xml:space="preserve">2.4946722984314</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">2.54887080192566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52099776268005</t>
+    <t xml:space="preserve">2.52099752426147</t>
   </si>
   <si>
     <t xml:space="preserve">2.5024151802063</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">2.51635193824768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46215391159058</t>
+    <t xml:space="preserve">2.462153673172</t>
   </si>
   <si>
     <t xml:space="preserve">2.47918725013733</t>
@@ -1724,31 +1724,31 @@
     <t xml:space="preserve">2.43428015708923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4497652053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45286202430725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46679902076721</t>
+    <t xml:space="preserve">2.44976544380188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45286273956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46679925918579</t>
   </si>
   <si>
     <t xml:space="preserve">2.44666838645935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4575080871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47144484519958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45905637741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42653775215149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44821715354919</t>
+    <t xml:space="preserve">2.45750784873962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47144436836243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45905661582947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42653751373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44821667671204</t>
   </si>
   <si>
     <t xml:space="preserve">2.42963433265686</t>
@@ -1757,40 +1757,40 @@
     <t xml:space="preserve">2.48692989349365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5302882194519</t>
+    <t xml:space="preserve">2.53028845787048</t>
   </si>
   <si>
     <t xml:space="preserve">2.53803133964539</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54112863540649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54422521591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55661344528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55816197395325</t>
+    <t xml:space="preserve">2.54112839698792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54422545433044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55661368370056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55816173553467</t>
   </si>
   <si>
     <t xml:space="preserve">2.53648257255554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53493428230286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52873992919922</t>
+    <t xml:space="preserve">2.53493404388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5287401676178</t>
   </si>
   <si>
     <t xml:space="preserve">2.51790070533752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56435632705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5906810760498</t>
+    <t xml:space="preserve">2.56435608863831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59068131446838</t>
   </si>
   <si>
     <t xml:space="preserve">2.60306930541992</t>
@@ -1799,31 +1799,31 @@
     <t xml:space="preserve">2.60461783409119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59997200965881</t>
+    <t xml:space="preserve">2.59997248649597</t>
   </si>
   <si>
     <t xml:space="preserve">2.60152077674866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58913278579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58603549003601</t>
+    <t xml:space="preserve">2.58913254737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58603525161743</t>
   </si>
   <si>
     <t xml:space="preserve">2.64642810821533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65262222290039</t>
+    <t xml:space="preserve">2.65262198448181</t>
   </si>
   <si>
     <t xml:space="preserve">2.68514108657837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71611142158508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69698405265808</t>
+    <t xml:space="preserve">2.7161111831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69698429107666</t>
   </si>
   <si>
     <t xml:space="preserve">2.67945051193237</t>
@@ -1835,13 +1835,13 @@
     <t xml:space="preserve">2.65075898170471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68104457855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66669869422913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73045754432678</t>
+    <t xml:space="preserve">2.68104434013367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66669893264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7304573059082</t>
   </si>
   <si>
     <t xml:space="preserve">2.81174921989441</t>
@@ -1853,10 +1853,10 @@
     <t xml:space="preserve">2.78465175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77349424362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78305792808533</t>
+    <t xml:space="preserve">2.77349400520325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78305816650391</t>
   </si>
   <si>
     <t xml:space="preserve">2.79740357398987</t>
@@ -1865,25 +1865,25 @@
     <t xml:space="preserve">2.79580950737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82768869400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80696749687195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75914835929871</t>
+    <t xml:space="preserve">2.8276891708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80696773529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75914812088013</t>
   </si>
   <si>
     <t xml:space="preserve">2.74480295181274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74958467483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73205089569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72886347770691</t>
+    <t xml:space="preserve">2.74958443641663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7320511341095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72886323928833</t>
   </si>
   <si>
     <t xml:space="preserve">2.73364520072937</t>
@@ -1895,13 +1895,13 @@
     <t xml:space="preserve">2.68582630157471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73683333396912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71132946014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69538998603821</t>
+    <t xml:space="preserve">2.73683285713196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7113299369812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69539022445679</t>
   </si>
   <si>
     <t xml:space="preserve">2.70654773712158</t>
@@ -1910,19 +1910,19 @@
     <t xml:space="preserve">2.72726917266846</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70495367050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73523902893066</t>
+    <t xml:space="preserve">2.70495390892029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73523879051208</t>
   </si>
   <si>
     <t xml:space="preserve">2.68742036819458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76233649253845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78783988952637</t>
+    <t xml:space="preserve">2.76233673095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78783965110779</t>
   </si>
   <si>
     <t xml:space="preserve">2.77827620506287</t>
@@ -1937,22 +1937,22 @@
     <t xml:space="preserve">2.88188362121582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87869572639465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91535687446594</t>
+    <t xml:space="preserve">2.87869548797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91535663604736</t>
   </si>
   <si>
     <t xml:space="preserve">2.89144730567932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88666558265686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88825964927673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91695094108582</t>
+    <t xml:space="preserve">2.88666534423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88825941085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91695070266724</t>
   </si>
   <si>
     <t xml:space="preserve">2.89622926712036</t>
@@ -1961,10 +1961,10 @@
     <t xml:space="preserve">2.80059146881104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79262208938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84522247314453</t>
+    <t xml:space="preserve">2.79262185096741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84522271156311</t>
   </si>
   <si>
     <t xml:space="preserve">2.81812524795532</t>
@@ -1979,25 +1979,25 @@
     <t xml:space="preserve">2.90738677978516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90419912338257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86913180351257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95201802253723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95042395591736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02055835723877</t>
+    <t xml:space="preserve">2.90419888496399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86913156509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95201778411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95042371749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02055811882019</t>
   </si>
   <si>
     <t xml:space="preserve">2.9647696018219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00143098831177</t>
+    <t xml:space="preserve">3.00143074989319</t>
   </si>
   <si>
     <t xml:space="preserve">2.95679998397827</t>
@@ -2006,31 +2006,31 @@
     <t xml:space="preserve">2.97114539146423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01577615737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02215218544006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00461864471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97911500930786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00302481651306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01418280601501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9838969707489</t>
+    <t xml:space="preserve">3.01577639579773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02215266227722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00461888313293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97911524772644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0030243396759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01418256759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98389720916748</t>
   </si>
   <si>
     <t xml:space="preserve">3.02374625205994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99664902687073</t>
+    <t xml:space="preserve">2.99664878845215</t>
   </si>
   <si>
     <t xml:space="preserve">2.96636366844177</t>
@@ -2045,16 +2045,16 @@
     <t xml:space="preserve">3.04606175422668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05881333351135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04924941062927</t>
+    <t xml:space="preserve">3.05881357192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04924964904785</t>
   </si>
   <si>
     <t xml:space="preserve">3.06997108459473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03012228012085</t>
+    <t xml:space="preserve">3.03012204170227</t>
   </si>
   <si>
     <t xml:space="preserve">3.05403161048889</t>
@@ -2069,13 +2069,13 @@
     <t xml:space="preserve">3.07315897941589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07475304603577</t>
+    <t xml:space="preserve">3.07475328445435</t>
   </si>
   <si>
     <t xml:space="preserve">3.10025644302368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17357873916626</t>
+    <t xml:space="preserve">3.17357897758484</t>
   </si>
   <si>
     <t xml:space="preserve">3.1974880695343</t>
@@ -2084,28 +2084,28 @@
     <t xml:space="preserve">3.19430017471313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21820998191833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19589424133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16242122650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17995429039001</t>
+    <t xml:space="preserve">3.21820974349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19589447975159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16242074966431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17995476722717</t>
   </si>
   <si>
     <t xml:space="preserve">3.15604519844055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18473672866821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17517256736755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19111227989197</t>
+    <t xml:space="preserve">3.18473625183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17517232894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19111251831055</t>
   </si>
   <si>
     <t xml:space="preserve">3.06200122833252</t>
@@ -2114,40 +2114,40 @@
     <t xml:space="preserve">3.08750486373901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1241660118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1018500328064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09547448158264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0715651512146</t>
+    <t xml:space="preserve">3.12416577339172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10185027122498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09547472000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07156491279602</t>
   </si>
   <si>
     <t xml:space="preserve">3.10344457626343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11141395568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06040740013123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12735366821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17198467254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16879677772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16401481628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22139716148376</t>
+    <t xml:space="preserve">3.11141419410706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0604076385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12735390663147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17198491096497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16879653930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16401529312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22139739990234</t>
   </si>
   <si>
     <t xml:space="preserve">3.16082715988159</t>
@@ -2156,7 +2156,7 @@
     <t xml:space="preserve">3.16560864448547</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10822629928589</t>
+    <t xml:space="preserve">3.10822606086731</t>
   </si>
   <si>
     <t xml:space="preserve">3.09706854820251</t>
@@ -2165,25 +2165,25 @@
     <t xml:space="preserve">3.10663223266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0811288356781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07794070243835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1432933807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18633031845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18314266204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13213586807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27240443229675</t>
+    <t xml:space="preserve">3.08112859725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07794094085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14329361915588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18633055686951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18314242362976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13213562965393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27240419387817</t>
   </si>
   <si>
     <t xml:space="preserve">3.37760591506958</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">3.44774055480957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44614601135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37919974327087</t>
+    <t xml:space="preserve">3.44614624977112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37919950485229</t>
   </si>
   <si>
     <t xml:space="preserve">3.26921653747559</t>
@@ -2213,7 +2213,7 @@
     <t xml:space="preserve">3.33297491073608</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37282419204712</t>
+    <t xml:space="preserve">3.37282395362854</t>
   </si>
   <si>
     <t xml:space="preserve">3.38557577133179</t>
@@ -2222,73 +2222,73 @@
     <t xml:space="preserve">3.40948510169983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4270191192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43977022171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47802543640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45252203941345</t>
+    <t xml:space="preserve">3.42701864242554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43977046012878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47802567481995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45252180099487</t>
   </si>
   <si>
     <t xml:space="preserve">3.45730400085449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47005581855774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55612969398499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53700232505798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51628112792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33935046195984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30906510353088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33775687217712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27878022193909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09069275856018</t>
+    <t xml:space="preserve">3.47005605697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55612945556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5370020866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51628088951111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.339350938797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30906558036804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33775663375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27877998352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0906925201416</t>
   </si>
   <si>
     <t xml:space="preserve">3.11300802230835</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26124668121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83247089385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65872883796692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69060826301575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22038960456848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55830931663513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46585917472839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51049041748047</t>
+    <t xml:space="preserve">3.2612464427948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83247065544128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6587290763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69060778617859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2203893661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55830907821655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46585965156555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51049065589905</t>
   </si>
   <si>
     <t xml:space="preserve">2.5168662071228</t>
@@ -2306,19 +2306,19 @@
     <t xml:space="preserve">2.41804051399231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44035649299622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50252056121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62206792831421</t>
+    <t xml:space="preserve">2.44035625457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50252079963684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62206768989563</t>
   </si>
   <si>
     <t xml:space="preserve">2.60453391075134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52802395820618</t>
+    <t xml:space="preserve">2.52802419662476</t>
   </si>
   <si>
     <t xml:space="preserve">2.56468510627747</t>
@@ -2327,31 +2327,31 @@
     <t xml:space="preserve">2.53121209144592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55193328857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45948338508606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57584309577942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56787252426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54715156555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54396367073059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60772204399109</t>
+    <t xml:space="preserve">2.55193305015564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45948362350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57584285736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56787276268005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54715204238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54396343231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60772228240967</t>
   </si>
   <si>
     <t xml:space="preserve">2.62047386169434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5184600353241</t>
+    <t xml:space="preserve">2.51846051216125</t>
   </si>
   <si>
     <t xml:space="preserve">2.59018850326538</t>
@@ -2366,22 +2366,22 @@
     <t xml:space="preserve">2.69220232963562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57903099060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57265472412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52483582496643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49295711517334</t>
+    <t xml:space="preserve">2.57903075218201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57265496253967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52483630180359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49295687675476</t>
   </si>
   <si>
     <t xml:space="preserve">2.59178280830383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61887955665588</t>
+    <t xml:space="preserve">2.61887979507446</t>
   </si>
   <si>
     <t xml:space="preserve">2.56149697303772</t>
@@ -2396,49 +2396,49 @@
     <t xml:space="preserve">2.51367831230164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50092673301697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55352735519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54874587059021</t>
+    <t xml:space="preserve">2.50092649459839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55352759361267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54874539375305</t>
   </si>
   <si>
     <t xml:space="preserve">2.65713500976562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66032290458679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85159826278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85638046264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81653118133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77668237686157</t>
+    <t xml:space="preserve">2.66032266616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85159850120544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85638022422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81653094291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77668213844299</t>
   </si>
   <si>
     <t xml:space="preserve">2.6778564453125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80218553543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78943371772766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77030658721924</t>
+    <t xml:space="preserve">2.80218529701233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78943395614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77030634880066</t>
   </si>
   <si>
     <t xml:space="preserve">2.75755453109741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75436663627625</t>
+    <t xml:space="preserve">2.75436687469482</t>
   </si>
   <si>
     <t xml:space="preserve">2.68901419639587</t>
@@ -2447,37 +2447,37 @@
     <t xml:space="preserve">2.63800740242004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70335960388184</t>
+    <t xml:space="preserve">2.70335984230042</t>
   </si>
   <si>
     <t xml:space="preserve">2.70017170906067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72567510604858</t>
+    <t xml:space="preserve">2.72567534446716</t>
   </si>
   <si>
     <t xml:space="preserve">2.74209499359131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69940400123596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71418118476868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.641934633255</t>
+    <t xml:space="preserve">2.69940376281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71418142318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64193487167358</t>
   </si>
   <si>
     <t xml:space="preserve">2.63372492790222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6747739315033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63865065574646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65014457702637</t>
+    <t xml:space="preserve">2.67477416992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63865041732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65014481544495</t>
   </si>
   <si>
     <t xml:space="preserve">2.69447803497314</t>
@@ -2486,10 +2486,10 @@
     <t xml:space="preserve">2.73060131072998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73388504981995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7355272769928</t>
+    <t xml:space="preserve">2.73388528823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73552703857422</t>
   </si>
   <si>
     <t xml:space="preserve">2.76508283615112</t>
@@ -2504,10 +2504,10 @@
     <t xml:space="preserve">2.63536667823792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70268797874451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68790984153748</t>
+    <t xml:space="preserve">2.70268774032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68791007995605</t>
   </si>
   <si>
     <t xml:space="preserve">2.59267544746399</t>
@@ -2522,7 +2522,7 @@
     <t xml:space="preserve">2.59595918655396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58774971961975</t>
+    <t xml:space="preserve">2.58774948120117</t>
   </si>
   <si>
     <t xml:space="preserve">2.66820621490479</t>
@@ -2531,19 +2531,19 @@
     <t xml:space="preserve">2.72403335571289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78642821311951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77657628059387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75851464271545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66656422615051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70925569534302</t>
+    <t xml:space="preserve">2.78642845153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77657675743103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75851488113403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66656446456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70925545692444</t>
   </si>
   <si>
     <t xml:space="preserve">2.68298387527466</t>
@@ -2555,13 +2555,13 @@
     <t xml:space="preserve">2.75030493736267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72239136695862</t>
+    <t xml:space="preserve">2.72239112854004</t>
   </si>
   <si>
     <t xml:space="preserve">2.64686059951782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62715721130371</t>
+    <t xml:space="preserve">2.62715697288513</t>
   </si>
   <si>
     <t xml:space="preserve">2.62879872322083</t>
@@ -2570,7 +2570,7 @@
     <t xml:space="preserve">2.6156632900238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69283580780029</t>
+    <t xml:space="preserve">2.69283556938171</t>
   </si>
   <si>
     <t xml:space="preserve">2.59760141372681</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">2.66492223739624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67970013618469</t>
+    <t xml:space="preserve">2.67970037460327</t>
   </si>
   <si>
     <t xml:space="preserve">2.69776177406311</t>
@@ -2600,31 +2600,31 @@
     <t xml:space="preserve">2.63700866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62387323379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60745310783386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64521884918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63044118881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54998397827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55819392204285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54505801200867</t>
+    <t xml:space="preserve">2.62387347221375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60745334625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64521837234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63044095039368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54998421669006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55819368362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54505848884583</t>
   </si>
   <si>
     <t xml:space="preserve">2.51386094093323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52042865753174</t>
+    <t xml:space="preserve">2.52042841911316</t>
   </si>
   <si>
     <t xml:space="preserve">2.50236701965332</t>
@@ -2633,25 +2633,25 @@
     <t xml:space="preserve">2.472811460495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42191028594971</t>
+    <t xml:space="preserve">2.42191052436829</t>
   </si>
   <si>
     <t xml:space="preserve">2.44325613975525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35951519012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38414478302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41205835342407</t>
+    <t xml:space="preserve">2.35951542854309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3841450214386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41205859184265</t>
   </si>
   <si>
     <t xml:space="preserve">2.46295952796936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39563894271851</t>
+    <t xml:space="preserve">2.39563870429993</t>
   </si>
   <si>
     <t xml:space="preserve">2.37593507766724</t>
@@ -2660,13 +2660,13 @@
     <t xml:space="preserve">2.37757682800293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31518173217773</t>
+    <t xml:space="preserve">2.31518197059631</t>
   </si>
   <si>
     <t xml:space="preserve">2.29219460487366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23472547531128</t>
+    <t xml:space="preserve">2.2347252368927</t>
   </si>
   <si>
     <t xml:space="preserve">2.19695997238159</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">2.23636722564697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25442886352539</t>
+    <t xml:space="preserve">2.25442910194397</t>
   </si>
   <si>
     <t xml:space="preserve">2.3102560043335</t>
@@ -2687,22 +2687,22 @@
     <t xml:space="preserve">2.30533027648926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28070092201233</t>
+    <t xml:space="preserve">2.28070068359375</t>
   </si>
   <si>
     <t xml:space="preserve">2.45474982261658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42519450187683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44982385635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49251532554626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47937917709351</t>
+    <t xml:space="preserve">2.42519426345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44982361793518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49251508712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47937941551208</t>
   </si>
   <si>
     <t xml:space="preserve">2.56147813796997</t>
@@ -2711,31 +2711,31 @@
     <t xml:space="preserve">2.50893473625183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49579906463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50400900840759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48102116584778</t>
+    <t xml:space="preserve">2.49579882621765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50400876998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48102140426636</t>
   </si>
   <si>
     <t xml:space="preserve">2.47609543800354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52207088470459</t>
+    <t xml:space="preserve">2.52207064628601</t>
   </si>
   <si>
     <t xml:space="preserve">2.53520655632019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51221895217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4711697101593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4399721622467</t>
+    <t xml:space="preserve">2.5122184753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47116947174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43997192382812</t>
   </si>
   <si>
     <t xml:space="preserve">2.46788573265076</t>
@@ -2744,55 +2744,55 @@
     <t xml:space="preserve">2.44489789009094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43011999130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41534233093262</t>
+    <t xml:space="preserve">2.43012022972107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41534209251404</t>
   </si>
   <si>
     <t xml:space="preserve">2.38907098770142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36444139480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39399695396423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36608338356018</t>
+    <t xml:space="preserve">2.36444115638733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39399647712708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3660831451416</t>
   </si>
   <si>
     <t xml:space="preserve">2.40384864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45146560668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33981156349182</t>
+    <t xml:space="preserve">2.45146584510803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33981132507324</t>
   </si>
   <si>
     <t xml:space="preserve">2.38742876052856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4531078338623</t>
+    <t xml:space="preserve">2.45310759544373</t>
   </si>
   <si>
     <t xml:space="preserve">2.45967578887939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44654011726379</t>
+    <t xml:space="preserve">2.44653987884521</t>
   </si>
   <si>
     <t xml:space="preserve">2.50565099716187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4416139125824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49087285995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48594760894775</t>
+    <t xml:space="preserve">2.44161367416382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49087309837341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48594737052917</t>
   </si>
   <si>
     <t xml:space="preserve">2.59431767463684</t>
@@ -2801,13 +2801,13 @@
     <t xml:space="preserve">2.5417742729187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38086104393005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33652782440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35787320137024</t>
+    <t xml:space="preserve">2.38086128234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33652758598328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35787343978882</t>
   </si>
   <si>
     <t xml:space="preserve">2.36772537231445</t>
@@ -2819,16 +2819,16 @@
     <t xml:space="preserve">2.46952748298645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49415707588196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55326819419861</t>
+    <t xml:space="preserve">2.49415731430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55326843261719</t>
   </si>
   <si>
     <t xml:space="preserve">2.51057696342468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52371263504028</t>
+    <t xml:space="preserve">2.52371287345886</t>
   </si>
   <si>
     <t xml:space="preserve">2.55491018295288</t>
@@ -2837,10 +2837,10 @@
     <t xml:space="preserve">2.58939146995544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54670023918152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53684830665588</t>
+    <t xml:space="preserve">2.5467004776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53684854507446</t>
   </si>
   <si>
     <t xml:space="preserve">2.52535462379456</t>
@@ -2852,37 +2852,37 @@
     <t xml:space="preserve">2.40220665931702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5286386013031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56312012672424</t>
+    <t xml:space="preserve">2.52863836288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56311988830566</t>
   </si>
   <si>
     <t xml:space="preserve">2.56968808174133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60416913032532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71582365036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68216276168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72895908355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70843482017517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69611954689026</t>
+    <t xml:space="preserve">2.6041693687439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71582341194153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68216300010681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72895932197571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70843458175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69611978530884</t>
   </si>
   <si>
     <t xml:space="preserve">2.71171855926514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73224329948425</t>
+    <t xml:space="preserve">2.73224306106567</t>
   </si>
   <si>
     <t xml:space="preserve">2.76918745040894</t>
@@ -2891,28 +2891,28 @@
     <t xml:space="preserve">2.76097774505615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75441002845764</t>
+    <t xml:space="preserve">2.75440979003906</t>
   </si>
   <si>
     <t xml:space="preserve">2.75523066520691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75605201721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74620032310486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79381728172302</t>
+    <t xml:space="preserve">2.75605154037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74620008468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79381704330444</t>
   </si>
   <si>
     <t xml:space="preserve">2.76261973381042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76672458648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79710125923157</t>
+    <t xml:space="preserve">2.7667248249054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79710149765015</t>
   </si>
   <si>
     <t xml:space="preserve">2.83815050125122</t>
@@ -2921,16 +2921,16 @@
     <t xml:space="preserve">2.77082967758179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77247142791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76426196098328</t>
+    <t xml:space="preserve">2.77247166633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7642617225647</t>
   </si>
   <si>
     <t xml:space="preserve">2.86278009414673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83240365982056</t>
+    <t xml:space="preserve">2.83240342140198</t>
   </si>
   <si>
     <t xml:space="preserve">2.82255172729492</t>
@@ -2939,10 +2939,10 @@
     <t xml:space="preserve">2.86031723022461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87837910652161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88330483436584</t>
+    <t xml:space="preserve">2.87837862968445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88330507278442</t>
   </si>
   <si>
     <t xml:space="preserve">2.88740968704224</t>
@@ -2960,19 +2960,19 @@
     <t xml:space="preserve">2.86606383323669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86360096931458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87427401542664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89726138114929</t>
+    <t xml:space="preserve">2.86360120773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87427377700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89726161956787</t>
   </si>
   <si>
     <t xml:space="preserve">2.93256402015686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95883560180664</t>
+    <t xml:space="preserve">2.95883536338806</t>
   </si>
   <si>
     <t xml:space="preserve">2.97197103500366</t>
@@ -2981,52 +2981,52 @@
     <t xml:space="preserve">3.02533531188965</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00481104850769</t>
+    <t xml:space="preserve">3.00481057167053</t>
   </si>
   <si>
     <t xml:space="preserve">3.00809502601624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04093432426453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01794648170471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04586005210876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02123045921326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00727391242981</t>
+    <t xml:space="preserve">3.04093408584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01794672012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04586029052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02123022079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00727367401123</t>
   </si>
   <si>
     <t xml:space="preserve">2.98921203613281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95801424980164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90218758583069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92353320121765</t>
+    <t xml:space="preserve">2.95801448822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90218734741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92353343963623</t>
   </si>
   <si>
     <t xml:space="preserve">2.89561939239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89069366455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89151453971863</t>
+    <t xml:space="preserve">2.8906934261322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89151477813721</t>
   </si>
   <si>
     <t xml:space="preserve">2.8668851852417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89479827880859</t>
+    <t xml:space="preserve">2.89479851722717</t>
   </si>
   <si>
     <t xml:space="preserve">2.90920472145081</t>
@@ -3035,13 +3035,13 @@
     <t xml:space="preserve">2.89649343490601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96005034446716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86598610877991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86429142951965</t>
+    <t xml:space="preserve">2.96005058288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86598634719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86429166793823</t>
   </si>
   <si>
     <t xml:space="preserve">2.93208527565002</t>
@@ -3056,16 +3056,16 @@
     <t xml:space="preserve">2.89564609527588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92615342140198</t>
+    <t xml:space="preserve">2.9261531829834</t>
   </si>
   <si>
     <t xml:space="preserve">2.84225821495056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85073280334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94733881950378</t>
+    <t xml:space="preserve">2.85073256492615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94733905792236</t>
   </si>
   <si>
     <t xml:space="preserve">2.9998791217804</t>
@@ -3086,10 +3086,10 @@
     <t xml:space="preserve">3.04055571556091</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04479265213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02275943756104</t>
+    <t xml:space="preserve">3.04479241371155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02275919914246</t>
   </si>
   <si>
     <t xml:space="preserve">3.01004838943481</t>
@@ -3101,22 +3101,22 @@
     <t xml:space="preserve">3.02021718025208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04648756980896</t>
+    <t xml:space="preserve">3.04648733139038</t>
   </si>
   <si>
     <t xml:space="preserve">3.03547096252441</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08546900749207</t>
+    <t xml:space="preserve">3.08546876907349</t>
   </si>
   <si>
     <t xml:space="preserve">3.09733271598816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13122963905334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14563584327698</t>
+    <t xml:space="preserve">3.13122987747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14563608169556</t>
   </si>
   <si>
     <t xml:space="preserve">3.15665245056152</t>
@@ -3125,37 +3125,37 @@
     <t xml:space="preserve">3.18038034439087</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19648122787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18546485900879</t>
+    <t xml:space="preserve">3.19648146629333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18546509742737</t>
   </si>
   <si>
     <t xml:space="preserve">3.18715977668762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16682171821594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12953495979309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10157012939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11597633361816</t>
+    <t xml:space="preserve">3.16682147979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12953519821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10156989097595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11597609519958</t>
   </si>
   <si>
     <t xml:space="preserve">3.11089158058167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10411238670349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13716173171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12275552749634</t>
+    <t xml:space="preserve">3.10411214828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13716149330139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12275528907776</t>
   </si>
   <si>
     <t xml:space="preserve">3.11004400253296</t>
@@ -3173,7 +3173,7 @@
     <t xml:space="preserve">3.07360506057739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09902763366699</t>
+    <t xml:space="preserve">3.09902787208557</t>
   </si>
   <si>
     <t xml:space="preserve">3.04987716674805</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">3.08631634712219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08292675018311</t>
+    <t xml:space="preserve">3.08292651176453</t>
   </si>
   <si>
     <t xml:space="preserve">3.09224820137024</t>
@@ -3197,34 +3197,34 @@
     <t xml:space="preserve">3.02360725402832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97445631027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01428532600403</t>
+    <t xml:space="preserve">2.9744565486908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01428508758545</t>
   </si>
   <si>
     <t xml:space="preserve">2.99648952484131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99564218521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99818444252014</t>
+    <t xml:space="preserve">2.9956419467926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99818420410156</t>
   </si>
   <si>
     <t xml:space="preserve">3.00411605834961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96089792251587</t>
+    <t xml:space="preserve">2.96089768409729</t>
   </si>
   <si>
     <t xml:space="preserve">2.98547291755676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91089940071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87785005569458</t>
+    <t xml:space="preserve">2.91089963912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87785029411316</t>
   </si>
   <si>
     <t xml:space="preserve">2.91174721717834</t>
@@ -3233,10 +3233,10 @@
     <t xml:space="preserve">2.94564414024353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97530388832092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95327091217041</t>
+    <t xml:space="preserve">2.97530364990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95327067375183</t>
   </si>
   <si>
     <t xml:space="preserve">2.92445826530457</t>
@@ -3251,10 +3251,10 @@
     <t xml:space="preserve">3.03377604484558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04902958869934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01767492294312</t>
+    <t xml:space="preserve">3.04902982711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01767516136169</t>
   </si>
   <si>
     <t xml:space="preserve">3.05241942405701</t>
@@ -3263,13 +3263,13 @@
     <t xml:space="preserve">2.99733686447144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01259064674377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9947943687439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03462338447571</t>
+    <t xml:space="preserve">3.0125904083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99479460716248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03462362289429</t>
   </si>
   <si>
     <t xml:space="preserve">3.1125864982605</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">3.09309577941895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05665683746338</t>
+    <t xml:space="preserve">3.0566565990448</t>
   </si>
   <si>
     <t xml:space="preserve">3.01682758331299</t>
@@ -3287,40 +3287,40 @@
     <t xml:space="preserve">3.05750393867493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06936740875244</t>
+    <t xml:space="preserve">3.06936764717102</t>
   </si>
   <si>
     <t xml:space="preserve">3.07275748252869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03208112716675</t>
+    <t xml:space="preserve">3.03208136558533</t>
   </si>
   <si>
     <t xml:space="preserve">3.02953886985779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00072646141052</t>
+    <t xml:space="preserve">3.0007266998291</t>
   </si>
   <si>
     <t xml:space="preserve">2.85581707954407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8702232837677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88547706604004</t>
+    <t xml:space="preserve">2.87022352218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88547682762146</t>
   </si>
   <si>
     <t xml:space="preserve">2.95750784873962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88971424102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02530169487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98208332061768</t>
+    <t xml:space="preserve">2.88971400260925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02530193328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9820830821991</t>
   </si>
   <si>
     <t xml:space="preserve">3.0083532333374</t>
@@ -3335,58 +3335,58 @@
     <t xml:space="preserve">3.02445459365845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04564023017883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05072426795959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06089377403259</t>
+    <t xml:space="preserve">3.04563999176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05072450637817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06089353561401</t>
   </si>
   <si>
     <t xml:space="preserve">3.11682343482971</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10241746902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14055132865906</t>
+    <t xml:space="preserve">3.10241723060608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14055156707764</t>
   </si>
   <si>
     <t xml:space="preserve">3.11173892021179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0871639251709</t>
+    <t xml:space="preserve">3.08716344833374</t>
   </si>
   <si>
     <t xml:space="preserve">3.02699661254883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01343774795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99394750595093</t>
+    <t xml:space="preserve">3.0134379863739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99394702911377</t>
   </si>
   <si>
     <t xml:space="preserve">2.97106671333313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98123574256897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9490339756012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90835738182068</t>
+    <t xml:space="preserve">2.98123550415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94903349876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9083571434021</t>
   </si>
   <si>
     <t xml:space="preserve">2.91767907142639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97360873222351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07614731788635</t>
+    <t xml:space="preserve">2.97360897064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07614755630493</t>
   </si>
   <si>
     <t xml:space="preserve">3.14817810058594</t>
@@ -3398,10 +3398,10 @@
     <t xml:space="preserve">3.07021522521973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93886470794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88039231300354</t>
+    <t xml:space="preserve">2.9388644695282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88039255142212</t>
   </si>
   <si>
     <t xml:space="preserve">2.9185266494751</t>
@@ -3416,28 +3416,28 @@
     <t xml:space="preserve">2.86005425453186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88717174530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87276554107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84310579299927</t>
+    <t xml:space="preserve">2.88717198371887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87276577949524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84310555458069</t>
   </si>
   <si>
     <t xml:space="preserve">2.83802127838135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79734492301941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80836153030396</t>
+    <t xml:space="preserve">2.79734516143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80836129188538</t>
   </si>
   <si>
     <t xml:space="preserve">2.82446241378784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74056768417358</t>
+    <t xml:space="preserve">2.740567445755</t>
   </si>
   <si>
     <t xml:space="preserve">2.93632221221924</t>
@@ -3446,7 +3446,7 @@
     <t xml:space="preserve">2.83208918571472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78971838951111</t>
+    <t xml:space="preserve">2.78971815109253</t>
   </si>
   <si>
     <t xml:space="preserve">2.76260042190552</t>
@@ -3455,10 +3455,10 @@
     <t xml:space="preserve">2.69904351234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71175527572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77446436882019</t>
+    <t xml:space="preserve">2.71175503730774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77446460723877</t>
   </si>
   <si>
     <t xml:space="preserve">2.87700271606445</t>
@@ -3467,19 +3467,19 @@
     <t xml:space="preserve">2.86344385147095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85666465759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85157990455627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81937789916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85412216186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89140868186951</t>
+    <t xml:space="preserve">2.85666441917419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85158014297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81937766075134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85412263870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89140892028809</t>
   </si>
   <si>
     <t xml:space="preserve">2.7880232334137</t>
@@ -3488,25 +3488,25 @@
     <t xml:space="preserve">2.75666880607605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.814293384552</t>
+    <t xml:space="preserve">2.81429362297058</t>
   </si>
   <si>
     <t xml:space="preserve">2.82700490951538</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85327506065369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83547878265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87615513801575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90750980377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00581121444702</t>
+    <t xml:space="preserve">2.85327482223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83547902107239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87615537643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90751004219055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00581097602844</t>
   </si>
   <si>
     <t xml:space="preserve">3.04733467102051</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">3.01598024368286</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04818201065063</t>
+    <t xml:space="preserve">3.04818224906921</t>
   </si>
   <si>
     <t xml:space="preserve">2.97276139259338</t>
@@ -3536,7 +3536,7 @@
     <t xml:space="preserve">2.9524233341217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98632025718689</t>
+    <t xml:space="preserve">2.98632049560547</t>
   </si>
   <si>
     <t xml:space="preserve">3.06343579292297</t>
@@ -3545,7 +3545,7 @@
     <t xml:space="preserve">2.84141087532043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86513900756836</t>
+    <t xml:space="preserve">2.86513876914978</t>
   </si>
   <si>
     <t xml:space="preserve">2.92954301834106</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">3.03801321983337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98801493644714</t>
+    <t xml:space="preserve">2.98801517486572</t>
   </si>
   <si>
     <t xml:space="preserve">2.96598219871521</t>
@@ -3566,13 +3566,13 @@
     <t xml:space="preserve">2.89056158065796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86683368682861</t>
+    <t xml:space="preserve">2.86683344841003</t>
   </si>
   <si>
     <t xml:space="preserve">2.82785201072693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86174893379211</t>
+    <t xml:space="preserve">2.86174917221069</t>
   </si>
   <si>
     <t xml:space="preserve">2.83717393875122</t>
@@ -3581,19 +3581,19 @@
     <t xml:space="preserve">2.83886861801147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7270085811615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53125381469727</t>
+    <t xml:space="preserve">2.72700881958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53125405311584</t>
   </si>
   <si>
     <t xml:space="preserve">2.41685175895691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35668468475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45837569236755</t>
+    <t xml:space="preserve">2.35668444633484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45837545394897</t>
   </si>
   <si>
     <t xml:space="preserve">2.38888669013977</t>
@@ -3605,19 +3605,19 @@
     <t xml:space="preserve">2.3823139667511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34250545501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32569742202759</t>
+    <t xml:space="preserve">2.34250521659851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32569718360901</t>
   </si>
   <si>
     <t xml:space="preserve">2.37435221672058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46193075180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46812319755554</t>
+    <t xml:space="preserve">2.46193051338196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46812295913696</t>
   </si>
   <si>
     <t xml:space="preserve">2.49908542633057</t>
@@ -3629,25 +3629,25 @@
     <t xml:space="preserve">2.44158434867859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4875853061676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48493099212646</t>
+    <t xml:space="preserve">2.48758482933044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48493123054504</t>
   </si>
   <si>
     <t xml:space="preserve">2.41327595710754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45750784873962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49112343788147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47696948051453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45927667617798</t>
+    <t xml:space="preserve">2.45750761032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49112367630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47696924209595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45927691459656</t>
   </si>
   <si>
     <t xml:space="preserve">2.37523674964905</t>
@@ -3659,7 +3659,7 @@
     <t xml:space="preserve">2.37789058685303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38673710823059</t>
+    <t xml:space="preserve">2.38673686981201</t>
   </si>
   <si>
     <t xml:space="preserve">2.41150689125061</t>
@@ -3686,19 +3686,19 @@
     <t xml:space="preserve">2.44689202308655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50970053672791</t>
+    <t xml:space="preserve">2.50970077514648</t>
   </si>
   <si>
     <t xml:space="preserve">2.50527763366699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47077703475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44246888160706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4398148059845</t>
+    <t xml:space="preserve">2.47077679634094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44246864318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43981504440308</t>
   </si>
   <si>
     <t xml:space="preserve">2.4433536529541</t>
@@ -3722,13 +3722,13 @@
     <t xml:space="preserve">2.42300701141357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40442943572998</t>
+    <t xml:space="preserve">2.40442967414856</t>
   </si>
   <si>
     <t xml:space="preserve">2.36904430389404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29650449752808</t>
+    <t xml:space="preserve">2.29650473594666</t>
   </si>
   <si>
     <t xml:space="preserve">2.35312104225159</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">2.21246433258057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24342679977417</t>
+    <t xml:space="preserve">2.24342656135559</t>
   </si>
   <si>
     <t xml:space="preserve">2.18504095077515</t>
@@ -3752,7 +3752,7 @@
     <t xml:space="preserve">2.12842440605164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11603975296021</t>
+    <t xml:space="preserve">2.11603951454163</t>
   </si>
   <si>
     <t xml:space="preserve">2.2009642124176</t>
@@ -3764,40 +3764,40 @@
     <t xml:space="preserve">2.23015713691711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14965581893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14700174331665</t>
+    <t xml:space="preserve">2.14965558052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14700198173523</t>
   </si>
   <si>
     <t xml:space="preserve">2.11957812309265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1063084602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07800054550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07357740402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04261517524719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97803723812103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98422968387604</t>
+    <t xml:space="preserve">2.10630869865417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07800030708313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07357716560364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04261541366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97803711891174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98422956466675</t>
   </si>
   <si>
     <t xml:space="preserve">1.87895834445953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92584371566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9161125421524</t>
+    <t xml:space="preserve">1.9258439540863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91611266136169</t>
   </si>
   <si>
     <t xml:space="preserve">1.93380570411682</t>
@@ -3812,19 +3812,19 @@
     <t xml:space="preserve">1.90018951892853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84003436565399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82588028907776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87011194229126</t>
+    <t xml:space="preserve">1.84003448486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82588016986847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87011218070984</t>
   </si>
   <si>
     <t xml:space="preserve">1.80464911460876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77280247211456</t>
+    <t xml:space="preserve">1.77280235290527</t>
   </si>
   <si>
     <t xml:space="preserve">1.80022609233856</t>
@@ -3833,28 +3833,28 @@
     <t xml:space="preserve">1.83030343055725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87807357311249</t>
+    <t xml:space="preserve">1.87807369232178</t>
   </si>
   <si>
     <t xml:space="preserve">1.88249695301056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8630348443985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87541949748993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85153472423553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91257441043854</t>
+    <t xml:space="preserve">1.86303472518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87541961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85153460502625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91257429122925</t>
   </si>
   <si>
     <t xml:space="preserve">1.99838364124298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01696085929871</t>
+    <t xml:space="preserve">2.01696109771729</t>
   </si>
   <si>
     <t xml:space="preserve">2.12577080726624</t>
@@ -3866,7 +3866,7 @@
     <t xml:space="preserve">2.14434790611267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14257836341858</t>
+    <t xml:space="preserve">2.14257884025574</t>
   </si>
   <si>
     <t xml:space="preserve">2.13196301460266</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">2.28058123588562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29915857315063</t>
+    <t xml:space="preserve">2.29915833473206</t>
   </si>
   <si>
     <t xml:space="preserve">2.33454370498657</t>
@@ -3902,10 +3902,10 @@
     <t xml:space="preserve">2.33631300926208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32835125923157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3274667263031</t>
+    <t xml:space="preserve">2.32835149765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32746648788452</t>
   </si>
   <si>
     <t xml:space="preserve">2.30623555183411</t>
@@ -3917,37 +3917,37 @@
     <t xml:space="preserve">2.35046720504761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33188986778259</t>
+    <t xml:space="preserve">2.33188962936401</t>
   </si>
   <si>
     <t xml:space="preserve">2.34338998794556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35400557518005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37169814109802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37965989112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37612175941467</t>
+    <t xml:space="preserve">2.35400581359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3716983795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37966012954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37612152099609</t>
   </si>
   <si>
     <t xml:space="preserve">2.4327380657196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48050785064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50350856781006</t>
+    <t xml:space="preserve">2.48050808906555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50350832939148</t>
   </si>
   <si>
     <t xml:space="preserve">2.44600749015808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3106586933136</t>
+    <t xml:space="preserve">2.31065845489502</t>
   </si>
   <si>
     <t xml:space="preserve">2.25669622421265</t>
@@ -3956,10 +3956,10 @@
     <t xml:space="preserve">2.2726194858551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26200389862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24165749549866</t>
+    <t xml:space="preserve">2.26200413703918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24165725708008</t>
   </si>
   <si>
     <t xml:space="preserve">2.25758075714111</t>
@@ -3968,7 +3968,7 @@
     <t xml:space="preserve">2.25492691993713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20273351669312</t>
+    <t xml:space="preserve">2.20273375511169</t>
   </si>
   <si>
     <t xml:space="preserve">2.25227308273315</t>
@@ -3977,7 +3977,7 @@
     <t xml:space="preserve">2.22838807106018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28765821456909</t>
+    <t xml:space="preserve">2.28765845298767</t>
   </si>
   <si>
     <t xml:space="preserve">2.2894275188446</t>
@@ -3989,13 +3989,13 @@
     <t xml:space="preserve">2.32304334640503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45043039321899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45131516456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42389130592346</t>
+    <t xml:space="preserve">2.45043063163757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45131492614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42389154434204</t>
   </si>
   <si>
     <t xml:space="preserve">2.42919921875</t>
@@ -4007,13 +4007,13 @@
     <t xml:space="preserve">2.34781336784363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38850617408752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41416049003601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40177583694458</t>
+    <t xml:space="preserve">2.3885064125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41416072845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.401775598526</t>
   </si>
   <si>
     <t xml:space="preserve">2.39646816253662</t>
@@ -4022,19 +4022,19 @@
     <t xml:space="preserve">2.34692859649658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34073615074158</t>
+    <t xml:space="preserve">2.340735912323</t>
   </si>
   <si>
     <t xml:space="preserve">2.3442747592926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41062211990356</t>
+    <t xml:space="preserve">2.41062188148499</t>
   </si>
   <si>
     <t xml:space="preserve">2.37081384658813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31596636772156</t>
+    <t xml:space="preserve">2.31596660614014</t>
   </si>
   <si>
     <t xml:space="preserve">2.28854274749756</t>
@@ -4043,13 +4043,13 @@
     <t xml:space="preserve">2.29561996459961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3000431060791</t>
+    <t xml:space="preserve">2.30004286766052</t>
   </si>
   <si>
     <t xml:space="preserve">2.29473543167114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26642727851868</t>
+    <t xml:space="preserve">2.2664270401001</t>
   </si>
   <si>
     <t xml:space="preserve">2.23458027839661</t>
@@ -4061,13 +4061,13 @@
     <t xml:space="preserve">2.22219562530518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23192667961121</t>
+    <t xml:space="preserve">2.23192620277405</t>
   </si>
   <si>
     <t xml:space="preserve">2.1753101348877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1947717666626</t>
+    <t xml:space="preserve">2.19477200508118</t>
   </si>
   <si>
     <t xml:space="preserve">2.22573399543762</t>
@@ -4079,49 +4079,49 @@
     <t xml:space="preserve">2.15054035186768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1125009059906</t>
+    <t xml:space="preserve">2.11250114440918</t>
   </si>
   <si>
     <t xml:space="preserve">2.10807776451111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13727045059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12753963470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11692404747009</t>
+    <t xml:space="preserve">2.13727068901062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12753987312317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11692428588867</t>
   </si>
   <si>
     <t xml:space="preserve">2.18857932090759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20627212524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22131085395813</t>
+    <t xml:space="preserve">2.20627188682556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22131061553955</t>
   </si>
   <si>
     <t xml:space="preserve">2.20361804962158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21423363685608</t>
+    <t xml:space="preserve">2.21423387527466</t>
   </si>
   <si>
     <t xml:space="preserve">2.24254202842712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30181241035461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29827380180359</t>
+    <t xml:space="preserve">2.30181217193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29827404022217</t>
   </si>
   <si>
     <t xml:space="preserve">2.40266036987305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42212224006653</t>
+    <t xml:space="preserve">2.42212247848511</t>
   </si>
   <si>
     <t xml:space="preserve">2.31950497627258</t>
@@ -4133,7 +4133,7 @@
     <t xml:space="preserve">2.39027547836304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46989226341248</t>
+    <t xml:space="preserve">2.46989250183105</t>
   </si>
   <si>
     <t xml:space="preserve">2.49820065498352</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">2.44512248039246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49643135070801</t>
+    <t xml:space="preserve">2.49643111228943</t>
   </si>
   <si>
     <t xml:space="preserve">2.53181672096252</t>
@@ -4151,7 +4151,7 @@
     <t xml:space="preserve">2.52297043800354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54066276550293</t>
+    <t xml:space="preserve">2.54066300392151</t>
   </si>
   <si>
     <t xml:space="preserve">2.62381839752197</t>
@@ -4172,49 +4172,49 @@
     <t xml:space="preserve">2.53712439537048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61497235298157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63266468048096</t>
+    <t xml:space="preserve">2.61497211456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63266491889954</t>
   </si>
   <si>
     <t xml:space="preserve">2.62204885482788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54950952529907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52827835083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57958674430847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58135581016541</t>
+    <t xml:space="preserve">2.54950928688049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5282781124115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57958650588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58135604858398</t>
   </si>
   <si>
     <t xml:space="preserve">2.60966444015503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58666372299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59020256996155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.538893699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.572509765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54420161247253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55304789543152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56366348266602</t>
+    <t xml:space="preserve">2.58666396141052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59020233154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53889346122742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57250952720642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54420137405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55304765701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56366324424744</t>
   </si>
   <si>
     <t xml:space="preserve">2.55127859115601</t>
@@ -4223,13 +4223,13 @@
     <t xml:space="preserve">2.53004717826843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56897139549255</t>
+    <t xml:space="preserve">2.56897115707397</t>
   </si>
   <si>
     <t xml:space="preserve">2.51812791824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52922129631042</t>
+    <t xml:space="preserve">2.52922105789185</t>
   </si>
   <si>
     <t xml:space="preserve">2.53661632537842</t>
@@ -4256,16 +4256,16 @@
     <t xml:space="preserve">2.46451139450073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41274356842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40904593467712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42013907432556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44787192344666</t>
+    <t xml:space="preserve">2.41274380683899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4090461730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42013931274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44787168502808</t>
   </si>
   <si>
     <t xml:space="preserve">2.47375583648682</t>
@@ -4286,10 +4286,10 @@
     <t xml:space="preserve">2.52737212181091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54216289520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53846549987793</t>
+    <t xml:space="preserve">2.54216313362122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53846526145935</t>
   </si>
   <si>
     <t xml:space="preserve">2.58653521537781</t>
@@ -4298,7 +4298,7 @@
     <t xml:space="preserve">2.56250047683716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59393048286438</t>
+    <t xml:space="preserve">2.59393072128296</t>
   </si>
   <si>
     <t xml:space="preserve">2.63275647163391</t>
@@ -4313,10 +4313,10 @@
     <t xml:space="preserve">2.60132598876953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45711612701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39980173110962</t>
+    <t xml:space="preserve">2.45711588859558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3998019695282</t>
   </si>
   <si>
     <t xml:space="preserve">2.44602274894714</t>
@@ -4328,10 +4328,10 @@
     <t xml:space="preserve">2.47190690040588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47005772590637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42383694648743</t>
+    <t xml:space="preserve">2.47005796432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42383670806885</t>
   </si>
   <si>
     <t xml:space="preserve">2.38316226005554</t>
@@ -4343,34 +4343,34 @@
     <t xml:space="preserve">2.49594187736511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52182579040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5403139591217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55140709877014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57913994789124</t>
+    <t xml:space="preserve">2.52182555198669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54031419754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55140733718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57913970947266</t>
   </si>
   <si>
     <t xml:space="preserve">2.5680468082428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58468627929688</t>
+    <t xml:space="preserve">2.58468651771545</t>
   </si>
   <si>
     <t xml:space="preserve">2.57544207572937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54770970344543</t>
+    <t xml:space="preserve">2.54770946502686</t>
   </si>
   <si>
     <t xml:space="preserve">2.60687255859375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60317468643188</t>
+    <t xml:space="preserve">2.60317492485046</t>
   </si>
   <si>
     <t xml:space="preserve">2.6456983089447</t>
@@ -4394,7 +4394,7 @@
     <t xml:space="preserve">2.667884349823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69376826286316</t>
+    <t xml:space="preserve">2.69376850128174</t>
   </si>
   <si>
     <t xml:space="preserve">2.56434917449951</t>
@@ -4427,22 +4427,22 @@
     <t xml:space="preserve">2.35358071327209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39795327186584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41089487075806</t>
+    <t xml:space="preserve">2.39795303344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41089510917664</t>
   </si>
   <si>
     <t xml:space="preserve">2.42753434181213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40534853935242</t>
+    <t xml:space="preserve">2.40534830093384</t>
   </si>
   <si>
     <t xml:space="preserve">2.39240646362305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37206935882568</t>
+    <t xml:space="preserve">2.3720691204071</t>
   </si>
   <si>
     <t xml:space="preserve">2.34988307952881</t>
@@ -4457,7 +4457,7 @@
     <t xml:space="preserve">2.34803414344788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45341825485229</t>
+    <t xml:space="preserve">2.45341849327087</t>
   </si>
   <si>
     <t xml:space="preserve">2.49224424362183</t>
@@ -4469,7 +4469,7 @@
     <t xml:space="preserve">2.49779057502747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4626624584198</t>
+    <t xml:space="preserve">2.46266269683838</t>
   </si>
   <si>
     <t xml:space="preserve">2.45526719093323</t>
@@ -4484,7 +4484,7 @@
     <t xml:space="preserve">2.62536096572876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64015173912048</t>
+    <t xml:space="preserve">2.64015197753906</t>
   </si>
   <si>
     <t xml:space="preserve">2.62720990180969</t>
@@ -4493,19 +4493,19 @@
     <t xml:space="preserve">2.63090753555298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68082642555237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68637299537659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68822193145752</t>
+    <t xml:space="preserve">2.68082666397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68637275695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68822169303894</t>
   </si>
   <si>
     <t xml:space="preserve">2.66603565216064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68267512321472</t>
+    <t xml:space="preserve">2.6826753616333</t>
   </si>
   <si>
     <t xml:space="preserve">2.68452405929565</t>
@@ -4514,19 +4514,19 @@
     <t xml:space="preserve">2.69007062911987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74368691444397</t>
+    <t xml:space="preserve">2.74368715286255</t>
   </si>
   <si>
     <t xml:space="preserve">2.71225690841675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69561719894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73444271087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80100131034851</t>
+    <t xml:space="preserve">2.69561696052551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73444294929504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80100154876709</t>
   </si>
   <si>
     <t xml:space="preserve">2.78990817070007</t>
@@ -4538,7 +4538,7 @@
     <t xml:space="preserve">2.79545474052429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78621077537537</t>
+    <t xml:space="preserve">2.78621053695679</t>
   </si>
   <si>
     <t xml:space="preserve">2.76772212982178</t>
@@ -4550,7 +4550,7 @@
     <t xml:space="preserve">2.75662922859192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73998951911926</t>
+    <t xml:space="preserve">2.73998928070068</t>
   </si>
   <si>
     <t xml:space="preserve">2.74738478660583</t>
@@ -4598,22 +4598,22 @@
     <t xml:space="preserve">2.98033928871155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96924638748169</t>
+    <t xml:space="preserve">2.96924614906311</t>
   </si>
   <si>
     <t xml:space="preserve">3.02286291122437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92672300338745</t>
+    <t xml:space="preserve">2.92672276496887</t>
   </si>
   <si>
     <t xml:space="preserve">2.91562986373901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87495493888855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90083909034729</t>
+    <t xml:space="preserve">2.87495517730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90083885192871</t>
   </si>
   <si>
     <t xml:space="preserve">2.9193274974823</t>
@@ -4640,7 +4640,7 @@
     <t xml:space="preserve">2.99513030052185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98773503303528</t>
+    <t xml:space="preserve">2.9877347946167</t>
   </si>
   <si>
     <t xml:space="preserve">2.98958349227905</t>
@@ -4649,16 +4649,16 @@
     <t xml:space="preserve">2.93411827087402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96000218391418</t>
+    <t xml:space="preserve">2.96000194549561</t>
   </si>
   <si>
     <t xml:space="preserve">2.94890904426575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95445561408997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97849059104919</t>
+    <t xml:space="preserve">2.95445585250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97849035263062</t>
   </si>
   <si>
     <t xml:space="preserve">2.95260691642761</t>
@@ -4682,10 +4682,10 @@
     <t xml:space="preserve">3.08572363853455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09496784210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11900305747986</t>
+    <t xml:space="preserve">3.09496808052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11900281906128</t>
   </si>
   <si>
     <t xml:space="preserve">3.05983972549438</t>
@@ -4703,13 +4703,13 @@
     <t xml:space="preserve">3.06908392906189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02471160888672</t>
+    <t xml:space="preserve">3.0247118473053</t>
   </si>
   <si>
     <t xml:space="preserve">3.01916527748108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97479271888733</t>
+    <t xml:space="preserve">2.97479295730591</t>
   </si>
   <si>
     <t xml:space="preserve">2.92302513122559</t>
@@ -4718,7 +4718,7 @@
     <t xml:space="preserve">2.93781590461731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88419914245605</t>
+    <t xml:space="preserve">2.88419938087463</t>
   </si>
   <si>
     <t xml:space="preserve">2.90823435783386</t>
@@ -4733,19 +4733,19 @@
     <t xml:space="preserve">2.95815324783325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97109532356262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01546740531921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11345624923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13933992385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10975885391235</t>
+    <t xml:space="preserve">2.97109508514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01546764373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11345648765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13934016227722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10975861549377</t>
   </si>
   <si>
     <t xml:space="preserve">3.16337513923645</t>
@@ -4754,7 +4754,7 @@
     <t xml:space="preserve">3.13379383087158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15782833099365</t>
+    <t xml:space="preserve">3.15782856941223</t>
   </si>
   <si>
     <t xml:space="preserve">3.16892170906067</t>
@@ -4763,7 +4763,7 @@
     <t xml:space="preserve">3.19480562210083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24287557601929</t>
+    <t xml:space="preserve">3.24287533760071</t>
   </si>
   <si>
     <t xml:space="preserve">3.20959615707397</t>
@@ -4772,7 +4772,7 @@
     <t xml:space="preserve">3.20589852333069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23548007011414</t>
+    <t xml:space="preserve">3.23548030853271</t>
   </si>
   <si>
     <t xml:space="preserve">3.29464316368103</t>
@@ -4787,10 +4787,10 @@
     <t xml:space="preserve">3.20774745941162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17446804046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12085175514221</t>
+    <t xml:space="preserve">3.17446827888489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12085151672363</t>
   </si>
   <si>
     <t xml:space="preserve">3.07832813262939</t>
@@ -4802,7 +4802,7 @@
     <t xml:space="preserve">3.09866547584534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07647967338562</t>
+    <t xml:space="preserve">3.07647943496704</t>
   </si>
   <si>
     <t xml:space="preserve">3.06723523139954</t>
@@ -4817,19 +4817,19 @@
     <t xml:space="preserve">3.19665431976318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20404982566833</t>
+    <t xml:space="preserve">3.20405006408691</t>
   </si>
   <si>
     <t xml:space="preserve">3.19850325584412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1245493888855</t>
+    <t xml:space="preserve">3.12454962730408</t>
   </si>
   <si>
     <t xml:space="preserve">3.16707301139832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14858412742615</t>
+    <t xml:space="preserve">3.14858436584473</t>
   </si>
   <si>
     <t xml:space="preserve">3.00067663192749</t>
@@ -4838,7 +4838,7 @@
     <t xml:space="preserve">3.04874682426453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10051465034485</t>
+    <t xml:space="preserve">3.10051441192627</t>
   </si>
   <si>
     <t xml:space="preserve">3.14488673210144</t>
@@ -5748,6 +5748,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.07399988174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04400014877319</t>
   </si>
 </sst>
 </file>
@@ -72516,7 +72519,7 @@
     </row>
     <row r="2556">
       <c r="A2556" s="1" t="n">
-        <v>46044.6911574074</v>
+        <v>46044.3333333333</v>
       </c>
       <c r="B2556" t="n">
         <v>4611198</v>
@@ -72537,6 +72540,32 @@
         <v>1804</v>
       </c>
       <c r="H2556" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2557">
+      <c r="A2557" s="1" t="n">
+        <v>46045.6911689815</v>
+      </c>
+      <c r="B2557" t="n">
+        <v>2945702</v>
+      </c>
+      <c r="C2557" t="n">
+        <v>4.08599996566772</v>
+      </c>
+      <c r="D2557" t="n">
+        <v>4.02600002288818</v>
+      </c>
+      <c r="E2557" t="n">
+        <v>4.07200002670288</v>
+      </c>
+      <c r="F2557" t="n">
+        <v>4.04400014877319</v>
+      </c>
+      <c r="G2557" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H2557" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HER.MI.xlsx
+++ b/data/HER.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1913" uniqueCount="1913">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1914" uniqueCount="1914">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70756638050079</t>
+    <t xml:space="preserve">1.70756649971008</t>
   </si>
   <si>
     <t xml:space="preserve">HER.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70896399021149</t>
+    <t xml:space="preserve">1.70896410942078</t>
   </si>
   <si>
     <t xml:space="preserve">1.70616912841797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71036112308502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68800354003906</t>
+    <t xml:space="preserve">1.71036088466644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68800342082977</t>
   </si>
   <si>
     <t xml:space="preserve">1.72573220729828</t>
@@ -62,106 +62,106 @@
     <t xml:space="preserve">1.79140758514404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79420244693756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77044725418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74669229984283</t>
+    <t xml:space="preserve">1.79420220851898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7704473733902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74669253826141</t>
   </si>
   <si>
     <t xml:space="preserve">1.70337426662445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77324235439301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74948716163635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76625549793243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80538129806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79001021385193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80398380756378</t>
+    <t xml:space="preserve">1.77324211597443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74948704242706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76625525951385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80538141727448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79001033306122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80398368835449</t>
   </si>
   <si>
     <t xml:space="preserve">1.83472561836243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81655967235565</t>
+    <t xml:space="preserve">1.81656002998352</t>
   </si>
   <si>
     <t xml:space="preserve">1.80258631706238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8486989736557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85568559169769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84031522274017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82354640960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82913601398468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72852671146393</t>
+    <t xml:space="preserve">1.84869885444641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85568583011627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84031498432159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82354664802551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82913637161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72852659225464</t>
   </si>
   <si>
     <t xml:space="preserve">1.74110305309296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75926864147186</t>
+    <t xml:space="preserve">1.75926828384399</t>
   </si>
   <si>
     <t xml:space="preserve">1.6991822719574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75507640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7955995798111</t>
+    <t xml:space="preserve">1.75507664680481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79559969902039</t>
   </si>
   <si>
     <t xml:space="preserve">1.78302347660065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77603685855865</t>
+    <t xml:space="preserve">1.77603662014008</t>
   </si>
   <si>
     <t xml:space="preserve">1.79839444160461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80118930339813</t>
+    <t xml:space="preserve">1.80118942260742</t>
   </si>
   <si>
     <t xml:space="preserve">1.82075202465057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8305332660675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78861308097839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76485776901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74529469013214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73970544338226</t>
+    <t xml:space="preserve">1.83053350448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7886129617691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76485800743103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74529457092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73970568180084</t>
   </si>
   <si>
     <t xml:space="preserve">1.72992408275604</t>
@@ -170,67 +170,67 @@
     <t xml:space="preserve">1.74389743804932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73271882534027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76346075534821</t>
+    <t xml:space="preserve">1.73271906375885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76346051692963</t>
   </si>
   <si>
     <t xml:space="preserve">1.7788313627243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76066601276398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77463948726654</t>
+    <t xml:space="preserve">1.7606657743454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77463936805725</t>
   </si>
   <si>
     <t xml:space="preserve">1.7969970703125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83752012252808</t>
+    <t xml:space="preserve">1.83752024173737</t>
   </si>
   <si>
     <t xml:space="preserve">1.81097078323364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85708343982697</t>
+    <t xml:space="preserve">1.8570830821991</t>
   </si>
   <si>
     <t xml:space="preserve">1.84310984611511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76765275001526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78162622451782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78721582889557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77743399143219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.780228972435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80817592144012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80957305431366</t>
+    <t xml:space="preserve">1.76765263080597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78162634372711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78721535205841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77743422985077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78022885322571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80817580223083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80957329273224</t>
   </si>
   <si>
     <t xml:space="preserve">1.79280495643616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78442072868347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75647377967834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74808967113495</t>
+    <t xml:space="preserve">1.78442096710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75647389888763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74808979034424</t>
   </si>
   <si>
     <t xml:space="preserve">1.82634162902832</t>
@@ -239,31 +239,31 @@
     <t xml:space="preserve">1.84590435028076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83193075656891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84450709819794</t>
+    <t xml:space="preserve">1.8319308757782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84450745582581</t>
   </si>
   <si>
     <t xml:space="preserve">1.82214939594269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83332824707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82494378089905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81376576423645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76206314563751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73132121562958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74250018596649</t>
+    <t xml:space="preserve">1.83332812786102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82494413852692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81376516819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76206338405609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73132145404816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7425000667572</t>
   </si>
   <si>
     <t xml:space="preserve">1.71175861358643</t>
@@ -275,142 +275,142 @@
     <t xml:space="preserve">1.77344810962677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74012362957001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75895917415619</t>
+    <t xml:space="preserve">1.74012351036072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75895929336548</t>
   </si>
   <si>
     <t xml:space="preserve">1.70390117168427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67347431182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70969653129578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73867452144623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78069257736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83430182933807</t>
+    <t xml:space="preserve">1.6734744310379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70969676971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73867475986481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78069281578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83430206775665</t>
   </si>
   <si>
     <t xml:space="preserve">1.80822145938873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.811119556427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78503942489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77924382686615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72708356380463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76040816307068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7459192276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77055060863495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76620364189148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76185703277588</t>
+    <t xml:space="preserve">1.81111943721771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78503954410553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77924406528473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72708344459534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76040828227997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74591934680939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77055037021637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76620376110077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76185739040375</t>
   </si>
   <si>
     <t xml:space="preserve">1.76910150051117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77489745616913</t>
+    <t xml:space="preserve">1.77489697933197</t>
   </si>
   <si>
     <t xml:space="preserve">1.78359043598175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8371993303299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85748422145844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85023951530457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83575081825256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86617767810822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83140408992767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84444403648376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79663074016571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81981301307678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81256854534149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74881720542908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7444703578949</t>
+    <t xml:space="preserve">1.83719980716705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85748410224915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85023939609528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83575057983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8661777973175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83140385150909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84444415569305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79663062095642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81981289386749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8125684261322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74881684780121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74447047710419</t>
   </si>
   <si>
     <t xml:space="preserve">1.77634596824646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79083502292633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79952824115753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78648829460144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78938639163971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81546592712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75606155395508</t>
+    <t xml:space="preserve">1.79083478450775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79952800273895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78648841381073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78938603401184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8154661655426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7560613155365</t>
   </si>
   <si>
     <t xml:space="preserve">1.73577702045441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70679914951324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73722577095032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7546124458313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71114540100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70824778079987</t>
+    <t xml:space="preserve">1.70679891109467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7372260093689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75461268424988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71114599704742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70824801921844</t>
   </si>
   <si>
     <t xml:space="preserve">1.70245242118835</t>
@@ -419,13 +419,13 @@
     <t xml:space="preserve">1.69231021404266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71694111824036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69665682315826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63145637512207</t>
+    <t xml:space="preserve">1.71694123744965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69665670394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63145661354065</t>
   </si>
   <si>
     <t xml:space="preserve">1.60537660121918</t>
@@ -437,55 +437,55 @@
     <t xml:space="preserve">1.57929623126984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60102987289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60972309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61406993865967</t>
+    <t xml:space="preserve">1.601029753685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6097229719162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61406970024109</t>
   </si>
   <si>
     <t xml:space="preserve">1.62131404876709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63290524482727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61841642856598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63870084285736</t>
+    <t xml:space="preserve">1.63290548324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61841630935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63870096206665</t>
   </si>
   <si>
     <t xml:space="preserve">1.63725197315216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65029215812683</t>
+    <t xml:space="preserve">1.65029203891754</t>
   </si>
   <si>
     <t xml:space="preserve">1.62276303768158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61551880836487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61696743965149</t>
+    <t xml:space="preserve">1.61551856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61696767807007</t>
   </si>
   <si>
     <t xml:space="preserve">1.62566077709198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66188311576843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66912758350372</t>
+    <t xml:space="preserve">1.66188299655914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66912770271301</t>
   </si>
   <si>
     <t xml:space="preserve">1.68796336650848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59378516674042</t>
+    <t xml:space="preserve">1.59378504753113</t>
   </si>
   <si>
     <t xml:space="preserve">1.56625604629517</t>
@@ -497,25 +497,25 @@
     <t xml:space="preserve">1.54307389259338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4604868888855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46338450908661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44599795341492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44527328014374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4503448009491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43006002902985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42209100723267</t>
+    <t xml:space="preserve">1.46048665046692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4633846282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44599783420563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44527339935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45034456253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43005979061127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42209112644196</t>
   </si>
   <si>
     <t xml:space="preserve">1.3960108757019</t>
@@ -524,109 +524,109 @@
     <t xml:space="preserve">1.3945620059967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40905106067657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41267311573029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3981841802597</t>
+    <t xml:space="preserve">1.409050822258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41267335414886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39818429946899</t>
   </si>
   <si>
     <t xml:space="preserve">1.40180647373199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.405428647995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41629564762115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38152194023132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35906410217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37717545032501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43875336647034</t>
+    <t xml:space="preserve">1.40542876720428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41629540920258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38152182102203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35906422138214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37717521190643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43875312805176</t>
   </si>
   <si>
     <t xml:space="preserve">1.48077130317688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49236261844635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48511815071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53293144702911</t>
+    <t xml:space="preserve">1.49236238002777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48511791229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5329315662384</t>
   </si>
   <si>
     <t xml:space="preserve">1.52713596820831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50105571746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50685131549835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54886937141418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55756282806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57060289382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5908876657486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56915390491486</t>
+    <t xml:space="preserve">1.50105595588684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50685143470764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54886949062347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55756294727325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57060277462006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59088730812073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56915378570557</t>
   </si>
   <si>
     <t xml:space="preserve">1.58798968791962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.608274102211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5966831445694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59958064556122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56480729579926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65174090862274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64159882068634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65319001674652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65463852882385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65898537635803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64014971256256</t>
+    <t xml:space="preserve">1.60827422142029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59668290615082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59958076477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56480753421783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65174102783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64159893989563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65318977832794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65463876724243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65898561477661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64014983177185</t>
   </si>
   <si>
     <t xml:space="preserve">1.64304745197296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57494962215424</t>
+    <t xml:space="preserve">1.57494950294495</t>
   </si>
   <si>
     <t xml:space="preserve">1.57784724235535</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">1.55176723003387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58654081821442</t>
+    <t xml:space="preserve">1.58654069900513</t>
   </si>
   <si>
     <t xml:space="preserve">1.63000750541687</t>
@@ -647,64 +647,64 @@
     <t xml:space="preserve">1.66622996330261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67782115936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69086134433746</t>
+    <t xml:space="preserve">1.67782127857208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69086110591888</t>
   </si>
   <si>
     <t xml:space="preserve">1.69375920295715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69810605049133</t>
+    <t xml:space="preserve">1.69810569286346</t>
   </si>
   <si>
     <t xml:space="preserve">1.69520771503448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71404349803925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72998118400574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73432779312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71983909606934</t>
+    <t xml:space="preserve">1.71404337882996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72998130321503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73432815074921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7198394536972</t>
   </si>
   <si>
     <t xml:space="preserve">1.72418570518494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71549212932587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71839022636414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74157249927521</t>
+    <t xml:space="preserve">1.71549236774445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71839010715485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7415726184845</t>
   </si>
   <si>
     <t xml:space="preserve">1.78214180469513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78793704509735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8140172958374</t>
+    <t xml:space="preserve">1.78793728351593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81401741504669</t>
   </si>
   <si>
     <t xml:space="preserve">1.82995498180389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86907529830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89950215816498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91399109363556</t>
+    <t xml:space="preserve">1.86907541751862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8995019197464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91399097442627</t>
   </si>
   <si>
     <t xml:space="preserve">1.91543984413147</t>
@@ -713,91 +713,91 @@
     <t xml:space="preserve">1.8806666135788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8719733953476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88935995101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90095067024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90529751777649</t>
+    <t xml:space="preserve">1.87197315692902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88935983181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90095090866089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90529763698578</t>
   </si>
   <si>
     <t xml:space="preserve">1.91254222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94441819190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93717312812805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87921786308289</t>
+    <t xml:space="preserve">1.94441783428192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93717348575592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8792177438736</t>
   </si>
   <si>
     <t xml:space="preserve">1.88356423377991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92847967147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89805316925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88791108131409</t>
+    <t xml:space="preserve">1.92848002910614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89805328845978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88791084289551</t>
   </si>
   <si>
     <t xml:space="preserve">1.90240001678467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91688895225525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92413318157196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93572473526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93862211704254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9487646818161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99512934684753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02845406532288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05743169784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06902265548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05163669586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10234761238098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06467604637146</t>
+    <t xml:space="preserve">1.91688871383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92413330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93572437763214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93862247467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94876456260681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99512887001038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0284538269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05743193626404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06902313232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05163621902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10234713554382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06467628479004</t>
   </si>
   <si>
     <t xml:space="preserve">2.0385959148407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07336950302124</t>
+    <t xml:space="preserve">2.07336974143982</t>
   </si>
   <si>
     <t xml:space="preserve">2.08640956878662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12842750549316</t>
+    <t xml:space="preserve">2.12842774391174</t>
   </si>
   <si>
     <t xml:space="preserve">2.11248970031738</t>
@@ -806,10 +806,10 @@
     <t xml:space="preserve">2.11104106903076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10089874267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05453372001648</t>
+    <t xml:space="preserve">2.1008985042572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05453395843506</t>
   </si>
   <si>
     <t xml:space="preserve">2.0893075466156</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">2.12263226509094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0791654586792</t>
+    <t xml:space="preserve">2.07916498184204</t>
   </si>
   <si>
     <t xml:space="preserve">2.1037962436676</t>
@@ -830,10 +830,10 @@
     <t xml:space="preserve">2.10814332962036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14726328849792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13277411460876</t>
+    <t xml:space="preserve">2.1472635269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13277435302734</t>
   </si>
   <si>
     <t xml:space="preserve">2.15450763702393</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">2.14291644096375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15595674514771</t>
+    <t xml:space="preserve">2.15595650672913</t>
   </si>
   <si>
     <t xml:space="preserve">2.16790914535522</t>
@@ -857,55 +857,55 @@
     <t xml:space="preserve">2.09918165206909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11262845993042</t>
+    <t xml:space="preserve">2.112628698349</t>
   </si>
   <si>
     <t xml:space="preserve">2.07228803634644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05884146690369</t>
+    <t xml:space="preserve">2.05884170532227</t>
   </si>
   <si>
     <t xml:space="preserve">2.01700758934021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99907863140106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01103067398071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00804281234741</t>
+    <t xml:space="preserve">1.99907851219177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01103091239929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00804305076599</t>
   </si>
   <si>
     <t xml:space="preserve">1.99758434295654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95126783847809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97069084644318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00505447387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98264372348785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0304536819458</t>
+    <t xml:space="preserve">1.95126736164093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97069048881531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00505471229553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98264348506927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03045415878296</t>
   </si>
   <si>
     <t xml:space="preserve">2.05286526679993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0394184589386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03194785118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04539489746094</t>
+    <t xml:space="preserve">2.03941869735718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03194808959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04539465904236</t>
   </si>
   <si>
     <t xml:space="preserve">2.0244779586792</t>
@@ -914,16 +914,16 @@
     <t xml:space="preserve">2.06182956695557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0767707824707</t>
+    <t xml:space="preserve">2.07677030563354</t>
   </si>
   <si>
     <t xml:space="preserve">2.03344202041626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01401901245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05435943603516</t>
+    <t xml:space="preserve">2.01401925086975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05435919761658</t>
   </si>
   <si>
     <t xml:space="preserve">2.04390072822571</t>
@@ -941,22 +941,22 @@
     <t xml:space="preserve">2.04987716674805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00206637382507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05585360527039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03493618965149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99459624290466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.975172996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96172630786896</t>
+    <t xml:space="preserve">2.00206661224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05585312843323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03493642807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99459600448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97517311573029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96172642707825</t>
   </si>
   <si>
     <t xml:space="preserve">1.96770286560059</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">2.02597212791443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01252508163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00953722000122</t>
+    <t xml:space="preserve">2.01252484321594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00953698158264</t>
   </si>
   <si>
     <t xml:space="preserve">2.00356030464172</t>
@@ -983,61 +983,61 @@
     <t xml:space="preserve">2.00057244300842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98563170433044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98712587356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97218501567841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02148985862732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03792452812195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06033539772034</t>
+    <t xml:space="preserve">1.98563158512115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98712599277496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97218489646912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02148962020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03792405128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06033563613892</t>
   </si>
   <si>
     <t xml:space="preserve">2.07079434394836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07378244400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06631207466125</t>
+    <t xml:space="preserve">2.07378220558167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06631183624268</t>
   </si>
   <si>
     <t xml:space="preserve">2.0633237361908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07527637481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08424115180969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10665202140808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12458109855652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14998030662537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16043925285339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18135619163513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19629669189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18733263015747</t>
+    <t xml:space="preserve">2.07527613639832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08424091339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10665225982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1245813369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14998078346252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16043877601624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18135595321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19629693031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18733215332031</t>
   </si>
   <si>
     <t xml:space="preserve">2.1798620223999</t>
@@ -1046,34 +1046,34 @@
     <t xml:space="preserve">2.16641521453857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1708972454071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19181489944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19330859184265</t>
+    <t xml:space="preserve">2.17089748382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.191814661026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19330906867981</t>
   </si>
   <si>
     <t xml:space="preserve">2.19480276107788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22468400001526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27100110054016</t>
+    <t xml:space="preserve">2.22468423843384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.271000623703</t>
   </si>
   <si>
     <t xml:space="preserve">2.2560601234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25904822349548</t>
+    <t xml:space="preserve">2.2590479850769</t>
   </si>
   <si>
     <t xml:space="preserve">2.28145956993103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2949059009552</t>
+    <t xml:space="preserve">2.29490637779236</t>
   </si>
   <si>
     <t xml:space="preserve">2.30536484718323</t>
@@ -1082,127 +1082,127 @@
     <t xml:space="preserve">2.30088233947754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33972859382629</t>
+    <t xml:space="preserve">2.33972883224487</t>
   </si>
   <si>
     <t xml:space="preserve">2.28892970085144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27398920059204</t>
+    <t xml:space="preserve">2.27398896217346</t>
   </si>
   <si>
     <t xml:space="preserve">2.303870677948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31582307815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25456571578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25755429267883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27847146987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22916650772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22617793083191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21870803833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17388582229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15446281433105</t>
+    <t xml:space="preserve">2.31582355499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25456595420837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25755405426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27847123146057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22916674613953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22617816925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21870827674866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17388558387756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15446257591248</t>
   </si>
   <si>
     <t xml:space="preserve">2.21123790740967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26054239273071</t>
+    <t xml:space="preserve">2.26054215431213</t>
   </si>
   <si>
     <t xml:space="preserve">2.31134104728699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2411196231842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26950693130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23813104629517</t>
+    <t xml:space="preserve">2.24111938476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26950669288635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23813128471375</t>
   </si>
   <si>
     <t xml:space="preserve">2.27697730064392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28594160079956</t>
+    <t xml:space="preserve">2.28594136238098</t>
   </si>
   <si>
     <t xml:space="preserve">2.29938840866089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24709558486938</t>
+    <t xml:space="preserve">2.24709534645081</t>
   </si>
   <si>
     <t xml:space="preserve">2.2799654006958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24560189247131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18434453010559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13503980636597</t>
+    <t xml:space="preserve">2.24560117721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18434429168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13503956794739</t>
   </si>
   <si>
     <t xml:space="preserve">2.11113452911377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05734753608704</t>
+    <t xml:space="preserve">2.05734705924988</t>
   </si>
   <si>
     <t xml:space="preserve">2.02896022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09469962120056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12607502937317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13354516029358</t>
+    <t xml:space="preserve">2.09469938278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12607526779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13354563713074</t>
   </si>
   <si>
     <t xml:space="preserve">2.09320545196533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06929993629456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04091238975525</t>
+    <t xml:space="preserve">2.06930017471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04091286659241</t>
   </si>
   <si>
     <t xml:space="preserve">2.08573508262634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08274698257446</t>
+    <t xml:space="preserve">2.08274674415588</t>
   </si>
   <si>
     <t xml:space="preserve">2.08125281333923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10216999053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09768748283386</t>
+    <t xml:space="preserve">2.10216975212097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09768795967102</t>
   </si>
   <si>
     <t xml:space="preserve">2.12009882926941</t>
@@ -1214,25 +1214,25 @@
     <t xml:space="preserve">2.22169613838196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23066091537476</t>
+    <t xml:space="preserve">2.23066067695618</t>
   </si>
   <si>
     <t xml:space="preserve">2.24261355400085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26353025436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23514270782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25307202339172</t>
+    <t xml:space="preserve">2.26353049278259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23514294624329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25307178497314</t>
   </si>
   <si>
     <t xml:space="preserve">2.29341173171997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29789423942566</t>
+    <t xml:space="preserve">2.29789400100708</t>
   </si>
   <si>
     <t xml:space="preserve">2.28444766998291</t>
@@ -1241,19 +1241,19 @@
     <t xml:space="preserve">2.2276725769043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25157761573792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14101576805115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12159276008606</t>
+    <t xml:space="preserve">2.25157785415649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14101600646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12159299850464</t>
   </si>
   <si>
     <t xml:space="preserve">2.02298355102539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94678544998169</t>
+    <t xml:space="preserve">1.94678556919098</t>
   </si>
   <si>
     <t xml:space="preserve">1.96471452713013</t>
@@ -1262,13 +1262,13 @@
     <t xml:space="preserve">1.98114955425262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96919667720795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97816109657288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94827961921692</t>
+    <t xml:space="preserve">1.96919679641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97816121578217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94827973842621</t>
   </si>
   <si>
     <t xml:space="preserve">2.02856683731079</t>
@@ -1277,19 +1277,19 @@
     <t xml:space="preserve">2.06108593940735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07192540168762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03785824775696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04095506668091</t>
+    <t xml:space="preserve">2.0719256401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03785800933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04095482826233</t>
   </si>
   <si>
     <t xml:space="preserve">2.07347393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0595371723175</t>
+    <t xml:space="preserve">2.05953741073608</t>
   </si>
   <si>
     <t xml:space="preserve">2.08895921707153</t>
@@ -1298,10 +1298,10 @@
     <t xml:space="preserve">2.06727981567383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10599303245544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13541507720947</t>
+    <t xml:space="preserve">2.10599327087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13541483879089</t>
   </si>
   <si>
     <t xml:space="preserve">2.15399742126465</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">2.16019129753113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14470601081848</t>
+    <t xml:space="preserve">2.14470624923706</t>
   </si>
   <si>
     <t xml:space="preserve">2.13696336746216</t>
@@ -1319,73 +1319,73 @@
     <t xml:space="preserve">2.14780306816101</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13386654853821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16793370246887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17257928848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15244889259338</t>
+    <t xml:space="preserve">2.13386631011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16793394088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17257952690125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15244841575623</t>
   </si>
   <si>
     <t xml:space="preserve">2.10444450378418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09205651283264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20664668083191</t>
+    <t xml:space="preserve">2.09205603599548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20664691925049</t>
   </si>
   <si>
     <t xml:space="preserve">2.17103099822998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19580745697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18651652336121</t>
+    <t xml:space="preserve">2.19580698013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18651604652405</t>
   </si>
   <si>
     <t xml:space="preserve">2.21748685836792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21593809127808</t>
+    <t xml:space="preserve">2.21593832969666</t>
   </si>
   <si>
     <t xml:space="preserve">2.1834192276001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16328859329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15090036392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13231778144836</t>
+    <t xml:space="preserve">2.16328835487366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15090012550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13231754302979</t>
   </si>
   <si>
     <t xml:space="preserve">2.12612390518188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11993002891541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16638541221619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15709447860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14935183525085</t>
+    <t xml:space="preserve">2.11992955207825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16638565063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15709400177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14935159683228</t>
   </si>
   <si>
     <t xml:space="preserve">2.09670186042786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09979891777039</t>
+    <t xml:space="preserve">2.09979915618896</t>
   </si>
   <si>
     <t xml:space="preserve">2.09050798416138</t>
@@ -1397,16 +1397,16 @@
     <t xml:space="preserve">2.12457513809204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12767243385315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18806457519531</t>
+    <t xml:space="preserve">2.12767219543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18806481361389</t>
   </si>
   <si>
     <t xml:space="preserve">2.20045304298401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1973557472229</t>
+    <t xml:space="preserve">2.19735598564148</t>
   </si>
   <si>
     <t xml:space="preserve">2.20200157165527</t>
@@ -1421,13 +1421,13 @@
     <t xml:space="preserve">2.1756763458252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12147831916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11683249473572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07657098770142</t>
+    <t xml:space="preserve">2.12147808074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1168327331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07657074928284</t>
   </si>
   <si>
     <t xml:space="preserve">2.06882834434509</t>
@@ -1436,97 +1436,97 @@
     <t xml:space="preserve">2.05179452896118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01462984085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96197998523712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98211109638214</t>
+    <t xml:space="preserve">2.01463007926941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96197986602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98211085796356</t>
   </si>
   <si>
     <t xml:space="preserve">1.93720376491547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90313625335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86287462711334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91552448272705</t>
+    <t xml:space="preserve">1.90313649177551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86287486553192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91552424430847</t>
   </si>
   <si>
     <t xml:space="preserve">1.87216579914093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89384520053864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90158796310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87061715126038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85977745056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92791259288788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89694225788116</t>
+    <t xml:space="preserve">1.89384531974792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90158808231354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87061703205109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85977756977081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92791283130646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89694213867188</t>
   </si>
   <si>
     <t xml:space="preserve">1.89074802398682</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87990832328796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88919949531555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88765108585358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90468502044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9217187166214</t>
+    <t xml:space="preserve">1.87990844249725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88919961452484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88765096664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90468490123749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92171859741211</t>
   </si>
   <si>
     <t xml:space="preserve">1.96662569046021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91862165927887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97901403903961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96972298622131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97746515274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94184947013855</t>
+    <t xml:space="preserve">1.91862142086029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9790141582489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96972286701202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97746527194977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94184923171997</t>
   </si>
   <si>
     <t xml:space="preserve">1.93100965023041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92481589317322</t>
+    <t xml:space="preserve">1.92481553554535</t>
   </si>
   <si>
     <t xml:space="preserve">1.92017018795013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89229679107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90933072566986</t>
+    <t xml:space="preserve">1.89229667186737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90933060646057</t>
   </si>
   <si>
     <t xml:space="preserve">1.87836003303528</t>
@@ -1538,13 +1538,13 @@
     <t xml:space="preserve">1.8690687417984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9480437040329</t>
+    <t xml:space="preserve">1.94804382324219</t>
   </si>
   <si>
     <t xml:space="preserve">1.98675656318665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09360456466675</t>
+    <t xml:space="preserve">2.09360480308533</t>
   </si>
   <si>
     <t xml:space="preserve">2.03630948066711</t>
@@ -1556,73 +1556,73 @@
     <t xml:space="preserve">2.0982506275177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08276534080505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19116163253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19425868988037</t>
+    <t xml:space="preserve">2.08276510238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19116187095642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19425892829895</t>
   </si>
   <si>
     <t xml:space="preserve">2.1787736415863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20509839057922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2097442150116</t>
+    <t xml:space="preserve">2.2050986289978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20974445343018</t>
   </si>
   <si>
     <t xml:space="preserve">2.22987508773804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20354986190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19890427589417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22677779197693</t>
+    <t xml:space="preserve">2.20355010032654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19890451431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22677755355835</t>
   </si>
   <si>
     <t xml:space="preserve">2.26084542274475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26239395141602</t>
+    <t xml:space="preserve">2.26239371299744</t>
   </si>
   <si>
     <t xml:space="preserve">2.28562164306641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29336428642273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28252482414246</t>
+    <t xml:space="preserve">2.29336476325989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28252458572388</t>
   </si>
   <si>
     <t xml:space="preserve">2.28407335281372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29026746749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27013683319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25619983673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28097629547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30265522003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30110692977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30730128288269</t>
+    <t xml:space="preserve">2.2902672290802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27013635635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25620007514954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28097653388977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30265545845032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30110716819763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30730104446411</t>
   </si>
   <si>
     <t xml:space="preserve">2.29800987243652</t>
@@ -1643,19 +1643,19 @@
     <t xml:space="preserve">2.25465154647827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26858806610107</t>
+    <t xml:space="preserve">2.26858830451965</t>
   </si>
   <si>
     <t xml:space="preserve">2.26549100875854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29955863952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29646134376526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31349515914917</t>
+    <t xml:space="preserve">2.29955887794495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29646158218384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31349539756775</t>
   </si>
   <si>
     <t xml:space="preserve">2.32123780250549</t>
@@ -1664,46 +1664,46 @@
     <t xml:space="preserve">2.25774812698364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23916602134705</t>
+    <t xml:space="preserve">2.23916578292847</t>
   </si>
   <si>
     <t xml:space="preserve">2.34446573257446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38008189201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38163042068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40330958366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4280858039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43118333816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47608995437622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4946722984314</t>
+    <t xml:space="preserve">2.38008165359497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38163018226624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40330982208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42808604240417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4311830997467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4760901927948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49467253684998</t>
   </si>
   <si>
     <t xml:space="preserve">2.49002718925476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49622130393982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50860929489136</t>
+    <t xml:space="preserve">2.49622106552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50860953330994</t>
   </si>
   <si>
     <t xml:space="preserve">2.54887080192566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52099752426147</t>
+    <t xml:space="preserve">2.52099776268005</t>
   </si>
   <si>
     <t xml:space="preserve">2.5024151802063</t>
@@ -1715,34 +1715,34 @@
     <t xml:space="preserve">2.462153673172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47918725013733</t>
+    <t xml:space="preserve">2.47918701171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.46525073051453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43428015708923</t>
+    <t xml:space="preserve">2.43427991867065</t>
   </si>
   <si>
     <t xml:space="preserve">2.44976544380188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45286273956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46679925918579</t>
+    <t xml:space="preserve">2.45286226272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46679878234863</t>
   </si>
   <si>
     <t xml:space="preserve">2.44666838645935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45750784873962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47144436836243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45905661582947</t>
+    <t xml:space="preserve">2.45750761032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47144460678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45905637741089</t>
   </si>
   <si>
     <t xml:space="preserve">2.42653751373291</t>
@@ -1754,7 +1754,7 @@
     <t xml:space="preserve">2.42963433265686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48692989349365</t>
+    <t xml:space="preserve">2.48692965507507</t>
   </si>
   <si>
     <t xml:space="preserve">2.53028845787048</t>
@@ -1763,16 +1763,16 @@
     <t xml:space="preserve">2.53803133964539</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54112839698792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54422545433044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55661368370056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55816173553467</t>
+    <t xml:space="preserve">2.54112815856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54422521591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55661344528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55816221237183</t>
   </si>
   <si>
     <t xml:space="preserve">2.53648257255554</t>
@@ -1784,22 +1784,22 @@
     <t xml:space="preserve">2.5287401676178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51790070533752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56435608863831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59068131446838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60306930541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60461783409119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59997248649597</t>
+    <t xml:space="preserve">2.51790046691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56435632705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5906810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6030695438385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60461807250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59997224807739</t>
   </si>
   <si>
     <t xml:space="preserve">2.60152077674866</t>
@@ -1808,19 +1808,19 @@
     <t xml:space="preserve">2.58913254737854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58603525161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64642810821533</t>
+    <t xml:space="preserve">2.58603549003601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64642786979675</t>
   </si>
   <si>
     <t xml:space="preserve">2.65262198448181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68514108657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7161111831665</t>
+    <t xml:space="preserve">2.68514084815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71611166000366</t>
   </si>
   <si>
     <t xml:space="preserve">2.69698429107666</t>
@@ -1829,58 +1829,58 @@
     <t xml:space="preserve">2.67945051193237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68263816833496</t>
+    <t xml:space="preserve">2.68263840675354</t>
   </si>
   <si>
     <t xml:space="preserve">2.65075898170471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68104434013367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66669893264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7304573059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81174921989441</t>
+    <t xml:space="preserve">2.68104457855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66669869422913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73045706748962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81174945831299</t>
   </si>
   <si>
     <t xml:space="preserve">2.80856156349182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78465175628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77349400520325</t>
+    <t xml:space="preserve">2.7846519947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77349424362183</t>
   </si>
   <si>
     <t xml:space="preserve">2.78305816650391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79740357398987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79580950737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8276891708374</t>
+    <t xml:space="preserve">2.79740381240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79580974578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82768869400024</t>
   </si>
   <si>
     <t xml:space="preserve">2.80696773529053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75914812088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74480295181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74958443641663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7320511341095</t>
+    <t xml:space="preserve">2.75914859771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74480271339417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74958491325378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73205089569092</t>
   </si>
   <si>
     <t xml:space="preserve">2.72886323928833</t>
@@ -1895,16 +1895,16 @@
     <t xml:space="preserve">2.68582630157471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73683285713196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7113299369812</t>
+    <t xml:space="preserve">2.73683309555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71132969856262</t>
   </si>
   <si>
     <t xml:space="preserve">2.69539022445679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70654773712158</t>
+    <t xml:space="preserve">2.70654797554016</t>
   </si>
   <si>
     <t xml:space="preserve">2.72726917266846</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">2.76233673095703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78783965110779</t>
+    <t xml:space="preserve">2.78784012794495</t>
   </si>
   <si>
     <t xml:space="preserve">2.77827620506287</t>
@@ -1931,67 +1931,67 @@
     <t xml:space="preserve">2.78624606132507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81334328651428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88188362121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87869548797607</t>
+    <t xml:space="preserve">2.81334352493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8818838596344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87869572639465</t>
   </si>
   <si>
     <t xml:space="preserve">2.91535663604736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89144730567932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88666534423828</t>
+    <t xml:space="preserve">2.8914475440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88666558265686</t>
   </si>
   <si>
     <t xml:space="preserve">2.88825941085815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91695070266724</t>
+    <t xml:space="preserve">2.91695094108582</t>
   </si>
   <si>
     <t xml:space="preserve">2.89622926712036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80059146881104</t>
+    <t xml:space="preserve">2.80059123039246</t>
   </si>
   <si>
     <t xml:space="preserve">2.79262185096741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84522271156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81812524795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82131314277649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84681630134583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90738677978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90419888496399</t>
+    <t xml:space="preserve">2.84522247314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81812500953674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82131266593933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84681606292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90738725662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90419936180115</t>
   </si>
   <si>
     <t xml:space="preserve">2.86913156509399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95201778411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95042371749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02055811882019</t>
+    <t xml:space="preserve">2.95201802253723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95042395591736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02055835723877</t>
   </si>
   <si>
     <t xml:space="preserve">2.9647696018219</t>
@@ -2000,7 +2000,7 @@
     <t xml:space="preserve">3.00143074989319</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95679998397827</t>
+    <t xml:space="preserve">2.95679974555969</t>
   </si>
   <si>
     <t xml:space="preserve">2.97114539146423</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">3.01577639579773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02215266227722</t>
+    <t xml:space="preserve">3.02215242385864</t>
   </si>
   <si>
     <t xml:space="preserve">3.00461888313293</t>
@@ -2018,10 +2018,10 @@
     <t xml:space="preserve">2.97911524772644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0030243396759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01418256759644</t>
+    <t xml:space="preserve">3.00302457809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01418280601501</t>
   </si>
   <si>
     <t xml:space="preserve">2.98389720916748</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">2.99664878845215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96636366844177</t>
+    <t xml:space="preserve">2.96636343002319</t>
   </si>
   <si>
     <t xml:space="preserve">2.99346113204956</t>
@@ -2045,22 +2045,22 @@
     <t xml:space="preserve">3.04606175422668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05881357192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04924964904785</t>
+    <t xml:space="preserve">3.05881333351135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04924941062927</t>
   </si>
   <si>
     <t xml:space="preserve">3.06997108459473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03012204170227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05403161048889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06678342819214</t>
+    <t xml:space="preserve">3.03012228012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05403137207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06678318977356</t>
   </si>
   <si>
     <t xml:space="preserve">3.05243754386902</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">3.07315897941589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07475328445435</t>
+    <t xml:space="preserve">3.07475304603577</t>
   </si>
   <si>
     <t xml:space="preserve">3.10025644302368</t>
@@ -2078,13 +2078,13 @@
     <t xml:space="preserve">3.17357897758484</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1974880695343</t>
+    <t xml:space="preserve">3.19748830795288</t>
   </si>
   <si>
     <t xml:space="preserve">3.19430017471313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21820974349976</t>
+    <t xml:space="preserve">3.21820998191833</t>
   </si>
   <si>
     <t xml:space="preserve">3.19589447975159</t>
@@ -2093,16 +2093,16 @@
     <t xml:space="preserve">3.16242074966431</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17995476722717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15604519844055</t>
+    <t xml:space="preserve">3.17995452880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15604496002197</t>
   </si>
   <si>
     <t xml:space="preserve">3.18473625183105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17517232894897</t>
+    <t xml:space="preserve">3.17517256736755</t>
   </si>
   <si>
     <t xml:space="preserve">3.19111251831055</t>
@@ -2114,16 +2114,16 @@
     <t xml:space="preserve">3.08750486373901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12416577339172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10185027122498</t>
+    <t xml:space="preserve">3.12416625022888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10185050964355</t>
   </si>
   <si>
     <t xml:space="preserve">3.09547472000122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07156491279602</t>
+    <t xml:space="preserve">3.0715651512146</t>
   </si>
   <si>
     <t xml:space="preserve">3.10344457626343</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">3.11141419410706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0604076385498</t>
+    <t xml:space="preserve">3.06040740013123</t>
   </si>
   <si>
     <t xml:space="preserve">3.12735390663147</t>
@@ -2141,31 +2141,31 @@
     <t xml:space="preserve">3.17198491096497</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16879653930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16401529312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22139739990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16082715988159</t>
+    <t xml:space="preserve">3.1687970161438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16401505470276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22139763832092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16082692146301</t>
   </si>
   <si>
     <t xml:space="preserve">3.16560864448547</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10822606086731</t>
+    <t xml:space="preserve">3.10822653770447</t>
   </si>
   <si>
     <t xml:space="preserve">3.09706854820251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10663223266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08112859725952</t>
+    <t xml:space="preserve">3.10663247108459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0811288356781</t>
   </si>
   <si>
     <t xml:space="preserve">3.07794094085693</t>
@@ -2174,22 +2174,22 @@
     <t xml:space="preserve">3.14329361915588</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18633055686951</t>
+    <t xml:space="preserve">3.18633008003235</t>
   </si>
   <si>
     <t xml:space="preserve">3.18314242362976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13213562965393</t>
+    <t xml:space="preserve">3.13213586807251</t>
   </si>
   <si>
     <t xml:space="preserve">3.27240419387817</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37760591506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31384706497192</t>
+    <t xml:space="preserve">3.377605676651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31384754180908</t>
   </si>
   <si>
     <t xml:space="preserve">3.44774055480957</t>
@@ -2204,10 +2204,10 @@
     <t xml:space="preserve">3.26921653747559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27718639373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28675007820129</t>
+    <t xml:space="preserve">3.27718615531921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28674983978271</t>
   </si>
   <si>
     <t xml:space="preserve">3.33297491073608</t>
@@ -2219,25 +2219,25 @@
     <t xml:space="preserve">3.38557577133179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40948510169983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42701864242554</t>
+    <t xml:space="preserve">3.40948486328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42701888084412</t>
   </si>
   <si>
     <t xml:space="preserve">3.43977046012878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47802567481995</t>
+    <t xml:space="preserve">3.47802495956421</t>
   </si>
   <si>
     <t xml:space="preserve">3.45252180099487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45730400085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47005605697632</t>
+    <t xml:space="preserve">3.45730423927307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47005581855774</t>
   </si>
   <si>
     <t xml:space="preserve">3.55612945556641</t>
@@ -2246,22 +2246,22 @@
     <t xml:space="preserve">3.5370020866394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51628088951111</t>
+    <t xml:space="preserve">3.51628065109253</t>
   </si>
   <si>
     <t xml:space="preserve">3.339350938797</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30906558036804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33775663375854</t>
+    <t xml:space="preserve">3.30906534194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33775687217712</t>
   </si>
   <si>
     <t xml:space="preserve">3.27877998352051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0906925201416</t>
+    <t xml:space="preserve">3.09069228172302</t>
   </si>
   <si>
     <t xml:space="preserve">3.11300802230835</t>
@@ -2273,79 +2273,79 @@
     <t xml:space="preserve">2.83247065544128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6587290763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69060778617859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2203893661499</t>
+    <t xml:space="preserve">2.65872883796692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69060826301575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22038912773132</t>
   </si>
   <si>
     <t xml:space="preserve">2.55830907821655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46585965156555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51049065589905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5168662071228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46107769012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58381271362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44195008277893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41804051399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44035625457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50252079963684</t>
+    <t xml:space="preserve">2.46585941314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51049017906189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51686644554138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46107745170593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58381295204163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44194984436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41804027557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44035601615906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50252056121826</t>
   </si>
   <si>
     <t xml:space="preserve">2.62206768989563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60453391075134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52802419662476</t>
+    <t xml:space="preserve">2.60453414916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52802395820618</t>
   </si>
   <si>
     <t xml:space="preserve">2.56468510627747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53121209144592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55193305015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45948362350464</t>
+    <t xml:space="preserve">2.53121185302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55193328857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45948386192322</t>
   </si>
   <si>
     <t xml:space="preserve">2.57584285736084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56787276268005</t>
+    <t xml:space="preserve">2.56787300109863</t>
   </si>
   <si>
     <t xml:space="preserve">2.54715204238892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54396343231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60772228240967</t>
+    <t xml:space="preserve">2.54396367073059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60772204399109</t>
   </si>
   <si>
     <t xml:space="preserve">2.62047386169434</t>
@@ -2354,13 +2354,13 @@
     <t xml:space="preserve">2.51846051216125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59018850326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58062481880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67307472229004</t>
+    <t xml:space="preserve">2.59018874168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5806245803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67307448387146</t>
   </si>
   <si>
     <t xml:space="preserve">2.69220232963562</t>
@@ -2369,10 +2369,10 @@
     <t xml:space="preserve">2.57903075218201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57265496253967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52483630180359</t>
+    <t xml:space="preserve">2.57265520095825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52483606338501</t>
   </si>
   <si>
     <t xml:space="preserve">2.49295687675476</t>
@@ -2384,22 +2384,22 @@
     <t xml:space="preserve">2.61887979507446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56149697303772</t>
+    <t xml:space="preserve">2.5614972114563</t>
   </si>
   <si>
     <t xml:space="preserve">2.47542333602905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46267151832581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51367831230164</t>
+    <t xml:space="preserve">2.46267127990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51367807388306</t>
   </si>
   <si>
     <t xml:space="preserve">2.50092649459839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55352759361267</t>
+    <t xml:space="preserve">2.55352735519409</t>
   </si>
   <si>
     <t xml:space="preserve">2.54874539375305</t>
@@ -2408,19 +2408,19 @@
     <t xml:space="preserve">2.65713500976562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66032266616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85159850120544</t>
+    <t xml:space="preserve">2.66032290458679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85159826278687</t>
   </si>
   <si>
     <t xml:space="preserve">2.85638022422791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81653094291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77668213844299</t>
+    <t xml:space="preserve">2.81653118133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77668190002441</t>
   </si>
   <si>
     <t xml:space="preserve">2.6778564453125</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">2.75755453109741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75436687469482</t>
+    <t xml:space="preserve">2.75436639785767</t>
   </si>
   <si>
     <t xml:space="preserve">2.68901419639587</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">2.70335984230042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70017170906067</t>
+    <t xml:space="preserve">2.70017218589783</t>
   </si>
   <si>
     <t xml:space="preserve">2.72567534446716</t>
@@ -2471,34 +2471,37 @@
     <t xml:space="preserve">2.63372492790222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67477416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63865041732788</t>
+    <t xml:space="preserve">2.6747739315033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63865089416504</t>
   </si>
   <si>
     <t xml:space="preserve">2.65014481544495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69447803497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73060131072998</t>
+    <t xml:space="preserve">2.69447779655457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7306010723114</t>
   </si>
   <si>
     <t xml:space="preserve">2.73388528823853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73552703857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76508283615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66163849830627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61894702911377</t>
+    <t xml:space="preserve">2.7355272769928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76508259773254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72567510604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66163873672485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61894726753235</t>
   </si>
   <si>
     <t xml:space="preserve">2.63536667823792</t>
@@ -2507,19 +2510,19 @@
     <t xml:space="preserve">2.70268774032593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68791007995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59267544746399</t>
+    <t xml:space="preserve">2.68790984153748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59267568588257</t>
   </si>
   <si>
     <t xml:space="preserve">2.61073732376099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60252737998962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59595918655396</t>
+    <t xml:space="preserve">2.6025276184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59595942497253</t>
   </si>
   <si>
     <t xml:space="preserve">2.58774948120117</t>
@@ -2534,16 +2537,16 @@
     <t xml:space="preserve">2.78642845153809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77657675743103</t>
+    <t xml:space="preserve">2.77657651901245</t>
   </si>
   <si>
     <t xml:space="preserve">2.75851488113403</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66656446456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70925545692444</t>
+    <t xml:space="preserve">2.66656422615051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70925569534302</t>
   </si>
   <si>
     <t xml:space="preserve">2.68298387527466</t>
@@ -2567,37 +2570,37 @@
     <t xml:space="preserve">2.62879872322083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6156632900238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69283556938171</t>
+    <t xml:space="preserve">2.61566305160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69283604621887</t>
   </si>
   <si>
     <t xml:space="preserve">2.59760141372681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64850282669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64029312133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68134212493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66492223739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67970037460327</t>
+    <t xml:space="preserve">2.64850258827209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64029288291931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68134236335754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66492247581482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67969989776611</t>
   </si>
   <si>
     <t xml:space="preserve">2.69776177406311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71253943443298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63700866699219</t>
+    <t xml:space="preserve">2.71253967285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63700842857361</t>
   </si>
   <si>
     <t xml:space="preserve">2.62387347221375</t>
@@ -2615,7 +2618,7 @@
     <t xml:space="preserve">2.54998421669006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55819368362427</t>
+    <t xml:space="preserve">2.55819392204285</t>
   </si>
   <si>
     <t xml:space="preserve">2.54505848884583</t>
@@ -2627,7 +2630,7 @@
     <t xml:space="preserve">2.52042841911316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50236701965332</t>
+    <t xml:space="preserve">2.5023672580719</t>
   </si>
   <si>
     <t xml:space="preserve">2.472811460495</t>
@@ -2636,7 +2639,7 @@
     <t xml:space="preserve">2.42191052436829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44325613975525</t>
+    <t xml:space="preserve">2.44325590133667</t>
   </si>
   <si>
     <t xml:space="preserve">2.35951542854309</t>
@@ -2657,37 +2660,37 @@
     <t xml:space="preserve">2.37593507766724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37757682800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31518197059631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29219460487366</t>
+    <t xml:space="preserve">2.37757658958435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31518220901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29219436645508</t>
   </si>
   <si>
     <t xml:space="preserve">2.2347252368927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19695997238159</t>
+    <t xml:space="preserve">2.19696021080017</t>
   </si>
   <si>
     <t xml:space="preserve">2.21666383743286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23636722564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25442910194397</t>
+    <t xml:space="preserve">2.23636746406555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25442934036255</t>
   </si>
   <si>
     <t xml:space="preserve">2.3102560043335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30533027648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28070068359375</t>
+    <t xml:space="preserve">2.30533051490784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28070044517517</t>
   </si>
   <si>
     <t xml:space="preserve">2.45474982261658</t>
@@ -2696,25 +2699,25 @@
     <t xml:space="preserve">2.42519426345825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44982361793518</t>
+    <t xml:space="preserve">2.44982385635376</t>
   </si>
   <si>
     <t xml:space="preserve">2.49251508712769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47937941551208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56147813796997</t>
+    <t xml:space="preserve">2.47937965393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56147789955139</t>
   </si>
   <si>
     <t xml:space="preserve">2.50893473625183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49579882621765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50400876998901</t>
+    <t xml:space="preserve">2.49579906463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50400900840759</t>
   </si>
   <si>
     <t xml:space="preserve">2.48102140426636</t>
@@ -2723,13 +2726,13 @@
     <t xml:space="preserve">2.47609543800354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52207064628601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53520655632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5122184753418</t>
+    <t xml:space="preserve">2.52207088470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53520631790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51221871376038</t>
   </si>
   <si>
     <t xml:space="preserve">2.47116947174072</t>
@@ -2738,7 +2741,7 @@
     <t xml:space="preserve">2.43997192382812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46788573265076</t>
+    <t xml:space="preserve">2.46788549423218</t>
   </si>
   <si>
     <t xml:space="preserve">2.44489789009094</t>
@@ -2747,46 +2750,46 @@
     <t xml:space="preserve">2.43012022972107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41534209251404</t>
+    <t xml:space="preserve">2.4153425693512</t>
   </si>
   <si>
     <t xml:space="preserve">2.38907098770142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36444115638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39399647712708</t>
+    <t xml:space="preserve">2.36444139480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39399671554565</t>
   </si>
   <si>
     <t xml:space="preserve">2.3660831451416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40384864807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45146584510803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33981132507324</t>
+    <t xml:space="preserve">2.40384840965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45146560668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33981156349182</t>
   </si>
   <si>
     <t xml:space="preserve">2.38742876052856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45310759544373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45967578887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44653987884521</t>
+    <t xml:space="preserve">2.4531078338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45967602729797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44653964042664</t>
   </si>
   <si>
     <t xml:space="preserve">2.50565099716187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44161367416382</t>
+    <t xml:space="preserve">2.4416139125824</t>
   </si>
   <si>
     <t xml:space="preserve">2.49087309837341</t>
@@ -2801,25 +2804,25 @@
     <t xml:space="preserve">2.5417742729187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38086128234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33652758598328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35787343978882</t>
+    <t xml:space="preserve">2.38086104393005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33652782440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35787320137024</t>
   </si>
   <si>
     <t xml:space="preserve">2.36772537231445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32995986938477</t>
+    <t xml:space="preserve">2.32995963096619</t>
   </si>
   <si>
     <t xml:space="preserve">2.46952748298645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49415731430054</t>
+    <t xml:space="preserve">2.49415707588196</t>
   </si>
   <si>
     <t xml:space="preserve">2.55326843261719</t>
@@ -2828,28 +2831,28 @@
     <t xml:space="preserve">2.51057696342468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52371287345886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55491018295288</t>
+    <t xml:space="preserve">2.52371263504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55491042137146</t>
   </si>
   <si>
     <t xml:space="preserve">2.58939146995544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5467004776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53684854507446</t>
+    <t xml:space="preserve">2.54670023918152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53684830665588</t>
   </si>
   <si>
     <t xml:space="preserve">2.52535462379456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43176198005676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40220665931702</t>
+    <t xml:space="preserve">2.43176221847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4022068977356</t>
   </si>
   <si>
     <t xml:space="preserve">2.52863836288452</t>
@@ -2864,10 +2867,10 @@
     <t xml:space="preserve">2.6041693687439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71582341194153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68216300010681</t>
+    <t xml:space="preserve">2.71582365036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68216323852539</t>
   </si>
   <si>
     <t xml:space="preserve">2.72895932197571</t>
@@ -2882,7 +2885,7 @@
     <t xml:space="preserve">2.71171855926514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73224306106567</t>
+    <t xml:space="preserve">2.73224329948425</t>
   </si>
   <si>
     <t xml:space="preserve">2.76918745040894</t>
@@ -2894,112 +2897,112 @@
     <t xml:space="preserve">2.75440979003906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75523066520691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75605154037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74620008468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79381704330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76261973381042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7667248249054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79710149765015</t>
+    <t xml:space="preserve">2.75523090362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75605177879333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7461998462677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79381728172302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.762619972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76672458648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79710125923157</t>
   </si>
   <si>
     <t xml:space="preserve">2.83815050125122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77082967758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77247166633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7642617225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86278009414673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83240342140198</t>
+    <t xml:space="preserve">2.77082991600037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77247190475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76426148414612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86278033256531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83240389823914</t>
   </si>
   <si>
     <t xml:space="preserve">2.82255172729492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86031723022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87837862968445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88330507278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88740968704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88248372077942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86524295806885</t>
+    <t xml:space="preserve">2.86031699180603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87837910652161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88330483436584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88740992546082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.882483959198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86524271965027</t>
   </si>
   <si>
     <t xml:space="preserve">2.86113810539246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86606383323669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86360120773315</t>
+    <t xml:space="preserve">2.86606407165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86360096931458</t>
   </si>
   <si>
     <t xml:space="preserve">2.87427377700806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89726161956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93256402015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95883536338806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97197103500366</t>
+    <t xml:space="preserve">2.89726138114929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93256378173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95883560180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97197127342224</t>
   </si>
   <si>
     <t xml:space="preserve">3.02533531188965</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00481057167053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00809502601624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04093408584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01794672012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04586029052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02123022079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00727367401123</t>
+    <t xml:space="preserve">3.00481081008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00809478759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04093432426453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01794695854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04586005210876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02123045921326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00727391242981</t>
   </si>
   <si>
     <t xml:space="preserve">2.98921203613281</t>
@@ -3008,16 +3011,16 @@
     <t xml:space="preserve">2.95801448822021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90218734741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92353343963623</t>
+    <t xml:space="preserve">2.90218758583069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92353296279907</t>
   </si>
   <si>
     <t xml:space="preserve">2.89561939239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8906934261322</t>
+    <t xml:space="preserve">2.89069366455078</t>
   </si>
   <si>
     <t xml:space="preserve">2.89151477813721</t>
@@ -3035,13 +3038,13 @@
     <t xml:space="preserve">2.89649343490601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96005058288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86598634719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86429166793823</t>
+    <t xml:space="preserve">2.96005034446716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86598610877991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86429142951965</t>
   </si>
   <si>
     <t xml:space="preserve">2.93208527565002</t>
@@ -3053,19 +3056,19 @@
     <t xml:space="preserve">2.92191600799561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89564609527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9261531829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84225821495056</t>
+    <t xml:space="preserve">2.8956458568573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92615342140198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84225845336914</t>
   </si>
   <si>
     <t xml:space="preserve">2.85073256492615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94733905792236</t>
+    <t xml:space="preserve">2.94733881950378</t>
   </si>
   <si>
     <t xml:space="preserve">2.9998791217804</t>
@@ -3074,25 +3077,25 @@
     <t xml:space="preserve">2.9778459072113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99055743217468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03292846679688</t>
+    <t xml:space="preserve">2.99055767059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03292870521545</t>
   </si>
   <si>
     <t xml:space="preserve">3.06428337097168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04055571556091</t>
+    <t xml:space="preserve">3.04055547714233</t>
   </si>
   <si>
     <t xml:space="preserve">3.04479241371155</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02275919914246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01004838943481</t>
+    <t xml:space="preserve">3.02275943756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01004815101624</t>
   </si>
   <si>
     <t xml:space="preserve">3.00157403945923</t>
@@ -3101,19 +3104,19 @@
     <t xml:space="preserve">3.02021718025208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04648733139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03547096252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08546876907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09733271598816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13122987747192</t>
+    <t xml:space="preserve">3.04648756980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03547120094299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08546900749207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09733295440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13122963905334</t>
   </si>
   <si>
     <t xml:space="preserve">3.14563608169556</t>
@@ -3128,7 +3131,7 @@
     <t xml:space="preserve">3.19648146629333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18546509742737</t>
+    <t xml:space="preserve">3.18546485900879</t>
   </si>
   <si>
     <t xml:space="preserve">3.18715977668762</t>
@@ -3137,28 +3140,28 @@
     <t xml:space="preserve">3.16682147979736</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12953519821167</t>
+    <t xml:space="preserve">3.12953495979309</t>
   </si>
   <si>
     <t xml:space="preserve">3.10156989097595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11597609519958</t>
+    <t xml:space="preserve">3.11597633361816</t>
   </si>
   <si>
     <t xml:space="preserve">3.11089158058167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10411214828491</t>
+    <t xml:space="preserve">3.10411238670349</t>
   </si>
   <si>
     <t xml:space="preserve">3.13716149330139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12275528907776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11004400253296</t>
+    <t xml:space="preserve">3.12275552749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11004424095154</t>
   </si>
   <si>
     <t xml:space="preserve">3.1252977848053</t>
@@ -3170,16 +3173,16 @@
     <t xml:space="preserve">3.03631830215454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07360506057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09902787208557</t>
+    <t xml:space="preserve">3.07360482215881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09902763366699</t>
   </si>
   <si>
     <t xml:space="preserve">3.04987716674805</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08377385139465</t>
+    <t xml:space="preserve">3.08377408981323</t>
   </si>
   <si>
     <t xml:space="preserve">3.04140281677246</t>
@@ -3191,7 +3194,7 @@
     <t xml:space="preserve">3.08292651176453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09224820137024</t>
+    <t xml:space="preserve">3.09224796295166</t>
   </si>
   <si>
     <t xml:space="preserve">3.02360725402832</t>
@@ -3200,22 +3203,22 @@
     <t xml:space="preserve">2.9744565486908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01428508758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99648952484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9956419467926</t>
+    <t xml:space="preserve">3.01428532600403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99648928642273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99564218521118</t>
   </si>
   <si>
     <t xml:space="preserve">2.99818420410156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00411605834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96089768409729</t>
+    <t xml:space="preserve">3.00411629676819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96089744567871</t>
   </si>
   <si>
     <t xml:space="preserve">2.98547291755676</t>
@@ -3233,7 +3236,7 @@
     <t xml:space="preserve">2.94564414024353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97530364990234</t>
+    <t xml:space="preserve">2.97530388832092</t>
   </si>
   <si>
     <t xml:space="preserve">2.95327067375183</t>
@@ -3251,10 +3254,10 @@
     <t xml:space="preserve">3.03377604484558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04902982711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01767516136169</t>
+    <t xml:space="preserve">3.04902958869934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01767492294312</t>
   </si>
   <si>
     <t xml:space="preserve">3.05241942405701</t>
@@ -3272,7 +3275,7 @@
     <t xml:space="preserve">3.03462362289429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1125864982605</t>
+    <t xml:space="preserve">3.11258625984192</t>
   </si>
   <si>
     <t xml:space="preserve">3.09309577941895</t>
@@ -3284,7 +3287,7 @@
     <t xml:space="preserve">3.01682758331299</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05750393867493</t>
+    <t xml:space="preserve">3.05750370025635</t>
   </si>
   <si>
     <t xml:space="preserve">3.06936764717102</t>
@@ -3296,10 +3299,10 @@
     <t xml:space="preserve">3.03208136558533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02953886985779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0007266998291</t>
+    <t xml:space="preserve">3.02953910827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00072646141052</t>
   </si>
   <si>
     <t xml:space="preserve">2.85581707954407</t>
@@ -3311,7 +3314,7 @@
     <t xml:space="preserve">2.88547682762146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95750784873962</t>
+    <t xml:space="preserve">2.95750761032104</t>
   </si>
   <si>
     <t xml:space="preserve">2.88971400260925</t>
@@ -3329,16 +3332,16 @@
     <t xml:space="preserve">2.97869372367859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00326871871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02445459365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04563999176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05072450637817</t>
+    <t xml:space="preserve">3.00326895713806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02445435523987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04564023017883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05072426795959</t>
   </si>
   <si>
     <t xml:space="preserve">3.06089353561401</t>
@@ -3350,31 +3353,31 @@
     <t xml:space="preserve">3.10241723060608</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14055156707764</t>
+    <t xml:space="preserve">3.14055132865906</t>
   </si>
   <si>
     <t xml:space="preserve">3.11173892021179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08716344833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02699661254883</t>
+    <t xml:space="preserve">3.0871639251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02699637413025</t>
   </si>
   <si>
     <t xml:space="preserve">3.0134379863739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99394702911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97106671333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98123550415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94903349876404</t>
+    <t xml:space="preserve">2.99394726753235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97106695175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98123574256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94903373718262</t>
   </si>
   <si>
     <t xml:space="preserve">2.9083571434021</t>
@@ -3389,7 +3392,7 @@
     <t xml:space="preserve">3.07614755630493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14817810058594</t>
+    <t xml:space="preserve">3.14817833900452</t>
   </si>
   <si>
     <t xml:space="preserve">3.13377213478088</t>
@@ -3401,10 +3404,10 @@
     <t xml:space="preserve">2.9388644695282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88039255142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9185266494751</t>
+    <t xml:space="preserve">2.88039231300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91852641105652</t>
   </si>
   <si>
     <t xml:space="preserve">2.93801712989807</t>
@@ -3419,13 +3422,13 @@
     <t xml:space="preserve">2.88717198371887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87276577949524</t>
+    <t xml:space="preserve">2.87276554107666</t>
   </si>
   <si>
     <t xml:space="preserve">2.84310555458069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83802127838135</t>
+    <t xml:space="preserve">2.83802103996277</t>
   </si>
   <si>
     <t xml:space="preserve">2.79734516143799</t>
@@ -3434,10 +3437,10 @@
     <t xml:space="preserve">2.80836129188538</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82446241378784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.740567445755</t>
+    <t xml:space="preserve">2.82446217536926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74056720733643</t>
   </si>
   <si>
     <t xml:space="preserve">2.93632221221924</t>
@@ -3461,10 +3464,10 @@
     <t xml:space="preserve">2.77446460723877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87700271606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86344385147095</t>
+    <t xml:space="preserve">2.87700247764587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86344361305237</t>
   </si>
   <si>
     <t xml:space="preserve">2.85666441917419</t>
@@ -3473,22 +3476,22 @@
     <t xml:space="preserve">2.85158014297485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81937766075134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85412263870239</t>
+    <t xml:space="preserve">2.81937789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85412216186523</t>
   </si>
   <si>
     <t xml:space="preserve">2.89140892028809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7880232334137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75666880607605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81429362297058</t>
+    <t xml:space="preserve">2.78802347183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75666856765747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.814293384552</t>
   </si>
   <si>
     <t xml:space="preserve">2.82700490951538</t>
@@ -3509,10 +3512,10 @@
     <t xml:space="preserve">3.00581097602844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04733467102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00496363639832</t>
+    <t xml:space="preserve">3.04733443260193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00496387481689</t>
   </si>
   <si>
     <t xml:space="preserve">3.04394507408142</t>
@@ -3521,7 +3524,7 @@
     <t xml:space="preserve">3.05835127830505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01598024368286</t>
+    <t xml:space="preserve">3.01598048210144</t>
   </si>
   <si>
     <t xml:space="preserve">3.04818224906921</t>
@@ -3533,10 +3536,10 @@
     <t xml:space="preserve">2.98377799987793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9524233341217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98632049560547</t>
+    <t xml:space="preserve">2.95242357254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98632025718689</t>
   </si>
   <si>
     <t xml:space="preserve">3.06343579292297</t>
@@ -3554,7 +3557,7 @@
     <t xml:space="preserve">2.95072865486145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03801321983337</t>
+    <t xml:space="preserve">3.03801298141479</t>
   </si>
   <si>
     <t xml:space="preserve">2.98801517486572</t>
@@ -3563,7 +3566,7 @@
     <t xml:space="preserve">2.96598219871521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89056158065796</t>
+    <t xml:space="preserve">2.89056181907654</t>
   </si>
   <si>
     <t xml:space="preserve">2.86683344841003</t>
@@ -3572,7 +3575,7 @@
     <t xml:space="preserve">2.82785201072693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86174917221069</t>
+    <t xml:space="preserve">2.86174941062927</t>
   </si>
   <si>
     <t xml:space="preserve">2.83717393875122</t>
@@ -3593,7 +3596,7 @@
     <t xml:space="preserve">2.35668444633484</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45837545394897</t>
+    <t xml:space="preserve">2.45837569236755</t>
   </si>
   <si>
     <t xml:space="preserve">2.38888669013977</t>
@@ -3605,7 +3608,7 @@
     <t xml:space="preserve">2.3823139667511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34250521659851</t>
+    <t xml:space="preserve">2.34250545501709</t>
   </si>
   <si>
     <t xml:space="preserve">2.32569718360901</t>
@@ -3614,10 +3617,10 @@
     <t xml:space="preserve">2.37435221672058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46193051338196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46812295913696</t>
+    <t xml:space="preserve">2.46193075180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46812319755554</t>
   </si>
   <si>
     <t xml:space="preserve">2.49908542633057</t>
@@ -3626,19 +3629,16 @@
     <t xml:space="preserve">2.47608494758606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44158434867859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48758482933044</t>
+    <t xml:space="preserve">2.44158411026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48758506774902</t>
   </si>
   <si>
     <t xml:space="preserve">2.48493123054504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41327595710754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45750761032104</t>
+    <t xml:space="preserve">2.41327571868896</t>
   </si>
   <si>
     <t xml:space="preserve">2.49112367630005</t>
@@ -3647,16 +3647,16 @@
     <t xml:space="preserve">2.47696924209595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45927691459656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37523674964905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30446624755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37789058685303</t>
+    <t xml:space="preserve">2.45927667617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37523698806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30446600914001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37789082527161</t>
   </si>
   <si>
     <t xml:space="preserve">2.38673686981201</t>
@@ -3665,7 +3665,7 @@
     <t xml:space="preserve">2.41150689125061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38319849967957</t>
+    <t xml:space="preserve">2.38319826126099</t>
   </si>
   <si>
     <t xml:space="preserve">2.40619897842407</t>
@@ -3674,13 +3674,13 @@
     <t xml:space="preserve">2.41946816444397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40089106559753</t>
+    <t xml:space="preserve">2.40089130401611</t>
   </si>
   <si>
     <t xml:space="preserve">2.47873878479004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43008399009705</t>
+    <t xml:space="preserve">2.43008375167847</t>
   </si>
   <si>
     <t xml:space="preserve">2.44689202308655</t>
@@ -3689,7 +3689,7 @@
     <t xml:space="preserve">2.50970077514648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50527763366699</t>
+    <t xml:space="preserve">2.50527787208557</t>
   </si>
   <si>
     <t xml:space="preserve">2.47077679634094</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">2.4433536529541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46900773048401</t>
+    <t xml:space="preserve">2.46900796890259</t>
   </si>
   <si>
     <t xml:space="preserve">2.47520017623901</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">2.36904430389404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29650473594666</t>
+    <t xml:space="preserve">2.29650449752808</t>
   </si>
   <si>
     <t xml:space="preserve">2.35312104225159</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">2.24342656135559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18504095077515</t>
+    <t xml:space="preserve">2.18504071235657</t>
   </si>
   <si>
     <t xml:space="preserve">2.07269263267517</t>
@@ -3764,7 +3764,7 @@
     <t xml:space="preserve">2.23015713691711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14965558052063</t>
+    <t xml:space="preserve">2.14965581893921</t>
   </si>
   <si>
     <t xml:space="preserve">2.14700198173523</t>
@@ -3779,22 +3779,22 @@
     <t xml:space="preserve">2.07800030708313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07357716560364</t>
+    <t xml:space="preserve">2.07357740402222</t>
   </si>
   <si>
     <t xml:space="preserve">2.04261541366577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97803711891174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98422956466675</t>
+    <t xml:space="preserve">1.97803699970245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98422932624817</t>
   </si>
   <si>
     <t xml:space="preserve">1.87895834445953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9258439540863</t>
+    <t xml:space="preserve">1.92584371566772</t>
   </si>
   <si>
     <t xml:space="preserve">1.91611266136169</t>
@@ -3815,13 +3815,13 @@
     <t xml:space="preserve">1.84003448486328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82588016986847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87011218070984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80464911460876</t>
+    <t xml:space="preserve">1.82588028907776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87011206150055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80464923381805</t>
   </si>
   <si>
     <t xml:space="preserve">1.77280235290527</t>
@@ -3836,13 +3836,13 @@
     <t xml:space="preserve">1.87807369232178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88249695301056</t>
+    <t xml:space="preserve">1.88249683380127</t>
   </si>
   <si>
     <t xml:space="preserve">1.86303472518921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87541961669922</t>
+    <t xml:space="preserve">1.87541949748993</t>
   </si>
   <si>
     <t xml:space="preserve">1.85153460502625</t>
@@ -3851,10 +3851,10 @@
     <t xml:space="preserve">1.91257429122925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99838364124298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01696109771729</t>
+    <t xml:space="preserve">1.99838376045227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01696085929871</t>
   </si>
   <si>
     <t xml:space="preserve">2.12577080726624</t>
@@ -3866,10 +3866,10 @@
     <t xml:space="preserve">2.14434790611267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14257884025574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13196301460266</t>
+    <t xml:space="preserve">2.14257860183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13196325302124</t>
   </si>
   <si>
     <t xml:space="preserve">2.1779637336731</t>
@@ -3890,22 +3890,22 @@
     <t xml:space="preserve">2.28058123588562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29915833473206</t>
+    <t xml:space="preserve">2.29915857315063</t>
   </si>
   <si>
     <t xml:space="preserve">2.33454370498657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31773567199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33631300926208</t>
+    <t xml:space="preserve">2.31773591041565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33631277084351</t>
   </si>
   <si>
     <t xml:space="preserve">2.32835149765015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32746648788452</t>
+    <t xml:space="preserve">2.3274667263031</t>
   </si>
   <si>
     <t xml:space="preserve">2.30623555183411</t>
@@ -3917,7 +3917,7 @@
     <t xml:space="preserve">2.35046720504761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33188962936401</t>
+    <t xml:space="preserve">2.33188986778259</t>
   </si>
   <si>
     <t xml:space="preserve">2.34338998794556</t>
@@ -3929,7 +3929,7 @@
     <t xml:space="preserve">2.3716983795166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37966012954712</t>
+    <t xml:space="preserve">2.37965989112854</t>
   </si>
   <si>
     <t xml:space="preserve">2.37612152099609</t>
@@ -3938,7 +3938,7 @@
     <t xml:space="preserve">2.4327380657196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48050808906555</t>
+    <t xml:space="preserve">2.48050785064697</t>
   </si>
   <si>
     <t xml:space="preserve">2.50350832939148</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">2.44600749015808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31065845489502</t>
+    <t xml:space="preserve">2.3106586933136</t>
   </si>
   <si>
     <t xml:space="preserve">2.25669622421265</t>
@@ -3956,31 +3956,31 @@
     <t xml:space="preserve">2.2726194858551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26200413703918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24165725708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25758075714111</t>
+    <t xml:space="preserve">2.26200389862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24165749549866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25758051872253</t>
   </si>
   <si>
     <t xml:space="preserve">2.25492691993713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20273375511169</t>
+    <t xml:space="preserve">2.20273351669312</t>
   </si>
   <si>
     <t xml:space="preserve">2.25227308273315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22838807106018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28765845298767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2894275188446</t>
+    <t xml:space="preserve">2.2283878326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28765821456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28942728042603</t>
   </si>
   <si>
     <t xml:space="preserve">2.33542847633362</t>
@@ -3992,13 +3992,13 @@
     <t xml:space="preserve">2.45043063163757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45131492614746</t>
+    <t xml:space="preserve">2.45131516456604</t>
   </si>
   <si>
     <t xml:space="preserve">2.42389154434204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42919921875</t>
+    <t xml:space="preserve">2.42919945716858</t>
   </si>
   <si>
     <t xml:space="preserve">2.40708374977112</t>
@@ -4043,16 +4043,16 @@
     <t xml:space="preserve">2.29561996459961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30004286766052</t>
+    <t xml:space="preserve">2.3000431060791</t>
   </si>
   <si>
     <t xml:space="preserve">2.29473543167114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2664270401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23458027839661</t>
+    <t xml:space="preserve">2.26642727851868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23458051681519</t>
   </si>
   <si>
     <t xml:space="preserve">2.22661876678467</t>
@@ -4070,16 +4070,16 @@
     <t xml:space="preserve">2.19477200508118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22573399543762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1815025806427</t>
+    <t xml:space="preserve">2.2257342338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18150234222412</t>
   </si>
   <si>
     <t xml:space="preserve">2.15054035186768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11250114440918</t>
+    <t xml:space="preserve">2.1125009059906</t>
   </si>
   <si>
     <t xml:space="preserve">2.10807776451111</t>
@@ -4088,7 +4088,7 @@
     <t xml:space="preserve">2.13727068901062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12753987312317</t>
+    <t xml:space="preserve">2.12753963470459</t>
   </si>
   <si>
     <t xml:space="preserve">2.11692428588867</t>
@@ -4097,7 +4097,7 @@
     <t xml:space="preserve">2.18857932090759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20627188682556</t>
+    <t xml:space="preserve">2.20627212524414</t>
   </si>
   <si>
     <t xml:space="preserve">2.22131061553955</t>
@@ -4106,13 +4106,13 @@
     <t xml:space="preserve">2.20361804962158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21423387527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24254202842712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30181217193604</t>
+    <t xml:space="preserve">2.21423363685608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24254179000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30181241035461</t>
   </si>
   <si>
     <t xml:space="preserve">2.29827404022217</t>
@@ -4124,10 +4124,10 @@
     <t xml:space="preserve">2.42212247848511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31950497627258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39558339118958</t>
+    <t xml:space="preserve">2.319504737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.395583152771</t>
   </si>
   <si>
     <t xml:space="preserve">2.39027547836304</t>
@@ -4142,10 +4142,10 @@
     <t xml:space="preserve">2.44512248039246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49643111228943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53181672096252</t>
+    <t xml:space="preserve">2.49643135070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53181648254395</t>
   </si>
   <si>
     <t xml:space="preserve">2.52297043800354</t>
@@ -4163,7 +4163,7 @@
     <t xml:space="preserve">2.67689633369446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67866563796997</t>
+    <t xml:space="preserve">2.67866587638855</t>
   </si>
   <si>
     <t xml:space="preserve">2.6379725933075</t>
@@ -4175,13 +4175,13 @@
     <t xml:space="preserve">2.61497211456299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63266491889954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62204885482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54950928688049</t>
+    <t xml:space="preserve">2.63266468048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62204909324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54950904846191</t>
   </si>
   <si>
     <t xml:space="preserve">2.5282781124115</t>
@@ -4205,10 +4205,10 @@
     <t xml:space="preserve">2.53889346122742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57250952720642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54420137405396</t>
+    <t xml:space="preserve">2.572509765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54420161247253</t>
   </si>
   <si>
     <t xml:space="preserve">2.55304765701294</t>
@@ -4220,7 +4220,7 @@
     <t xml:space="preserve">2.55127859115601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53004717826843</t>
+    <t xml:space="preserve">2.53004741668701</t>
   </si>
   <si>
     <t xml:space="preserve">2.56897115707397</t>
@@ -5751,6 +5751,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.04400014877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01000022888184</t>
   </si>
 </sst>
 </file>
@@ -36189,7 +36192,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1158" t="s">
-        <v>813</v>
+        <v>827</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -36215,7 +36218,7 @@
         <v>3.24200010299683</v>
       </c>
       <c r="G1159" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -36241,7 +36244,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1160" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -36267,7 +36270,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1161" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -36293,7 +36296,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G1162" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -36345,7 +36348,7 @@
         <v>3.2739999294281</v>
       </c>
       <c r="G1164" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -36371,7 +36374,7 @@
         <v>3.15799999237061</v>
       </c>
       <c r="G1165" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -36397,7 +36400,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1166" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -36423,7 +36426,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1167" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -36449,7 +36452,7 @@
         <v>3.16199994087219</v>
       </c>
       <c r="G1168" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -36475,7 +36478,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G1169" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -36501,7 +36504,7 @@
         <v>3.25</v>
       </c>
       <c r="G1170" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -36527,7 +36530,7 @@
         <v>3.31800007820129</v>
       </c>
       <c r="G1171" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -36553,7 +36556,7 @@
         <v>3.39400005340576</v>
       </c>
       <c r="G1172" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -36579,7 +36582,7 @@
         <v>3.38199996948242</v>
       </c>
       <c r="G1173" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -36605,7 +36608,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1174" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -36657,7 +36660,7 @@
         <v>3.24799990653992</v>
       </c>
       <c r="G1176" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -36683,7 +36686,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1177" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -36709,7 +36712,7 @@
         <v>3.26799988746643</v>
       </c>
       <c r="G1178" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -36735,7 +36738,7 @@
         <v>3.24399995803833</v>
       </c>
       <c r="G1179" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -36761,7 +36764,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1180" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -36787,7 +36790,7 @@
         <v>3.31599998474121</v>
       </c>
       <c r="G1181" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -36813,7 +36816,7 @@
         <v>3.25</v>
       </c>
       <c r="G1182" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -36839,7 +36842,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G1183" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -36865,7 +36868,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1184" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -36891,7 +36894,7 @@
         <v>3.20199990272522</v>
       </c>
       <c r="G1185" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -36917,7 +36920,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G1186" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -36943,7 +36946,7 @@
         <v>3.26799988746643</v>
       </c>
       <c r="G1187" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -36969,7 +36972,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1188" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -36995,7 +36998,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G1189" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -37021,7 +37024,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G1190" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -37047,7 +37050,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G1191" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -37073,7 +37076,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G1192" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -37099,7 +37102,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G1193" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -37125,7 +37128,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G1194" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -37151,7 +37154,7 @@
         <v>3.24200010299683</v>
       </c>
       <c r="G1195" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -37177,7 +37180,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G1196" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -37203,7 +37206,7 @@
         <v>3.28600001335144</v>
       </c>
       <c r="G1197" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -37229,7 +37232,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G1198" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -37255,7 +37258,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G1199" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -37307,7 +37310,7 @@
         <v>3.21199989318848</v>
       </c>
       <c r="G1201" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -37333,7 +37336,7 @@
         <v>3.22399997711182</v>
       </c>
       <c r="G1202" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -37359,7 +37362,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G1203" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -37385,7 +37388,7 @@
         <v>3.17600011825562</v>
       </c>
       <c r="G1204" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -37411,7 +37414,7 @@
         <v>3.22199988365173</v>
       </c>
       <c r="G1205" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -37437,7 +37440,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G1206" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -37463,7 +37466,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G1207" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -37489,7 +37492,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G1208" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -37515,7 +37518,7 @@
         <v>3.15799999237061</v>
       </c>
       <c r="G1209" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -37541,7 +37544,7 @@
         <v>3.1159999370575</v>
       </c>
       <c r="G1210" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -37567,7 +37570,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1211" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -37593,7 +37596,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G1212" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -37619,7 +37622,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1213" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -37645,7 +37648,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G1214" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -37671,7 +37674,7 @@
         <v>3.01200008392334</v>
       </c>
       <c r="G1215" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -37697,7 +37700,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1216" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -37723,7 +37726,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G1217" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -37749,7 +37752,7 @@
         <v>2.87400007247925</v>
       </c>
       <c r="G1218" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -37775,7 +37778,7 @@
         <v>2.90400004386902</v>
       </c>
       <c r="G1219" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -37801,7 +37804,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G1220" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -37827,7 +37830,7 @@
         <v>3</v>
       </c>
       <c r="G1221" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -37853,7 +37856,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G1222" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -37879,7 +37882,7 @@
         <v>2.89400005340576</v>
       </c>
       <c r="G1223" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -37905,7 +37908,7 @@
         <v>2.89599990844727</v>
       </c>
       <c r="G1224" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -37931,7 +37934,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1225" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -37957,7 +37960,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G1226" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -37983,7 +37986,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G1227" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -38009,7 +38012,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G1228" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -38035,7 +38038,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1229" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -38061,7 +38064,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G1230" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -38087,7 +38090,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G1231" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -38113,7 +38116,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G1232" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -38139,7 +38142,7 @@
         <v>2.80800008773804</v>
       </c>
       <c r="G1233" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -38165,7 +38168,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G1234" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -38191,7 +38194,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1235" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -38217,7 +38220,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G1236" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -38243,7 +38246,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G1237" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -38269,7 +38272,7 @@
         <v>3.03600001335144</v>
       </c>
       <c r="G1238" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -38295,7 +38298,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1239" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -38321,7 +38324,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1240" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -38347,7 +38350,7 @@
         <v>3.05599999427795</v>
       </c>
       <c r="G1241" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -38373,7 +38376,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1242" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -38399,7 +38402,7 @@
         <v>3.03600001335144</v>
       </c>
       <c r="G1243" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -38425,7 +38428,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1244" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -38451,7 +38454,7 @@
         <v>3.0220000743866</v>
       </c>
       <c r="G1245" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -38477,7 +38480,7 @@
         <v>3.01600003242493</v>
       </c>
       <c r="G1246" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -38503,7 +38506,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G1247" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -38529,7 +38532,7 @@
         <v>3.08800005912781</v>
       </c>
       <c r="G1248" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -38555,7 +38558,7 @@
         <v>3.17600011825562</v>
       </c>
       <c r="G1249" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -38581,7 +38584,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1250" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -38607,7 +38610,7 @@
         <v>3.03600001335144</v>
       </c>
       <c r="G1251" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -38633,7 +38636,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1252" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -38659,7 +38662,7 @@
         <v>2.97199988365173</v>
       </c>
       <c r="G1253" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -38685,7 +38688,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G1254" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -38711,7 +38714,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G1255" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -38737,7 +38740,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1256" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -38763,7 +38766,7 @@
         <v>2.94199991226196</v>
       </c>
       <c r="G1257" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -38789,7 +38792,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1258" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -38815,7 +38818,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1259" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -38841,7 +38844,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G1260" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -38867,7 +38870,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G1261" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -38893,7 +38896,7 @@
         <v>2.92799997329712</v>
       </c>
       <c r="G1262" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -38919,7 +38922,7 @@
         <v>2.98600006103516</v>
       </c>
       <c r="G1263" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -38945,7 +38948,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1264" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -38971,7 +38974,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1265" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -38997,7 +39000,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G1266" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -39023,7 +39026,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G1267" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -39049,7 +39052,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G1268" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -39075,7 +39078,7 @@
         <v>2.99600005149841</v>
       </c>
       <c r="G1269" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -39101,7 +39104,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1270" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -39127,7 +39130,7 @@
         <v>3.05200004577637</v>
       </c>
       <c r="G1271" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -39153,7 +39156,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="G1272" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -39179,7 +39182,7 @@
         <v>3.03399991989136</v>
       </c>
       <c r="G1273" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -39205,7 +39208,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G1274" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -39231,7 +39234,7 @@
         <v>3.02800011634827</v>
       </c>
       <c r="G1275" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -39257,7 +39260,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1276" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -39283,7 +39286,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1277" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -39309,7 +39312,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1278" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -39335,7 +39338,7 @@
         <v>3.08800005912781</v>
       </c>
       <c r="G1279" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -39361,7 +39364,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1280" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -39387,7 +39390,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G1281" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -39413,7 +39416,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1282" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -39439,7 +39442,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1283" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -39465,7 +39468,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1284" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -39491,7 +39494,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G1285" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -39517,7 +39520,7 @@
         <v>2.87199997901917</v>
       </c>
       <c r="G1286" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -39543,7 +39546,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G1287" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -39569,7 +39572,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G1288" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -39595,7 +39598,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G1289" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -39621,7 +39624,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G1290" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -39647,7 +39650,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1291" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -39673,7 +39676,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1292" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -39699,7 +39702,7 @@
         <v>3</v>
       </c>
       <c r="G1293" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -39725,7 +39728,7 @@
         <v>3.00799989700317</v>
       </c>
       <c r="G1294" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -39751,7 +39754,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G1295" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -39777,7 +39780,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1296" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -39803,7 +39806,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G1297" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -39829,7 +39832,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G1298" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -39855,7 +39858,7 @@
         <v>3.11199998855591</v>
       </c>
       <c r="G1299" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -39881,7 +39884,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1300" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -39907,7 +39910,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G1301" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -39933,7 +39936,7 @@
         <v>3.10199999809265</v>
       </c>
       <c r="G1302" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -39959,7 +39962,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1303" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -39985,7 +39988,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G1304" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -40011,7 +40014,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G1305" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -40037,7 +40040,7 @@
         <v>3.01600003242493</v>
       </c>
       <c r="G1306" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -40063,7 +40066,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1307" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -40089,7 +40092,7 @@
         <v>3.00799989700317</v>
       </c>
       <c r="G1308" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -40115,7 +40118,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G1309" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -40141,7 +40144,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G1310" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -40167,7 +40170,7 @@
         <v>3.0220000743866</v>
       </c>
       <c r="G1311" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -40193,7 +40196,7 @@
         <v>2.97199988365173</v>
       </c>
       <c r="G1312" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -40219,7 +40222,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1313" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -40245,7 +40248,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G1314" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -40271,7 +40274,7 @@
         <v>2.92600011825562</v>
       </c>
       <c r="G1315" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -40297,7 +40300,7 @@
         <v>3.00799989700317</v>
       </c>
       <c r="G1316" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -40323,7 +40326,7 @@
         <v>3.05200004577637</v>
       </c>
       <c r="G1317" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -40349,7 +40352,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1318" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -40375,7 +40378,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1319" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -40401,7 +40404,7 @@
         <v>3.11199998855591</v>
       </c>
       <c r="G1320" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -40427,7 +40430,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1321" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -40453,7 +40456,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1322" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -40479,7 +40482,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G1323" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -40505,7 +40508,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G1324" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -40531,7 +40534,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1325" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -40557,7 +40560,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1326" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -40583,7 +40586,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1327" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -40609,7 +40612,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G1328" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -40635,7 +40638,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1329" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -40739,7 +40742,7 @@
         <v>3.26799988746643</v>
       </c>
       <c r="G1333" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -40765,7 +40768,7 @@
         <v>3.25</v>
       </c>
       <c r="G1334" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -40791,7 +40794,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G1335" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -40817,7 +40820,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G1336" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -40843,7 +40846,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G1337" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -40869,7 +40872,7 @@
         <v>3.26699995994568</v>
       </c>
       <c r="G1338" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -40921,7 +40924,7 @@
         <v>3.32399988174438</v>
       </c>
       <c r="G1340" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -40947,7 +40950,7 @@
         <v>3.29900002479553</v>
       </c>
       <c r="G1341" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -40973,7 +40976,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G1342" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -40999,7 +41002,7 @@
         <v>3.30299997329712</v>
       </c>
       <c r="G1343" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -41025,7 +41028,7 @@
         <v>3.32800006866455</v>
       </c>
       <c r="G1344" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -41051,7 +41054,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1345" t="s">
-        <v>813</v>
+        <v>827</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -41077,7 +41080,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G1346" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -41103,7 +41106,7 @@
         <v>3.37299990653992</v>
       </c>
       <c r="G1347" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -41129,7 +41132,7 @@
         <v>3.36299991607666</v>
       </c>
       <c r="G1348" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -41155,7 +41158,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G1349" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -41181,7 +41184,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1350" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -41207,7 +41210,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G1351" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -41233,7 +41236,7 @@
         <v>3.35700011253357</v>
       </c>
       <c r="G1352" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -41259,7 +41262,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1353" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -41285,7 +41288,7 @@
         <v>3.40300011634827</v>
       </c>
       <c r="G1354" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -41311,7 +41314,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1355" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -41337,7 +41340,7 @@
         <v>3.35700011253357</v>
       </c>
       <c r="G1356" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -41363,7 +41366,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1357" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -41389,7 +41392,7 @@
         <v>3.40700006484985</v>
       </c>
       <c r="G1358" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -41415,7 +41418,7 @@
         <v>3.45700001716614</v>
       </c>
       <c r="G1359" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -41441,7 +41444,7 @@
         <v>3.375</v>
       </c>
       <c r="G1360" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -41467,7 +41470,7 @@
         <v>3.37700009346008</v>
       </c>
       <c r="G1361" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -41493,7 +41496,7 @@
         <v>3.36700010299683</v>
       </c>
       <c r="G1362" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -41519,7 +41522,7 @@
         <v>3.40700006484985</v>
       </c>
       <c r="G1363" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -41545,7 +41548,7 @@
         <v>3.48699998855591</v>
       </c>
       <c r="G1364" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -41571,7 +41574,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1365" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -41597,7 +41600,7 @@
         <v>3.43799996376038</v>
       </c>
       <c r="G1366" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -41623,7 +41626,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G1367" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -41649,7 +41652,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G1368" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -41675,7 +41678,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G1369" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -41701,7 +41704,7 @@
         <v>3.51699995994568</v>
       </c>
       <c r="G1370" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -41727,7 +41730,7 @@
         <v>3.51099991798401</v>
       </c>
       <c r="G1371" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -41753,7 +41756,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1372" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -41779,7 +41782,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1373" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -41805,7 +41808,7 @@
         <v>3.4909999370575</v>
       </c>
       <c r="G1374" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -41831,7 +41834,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G1375" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -41857,7 +41860,7 @@
         <v>3.50099992752075</v>
       </c>
       <c r="G1376" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -41883,7 +41886,7 @@
         <v>3.52900004386902</v>
       </c>
       <c r="G1377" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -41909,7 +41912,7 @@
         <v>3.57200002670288</v>
       </c>
       <c r="G1378" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -41935,7 +41938,7 @@
         <v>3.60400009155273</v>
       </c>
       <c r="G1379" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -41961,7 +41964,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1380" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -41987,7 +41990,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G1381" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -42013,7 +42016,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1382" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -42039,7 +42042,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G1383" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -42065,7 +42068,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G1384" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -42091,7 +42094,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G1385" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -42117,7 +42120,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1386" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -42143,7 +42146,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1387" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -42169,7 +42172,7 @@
         <v>3.66300010681152</v>
       </c>
       <c r="G1388" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -42195,7 +42198,7 @@
         <v>3.64100003242493</v>
       </c>
       <c r="G1389" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -42221,7 +42224,7 @@
         <v>3.6029999256134</v>
       </c>
       <c r="G1390" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -42247,7 +42250,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1391" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -42273,7 +42276,7 @@
         <v>3.56100010871887</v>
       </c>
       <c r="G1392" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -42299,7 +42302,7 @@
         <v>3.52699995040894</v>
       </c>
       <c r="G1393" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -42325,7 +42328,7 @@
         <v>3.52099990844727</v>
       </c>
       <c r="G1394" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -42351,7 +42354,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G1395" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -42377,7 +42380,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G1396" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -42403,7 +42406,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G1397" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -42429,7 +42432,7 @@
         <v>3.52600002288818</v>
       </c>
       <c r="G1398" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -42455,7 +42458,7 @@
         <v>3.43300008773804</v>
       </c>
       <c r="G1399" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -42481,7 +42484,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G1400" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -42507,7 +42510,7 @@
         <v>3.49300003051758</v>
       </c>
       <c r="G1401" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -42533,7 +42536,7 @@
         <v>3.38199996948242</v>
       </c>
       <c r="G1402" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -42559,7 +42562,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1403" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -42585,7 +42588,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1404" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -42611,7 +42614,7 @@
         <v>3.46099996566772</v>
       </c>
       <c r="G1405" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -42637,7 +42640,7 @@
         <v>3.44799995422363</v>
       </c>
       <c r="G1406" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -42663,7 +42666,7 @@
         <v>3.41700005531311</v>
       </c>
       <c r="G1407" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -42689,7 +42692,7 @@
         <v>3.45300006866455</v>
       </c>
       <c r="G1408" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -42715,7 +42718,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G1409" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -42741,7 +42744,7 @@
         <v>3.36400008201599</v>
       </c>
       <c r="G1410" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -42767,7 +42770,7 @@
         <v>3.41700005531311</v>
       </c>
       <c r="G1411" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -42793,7 +42796,7 @@
         <v>3.4779999256134</v>
       </c>
       <c r="G1412" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -42819,7 +42822,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1413" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -42845,7 +42848,7 @@
         <v>3.51399993896484</v>
       </c>
       <c r="G1414" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -42871,7 +42874,7 @@
         <v>3.52900004386902</v>
       </c>
       <c r="G1415" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -42897,7 +42900,7 @@
         <v>3.5789999961853</v>
       </c>
       <c r="G1416" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -42923,7 +42926,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G1417" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -42949,7 +42952,7 @@
         <v>3.58800005912781</v>
       </c>
       <c r="G1418" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -42975,7 +42978,7 @@
         <v>3.59299993515015</v>
       </c>
       <c r="G1419" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -43001,7 +43004,7 @@
         <v>3.56699991226196</v>
       </c>
       <c r="G1420" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -43027,7 +43030,7 @@
         <v>3.55200004577637</v>
       </c>
       <c r="G1421" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -43053,7 +43056,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G1422" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -43079,7 +43082,7 @@
         <v>3.56399989128113</v>
       </c>
       <c r="G1423" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -43105,7 +43108,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G1424" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -43131,7 +43134,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G1425" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -43157,7 +43160,7 @@
         <v>3.64100003242493</v>
       </c>
       <c r="G1426" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -43183,7 +43186,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1427" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -43209,7 +43212,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G1428" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -43235,7 +43238,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G1429" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -43261,7 +43264,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1430" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -43287,7 +43290,7 @@
         <v>3.75300002098083</v>
       </c>
       <c r="G1431" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -43313,7 +43316,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G1432" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -43339,7 +43342,7 @@
         <v>3.7590000629425</v>
       </c>
       <c r="G1433" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -43365,7 +43368,7 @@
         <v>3.76099991798401</v>
       </c>
       <c r="G1434" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -43391,7 +43394,7 @@
         <v>3.73699998855591</v>
       </c>
       <c r="G1435" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -43417,7 +43420,7 @@
         <v>3.69300007820129</v>
       </c>
       <c r="G1436" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -43443,7 +43446,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1437" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -43469,7 +43472,7 @@
         <v>3.67700004577637</v>
       </c>
       <c r="G1438" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -43495,7 +43498,7 @@
         <v>3.6710000038147</v>
       </c>
       <c r="G1439" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -43521,7 +43524,7 @@
         <v>3.66300010681152</v>
       </c>
       <c r="G1440" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -43547,7 +43550,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G1441" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -43573,7 +43576,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G1442" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -43599,7 +43602,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1443" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -43625,7 +43628,7 @@
         <v>3.68799996376038</v>
       </c>
       <c r="G1444" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -43651,7 +43654,7 @@
         <v>3.63599991798401</v>
       </c>
       <c r="G1445" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -43677,7 +43680,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1446" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -43703,7 +43706,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1447" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -43729,7 +43732,7 @@
         <v>3.58299994468689</v>
       </c>
       <c r="G1448" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -43755,7 +43758,7 @@
         <v>3.62700009346008</v>
       </c>
       <c r="G1449" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -43781,7 +43784,7 @@
         <v>3.65700006484985</v>
       </c>
       <c r="G1450" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -43807,7 +43810,7 @@
         <v>3.59899997711182</v>
       </c>
       <c r="G1451" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -43833,7 +43836,7 @@
         <v>3.63899993896484</v>
       </c>
       <c r="G1452" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -43859,7 +43862,7 @@
         <v>3.63899993896484</v>
       </c>
       <c r="G1453" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -43885,7 +43888,7 @@
         <v>3.58899998664856</v>
       </c>
       <c r="G1454" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -43911,7 +43914,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G1455" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -43937,7 +43940,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G1456" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -43963,7 +43966,7 @@
         <v>3.6489999294281</v>
       </c>
       <c r="G1457" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -43989,7 +43992,7 @@
         <v>3.58299994468689</v>
       </c>
       <c r="G1458" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -44015,7 +44018,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G1459" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -44041,7 +44044,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1460" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -44067,7 +44070,7 @@
         <v>3.55699992179871</v>
       </c>
       <c r="G1461" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -44093,7 +44096,7 @@
         <v>3.53600001335144</v>
       </c>
       <c r="G1462" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -44119,7 +44122,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1463" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -44145,7 +44148,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G1464" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -44171,7 +44174,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1465" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -44197,7 +44200,7 @@
         <v>3.49399995803833</v>
       </c>
       <c r="G1466" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -44223,7 +44226,7 @@
         <v>3.52300000190735</v>
       </c>
       <c r="G1467" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -44249,7 +44252,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1468" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -44275,7 +44278,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G1469" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -44301,7 +44304,7 @@
         <v>3.43600010871887</v>
       </c>
       <c r="G1470" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -44327,7 +44330,7 @@
         <v>3.4760000705719</v>
       </c>
       <c r="G1471" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -44353,7 +44356,7 @@
         <v>3.51099991798401</v>
       </c>
       <c r="G1472" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -44379,7 +44382,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1473" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -44405,7 +44408,7 @@
         <v>3.45099997520447</v>
       </c>
       <c r="G1474" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -44431,7 +44434,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G1475" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -44457,7 +44460,7 @@
         <v>3.54299998283386</v>
       </c>
       <c r="G1476" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -44483,7 +44486,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1477" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -44509,7 +44512,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G1478" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -44535,7 +44538,7 @@
         <v>3.56100010871887</v>
       </c>
       <c r="G1479" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -44561,7 +44564,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G1480" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -44587,7 +44590,7 @@
         <v>3.58800005912781</v>
       </c>
       <c r="G1481" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -44613,7 +44616,7 @@
         <v>3.55699992179871</v>
       </c>
       <c r="G1482" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -44639,7 +44642,7 @@
         <v>3.53699994087219</v>
       </c>
       <c r="G1483" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -44665,7 +44668,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1484" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -44691,7 +44694,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1485" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -44717,7 +44720,7 @@
         <v>3.58100008964539</v>
       </c>
       <c r="G1486" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -44743,7 +44746,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G1487" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -44769,7 +44772,7 @@
         <v>3.67300009727478</v>
       </c>
       <c r="G1488" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -44795,7 +44798,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1489" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -44821,7 +44824,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G1490" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -44847,7 +44850,7 @@
         <v>3.60700011253357</v>
       </c>
       <c r="G1491" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -44873,7 +44876,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1492" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -44899,7 +44902,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G1493" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -44925,7 +44928,7 @@
         <v>3.65700006484985</v>
       </c>
       <c r="G1494" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -44951,7 +44954,7 @@
         <v>3.62199997901917</v>
       </c>
       <c r="G1495" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -44977,7 +44980,7 @@
         <v>3.56699991226196</v>
       </c>
       <c r="G1496" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -45003,7 +45006,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G1497" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -45029,7 +45032,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G1498" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -45055,7 +45058,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1499" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -45081,7 +45084,7 @@
         <v>3.53699994087219</v>
       </c>
       <c r="G1500" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -45107,7 +45110,7 @@
         <v>3.54099988937378</v>
       </c>
       <c r="G1501" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -45133,7 +45136,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1502" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -45159,7 +45162,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1503" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -45185,7 +45188,7 @@
         <v>3.38700008392334</v>
       </c>
       <c r="G1504" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -45211,7 +45214,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1505" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -45237,7 +45240,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1506" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -45263,7 +45266,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1507" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -45289,7 +45292,7 @@
         <v>3.41700005531311</v>
       </c>
       <c r="G1508" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -45315,7 +45318,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1509" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -45341,7 +45344,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1510" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -45367,7 +45370,7 @@
         <v>3.51900005340576</v>
       </c>
       <c r="G1511" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -45393,7 +45396,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1512" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -45419,7 +45422,7 @@
         <v>3.55699992179871</v>
       </c>
       <c r="G1513" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -45445,7 +45448,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G1514" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -45471,7 +45474,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G1515" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -45497,7 +45500,7 @@
         <v>3.54399991035461</v>
       </c>
       <c r="G1516" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -45523,7 +45526,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1517" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -45549,7 +45552,7 @@
         <v>3.56900000572205</v>
       </c>
       <c r="G1518" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -45575,7 +45578,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G1519" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -45601,7 +45604,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1520" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -45627,7 +45630,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G1521" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -45653,7 +45656,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1522" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -45679,7 +45682,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G1523" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -45705,7 +45708,7 @@
         <v>3.67799997329712</v>
       </c>
       <c r="G1524" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -45731,7 +45734,7 @@
         <v>3.66300010681152</v>
       </c>
       <c r="G1525" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -45757,7 +45760,7 @@
         <v>3.66100001335144</v>
       </c>
       <c r="G1526" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -45783,7 +45786,7 @@
         <v>3.70600008964539</v>
       </c>
       <c r="G1527" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -45809,7 +45812,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G1528" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -45835,7 +45838,7 @@
         <v>3.64299988746643</v>
       </c>
       <c r="G1529" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -45861,7 +45864,7 @@
         <v>3.57200002670288</v>
       </c>
       <c r="G1530" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -45887,7 +45890,7 @@
         <v>3.57200002670288</v>
       </c>
       <c r="G1531" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -45913,7 +45916,7 @@
         <v>3.58800005912781</v>
       </c>
       <c r="G1532" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -45939,7 +45942,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1533" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -45965,7 +45968,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G1534" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -45991,7 +45994,7 @@
         <v>3.53299999237061</v>
       </c>
       <c r="G1535" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -46017,7 +46020,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G1536" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -46043,7 +46046,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G1537" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -46069,7 +46072,7 @@
         <v>3.47399997711182</v>
       </c>
       <c r="G1538" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -46095,7 +46098,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1539" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -46121,7 +46124,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G1540" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -46147,7 +46150,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1541" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -46173,7 +46176,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G1542" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -46199,7 +46202,7 @@
         <v>3.44300007820129</v>
       </c>
       <c r="G1543" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -46225,7 +46228,7 @@
         <v>3.5090000629425</v>
       </c>
       <c r="G1544" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -46251,7 +46254,7 @@
         <v>3.58899998664856</v>
       </c>
       <c r="G1545" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -46277,7 +46280,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1546" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -46303,7 +46306,7 @@
         <v>3.67799997329712</v>
       </c>
       <c r="G1547" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -46329,7 +46332,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G1548" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -46355,7 +46358,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1549" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -46381,7 +46384,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G1550" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -46407,7 +46410,7 @@
         <v>3.62299990653992</v>
       </c>
       <c r="G1551" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -46433,7 +46436,7 @@
         <v>3.46799993515015</v>
       </c>
       <c r="G1552" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -46459,7 +46462,7 @@
         <v>3.3989999294281</v>
       </c>
       <c r="G1553" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -46485,7 +46488,7 @@
         <v>3.44400000572205</v>
       </c>
       <c r="G1554" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -46511,7 +46514,7 @@
         <v>3.46700000762939</v>
       </c>
       <c r="G1555" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -46537,7 +46540,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G1556" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -46563,7 +46566,7 @@
         <v>3.375</v>
       </c>
       <c r="G1557" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -46589,7 +46592,7 @@
         <v>3.40700006484985</v>
       </c>
       <c r="G1558" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -46615,7 +46618,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1559" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -46641,7 +46644,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G1560" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -46667,7 +46670,7 @@
         <v>3.34899997711182</v>
       </c>
       <c r="G1561" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -46693,7 +46696,7 @@
         <v>3.30100011825562</v>
       </c>
       <c r="G1562" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -46719,7 +46722,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G1563" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -46745,7 +46748,7 @@
         <v>3.33299994468689</v>
       </c>
       <c r="G1564" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -46771,7 +46774,7 @@
         <v>3.23399996757507</v>
       </c>
       <c r="G1565" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -46797,7 +46800,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1566" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -46823,7 +46826,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1567" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -46849,7 +46852,7 @@
         <v>3.34200000762939</v>
       </c>
       <c r="G1568" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -46875,7 +46878,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G1569" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -46901,7 +46904,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1570" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -46927,7 +46930,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G1571" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -46953,7 +46956,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1572" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -46979,7 +46982,7 @@
         <v>3.2739999294281</v>
       </c>
       <c r="G1573" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -47005,7 +47008,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1574" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -47031,7 +47034,7 @@
         <v>3.37899994850159</v>
       </c>
       <c r="G1575" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -47057,7 +47060,7 @@
         <v>3.37100005149841</v>
       </c>
       <c r="G1576" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -47083,7 +47086,7 @@
         <v>3.34200000762939</v>
       </c>
       <c r="G1577" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -47109,7 +47112,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1578" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -47135,7 +47138,7 @@
         <v>3.32699990272522</v>
       </c>
       <c r="G1579" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -47161,7 +47164,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G1580" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -47187,7 +47190,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G1581" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -47213,7 +47216,7 @@
         <v>3.37100005149841</v>
       </c>
       <c r="G1582" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -47239,7 +47242,7 @@
         <v>3.41199994087219</v>
       </c>
       <c r="G1583" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -47265,7 +47268,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1584" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -47291,7 +47294,7 @@
         <v>3.25300002098083</v>
       </c>
       <c r="G1585" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -47317,7 +47320,7 @@
         <v>3.32100009918213</v>
       </c>
       <c r="G1586" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -47343,7 +47346,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G1587" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -47369,7 +47372,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G1588" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -47395,7 +47398,7 @@
         <v>3.36700010299683</v>
       </c>
       <c r="G1589" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -47421,7 +47424,7 @@
         <v>3.34599995613098</v>
       </c>
       <c r="G1590" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -47447,7 +47450,7 @@
         <v>3.36700010299683</v>
       </c>
       <c r="G1591" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -47473,7 +47476,7 @@
         <v>3.39400005340576</v>
       </c>
       <c r="G1592" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -47499,7 +47502,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G1593" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -47525,7 +47528,7 @@
         <v>3.43099999427795</v>
       </c>
       <c r="G1594" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -47551,7 +47554,7 @@
         <v>3.54699993133545</v>
       </c>
       <c r="G1595" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -47577,7 +47580,7 @@
         <v>3.64100003242493</v>
       </c>
       <c r="G1596" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -47603,7 +47606,7 @@
         <v>3.66100001335144</v>
       </c>
       <c r="G1597" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -47629,7 +47632,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G1598" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -47655,7 +47658,7 @@
         <v>3.5789999961853</v>
       </c>
       <c r="G1599" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -47681,7 +47684,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G1600" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -47707,7 +47710,7 @@
         <v>3.5460000038147</v>
       </c>
       <c r="G1601" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -47733,7 +47736,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1602" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -47759,7 +47762,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G1603" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -47785,7 +47788,7 @@
         <v>3.60899996757507</v>
       </c>
       <c r="G1604" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -47811,7 +47814,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G1605" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -47837,7 +47840,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G1606" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -47863,7 +47866,7 @@
         <v>3.55900001525879</v>
       </c>
       <c r="G1607" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -47889,7 +47892,7 @@
         <v>3.59699988365173</v>
       </c>
       <c r="G1608" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -47915,7 +47918,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G1609" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -47941,7 +47944,7 @@
         <v>3.50799989700317</v>
       </c>
       <c r="G1610" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -47967,7 +47970,7 @@
         <v>3.55900001525879</v>
       </c>
       <c r="G1611" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -47993,7 +47996,7 @@
         <v>3.57200002670288</v>
       </c>
       <c r="G1612" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -48019,7 +48022,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G1613" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -48045,7 +48048,7 @@
         <v>3.52099990844727</v>
       </c>
       <c r="G1614" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -48071,7 +48074,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G1615" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -48097,7 +48100,7 @@
         <v>3.5239999294281</v>
       </c>
       <c r="G1616" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -48123,7 +48126,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1617" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -48149,7 +48152,7 @@
         <v>3.3529999256134</v>
       </c>
       <c r="G1618" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -48175,7 +48178,7 @@
         <v>3.38100004196167</v>
       </c>
       <c r="G1619" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -48201,7 +48204,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G1620" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -48227,7 +48230,7 @@
         <v>3.45700001716614</v>
       </c>
       <c r="G1621" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -48253,7 +48256,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1622" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -48279,7 +48282,7 @@
         <v>3.43600010871887</v>
       </c>
       <c r="G1623" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -48305,7 +48308,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G1624" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -48331,7 +48334,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1625" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -48357,7 +48360,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1626" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -48383,7 +48386,7 @@
         <v>3.54699993133545</v>
       </c>
       <c r="G1627" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -48409,7 +48412,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G1628" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -48435,7 +48438,7 @@
         <v>3.52600002288818</v>
       </c>
       <c r="G1629" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -48461,7 +48464,7 @@
         <v>3.5</v>
       </c>
       <c r="G1630" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -48487,7 +48490,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1631" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -48513,7 +48516,7 @@
         <v>3.41100001335144</v>
       </c>
       <c r="G1632" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -48539,7 +48542,7 @@
         <v>3.38299989700317</v>
       </c>
       <c r="G1633" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -48565,7 +48568,7 @@
         <v>3.33699989318848</v>
       </c>
       <c r="G1634" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -48591,7 +48594,7 @@
         <v>3.37700009346008</v>
       </c>
       <c r="G1635" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -48617,7 +48620,7 @@
         <v>3.34800004959106</v>
       </c>
       <c r="G1636" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -48643,7 +48646,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1637" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -48669,7 +48672,7 @@
         <v>3.21799993515015</v>
       </c>
       <c r="G1638" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -48695,7 +48698,7 @@
         <v>2.98699998855591</v>
       </c>
       <c r="G1639" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -48721,7 +48724,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G1640" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -48747,7 +48750,7 @@
         <v>2.78099989891052</v>
       </c>
       <c r="G1641" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -48773,7 +48776,7 @@
         <v>2.90100002288818</v>
       </c>
       <c r="G1642" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -48799,7 +48802,7 @@
         <v>2.81900000572205</v>
       </c>
       <c r="G1643" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -48825,7 +48828,7 @@
         <v>2.8529999256134</v>
       </c>
       <c r="G1644" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -48851,7 +48854,7 @@
         <v>2.69300007820129</v>
       </c>
       <c r="G1645" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -48877,7 +48880,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G1646" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -48903,7 +48906,7 @@
         <v>2.62899994850159</v>
       </c>
       <c r="G1647" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -48929,7 +48932,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G1648" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -48955,7 +48958,7 @@
         <v>2.78299999237061</v>
       </c>
       <c r="G1649" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -48981,7 +48984,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1650" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -49007,7 +49010,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1651" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -49033,7 +49036,7 @@
         <v>2.79900002479553</v>
       </c>
       <c r="G1652" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -49059,7 +49062,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1653" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -49085,7 +49088,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G1654" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -49111,7 +49114,7 @@
         <v>2.80900001525879</v>
       </c>
       <c r="G1655" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -49137,7 +49140,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G1656" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -49163,7 +49166,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G1657" t="s">
-        <v>1208</v>
+        <v>574</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -49189,7 +49192,7 @@
         <v>2.80900001525879</v>
       </c>
       <c r="G1658" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -49579,7 +49582,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G1673" t="s">
-        <v>1208</v>
+        <v>574</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -52075,7 +52078,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G1769" t="s">
-        <v>1208</v>
+        <v>574</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -52829,7 +52832,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G1798" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -54363,7 +54366,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G1857" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -54649,7 +54652,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1868" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -72545,7 +72548,7 @@
     </row>
     <row r="2557">
       <c r="A2557" s="1" t="n">
-        <v>46045.6911689815</v>
+        <v>46045.3333333333</v>
       </c>
       <c r="B2557" t="n">
         <v>2945702</v>
@@ -72566,6 +72569,32 @@
         <v>1912</v>
       </c>
       <c r="H2557" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2558">
+      <c r="A2558" s="1" t="n">
+        <v>46048.6912962963</v>
+      </c>
+      <c r="B2558" t="n">
+        <v>3431703</v>
+      </c>
+      <c r="C2558" t="n">
+        <v>4.05600023269653</v>
+      </c>
+      <c r="D2558" t="n">
+        <v>4.01000022888184</v>
+      </c>
+      <c r="E2558" t="n">
+        <v>4.05600023269653</v>
+      </c>
+      <c r="F2558" t="n">
+        <v>4.01000022888184</v>
+      </c>
+      <c r="G2558" t="s">
+        <v>1913</v>
+      </c>
+      <c r="H2558" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HER.MI.xlsx
+++ b/data/HER.MI.xlsx
@@ -53,157 +53,157 @@
     <t xml:space="preserve">1.71036124229431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68800330162048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72573184967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79140782356262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79420256614685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77044773101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74669218063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70337438583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77324223518372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74948728084564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76625537872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80538129806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79001033306122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80398392677307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83472573757172</t>
+    <t xml:space="preserve">1.68800354003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7257319688797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79140746593475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79420244693756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77044725418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74669241905212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70337450504303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77324187755585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74948704242706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76625573635101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80538153648376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79001045227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80398404598236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83472514152527</t>
   </si>
   <si>
     <t xml:space="preserve">1.81656002998352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80258619785309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84869933128357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85568618774414</t>
+    <t xml:space="preserve">1.80258643627167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84869909286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85568583011627</t>
   </si>
   <si>
     <t xml:space="preserve">1.84031498432159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82354652881622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82913601398468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72852683067322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74110293388367</t>
+    <t xml:space="preserve">1.82354664802551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82913625240326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72852659225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74110305309296</t>
   </si>
   <si>
     <t xml:space="preserve">1.75926840305328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69918239116669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75507616996765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79559946060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78302359580994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77603662014008</t>
+    <t xml:space="preserve">1.69918203353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75507640838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79559981822968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78302323818207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77603673934937</t>
   </si>
   <si>
     <t xml:space="preserve">1.79839444160461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80118930339813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82075214385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8305332660675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78861284255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76485753059387</t>
+    <t xml:space="preserve">1.80118918418884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82075202465057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83053374290466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78861260414124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76485788822174</t>
   </si>
   <si>
     <t xml:space="preserve">1.74529492855072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73970556259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72992432117462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74389755725861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73271882534027</t>
+    <t xml:space="preserve">1.73970532417297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72992444038391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7438976764679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73271894454956</t>
   </si>
   <si>
     <t xml:space="preserve">1.76346063613892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7788313627243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76066613197327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77463972568512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7969970703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83752036094666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81097066402435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85708332061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84310972690582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76765286922455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78162622451782</t>
+    <t xml:space="preserve">1.77883148193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76066565513611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77463924884796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79699695110321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83752024173737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81097078323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85708320140839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84310984611511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76765275001526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78162634372711</t>
   </si>
   <si>
     <t xml:space="preserve">1.78721582889557</t>
@@ -212,136 +212,136 @@
     <t xml:space="preserve">1.77743411064148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78022885322571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8081761598587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80957281589508</t>
+    <t xml:space="preserve">1.780228972435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80817592144012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80957305431366</t>
   </si>
   <si>
     <t xml:space="preserve">1.79280495643616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78442084789276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75647401809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74808955192566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82634127140045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84590435028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83193111419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84450721740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82214939594269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83332800865173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8249443769455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81376516819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76206302642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73132121562958</t>
+    <t xml:space="preserve">1.78442096710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75647366046906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74809002876282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82634174823761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84590458869934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83193099498749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84450733661652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82214951515198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83332812786102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82494401931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81376528739929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76206338405609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73132133483887</t>
   </si>
   <si>
     <t xml:space="preserve">1.74250030517578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71175861358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75751078128815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77344846725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74012351036072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75895917415619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70390129089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67347455024719</t>
+    <t xml:space="preserve">1.71175873279572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75751042366028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77344822883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74012386798859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75895941257477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70390117168427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6734744310379</t>
   </si>
   <si>
     <t xml:space="preserve">1.70969676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73867475986481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78069293498993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83430206775665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80822157859802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81111931800842</t>
+    <t xml:space="preserve">1.73867464065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78069281578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83430182933807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80822169780731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81111943721771</t>
   </si>
   <si>
     <t xml:space="preserve">1.78503942489624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77924406528473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72708332538605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76040804386139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7459192276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77055048942566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76620364189148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76185667514801</t>
+    <t xml:space="preserve">1.77924382686615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72708380222321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76040840148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74591934680939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77055037021637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76620388031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76185691356659</t>
   </si>
   <si>
     <t xml:space="preserve">1.76910161972046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77489721775055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78359031677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83719992637634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85748422145844</t>
+    <t xml:space="preserve">1.77489733695984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78359055519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83719956874847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85748410224915</t>
   </si>
   <si>
     <t xml:space="preserve">1.85023975372314</t>
@@ -350,13 +350,13 @@
     <t xml:space="preserve">1.83575069904327</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86617743968964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83140432834625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84444403648376</t>
+    <t xml:space="preserve">1.86617767810822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83140444755554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84444415569305</t>
   </si>
   <si>
     <t xml:space="preserve">1.79663074016571</t>
@@ -368,70 +368,73 @@
     <t xml:space="preserve">1.81256866455078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7488169670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74447011947632</t>
+    <t xml:space="preserve">1.74881708621979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74447000026703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76765251159668</t>
   </si>
   <si>
     <t xml:space="preserve">1.77634584903717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79083490371704</t>
+    <t xml:space="preserve">1.79083502292633</t>
   </si>
   <si>
     <t xml:space="preserve">1.79952847957611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78648829460144</t>
+    <t xml:space="preserve">1.78648841381073</t>
   </si>
   <si>
     <t xml:space="preserve">1.78938603401184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81546640396118</t>
+    <t xml:space="preserve">1.8154661655426</t>
   </si>
   <si>
     <t xml:space="preserve">1.75606143474579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73577702045441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70679914951324</t>
+    <t xml:space="preserve">1.73577678203583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70679926872253</t>
   </si>
   <si>
     <t xml:space="preserve">1.73722589015961</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7546124458313</t>
+    <t xml:space="preserve">1.75461268424988</t>
   </si>
   <si>
     <t xml:space="preserve">1.71114563941956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70824790000916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70245230197906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69231021404266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71694135665894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69665682315826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63145649433136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60537624359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59233605861664</t>
+    <t xml:space="preserve">1.70824801921844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70245218276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69230997562408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71694099903107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69665670394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63145673274994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60537648200989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59233617782593</t>
   </si>
   <si>
     <t xml:space="preserve">1.57929623126984</t>
@@ -443,55 +446,55 @@
     <t xml:space="preserve">1.6097229719162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6140695810318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62131416797638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63290524482727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61841642856598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63870072364807</t>
+    <t xml:space="preserve">1.61406970024109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62131404876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63290500640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6184161901474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63870084285736</t>
   </si>
   <si>
     <t xml:space="preserve">1.63725197315216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65029203891754</t>
+    <t xml:space="preserve">1.65029215812683</t>
   </si>
   <si>
     <t xml:space="preserve">1.62276303768158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61551868915558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61696743965149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62566065788269</t>
+    <t xml:space="preserve">1.61551856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61696755886078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62566089630127</t>
   </si>
   <si>
     <t xml:space="preserve">1.66188323497772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66912758350372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68796324729919</t>
+    <t xml:space="preserve">1.66912746429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68796348571777</t>
   </si>
   <si>
     <t xml:space="preserve">1.59378528594971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56625616550446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56335842609406</t>
+    <t xml:space="preserve">1.56625604629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56335830688477</t>
   </si>
   <si>
     <t xml:space="preserve">1.54307389259338</t>
@@ -500,10 +503,10 @@
     <t xml:space="preserve">1.46048676967621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4633846282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44599783420563</t>
+    <t xml:space="preserve">1.46338450908661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44599771499634</t>
   </si>
   <si>
     <t xml:space="preserve">1.44527339935303</t>
@@ -515,88 +518,88 @@
     <t xml:space="preserve">1.43005990982056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42209112644196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39601099491119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39456188678741</t>
+    <t xml:space="preserve">1.42209100723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3960108757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3945620059967</t>
   </si>
   <si>
     <t xml:space="preserve">1.40905106067657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41267323493958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3981841802597</t>
+    <t xml:space="preserve">1.41267311573029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39818429946899</t>
   </si>
   <si>
     <t xml:space="preserve">1.40180623531342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40542876720428</t>
+    <t xml:space="preserve">1.40542888641357</t>
   </si>
   <si>
     <t xml:space="preserve">1.41629552841187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38152182102203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35906422138214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37717533111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43875324726105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48077118396759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49236238002777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48511815071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5329315662384</t>
+    <t xml:space="preserve">1.38152205944061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35906434059143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37717521190643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43875336647034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48077142238617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49236249923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48511791229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53293144702911</t>
   </si>
   <si>
     <t xml:space="preserve">1.52713596820831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50105595588684</t>
+    <t xml:space="preserve">1.50105583667755</t>
   </si>
   <si>
     <t xml:space="preserve">1.50685143470764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54886937141418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55756282806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57060277462006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59088754653931</t>
+    <t xml:space="preserve">1.54886949062347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55756306648254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57060253620148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59088730812073</t>
   </si>
   <si>
     <t xml:space="preserve">1.56915390491486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58798956871033</t>
+    <t xml:space="preserve">1.58798944950104</t>
   </si>
   <si>
     <t xml:space="preserve">1.608274102211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5966831445694</t>
+    <t xml:space="preserve">1.59668290615082</t>
   </si>
   <si>
     <t xml:space="preserve">1.59958076477051</t>
@@ -605,13 +608,13 @@
     <t xml:space="preserve">1.56480741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65174102783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64159870147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65318989753723</t>
+    <t xml:space="preserve">1.65174090862274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64159905910492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65318977832794</t>
   </si>
   <si>
     <t xml:space="preserve">1.65463864803314</t>
@@ -620,28 +623,28 @@
     <t xml:space="preserve">1.65898537635803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64014995098114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64304780960083</t>
+    <t xml:space="preserve">1.64014983177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64304769039154</t>
   </si>
   <si>
     <t xml:space="preserve">1.57494962215424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57784724235535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55176723003387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58654069900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63000762462616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68216741085052</t>
+    <t xml:space="preserve">1.57784736156464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55176711082458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58654057979584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63000750541687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68216800689697</t>
   </si>
   <si>
     <t xml:space="preserve">1.66622972488403</t>
@@ -653,13 +656,13 @@
     <t xml:space="preserve">1.69086146354675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69375896453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69810557365417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69520783424377</t>
+    <t xml:space="preserve">1.69375920295715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69810569286346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69520771503448</t>
   </si>
   <si>
     <t xml:space="preserve">1.71404349803925</t>
@@ -668,130 +671,130 @@
     <t xml:space="preserve">1.72998118400574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73432803153992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71983933448792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72418606281281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71549212932587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71839010715485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7415726184845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78214156627655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78793716430664</t>
+    <t xml:space="preserve">1.7343282699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71983897686005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72418594360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71549248695374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71839022636414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74157238006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78214144706726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78793728351593</t>
   </si>
   <si>
     <t xml:space="preserve">1.8140172958374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82995533943176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86907529830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8995019197464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91399133205414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91543996334076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88066637516022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87197315692902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88935983181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90095114707947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9052973985672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91254222393036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94441771507263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93717348575592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87921798229218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88356423377991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92848026752472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8980530500412</t>
+    <t xml:space="preserve">1.82995510101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86907517910004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89950227737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91399121284485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91544008255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88066649436951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8719733953476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88935995101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90095090866089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90529763698578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91254246234894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94441795349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93717360496521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87921786308289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8835643529892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92848014831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89805340766907</t>
   </si>
   <si>
     <t xml:space="preserve">1.88791084289551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90240001678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91688883304596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92413330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93572461605072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93862235546112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94876503944397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99512922763824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0284538269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05743145942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06902289390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05163645744324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1023473739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06467628479004</t>
+    <t xml:space="preserve">1.90239953994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91688871383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92413318157196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93572449684143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93862223625183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9487646818161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99512934684753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02845406532288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05743169784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06902313232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05163621902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10234761238098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06467604637146</t>
   </si>
   <si>
     <t xml:space="preserve">2.0385959148407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07336974143982</t>
+    <t xml:space="preserve">2.07336950302124</t>
   </si>
   <si>
     <t xml:space="preserve">2.0864098072052</t>
@@ -803,19 +806,19 @@
     <t xml:space="preserve">2.11248970031738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11104083061218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1008985042572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05453395843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08930706977844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12263154983521</t>
+    <t xml:space="preserve">2.11104130744934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10089874267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05453419685364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08930730819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12263202667236</t>
   </si>
   <si>
     <t xml:space="preserve">2.07916498184204</t>
@@ -827,7 +830,7 @@
     <t xml:space="preserve">2.11973452568054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10814356803894</t>
+    <t xml:space="preserve">2.10814309120178</t>
   </si>
   <si>
     <t xml:space="preserve">2.1472635269165</t>
@@ -836,7 +839,7 @@
     <t xml:space="preserve">2.13277435302734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15450811386108</t>
+    <t xml:space="preserve">2.15450763702393</t>
   </si>
   <si>
     <t xml:space="preserve">2.14291644096375</t>
@@ -851,16 +854,13 @@
     <t xml:space="preserve">2.17836785316467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17239141464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15595626831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09918189048767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.112628698349</t>
+    <t xml:space="preserve">2.17239165306091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09918165206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11262845993042</t>
   </si>
   <si>
     <t xml:space="preserve">2.07228827476501</t>
@@ -869,10 +869,10 @@
     <t xml:space="preserve">2.05884170532227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01700735092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99907863140106</t>
+    <t xml:space="preserve">2.01700758934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99907827377319</t>
   </si>
   <si>
     <t xml:space="preserve">2.01103091239929</t>
@@ -881,22 +881,22 @@
     <t xml:space="preserve">2.00804281234741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99758434295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95126807689667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97069072723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00505447387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98264348506927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03045439720154</t>
+    <t xml:space="preserve">1.99758446216583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9512677192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97069096565247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00505471229553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98264360427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03045392036438</t>
   </si>
   <si>
     <t xml:space="preserve">2.05286526679993</t>
@@ -905,70 +905,70 @@
     <t xml:space="preserve">2.0394184589386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03194808959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04539489746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0244779586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06182956695557</t>
+    <t xml:space="preserve">2.03194832801819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04539465904236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02447772026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06182980537415</t>
   </si>
   <si>
     <t xml:space="preserve">2.07677054405212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03344202041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01401925086975</t>
+    <t xml:space="preserve">2.03344225883484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01401901245117</t>
   </si>
   <si>
     <t xml:space="preserve">2.05435919761658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04390072822571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04240703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03643083572388</t>
+    <t xml:space="preserve">2.04390096664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04240655899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03643035888672</t>
   </si>
   <si>
     <t xml:space="preserve">2.04838299751282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04987716674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00206661224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05585360527039</t>
+    <t xml:space="preserve">2.04987692832947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00206613540649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05585336685181</t>
   </si>
   <si>
     <t xml:space="preserve">2.03493595123291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99459588527679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97517311573029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96172654628754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96770298480988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02597165107727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0125253200531</t>
+    <t xml:space="preserve">1.99459624290466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97517323493958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96172595024109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96770262718201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02597188949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01252508163452</t>
   </si>
   <si>
     <t xml:space="preserve">2.00953698158264</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">2.0035605430603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07826471328735</t>
+    <t xml:space="preserve">2.07826495170593</t>
   </si>
   <si>
     <t xml:space="preserve">2.01850128173828</t>
@@ -986,40 +986,40 @@
     <t xml:space="preserve">2.00057244300842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98563170433044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98712575435638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9721851348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02148962020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03792428970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06033563613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07079434394836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07378220558167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06631207466125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06332397460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07527637481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08424067497253</t>
+    <t xml:space="preserve">1.98563158512115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98712587356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97218525409698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02148985862732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03792452812195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06033539772034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07079458236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07378244400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06631183624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06332349777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07527661323547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08424091339111</t>
   </si>
   <si>
     <t xml:space="preserve">2.10665202140808</t>
@@ -1031,31 +1031,31 @@
     <t xml:space="preserve">2.14998030662537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16043901443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18135619163513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19629669189453</t>
+    <t xml:space="preserve">2.16043925285339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18135643005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19629693031311</t>
   </si>
   <si>
     <t xml:space="preserve">2.18733239173889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1798620223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16641521453857</t>
+    <t xml:space="preserve">2.17986226081848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16641545295715</t>
   </si>
   <si>
     <t xml:space="preserve">2.17089748382568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19181489944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19330859184265</t>
+    <t xml:space="preserve">2.19181442260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19330883026123</t>
   </si>
   <si>
     <t xml:space="preserve">2.19480299949646</t>
@@ -1064,25 +1064,25 @@
     <t xml:space="preserve">2.22468423843384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.271000623703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25606036186218</t>
+    <t xml:space="preserve">2.27100086212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25605988502502</t>
   </si>
   <si>
     <t xml:space="preserve">2.2590479850769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28145933151245</t>
+    <t xml:space="preserve">2.28145956993103</t>
   </si>
   <si>
     <t xml:space="preserve">2.2949059009552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30536460876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30088210105896</t>
+    <t xml:space="preserve">2.30536413192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30088233947754</t>
   </si>
   <si>
     <t xml:space="preserve">2.33972859382629</t>
@@ -1100,16 +1100,16 @@
     <t xml:space="preserve">2.3158233165741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25456643104553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25755405426025</t>
+    <t xml:space="preserve">2.25456595420837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25755381584167</t>
   </si>
   <si>
     <t xml:space="preserve">2.27847123146057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22916650772095</t>
+    <t xml:space="preserve">2.22916698455811</t>
   </si>
   <si>
     <t xml:space="preserve">2.22617864608765</t>
@@ -1118,19 +1118,19 @@
     <t xml:space="preserve">2.21870803833008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17388606071472</t>
+    <t xml:space="preserve">2.17388558387756</t>
   </si>
   <si>
     <t xml:space="preserve">2.15446257591248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21123790740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26054239273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31134057044983</t>
+    <t xml:space="preserve">2.21123743057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26054215431213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31134080886841</t>
   </si>
   <si>
     <t xml:space="preserve">2.24111914634705</t>
@@ -1139,22 +1139,22 @@
     <t xml:space="preserve">2.26950693130493</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23813128471375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27697730064392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28594160079956</t>
+    <t xml:space="preserve">2.23813104629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27697706222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28594136238098</t>
   </si>
   <si>
     <t xml:space="preserve">2.29938840866089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24709534645081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27996563911438</t>
+    <t xml:space="preserve">2.24709558486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2799654006958</t>
   </si>
   <si>
     <t xml:space="preserve">2.24560165405273</t>
@@ -1166,13 +1166,13 @@
     <t xml:space="preserve">2.13503956794739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11113429069519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05734729766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02895975112915</t>
+    <t xml:space="preserve">2.11113452911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05734753608704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02895998954773</t>
   </si>
   <si>
     <t xml:space="preserve">2.09469938278198</t>
@@ -1190,43 +1190,43 @@
     <t xml:space="preserve">2.06930017471313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04091238975525</t>
+    <t xml:space="preserve">2.04091262817383</t>
   </si>
   <si>
     <t xml:space="preserve">2.08573508262634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08274698257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08125257492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10216951370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09768748283386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12009859085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21273159980774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22169661521912</t>
+    <t xml:space="preserve">2.08274674415588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08125305175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10216975212097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09768772125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12009906768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21273183822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22169613838196</t>
   </si>
   <si>
     <t xml:space="preserve">2.23066067695618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24261355400085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26353025436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23514270782471</t>
+    <t xml:space="preserve">2.24261331558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26353073120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23514318466187</t>
   </si>
   <si>
     <t xml:space="preserve">2.25307178497314</t>
@@ -1235,73 +1235,73 @@
     <t xml:space="preserve">2.29341220855713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29789400100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28444743156433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22767281532288</t>
+    <t xml:space="preserve">2.29789447784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28444766998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2276725769043</t>
   </si>
   <si>
     <t xml:space="preserve">2.25157761573792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14101600646973</t>
+    <t xml:space="preserve">2.14101576805115</t>
   </si>
   <si>
     <t xml:space="preserve">2.12159276008606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02298355102539</t>
+    <t xml:space="preserve">2.02298378944397</t>
   </si>
   <si>
     <t xml:space="preserve">1.94678544998169</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96471452713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98114931583405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96919643878937</t>
+    <t xml:space="preserve">1.96471440792084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98114907741547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96919691562653</t>
   </si>
   <si>
     <t xml:space="preserve">1.97816133499146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9482798576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02856636047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06108593940735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0719256401062</t>
+    <t xml:space="preserve">1.94827973842621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02856659889221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06108570098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07192540168762</t>
   </si>
   <si>
     <t xml:space="preserve">2.0378577709198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04095482826233</t>
+    <t xml:space="preserve">2.04095506668091</t>
   </si>
   <si>
     <t xml:space="preserve">2.07347416877747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0595371723175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08895874023438</t>
+    <t xml:space="preserve">2.05953693389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08895921707153</t>
   </si>
   <si>
     <t xml:space="preserve">2.06727981567383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10599279403687</t>
+    <t xml:space="preserve">2.10599303245544</t>
   </si>
   <si>
     <t xml:space="preserve">2.13541483879089</t>
@@ -1310,10 +1310,10 @@
     <t xml:space="preserve">2.15399718284607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16019105911255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14470624923706</t>
+    <t xml:space="preserve">2.16019153594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14470601081848</t>
   </si>
   <si>
     <t xml:space="preserve">2.13696336746216</t>
@@ -1328,31 +1328,31 @@
     <t xml:space="preserve">2.16793394088745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17257928848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1524486541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10444474220276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09205627441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20664715766907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17103123664856</t>
+    <t xml:space="preserve">2.17257952690125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15244841575623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10444450378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09205651283264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20664691925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1710307598114</t>
   </si>
   <si>
     <t xml:space="preserve">2.19580745697021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18651628494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21748661994934</t>
+    <t xml:space="preserve">2.18651604652405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2174870967865</t>
   </si>
   <si>
     <t xml:space="preserve">2.21593832969666</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">2.1834192276001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16328835487366</t>
+    <t xml:space="preserve">2.16328811645508</t>
   </si>
   <si>
     <t xml:space="preserve">2.15090036392212</t>
@@ -1370,10 +1370,10 @@
     <t xml:space="preserve">2.13231778144836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12612390518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11992979049683</t>
+    <t xml:space="preserve">2.12612366676331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11992955207825</t>
   </si>
   <si>
     <t xml:space="preserve">2.16638541221619</t>
@@ -1397,34 +1397,34 @@
     <t xml:space="preserve">2.10754132270813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12457513809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12767219543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18806481361389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20045304298401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19735550880432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20200133323669</t>
+    <t xml:space="preserve">2.12457489967346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12767243385315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18806505203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20045280456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19735598564148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20200157165527</t>
   </si>
   <si>
     <t xml:space="preserve">2.20819544792175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21129250526428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1756763458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12147808074951</t>
+    <t xml:space="preserve">2.21129274368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17567658424377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12147831916809</t>
   </si>
   <si>
     <t xml:space="preserve">2.11683249473572</t>
@@ -1439,25 +1439,25 @@
     <t xml:space="preserve">2.05179476737976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01463007926941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96198010444641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98211097717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93720400333405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90313625335693</t>
+    <t xml:space="preserve">2.01462984085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96197998523712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98211085796356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93720376491547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90313637256622</t>
   </si>
   <si>
     <t xml:space="preserve">1.86287462711334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91552460193634</t>
+    <t xml:space="preserve">1.91552436351776</t>
   </si>
   <si>
     <t xml:space="preserve">1.87216591835022</t>
@@ -1466,85 +1466,85 @@
     <t xml:space="preserve">1.89384520053864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90158784389496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87061679363251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85977756977081</t>
+    <t xml:space="preserve">1.90158808231354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87061738967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85977792739868</t>
   </si>
   <si>
     <t xml:space="preserve">1.92791259288788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89694237709045</t>
+    <t xml:space="preserve">1.89694225788116</t>
   </si>
   <si>
     <t xml:space="preserve">1.89074814319611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87990856170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88919961452484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88765120506287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90468513965607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92171859741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96662557125092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.918621301651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97901380062103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96972274780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97746562957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94184935092926</t>
+    <t xml:space="preserve">1.87990844249725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88919973373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88765108585358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90468466281891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92171847820282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96662592887878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91862142086029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97901391983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96972250938416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97746539115906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94184947013855</t>
   </si>
   <si>
     <t xml:space="preserve">1.9310097694397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92481577396393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92017006874084</t>
+    <t xml:space="preserve">1.92481553554535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92017018795013</t>
   </si>
   <si>
     <t xml:space="preserve">1.89229667186737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90933036804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87836015224457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93875229358673</t>
+    <t xml:space="preserve">1.90933048725128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87835991382599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93875253200531</t>
   </si>
   <si>
     <t xml:space="preserve">1.8690687417984</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94804334640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98675656318665</t>
+    <t xml:space="preserve">1.94804346561432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98675668239594</t>
   </si>
   <si>
     <t xml:space="preserve">2.09360480308533</t>
@@ -1553,10 +1553,10 @@
     <t xml:space="preserve">2.03630948066711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06573128700256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09825086593628</t>
+    <t xml:space="preserve">2.06573104858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09825015068054</t>
   </si>
   <si>
     <t xml:space="preserve">2.08276510238647</t>
@@ -1565,16 +1565,16 @@
     <t xml:space="preserve">2.19116163253784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19425916671753</t>
+    <t xml:space="preserve">2.19425868988037</t>
   </si>
   <si>
     <t xml:space="preserve">2.1787736415863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20509886741638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20974397659302</t>
+    <t xml:space="preserve">2.2050986289978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2097442150116</t>
   </si>
   <si>
     <t xml:space="preserve">2.22987508773804</t>
@@ -1583,70 +1583,70 @@
     <t xml:space="preserve">2.20354986190796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19890475273132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22677755355835</t>
+    <t xml:space="preserve">2.19890451431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22677803039551</t>
   </si>
   <si>
     <t xml:space="preserve">2.26084542274475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26239371299744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28562164306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29336428642273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28252458572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28407335281372</t>
+    <t xml:space="preserve">2.26239395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28562188148499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29336452484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28252482414246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2840735912323</t>
   </si>
   <si>
     <t xml:space="preserve">2.2902672290802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27013611793518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25619959831238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28097605705261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3026556968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30110692977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30730080604553</t>
+    <t xml:space="preserve">2.27013635635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25619983673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28097653388977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30265522003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30110669136047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30730128288269</t>
   </si>
   <si>
     <t xml:space="preserve">2.29800987243652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28871917724609</t>
+    <t xml:space="preserve">2.28871870040894</t>
   </si>
   <si>
     <t xml:space="preserve">2.25929689407349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32433485984802</t>
+    <t xml:space="preserve">2.32433462142944</t>
   </si>
   <si>
     <t xml:space="preserve">2.29181599617004</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25465130805969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2685878276825</t>
+    <t xml:space="preserve">2.25465106964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26858806610107</t>
   </si>
   <si>
     <t xml:space="preserve">2.26549124717712</t>
@@ -1655,130 +1655,130 @@
     <t xml:space="preserve">2.29955840110779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29646158218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31349515914917</t>
+    <t xml:space="preserve">2.29646134376526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31349492073059</t>
   </si>
   <si>
     <t xml:space="preserve">2.32123804092407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25774836540222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23916602134705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34446573257446</t>
+    <t xml:space="preserve">2.25774812698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23916625976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34446597099304</t>
   </si>
   <si>
     <t xml:space="preserve">2.38008165359497</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38163042068481</t>
+    <t xml:space="preserve">2.38162994384766</t>
   </si>
   <si>
     <t xml:space="preserve">2.40330958366394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4280858039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43118333816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4760901927948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49467277526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49002718925476</t>
+    <t xml:space="preserve">2.42808604240417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43118286132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47609043121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49467253684998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49002695083618</t>
   </si>
   <si>
     <t xml:space="preserve">2.49622106552124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50860953330994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54887104034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52099752426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50241541862488</t>
+    <t xml:space="preserve">2.50860929489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54887080192566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52099776268005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5024151802063</t>
   </si>
   <si>
     <t xml:space="preserve">2.5163516998291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.462153673172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47918701171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46525049209595</t>
+    <t xml:space="preserve">2.46215343475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47918725013733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46525073051453</t>
   </si>
   <si>
     <t xml:space="preserve">2.43428015708923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4497652053833</t>
+    <t xml:space="preserve">2.44976496696472</t>
   </si>
   <si>
     <t xml:space="preserve">2.45286226272583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46679902076721</t>
+    <t xml:space="preserve">2.46679925918579</t>
   </si>
   <si>
     <t xml:space="preserve">2.44666838645935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4575080871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47144460678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45905637741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42653751373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44821691513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42963457107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48692965507507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53028845787048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53803110122681</t>
+    <t xml:space="preserve">2.45750832557678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47144484519958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45905661582947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42653775215149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44821715354919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42963433265686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48692989349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5302882194519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53803133964539</t>
   </si>
   <si>
     <t xml:space="preserve">2.54112839698792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54422545433044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55661368370056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55816221237183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53648281097412</t>
+    <t xml:space="preserve">2.54422521591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55661344528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55816173553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53648257255554</t>
   </si>
   <si>
     <t xml:space="preserve">2.53493404388428</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">2.5287401676178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51790022850037</t>
+    <t xml:space="preserve">2.51790046691895</t>
   </si>
   <si>
     <t xml:space="preserve">2.56435608863831</t>
@@ -1796,55 +1796,55 @@
     <t xml:space="preserve">2.5906810760498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6030695438385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60461807250977</t>
+    <t xml:space="preserve">2.60306930541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60461783409119</t>
   </si>
   <si>
     <t xml:space="preserve">2.59997224807739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60152053833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58913254737854</t>
+    <t xml:space="preserve">2.60152101516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58913278579712</t>
   </si>
   <si>
     <t xml:space="preserve">2.58603549003601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64642786979675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65262198448181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68514084815979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71611142158508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69698429107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67945027351379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68263840675354</t>
+    <t xml:space="preserve">2.64642810821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65262222290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68514132499695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71611166000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69698405265808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67945051193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68263816833496</t>
   </si>
   <si>
     <t xml:space="preserve">2.65075922012329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68104434013367</t>
+    <t xml:space="preserve">2.68104457855225</t>
   </si>
   <si>
     <t xml:space="preserve">2.66669869422913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73045706748962</t>
+    <t xml:space="preserve">2.73045754432678</t>
   </si>
   <si>
     <t xml:space="preserve">2.81174921989441</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">2.79740357398987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79580974578857</t>
+    <t xml:space="preserve">2.79580950737</t>
   </si>
   <si>
     <t xml:space="preserve">2.82768869400024</t>
@@ -1874,16 +1874,16 @@
     <t xml:space="preserve">2.80696749687195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75914859771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74480295181274</t>
+    <t xml:space="preserve">2.75914835929871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74480271339417</t>
   </si>
   <si>
     <t xml:space="preserve">2.74958467483521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73205137252808</t>
+    <t xml:space="preserve">2.7320511341095</t>
   </si>
   <si>
     <t xml:space="preserve">2.72886323928833</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">2.73683333396912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7113299369812</t>
+    <t xml:space="preserve">2.71132946014404</t>
   </si>
   <si>
     <t xml:space="preserve">2.69538998603821</t>
@@ -1913,10 +1913,10 @@
     <t xml:space="preserve">2.72726917266846</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70495367050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73523902893066</t>
+    <t xml:space="preserve">2.70495390892029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73523926734924</t>
   </si>
   <si>
     <t xml:space="preserve">2.687420129776</t>
@@ -1928,13 +1928,13 @@
     <t xml:space="preserve">2.78783988952637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77827596664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78624582290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81334328651428</t>
+    <t xml:space="preserve">2.77827620506287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78624606132507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8133430480957</t>
   </si>
   <si>
     <t xml:space="preserve">2.88188362121582</t>
@@ -1943,61 +1943,61 @@
     <t xml:space="preserve">2.87869572639465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91535687446594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8914475440979</t>
+    <t xml:space="preserve">2.91535711288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89144730567932</t>
   </si>
   <si>
     <t xml:space="preserve">2.88666558265686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88825941085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91695070266724</t>
+    <t xml:space="preserve">2.88825964927673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91695094108582</t>
   </si>
   <si>
     <t xml:space="preserve">2.89622902870178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80059146881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79262208938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84522223472595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8181254863739</t>
+    <t xml:space="preserve">2.80059123039246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79262185096741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84522247314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81812524795532</t>
   </si>
   <si>
     <t xml:space="preserve">2.82131314277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8468165397644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90738701820374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90419888496399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86913204193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95201778411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95042419433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02055811882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96476984024048</t>
+    <t xml:space="preserve">2.84681630134583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90738677978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90419912338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86913180351257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95201826095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95042371749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02055835723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9647696018219</t>
   </si>
   <si>
     <t xml:space="preserve">3.00143098831177</t>
@@ -2012,16 +2012,16 @@
     <t xml:space="preserve">3.01577639579773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02215242385864</t>
+    <t xml:space="preserve">3.02215194702148</t>
   </si>
   <si>
     <t xml:space="preserve">3.00461864471436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97911524772644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0030243396759</t>
+    <t xml:space="preserve">2.97911500930786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00302481651306</t>
   </si>
   <si>
     <t xml:space="preserve">3.01418256759644</t>
@@ -2039,10 +2039,10 @@
     <t xml:space="preserve">2.96636343002319</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99346137046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00621294975281</t>
+    <t xml:space="preserve">2.99346089363098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00621271133423</t>
   </si>
   <si>
     <t xml:space="preserve">3.04606175422668</t>
@@ -2051,76 +2051,76 @@
     <t xml:space="preserve">3.05881333351135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04924964904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06997108459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03012228012085</t>
+    <t xml:space="preserve">3.04924941062927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06997132301331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03012204170227</t>
   </si>
   <si>
     <t xml:space="preserve">3.05403184890747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06678318977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05243754386902</t>
+    <t xml:space="preserve">3.06678342819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0524377822876</t>
   </si>
   <si>
     <t xml:space="preserve">3.07315897941589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07475328445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10025668144226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17357897758484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19748830795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19430041313171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21820950508118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19589424133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16242074966431</t>
+    <t xml:space="preserve">3.07475304603577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10025644302368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17357873916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1974880695343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19430017471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21820974349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19589447975159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16242098808289</t>
   </si>
   <si>
     <t xml:space="preserve">3.17995452880859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15604543685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18473649024963</t>
+    <t xml:space="preserve">3.15604519844055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18473672866821</t>
   </si>
   <si>
     <t xml:space="preserve">3.17517256736755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19111227989197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0620014667511</t>
+    <t xml:space="preserve">3.19111251831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06200122833252</t>
   </si>
   <si>
     <t xml:space="preserve">3.08750486373901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12416577339172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10185027122498</t>
+    <t xml:space="preserve">3.1241660118103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1018500328064</t>
   </si>
   <si>
     <t xml:space="preserve">3.09547472000122</t>
@@ -2129,28 +2129,28 @@
     <t xml:space="preserve">3.0715651512146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10344433784485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11141443252563</t>
+    <t xml:space="preserve">3.10344457626343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11141419410706</t>
   </si>
   <si>
     <t xml:space="preserve">3.06040716171265</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12735390663147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17198491096497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1687970161438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16401505470276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22139716148376</t>
+    <t xml:space="preserve">3.12735366821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17198467254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16879677772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16401481628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22139739990234</t>
   </si>
   <si>
     <t xml:space="preserve">3.16082692146301</t>
@@ -2159,7 +2159,7 @@
     <t xml:space="preserve">3.16560888290405</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10822653770447</t>
+    <t xml:space="preserve">3.10822629928589</t>
   </si>
   <si>
     <t xml:space="preserve">3.09706854820251</t>
@@ -2168,37 +2168,37 @@
     <t xml:space="preserve">3.10663223266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08112859725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07794094085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14329361915588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18633055686951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18314218521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13213562965393</t>
+    <t xml:space="preserve">3.0811288356781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07794070243835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1432933807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18633031845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18314266204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13213586807251</t>
   </si>
   <si>
     <t xml:space="preserve">3.27240419387817</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37760615348816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3138473033905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44774007797241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44614624977112</t>
+    <t xml:space="preserve">3.37760591506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31384706497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44774055480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44614601135254</t>
   </si>
   <si>
     <t xml:space="preserve">3.37919974327087</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">3.26921653747559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27718615531921</t>
+    <t xml:space="preserve">3.27718639373779</t>
   </si>
   <si>
     <t xml:space="preserve">3.28675007820129</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">3.33297514915466</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37282395362854</t>
+    <t xml:space="preserve">3.37282419204712</t>
   </si>
   <si>
     <t xml:space="preserve">3.38557577133179</t>
@@ -2228,7 +2228,7 @@
     <t xml:space="preserve">3.42701888084412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43976998329163</t>
+    <t xml:space="preserve">3.43977022171021</t>
   </si>
   <si>
     <t xml:space="preserve">3.47802519798279</t>
@@ -2237,58 +2237,58 @@
     <t xml:space="preserve">3.45252180099487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45730376243591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47005534172058</t>
+    <t xml:space="preserve">3.45730400085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47005605697632</t>
   </si>
   <si>
     <t xml:space="preserve">3.55612969398499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53700256347656</t>
+    <t xml:space="preserve">3.5370020866394</t>
   </si>
   <si>
     <t xml:space="preserve">3.51628088951111</t>
   </si>
   <si>
-    <t xml:space="preserve">3.339350938797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30906534194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33775663375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27877974510193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09069299697876</t>
+    <t xml:space="preserve">3.33935046195984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30906510353088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3377571105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27878022193909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09069275856018</t>
   </si>
   <si>
     <t xml:space="preserve">3.11300802230835</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2612464427948</t>
+    <t xml:space="preserve">3.26124668121338</t>
   </si>
   <si>
     <t xml:space="preserve">2.83247089385986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6587290763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69060802459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2203893661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55830931663513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46585941314697</t>
+    <t xml:space="preserve">2.65872859954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69060826301575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22038960456848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55830907821655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46585917472839</t>
   </si>
   <si>
     <t xml:space="preserve">2.51049041748047</t>
@@ -2300,31 +2300,31 @@
     <t xml:space="preserve">2.46107769012451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58381247520447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44195008277893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41804051399231</t>
+    <t xml:space="preserve">2.58381295204163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44195032119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41804075241089</t>
   </si>
   <si>
     <t xml:space="preserve">2.44035625457764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50252032279968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62206768989563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60453414916992</t>
+    <t xml:space="preserve">2.50252056121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62206792831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60453391075134</t>
   </si>
   <si>
     <t xml:space="preserve">2.52802395820618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56468534469604</t>
+    <t xml:space="preserve">2.56468486785889</t>
   </si>
   <si>
     <t xml:space="preserve">2.53121209144592</t>
@@ -2339,7 +2339,7 @@
     <t xml:space="preserve">2.57584309577942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56787300109863</t>
+    <t xml:space="preserve">2.56787276268005</t>
   </si>
   <si>
     <t xml:space="preserve">2.54715156555176</t>
@@ -2348,31 +2348,31 @@
     <t xml:space="preserve">2.54396367073059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60772228240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62047362327576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51846051216125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59018850326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5806245803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67307448387146</t>
+    <t xml:space="preserve">2.60772204399109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62047386169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5184600353241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5901882648468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58062481880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67307472229004</t>
   </si>
   <si>
     <t xml:space="preserve">2.69220209121704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57903099060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57265496253967</t>
+    <t xml:space="preserve">2.57903075218201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57265472412109</t>
   </si>
   <si>
     <t xml:space="preserve">2.52483582496643</t>
@@ -2381,10 +2381,10 @@
     <t xml:space="preserve">2.49295711517334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59178233146667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61888003349304</t>
+    <t xml:space="preserve">2.59178256988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61887955665588</t>
   </si>
   <si>
     <t xml:space="preserve">2.56149697303772</t>
@@ -2405,16 +2405,16 @@
     <t xml:space="preserve">2.55352735519409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54874539375305</t>
+    <t xml:space="preserve">2.54874563217163</t>
   </si>
   <si>
     <t xml:space="preserve">2.65713500976562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66032290458679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85159850120544</t>
+    <t xml:space="preserve">2.66032266616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85159826278687</t>
   </si>
   <si>
     <t xml:space="preserve">2.85638022422791</t>
@@ -2423,64 +2423,64 @@
     <t xml:space="preserve">2.81653118133545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77668213844299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6778564453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80218529701233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78943371772766</t>
+    <t xml:space="preserve">2.77668237686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67785668373108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80218553543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78943395614624</t>
   </si>
   <si>
     <t xml:space="preserve">2.77030634880066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75755476951599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75436663627625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68901443481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63800764083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70335984230042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70017194747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72567534446716</t>
+    <t xml:space="preserve">2.75755453109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75436639785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68901419639587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63800740242004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70335936546326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70017170906067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72567510604858</t>
   </si>
   <si>
     <t xml:space="preserve">2.74209499359131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6994035243988</t>
+    <t xml:space="preserve">2.69940376281738</t>
   </si>
   <si>
     <t xml:space="preserve">2.71418142318726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64193487167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63372492790222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67477440834045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63865041732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65014457702637</t>
+    <t xml:space="preserve">2.641934633255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63372468948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67477416992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63865065574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65014433860779</t>
   </si>
   <si>
     <t xml:space="preserve">2.69447803497314</t>
@@ -2498,28 +2498,28 @@
     <t xml:space="preserve">2.76508259773254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6616382598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61894726753235</t>
+    <t xml:space="preserve">2.66163849830627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61894702911377</t>
   </si>
   <si>
     <t xml:space="preserve">2.63536691665649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70268774032593</t>
+    <t xml:space="preserve">2.70268797874451</t>
   </si>
   <si>
     <t xml:space="preserve">2.68790984153748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59267544746399</t>
+    <t xml:space="preserve">2.59267568588257</t>
   </si>
   <si>
     <t xml:space="preserve">2.61073732376099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60252737998962</t>
+    <t xml:space="preserve">2.6025276184082</t>
   </si>
   <si>
     <t xml:space="preserve">2.59595942497253</t>
@@ -2528,25 +2528,25 @@
     <t xml:space="preserve">2.58774948120117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66820621490479</t>
+    <t xml:space="preserve">2.66820645332336</t>
   </si>
   <si>
     <t xml:space="preserve">2.72403335571289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78642821311951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77657651901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75851488113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66656446456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70925569534302</t>
+    <t xml:space="preserve">2.78642845153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77657628059387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75851464271545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66656422615051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70925545692444</t>
   </si>
   <si>
     <t xml:space="preserve">2.68298387527466</t>
@@ -2555,10 +2555,10 @@
     <t xml:space="preserve">2.66328024864197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75030493736267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72239112854004</t>
+    <t xml:space="preserve">2.75030517578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7223916053772</t>
   </si>
   <si>
     <t xml:space="preserve">2.64686036109924</t>
@@ -2567,7 +2567,7 @@
     <t xml:space="preserve">2.62715697288513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6287989616394</t>
+    <t xml:space="preserve">2.62879872322083</t>
   </si>
   <si>
     <t xml:space="preserve">2.6156632900238</t>
@@ -2579,34 +2579,34 @@
     <t xml:space="preserve">2.59760141372681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64850282669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64029264450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68134212493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66492247581482</t>
+    <t xml:space="preserve">2.64850258827209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64029312133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68134188652039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66492223739624</t>
   </si>
   <si>
     <t xml:space="preserve">2.67970013618469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69776201248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71253967285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63700890541077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62387299537659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60745334625244</t>
+    <t xml:space="preserve">2.69776153564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71253943443298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63700866699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62387347221375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60745310783386</t>
   </si>
   <si>
     <t xml:space="preserve">2.64521861076355</t>
@@ -2615,13 +2615,13 @@
     <t xml:space="preserve">2.63044095039368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54998421669006</t>
+    <t xml:space="preserve">2.54998397827148</t>
   </si>
   <si>
     <t xml:space="preserve">2.55819392204285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54505848884583</t>
+    <t xml:space="preserve">2.54505825042725</t>
   </si>
   <si>
     <t xml:space="preserve">2.51386094093323</t>
@@ -2633,10 +2633,10 @@
     <t xml:space="preserve">2.50236701965332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47281169891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42191052436829</t>
+    <t xml:space="preserve">2.472811460495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42191028594971</t>
   </si>
   <si>
     <t xml:space="preserve">2.44325613975525</t>
@@ -2645,16 +2645,16 @@
     <t xml:space="preserve">2.35951542854309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38414525985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41205811500549</t>
+    <t xml:space="preserve">2.38414478302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41205835342407</t>
   </si>
   <si>
     <t xml:space="preserve">2.46295952796936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39563870429993</t>
+    <t xml:space="preserve">2.39563894271851</t>
   </si>
   <si>
     <t xml:space="preserve">2.37593531608582</t>
@@ -2663,118 +2663,118 @@
     <t xml:space="preserve">2.37757682800293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31518197059631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29219460487366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23472499847412</t>
+    <t xml:space="preserve">2.31518173217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29219436645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2347252368927</t>
   </si>
   <si>
     <t xml:space="preserve">2.19695997238159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21666383743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23636746406555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25442934036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31025576591492</t>
+    <t xml:space="preserve">2.21666359901428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23636698722839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25442886352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3102560043335</t>
   </si>
   <si>
     <t xml:space="preserve">2.30533027648926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28070068359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.454749584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42519426345825</t>
+    <t xml:space="preserve">2.28070092201233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45475006103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42519450187683</t>
   </si>
   <si>
     <t xml:space="preserve">2.44982385635376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49251508712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47937941551208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56147789955139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50893497467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49579882621765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50400876998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48102140426636</t>
+    <t xml:space="preserve">2.49251532554626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47937917709351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56147813796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50893473625183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49579906463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50400900840759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48102116584778</t>
   </si>
   <si>
     <t xml:space="preserve">2.47609543800354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52207064628601</t>
+    <t xml:space="preserve">2.52207088470459</t>
   </si>
   <si>
     <t xml:space="preserve">2.53520655632019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51221895217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47116947174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43997192382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46788597106934</t>
+    <t xml:space="preserve">2.51221871376038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4711697101593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4399721622467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46788549423218</t>
   </si>
   <si>
     <t xml:space="preserve">2.44489789009094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43012022972107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41534209251404</t>
+    <t xml:space="preserve">2.43011999130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4153425693512</t>
   </si>
   <si>
     <t xml:space="preserve">2.38907098770142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36444115638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39399647712708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3660831451416</t>
+    <t xml:space="preserve">2.36444139480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39399695396423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36608338356018</t>
   </si>
   <si>
     <t xml:space="preserve">2.40384840965271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45146608352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33981156349182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38742899894714</t>
+    <t xml:space="preserve">2.45146560668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3398118019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38742876052856</t>
   </si>
   <si>
     <t xml:space="preserve">2.45310759544373</t>
@@ -2789,25 +2789,25 @@
     <t xml:space="preserve">2.50565123558044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44161367416382</t>
+    <t xml:space="preserve">2.4416139125824</t>
   </si>
   <si>
     <t xml:space="preserve">2.49087309837341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48594737052917</t>
+    <t xml:space="preserve">2.48594760894775</t>
   </si>
   <si>
     <t xml:space="preserve">2.59431767463684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5417742729187</t>
+    <t xml:space="preserve">2.54177451133728</t>
   </si>
   <si>
     <t xml:space="preserve">2.38086104393005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33652758598328</t>
+    <t xml:space="preserve">2.33652782440186</t>
   </si>
   <si>
     <t xml:space="preserve">2.35787343978882</t>
@@ -2837,28 +2837,28 @@
     <t xml:space="preserve">2.55491018295288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58939170837402</t>
+    <t xml:space="preserve">2.58939146995544</t>
   </si>
   <si>
     <t xml:space="preserve">2.54670023918152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53684830665588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52535438537598</t>
+    <t xml:space="preserve">2.53684854507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52535462379456</t>
   </si>
   <si>
     <t xml:space="preserve">2.43176198005676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40220665931702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52863836288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56311964988708</t>
+    <t xml:space="preserve">2.40220642089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5286386013031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56312012672424</t>
   </si>
   <si>
     <t xml:space="preserve">2.56968808174133</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">2.71582365036011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68216300010681</t>
+    <t xml:space="preserve">2.68216276168823</t>
   </si>
   <si>
     <t xml:space="preserve">2.72895908355713</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">2.70843482017517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69612002372742</t>
+    <t xml:space="preserve">2.69611954689026</t>
   </si>
   <si>
     <t xml:space="preserve">2.71171832084656</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">2.73224329948425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76918768882751</t>
+    <t xml:space="preserve">2.76918745040894</t>
   </si>
   <si>
     <t xml:space="preserve">2.76097774505615</t>
@@ -2897,19 +2897,19 @@
     <t xml:space="preserve">2.75441002845764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75523114204407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75605154037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74620032310486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79381704330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76261973381042</t>
+    <t xml:space="preserve">2.75523066520691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75605201721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74620008468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79381728172302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76261949539185</t>
   </si>
   <si>
     <t xml:space="preserve">2.76672458648682</t>
@@ -2918,22 +2918,22 @@
     <t xml:space="preserve">2.79710125923157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8381507396698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77082967758179</t>
+    <t xml:space="preserve">2.83815050125122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77082943916321</t>
   </si>
   <si>
     <t xml:space="preserve">2.77247166633606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7642617225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86277985572815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83240342140198</t>
+    <t xml:space="preserve">2.76426196098328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86278009414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83240389823914</t>
   </si>
   <si>
     <t xml:space="preserve">2.82255172729492</t>
@@ -2954,22 +2954,22 @@
     <t xml:space="preserve">2.88248372077942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86524319648743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86113810539246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86606383323669</t>
+    <t xml:space="preserve">2.86524295806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86113786697388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86606407165527</t>
   </si>
   <si>
     <t xml:space="preserve">2.86360096931458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87427353858948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89726161956787</t>
+    <t xml:space="preserve">2.87427401542664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89726138114929</t>
   </si>
   <si>
     <t xml:space="preserve">2.93256402015686</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">3.04093408584595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01794648170471</t>
+    <t xml:space="preserve">3.01794672012329</t>
   </si>
   <si>
     <t xml:space="preserve">3.04586029052734</t>
@@ -3005,13 +3005,13 @@
     <t xml:space="preserve">3.00727367401123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98921227455139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95801448822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90218758583069</t>
+    <t xml:space="preserve">2.98921203613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95801424980164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90218782424927</t>
   </si>
   <si>
     <t xml:space="preserve">2.92353320121765</t>
@@ -3026,28 +3026,28 @@
     <t xml:space="preserve">2.89151477813721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86688494682312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89479851722717</t>
+    <t xml:space="preserve">2.8668851852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89479827880859</t>
   </si>
   <si>
     <t xml:space="preserve">2.90920472145081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89649319648743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96005058288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86598634719849</t>
+    <t xml:space="preserve">2.89649343490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96005034446716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86598610877991</t>
   </si>
   <si>
     <t xml:space="preserve">2.86429142951965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9320855140686</t>
+    <t xml:space="preserve">2.93208527565002</t>
   </si>
   <si>
     <t xml:space="preserve">2.93293261528015</t>
@@ -3059,13 +3059,13 @@
     <t xml:space="preserve">2.89564609527588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9261531829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84225845336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85073256492615</t>
+    <t xml:space="preserve">2.92615342140198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84225821495056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85073280334473</t>
   </si>
   <si>
     <t xml:space="preserve">2.94733881950378</t>
@@ -3083,13 +3083,13 @@
     <t xml:space="preserve">3.03292846679688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0642831325531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04055547714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04479241371155</t>
+    <t xml:space="preserve">3.06428337097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04055571556091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04479265213013</t>
   </si>
   <si>
     <t xml:space="preserve">3.02275943756104</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">3.00157403945923</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0202169418335</t>
+    <t xml:space="preserve">3.02021718025208</t>
   </si>
   <si>
     <t xml:space="preserve">3.04648756980896</t>
@@ -3110,25 +3110,25 @@
     <t xml:space="preserve">3.03547096252441</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08546876907349</t>
+    <t xml:space="preserve">3.08546900749207</t>
   </si>
   <si>
     <t xml:space="preserve">3.09733271598816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13122987747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14563608169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1566526889801</t>
+    <t xml:space="preserve">3.13122963905334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14563584327698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15665245056152</t>
   </si>
   <si>
     <t xml:space="preserve">3.18038034439087</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19648146629333</t>
+    <t xml:space="preserve">3.19648122787476</t>
   </si>
   <si>
     <t xml:space="preserve">3.18546485900879</t>
@@ -3137,7 +3137,7 @@
     <t xml:space="preserve">3.18715977668762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16682147979736</t>
+    <t xml:space="preserve">3.16682171821594</t>
   </si>
   <si>
     <t xml:space="preserve">3.12953495979309</t>
@@ -3146,7 +3146,7 @@
     <t xml:space="preserve">3.10157012939453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11597609519958</t>
+    <t xml:space="preserve">3.11597633361816</t>
   </si>
   <si>
     <t xml:space="preserve">3.11089158058167</t>
@@ -3155,10 +3155,10 @@
     <t xml:space="preserve">3.10411238670349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13716149330139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12275528907776</t>
+    <t xml:space="preserve">3.13716173171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12275552749634</t>
   </si>
   <si>
     <t xml:space="preserve">3.11004400253296</t>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">3.08123159408569</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03631806373596</t>
+    <t xml:space="preserve">3.03631830215454</t>
   </si>
   <si>
     <t xml:space="preserve">3.07360506057739</t>
@@ -3179,28 +3179,28 @@
     <t xml:space="preserve">3.09902763366699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04987740516663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08377408981323</t>
+    <t xml:space="preserve">3.04987716674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08377385139465</t>
   </si>
   <si>
     <t xml:space="preserve">3.04140281677246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08631610870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08292651176453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09224843978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02360701560974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9744565486908</t>
+    <t xml:space="preserve">3.08631634712219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08292675018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09224820137024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02360725402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97445631027222</t>
   </si>
   <si>
     <t xml:space="preserve">3.01428532600403</t>
@@ -3209,22 +3209,22 @@
     <t xml:space="preserve">2.99648952484131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9956419467926</t>
+    <t xml:space="preserve">2.99564218521118</t>
   </si>
   <si>
     <t xml:space="preserve">2.99818444252014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00411629676819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96089768409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98547315597534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91089963912964</t>
+    <t xml:space="preserve">3.00411605834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96089792251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98547291755676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91089940071106</t>
   </si>
   <si>
     <t xml:space="preserve">2.87785005569458</t>
@@ -3236,10 +3236,10 @@
     <t xml:space="preserve">2.94564414024353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97530364990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95327067375183</t>
+    <t xml:space="preserve">2.97530388832092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95327091217041</t>
   </si>
   <si>
     <t xml:space="preserve">2.92445826530457</t>
@@ -3254,10 +3254,10 @@
     <t xml:space="preserve">3.03377604484558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04902982711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01767516136169</t>
+    <t xml:space="preserve">3.04902958869934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01767492294312</t>
   </si>
   <si>
     <t xml:space="preserve">3.05241942405701</t>
@@ -3266,13 +3266,13 @@
     <t xml:space="preserve">2.99733686447144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0125904083252</t>
+    <t xml:space="preserve">3.01259064674377</t>
   </si>
   <si>
     <t xml:space="preserve">2.9947943687439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03462362289429</t>
+    <t xml:space="preserve">3.03462338447571</t>
   </si>
   <si>
     <t xml:space="preserve">3.1125864982605</t>
@@ -3281,7 +3281,7 @@
     <t xml:space="preserve">3.09309577941895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0566565990448</t>
+    <t xml:space="preserve">3.05665683746338</t>
   </si>
   <si>
     <t xml:space="preserve">3.01682758331299</t>
@@ -3290,28 +3290,28 @@
     <t xml:space="preserve">3.05750393867493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06936764717102</t>
+    <t xml:space="preserve">3.06936740875244</t>
   </si>
   <si>
     <t xml:space="preserve">3.07275748252869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03208136558533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02953863143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0007266998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85581684112549</t>
+    <t xml:space="preserve">3.03208112716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02953886985779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00072646141052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85581707954407</t>
   </si>
   <si>
     <t xml:space="preserve">2.8702232837677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88547682762146</t>
+    <t xml:space="preserve">2.88547706604004</t>
   </si>
   <si>
     <t xml:space="preserve">2.95750784873962</t>
@@ -3320,73 +3320,73 @@
     <t xml:space="preserve">2.88971424102783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02530193328857</t>
+    <t xml:space="preserve">3.02530169487</t>
   </si>
   <si>
     <t xml:space="preserve">2.98208332061768</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00835347175598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97869348526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0032684803009</t>
+    <t xml:space="preserve">3.0083532333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97869372367859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00326871871948</t>
   </si>
   <si>
     <t xml:space="preserve">3.02445459365845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04563999176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05072450637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06089353561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11682367324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10241723060608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14055156707764</t>
+    <t xml:space="preserve">3.04564023017883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05072426795959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06089377403259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11682343482971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10241746902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14055132865906</t>
   </si>
   <si>
     <t xml:space="preserve">3.11173892021179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08716368675232</t>
+    <t xml:space="preserve">3.0871639251709</t>
   </si>
   <si>
     <t xml:space="preserve">3.02699661254883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0134379863739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99394726753235</t>
+    <t xml:space="preserve">3.01343774795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99394750595093</t>
   </si>
   <si>
     <t xml:space="preserve">2.97106671333313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98123550415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94903373718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9083571434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91767930984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97360920906067</t>
+    <t xml:space="preserve">2.98123574256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9490339756012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90835738182068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91767907142639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97360873222351</t>
   </si>
   <si>
     <t xml:space="preserve">3.07614731788635</t>
@@ -3395,16 +3395,16 @@
     <t xml:space="preserve">3.14817810058594</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1337718963623</t>
+    <t xml:space="preserve">3.13377213478088</t>
   </si>
   <si>
     <t xml:space="preserve">3.07021522521973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9388644695282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88039255142212</t>
+    <t xml:space="preserve">2.93886470794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88039231300354</t>
   </si>
   <si>
     <t xml:space="preserve">2.9185266494751</t>
@@ -3413,34 +3413,34 @@
     <t xml:space="preserve">2.93801712989807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92530584335327</t>
+    <t xml:space="preserve">2.92530560493469</t>
   </si>
   <si>
     <t xml:space="preserve">2.86005425453186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88717198371887</t>
+    <t xml:space="preserve">2.88717174530029</t>
   </si>
   <si>
     <t xml:space="preserve">2.87276554107666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84310555458069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83802151679993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79734516143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8083610534668</t>
+    <t xml:space="preserve">2.84310579299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83802127838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79734492301941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80836153030396</t>
   </si>
   <si>
     <t xml:space="preserve">2.82446241378784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.740567445755</t>
+    <t xml:space="preserve">2.74056768417358</t>
   </si>
   <si>
     <t xml:space="preserve">2.93632221221924</t>
@@ -3449,49 +3449,49 @@
     <t xml:space="preserve">2.83208918571472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78971791267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7626006603241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69904375076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71175503730774</t>
+    <t xml:space="preserve">2.78971838951111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76260042190552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69904351234436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71175527572632</t>
   </si>
   <si>
     <t xml:space="preserve">2.77446436882019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87700295448303</t>
+    <t xml:space="preserve">2.87700271606445</t>
   </si>
   <si>
     <t xml:space="preserve">2.86344385147095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85666441917419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85158014297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81937766075134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85412240028381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89140892028809</t>
+    <t xml:space="preserve">2.85666465759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85157990455627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81937789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85412216186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89140868186951</t>
   </si>
   <si>
     <t xml:space="preserve">2.7880232334137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75666856765747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81429362297058</t>
+    <t xml:space="preserve">2.75666880607605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.814293384552</t>
   </si>
   <si>
     <t xml:space="preserve">2.82700490951538</t>
@@ -3500,16 +3500,16 @@
     <t xml:space="preserve">2.85327506065369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83547902107239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87615537643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90751004219055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00581097602844</t>
+    <t xml:space="preserve">2.83547878265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87615513801575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90750980377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00581121444702</t>
   </si>
   <si>
     <t xml:space="preserve">3.04733467102051</t>
@@ -3518,40 +3518,40 @@
     <t xml:space="preserve">3.00496363639832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04394483566284</t>
+    <t xml:space="preserve">3.04394507408142</t>
   </si>
   <si>
     <t xml:space="preserve">3.05835127830505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01598000526428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04818224906921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97276163101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98377823829651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95242357254028</t>
+    <t xml:space="preserve">3.01598024368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04818201065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97276139259338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98377799987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9524233341217</t>
   </si>
   <si>
     <t xml:space="preserve">2.98632025718689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06343603134155</t>
+    <t xml:space="preserve">3.06343579292297</t>
   </si>
   <si>
     <t xml:space="preserve">2.84141087532043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86513876914978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92954277992249</t>
+    <t xml:space="preserve">2.86513900756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92954301834106</t>
   </si>
   <si>
     <t xml:space="preserve">2.95072865486145</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">3.03801321983337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98801517486572</t>
+    <t xml:space="preserve">2.98801493644714</t>
   </si>
   <si>
     <t xml:space="preserve">2.96598219871521</t>
@@ -3572,10 +3572,10 @@
     <t xml:space="preserve">2.86683368682861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82785224914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86174917221069</t>
+    <t xml:space="preserve">2.82785201072693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86174893379211</t>
   </si>
   <si>
     <t xml:space="preserve">2.83717393875122</t>
@@ -3587,22 +3587,22 @@
     <t xml:space="preserve">2.7270085811615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53125405311584</t>
+    <t xml:space="preserve">2.53125381469727</t>
   </si>
   <si>
     <t xml:space="preserve">2.41685175895691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35668444633484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45837545394897</t>
+    <t xml:space="preserve">2.35668468475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45837569236755</t>
   </si>
   <si>
     <t xml:space="preserve">2.38888669013977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41769886016846</t>
+    <t xml:space="preserve">2.41769909858704</t>
   </si>
   <si>
     <t xml:space="preserve">2.3823139667511</t>
@@ -3611,7 +3611,7 @@
     <t xml:space="preserve">2.34250545501709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32569718360901</t>
+    <t xml:space="preserve">2.32569742202759</t>
   </si>
   <si>
     <t xml:space="preserve">2.37435221672058</t>
@@ -3620,19 +3620,19 @@
     <t xml:space="preserve">2.46193075180054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46812295913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49908518791199</t>
+    <t xml:space="preserve">2.46812319755554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49908542633057</t>
   </si>
   <si>
     <t xml:space="preserve">2.47608494758606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44158411026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48758506774902</t>
+    <t xml:space="preserve">2.44158434867859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4875853061676</t>
   </si>
   <si>
     <t xml:space="preserve">2.48493099212646</t>
@@ -3644,10 +3644,10 @@
     <t xml:space="preserve">2.45750784873962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49112367630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47696924209595</t>
+    <t xml:space="preserve">2.49112343788147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47696948051453</t>
   </si>
   <si>
     <t xml:space="preserve">2.45927667617798</t>
@@ -3662,13 +3662,13 @@
     <t xml:space="preserve">2.37789058685303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38673686981201</t>
+    <t xml:space="preserve">2.38673710823059</t>
   </si>
   <si>
     <t xml:space="preserve">2.41150689125061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38319826126099</t>
+    <t xml:space="preserve">2.38319849967957</t>
   </si>
   <si>
     <t xml:space="preserve">2.40619897842407</t>
@@ -3689,19 +3689,19 @@
     <t xml:space="preserve">2.44689202308655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50970077514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50527787208557</t>
+    <t xml:space="preserve">2.50970053672791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50527763366699</t>
   </si>
   <si>
     <t xml:space="preserve">2.47077703475952</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44246864318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43981504440308</t>
+    <t xml:space="preserve">2.44246888160706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4398148059845</t>
   </si>
   <si>
     <t xml:space="preserve">2.4433536529541</t>
@@ -3710,10 +3710,10 @@
     <t xml:space="preserve">2.46900773048401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47520041465759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44954609870911</t>
+    <t xml:space="preserve">2.47520017623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44954586029053</t>
   </si>
   <si>
     <t xml:space="preserve">2.43804574012756</t>
@@ -3725,7 +3725,7 @@
     <t xml:space="preserve">2.42300701141357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40442967414856</t>
+    <t xml:space="preserve">2.40442943572998</t>
   </si>
   <si>
     <t xml:space="preserve">2.36904430389404</t>
@@ -3734,10 +3734,10 @@
     <t xml:space="preserve">2.29650449752808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35312128067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2115797996521</t>
+    <t xml:space="preserve">2.35312104225159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21158003807068</t>
   </si>
   <si>
     <t xml:space="preserve">2.21246433258057</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">2.24342679977417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18504071235657</t>
+    <t xml:space="preserve">2.18504095077515</t>
   </si>
   <si>
     <t xml:space="preserve">2.07269263267517</t>
@@ -3755,13 +3755,13 @@
     <t xml:space="preserve">2.12842440605164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11603951454163</t>
+    <t xml:space="preserve">2.11603975296021</t>
   </si>
   <si>
     <t xml:space="preserve">2.2009642124176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25935006141663</t>
+    <t xml:space="preserve">2.25934982299805</t>
   </si>
   <si>
     <t xml:space="preserve">2.23015713691711</t>
@@ -3776,7 +3776,7 @@
     <t xml:space="preserve">2.11957812309265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10630869865417</t>
+    <t xml:space="preserve">2.1063084602356</t>
   </si>
   <si>
     <t xml:space="preserve">2.07800054550171</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">1.97803723812103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98422956466675</t>
+    <t xml:space="preserve">1.98422968387604</t>
   </si>
   <si>
     <t xml:space="preserve">1.87895834445953</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">1.92584371566772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91611266136169</t>
+    <t xml:space="preserve">1.9161125421524</t>
   </si>
   <si>
     <t xml:space="preserve">1.93380570411682</t>
@@ -3815,7 +3815,7 @@
     <t xml:space="preserve">1.90018951892853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84003448486328</t>
+    <t xml:space="preserve">1.84003436565399</t>
   </si>
   <si>
     <t xml:space="preserve">1.82588028907776</t>
@@ -3824,10 +3824,10 @@
     <t xml:space="preserve">1.87011194229126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80464923381805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77280235290527</t>
+    <t xml:space="preserve">1.80464911460876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77280247211456</t>
   </si>
   <si>
     <t xml:space="preserve">1.80022609233856</t>
@@ -3836,10 +3836,10 @@
     <t xml:space="preserve">1.83030343055725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87807369232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88249683380127</t>
+    <t xml:space="preserve">1.87807357311249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88249695301056</t>
   </si>
   <si>
     <t xml:space="preserve">1.8630348443985</t>
@@ -3854,13 +3854,13 @@
     <t xml:space="preserve">1.91257441043854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99838352203369</t>
+    <t xml:space="preserve">1.99838364124298</t>
   </si>
   <si>
     <t xml:space="preserve">2.01696085929871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12577056884766</t>
+    <t xml:space="preserve">2.12577080726624</t>
   </si>
   <si>
     <t xml:space="preserve">2.13373231887817</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">2.14257836341858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13196325302124</t>
+    <t xml:space="preserve">2.13196301460266</t>
   </si>
   <si>
     <t xml:space="preserve">2.1779637336731</t>
@@ -3884,7 +3884,7 @@
     <t xml:space="preserve">2.23281097412109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27969622612</t>
+    <t xml:space="preserve">2.27969646453857</t>
   </si>
   <si>
     <t xml:space="preserve">2.30800461769104</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">2.33631300926208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32835149765015</t>
+    <t xml:space="preserve">2.32835125923157</t>
   </si>
   <si>
     <t xml:space="preserve">2.3274667263031</t>
@@ -3926,16 +3926,16 @@
     <t xml:space="preserve">2.34338998794556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35400581359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3716983795166</t>
+    <t xml:space="preserve">2.35400557518005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37169814109802</t>
   </si>
   <si>
     <t xml:space="preserve">2.37965989112854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37612152099609</t>
+    <t xml:space="preserve">2.37612175941467</t>
   </si>
   <si>
     <t xml:space="preserve">2.4327380657196</t>
@@ -3944,13 +3944,13 @@
     <t xml:space="preserve">2.48050785064697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50350832939148</t>
+    <t xml:space="preserve">2.50350856781006</t>
   </si>
   <si>
     <t xml:space="preserve">2.44600749015808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31065893173218</t>
+    <t xml:space="preserve">2.3106586933136</t>
   </si>
   <si>
     <t xml:space="preserve">2.25669622421265</t>
@@ -3971,19 +3971,19 @@
     <t xml:space="preserve">2.25492691993713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20273327827454</t>
+    <t xml:space="preserve">2.20273351669312</t>
   </si>
   <si>
     <t xml:space="preserve">2.25227308273315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2283878326416</t>
+    <t xml:space="preserve">2.22838807106018</t>
   </si>
   <si>
     <t xml:space="preserve">2.28765821456909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28942728042603</t>
+    <t xml:space="preserve">2.2894275188446</t>
   </si>
   <si>
     <t xml:space="preserve">2.33542847633362</t>
@@ -3998,25 +3998,25 @@
     <t xml:space="preserve">2.45131516456604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42389154434204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42919945716858</t>
+    <t xml:space="preserve">2.42389130592346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42919921875</t>
   </si>
   <si>
     <t xml:space="preserve">2.40708374977112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34781312942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3885064125061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41416072845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.401775598526</t>
+    <t xml:space="preserve">2.34781336784363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38850617408752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41416049003601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40177583694458</t>
   </si>
   <si>
     <t xml:space="preserve">2.39646816253662</t>
@@ -4025,7 +4025,7 @@
     <t xml:space="preserve">2.34692859649658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.340735912323</t>
+    <t xml:space="preserve">2.34073615074158</t>
   </si>
   <si>
     <t xml:space="preserve">2.3442747592926</t>
@@ -4043,7 +4043,7 @@
     <t xml:space="preserve">2.28854274749756</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29562020301819</t>
+    <t xml:space="preserve">2.29561996459961</t>
   </si>
   <si>
     <t xml:space="preserve">2.3000431060791</t>
@@ -4055,7 +4055,7 @@
     <t xml:space="preserve">2.26642727851868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23458051681519</t>
+    <t xml:space="preserve">2.23458027839661</t>
   </si>
   <si>
     <t xml:space="preserve">2.22661876678467</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">2.22219562530518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23192644119263</t>
+    <t xml:space="preserve">2.23192667961121</t>
   </si>
   <si>
     <t xml:space="preserve">2.1753101348877</t>
@@ -4076,7 +4076,7 @@
     <t xml:space="preserve">2.22573399543762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18150234222412</t>
+    <t xml:space="preserve">2.1815025806427</t>
   </si>
   <si>
     <t xml:space="preserve">2.15054035186768</t>
@@ -4085,10 +4085,10 @@
     <t xml:space="preserve">2.1125009059906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10807800292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13727068901062</t>
+    <t xml:space="preserve">2.10807776451111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13727045059204</t>
   </si>
   <si>
     <t xml:space="preserve">2.12753963470459</t>
@@ -4103,7 +4103,7 @@
     <t xml:space="preserve">2.20627212524414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22131061553955</t>
+    <t xml:space="preserve">2.22131085395813</t>
   </si>
   <si>
     <t xml:space="preserve">2.20361804962158</t>
@@ -4154,28 +4154,28 @@
     <t xml:space="preserve">2.52297043800354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54066300392151</t>
+    <t xml:space="preserve">2.54066276550293</t>
   </si>
   <si>
     <t xml:space="preserve">2.62381839752197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65035724639893</t>
+    <t xml:space="preserve">2.6503574848175</t>
   </si>
   <si>
     <t xml:space="preserve">2.67689633369446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67866587638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63797283172607</t>
+    <t xml:space="preserve">2.67866563796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6379725933075</t>
   </si>
   <si>
     <t xml:space="preserve">2.53712439537048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61497211456299</t>
+    <t xml:space="preserve">2.61497235298157</t>
   </si>
   <si>
     <t xml:space="preserve">2.63266468048096</t>
@@ -4184,28 +4184,28 @@
     <t xml:space="preserve">2.62204885482788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54950928688049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5282781124115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57958650588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58135604858398</t>
+    <t xml:space="preserve">2.54950952529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52827835083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57958674430847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58135581016541</t>
   </si>
   <si>
     <t xml:space="preserve">2.60966444015503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58666396141052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59020233154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53889346122742</t>
+    <t xml:space="preserve">2.58666372299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59020256996155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.538893699646</t>
   </si>
   <si>
     <t xml:space="preserve">2.572509765625</t>
@@ -4214,16 +4214,16 @@
     <t xml:space="preserve">2.54420161247253</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55304765701294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56366324424744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55127882957458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53004741668701</t>
+    <t xml:space="preserve">2.55304789543152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56366348266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55127859115601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53004717826843</t>
   </si>
   <si>
     <t xml:space="preserve">2.56897139549255</t>
@@ -4232,7 +4232,7 @@
     <t xml:space="preserve">2.51812791824341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52922105789185</t>
+    <t xml:space="preserve">2.52922129631042</t>
   </si>
   <si>
     <t xml:space="preserve">2.53661632537842</t>
@@ -4259,16 +4259,16 @@
     <t xml:space="preserve">2.46451139450073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41274380683899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4090461730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42013931274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44787168502808</t>
+    <t xml:space="preserve">2.41274356842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40904593467712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42013907432556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44787192344666</t>
   </si>
   <si>
     <t xml:space="preserve">2.47375583648682</t>
@@ -4289,10 +4289,10 @@
     <t xml:space="preserve">2.52737212181091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54216313362122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53846526145935</t>
+    <t xml:space="preserve">2.54216289520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53846549987793</t>
   </si>
   <si>
     <t xml:space="preserve">2.58653521537781</t>
@@ -4301,7 +4301,7 @@
     <t xml:space="preserve">2.56250047683716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59393072128296</t>
+    <t xml:space="preserve">2.59393048286438</t>
   </si>
   <si>
     <t xml:space="preserve">2.63275647163391</t>
@@ -4316,10 +4316,10 @@
     <t xml:space="preserve">2.60132598876953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45711588859558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3998019695282</t>
+    <t xml:space="preserve">2.45711612701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39980173110962</t>
   </si>
   <si>
     <t xml:space="preserve">2.44602274894714</t>
@@ -4331,10 +4331,10 @@
     <t xml:space="preserve">2.47190690040588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47005796432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42383670806885</t>
+    <t xml:space="preserve">2.47005772590637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42383694648743</t>
   </si>
   <si>
     <t xml:space="preserve">2.38316226005554</t>
@@ -4346,34 +4346,34 @@
     <t xml:space="preserve">2.49594187736511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52182555198669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54031419754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55140733718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57913970947266</t>
+    <t xml:space="preserve">2.52182579040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5403139591217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55140709877014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57913994789124</t>
   </si>
   <si>
     <t xml:space="preserve">2.5680468082428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58468651771545</t>
+    <t xml:space="preserve">2.58468627929688</t>
   </si>
   <si>
     <t xml:space="preserve">2.57544207572937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54770946502686</t>
+    <t xml:space="preserve">2.54770970344543</t>
   </si>
   <si>
     <t xml:space="preserve">2.60687255859375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60317492485046</t>
+    <t xml:space="preserve">2.60317468643188</t>
   </si>
   <si>
     <t xml:space="preserve">2.6456983089447</t>
@@ -4397,7 +4397,7 @@
     <t xml:space="preserve">2.667884349823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69376850128174</t>
+    <t xml:space="preserve">2.69376826286316</t>
   </si>
   <si>
     <t xml:space="preserve">2.56434917449951</t>
@@ -4430,22 +4430,22 @@
     <t xml:space="preserve">2.35358071327209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39795303344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41089510917664</t>
+    <t xml:space="preserve">2.39795327186584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41089487075806</t>
   </si>
   <si>
     <t xml:space="preserve">2.42753434181213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40534830093384</t>
+    <t xml:space="preserve">2.40534853935242</t>
   </si>
   <si>
     <t xml:space="preserve">2.39240646362305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3720691204071</t>
+    <t xml:space="preserve">2.37206935882568</t>
   </si>
   <si>
     <t xml:space="preserve">2.34988307952881</t>
@@ -4460,7 +4460,7 @@
     <t xml:space="preserve">2.34803414344788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45341849327087</t>
+    <t xml:space="preserve">2.45341825485229</t>
   </si>
   <si>
     <t xml:space="preserve">2.49224424362183</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">2.49779057502747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46266269683838</t>
+    <t xml:space="preserve">2.4626624584198</t>
   </si>
   <si>
     <t xml:space="preserve">2.45526719093323</t>
@@ -4487,7 +4487,7 @@
     <t xml:space="preserve">2.62536096572876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64015197753906</t>
+    <t xml:space="preserve">2.64015173912048</t>
   </si>
   <si>
     <t xml:space="preserve">2.62720990180969</t>
@@ -4496,19 +4496,19 @@
     <t xml:space="preserve">2.63090753555298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68082666397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68637275695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68822169303894</t>
+    <t xml:space="preserve">2.68082642555237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68637299537659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68822193145752</t>
   </si>
   <si>
     <t xml:space="preserve">2.66603565216064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6826753616333</t>
+    <t xml:space="preserve">2.68267512321472</t>
   </si>
   <si>
     <t xml:space="preserve">2.68452405929565</t>
@@ -4517,19 +4517,19 @@
     <t xml:space="preserve">2.69007062911987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74368715286255</t>
+    <t xml:space="preserve">2.74368691444397</t>
   </si>
   <si>
     <t xml:space="preserve">2.71225690841675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69561696052551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73444294929504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80100154876709</t>
+    <t xml:space="preserve">2.69561719894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73444271087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80100131034851</t>
   </si>
   <si>
     <t xml:space="preserve">2.78990817070007</t>
@@ -4541,7 +4541,7 @@
     <t xml:space="preserve">2.79545474052429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78621053695679</t>
+    <t xml:space="preserve">2.78621077537537</t>
   </si>
   <si>
     <t xml:space="preserve">2.76772212982178</t>
@@ -4553,7 +4553,7 @@
     <t xml:space="preserve">2.75662922859192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73998928070068</t>
+    <t xml:space="preserve">2.73998951911926</t>
   </si>
   <si>
     <t xml:space="preserve">2.74738478660583</t>
@@ -4601,22 +4601,22 @@
     <t xml:space="preserve">2.98033928871155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96924614906311</t>
+    <t xml:space="preserve">2.96924638748169</t>
   </si>
   <si>
     <t xml:space="preserve">3.02286291122437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92672276496887</t>
+    <t xml:space="preserve">2.92672300338745</t>
   </si>
   <si>
     <t xml:space="preserve">2.91562986373901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87495517730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90083885192871</t>
+    <t xml:space="preserve">2.87495493888855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90083909034729</t>
   </si>
   <si>
     <t xml:space="preserve">2.9193274974823</t>
@@ -4643,7 +4643,7 @@
     <t xml:space="preserve">2.99513030052185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9877347946167</t>
+    <t xml:space="preserve">2.98773503303528</t>
   </si>
   <si>
     <t xml:space="preserve">2.98958349227905</t>
@@ -4652,16 +4652,16 @@
     <t xml:space="preserve">2.93411827087402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96000194549561</t>
+    <t xml:space="preserve">2.96000218391418</t>
   </si>
   <si>
     <t xml:space="preserve">2.94890904426575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95445585250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97849035263062</t>
+    <t xml:space="preserve">2.95445561408997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97849059104919</t>
   </si>
   <si>
     <t xml:space="preserve">2.95260691642761</t>
@@ -4685,10 +4685,10 @@
     <t xml:space="preserve">3.08572363853455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09496808052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11900281906128</t>
+    <t xml:space="preserve">3.09496784210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11900305747986</t>
   </si>
   <si>
     <t xml:space="preserve">3.05983972549438</t>
@@ -4706,13 +4706,13 @@
     <t xml:space="preserve">3.06908392906189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0247118473053</t>
+    <t xml:space="preserve">3.02471160888672</t>
   </si>
   <si>
     <t xml:space="preserve">3.01916527748108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97479295730591</t>
+    <t xml:space="preserve">2.97479271888733</t>
   </si>
   <si>
     <t xml:space="preserve">2.92302513122559</t>
@@ -4721,7 +4721,7 @@
     <t xml:space="preserve">2.93781590461731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88419938087463</t>
+    <t xml:space="preserve">2.88419914245605</t>
   </si>
   <si>
     <t xml:space="preserve">2.90823435783386</t>
@@ -4736,19 +4736,19 @@
     <t xml:space="preserve">2.95815324783325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97109508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01546764373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11345648765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13934016227722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10975861549377</t>
+    <t xml:space="preserve">2.97109532356262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01546740531921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11345624923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13933992385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10975885391235</t>
   </si>
   <si>
     <t xml:space="preserve">3.16337513923645</t>
@@ -4757,7 +4757,7 @@
     <t xml:space="preserve">3.13379383087158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15782856941223</t>
+    <t xml:space="preserve">3.15782833099365</t>
   </si>
   <si>
     <t xml:space="preserve">3.16892170906067</t>
@@ -4766,7 +4766,7 @@
     <t xml:space="preserve">3.19480562210083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24287533760071</t>
+    <t xml:space="preserve">3.24287557601929</t>
   </si>
   <si>
     <t xml:space="preserve">3.20959615707397</t>
@@ -4775,7 +4775,7 @@
     <t xml:space="preserve">3.20589852333069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23548030853271</t>
+    <t xml:space="preserve">3.23548007011414</t>
   </si>
   <si>
     <t xml:space="preserve">3.29464316368103</t>
@@ -4790,10 +4790,10 @@
     <t xml:space="preserve">3.20774745941162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17446827888489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12085151672363</t>
+    <t xml:space="preserve">3.17446804046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12085175514221</t>
   </si>
   <si>
     <t xml:space="preserve">3.07832813262939</t>
@@ -4805,7 +4805,7 @@
     <t xml:space="preserve">3.09866547584534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07647943496704</t>
+    <t xml:space="preserve">3.07647967338562</t>
   </si>
   <si>
     <t xml:space="preserve">3.06723523139954</t>
@@ -4820,19 +4820,19 @@
     <t xml:space="preserve">3.19665431976318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20405006408691</t>
+    <t xml:space="preserve">3.20404982566833</t>
   </si>
   <si>
     <t xml:space="preserve">3.19850325584412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12454962730408</t>
+    <t xml:space="preserve">3.1245493888855</t>
   </si>
   <si>
     <t xml:space="preserve">3.16707301139832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14858436584473</t>
+    <t xml:space="preserve">3.14858412742615</t>
   </si>
   <si>
     <t xml:space="preserve">3.00067663192749</t>
@@ -4841,7 +4841,7 @@
     <t xml:space="preserve">3.04874682426453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10051441192627</t>
+    <t xml:space="preserve">3.10051465034485</t>
   </si>
   <si>
     <t xml:space="preserve">3.14488673210144</t>
@@ -10415,7 +10415,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G166" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -10467,7 +10467,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G168" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -10519,7 +10519,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G170" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -10545,7 +10545,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G171" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -10597,7 +10597,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G173" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -10623,7 +10623,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G174" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -10649,7 +10649,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G175" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -10675,7 +10675,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G176" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -10753,7 +10753,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G179" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -10779,7 +10779,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G180" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -10831,7 +10831,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G182" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -10857,7 +10857,7 @@
         <v>2.35599994659424</v>
       </c>
       <c r="G183" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -10883,7 +10883,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G184" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -10909,7 +10909,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G185" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -10935,7 +10935,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G186" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -10961,7 +10961,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G187" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -10987,7 +10987,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G188" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -11013,7 +11013,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G189" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -11039,7 +11039,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G190" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -11065,7 +11065,7 @@
         <v>2.33599996566772</v>
       </c>
       <c r="G191" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -11091,7 +11091,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G192" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -11117,7 +11117,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G193" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -11143,7 +11143,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G194" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -11169,7 +11169,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G195" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -11195,7 +11195,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G196" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -11221,7 +11221,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G197" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -11247,7 +11247,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G198" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -11273,7 +11273,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G199" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -11299,7 +11299,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G200" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -11325,7 +11325,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G201" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -11351,7 +11351,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G202" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -11377,7 +11377,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G203" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -11403,7 +11403,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G204" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -11429,7 +11429,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G205" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -11455,7 +11455,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G206" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -11481,7 +11481,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G207" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -11507,7 +11507,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G208" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -11533,7 +11533,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G209" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -11559,7 +11559,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G210" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -11585,7 +11585,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G211" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -11611,7 +11611,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G212" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -11637,7 +11637,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G213" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -11663,7 +11663,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G214" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -11715,7 +11715,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G216" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -11741,7 +11741,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G217" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -11767,7 +11767,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G218" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -11793,7 +11793,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G219" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -11819,7 +11819,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G220" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -11845,7 +11845,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G221" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -11871,7 +11871,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G222" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -11897,7 +11897,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G223" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -11923,7 +11923,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G224" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -11949,7 +11949,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G225" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -11975,7 +11975,7 @@
         <v>2.00200009346008</v>
       </c>
       <c r="G226" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -12001,7 +12001,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G227" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -12027,7 +12027,7 @@
         <v>1.96300005912781</v>
       </c>
       <c r="G228" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -12053,7 +12053,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G229" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -12079,7 +12079,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G230" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -12105,7 +12105,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G231" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -12131,7 +12131,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G232" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -12157,7 +12157,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G233" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -12183,7 +12183,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G234" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -12209,7 +12209,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G235" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -12235,7 +12235,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G236" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -12261,7 +12261,7 @@
         <v>1.90699994564056</v>
       </c>
       <c r="G237" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -12287,7 +12287,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G238" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -12313,7 +12313,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G239" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -12339,7 +12339,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G240" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -12365,7 +12365,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G241" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -12391,7 +12391,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G242" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -12417,7 +12417,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G243" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -12443,7 +12443,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G244" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -12469,7 +12469,7 @@
         <v>2.1159999370575</v>
       </c>
       <c r="G245" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -12495,7 +12495,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G246" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -12521,7 +12521,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G247" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -12547,7 +12547,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G248" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -12573,7 +12573,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G249" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -12599,7 +12599,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G250" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -12625,7 +12625,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G251" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -12651,7 +12651,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G252" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -12677,7 +12677,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G253" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -12703,7 +12703,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G254" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -12729,7 +12729,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G255" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -12755,7 +12755,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G256" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -12781,7 +12781,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G257" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -12807,7 +12807,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G258" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -12833,7 +12833,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G259" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -12859,7 +12859,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G260" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -12885,7 +12885,7 @@
         <v>2.20799994468689</v>
       </c>
       <c r="G261" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -12911,7 +12911,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G262" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -12937,7 +12937,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G263" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -12963,7 +12963,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G264" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -12989,7 +12989,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G265" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -13015,7 +13015,7 @@
         <v>2.30399990081787</v>
       </c>
       <c r="G266" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -13041,7 +13041,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G267" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -13067,7 +13067,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G268" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -13093,7 +13093,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G269" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -13119,7 +13119,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G270" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -13145,7 +13145,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G271" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -13171,7 +13171,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G272" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -13197,7 +13197,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G273" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -13223,7 +13223,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G274" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -13249,7 +13249,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G275" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -13275,7 +13275,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G276" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -13301,7 +13301,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G277" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -13327,7 +13327,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G278" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -13353,7 +13353,7 @@
         <v>2.15799999237061</v>
       </c>
       <c r="G279" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -13379,7 +13379,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G280" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -13405,7 +13405,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G281" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -13431,7 +13431,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G282" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -13457,7 +13457,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G283" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -13483,7 +13483,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G284" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -13509,7 +13509,7 @@
         <v>2.25</v>
       </c>
       <c r="G285" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -13535,7 +13535,7 @@
         <v>2.25</v>
       </c>
       <c r="G286" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -13561,7 +13561,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G287" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -13587,7 +13587,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G288" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -13613,7 +13613,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G289" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -13639,7 +13639,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G290" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -13665,7 +13665,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G291" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -13691,7 +13691,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G292" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -13717,7 +13717,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G293" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -13743,7 +13743,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G294" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -13769,7 +13769,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G295" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -13795,7 +13795,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G296" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -13821,7 +13821,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G297" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -13847,7 +13847,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G298" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -13873,7 +13873,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G299" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -13925,7 +13925,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G301" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -13951,7 +13951,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G302" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -13977,7 +13977,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G303" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -14003,7 +14003,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G304" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -14029,7 +14029,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G305" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -14055,7 +14055,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G306" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -14081,7 +14081,7 @@
         <v>2.36800003051758</v>
       </c>
       <c r="G307" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -14107,7 +14107,7 @@
         <v>2.37199997901917</v>
       </c>
       <c r="G308" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -14133,7 +14133,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G309" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -14159,7 +14159,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G310" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -14185,7 +14185,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G311" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -14211,7 +14211,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G312" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -14237,7 +14237,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G313" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -14263,7 +14263,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G314" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -14289,7 +14289,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G315" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -14315,7 +14315,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G316" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -14341,7 +14341,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G317" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -14367,7 +14367,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G318" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -14393,7 +14393,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G319" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -14419,7 +14419,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G320" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -14445,7 +14445,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G321" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -14471,7 +14471,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G322" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -14497,7 +14497,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G323" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -14523,7 +14523,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G324" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -14549,7 +14549,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G325" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -14575,7 +14575,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G326" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -14601,7 +14601,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G327" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -14627,7 +14627,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G328" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -14653,7 +14653,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G329" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -14679,7 +14679,7 @@
         <v>2.67400002479553</v>
       </c>
       <c r="G330" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -14705,7 +14705,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G331" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -14731,7 +14731,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G332" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -14757,7 +14757,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G333" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -14783,7 +14783,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G334" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -14809,7 +14809,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G335" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -14835,7 +14835,7 @@
         <v>2.66199994087219</v>
       </c>
       <c r="G336" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -14861,7 +14861,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G337" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -14887,7 +14887,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G338" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -14913,7 +14913,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G339" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -14939,7 +14939,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G340" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -14965,7 +14965,7 @@
         <v>2.64599990844727</v>
       </c>
       <c r="G341" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -14991,7 +14991,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G342" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -15017,7 +15017,7 @@
         <v>2.67199993133545</v>
       </c>
       <c r="G343" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -15043,7 +15043,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G344" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -15069,7 +15069,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G345" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -15095,7 +15095,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G346" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -15121,7 +15121,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G347" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -15147,7 +15147,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G348" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -15173,7 +15173,7 @@
         <v>2.85599994659424</v>
       </c>
       <c r="G349" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -15199,7 +15199,7 @@
         <v>2.83200001716614</v>
       </c>
       <c r="G350" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -15225,7 +15225,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G351" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -15251,7 +15251,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G352" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -15277,7 +15277,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G353" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -15303,7 +15303,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G354" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -15329,7 +15329,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G355" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -15355,7 +15355,7 @@
         <v>2.93799996376038</v>
       </c>
       <c r="G356" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -15381,7 +15381,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G357" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -15407,7 +15407,7 @@
         <v>2.91400003433228</v>
       </c>
       <c r="G358" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -15433,7 +15433,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G359" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -15459,7 +15459,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G360" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -15485,7 +15485,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G361" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -15511,7 +15511,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G362" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -15537,7 +15537,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G363" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -15563,7 +15563,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G364" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -15589,7 +15589,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G365" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -15615,7 +15615,7 @@
         <v>2.90400004386902</v>
       </c>
       <c r="G366" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -15641,7 +15641,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G367" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -15667,7 +15667,7 @@
         <v>2.92600011825562</v>
       </c>
       <c r="G368" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -15693,7 +15693,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G369" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -15719,7 +15719,7 @@
         <v>2.96399998664856</v>
       </c>
       <c r="G370" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -15745,7 +15745,7 @@
         <v>2.94400000572205</v>
       </c>
       <c r="G371" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -15771,7 +15771,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="G372" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -15797,7 +15797,7 @@
         <v>2.95799994468689</v>
       </c>
       <c r="G373" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -15823,7 +15823,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G374" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -15849,7 +15849,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G375" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -15875,7 +15875,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G376" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -15901,7 +15901,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G377" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -15927,7 +15927,7 @@
         <v>2.88599991798401</v>
       </c>
       <c r="G378" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -18683,7 +18683,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G484" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -18735,7 +18735,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G486" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -72719,7 +72719,7 @@
     </row>
     <row r="2563">
       <c r="A2563" s="1" t="n">
-        <v>46055.691099537</v>
+        <v>46055.3333333333</v>
       </c>
       <c r="B2563" t="n">
         <v>4469896</v>
@@ -72740,6 +72740,32 @@
         <v>1918</v>
       </c>
       <c r="H2563" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2564">
+      <c r="A2564" s="1" t="n">
+        <v>46056.6911458333</v>
+      </c>
+      <c r="B2564" t="n">
+        <v>3392503</v>
+      </c>
+      <c r="C2564" t="n">
+        <v>4.21199989318848</v>
+      </c>
+      <c r="D2564" t="n">
+        <v>4.13399982452393</v>
+      </c>
+      <c r="E2564" t="n">
+        <v>4.17999982833862</v>
+      </c>
+      <c r="F2564" t="n">
+        <v>4.21199989318848</v>
+      </c>
+      <c r="G2564" t="s">
+        <v>1911</v>
+      </c>
+      <c r="H2564" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/HER.MI.xlsx
+++ b/data/HER.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1919" uniqueCount="1919">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1920" uniqueCount="1920">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,76 +44,76 @@
     <t xml:space="preserve">HER.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7089638710022</t>
+    <t xml:space="preserve">1.70896399021149</t>
   </si>
   <si>
     <t xml:space="preserve">1.70616912841797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71036124229431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68800354003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7257319688797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79140746593475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79420244693756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77044725418091</t>
+    <t xml:space="preserve">1.71036100387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68800342082977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72573232650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79140770435333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79420268535614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77044749259949</t>
   </si>
   <si>
     <t xml:space="preserve">1.74669241905212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70337450504303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77324187755585</t>
+    <t xml:space="preserve">1.70337426662445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77324211597443</t>
   </si>
   <si>
     <t xml:space="preserve">1.74948704242706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76625573635101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80538153648376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79001045227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80398404598236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83472514152527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81656002998352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80258643627167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84869909286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85568583011627</t>
+    <t xml:space="preserve">1.76625537872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80538129806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79001033306122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80398368835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83472573757172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81655979156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80258631706238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8486989736557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85568594932556</t>
   </si>
   <si>
     <t xml:space="preserve">1.84031498432159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82354664802551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82913625240326</t>
+    <t xml:space="preserve">1.82354652881622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82913601398468</t>
   </si>
   <si>
     <t xml:space="preserve">1.72852659225464</t>
@@ -122,124 +122,124 @@
     <t xml:space="preserve">1.74110305309296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75926840305328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69918203353882</t>
+    <t xml:space="preserve">1.7592681646347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69918239116669</t>
   </si>
   <si>
     <t xml:space="preserve">1.75507640838623</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79559981822968</t>
+    <t xml:space="preserve">1.79559969902039</t>
   </si>
   <si>
     <t xml:space="preserve">1.78302323818207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77603673934937</t>
+    <t xml:space="preserve">1.77603662014008</t>
   </si>
   <si>
     <t xml:space="preserve">1.79839444160461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80118918418884</t>
+    <t xml:space="preserve">1.80118942260742</t>
   </si>
   <si>
     <t xml:space="preserve">1.82075202465057</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83053374290466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78861260414124</t>
+    <t xml:space="preserve">1.83053362369537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78861284255981</t>
   </si>
   <si>
     <t xml:space="preserve">1.76485788822174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74529492855072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73970532417297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72992444038391</t>
+    <t xml:space="preserve">1.74529504776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73970544338226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72992408275604</t>
   </si>
   <si>
     <t xml:space="preserve">1.7438976764679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73271894454956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76346063613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77883148193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76066565513611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77463924884796</t>
+    <t xml:space="preserve">1.73271906375885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76346051692963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7788313627243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76066613197327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77463948726654</t>
   </si>
   <si>
     <t xml:space="preserve">1.79699695110321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83752024173737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81097078323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85708320140839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84310984611511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76765275001526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78162634372711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78721582889557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77743411064148</t>
+    <t xml:space="preserve">1.83752059936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81097042560577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85708355903625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84310960769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76765286922455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78162610530853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78721570968628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77743399143219</t>
   </si>
   <si>
     <t xml:space="preserve">1.780228972435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80817592144012</t>
+    <t xml:space="preserve">1.8081761598587</t>
   </si>
   <si>
     <t xml:space="preserve">1.80957305431366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79280495643616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78442096710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75647366046906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74809002876282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82634174823761</t>
+    <t xml:space="preserve">1.79280471801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78442108631134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75647401809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74808979034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82634139060974</t>
   </si>
   <si>
     <t xml:space="preserve">1.84590458869934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83193099498749</t>
+    <t xml:space="preserve">1.8319308757782</t>
   </si>
   <si>
     <t xml:space="preserve">1.84450733661652</t>
@@ -248,13 +248,13 @@
     <t xml:space="preserve">1.82214951515198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83332812786102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82494401931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81376528739929</t>
+    <t xml:space="preserve">1.8333283662796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82494425773621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81376516819</t>
   </si>
   <si>
     <t xml:space="preserve">1.76206338405609</t>
@@ -263,184 +263,184 @@
     <t xml:space="preserve">1.73132133483887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74250030517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71175873279572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75751042366028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77344822883606</t>
+    <t xml:space="preserve">1.74250018596649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71175849437714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75751054286957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77344810962677</t>
   </si>
   <si>
     <t xml:space="preserve">1.74012386798859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75895941257477</t>
+    <t xml:space="preserve">1.75895929336548</t>
   </si>
   <si>
     <t xml:space="preserve">1.70390117168427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6734744310379</t>
+    <t xml:space="preserve">1.67347431182861</t>
   </si>
   <si>
     <t xml:space="preserve">1.70969676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73867464065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78069281578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83430182933807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80822169780731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81111943721771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78503942489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77924382686615</t>
+    <t xml:space="preserve">1.73867475986481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78069257736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83430194854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8082218170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81111967563629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78503906726837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77924394607544</t>
   </si>
   <si>
     <t xml:space="preserve">1.72708380222321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76040840148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74591934680939</t>
+    <t xml:space="preserve">1.76040804386139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74591898918152</t>
   </si>
   <si>
     <t xml:space="preserve">1.77055037021637</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76620388031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76185691356659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76910161972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77489733695984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78359055519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83719956874847</t>
+    <t xml:space="preserve">1.76620352268219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76185703277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76910150051117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77489697933197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78359031677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83719968795776</t>
   </si>
   <si>
     <t xml:space="preserve">1.85748410224915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85023975372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83575069904327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86617767810822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83140444755554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84444415569305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79663074016571</t>
+    <t xml:space="preserve">1.85023963451385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83575081825256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86617708206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83140420913696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84444403648376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.796630859375</t>
   </si>
   <si>
     <t xml:space="preserve">1.81981289386749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81256866455078</t>
+    <t xml:space="preserve">1.8125684261322</t>
   </si>
   <si>
     <t xml:space="preserve">1.74881708621979</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74447000026703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76765251159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77634584903717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79083502292633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79952847957611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78648841381073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78938603401184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8154661655426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75606143474579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73577678203583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70679926872253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73722589015961</t>
+    <t xml:space="preserve">1.74447047710419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76765239238739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77634620666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79083490371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79952824115753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78648865222931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78938639163971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81546628475189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7560613155365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73577654361725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70679879188538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7372260093689</t>
   </si>
   <si>
     <t xml:space="preserve">1.75461268424988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71114563941956</t>
+    <t xml:space="preserve">1.71114575862885</t>
   </si>
   <si>
     <t xml:space="preserve">1.70824801921844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70245218276978</t>
+    <t xml:space="preserve">1.70245230197906</t>
   </si>
   <si>
     <t xml:space="preserve">1.69230997562408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71694099903107</t>
+    <t xml:space="preserve">1.71694111824036</t>
   </si>
   <si>
     <t xml:space="preserve">1.69665670394897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63145673274994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60537648200989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59233617782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57929623126984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.601029753685</t>
+    <t xml:space="preserve">1.63145649433136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6053763628006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59233605861664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57929635047913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60102963447571</t>
   </si>
   <si>
     <t xml:space="preserve">1.6097229719162</t>
@@ -449,16 +449,16 @@
     <t xml:space="preserve">1.61406970024109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62131404876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63290500640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6184161901474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63870084285736</t>
+    <t xml:space="preserve">1.62131416797638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63290512561798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61841630935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63870096206665</t>
   </si>
   <si>
     <t xml:space="preserve">1.63725197315216</t>
@@ -467,22 +467,22 @@
     <t xml:space="preserve">1.65029215812683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62276303768158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61551856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61696755886078</t>
+    <t xml:space="preserve">1.62276315689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61551868915558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61696743965149</t>
   </si>
   <si>
     <t xml:space="preserve">1.62566089630127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66188323497772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66912746429443</t>
+    <t xml:space="preserve">1.66188335418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66912758350372</t>
   </si>
   <si>
     <t xml:space="preserve">1.68796348571777</t>
@@ -491,10 +491,10 @@
     <t xml:space="preserve">1.59378528594971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56625604629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56335830688477</t>
+    <t xml:space="preserve">1.56625592708588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56335842609406</t>
   </si>
   <si>
     <t xml:space="preserve">1.54307389259338</t>
@@ -503,13 +503,13 @@
     <t xml:space="preserve">1.46048676967621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46338450908661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44599771499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44527339935303</t>
+    <t xml:space="preserve">1.4633846282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44599795341492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44527328014374</t>
   </si>
   <si>
     <t xml:space="preserve">1.45034456253052</t>
@@ -518,79 +518,79 @@
     <t xml:space="preserve">1.43005990982056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42209100723267</t>
+    <t xml:space="preserve">1.42209112644196</t>
   </si>
   <si>
     <t xml:space="preserve">1.3960108757019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3945620059967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40905106067657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41267311573029</t>
+    <t xml:space="preserve">1.39456188678741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40905094146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41267323493958</t>
   </si>
   <si>
     <t xml:space="preserve">1.39818429946899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40180623531342</t>
+    <t xml:space="preserve">1.40180647373199</t>
   </si>
   <si>
     <t xml:space="preserve">1.40542888641357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41629552841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38152205944061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35906434059143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37717521190643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43875336647034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48077142238617</t>
+    <t xml:space="preserve">1.41629564762115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38152194023132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35906410217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37717533111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43875324726105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48077118396759</t>
   </si>
   <si>
     <t xml:space="preserve">1.49236249923706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48511791229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53293144702911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52713596820831</t>
+    <t xml:space="preserve">1.48511803150177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5329315662384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52713620662689</t>
   </si>
   <si>
     <t xml:space="preserve">1.50105583667755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50685143470764</t>
+    <t xml:space="preserve">1.50685131549835</t>
   </si>
   <si>
     <t xml:space="preserve">1.54886949062347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55756306648254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57060253620148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59088730812073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56915390491486</t>
+    <t xml:space="preserve">1.55756270885468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57060277462006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59088718891144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56915402412415</t>
   </si>
   <si>
     <t xml:space="preserve">1.58798944950104</t>
@@ -599,19 +599,19 @@
     <t xml:space="preserve">1.608274102211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59668290615082</t>
+    <t xml:space="preserve">1.59668266773224</t>
   </si>
   <si>
     <t xml:space="preserve">1.59958076477051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56480741500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65174090862274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64159905910492</t>
+    <t xml:space="preserve">1.56480753421783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65174126625061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64159882068634</t>
   </si>
   <si>
     <t xml:space="preserve">1.65318977832794</t>
@@ -620,67 +620,67 @@
     <t xml:space="preserve">1.65463864803314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65898537635803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64014983177185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64304769039154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57494962215424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57784736156464</t>
+    <t xml:space="preserve">1.65898549556732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64014971256256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64304733276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57494974136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57784748077393</t>
   </si>
   <si>
     <t xml:space="preserve">1.55176711082458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58654057979584</t>
+    <t xml:space="preserve">1.58654069900513</t>
   </si>
   <si>
     <t xml:space="preserve">1.63000750541687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68216800689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66622972488403</t>
+    <t xml:space="preserve">1.68216776847839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66622996330261</t>
   </si>
   <si>
     <t xml:space="preserve">1.6778210401535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69086146354675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69375920295715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69810569286346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69520771503448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71404349803925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72998118400574</t>
+    <t xml:space="preserve">1.69086134433746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69375908374786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69810593128204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69520783424377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71404361724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72998142242432</t>
   </si>
   <si>
     <t xml:space="preserve">1.7343282699585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71983897686005</t>
+    <t xml:space="preserve">1.71983885765076</t>
   </si>
   <si>
     <t xml:space="preserve">1.72418594360352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71549248695374</t>
+    <t xml:space="preserve">1.71549236774445</t>
   </si>
   <si>
     <t xml:space="preserve">1.71839022636414</t>
@@ -689,10 +689,10 @@
     <t xml:space="preserve">1.74157238006592</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78214144706726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78793728351593</t>
+    <t xml:space="preserve">1.78214168548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78793692588806</t>
   </si>
   <si>
     <t xml:space="preserve">1.8140172958374</t>
@@ -704,76 +704,76 @@
     <t xml:space="preserve">1.86907517910004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89950227737427</t>
+    <t xml:space="preserve">1.89950251579285</t>
   </si>
   <si>
     <t xml:space="preserve">1.91399121284485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91544008255005</t>
+    <t xml:space="preserve">1.91543996334076</t>
   </si>
   <si>
     <t xml:space="preserve">1.88066649436951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8719733953476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88935995101929</t>
+    <t xml:space="preserve">1.87197327613831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88936018943787</t>
   </si>
   <si>
     <t xml:space="preserve">1.90095090866089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90529763698578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91254246234894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94441795349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93717360496521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87921786308289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8835643529892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92848014831543</t>
+    <t xml:space="preserve">1.90529775619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91254234313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94441783428192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93717348575592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87921762466431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88356423377991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92847979068756</t>
   </si>
   <si>
     <t xml:space="preserve">1.89805340766907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88791084289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90239953994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91688871383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92413318157196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93572449684143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93862223625183</t>
+    <t xml:space="preserve">1.88791108131409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90240001678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91688883304596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92413341999054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93572473526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93862247467041</t>
   </si>
   <si>
     <t xml:space="preserve">1.9487646818161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99512934684753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02845406532288</t>
+    <t xml:space="preserve">1.99512922763824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02845358848572</t>
   </si>
   <si>
     <t xml:space="preserve">2.05743169784546</t>
@@ -788,34 +788,34 @@
     <t xml:space="preserve">2.10234761238098</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06467604637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0385959148407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07336950302124</t>
+    <t xml:space="preserve">2.06467652320862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03859639167786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0733699798584</t>
   </si>
   <si>
     <t xml:space="preserve">2.0864098072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12842774391174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11248970031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11104130744934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10089874267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05453419685364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08930730819702</t>
+    <t xml:space="preserve">2.12842750549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11248993873596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11104083061218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1008985042572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05453372001648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08930778503418</t>
   </si>
   <si>
     <t xml:space="preserve">2.12263202667236</t>
@@ -824,43 +824,43 @@
     <t xml:space="preserve">2.07916498184204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10379648208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11973452568054</t>
+    <t xml:space="preserve">2.1037962436676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11973428726196</t>
   </si>
   <si>
     <t xml:space="preserve">2.10814309120178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1472635269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13277435302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15450763702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14291644096375</t>
+    <t xml:space="preserve">2.14726328849792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13277411460876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15450811386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14291620254517</t>
   </si>
   <si>
     <t xml:space="preserve">2.15595674514771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1679093837738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17836785316467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17239165306091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09918165206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11262845993042</t>
+    <t xml:space="preserve">2.16790962219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17836809158325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17239141464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09918189048767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.112628698349</t>
   </si>
   <si>
     <t xml:space="preserve">2.07228827476501</t>
@@ -872,7 +872,7 @@
     <t xml:space="preserve">2.01700758934021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99907827377319</t>
+    <t xml:space="preserve">1.99907863140106</t>
   </si>
   <si>
     <t xml:space="preserve">2.01103091239929</t>
@@ -881,10 +881,10 @@
     <t xml:space="preserve">2.00804281234741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99758446216583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9512677192688</t>
+    <t xml:space="preserve">1.99758422374725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95126783847809</t>
   </si>
   <si>
     <t xml:space="preserve">1.97069096565247</t>
@@ -902,7 +902,7 @@
     <t xml:space="preserve">2.05286526679993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0394184589386</t>
+    <t xml:space="preserve">2.03941822052002</t>
   </si>
   <si>
     <t xml:space="preserve">2.03194832801819</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">2.04539465904236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02447772026062</t>
+    <t xml:space="preserve">2.0244779586792</t>
   </si>
   <si>
     <t xml:space="preserve">2.06182980537415</t>
@@ -923,13 +923,13 @@
     <t xml:space="preserve">2.03344225883484</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01401901245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05435919761658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04390096664429</t>
+    <t xml:space="preserve">2.01401948928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05435943603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04390072822571</t>
   </si>
   <si>
     <t xml:space="preserve">2.04240655899048</t>
@@ -938,28 +938,28 @@
     <t xml:space="preserve">2.03643035888672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04838299751282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04987692832947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00206613540649</t>
+    <t xml:space="preserve">2.0483832359314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04987716674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00206637382507</t>
   </si>
   <si>
     <t xml:space="preserve">2.05585336685181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03493595123291</t>
+    <t xml:space="preserve">2.03493618965149</t>
   </si>
   <si>
     <t xml:space="preserve">1.99459624290466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97517323493958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96172595024109</t>
+    <t xml:space="preserve">1.97517311573029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96172630786896</t>
   </si>
   <si>
     <t xml:space="preserve">1.96770262718201</t>
@@ -968,106 +968,106 @@
     <t xml:space="preserve">2.02597188949585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01252508163452</t>
+    <t xml:space="preserve">2.0125253200531</t>
   </si>
   <si>
     <t xml:space="preserve">2.00953698158264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0035605430603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07826495170593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01850128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00057244300842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98563158512115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98712587356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97218525409698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02148985862732</t>
+    <t xml:space="preserve">2.00356030464172</t>
+  </si>
+  <si>
+    <t xml:space="pres